--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4296" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4314" uniqueCount="918">
   <si>
     <t>ID</t>
   </si>
@@ -1506,1186 +1506,1204 @@
     <t>ID39835414951284</t>
   </si>
   <si>
+    <t>1141205K</t>
+  </si>
+  <si>
+    <t>ID39835414951285</t>
+  </si>
+  <si>
+    <t>PRTDL-YK  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951286</t>
+  </si>
+  <si>
+    <t>PRTDL-SS  (牛肉)</t>
+  </si>
+  <si>
+    <t>SS25#88</t>
+  </si>
+  <si>
+    <t>異常 五月即期</t>
+  </si>
+  <si>
+    <t>ID39835414951287</t>
+  </si>
+  <si>
+    <t>JUJM (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951288</t>
+  </si>
+  <si>
+    <t>BFMC (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951289</t>
+  </si>
+  <si>
+    <t>ID39835414951290</t>
+  </si>
+  <si>
+    <t>TUE-ST  (牛肉)</t>
+  </si>
+  <si>
+    <t>24#7 24#6</t>
+  </si>
+  <si>
+    <t>ID39835414951291</t>
+  </si>
+  <si>
+    <t>ID39835414951292</t>
+  </si>
+  <si>
+    <t>ID39835414951293</t>
+  </si>
+  <si>
+    <t>CESA (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951294</t>
+  </si>
+  <si>
+    <t>ADC (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951295</t>
+  </si>
+  <si>
+    <t>ADK (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951296</t>
+  </si>
+  <si>
+    <t>ID39835414951297</t>
+  </si>
+  <si>
+    <t>ID39835414951298</t>
+  </si>
+  <si>
+    <t>JOT (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951299</t>
+  </si>
+  <si>
+    <t>JUP  (豬肉)</t>
+  </si>
+  <si>
+    <t>24#3</t>
+  </si>
+  <si>
+    <t>ID39835414951301</t>
+  </si>
+  <si>
+    <t>ID39835414951302</t>
+  </si>
+  <si>
+    <t>GF-CKM-TY  (牛肉)</t>
+  </si>
+  <si>
+    <t>26#2</t>
+  </si>
+  <si>
+    <t>ID39835414951303</t>
+  </si>
+  <si>
+    <t>DCC (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951304</t>
+  </si>
+  <si>
+    <t>ID39835414951305</t>
+  </si>
+  <si>
+    <t>PS-PRSTL （切） (牛肉)</t>
+  </si>
+  <si>
+    <t>1140909S</t>
+  </si>
+  <si>
+    <t>ID39835414951307</t>
+  </si>
+  <si>
+    <t>SPT (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951308</t>
+  </si>
+  <si>
+    <t>ADJM (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951309</t>
+  </si>
+  <si>
+    <t>JOP (豬肉)</t>
+  </si>
+  <si>
+    <t>25#4</t>
+  </si>
+  <si>
+    <t>2027-06-17T16:00:00.000Z</t>
+  </si>
+  <si>
+    <t>ID39835414951310</t>
+  </si>
+  <si>
+    <t>25#2  25#4</t>
+  </si>
+  <si>
+    <t>ID39835414951311</t>
+  </si>
+  <si>
+    <t>ACOB-TY  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951312</t>
+  </si>
+  <si>
+    <t>M5-TDL-ST  (牛肉)</t>
+  </si>
+  <si>
+    <t>24#5 24#6</t>
+  </si>
+  <si>
+    <t>ID39835414951313</t>
+  </si>
+  <si>
+    <t>ID39835414951314</t>
+  </si>
+  <si>
+    <t>RF-YK  (牛肉)</t>
+  </si>
+  <si>
+    <t>25#45</t>
+  </si>
+  <si>
+    <t>ID39835414951315</t>
+  </si>
+  <si>
+    <t>ADR8 (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951316</t>
+  </si>
+  <si>
+    <t>60PS (煙燻鴨胸)</t>
+  </si>
+  <si>
+    <t>ID39835414951317</t>
+  </si>
+  <si>
+    <t>OLR22 (羊肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951318</t>
+  </si>
+  <si>
+    <t>SPB2 (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951319</t>
+  </si>
+  <si>
+    <t>LR22 (羊肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951320</t>
+  </si>
+  <si>
+    <t>TS300 (三角煙燻腿)</t>
+  </si>
+  <si>
+    <t>ID39835414951322</t>
+  </si>
+  <si>
+    <t>SL (煙燻鴨腿)</t>
+  </si>
+  <si>
+    <t>ID39835414951323</t>
+  </si>
+  <si>
+    <t>TS (三角煙燻鴨胸)</t>
+  </si>
+  <si>
+    <t>ID39835414951325</t>
+  </si>
+  <si>
+    <t>12S (煙燻鴨胸)</t>
+  </si>
+  <si>
+    <t>ID39835414951326</t>
+  </si>
+  <si>
+    <t>BOSS物品</t>
+  </si>
+  <si>
+    <t>ID39835414951327</t>
+  </si>
+  <si>
+    <t>IST  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951328</t>
+  </si>
+  <si>
+    <t>ID39835414951329</t>
+  </si>
+  <si>
+    <t>ID39835414951330</t>
+  </si>
+  <si>
+    <t>ID39835414951331</t>
+  </si>
+  <si>
+    <t>SPL (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951332</t>
+  </si>
+  <si>
+    <t>1150205K</t>
+  </si>
+  <si>
+    <t>ID39835414951333</t>
+  </si>
+  <si>
+    <t>ADB2 (豬肉)</t>
+  </si>
+  <si>
+    <t>1141224K</t>
+  </si>
+  <si>
+    <t>ID39835414951334</t>
+  </si>
+  <si>
+    <t>ID39835414951335</t>
+  </si>
+  <si>
+    <t>ADL(豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951340</t>
+  </si>
+  <si>
+    <t>M45OB-MU  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951341</t>
+  </si>
+  <si>
+    <t>3/18 G9進貨</t>
+  </si>
+  <si>
+    <t>ID39835414951342</t>
+  </si>
+  <si>
+    <t>ID39835414951343</t>
+  </si>
+  <si>
+    <t>JOC2 (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951344</t>
+  </si>
+  <si>
+    <t>ID39835414951345</t>
+  </si>
+  <si>
+    <t>M67OB  (牛肉)</t>
+  </si>
+  <si>
+    <t>24#2</t>
+  </si>
+  <si>
+    <t>ID39835414951346</t>
+  </si>
+  <si>
+    <t>2026-11-21T16:00:00.000Z</t>
+  </si>
+  <si>
+    <t>ID39835414951347</t>
+  </si>
+  <si>
+    <t>ACRPC-TY  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951348</t>
+  </si>
+  <si>
+    <t>ID39835414951349</t>
+  </si>
+  <si>
+    <t>ID39835414951350</t>
+  </si>
+  <si>
+    <t>A5-TDL  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951351</t>
+  </si>
+  <si>
+    <t>A5-GB  (牛肉)</t>
+  </si>
+  <si>
+    <t>1150212K</t>
+  </si>
+  <si>
+    <t>ID39835414951353</t>
+  </si>
+  <si>
+    <t>M89BBLD-KR  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951354</t>
+  </si>
+  <si>
+    <t>1150120K</t>
+  </si>
+  <si>
+    <t>ID39835414951355</t>
+  </si>
+  <si>
+    <t>ID39835414951356</t>
+  </si>
+  <si>
+    <t>ID39835414951357</t>
+  </si>
+  <si>
+    <t>PRSRL-YK  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951358</t>
+  </si>
+  <si>
+    <t>1141230K</t>
+  </si>
+  <si>
+    <t>ID39835414951359</t>
+  </si>
+  <si>
+    <t>SRL  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951360</t>
+  </si>
+  <si>
+    <t>ID39835414951361</t>
+  </si>
+  <si>
+    <t>ID39835414951362</t>
+  </si>
+  <si>
+    <t>1150309K</t>
+  </si>
+  <si>
+    <t>ID39835414951364</t>
+  </si>
+  <si>
+    <t>M67RER-280-320-KR  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951365</t>
+  </si>
+  <si>
+    <t>M89RER-280-320-KR  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951366</t>
+  </si>
+  <si>
+    <t>M89SRL-280/320  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>TY25#13</t>
+  </si>
+  <si>
+    <t>ID39835414951367</t>
+  </si>
+  <si>
+    <t>M45SRL 280-320  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951368</t>
+  </si>
+  <si>
+    <t>PRRER 900-960  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951369</t>
+  </si>
+  <si>
+    <t>PRRER 1開3  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951370</t>
+  </si>
+  <si>
+    <t>PRRER 3CM  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951371</t>
+  </si>
+  <si>
+    <t>GMB ( (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951372</t>
+  </si>
+  <si>
+    <t>GMB (骨)(牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951373</t>
+  </si>
+  <si>
+    <t>GMB  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951374</t>
+  </si>
+  <si>
+    <t>PRRER400-450-YK  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951375</t>
+  </si>
+  <si>
+    <t>PRRER 185-225-GO  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951376</t>
+  </si>
+  <si>
+    <t>PRSTL 5CM-TA  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951377</t>
+  </si>
+  <si>
+    <t>PRRER 325-365-YK  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>1150113S</t>
+  </si>
+  <si>
+    <t>ID39835414951378</t>
+  </si>
+  <si>
+    <t>PRSRL 420-460-GO  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951379</t>
+  </si>
+  <si>
+    <t>PRRER-185-225  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951383</t>
+  </si>
+  <si>
+    <t>W (鴨腿)</t>
+  </si>
+  <si>
+    <t>ID39835414951384</t>
+  </si>
+  <si>
+    <t>CHSRL  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951385</t>
+  </si>
+  <si>
+    <t>CHRER-SS  (牛肉)</t>
+  </si>
+  <si>
+    <t>26#19</t>
+  </si>
+  <si>
+    <t>ID39835414951386</t>
+  </si>
+  <si>
+    <t>ID39835414951387</t>
+  </si>
+  <si>
+    <t>ID39835414951388</t>
+  </si>
+  <si>
+    <t>ID39835414951389</t>
+  </si>
+  <si>
+    <t>JURM (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951390</t>
+  </si>
+  <si>
+    <t>BJUC (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951391</t>
+  </si>
+  <si>
+    <t>ID39835414951392</t>
+  </si>
+  <si>
+    <t>ID39835414951393</t>
+  </si>
+  <si>
+    <t>EMSPL-SS  (牛肉)</t>
+  </si>
+  <si>
+    <t>1141023K</t>
+  </si>
+  <si>
+    <t>ID39835414951394</t>
+  </si>
+  <si>
+    <t>ACOB-SS  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951395</t>
+  </si>
+  <si>
+    <t>B2B (失真空)</t>
+  </si>
+  <si>
+    <t>ID39835414951398</t>
+  </si>
+  <si>
+    <t>ACCRM-SS  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951399</t>
+  </si>
+  <si>
+    <t>PRCFT-GO  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951400</t>
+  </si>
+  <si>
+    <t>BH5 (EU)</t>
+  </si>
+  <si>
+    <t>ID39835414951401</t>
+  </si>
+  <si>
+    <t>BH2 (EU)</t>
+  </si>
+  <si>
+    <t>1150114K</t>
+  </si>
+  <si>
+    <t>ID39835414951402</t>
+  </si>
+  <si>
+    <t>PRSRL-GO  (牛肉)</t>
+  </si>
+  <si>
+    <t>1141031K</t>
+  </si>
+  <si>
+    <t>ID39835414951403</t>
+  </si>
+  <si>
+    <t>TMC (羊肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951404</t>
+  </si>
+  <si>
+    <t>JOST (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951405</t>
+  </si>
+  <si>
+    <t>WFRERB延骨切  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951406</t>
+  </si>
+  <si>
+    <t>BFMR10延骨切  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951407</t>
+  </si>
+  <si>
+    <t>JOLT (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951408</t>
+  </si>
+  <si>
+    <t>PRTDL-GO  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951409</t>
+  </si>
+  <si>
+    <t>ID39835414951410</t>
+  </si>
+  <si>
+    <t>JOC (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951411</t>
+  </si>
+  <si>
+    <t>JUC (豬肉)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[異常] </t>
+  </si>
+  <si>
+    <t>ID39835414951412</t>
+  </si>
+  <si>
+    <t>CET (豬肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951413</t>
+  </si>
+  <si>
+    <t>CHTDL-YK  (牛肉)</t>
+  </si>
+  <si>
+    <t>ID39835414951414</t>
+  </si>
+  <si>
+    <t>PRRERB  (牛肉)(骨)</t>
+  </si>
+  <si>
+    <t>ID39835414951415</t>
+  </si>
+  <si>
+    <t>12B (鴨胸)</t>
+  </si>
+  <si>
+    <t>ID39835414951416</t>
+  </si>
+  <si>
+    <t>M-TL-4CM-KR  (牛肉)(切)(澳)</t>
+  </si>
+  <si>
+    <t>24#9</t>
+  </si>
+  <si>
+    <t>ID39835414951417</t>
+  </si>
+  <si>
+    <t>ID39835414951419</t>
+  </si>
+  <si>
+    <t>PRRER 280-320 SS  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951420</t>
+  </si>
+  <si>
+    <t>ID39835414951421</t>
+  </si>
+  <si>
+    <t>PRRER 400-450 (YK)  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>1150309S</t>
+  </si>
+  <si>
+    <t>ID39835414951422</t>
+  </si>
+  <si>
+    <t>PRSRL 280-320 (GO)  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>1150224S</t>
+  </si>
+  <si>
+    <t>ID39835414951423</t>
+  </si>
+  <si>
+    <t>GF-TL 4CM  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951424</t>
+  </si>
+  <si>
+    <t>PRRER對切  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951425</t>
+  </si>
+  <si>
+    <t>PRSRL 2.6CM  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951426</t>
+  </si>
+  <si>
+    <t>PRSRL-260-300 (GO)  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951427</t>
+  </si>
+  <si>
+    <t>PRRER-400-450  (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951428</t>
+  </si>
+  <si>
+    <t>ACRER-TY-280-320 (牛肉)(切)</t>
+  </si>
+  <si>
+    <t>ID39835414951429</t>
+  </si>
+  <si>
+    <t>PRRER-SS-2.6CM</t>
+  </si>
+  <si>
+    <t>1150206S</t>
+  </si>
+  <si>
+    <t>ID39835414951430</t>
+  </si>
+  <si>
+    <t>ID39835414951431</t>
+  </si>
+  <si>
+    <t>ID39835414951432</t>
+  </si>
+  <si>
+    <t>寄庫 EP350</t>
+  </si>
+  <si>
+    <t>ID39835414951433</t>
+  </si>
+  <si>
+    <t>BJUP (報廢)</t>
+  </si>
+  <si>
+    <t>ID39835414951434</t>
+  </si>
+  <si>
+    <t>JOC2 (報廢)</t>
+  </si>
+  <si>
+    <t>ID39835414951435</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>已入庫</t>
+  </si>
+  <si>
+    <t>ID39835414951436</t>
+  </si>
+  <si>
+    <t>ID39835414951437</t>
+  </si>
+  <si>
+    <t>ID39835414951438</t>
+  </si>
+  <si>
+    <t>M89BBLD-KR 十字切 （牛肉）（切）</t>
+  </si>
+  <si>
+    <t>ID177435335526120</t>
+  </si>
+  <si>
+    <t>ID177435503991768</t>
+  </si>
+  <si>
+    <t>L19</t>
+  </si>
+  <si>
+    <t>冷藏庫-左</t>
+  </si>
+  <si>
+    <t>PRRER-GO-C</t>
+  </si>
+  <si>
+    <t>冷藏庫-右</t>
+  </si>
+  <si>
+    <t>報廢區</t>
+  </si>
+  <si>
+    <t>報廢 (已申報)</t>
+  </si>
+  <si>
+    <t>PRSTL-950-1050-GO(牛肉）（切）</t>
+  </si>
+  <si>
+    <t>1150325S</t>
+  </si>
+  <si>
+    <t>CHRER-265-305-SS(牛肉）（切)</t>
+  </si>
+  <si>
+    <t>CHRER-265-305-YK(牛肉）（切)</t>
+  </si>
+  <si>
+    <t>GMB(骨）（美）(牛肉）（切)</t>
+  </si>
+  <si>
+    <t>GMB（美）(牛肉）（切)</t>
+  </si>
+  <si>
+    <t>TMC-對切（紐）(羊肉）（切)</t>
+  </si>
+  <si>
+    <t>GMB(牛肉)(切)</t>
+  </si>
+  <si>
+    <t>M67RER-3CM-KR</t>
+  </si>
+  <si>
+    <t>1150325S(牛肉)(切)</t>
+  </si>
+  <si>
+    <t>M89BBLD-十字切-KR</t>
+  </si>
+  <si>
+    <t>PRSRL-280-320-GO</t>
+  </si>
+  <si>
+    <t>PRSRL-2.6CM-GO</t>
+  </si>
+  <si>
+    <t>CHRER-265-305-YK</t>
+  </si>
+  <si>
+    <t>PRSRM-對切-SS</t>
+  </si>
+  <si>
+    <t>10Q</t>
+  </si>
+  <si>
+    <t>L16</t>
+  </si>
+  <si>
+    <t>L17</t>
+  </si>
+  <si>
+    <t>JOC2</t>
+  </si>
+  <si>
+    <t>PRSRL-420-460-GO</t>
+  </si>
+  <si>
+    <t>JUT</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>C規</t>
+  </si>
+  <si>
+    <t>JOT</t>
+  </si>
+  <si>
+    <t>ACSRMB對切</t>
+  </si>
+  <si>
+    <t>PRRERB延骨切</t>
+  </si>
+  <si>
+    <t>ACCRM</t>
+  </si>
+  <si>
+    <t>SS26#24</t>
+  </si>
+  <si>
+    <t>NR-OB</t>
+  </si>
+  <si>
+    <t>YK</t>
+  </si>
+  <si>
+    <t>ADL</t>
+  </si>
+  <si>
+    <t>ADS</t>
+  </si>
+  <si>
+    <t>PRRER-上林規</t>
+  </si>
+  <si>
+    <t>BFMR10-延骨切</t>
+  </si>
+  <si>
+    <t>L18</t>
+  </si>
+  <si>
+    <t>ADR8</t>
+  </si>
+  <si>
+    <t>TMC對切</t>
+  </si>
+  <si>
+    <t>CHRER-450-490-YK</t>
+  </si>
+  <si>
+    <t>PRSRL-280-320</t>
+  </si>
+  <si>
+    <t>TL-4CM</t>
+  </si>
+  <si>
+    <t>BH1</t>
+  </si>
+  <si>
+    <t>HTR-TY</t>
+  </si>
+  <si>
+    <t>MTLR</t>
+  </si>
+  <si>
+    <t>MT26#2</t>
+  </si>
+  <si>
+    <t>26.4.1入庫</t>
+  </si>
+  <si>
+    <t>T(鴨里肌)</t>
+  </si>
+  <si>
+    <t>M89TDL-KR</t>
+  </si>
+  <si>
+    <t>1130715K</t>
+  </si>
+  <si>
+    <t>CKM-KR</t>
+  </si>
+  <si>
+    <t>1140604K</t>
+  </si>
+  <si>
+    <t>RFM-KR</t>
+  </si>
+  <si>
+    <t>1141105K</t>
+  </si>
+  <si>
+    <t>ACTDL-TY</t>
+  </si>
+  <si>
+    <t>IST-KR</t>
+  </si>
+  <si>
+    <t>1141229K</t>
+  </si>
+  <si>
+    <t>TUE-KR</t>
+  </si>
+  <si>
+    <t>1131031K</t>
+  </si>
+  <si>
+    <t>SPL</t>
+  </si>
+  <si>
+    <t>龜本-大安 寄庫</t>
+  </si>
+  <si>
+    <t>ULV 寄庫 BFMR10</t>
+  </si>
+  <si>
+    <t>YUU 寄庫 JOP</t>
+  </si>
+  <si>
+    <t>頁小館 JUP(寄庫)</t>
+  </si>
+  <si>
+    <t>雅竹鐵板燒 JUP(寄庫)</t>
+  </si>
+  <si>
+    <t>饗豔-信義JOC(寄庫)</t>
+  </si>
+  <si>
+    <t>Lyon 里昂BJUP(寄庫)</t>
+  </si>
+  <si>
+    <t>錨隱廚 EP350 EP335(寄庫）(寄庫)</t>
+  </si>
+  <si>
+    <t>12PS (黑胡椒煙燻鴨胸</t>
+  </si>
+  <si>
+    <t>1150324K</t>
+  </si>
+  <si>
+    <t>M67RER</t>
+  </si>
+  <si>
+    <t>1140623K</t>
+  </si>
+  <si>
+    <t>GF-TUE-TY</t>
+  </si>
+  <si>
+    <t>1140922K</t>
+  </si>
+  <si>
+    <t>M9RER-KR</t>
+  </si>
+  <si>
+    <t>1150323K</t>
+  </si>
+  <si>
+    <t>ACSRL-TY</t>
+  </si>
+  <si>
+    <t>PRRER-SS</t>
+  </si>
+  <si>
+    <t>東豐東 JOC2(寄庫）</t>
+  </si>
+  <si>
+    <t>信鐵板燒 JOP(寄庫）</t>
+  </si>
+  <si>
+    <t>布爾喬亞 EP350(寄庫）</t>
+  </si>
+  <si>
+    <t>UNCLE二店 BJURM(寄庫）</t>
+  </si>
+  <si>
+    <t>CEJM</t>
+  </si>
+  <si>
+    <t>JUP</t>
+  </si>
+  <si>
+    <t>JURM</t>
+  </si>
+  <si>
+    <t>LR22</t>
+  </si>
+  <si>
+    <t>1150105K</t>
+  </si>
+  <si>
+    <t>1150407K</t>
+  </si>
+  <si>
+    <t>JUJM</t>
+  </si>
+  <si>
+    <t>PROB-YK</t>
+  </si>
+  <si>
+    <t>1150401K</t>
+  </si>
+  <si>
+    <t>ADB2</t>
+  </si>
+  <si>
+    <t>PRSRM</t>
+  </si>
+  <si>
+    <t>1150112K</t>
+  </si>
+  <si>
+    <t>GF-CKM-TY</t>
+  </si>
+  <si>
+    <t>26#4</t>
+  </si>
+  <si>
+    <t>M67TDL-KR</t>
+  </si>
+  <si>
+    <t>M89RER-KR</t>
+  </si>
+  <si>
+    <t>1150223K</t>
+  </si>
+  <si>
+    <t>PROB</t>
+  </si>
+  <si>
+    <t>1150331K</t>
+  </si>
+  <si>
+    <t>PRRER-YK</t>
+  </si>
+  <si>
+    <t>34B</t>
+  </si>
+  <si>
+    <t>35B (#35)</t>
+  </si>
+  <si>
+    <t>60S(5入）</t>
+  </si>
+  <si>
+    <t>12S(4入）</t>
+  </si>
+  <si>
+    <t>PRCER-GO</t>
+  </si>
+  <si>
+    <t>PRCER-GO-十字切</t>
+  </si>
+  <si>
+    <t>1150409S</t>
+  </si>
+  <si>
+    <t>PRRER</t>
+  </si>
+  <si>
+    <t>JOLT</t>
+  </si>
+  <si>
+    <t>AD&amp;SP 待驗</t>
+  </si>
+  <si>
+    <t>富美-宜蘭CKC2 寄庫</t>
+  </si>
+  <si>
+    <t>BLR20-HF</t>
+  </si>
+  <si>
+    <t>BLR24-HF</t>
+  </si>
+  <si>
+    <t>BLR22-HF</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY</t>
+  </si>
+  <si>
+    <t>1140423K</t>
+  </si>
+  <si>
+    <t>PRSRMB-GO</t>
+  </si>
+  <si>
+    <t>PRTDL-GO</t>
+  </si>
+  <si>
+    <t>PRRER-3cm</t>
+  </si>
+  <si>
+    <t>QC12</t>
+  </si>
+  <si>
     <t>1141022K</t>
   </si>
   <si>
-    <t>ID39835414951285</t>
-  </si>
-  <si>
-    <t>PRTDL-YK  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951286</t>
-  </si>
-  <si>
-    <t>PRTDL-SS  (牛肉)</t>
-  </si>
-  <si>
-    <t>SS25#88</t>
-  </si>
-  <si>
-    <t>異常 五月即期</t>
-  </si>
-  <si>
-    <t>ID39835414951287</t>
-  </si>
-  <si>
-    <t>JUJM (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951288</t>
-  </si>
-  <si>
-    <t>BFMC (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951289</t>
-  </si>
-  <si>
-    <t>ID39835414951290</t>
-  </si>
-  <si>
-    <t>TUE-ST  (牛肉)</t>
-  </si>
-  <si>
-    <t>24#7 24#6</t>
-  </si>
-  <si>
-    <t>ID39835414951291</t>
-  </si>
-  <si>
-    <t>ID39835414951292</t>
-  </si>
-  <si>
-    <t>ID39835414951293</t>
-  </si>
-  <si>
-    <t>CESA (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951294</t>
-  </si>
-  <si>
-    <t>ADC (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951295</t>
-  </si>
-  <si>
-    <t>ADK (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951296</t>
-  </si>
-  <si>
-    <t>ID39835414951297</t>
-  </si>
-  <si>
-    <t>ID39835414951298</t>
-  </si>
-  <si>
-    <t>JOT (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951299</t>
-  </si>
-  <si>
-    <t>JUP  (豬肉)</t>
-  </si>
-  <si>
-    <t>24#3</t>
-  </si>
-  <si>
-    <t>ID39835414951301</t>
-  </si>
-  <si>
-    <t>ID39835414951302</t>
-  </si>
-  <si>
-    <t>GF-CKM-TY  (牛肉)</t>
-  </si>
-  <si>
-    <t>26#2</t>
-  </si>
-  <si>
-    <t>ID39835414951303</t>
-  </si>
-  <si>
-    <t>DCC (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951304</t>
-  </si>
-  <si>
-    <t>ID39835414951305</t>
-  </si>
-  <si>
-    <t>PS-PRSTL （切） (牛肉)</t>
-  </si>
-  <si>
-    <t>1140909S</t>
-  </si>
-  <si>
-    <t>ID39835414951307</t>
-  </si>
-  <si>
-    <t>SPT (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951308</t>
-  </si>
-  <si>
-    <t>ADJM (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951309</t>
-  </si>
-  <si>
-    <t>JOP (豬肉)</t>
-  </si>
-  <si>
-    <t>25#4</t>
-  </si>
-  <si>
-    <t>2027-06-17T16:00:00.000Z</t>
-  </si>
-  <si>
-    <t>ID39835414951310</t>
-  </si>
-  <si>
-    <t>25#2  25#4</t>
-  </si>
-  <si>
-    <t>ID39835414951311</t>
-  </si>
-  <si>
-    <t>ACOB-TY  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951312</t>
-  </si>
-  <si>
-    <t>M5-TDL-ST  (牛肉)</t>
-  </si>
-  <si>
-    <t>24#5 24#6</t>
-  </si>
-  <si>
-    <t>ID39835414951313</t>
-  </si>
-  <si>
-    <t>ID39835414951314</t>
-  </si>
-  <si>
-    <t>RF-YK  (牛肉)</t>
-  </si>
-  <si>
-    <t>25#45</t>
-  </si>
-  <si>
-    <t>ID39835414951315</t>
-  </si>
-  <si>
-    <t>ADR8 (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951316</t>
-  </si>
-  <si>
-    <t>60PS (煙燻鴨胸)</t>
-  </si>
-  <si>
-    <t>ID39835414951317</t>
-  </si>
-  <si>
-    <t>OLR22 (羊肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951318</t>
-  </si>
-  <si>
-    <t>SPB2 (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951319</t>
-  </si>
-  <si>
-    <t>LR22 (羊肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951320</t>
-  </si>
-  <si>
-    <t>TS300 (三角煙燻腿)</t>
-  </si>
-  <si>
-    <t>ID39835414951322</t>
-  </si>
-  <si>
-    <t>SL (煙燻鴨腿)</t>
-  </si>
-  <si>
-    <t>ID39835414951323</t>
-  </si>
-  <si>
-    <t>TS (三角煙燻鴨胸)</t>
-  </si>
-  <si>
-    <t>ID39835414951325</t>
-  </si>
-  <si>
-    <t>12S (煙燻鴨胸)</t>
-  </si>
-  <si>
-    <t>ID39835414951326</t>
-  </si>
-  <si>
-    <t>BOSS物品</t>
-  </si>
-  <si>
-    <t>ID39835414951327</t>
-  </si>
-  <si>
-    <t>IST  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951328</t>
-  </si>
-  <si>
-    <t>ID39835414951329</t>
-  </si>
-  <si>
-    <t>ID39835414951330</t>
-  </si>
-  <si>
-    <t>ID39835414951331</t>
-  </si>
-  <si>
-    <t>SPL (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951332</t>
-  </si>
-  <si>
-    <t>1150205K</t>
-  </si>
-  <si>
-    <t>ID39835414951333</t>
-  </si>
-  <si>
-    <t>ADB2 (豬肉)</t>
-  </si>
-  <si>
-    <t>1141224K</t>
-  </si>
-  <si>
-    <t>ID39835414951334</t>
-  </si>
-  <si>
-    <t>ID39835414951335</t>
-  </si>
-  <si>
-    <t>ADL(豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951340</t>
-  </si>
-  <si>
-    <t>M45OB-MU  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951341</t>
-  </si>
-  <si>
-    <t>3/18 G9進貨</t>
-  </si>
-  <si>
-    <t>ID39835414951342</t>
-  </si>
-  <si>
-    <t>ID39835414951343</t>
-  </si>
-  <si>
-    <t>JOC2 (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951344</t>
-  </si>
-  <si>
-    <t>ID39835414951345</t>
-  </si>
-  <si>
-    <t>M67OB  (牛肉)</t>
-  </si>
-  <si>
-    <t>24#2</t>
-  </si>
-  <si>
-    <t>ID39835414951346</t>
-  </si>
-  <si>
-    <t>2026-11-21T16:00:00.000Z</t>
-  </si>
-  <si>
-    <t>ID39835414951347</t>
-  </si>
-  <si>
-    <t>ACRPC-TY  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951348</t>
-  </si>
-  <si>
-    <t>ID39835414951349</t>
-  </si>
-  <si>
-    <t>ID39835414951350</t>
-  </si>
-  <si>
-    <t>A5-TDL  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951351</t>
-  </si>
-  <si>
-    <t>A5-GB  (牛肉)</t>
-  </si>
-  <si>
-    <t>1150212K</t>
-  </si>
-  <si>
-    <t>ID39835414951353</t>
-  </si>
-  <si>
-    <t>M89BBLD-KR  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951354</t>
-  </si>
-  <si>
-    <t>1150120K</t>
-  </si>
-  <si>
-    <t>ID39835414951355</t>
-  </si>
-  <si>
-    <t>ID39835414951356</t>
-  </si>
-  <si>
-    <t>ID39835414951357</t>
-  </si>
-  <si>
-    <t>PRSRL-YK  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951358</t>
-  </si>
-  <si>
-    <t>1141230K</t>
-  </si>
-  <si>
-    <t>ID39835414951359</t>
-  </si>
-  <si>
-    <t>SRL  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951360</t>
-  </si>
-  <si>
-    <t>ID39835414951361</t>
-  </si>
-  <si>
-    <t>ID39835414951362</t>
-  </si>
-  <si>
-    <t>1150309K</t>
-  </si>
-  <si>
-    <t>ID39835414951364</t>
-  </si>
-  <si>
-    <t>M67RER-280-320-KR  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951365</t>
-  </si>
-  <si>
-    <t>M89RER-280-320-KR  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951366</t>
-  </si>
-  <si>
-    <t>M89SRL-280/320  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>TY25#13</t>
-  </si>
-  <si>
-    <t>ID39835414951367</t>
-  </si>
-  <si>
-    <t>M45SRL 280-320  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951368</t>
-  </si>
-  <si>
-    <t>PRRER 900-960  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951369</t>
-  </si>
-  <si>
-    <t>PRRER 1開3  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951370</t>
-  </si>
-  <si>
-    <t>PRRER 3CM  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951371</t>
-  </si>
-  <si>
-    <t>GMB ( (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951372</t>
-  </si>
-  <si>
-    <t>GMB (骨)(牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951373</t>
-  </si>
-  <si>
-    <t>GMB  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951374</t>
-  </si>
-  <si>
-    <t>PRRER400-450-YK  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951375</t>
-  </si>
-  <si>
-    <t>PRRER 185-225-GO  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951376</t>
-  </si>
-  <si>
-    <t>PRSTL 5CM-TA  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951377</t>
-  </si>
-  <si>
-    <t>PRRER 325-365-YK  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>1150113S</t>
-  </si>
-  <si>
-    <t>ID39835414951378</t>
-  </si>
-  <si>
-    <t>PRSRL 420-460-GO  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951379</t>
-  </si>
-  <si>
-    <t>PRRER-185-225  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951383</t>
-  </si>
-  <si>
-    <t>W (鴨腿)</t>
-  </si>
-  <si>
-    <t>ID39835414951384</t>
-  </si>
-  <si>
-    <t>CHSRL  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951385</t>
-  </si>
-  <si>
-    <t>CHRER-SS  (牛肉)</t>
-  </si>
-  <si>
-    <t>26#19</t>
-  </si>
-  <si>
-    <t>ID39835414951386</t>
-  </si>
-  <si>
-    <t>ID39835414951387</t>
-  </si>
-  <si>
-    <t>ID39835414951388</t>
-  </si>
-  <si>
-    <t>ID39835414951389</t>
-  </si>
-  <si>
-    <t>JURM (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951390</t>
-  </si>
-  <si>
-    <t>BJUC (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951391</t>
-  </si>
-  <si>
-    <t>ID39835414951392</t>
-  </si>
-  <si>
-    <t>ID39835414951393</t>
-  </si>
-  <si>
-    <t>EMSPL-SS  (牛肉)</t>
-  </si>
-  <si>
-    <t>1141023K</t>
-  </si>
-  <si>
-    <t>ID39835414951394</t>
-  </si>
-  <si>
-    <t>ACOB-SS  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951395</t>
-  </si>
-  <si>
-    <t>B2B (失真空)</t>
-  </si>
-  <si>
-    <t>ID39835414951398</t>
-  </si>
-  <si>
-    <t>ACCRM-SS  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951399</t>
-  </si>
-  <si>
-    <t>PRCFT-GO  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951400</t>
-  </si>
-  <si>
-    <t>BH5 (EU)</t>
-  </si>
-  <si>
-    <t>ID39835414951401</t>
-  </si>
-  <si>
-    <t>BH2 (EU)</t>
-  </si>
-  <si>
-    <t>1150114K</t>
-  </si>
-  <si>
-    <t>ID39835414951402</t>
-  </si>
-  <si>
-    <t>PRSRL-GO  (牛肉)</t>
-  </si>
-  <si>
-    <t>1141031K</t>
-  </si>
-  <si>
-    <t>ID39835414951403</t>
-  </si>
-  <si>
-    <t>TMC (羊肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951404</t>
-  </si>
-  <si>
-    <t>JOST (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951405</t>
-  </si>
-  <si>
-    <t>WFRERB延骨切  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951406</t>
-  </si>
-  <si>
-    <t>BFMR10延骨切  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951407</t>
-  </si>
-  <si>
-    <t>JOLT (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951408</t>
-  </si>
-  <si>
-    <t>PRTDL-GO  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951409</t>
-  </si>
-  <si>
-    <t>ID39835414951410</t>
-  </si>
-  <si>
-    <t>JOC (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951411</t>
-  </si>
-  <si>
-    <t>JUC (豬肉)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[異常] </t>
-  </si>
-  <si>
-    <t>ID39835414951412</t>
-  </si>
-  <si>
-    <t>CET (豬肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951413</t>
-  </si>
-  <si>
-    <t>CHTDL-YK  (牛肉)</t>
-  </si>
-  <si>
-    <t>ID39835414951414</t>
-  </si>
-  <si>
-    <t>PRRERB  (牛肉)(骨)</t>
-  </si>
-  <si>
-    <t>ID39835414951415</t>
-  </si>
-  <si>
-    <t>12B (鴨胸)</t>
-  </si>
-  <si>
-    <t>ID39835414951416</t>
-  </si>
-  <si>
-    <t>M-TL-4CM-KR  (牛肉)(切)(澳)</t>
-  </si>
-  <si>
-    <t>24#9</t>
-  </si>
-  <si>
-    <t>ID39835414951417</t>
-  </si>
-  <si>
-    <t>ID39835414951419</t>
-  </si>
-  <si>
-    <t>PRRER 280-320 SS  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951420</t>
-  </si>
-  <si>
-    <t>ID39835414951421</t>
-  </si>
-  <si>
-    <t>PRRER 400-450 (YK)  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>1150309S</t>
-  </si>
-  <si>
-    <t>ID39835414951422</t>
-  </si>
-  <si>
-    <t>PRSRL 280-320 (GO)  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>1150224S</t>
-  </si>
-  <si>
-    <t>ID39835414951423</t>
-  </si>
-  <si>
-    <t>GF-TL 4CM  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951424</t>
-  </si>
-  <si>
-    <t>PRRER對切  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951425</t>
-  </si>
-  <si>
-    <t>PRSRL 2.6CM  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951426</t>
-  </si>
-  <si>
-    <t>PRSRL-260-300 (GO)  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951427</t>
-  </si>
-  <si>
-    <t>PRRER-400-450  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951428</t>
-  </si>
-  <si>
-    <t>ACRER-TY-280-320 (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>ID39835414951429</t>
-  </si>
-  <si>
-    <t>PRRER-SS-2.6CM</t>
-  </si>
-  <si>
-    <t>1150206S</t>
-  </si>
-  <si>
-    <t>ID39835414951430</t>
-  </si>
-  <si>
-    <t>ID39835414951431</t>
-  </si>
-  <si>
-    <t>ID39835414951432</t>
-  </si>
-  <si>
-    <t>寄庫 EP350</t>
-  </si>
-  <si>
-    <t>ID39835414951433</t>
-  </si>
-  <si>
-    <t>BJUP (報廢)</t>
-  </si>
-  <si>
-    <t>ID39835414951434</t>
-  </si>
-  <si>
-    <t>JOC2 (報廢)</t>
-  </si>
-  <si>
-    <t>ID39835414951435</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>已入庫</t>
-  </si>
-  <si>
-    <t>ID39835414951436</t>
-  </si>
-  <si>
-    <t>ID39835414951437</t>
-  </si>
-  <si>
-    <t>ID39835414951438</t>
-  </si>
-  <si>
-    <t>M89BBLD-KR 十字切 （牛肉）（切）</t>
-  </si>
-  <si>
-    <t>ID177435335526120</t>
-  </si>
-  <si>
-    <t>ID177435503991768</t>
-  </si>
-  <si>
-    <t>L19</t>
-  </si>
-  <si>
-    <t>冷藏庫-左</t>
-  </si>
-  <si>
-    <t>PRRER-GO-C</t>
-  </si>
-  <si>
-    <t>冷藏庫-右</t>
-  </si>
-  <si>
-    <t>報廢區</t>
-  </si>
-  <si>
-    <t>報廢 (已申報)</t>
-  </si>
-  <si>
-    <t>PRSTL-950-1050-GO(牛肉）（切）</t>
-  </si>
-  <si>
-    <t>1150325S</t>
-  </si>
-  <si>
-    <t>CHRER-265-305-SS(牛肉）（切)</t>
-  </si>
-  <si>
-    <t>CHRER-265-305-YK(牛肉）（切)</t>
-  </si>
-  <si>
-    <t>GMB(骨）（美）(牛肉）（切)</t>
-  </si>
-  <si>
-    <t>GMB（美）(牛肉）（切)</t>
-  </si>
-  <si>
-    <t>TMC-對切（紐）(羊肉）（切)</t>
-  </si>
-  <si>
-    <t>GMB(牛肉)(切)</t>
-  </si>
-  <si>
-    <t>M67RER-3CM-KR</t>
-  </si>
-  <si>
-    <t>1150325S(牛肉)(切)</t>
-  </si>
-  <si>
-    <t>M89BBLD-十字切-KR</t>
-  </si>
-  <si>
-    <t>PRSRL-280-320-GO</t>
-  </si>
-  <si>
-    <t>PRSRL-2.6CM-GO</t>
-  </si>
-  <si>
-    <t>CHRER-265-305-YK</t>
-  </si>
-  <si>
-    <t>PRSRM-對切-SS</t>
-  </si>
-  <si>
-    <t>10Q</t>
-  </si>
-  <si>
-    <t>L16</t>
-  </si>
-  <si>
-    <t>L17</t>
-  </si>
-  <si>
-    <t>JOC2</t>
-  </si>
-  <si>
-    <t>PRSRL-420-460-GO</t>
-  </si>
-  <si>
-    <t>JUT</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>C規</t>
-  </si>
-  <si>
-    <t>JOT</t>
-  </si>
-  <si>
-    <t>ACSRMB對切</t>
-  </si>
-  <si>
-    <t>PRRERB延骨切</t>
-  </si>
-  <si>
-    <t>ACCRM</t>
-  </si>
-  <si>
-    <t>SS26#24</t>
-  </si>
-  <si>
-    <t>NR-OB</t>
-  </si>
-  <si>
-    <t>YK</t>
-  </si>
-  <si>
-    <t>ADL</t>
-  </si>
-  <si>
-    <t>ADS</t>
-  </si>
-  <si>
-    <t>PRRER-上林規</t>
-  </si>
-  <si>
-    <t>BFMR10-延骨切</t>
-  </si>
-  <si>
-    <t>L18</t>
-  </si>
-  <si>
-    <t>ADR8</t>
-  </si>
-  <si>
-    <t>TMC對切</t>
-  </si>
-  <si>
-    <t>CHRER-450-490-YK</t>
-  </si>
-  <si>
-    <t>PRSRL-280-320</t>
-  </si>
-  <si>
-    <t>TL-4CM</t>
-  </si>
-  <si>
-    <t>BH1</t>
-  </si>
-  <si>
-    <t>HTR-TY</t>
-  </si>
-  <si>
-    <t>MTLR</t>
-  </si>
-  <si>
-    <t>MT26#2</t>
-  </si>
-  <si>
-    <t>26.4.1入庫</t>
-  </si>
-  <si>
-    <t>T(鴨里肌)</t>
-  </si>
-  <si>
-    <t>M89TDL-KR</t>
-  </si>
-  <si>
-    <t>1130715K</t>
-  </si>
-  <si>
-    <t>CKM-KR</t>
-  </si>
-  <si>
-    <t>1140604K</t>
-  </si>
-  <si>
-    <t>RFM-KR</t>
-  </si>
-  <si>
-    <t>1141105K</t>
-  </si>
-  <si>
-    <t>ACTDL-TY</t>
-  </si>
-  <si>
-    <t>IST-KR</t>
-  </si>
-  <si>
-    <t>1141229K</t>
-  </si>
-  <si>
-    <t>TUE-KR</t>
-  </si>
-  <si>
-    <t>1131031K</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>龜本-大安 寄庫</t>
-  </si>
-  <si>
-    <t>ULV 寄庫 BFMR10</t>
-  </si>
-  <si>
-    <t>YUU 寄庫 JOP</t>
-  </si>
-  <si>
-    <t>頁小館 JUP(寄庫)</t>
-  </si>
-  <si>
-    <t>雅竹鐵板燒 JUP(寄庫)</t>
-  </si>
-  <si>
-    <t>饗豔-信義JOC(寄庫)</t>
-  </si>
-  <si>
-    <t>Lyon 里昂BJUP(寄庫)</t>
-  </si>
-  <si>
-    <t>錨隱廚 EP350 EP335(寄庫）(寄庫)</t>
-  </si>
-  <si>
-    <t>12PS (黑胡椒煙燻鴨胸</t>
-  </si>
-  <si>
-    <t>1150324K</t>
-  </si>
-  <si>
-    <t>M67RER</t>
-  </si>
-  <si>
-    <t>1140623K</t>
-  </si>
-  <si>
-    <t>GF-TUE-TY</t>
-  </si>
-  <si>
-    <t>1140922K</t>
-  </si>
-  <si>
-    <t>M9RER-KR</t>
-  </si>
-  <si>
-    <t>1150323K</t>
-  </si>
-  <si>
-    <t>ACSRL-TY</t>
-  </si>
-  <si>
-    <t>PRRER-SS</t>
-  </si>
-  <si>
-    <t>東豐東 JOC2(寄庫）</t>
-  </si>
-  <si>
-    <t>信鐵板燒 JOP(寄庫）</t>
-  </si>
-  <si>
-    <t>布爾喬亞 EP350(寄庫）</t>
-  </si>
-  <si>
-    <t>UNCLE二店 BJURM(寄庫）</t>
-  </si>
-  <si>
-    <t>CEJM</t>
-  </si>
-  <si>
-    <t>JUP</t>
-  </si>
-  <si>
-    <t>JURM</t>
-  </si>
-  <si>
-    <t>LR22</t>
-  </si>
-  <si>
-    <t>1150105K</t>
-  </si>
-  <si>
-    <t>1150407K</t>
-  </si>
-  <si>
-    <t>JUJM</t>
-  </si>
-  <si>
-    <t>PROB-YK</t>
-  </si>
-  <si>
-    <t>1150401K</t>
-  </si>
-  <si>
-    <t>ADB2</t>
-  </si>
-  <si>
-    <t>PRSRM</t>
-  </si>
-  <si>
-    <t>1150112K</t>
-  </si>
-  <si>
-    <t>GF-CKM-TY</t>
-  </si>
-  <si>
-    <t>26#4</t>
-  </si>
-  <si>
-    <t>M67TDL-KR</t>
-  </si>
-  <si>
-    <t>M89RER-KR</t>
-  </si>
-  <si>
-    <t>1150223K</t>
-  </si>
-  <si>
-    <t>PROB</t>
-  </si>
-  <si>
-    <t>1150331K</t>
-  </si>
-  <si>
-    <t>PRRER-YK</t>
-  </si>
-  <si>
-    <t>34B</t>
-  </si>
-  <si>
-    <t>35B (#35)</t>
-  </si>
-  <si>
-    <t>60S(5入）</t>
-  </si>
-  <si>
-    <t>12S(4入）</t>
-  </si>
-  <si>
     <t>PRCER</t>
-  </si>
-  <si>
-    <t>PRCER-GO-十字切</t>
-  </si>
-  <si>
-    <t>1150409S</t>
-  </si>
-  <si>
-    <t>PRRER</t>
-  </si>
-  <si>
-    <t>JOLT</t>
-  </si>
-  <si>
-    <t>AD&amp;SP 待驗</t>
-  </si>
-  <si>
-    <t>富美-宜蘭CKC2 寄庫</t>
-  </si>
-  <si>
-    <t>BLR20-HF</t>
-  </si>
-  <si>
-    <t>BLR24-HF</t>
-  </si>
-  <si>
-    <t>BLR22-HF</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY</t>
-  </si>
-  <si>
-    <t>1140423K</t>
   </si>
   <si>
     <t>日期時間</t>
@@ -7966,20 +7984,22 @@
       <c r="G228" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="H228" s="9"/>
+      <c r="H228" s="8" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="7" t="s">
         <v>495</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D229" s="13">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="E229" s="8" t="s">
         <v>74</v>
@@ -7988,7 +8008,7 @@
         <v>496</v>
       </c>
       <c r="G229" s="12">
-        <v>46604.0</v>
+        <v>46645.0</v>
       </c>
       <c r="H229" s="9"/>
     </row>
@@ -8083,17 +8103,21 @@
       <c r="B234" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C234" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D234" s="10">
-        <v>16.0</v>
-      </c>
-      <c r="E234" s="9" t="s">
+      <c r="C234" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D234" s="13">
+        <v>20.0</v>
+      </c>
+      <c r="E234" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F234" s="9"/>
-      <c r="G234" s="9"/>
+      <c r="F234" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G234" s="12">
+        <v>46416.0</v>
+      </c>
       <c r="H234" s="8" t="s">
         <v>181</v>
       </c>
@@ -12405,6 +12429,9 @@
       <c r="G439" s="15">
         <v>46596.0</v>
       </c>
+      <c r="H439" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1">
@@ -13276,16 +13303,84 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="16"/>
+      <c r="A483" s="1">
+        <v>1.776059127998E12</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C483" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D483" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E483" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="F483" s="2" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="484">
-      <c r="A484" s="16"/>
+      <c r="A484" s="1">
+        <v>1.77605914796E12</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C484" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D484" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E484" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F484" s="2" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="485">
-      <c r="A485" s="16"/>
+      <c r="A485" s="1">
+        <v>1.776067771744E12</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C485" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D485" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E485" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="F485" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G485" s="15">
+        <v>46468.0</v>
+      </c>
     </row>
     <row r="486">
-      <c r="A486" s="16"/>
+      <c r="A486" s="1">
+        <v>1.776068065666E12</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C486" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D486" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E486" s="2" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="16"/>
@@ -19417,7 +19512,7 @@
         <v>74</v>
       </c>
       <c r="F229" s="8" t="s">
-        <v>496</v>
+        <v>894</v>
       </c>
       <c r="G229" s="12">
         <v>46604.0</v>
@@ -24472,7 +24567,7 @@
         <v>18.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>878</v>
+        <v>895</v>
       </c>
       <c r="F471" s="2" t="s">
         <v>529</v>
@@ -25963,22 +26058,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>
@@ -26003,22 +26098,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="F1" s="9"/>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B2" s="10">
         <v>22.0</v>
@@ -26030,7 +26125,7 @@
         <v>2.0</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -26048,13 +26143,13 @@
         <v>2.0</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="F3" s="9"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="B4" s="10">
         <v>22.0</v>
@@ -26066,13 +26161,13 @@
         <v>2.0</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="F4" s="9"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="B5" s="10">
         <v>22.0</v>
@@ -26084,7 +26179,7 @@
         <v>2.0</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="F5" s="9"/>
     </row>
@@ -26102,7 +26197,7 @@
         <v>2.0</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="F6" s="9"/>
     </row>
@@ -26124,21 +26219,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B2" s="4">
         <v>22.0</v>
@@ -26147,7 +26242,7 @@
         <v>11.0</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3">
@@ -26161,7 +26256,7 @@
         <v>11.0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4">
@@ -26175,12 +26270,12 @@
         <v>5.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>908</v>
+        <v>914</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="B5" s="4">
         <v>15.0</v>
@@ -26189,12 +26284,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
     </row>
   </sheetData>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Inventory" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="「Inventory」的副本" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="「Inventory」0512" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="SearchLogs" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Zoneconfig" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="工作表1" sheetId="5" r:id="rId9"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6869" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6877" uniqueCount="1150">
   <si>
     <t>ID</t>
   </si>
@@ -2583,318 +2583,312 @@
     <t>1140425K</t>
   </si>
   <si>
-    <t>ID1778041492902</t>
+    <t>ID1778057927574</t>
+  </si>
+  <si>
+    <t>M67CFT-ST</t>
+  </si>
+  <si>
+    <t>24#5</t>
+  </si>
+  <si>
+    <t>ID1778057982808</t>
+  </si>
+  <si>
+    <t>M45SRK-ST</t>
+  </si>
+  <si>
+    <t>24#7</t>
+  </si>
+  <si>
+    <t>ID1778139472526</t>
+  </si>
+  <si>
+    <t>1150429K</t>
+  </si>
+  <si>
+    <t>ID1778139597971</t>
+  </si>
+  <si>
+    <t>ID1778197333009</t>
+  </si>
+  <si>
+    <t>BRD210</t>
+  </si>
+  <si>
+    <t>ID1778197382076</t>
+  </si>
+  <si>
+    <t>ID1778197425080</t>
+  </si>
+  <si>
+    <t>ID1778197500800</t>
+  </si>
+  <si>
+    <t>CE500</t>
+  </si>
+  <si>
+    <t>ID1778197520009</t>
+  </si>
+  <si>
+    <t>BE250</t>
+  </si>
+  <si>
+    <t>ID1778227773246</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY</t>
+  </si>
+  <si>
+    <t>1140528K</t>
+  </si>
+  <si>
+    <t>ID1778227799248</t>
+  </si>
+  <si>
+    <t>1140502K</t>
+  </si>
+  <si>
+    <t>ID1778229685758</t>
+  </si>
+  <si>
+    <t>ID1778229748526</t>
+  </si>
+  <si>
+    <t>ID1778229779479</t>
+  </si>
+  <si>
+    <t>CKM-KR</t>
+  </si>
+  <si>
+    <t>ID1778229839132</t>
+  </si>
+  <si>
+    <t>11400808K</t>
+  </si>
+  <si>
+    <t>ID1778229862985</t>
+  </si>
+  <si>
+    <t>ID1778229913502</t>
+  </si>
+  <si>
+    <t>CKC2</t>
+  </si>
+  <si>
+    <t>ID1778229996243</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230020559</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY-對切</t>
+  </si>
+  <si>
+    <t>ID1778230078956</t>
+  </si>
+  <si>
+    <t>PRSRMB-GO-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230144397</t>
+  </si>
+  <si>
+    <t>CHSRMB-YK-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230200332</t>
+  </si>
+  <si>
+    <t>PRRER-340-380-YK</t>
+  </si>
+  <si>
+    <t>1150507S</t>
+  </si>
+  <si>
+    <t>ID1778231133389</t>
+  </si>
+  <si>
+    <t>JUP (8月 10月)</t>
+  </si>
+  <si>
+    <t>ID1778231168084</t>
+  </si>
+  <si>
+    <t>JUP (8月-10月)</t>
+  </si>
+  <si>
+    <t>ID1778231224509</t>
+  </si>
+  <si>
+    <t>JUP (1月 3月)</t>
+  </si>
+  <si>
+    <t>ID1778231253827</t>
+  </si>
+  <si>
+    <t>JUP (2月 4月 5月)</t>
+  </si>
+  <si>
+    <t>ID1778231360305</t>
+  </si>
+  <si>
+    <t>JUP (6月 7月)</t>
+  </si>
+  <si>
+    <t>ID1778232035767</t>
+  </si>
+  <si>
+    <t>PSSTL-5cm</t>
+  </si>
+  <si>
+    <t>ID1778232117897</t>
+  </si>
+  <si>
+    <t>PRRER-對切-GO</t>
+  </si>
+  <si>
+    <t>ID1778232183702</t>
+  </si>
+  <si>
+    <t>PRSTL-950-1050-GO</t>
+  </si>
+  <si>
+    <t>ID1778232270846</t>
+  </si>
+  <si>
+    <t>CHSRL-280-320</t>
+  </si>
+  <si>
+    <t>1140618S</t>
+  </si>
+  <si>
+    <t>(半包)</t>
+  </si>
+  <si>
+    <t>ID1778464113039</t>
+  </si>
+  <si>
+    <t>LR28</t>
+  </si>
+  <si>
+    <t>[NEW]</t>
+  </si>
+  <si>
+    <t>ID1778464134245</t>
+  </si>
+  <si>
+    <t>LR26</t>
+  </si>
+  <si>
+    <t>ID1778464166470</t>
+  </si>
+  <si>
+    <t>LHS</t>
+  </si>
+  <si>
+    <t>ID1778464235655</t>
+  </si>
+  <si>
+    <t>CHTDL-YK(預定)</t>
+  </si>
+  <si>
+    <t>1141219K</t>
+  </si>
+  <si>
+    <t>ID1778464249488</t>
+  </si>
+  <si>
+    <t>1141224K</t>
+  </si>
+  <si>
+    <t>ID1778464298059</t>
+  </si>
+  <si>
+    <t>GF-HTR-TY</t>
+  </si>
+  <si>
+    <t>1140916K</t>
+  </si>
+  <si>
+    <t>ID1778464320356</t>
+  </si>
+  <si>
+    <t>1141002K</t>
+  </si>
+  <si>
+    <t>ID1778464331761</t>
+  </si>
+  <si>
+    <t>1141029K</t>
+  </si>
+  <si>
+    <t>ID1778464346113</t>
+  </si>
+  <si>
+    <t>1141119K</t>
+  </si>
+  <si>
+    <t>ID1778464356508</t>
+  </si>
+  <si>
+    <t>1141210K</t>
+  </si>
+  <si>
+    <t>ID1778541876765</t>
+  </si>
+  <si>
+    <t>木頭沾板</t>
+  </si>
+  <si>
+    <t>ID1778542317563</t>
+  </si>
+  <si>
+    <t>LR24</t>
+  </si>
+  <si>
+    <t>ID1778542503372</t>
+  </si>
+  <si>
+    <t>PRSTL-4.5CM-YK</t>
+  </si>
+  <si>
+    <t>1150429S</t>
+  </si>
+  <si>
+    <t>ID1778542971412</t>
+  </si>
+  <si>
+    <t>ID1778554675190</t>
+  </si>
+  <si>
+    <t>ID1778556077088</t>
+  </si>
+  <si>
+    <t>M89FM</t>
+  </si>
+  <si>
+    <t>ID1778556120999</t>
+  </si>
+  <si>
+    <t>M67-TDL-KR</t>
+  </si>
+  <si>
+    <t>ID1778556295035</t>
+  </si>
+  <si>
+    <t>GF-IE-MU</t>
+  </si>
+  <si>
+    <t>ID1778559275364</t>
   </si>
   <si>
     <t>PRCER-十字切-GO</t>
   </si>
   <si>
-    <t>(有空位）</t>
-  </si>
-  <si>
-    <t>ID1778057927574</t>
-  </si>
-  <si>
-    <t>M67CFT-ST</t>
-  </si>
-  <si>
-    <t>24#5</t>
-  </si>
-  <si>
-    <t>ID1778057982808</t>
-  </si>
-  <si>
-    <t>M45SRK-ST</t>
-  </si>
-  <si>
-    <t>24#7</t>
-  </si>
-  <si>
-    <t>ID1778139472526</t>
-  </si>
-  <si>
-    <t>1150429K</t>
-  </si>
-  <si>
-    <t>ID1778139597971</t>
-  </si>
-  <si>
-    <t>ID1778197333009</t>
-  </si>
-  <si>
-    <t>BRD210</t>
-  </si>
-  <si>
-    <t>ID1778197382076</t>
-  </si>
-  <si>
-    <t>ID1778197425080</t>
-  </si>
-  <si>
-    <t>ID1778197500800</t>
-  </si>
-  <si>
-    <t>CE500</t>
-  </si>
-  <si>
-    <t>ID1778197520009</t>
-  </si>
-  <si>
-    <t>BE250</t>
-  </si>
-  <si>
-    <t>ID1778227773246</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY</t>
-  </si>
-  <si>
-    <t>1140528K</t>
-  </si>
-  <si>
-    <t>ID1778227799248</t>
-  </si>
-  <si>
-    <t>1140502K</t>
-  </si>
-  <si>
-    <t>ID1778229685758</t>
-  </si>
-  <si>
-    <t>ID1778229748526</t>
-  </si>
-  <si>
-    <t>ID1778229779479</t>
-  </si>
-  <si>
-    <t>CKM-KR</t>
-  </si>
-  <si>
-    <t>ID1778229839132</t>
-  </si>
-  <si>
-    <t>11400808K</t>
-  </si>
-  <si>
-    <t>ID1778229862985</t>
-  </si>
-  <si>
-    <t>ID1778229913502</t>
-  </si>
-  <si>
-    <t>CKC2</t>
-  </si>
-  <si>
-    <t>ID1778229996243</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230020559</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY-對切</t>
-  </si>
-  <si>
-    <t>ID1778230078956</t>
-  </si>
-  <si>
-    <t>PRSRMB-GO-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230144397</t>
-  </si>
-  <si>
-    <t>CHSRMB-YK-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230200332</t>
-  </si>
-  <si>
-    <t>PRRER-340-380-YK</t>
-  </si>
-  <si>
-    <t>1150507S</t>
-  </si>
-  <si>
-    <t>ID1778231133389</t>
-  </si>
-  <si>
-    <t>JUP (8月 10月)</t>
-  </si>
-  <si>
-    <t>ID1778231168084</t>
-  </si>
-  <si>
-    <t>JUP (8月-10月)</t>
-  </si>
-  <si>
-    <t>ID1778231224509</t>
-  </si>
-  <si>
-    <t>JUP (1月 3月)</t>
-  </si>
-  <si>
-    <t>ID1778231253827</t>
-  </si>
-  <si>
-    <t>JUP (2月 4月 5月)</t>
-  </si>
-  <si>
-    <t>ID1778231360305</t>
-  </si>
-  <si>
-    <t>JUP (6月 7月)</t>
-  </si>
-  <si>
-    <t>ID1778232035767</t>
-  </si>
-  <si>
-    <t>PSSTL-5cm</t>
-  </si>
-  <si>
-    <t>ID1778232117897</t>
-  </si>
-  <si>
-    <t>PRRER-對切-GO</t>
-  </si>
-  <si>
-    <t>ID1778232183702</t>
-  </si>
-  <si>
-    <t>PRSTL-950-1050-GO</t>
-  </si>
-  <si>
-    <t>ID1778232270846</t>
-  </si>
-  <si>
-    <t>CHSRL-280-320</t>
-  </si>
-  <si>
-    <t>1140618S</t>
-  </si>
-  <si>
-    <t>(半包)</t>
-  </si>
-  <si>
-    <t>ID1778464113039</t>
-  </si>
-  <si>
-    <t>LR28</t>
-  </si>
-  <si>
-    <t>[NEW]</t>
-  </si>
-  <si>
-    <t>ID1778464134245</t>
-  </si>
-  <si>
-    <t>LR26</t>
-  </si>
-  <si>
-    <t>ID1778464166470</t>
-  </si>
-  <si>
-    <t>LHS</t>
-  </si>
-  <si>
-    <t>ID1778464235655</t>
-  </si>
-  <si>
-    <t>CHTDL-YK(預定)</t>
-  </si>
-  <si>
-    <t>1141219K</t>
-  </si>
-  <si>
-    <t>ID1778464249488</t>
-  </si>
-  <si>
-    <t>1141224K</t>
-  </si>
-  <si>
-    <t>ID1778464298059</t>
-  </si>
-  <si>
-    <t>GF-HTR-TY</t>
-  </si>
-  <si>
-    <t>1140916K</t>
-  </si>
-  <si>
-    <t>ID1778464320356</t>
-  </si>
-  <si>
-    <t>1141002K</t>
-  </si>
-  <si>
-    <t>ID1778464331761</t>
-  </si>
-  <si>
-    <t>1141029K</t>
-  </si>
-  <si>
-    <t>ID1778464346113</t>
-  </si>
-  <si>
-    <t>1141119K</t>
-  </si>
-  <si>
-    <t>ID1778464356508</t>
-  </si>
-  <si>
-    <t>1141210K</t>
-  </si>
-  <si>
-    <t>ID1778541876765</t>
-  </si>
-  <si>
-    <t>木頭沾板</t>
-  </si>
-  <si>
-    <t>ID1778542317563</t>
-  </si>
-  <si>
-    <t>LR24</t>
-  </si>
-  <si>
-    <t>ID1778542503372</t>
-  </si>
-  <si>
-    <t>PRSTL-4.5CM-YK</t>
-  </si>
-  <si>
-    <t>1150429S</t>
-  </si>
-  <si>
-    <t>ID1778542971412</t>
-  </si>
-  <si>
-    <t>ID1778554675190</t>
-  </si>
-  <si>
-    <t>ID1778556077088</t>
-  </si>
-  <si>
-    <t>M89FM</t>
-  </si>
-  <si>
-    <t>ID1778556120999</t>
-  </si>
-  <si>
-    <t>M67-TDL-KR</t>
-  </si>
-  <si>
-    <t>ID1778556295035</t>
-  </si>
-  <si>
-    <t>GF-IE-MU</t>
-  </si>
-  <si>
-    <t>ID1778559275364</t>
-  </si>
-  <si>
     <t>ID1778559302299</t>
   </si>
   <si>
@@ -2907,7 +2901,16 @@
     <t>PRSRL-420-460(半)-GO</t>
   </si>
   <si>
-    <t>1150121SS</t>
+    <t>ID1778572817969</t>
+  </si>
+  <si>
+    <t>1150430K</t>
+  </si>
+  <si>
+    <t>ID1778573066811</t>
+  </si>
+  <si>
+    <t>1150113S</t>
   </si>
   <si>
     <t>日期時間</t>
@@ -3217,9 +3220,6 @@
   </si>
   <si>
     <t>PRRER 325-365-YK  (牛肉)(切)</t>
-  </si>
-  <si>
-    <t>1150113S</t>
   </si>
   <si>
     <t>ACCRM-SS  (牛肉)</t>
@@ -14456,25 +14456,22 @@
         <v>855</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D476" s="2">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>856</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>154</v>
+        <v>857</v>
       </c>
       <c r="G476" s="9">
-        <v>46794.0</v>
-      </c>
-      <c r="H476" s="2" t="s">
-        <v>857</v>
+        <v>46194.0</v>
       </c>
     </row>
     <row r="477">
@@ -14497,7 +14494,7 @@
         <v>860</v>
       </c>
       <c r="G477" s="9">
-        <v>46194.0</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="478">
@@ -14505,70 +14502,67 @@
         <v>861</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D478" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E478" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F478" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="F478" s="3" t="s">
-        <v>863</v>
-      </c>
       <c r="G478" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D479" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F479" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="G479" s="9">
-        <v>46913.0</v>
+        <v>728</v>
+      </c>
+      <c r="F479" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D480" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F480" s="3">
-        <v>11505.0</v>
+        <v>865</v>
+      </c>
+      <c r="F480" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>10</v>
@@ -14580,7 +14574,7 @@
         <v>2.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>868</v>
+        <v>15</v>
       </c>
       <c r="F481" s="3" t="s">
         <v>243</v>
@@ -14588,7 +14582,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>10</v>
@@ -14600,35 +14594,38 @@
         <v>2.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>15</v>
+        <v>865</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D483" s="2">
         <v>2.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G483" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>10</v>
@@ -14637,37 +14634,37 @@
         <v>25</v>
       </c>
       <c r="D484" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="F484" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>871</v>
+      </c>
+      <c r="F484" s="4"/>
       <c r="G484" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C485" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D485" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E485" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="B485" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C485" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D485" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E485" s="2" t="s">
+      <c r="F485" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="F485" s="4"/>
       <c r="G485" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="486">
@@ -14684,61 +14681,58 @@
         <v>4.0</v>
       </c>
       <c r="E486" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F486" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="F486" s="3" t="s">
-        <v>877</v>
-      </c>
       <c r="G486" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D487" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="F487" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="G487" s="9">
-        <v>46484.0</v>
+        <v>600</v>
+      </c>
+      <c r="F487" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D488" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="F488" s="3">
-        <v>11505.0</v>
+        <v>803</v>
+      </c>
+      <c r="F488" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>32</v>
@@ -14750,35 +14744,38 @@
         <v>5.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>803</v>
+        <v>880</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>62</v>
+        <v>673</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D490" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E490" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F490" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="B490" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C490" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D490" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E490" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F490" s="3" t="s">
-        <v>673</v>
+      <c r="G490" s="9">
+        <v>46550.0</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>32</v>
@@ -14787,13 +14784,13 @@
         <v>11</v>
       </c>
       <c r="D491" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="F491" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="G491" s="9">
         <v>46550.0</v>
@@ -14801,53 +14798,53 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D492" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>885</v>
+        <v>393</v>
       </c>
       <c r="G492" s="9">
-        <v>46550.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C493" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D493" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E493" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="B493" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D493" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E493" s="2" t="s">
-        <v>888</v>
-      </c>
       <c r="F493" s="3" t="s">
-        <v>393</v>
+        <v>663</v>
       </c>
       <c r="G493" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>64</v>
@@ -14859,18 +14856,18 @@
         <v>17.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G494" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>64</v>
@@ -14882,18 +14879,18 @@
         <v>17.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G495" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>64</v>
@@ -14905,18 +14902,18 @@
         <v>17.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G496" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>64</v>
@@ -14928,13 +14925,13 @@
         <v>17.0</v>
       </c>
       <c r="E497" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="F497" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="F497" s="3" t="s">
-        <v>663</v>
-      </c>
       <c r="G497" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="498">
@@ -14945,24 +14942,21 @@
         <v>64</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D498" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>898</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="G498" s="9">
-        <v>46523.0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>64</v>
@@ -14974,7 +14968,7 @@
         <v>22.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>243</v>
@@ -14982,19 +14976,19 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C500" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D500" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="B500" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D500" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>903</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>243</v>
@@ -15002,19 +14996,19 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D501" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>243</v>
@@ -15022,7 +15016,7 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -15031,10 +15025,10 @@
         <v>27</v>
       </c>
       <c r="D502" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>243</v>
@@ -15042,73 +15036,76 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C503" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D503" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E503" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="B503" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D503" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E503" s="2" t="s">
-        <v>909</v>
-      </c>
       <c r="F503" s="3" t="s">
-        <v>243</v>
+        <v>194</v>
+      </c>
+      <c r="G503" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C504" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D504" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E504" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="B504" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D504" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E504" s="2" t="s">
-        <v>911</v>
-      </c>
       <c r="F504" s="3" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="G504" s="9">
-        <v>46281.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C505" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D505" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E505" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="B505" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D505" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="E505" s="2" t="s">
-        <v>913</v>
-      </c>
       <c r="F505" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G505" s="9">
-        <v>46949.0</v>
+        <v>46543.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>64</v>
@@ -15120,36 +15117,36 @@
         <v>15.0</v>
       </c>
       <c r="E506" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F506" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="F506" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="G506" s="9">
-        <v>46543.0</v>
+        <v>46303.0</v>
+      </c>
+      <c r="H506" s="2" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D507" s="2">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="G507" s="9">
-        <v>46303.0</v>
+        <v>534</v>
       </c>
       <c r="H507" s="2" t="s">
         <v>919</v>
@@ -15166,7 +15163,7 @@
         <v>11</v>
       </c>
       <c r="D508" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>921</v>
@@ -15174,54 +15171,51 @@
       <c r="F508" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="H508" s="2" t="s">
-        <v>922</v>
+      <c r="G508" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C509" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D509" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E509" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C509" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D509" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E509" s="2" t="s">
-        <v>924</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="G509" s="9">
-        <v>47146.0</v>
+      <c r="H509" s="2" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C510" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D510" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E510" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="B510" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D510" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E510" s="2" t="s">
+      <c r="F510" s="3" t="s">
         <v>926</v>
-      </c>
-      <c r="F510" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="H510" s="2" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="511">
@@ -15238,27 +15232,27 @@
         <v>18.0</v>
       </c>
       <c r="E511" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="F511" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="F511" s="3" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D512" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E512" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="B512" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D512" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E512" s="2" t="s">
-        <v>928</v>
       </c>
       <c r="F512" s="3" t="s">
         <v>931</v>
@@ -15278,15 +15272,18 @@
         <v>8.0</v>
       </c>
       <c r="E513" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="F513" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="F513" s="3" t="s">
-        <v>934</v>
+      <c r="G513" s="9">
+        <v>46604.0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>32</v>
@@ -15298,18 +15295,15 @@
         <v>8.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="G514" s="9">
-        <v>46604.0</v>
+        <v>935</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>32</v>
@@ -15321,15 +15315,15 @@
         <v>8.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F515" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>32</v>
@@ -15341,68 +15335,71 @@
         <v>8.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D517" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E517" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="B517" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C517" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D517" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="E517" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="F517" s="3" t="s">
-        <v>942</v>
-      </c>
+      <c r="F517" s="4"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D518" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E518" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="B518" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C518" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D518" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E518" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="F518" s="4"/>
+      <c r="F518" s="3" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D519" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E519" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="B519" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C519" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D519" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E519" s="2" t="s">
+      <c r="F519" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="F519" s="3" t="s">
-        <v>534</v>
+      <c r="G519" s="9">
+        <v>46792.0</v>
       </c>
     </row>
     <row r="520">
@@ -15410,27 +15407,22 @@
         <v>947</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D520" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="F520" s="3" t="s">
-        <v>949</v>
-      </c>
-      <c r="G520" s="9">
-        <v>46792.0</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="F520" s="4"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>32</v>
@@ -15439,16 +15431,21 @@
         <v>11</v>
       </c>
       <c r="D521" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F521" s="4"/>
+        <v>650</v>
+      </c>
+      <c r="F521" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G521" s="9">
+        <v>46416.0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>32</v>
@@ -15457,21 +15454,21 @@
         <v>11</v>
       </c>
       <c r="D522" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>57</v>
+        <v>752</v>
       </c>
       <c r="G522" s="9">
-        <v>46416.0</v>
+        <v>46768.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>32</v>
@@ -15483,76 +15480,76 @@
         <v>20.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>752</v>
+        <v>376</v>
       </c>
       <c r="G523" s="9">
-        <v>46768.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D524" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E524" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="B524" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C524" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D524" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E524" s="2" t="s">
-        <v>955</v>
-      </c>
       <c r="F524" s="3" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="G524" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D525" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E525" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="B525" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D525" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E525" s="2" t="s">
-        <v>957</v>
-      </c>
       <c r="F525" s="3" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="G525" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D526" s="2">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>856</v>
+        <v>956</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>154</v>
@@ -15563,7 +15560,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>64</v>
@@ -15572,39 +15569,39 @@
         <v>25</v>
       </c>
       <c r="D527" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>856</v>
+        <v>595</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>154</v>
       </c>
       <c r="G527" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C528" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D528" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="E528" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="B528" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C528" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D528" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E528" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="F528" s="3" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="G528" s="9">
-        <v>46484.0</v>
+        <v>46537.0</v>
       </c>
     </row>
     <row r="529">
@@ -15615,24 +15612,43 @@
         <v>64</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D529" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E529" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F529" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="G529" s="9">
+        <v>46792.0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D530" s="2">
         <v>16.0</v>
       </c>
-      <c r="E529" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="F529" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="G529" s="9">
-        <v>46537.0</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="19"/>
-      <c r="F530" s="4"/>
+      <c r="E530" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="F530" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="G530" s="9">
+        <v>46530.0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="19"/>
@@ -16311,7 +16327,6 @@
       <c r="F699" s="4"/>
     </row>
     <row r="700">
-      <c r="A700" s="19"/>
       <c r="F700" s="4"/>
     </row>
     <row r="701">
@@ -16325,9 +16340,6 @@
     </row>
     <row r="704">
       <c r="F704" s="4"/>
-    </row>
-    <row r="705">
-      <c r="F705" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -26966,25 +26978,22 @@
         <v>855</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D476" s="2">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>856</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>154</v>
+        <v>857</v>
       </c>
       <c r="G476" s="9">
-        <v>46794.0</v>
-      </c>
-      <c r="H476" s="2" t="s">
-        <v>857</v>
+        <v>46194.0</v>
       </c>
     </row>
     <row r="477">
@@ -27007,7 +27016,7 @@
         <v>860</v>
       </c>
       <c r="G477" s="9">
-        <v>46194.0</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="478">
@@ -27015,70 +27024,67 @@
         <v>861</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D478" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E478" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F478" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="F478" s="3" t="s">
-        <v>863</v>
-      </c>
       <c r="G478" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D479" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F479" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="G479" s="9">
-        <v>46913.0</v>
+        <v>728</v>
+      </c>
+      <c r="F479" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D480" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F480" s="3">
-        <v>11505.0</v>
+        <v>865</v>
+      </c>
+      <c r="F480" s="3" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>10</v>
@@ -27090,7 +27096,7 @@
         <v>2.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>868</v>
+        <v>15</v>
       </c>
       <c r="F481" s="3" t="s">
         <v>243</v>
@@ -27098,7 +27104,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>10</v>
@@ -27110,35 +27116,38 @@
         <v>2.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>15</v>
+        <v>865</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>243</v>
+        <v>16</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D483" s="2">
         <v>2.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G483" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>10</v>
@@ -27147,37 +27156,37 @@
         <v>25</v>
       </c>
       <c r="D484" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="F484" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>871</v>
+      </c>
+      <c r="F484" s="4"/>
       <c r="G484" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C485" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D485" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E485" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="B485" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C485" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D485" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E485" s="2" t="s">
+      <c r="F485" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="F485" s="4"/>
       <c r="G485" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="486">
@@ -27194,61 +27203,58 @@
         <v>4.0</v>
       </c>
       <c r="E486" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="F486" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="F486" s="3" t="s">
-        <v>877</v>
-      </c>
       <c r="G486" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D487" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="F487" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="G487" s="9">
-        <v>46484.0</v>
+        <v>600</v>
+      </c>
+      <c r="F487" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D488" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="F488" s="3">
-        <v>11505.0</v>
+        <v>803</v>
+      </c>
+      <c r="F488" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>32</v>
@@ -27260,35 +27266,38 @@
         <v>5.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>803</v>
+        <v>880</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>62</v>
+        <v>673</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D490" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E490" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F490" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="B490" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C490" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D490" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E490" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="F490" s="3" t="s">
-        <v>673</v>
+      <c r="G490" s="9">
+        <v>46550.0</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>32</v>
@@ -27297,13 +27306,13 @@
         <v>11</v>
       </c>
       <c r="D491" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="F491" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="G491" s="9">
         <v>46550.0</v>
@@ -27311,53 +27320,53 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D492" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>885</v>
+        <v>393</v>
       </c>
       <c r="G492" s="9">
-        <v>46550.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C493" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D493" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E493" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="B493" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D493" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E493" s="2" t="s">
-        <v>888</v>
-      </c>
       <c r="F493" s="3" t="s">
-        <v>393</v>
+        <v>663</v>
       </c>
       <c r="G493" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>64</v>
@@ -27369,18 +27378,18 @@
         <v>17.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G494" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>64</v>
@@ -27392,18 +27401,18 @@
         <v>17.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G495" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>64</v>
@@ -27415,18 +27424,18 @@
         <v>17.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G496" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>64</v>
@@ -27438,13 +27447,13 @@
         <v>17.0</v>
       </c>
       <c r="E497" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="F497" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="F497" s="3" t="s">
-        <v>663</v>
-      </c>
       <c r="G497" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="498">
@@ -27455,24 +27464,21 @@
         <v>64</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D498" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>898</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="G498" s="9">
-        <v>46523.0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>64</v>
@@ -27484,7 +27490,7 @@
         <v>22.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>243</v>
@@ -27492,19 +27498,19 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C500" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D500" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="B500" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D500" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>903</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>243</v>
@@ -27512,19 +27518,19 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D501" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>243</v>
@@ -27532,7 +27538,7 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -27541,10 +27547,10 @@
         <v>27</v>
       </c>
       <c r="D502" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>243</v>
@@ -27552,73 +27558,76 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C503" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D503" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E503" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="B503" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D503" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E503" s="2" t="s">
-        <v>909</v>
-      </c>
       <c r="F503" s="3" t="s">
-        <v>243</v>
+        <v>194</v>
+      </c>
+      <c r="G503" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C504" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D504" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E504" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="B504" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D504" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E504" s="2" t="s">
-        <v>911</v>
-      </c>
       <c r="F504" s="3" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="G504" s="9">
-        <v>46281.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C505" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D505" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E505" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="B505" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D505" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="E505" s="2" t="s">
-        <v>913</v>
-      </c>
       <c r="F505" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G505" s="9">
-        <v>46949.0</v>
+        <v>46543.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>64</v>
@@ -27630,36 +27639,36 @@
         <v>15.0</v>
       </c>
       <c r="E506" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F506" s="3" t="s">
         <v>915</v>
       </c>
-      <c r="F506" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="G506" s="9">
-        <v>46543.0</v>
+        <v>46303.0</v>
+      </c>
+      <c r="H506" s="2" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D507" s="2">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="G507" s="9">
-        <v>46303.0</v>
+        <v>534</v>
       </c>
       <c r="H507" s="2" t="s">
         <v>919</v>
@@ -27676,7 +27685,7 @@
         <v>11</v>
       </c>
       <c r="D508" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>921</v>
@@ -27684,54 +27693,51 @@
       <c r="F508" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="H508" s="2" t="s">
-        <v>922</v>
+      <c r="G508" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C509" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D509" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E509" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C509" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D509" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E509" s="2" t="s">
-        <v>924</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="G509" s="9">
-        <v>47146.0</v>
+      <c r="H509" s="2" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C510" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D510" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E510" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="B510" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D510" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E510" s="2" t="s">
+      <c r="F510" s="3" t="s">
         <v>926</v>
-      </c>
-      <c r="F510" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="H510" s="2" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="511">
@@ -27748,27 +27754,27 @@
         <v>18.0</v>
       </c>
       <c r="E511" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="F511" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="F511" s="3" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D512" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E512" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="B512" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D512" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E512" s="2" t="s">
-        <v>928</v>
       </c>
       <c r="F512" s="3" t="s">
         <v>931</v>
@@ -27788,15 +27794,18 @@
         <v>8.0</v>
       </c>
       <c r="E513" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="F513" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="F513" s="3" t="s">
-        <v>934</v>
+      <c r="G513" s="9">
+        <v>46604.0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>32</v>
@@ -27808,18 +27817,15 @@
         <v>8.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="G514" s="9">
-        <v>46604.0</v>
+        <v>935</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>32</v>
@@ -27831,15 +27837,15 @@
         <v>8.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F515" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>32</v>
@@ -27851,68 +27857,71 @@
         <v>8.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D517" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E517" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="B517" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C517" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D517" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="E517" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="F517" s="3" t="s">
-        <v>942</v>
-      </c>
+      <c r="F517" s="4"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D518" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E518" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="B518" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C518" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D518" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E518" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="F518" s="4"/>
+      <c r="F518" s="3" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D519" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E519" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="B519" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C519" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D519" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E519" s="2" t="s">
+      <c r="F519" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="F519" s="3" t="s">
-        <v>534</v>
+      <c r="G519" s="9">
+        <v>46792.0</v>
       </c>
     </row>
     <row r="520">
@@ -27920,27 +27929,22 @@
         <v>947</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D520" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="F520" s="3" t="s">
-        <v>949</v>
-      </c>
-      <c r="G520" s="9">
-        <v>46792.0</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="F520" s="4"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>32</v>
@@ -27949,16 +27953,21 @@
         <v>11</v>
       </c>
       <c r="D521" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F521" s="4"/>
+        <v>650</v>
+      </c>
+      <c r="F521" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G521" s="9">
+        <v>46416.0</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>32</v>
@@ -27967,21 +27976,21 @@
         <v>11</v>
       </c>
       <c r="D522" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>57</v>
+        <v>752</v>
       </c>
       <c r="G522" s="9">
-        <v>46416.0</v>
+        <v>46768.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>32</v>
@@ -27993,76 +28002,76 @@
         <v>20.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>752</v>
+        <v>376</v>
       </c>
       <c r="G523" s="9">
-        <v>46768.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D524" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E524" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="B524" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C524" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D524" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E524" s="2" t="s">
-        <v>955</v>
-      </c>
       <c r="F524" s="3" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="G524" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D525" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E525" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="B525" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D525" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E525" s="2" t="s">
-        <v>957</v>
-      </c>
       <c r="F525" s="3" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="G525" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D526" s="2">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>856</v>
+        <v>956</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>154</v>
@@ -28073,7 +28082,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>64</v>
@@ -28082,39 +28091,39 @@
         <v>25</v>
       </c>
       <c r="D527" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>856</v>
+        <v>595</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>154</v>
       </c>
       <c r="G527" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C528" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D528" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="E528" s="2" t="s">
         <v>960</v>
       </c>
-      <c r="B528" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C528" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D528" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E528" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="F528" s="3" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="G528" s="9">
-        <v>46484.0</v>
+        <v>46537.0</v>
       </c>
     </row>
     <row r="529">
@@ -28125,24 +28134,43 @@
         <v>64</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D529" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E529" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="F529" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="G529" s="9">
+        <v>46792.0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D530" s="2">
         <v>16.0</v>
       </c>
-      <c r="E529" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="F529" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="G529" s="9">
-        <v>46537.0</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="19"/>
-      <c r="F530" s="4"/>
+      <c r="E530" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="F530" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="G530" s="9">
+        <v>46530.0</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="19"/>
@@ -28821,7 +28849,6 @@
       <c r="F699" s="4"/>
     </row>
     <row r="700">
-      <c r="A700" s="19"/>
       <c r="F700" s="4"/>
     </row>
     <row r="701">
@@ -28835,9 +28862,6 @@
     </row>
     <row r="704">
       <c r="F704" s="4"/>
-    </row>
-    <row r="705">
-      <c r="F705" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -28856,22 +28880,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>966</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>965</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="2">
@@ -28911,22 +28935,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F1" s="12"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B2" s="13">
         <v>22.0</v>
@@ -28938,13 +28962,13 @@
         <v>2.0</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B3" s="13">
         <v>22.0</v>
@@ -28956,13 +28980,13 @@
         <v>2.0</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B4" s="13">
         <v>22.0</v>
@@ -28974,13 +28998,13 @@
         <v>2.0</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B5" s="13">
         <v>22.0</v>
@@ -28992,7 +29016,7 @@
         <v>2.0</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -29010,7 +29034,7 @@
         <v>2.0</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -29032,21 +29056,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B2" s="6">
         <v>22.0</v>
@@ -29055,12 +29079,12 @@
         <v>11.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B3" s="6">
         <v>22.0</v>
@@ -29069,7 +29093,7 @@
         <v>11.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="4">
@@ -29083,13 +29107,13 @@
         <v>5.0</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E4" s="22"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B5" s="6">
         <v>15.0</v>
@@ -29098,12 +29122,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -29124,25 +29148,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="2">
@@ -29268,7 +29292,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="9">
@@ -29477,7 +29501,7 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>364</v>
@@ -29496,7 +29520,7 @@
         <v>19.0</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>364</v>
@@ -29587,10 +29611,10 @@
         <v>17.0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -29868,7 +29892,7 @@
         <v>7.0</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>91</v>
@@ -29906,7 +29930,7 @@
         <v>7.0</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>91</v>
@@ -29925,7 +29949,7 @@
         <v>7.0</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>91</v>
@@ -30204,7 +30228,7 @@
         <v>1.0</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="12"/>
@@ -30401,7 +30425,7 @@
         <v>16.0</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>160</v>
@@ -30420,7 +30444,7 @@
         <v>16.0</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="12"/>
@@ -30437,7 +30461,7 @@
         <v>15.0</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>441</v>
@@ -30498,7 +30522,7 @@
         <v>13.0</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E75" s="14"/>
       <c r="F75" s="12"/>
@@ -30515,7 +30539,7 @@
         <v>12.0</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>157</v>
@@ -30707,7 +30731,7 @@
         <v>15.0</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E86" s="14"/>
       <c r="F86" s="12"/>
@@ -30724,7 +30748,7 @@
         <v>15.0</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E87" s="14"/>
       <c r="F87" s="12"/>
@@ -30758,7 +30782,7 @@
         <v>14.0</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E89" s="14"/>
       <c r="F89" s="12"/>
@@ -30809,7 +30833,7 @@
         <v>13.0</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E92" s="14"/>
       <c r="F92" s="12"/>
@@ -30826,7 +30850,7 @@
         <v>13.0</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E93" s="14"/>
       <c r="F93" s="12"/>
@@ -30966,12 +30990,12 @@
         <v>9.0</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E101" s="14"/>
       <c r="F101" s="12"/>
       <c r="G101" s="11" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="102">
@@ -30985,7 +31009,7 @@
         <v>9.0</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E102" s="14"/>
       <c r="F102" s="12"/>
@@ -31199,7 +31223,7 @@
         <v>2.0</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="E114" s="14"/>
       <c r="F114" s="12"/>
@@ -31216,7 +31240,7 @@
         <v>1.0</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="12"/>
@@ -31307,7 +31331,7 @@
         <v>13.0</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E120" s="17" t="s">
         <v>157</v>
@@ -31316,7 +31340,7 @@
         <v>46481.0</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="121">
@@ -31330,7 +31354,7 @@
         <v>13.0</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>157</v>
@@ -31408,7 +31432,7 @@
         <v>4.0</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="12"/>
@@ -31463,7 +31487,7 @@
         <v>16.0</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>246</v>
@@ -31482,7 +31506,7 @@
         <v>16.0</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E129" s="14" t="s">
         <v>249</v>
@@ -31501,7 +31525,7 @@
         <v>16.0</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E130" s="14" t="s">
         <v>246</v>
@@ -31520,7 +31544,7 @@
         <v>12.0</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>194</v>
@@ -31541,7 +31565,7 @@
         <v>12.0</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>199</v>
@@ -31579,7 +31603,7 @@
         <v>12.0</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E134" s="14"/>
       <c r="F134" s="12"/>
@@ -31991,7 +32015,7 @@
         <v>307</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
@@ -32161,7 +32185,7 @@
         <v>8.0</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E166" s="17" t="s">
         <v>326</v>
@@ -32202,7 +32226,7 @@
         <v>330</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
@@ -32275,7 +32299,7 @@
         <v>6.0</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E172" s="17" t="s">
         <v>37</v>
@@ -32431,7 +32455,7 @@
         <v>4.0</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E180" s="17" t="s">
         <v>558</v>
@@ -32450,10 +32474,10 @@
         <v>4.0</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E181" s="17" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F181" s="12"/>
       <c r="G181" s="12"/>
@@ -32472,7 +32496,7 @@
         <v>90</v>
       </c>
       <c r="E182" s="17" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F182" s="12"/>
       <c r="G182" s="12"/>
@@ -32590,7 +32614,7 @@
         <v>317</v>
       </c>
       <c r="E188" s="17" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F188" s="12"/>
       <c r="G188" s="12"/>
@@ -32649,7 +32673,7 @@
         <v>371</v>
       </c>
       <c r="E191" s="14" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F191" s="12"/>
       <c r="G191" s="12"/>
@@ -32741,7 +32765,7 @@
         <v>1.0</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E196" s="17" t="s">
         <v>388</v>
@@ -32817,12 +32841,12 @@
         <v>22.0</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E200" s="14"/>
       <c r="F200" s="12"/>
       <c r="G200" s="11" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="201">
@@ -32916,7 +32940,7 @@
         <v>19.0</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E205" s="17" t="s">
         <v>407</v>
@@ -32954,7 +32978,7 @@
         <v>19.0</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E207" s="17" t="s">
         <v>16</v>
@@ -32976,7 +33000,7 @@
         <v>65</v>
       </c>
       <c r="E208" s="17" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F208" s="18">
         <v>46645.0</v>
@@ -32994,10 +33018,10 @@
         <v>17.0</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E209" s="17" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F209" s="18">
         <v>46663.0</v>
@@ -33015,14 +33039,14 @@
         <v>17.0</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E210" s="17" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F210" s="12"/>
       <c r="G210" s="11" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="211">
@@ -33093,7 +33117,7 @@
         <v>15.0</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E214" s="17" t="s">
         <v>407</v>
@@ -33211,7 +33235,7 @@
         <v>11.0</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E220" s="17" t="s">
         <v>418</v>
@@ -33230,7 +33254,7 @@
         <v>12.0</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E221" s="17" t="s">
         <v>37</v>
@@ -33310,7 +33334,7 @@
         <v>9.0</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E225" s="17" t="s">
         <v>430</v>
@@ -33355,7 +33379,7 @@
         <v>87</v>
       </c>
       <c r="E227" s="17" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F227" s="12"/>
       <c r="G227" s="12"/>
@@ -33371,10 +33395,10 @@
         <v>8.0</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E228" s="17" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F228" s="12"/>
       <c r="G228" s="12"/>
@@ -33412,7 +33436,7 @@
         <v>438</v>
       </c>
       <c r="E230" s="17" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F230" s="18">
         <v>46521.0</v>
@@ -33508,7 +33532,7 @@
         <v>5.0</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E235" s="17" t="s">
         <v>37</v>
@@ -33632,7 +33656,7 @@
         <v>463</v>
       </c>
       <c r="E242" s="14" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F242" s="12"/>
       <c r="G242" s="12"/>
@@ -33651,7 +33675,7 @@
         <v>465</v>
       </c>
       <c r="E243" s="14" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="F243" s="12"/>
       <c r="G243" s="12"/>
@@ -33724,7 +33748,7 @@
         <v>1.0</v>
       </c>
       <c r="D247" s="11" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E247" s="17" t="s">
         <v>393</v>
@@ -33766,7 +33790,7 @@
         <v>11.0</v>
       </c>
       <c r="D249" s="11" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E249" s="17" t="s">
         <v>16</v>
@@ -34146,10 +34170,10 @@
         <v>16.0</v>
       </c>
       <c r="D269" s="12" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E269" s="14" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F269" s="12"/>
       <c r="G269" s="12"/>
@@ -34165,10 +34189,10 @@
         <v>16.0</v>
       </c>
       <c r="D270" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E270" s="14" t="s">
         <v>1059</v>
-      </c>
-      <c r="E270" s="14" t="s">
-        <v>1058</v>
       </c>
       <c r="F270" s="12"/>
       <c r="G270" s="12"/>
@@ -34184,7 +34208,7 @@
         <v>15.0</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E271" s="14"/>
       <c r="F271" s="12"/>
@@ -34201,7 +34225,7 @@
         <v>15.0</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E272" s="14"/>
       <c r="F272" s="12"/>
@@ -34218,7 +34242,7 @@
         <v>15.0</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E273" s="17" t="s">
         <v>154</v>
@@ -34239,7 +34263,7 @@
         <v>14.0</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E274" s="14"/>
       <c r="F274" s="12"/>
@@ -34256,7 +34280,7 @@
         <v>12.0</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E275" s="14"/>
       <c r="F275" s="12"/>
@@ -34275,7 +34299,7 @@
         <v>12.0</v>
       </c>
       <c r="D276" s="12" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="E276" s="14" t="s">
         <v>194</v>
@@ -34296,10 +34320,10 @@
         <v>12.0</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E277" s="17" t="s">
-        <v>1067</v>
+        <v>964</v>
       </c>
       <c r="F277" s="12"/>
       <c r="G277" s="11" t="s">
@@ -34902,7 +34926,7 @@
         <v>1082</v>
       </c>
       <c r="E310" s="14" t="s">
-        <v>1067</v>
+        <v>964</v>
       </c>
       <c r="F310" s="12"/>
       <c r="G310" s="12"/>
@@ -35988,7 +36012,7 @@
         <v>3.0</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>40</v>
@@ -36005,7 +36029,7 @@
         <v>3.0</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>1106</v>
@@ -36957,7 +36981,7 @@
         <v>4.0</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="E425" s="3" t="s">
         <v>558</v>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7139" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7140" uniqueCount="1199">
   <si>
     <t>ID</t>
   </si>
@@ -2911,6 +2911,9 @@
   </si>
   <si>
     <t>CHSRM-SS</t>
+  </si>
+  <si>
+    <t>[異常] CHECK!</t>
   </si>
   <si>
     <t>ID1778744050012</t>
@@ -16098,10 +16101,13 @@
       <c r="G537" s="9">
         <v>46732.0</v>
       </c>
+      <c r="H537" s="2" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>32</v>
@@ -16113,7 +16119,7 @@
         <v>6.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>431</v>
@@ -16124,7 +16130,7 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>32</v>
@@ -16147,7 +16153,7 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>32</v>
@@ -16159,7 +16165,7 @@
         <v>4.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F540" s="3" t="s">
         <v>358</v>
@@ -16167,7 +16173,7 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>32</v>
@@ -16179,7 +16185,7 @@
         <v>1.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F541" s="3" t="s">
         <v>123</v>
@@ -16187,7 +16193,7 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>32</v>
@@ -16199,7 +16205,7 @@
         <v>2.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F542" s="3" t="s">
         <v>421</v>
@@ -16210,7 +16216,7 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>61</v>
@@ -16230,7 +16236,7 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>32</v>
@@ -16242,7 +16248,7 @@
         <v>8.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F544" s="3" t="s">
         <v>814</v>
@@ -16250,7 +16256,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>32</v>
@@ -16262,7 +16268,7 @@
         <v>8.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>371</v>
@@ -16270,7 +16276,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>61</v>
@@ -16282,7 +16288,7 @@
         <v>21.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F546" s="3" t="s">
         <v>484</v>
@@ -16290,7 +16296,7 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>32</v>
@@ -16313,7 +16319,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>61</v>
@@ -16333,7 +16339,7 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>32</v>
@@ -16348,7 +16354,7 @@
         <v>752</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G549" s="9">
         <v>46282.0</v>
@@ -16356,7 +16362,7 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>32</v>
@@ -16379,7 +16385,7 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>32</v>
@@ -29021,7 +29027,7 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>32</v>
@@ -29033,7 +29039,7 @@
         <v>6.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>431</v>
@@ -29044,7 +29050,7 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>32</v>
@@ -29067,7 +29073,7 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>32</v>
@@ -29079,7 +29085,7 @@
         <v>4.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F540" s="3" t="s">
         <v>358</v>
@@ -29087,7 +29093,7 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>32</v>
@@ -29099,7 +29105,7 @@
         <v>1.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F541" s="3" t="s">
         <v>123</v>
@@ -29107,7 +29113,7 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>32</v>
@@ -29119,7 +29125,7 @@
         <v>2.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F542" s="3" t="s">
         <v>421</v>
@@ -29130,7 +29136,7 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>61</v>
@@ -29150,7 +29156,7 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>32</v>
@@ -29162,7 +29168,7 @@
         <v>8.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F544" s="3" t="s">
         <v>814</v>
@@ -29170,7 +29176,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>32</v>
@@ -29182,7 +29188,7 @@
         <v>8.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>371</v>
@@ -29190,7 +29196,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>61</v>
@@ -29202,7 +29208,7 @@
         <v>21.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F546" s="3" t="s">
         <v>484</v>
@@ -29210,7 +29216,7 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>32</v>
@@ -29233,7 +29239,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>61</v>
@@ -29253,7 +29259,7 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>32</v>
@@ -29268,7 +29274,7 @@
         <v>752</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G549" s="9">
         <v>46282.0</v>
@@ -29276,7 +29282,7 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>32</v>
@@ -29299,7 +29305,7 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>32</v>
@@ -29820,22 +29826,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>988</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>987</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="2">
@@ -29875,22 +29881,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F1" s="12"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B2" s="13">
         <v>22.0</v>
@@ -29902,13 +29908,13 @@
         <v>2.0</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B3" s="13">
         <v>22.0</v>
@@ -29920,13 +29926,13 @@
         <v>2.0</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B4" s="13">
         <v>22.0</v>
@@ -29938,13 +29944,13 @@
         <v>2.0</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B5" s="13">
         <v>22.0</v>
@@ -29956,7 +29962,7 @@
         <v>2.0</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -29974,7 +29980,7 @@
         <v>2.0</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -29996,21 +30002,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B2" s="6">
         <v>22.0</v>
@@ -30019,12 +30025,12 @@
         <v>11.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B3" s="6">
         <v>22.0</v>
@@ -30033,7 +30039,7 @@
         <v>11.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="4">
@@ -30047,13 +30053,13 @@
         <v>5.0</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E4" s="22"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B5" s="6">
         <v>15.0</v>
@@ -30062,12 +30068,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
   </sheetData>
@@ -30088,25 +30094,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="2">
@@ -30232,7 +30238,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="9">
@@ -30308,7 +30314,7 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>37</v>
@@ -30368,7 +30374,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="12"/>
@@ -30384,7 +30390,7 @@
         <v>5.0</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>16</v>
@@ -30405,7 +30411,7 @@
         <v>5.0</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="12"/>
@@ -30441,7 +30447,7 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>358</v>
@@ -30460,7 +30466,7 @@
         <v>19.0</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>358</v>
@@ -30498,7 +30504,7 @@
         <v>18.0</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12"/>
@@ -30551,10 +30557,10 @@
         <v>17.0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -30621,7 +30627,7 @@
         <v>15.0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>70</v>
@@ -30718,7 +30724,7 @@
         <v>10.0</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>70</v>
@@ -30737,7 +30743,7 @@
         <v>9.0</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>70</v>
@@ -30756,7 +30762,7 @@
         <v>9.0</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>70</v>
@@ -30775,7 +30781,7 @@
         <v>8.0</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>70</v>
@@ -30832,7 +30838,7 @@
         <v>7.0</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>88</v>
@@ -30851,7 +30857,7 @@
         <v>7.0</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>88</v>
@@ -30870,7 +30876,7 @@
         <v>7.0</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>88</v>
@@ -30889,7 +30895,7 @@
         <v>7.0</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>88</v>
@@ -31058,7 +31064,7 @@
         <v>2.0</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>118</v>
@@ -31168,7 +31174,7 @@
         <v>1.0</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="12"/>
@@ -31365,7 +31371,7 @@
         <v>16.0</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>158</v>
@@ -31384,7 +31390,7 @@
         <v>16.0</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="12"/>
@@ -31401,7 +31407,7 @@
         <v>15.0</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>431</v>
@@ -31462,7 +31468,7 @@
         <v>13.0</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="E75" s="14"/>
       <c r="F75" s="12"/>
@@ -31479,7 +31485,7 @@
         <v>12.0</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>155</v>
@@ -31519,7 +31525,7 @@
         <v>9.0</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="E78" s="17">
         <v>11503.0</v>
@@ -31654,7 +31660,7 @@
         <v>1.0</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E85" s="14"/>
       <c r="F85" s="12"/>
@@ -31671,7 +31677,7 @@
         <v>15.0</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E86" s="14"/>
       <c r="F86" s="12"/>
@@ -31688,7 +31694,7 @@
         <v>15.0</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E87" s="14"/>
       <c r="F87" s="12"/>
@@ -31722,7 +31728,7 @@
         <v>14.0</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E89" s="14"/>
       <c r="F89" s="12"/>
@@ -31773,7 +31779,7 @@
         <v>13.0</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E92" s="14"/>
       <c r="F92" s="12"/>
@@ -31790,7 +31796,7 @@
         <v>13.0</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E93" s="14"/>
       <c r="F93" s="12"/>
@@ -31858,7 +31864,7 @@
         <v>11.0</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>249</v>
@@ -31913,7 +31919,7 @@
         <v>10.0</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E100" s="14"/>
       <c r="F100" s="12"/>
@@ -31930,12 +31936,12 @@
         <v>9.0</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E101" s="14"/>
       <c r="F101" s="12"/>
       <c r="G101" s="11" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="102">
@@ -31949,7 +31955,7 @@
         <v>9.0</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E102" s="14"/>
       <c r="F102" s="12"/>
@@ -32108,7 +32114,7 @@
         <v>6.0</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="E111" s="17">
         <v>11504.0</v>
@@ -32163,7 +32169,7 @@
         <v>2.0</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E114" s="14"/>
       <c r="F114" s="12"/>
@@ -32180,7 +32186,7 @@
         <v>1.0</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="12"/>
@@ -32216,7 +32222,7 @@
         <v>15.0</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E117" s="14"/>
       <c r="F117" s="12"/>
@@ -32271,7 +32277,7 @@
         <v>13.0</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E120" s="17" t="s">
         <v>155</v>
@@ -32280,7 +32286,7 @@
         <v>46481.0</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="121">
@@ -32294,7 +32300,7 @@
         <v>13.0</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>155</v>
@@ -32372,7 +32378,7 @@
         <v>4.0</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="12"/>
@@ -32427,7 +32433,7 @@
         <v>16.0</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>239</v>
@@ -32446,7 +32452,7 @@
         <v>16.0</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E129" s="14" t="s">
         <v>242</v>
@@ -32465,7 +32471,7 @@
         <v>16.0</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E130" s="14" t="s">
         <v>239</v>
@@ -32484,7 +32490,7 @@
         <v>12.0</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>192</v>
@@ -32505,7 +32511,7 @@
         <v>12.0</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>249</v>
@@ -32526,7 +32532,7 @@
         <v>12.0</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E133" s="14"/>
       <c r="F133" s="12"/>
@@ -32543,7 +32549,7 @@
         <v>12.0</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E134" s="14"/>
       <c r="F134" s="12"/>
@@ -32955,7 +32961,7 @@
         <v>302</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
@@ -33085,7 +33091,7 @@
         <v>8.0</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="E164" s="17" t="s">
         <v>316</v>
@@ -33125,7 +33131,7 @@
         <v>8.0</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E166" s="17" t="s">
         <v>320</v>
@@ -33166,7 +33172,7 @@
         <v>324</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
@@ -33239,7 +33245,7 @@
         <v>6.0</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E172" s="17" t="s">
         <v>37</v>
@@ -33395,7 +33401,7 @@
         <v>4.0</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E180" s="17" t="s">
         <v>539</v>
@@ -33414,10 +33420,10 @@
         <v>4.0</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E181" s="17" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F181" s="12"/>
       <c r="G181" s="12"/>
@@ -33436,7 +33442,7 @@
         <v>87</v>
       </c>
       <c r="E182" s="17" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F182" s="12"/>
       <c r="G182" s="12"/>
@@ -33535,7 +33541,7 @@
         <v>312</v>
       </c>
       <c r="E187" s="17" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F187" s="12"/>
       <c r="G187" s="12"/>
@@ -33554,7 +33560,7 @@
         <v>312</v>
       </c>
       <c r="E188" s="17" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F188" s="12"/>
       <c r="G188" s="12"/>
@@ -33705,7 +33711,7 @@
         <v>1.0</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E196" s="17" t="s">
         <v>383</v>
@@ -33781,12 +33787,12 @@
         <v>22.0</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E200" s="14"/>
       <c r="F200" s="12"/>
       <c r="G200" s="11" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="201">
@@ -33880,7 +33886,7 @@
         <v>19.0</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E205" s="17" t="s">
         <v>400</v>
@@ -33918,7 +33924,7 @@
         <v>19.0</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E207" s="17" t="s">
         <v>16</v>
@@ -33940,7 +33946,7 @@
         <v>62</v>
       </c>
       <c r="E208" s="17" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F208" s="18">
         <v>46645.0</v>
@@ -33958,10 +33964,10 @@
         <v>17.0</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E209" s="17" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F209" s="18">
         <v>46663.0</v>
@@ -33979,14 +33985,14 @@
         <v>17.0</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E210" s="17" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F210" s="12"/>
       <c r="G210" s="11" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="211">
@@ -34057,7 +34063,7 @@
         <v>15.0</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="E214" s="17" t="s">
         <v>400</v>
@@ -34175,7 +34181,7 @@
         <v>11.0</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E220" s="17" t="s">
         <v>411</v>
@@ -34194,7 +34200,7 @@
         <v>12.0</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E221" s="17" t="s">
         <v>37</v>
@@ -34213,7 +34219,7 @@
         <v>11.0</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E222" s="14" t="s">
         <v>281</v>
@@ -34274,7 +34280,7 @@
         <v>9.0</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E225" s="17" t="s">
         <v>421</v>
@@ -34295,7 +34301,7 @@
         <v>9.0</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E226" s="14" t="s">
         <v>397</v>
@@ -34316,10 +34322,10 @@
         <v>8.0</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E227" s="17" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F227" s="12"/>
       <c r="G227" s="12"/>
@@ -34335,10 +34341,10 @@
         <v>8.0</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E228" s="17" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F228" s="12"/>
       <c r="G228" s="12"/>
@@ -34354,7 +34360,7 @@
         <v>7.0</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E229" s="17" t="s">
         <v>397</v>
@@ -34376,7 +34382,7 @@
         <v>428</v>
       </c>
       <c r="E230" s="17" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F230" s="18">
         <v>46521.0</v>
@@ -34472,7 +34478,7 @@
         <v>5.0</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E235" s="17" t="s">
         <v>37</v>
@@ -34650,7 +34656,7 @@
         <v>7.0</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E245" s="17" t="s">
         <v>431</v>
@@ -34688,14 +34694,14 @@
         <v>1.0</v>
       </c>
       <c r="D247" s="11" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E247" s="17" t="s">
         <v>281</v>
       </c>
       <c r="F247" s="12"/>
       <c r="G247" s="11" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="248">
@@ -34709,14 +34715,14 @@
         <v>10.0</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E248" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F248" s="12"/>
       <c r="G248" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="249">
@@ -34730,7 +34736,7 @@
         <v>11.0</v>
       </c>
       <c r="D249" s="11" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E249" s="17" t="s">
         <v>16</v>
@@ -34756,7 +34762,7 @@
       </c>
       <c r="F250" s="12"/>
       <c r="G250" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="251">
@@ -34777,7 +34783,7 @@
       </c>
       <c r="F251" s="12"/>
       <c r="G251" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="252">
@@ -34800,7 +34806,7 @@
         <v>46347.0</v>
       </c>
       <c r="G252" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="253">
@@ -34821,7 +34827,7 @@
       </c>
       <c r="F253" s="12"/>
       <c r="G253" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="254">
@@ -34835,14 +34841,14 @@
         <v>22.0</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E254" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F254" s="12"/>
       <c r="G254" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="255">
@@ -34863,7 +34869,7 @@
       </c>
       <c r="F255" s="12"/>
       <c r="G255" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="256">
@@ -34968,7 +34974,7 @@
         <v>21.0</v>
       </c>
       <c r="D261" s="12" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E261" s="14"/>
       <c r="F261" s="12"/>
@@ -35023,7 +35029,7 @@
         <v>19.0</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E264" s="14"/>
       <c r="F264" s="12"/>
@@ -35110,10 +35116,10 @@
         <v>16.0</v>
       </c>
       <c r="D269" s="12" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E269" s="14" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F269" s="12"/>
       <c r="G269" s="12"/>
@@ -35129,10 +35135,10 @@
         <v>16.0</v>
       </c>
       <c r="D270" s="12" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E270" s="14" t="s">
         <v>1101</v>
-      </c>
-      <c r="E270" s="14" t="s">
-        <v>1100</v>
       </c>
       <c r="F270" s="12"/>
       <c r="G270" s="12"/>
@@ -35148,7 +35154,7 @@
         <v>15.0</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E271" s="14"/>
       <c r="F271" s="12"/>
@@ -35165,7 +35171,7 @@
         <v>15.0</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="E272" s="14"/>
       <c r="F272" s="12"/>
@@ -35182,7 +35188,7 @@
         <v>15.0</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="E273" s="17" t="s">
         <v>152</v>
@@ -35203,7 +35209,7 @@
         <v>14.0</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E274" s="14"/>
       <c r="F274" s="12"/>
@@ -35220,7 +35226,7 @@
         <v>12.0</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="E275" s="14"/>
       <c r="F275" s="12"/>
@@ -35239,7 +35245,7 @@
         <v>12.0</v>
       </c>
       <c r="D276" s="12" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="E276" s="14" t="s">
         <v>192</v>
@@ -35260,10 +35266,10 @@
         <v>12.0</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E277" s="17" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F277" s="12"/>
       <c r="G277" s="11" t="s">
@@ -35404,7 +35410,7 @@
         <v>505</v>
       </c>
       <c r="E284" s="14" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F284" s="12"/>
       <c r="G284" s="12"/>
@@ -35437,10 +35443,10 @@
         <v>22.0</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E286" s="17" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F286" s="12"/>
       <c r="G286" s="12"/>
@@ -35490,7 +35496,7 @@
         <v>21.0</v>
       </c>
       <c r="D289" s="12" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E289" s="14" t="s">
         <v>128</v>
@@ -35509,7 +35515,7 @@
         <v>20.0</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E290" s="14"/>
       <c r="F290" s="12"/>
@@ -35526,7 +35532,7 @@
         <v>20.0</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E291" s="14" t="s">
         <v>431</v>
@@ -35649,12 +35655,12 @@
         <v>18.0</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E298" s="14"/>
       <c r="F298" s="12"/>
       <c r="G298" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="299">
@@ -35755,7 +35761,7 @@
         <v>16.0</v>
       </c>
       <c r="D304" s="12" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E304" s="14"/>
       <c r="F304" s="12"/>
@@ -35772,7 +35778,7 @@
         <v>16.0</v>
       </c>
       <c r="D305" s="12" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E305" s="14"/>
       <c r="F305" s="12"/>
@@ -35789,10 +35795,10 @@
         <v>16.0</v>
       </c>
       <c r="D306" s="12" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E306" s="14" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F306" s="12"/>
       <c r="G306" s="12"/>
@@ -35808,10 +35814,10 @@
         <v>16.0</v>
       </c>
       <c r="D307" s="12" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="E307" s="14" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F307" s="12"/>
       <c r="G307" s="12"/>
@@ -35844,7 +35850,7 @@
         <v>15.0</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="E309" s="14" t="s">
         <v>155</v>
@@ -35863,10 +35869,10 @@
         <v>15.0</v>
       </c>
       <c r="D310" s="12" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E310" s="14" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F310" s="12"/>
       <c r="G310" s="12"/>
@@ -35882,7 +35888,7 @@
         <v>15.0</v>
       </c>
       <c r="D311" s="12" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="E311" s="14"/>
       <c r="F311" s="12"/>
@@ -35899,7 +35905,7 @@
         <v>15.0</v>
       </c>
       <c r="D312" s="12" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E312" s="14"/>
       <c r="F312" s="12"/>
@@ -35916,7 +35922,7 @@
         <v>15.0</v>
       </c>
       <c r="D313" s="12" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E313" s="14"/>
       <c r="F313" s="12"/>
@@ -35992,7 +35998,7 @@
         <v>22.0</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E317" s="14"/>
       <c r="F317" s="12"/>
@@ -36047,7 +36053,7 @@
         <v>22.0</v>
       </c>
       <c r="D320" s="11" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E320" s="17">
         <v>11503.0</v>
@@ -36056,7 +36062,7 @@
         <v>46543.0</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="321">
@@ -36096,7 +36102,7 @@
       </c>
       <c r="F322" s="12"/>
       <c r="G322" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="323">
@@ -36129,7 +36135,7 @@
         <v>11.0</v>
       </c>
       <c r="D324" s="11" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E324" s="17">
         <v>11503.0</v>
@@ -36227,7 +36233,7 @@
         <v>7.0</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>572</v>
@@ -36247,7 +36253,7 @@
         <v>7.0</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>572</v>
@@ -36330,7 +36336,7 @@
         <v>8.0</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>572</v>
@@ -36367,7 +36373,7 @@
         <v>8.0</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>577</v>
@@ -36447,7 +36453,7 @@
         <v>8.0</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>577</v>
@@ -36467,7 +36473,7 @@
         <v>8.0</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>577</v>
@@ -36507,7 +36513,7 @@
         <v>17.0</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E343" s="3">
         <v>11305.0</v>
@@ -36524,7 +36530,7 @@
         <v>8.0</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>16</v>
@@ -36576,7 +36582,7 @@
         <v>6.0</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E347" s="3">
         <v>11503.0</v>
@@ -36593,7 +36599,7 @@
         <v>10.0</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E348" s="3">
         <v>11502.0</v>
@@ -36610,7 +36616,7 @@
         <v>10.0</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E349" s="3">
         <v>11502.0</v>
@@ -36627,7 +36633,7 @@
         <v>21.0</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>16</v>
@@ -36691,7 +36697,7 @@
         <v>8.0</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>585</v>
@@ -36711,10 +36717,10 @@
         <v>6.0</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="355">
@@ -36728,7 +36734,7 @@
         <v>3.0</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>431</v>
@@ -36765,7 +36771,7 @@
         <v>11.0</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E357" s="4"/>
       <c r="G357" s="2" t="s">
@@ -36801,7 +36807,7 @@
         <v>11.0</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E359" s="3">
         <v>11503.0</v>
@@ -36865,7 +36871,7 @@
         <v>21.0</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E363" s="4"/>
     </row>
@@ -36889,7 +36895,7 @@
         <v>46395.0</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="365">
@@ -36903,7 +36909,7 @@
         <v>10.0</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="E365" s="4"/>
     </row>
@@ -36918,7 +36924,7 @@
         <v>1.0</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>16</v>
@@ -36938,7 +36944,7 @@
         <v>592</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="368">
@@ -36972,7 +36978,7 @@
         <v>834</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="370">
@@ -37023,7 +37029,7 @@
         <v>936</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F372" s="9">
         <v>46676.0</v>
@@ -37211,7 +37217,7 @@
         <v>15.0</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="E384" s="3">
         <v>11412.0</v>
@@ -37245,10 +37251,10 @@
         <v>19.0</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="387">
@@ -37262,7 +37268,7 @@
         <v>19.0</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>358</v>
@@ -37330,7 +37336,7 @@
         <v>14.0</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>607</v>
@@ -37409,7 +37415,7 @@
         <v>15.0</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>281</v>
@@ -37426,7 +37432,7 @@
         <v>4.0</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="E397" s="3" t="s">
         <v>236</v>
@@ -37443,7 +37449,7 @@
         <v>10.0</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>37</v>
@@ -37514,7 +37520,7 @@
         <v>8.0</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>431</v>
@@ -37583,7 +37589,7 @@
         <v>16.0</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>620</v>
@@ -37634,7 +37640,7 @@
         <v>8.0</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>624</v>
@@ -37668,7 +37674,7 @@
         <v>17.0</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>627</v>
@@ -37702,7 +37708,7 @@
         <v>9.0</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E413" s="3">
         <v>11504.0</v>
@@ -37737,7 +37743,7 @@
         <v>3.0</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>236</v>
@@ -37791,7 +37797,7 @@
         <v>19.0</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>514</v>
@@ -37831,7 +37837,7 @@
         <v>10.0</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E420" s="4"/>
     </row>
@@ -37846,7 +37852,7 @@
         <v>11.0</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="E421" s="4"/>
     </row>
@@ -37901,7 +37907,7 @@
         <v>4.0</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>16</v>
@@ -37992,7 +37998,7 @@
         <v>17.0</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>192</v>
@@ -38181,13 +38187,13 @@
         <v>19.0</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G439" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="440">
@@ -38201,7 +38207,7 @@
         <v>19.0</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E440" s="3" t="s">
         <v>506</v>
@@ -38235,7 +38241,7 @@
         <v>2.0</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>146</v>
@@ -39193,10 +39199,10 @@
         <v>17.0</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="F491" s="9">
         <v>46247.0</v>
@@ -39247,7 +39253,7 @@
         <v>8.0</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E494" s="4"/>
       <c r="F494" s="9">
@@ -39265,7 +39271,7 @@
         <v>18.0</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E495" s="3" t="s">
         <v>236</v>
@@ -39376,7 +39382,7 @@
         <v>9.0</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E501" s="3" t="s">
         <v>431</v>
@@ -39430,7 +39436,7 @@
         <v>13.0</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E504" s="4"/>
     </row>
@@ -39445,7 +39451,7 @@
         <v>13.0</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E505" s="4"/>
     </row>
@@ -39460,7 +39466,7 @@
         <v>12.0</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E506" s="4"/>
       <c r="G506" s="2" t="s">
@@ -39478,7 +39484,7 @@
         <v>15.0</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E507" s="4"/>
     </row>
@@ -39493,7 +39499,7 @@
         <v>15.0</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E508" s="4"/>
     </row>
@@ -39508,7 +39514,7 @@
         <v>15.0</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E509" s="4"/>
     </row>
@@ -39523,7 +39529,7 @@
         <v>15.0</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E510" s="4"/>
     </row>
@@ -39538,7 +39544,7 @@
         <v>15.0</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E511" s="4"/>
     </row>
@@ -39553,7 +39559,7 @@
         <v>15.0</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E512" s="4"/>
     </row>
@@ -39568,7 +39574,7 @@
         <v>15.0</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E513" s="4"/>
     </row>
@@ -39583,7 +39589,7 @@
         <v>15.0</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E514" s="4"/>
     </row>
@@ -39598,7 +39604,7 @@
         <v>17.0</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E515" s="3" t="s">
         <v>627</v>
@@ -39666,7 +39672,7 @@
         <v>16.0</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E519" s="4"/>
     </row>
@@ -39681,7 +39687,7 @@
         <v>14.0</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E520" s="4"/>
     </row>
@@ -39696,7 +39702,7 @@
         <v>14.0</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E521" s="4"/>
     </row>
@@ -39711,7 +39717,7 @@
         <v>14.0</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E522" s="4"/>
     </row>
@@ -39726,7 +39732,7 @@
         <v>14.0</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E523" s="3" t="s">
         <v>572</v>
@@ -39919,7 +39925,7 @@
         <v>14.0</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="E533" s="3" t="s">
         <v>716</v>
@@ -39939,7 +39945,7 @@
         <v>16.0</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E534" s="3" t="s">
         <v>152</v>
@@ -39959,7 +39965,7 @@
         <v>16.0</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="E535" s="3" t="s">
         <v>152</v>
@@ -39982,7 +39988,7 @@
         <v>936</v>
       </c>
       <c r="E536" s="3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F536" s="9">
         <v>46725.0</v>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7627" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7637" uniqueCount="1384">
   <si>
     <t>ID</t>
   </si>
@@ -3355,6 +3355,12 @@
   </si>
   <si>
     <t>M89SRL-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779719332195</t>
+  </si>
+  <si>
+    <t>KR-MP</t>
   </si>
   <si>
     <t>日期時間</t>
@@ -18044,8 +18050,27 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="19"/>
-      <c r="F599" s="4"/>
+      <c r="A599" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D599" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E599" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F599" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="G599" s="9">
+        <v>46769.0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="19"/>
@@ -31695,8 +31720,27 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="19"/>
-      <c r="F599" s="4"/>
+      <c r="A599" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D599" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E599" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F599" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="G599" s="9">
+        <v>46769.0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="19"/>
@@ -31834,22 +31878,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="2">
@@ -31889,22 +31933,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="F1" s="12"/>
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B2" s="13">
         <v>22.0</v>
@@ -31916,13 +31960,13 @@
         <v>2.0</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B3" s="13">
         <v>22.0</v>
@@ -31934,13 +31978,13 @@
         <v>2.0</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B4" s="13">
         <v>22.0</v>
@@ -31952,13 +31996,13 @@
         <v>2.0</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B5" s="13">
         <v>22.0</v>
@@ -31970,7 +32014,7 @@
         <v>2.0</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -31988,7 +32032,7 @@
         <v>2.0</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="F6" s="12"/>
     </row>
@@ -32010,21 +32054,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B2" s="6">
         <v>22.0</v>
@@ -32033,12 +32077,12 @@
         <v>11.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B3" s="6">
         <v>22.0</v>
@@ -32047,7 +32091,7 @@
         <v>11.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="4">
@@ -32061,13 +32105,13 @@
         <v>5.0</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E4" s="22"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B5" s="6">
         <v>15.0</v>
@@ -32076,12 +32120,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
   </sheetData>
@@ -32102,25 +32146,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="2">
@@ -32246,7 +32290,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="9">
@@ -32322,7 +32366,7 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>37</v>
@@ -32382,7 +32426,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="F16" s="15"/>
       <c r="G16" s="12"/>
@@ -32398,7 +32442,7 @@
         <v>5.0</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>16</v>
@@ -32419,7 +32463,7 @@
         <v>5.0</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="12"/>
@@ -32455,7 +32499,7 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>345</v>
@@ -32474,7 +32518,7 @@
         <v>19.0</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>345</v>
@@ -32512,7 +32556,7 @@
         <v>18.0</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12"/>
@@ -32565,10 +32609,10 @@
         <v>17.0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -32584,7 +32628,7 @@
         <v>17.0</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="12"/>
@@ -32635,7 +32679,7 @@
         <v>15.0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>64</v>
@@ -32732,7 +32776,7 @@
         <v>10.0</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>64</v>
@@ -32751,7 +32795,7 @@
         <v>9.0</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>64</v>
@@ -32770,7 +32814,7 @@
         <v>9.0</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>64</v>
@@ -32789,7 +32833,7 @@
         <v>8.0</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>64</v>
@@ -32846,7 +32890,7 @@
         <v>7.0</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>82</v>
@@ -32865,7 +32909,7 @@
         <v>7.0</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>82</v>
@@ -32884,7 +32928,7 @@
         <v>7.0</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>82</v>
@@ -32903,7 +32947,7 @@
         <v>7.0</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>82</v>
@@ -33072,7 +33116,7 @@
         <v>2.0</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>113</v>
@@ -33182,7 +33226,7 @@
         <v>1.0</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="12"/>
@@ -33360,10 +33404,10 @@
         <v>18.0</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
@@ -33379,7 +33423,7 @@
         <v>16.0</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>147</v>
@@ -33398,7 +33442,7 @@
         <v>16.0</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="12"/>
@@ -33415,7 +33459,7 @@
         <v>15.0</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>419</v>
@@ -33434,7 +33478,7 @@
         <v>14.0</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>680</v>
@@ -33476,7 +33520,7 @@
         <v>13.0</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="E75" s="14"/>
       <c r="F75" s="12"/>
@@ -33493,7 +33537,7 @@
         <v>12.0</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="E76" s="17" t="s">
         <v>144</v>
@@ -33533,7 +33577,7 @@
         <v>9.0</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="E78" s="17">
         <v>11503.0</v>
@@ -33668,7 +33712,7 @@
         <v>1.0</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E85" s="14"/>
       <c r="F85" s="12"/>
@@ -33685,7 +33729,7 @@
         <v>15.0</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="E86" s="14"/>
       <c r="F86" s="12"/>
@@ -33702,7 +33746,7 @@
         <v>15.0</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="E87" s="14"/>
       <c r="F87" s="12"/>
@@ -33736,7 +33780,7 @@
         <v>14.0</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="E89" s="14"/>
       <c r="F89" s="12"/>
@@ -33787,7 +33831,7 @@
         <v>13.0</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="E92" s="14"/>
       <c r="F92" s="12"/>
@@ -33804,7 +33848,7 @@
         <v>13.0</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="E93" s="14"/>
       <c r="F93" s="12"/>
@@ -33838,7 +33882,7 @@
         <v>11.0</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="E95" s="14"/>
       <c r="F95" s="12"/>
@@ -33855,7 +33899,7 @@
         <v>11.0</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="E96" s="14"/>
       <c r="F96" s="12"/>
@@ -33872,7 +33916,7 @@
         <v>11.0</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>239</v>
@@ -33910,7 +33954,7 @@
         <v>10.0</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="E99" s="14"/>
       <c r="F99" s="12"/>
@@ -33927,7 +33971,7 @@
         <v>10.0</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E100" s="14"/>
       <c r="F100" s="12"/>
@@ -33944,12 +33988,12 @@
         <v>9.0</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="E101" s="14"/>
       <c r="F101" s="12"/>
       <c r="G101" s="11" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="102">
@@ -33963,7 +34007,7 @@
         <v>9.0</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="E102" s="14"/>
       <c r="F102" s="12"/>
@@ -33980,7 +34024,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="E103" s="14"/>
       <c r="F103" s="12"/>
@@ -34122,7 +34166,7 @@
         <v>6.0</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E111" s="17">
         <v>11504.0</v>
@@ -34177,7 +34221,7 @@
         <v>2.0</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E114" s="14"/>
       <c r="F114" s="12"/>
@@ -34194,7 +34238,7 @@
         <v>1.0</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E115" s="14"/>
       <c r="F115" s="12"/>
@@ -34230,7 +34274,7 @@
         <v>15.0</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E117" s="14"/>
       <c r="F117" s="12"/>
@@ -34285,7 +34329,7 @@
         <v>13.0</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E120" s="17" t="s">
         <v>144</v>
@@ -34294,7 +34338,7 @@
         <v>46481.0</v>
       </c>
       <c r="G120" s="11" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="121">
@@ -34308,7 +34352,7 @@
         <v>13.0</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>144</v>
@@ -34386,7 +34430,7 @@
         <v>4.0</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E125" s="14"/>
       <c r="F125" s="12"/>
@@ -34441,7 +34485,7 @@
         <v>16.0</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>226</v>
@@ -34460,7 +34504,7 @@
         <v>16.0</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="E129" s="14" t="s">
         <v>230</v>
@@ -34479,7 +34523,7 @@
         <v>16.0</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="E130" s="14" t="s">
         <v>226</v>
@@ -34498,7 +34542,7 @@
         <v>12.0</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>236</v>
@@ -34519,7 +34563,7 @@
         <v>12.0</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>239</v>
@@ -34540,7 +34584,7 @@
         <v>12.0</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E133" s="14"/>
       <c r="F133" s="12"/>
@@ -34557,7 +34601,7 @@
         <v>12.0</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="E134" s="14"/>
       <c r="F134" s="12"/>
@@ -34688,7 +34732,7 @@
         <v>11.0</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="E141" s="14"/>
       <c r="F141" s="12"/>
@@ -34813,7 +34857,7 @@
         <v>16.0</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="E148" s="14"/>
       <c r="F148" s="12"/>
@@ -34830,7 +34874,7 @@
         <v>16.0</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E149" s="14"/>
       <c r="F149" s="12"/>
@@ -34847,7 +34891,7 @@
         <v>16.0</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E150" s="14"/>
       <c r="F150" s="12"/>
@@ -34864,7 +34908,7 @@
         <v>16.0</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E151" s="14"/>
       <c r="F151" s="12"/>
@@ -34898,7 +34942,7 @@
         <v>12.0</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="E153" s="14"/>
       <c r="F153" s="12"/>
@@ -34915,7 +34959,7 @@
         <v>12.0</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="E154" s="14"/>
       <c r="F154" s="12"/>
@@ -34969,7 +35013,7 @@
         <v>291</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
@@ -35099,7 +35143,7 @@
         <v>8.0</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="E164" s="17" t="s">
         <v>305</v>
@@ -35139,7 +35183,7 @@
         <v>8.0</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="E166" s="17" t="s">
         <v>309</v>
@@ -35180,7 +35224,7 @@
         <v>313</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
@@ -35253,7 +35297,7 @@
         <v>6.0</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="E172" s="17" t="s">
         <v>37</v>
@@ -35409,7 +35453,7 @@
         <v>4.0</v>
       </c>
       <c r="D180" s="11" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E180" s="17" t="s">
         <v>520</v>
@@ -35428,10 +35472,10 @@
         <v>4.0</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E181" s="17" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="F181" s="12"/>
       <c r="G181" s="12"/>
@@ -35450,7 +35494,7 @@
         <v>81</v>
       </c>
       <c r="E182" s="17" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="F182" s="12"/>
       <c r="G182" s="12"/>
@@ -35549,7 +35593,7 @@
         <v>301</v>
       </c>
       <c r="E187" s="17" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="F187" s="12"/>
       <c r="G187" s="12"/>
@@ -35568,7 +35612,7 @@
         <v>301</v>
       </c>
       <c r="E188" s="17" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="F188" s="12"/>
       <c r="G188" s="12"/>
@@ -35719,7 +35763,7 @@
         <v>1.0</v>
       </c>
       <c r="D196" s="11" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="E196" s="17" t="s">
         <v>370</v>
@@ -35795,12 +35839,12 @@
         <v>22.0</v>
       </c>
       <c r="D200" s="11" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E200" s="14"/>
       <c r="F200" s="12"/>
       <c r="G200" s="11" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="201">
@@ -35894,7 +35938,7 @@
         <v>19.0</v>
       </c>
       <c r="D205" s="11" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E205" s="17" t="s">
         <v>387</v>
@@ -35932,7 +35976,7 @@
         <v>19.0</v>
       </c>
       <c r="D207" s="11" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E207" s="17" t="s">
         <v>16</v>
@@ -35951,10 +35995,10 @@
         <v>21.0</v>
       </c>
       <c r="D208" s="11" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="E208" s="17" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F208" s="18">
         <v>46645.0</v>
@@ -35972,10 +36016,10 @@
         <v>17.0</v>
       </c>
       <c r="D209" s="11" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E209" s="17" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F209" s="18">
         <v>46663.0</v>
@@ -35993,14 +36037,14 @@
         <v>17.0</v>
       </c>
       <c r="D210" s="11" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="E210" s="17" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F210" s="12"/>
       <c r="G210" s="11" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="211">
@@ -36052,7 +36096,7 @@
         <v>15.0</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E213" s="17" t="s">
         <v>384</v>
@@ -36071,7 +36115,7 @@
         <v>15.0</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E214" s="17" t="s">
         <v>387</v>
@@ -36128,7 +36172,7 @@
         <v>14.0</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="E217" s="17" t="s">
         <v>16</v>
@@ -36189,7 +36233,7 @@
         <v>11.0</v>
       </c>
       <c r="D220" s="11" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E220" s="17" t="s">
         <v>398</v>
@@ -36208,7 +36252,7 @@
         <v>12.0</v>
       </c>
       <c r="D221" s="11" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="E221" s="17" t="s">
         <v>37</v>
@@ -36227,7 +36271,7 @@
         <v>11.0</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="E222" s="14" t="s">
         <v>271</v>
@@ -36267,7 +36311,7 @@
         <v>9.0</v>
       </c>
       <c r="D224" s="11" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E224" s="17" t="s">
         <v>223</v>
@@ -36288,7 +36332,7 @@
         <v>9.0</v>
       </c>
       <c r="D225" s="11" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E225" s="17" t="s">
         <v>408</v>
@@ -36309,7 +36353,7 @@
         <v>9.0</v>
       </c>
       <c r="D226" s="12" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="E226" s="14" t="s">
         <v>384</v>
@@ -36330,10 +36374,10 @@
         <v>8.0</v>
       </c>
       <c r="D227" s="11" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E227" s="17" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="F227" s="12"/>
       <c r="G227" s="12"/>
@@ -36349,10 +36393,10 @@
         <v>8.0</v>
       </c>
       <c r="D228" s="11" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E228" s="17" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F228" s="12"/>
       <c r="G228" s="12"/>
@@ -36368,7 +36412,7 @@
         <v>7.0</v>
       </c>
       <c r="D229" s="11" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="E229" s="17" t="s">
         <v>384</v>
@@ -36390,7 +36434,7 @@
         <v>416</v>
       </c>
       <c r="E230" s="17" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="F230" s="18">
         <v>46521.0</v>
@@ -36467,7 +36511,7 @@
         <v>5.0</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="E234" s="14" t="s">
         <v>384</v>
@@ -36486,7 +36530,7 @@
         <v>5.0</v>
       </c>
       <c r="D235" s="11" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E235" s="17" t="s">
         <v>37</v>
@@ -36539,7 +36583,7 @@
         <v>2.0</v>
       </c>
       <c r="D238" s="11" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E238" s="14"/>
       <c r="F238" s="12"/>
@@ -36590,7 +36634,7 @@
         <v>3.0</v>
       </c>
       <c r="D241" s="12" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="E241" s="14"/>
       <c r="F241" s="12"/>
@@ -36607,7 +36651,7 @@
         <v>3.0</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="E242" s="14" t="s">
         <v>911</v>
@@ -36626,7 +36670,7 @@
         <v>3.0</v>
       </c>
       <c r="D243" s="12" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E243" s="14" t="s">
         <v>909</v>
@@ -36645,7 +36689,7 @@
         <v>7.0</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E244" s="17" t="s">
         <v>419</v>
@@ -36664,7 +36708,7 @@
         <v>7.0</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E245" s="17" t="s">
         <v>419</v>
@@ -36702,14 +36746,14 @@
         <v>1.0</v>
       </c>
       <c r="D247" s="11" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E247" s="17" t="s">
         <v>271</v>
       </c>
       <c r="F247" s="12"/>
       <c r="G247" s="11" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="248">
@@ -36723,14 +36767,14 @@
         <v>10.0</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="E248" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F248" s="12"/>
       <c r="G248" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="249">
@@ -36744,7 +36788,7 @@
         <v>11.0</v>
       </c>
       <c r="D249" s="11" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E249" s="17" t="s">
         <v>16</v>
@@ -36770,7 +36814,7 @@
       </c>
       <c r="F250" s="12"/>
       <c r="G250" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="251">
@@ -36791,7 +36835,7 @@
       </c>
       <c r="F251" s="12"/>
       <c r="G251" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="252">
@@ -36814,7 +36858,7 @@
         <v>46347.0</v>
       </c>
       <c r="G252" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="253">
@@ -36835,7 +36879,7 @@
       </c>
       <c r="F253" s="12"/>
       <c r="G253" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="254">
@@ -36849,14 +36893,14 @@
         <v>22.0</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="E254" s="14" t="s">
         <v>16</v>
       </c>
       <c r="F254" s="12"/>
       <c r="G254" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="255">
@@ -36877,7 +36921,7 @@
       </c>
       <c r="F255" s="12"/>
       <c r="G255" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="256">
@@ -36982,7 +37026,7 @@
         <v>21.0</v>
       </c>
       <c r="D261" s="12" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E261" s="14"/>
       <c r="F261" s="12"/>
@@ -37037,7 +37081,7 @@
         <v>19.0</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="E264" s="14"/>
       <c r="F264" s="12"/>
@@ -37090,7 +37134,7 @@
         <v>17.0</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E267" s="14"/>
       <c r="F267" s="12"/>
@@ -37107,7 +37151,7 @@
         <v>17.0</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="E268" s="17"/>
       <c r="F268" s="12"/>
@@ -37124,10 +37168,10 @@
         <v>16.0</v>
       </c>
       <c r="D269" s="12" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E269" s="14" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F269" s="12"/>
       <c r="G269" s="12"/>
@@ -37143,10 +37187,10 @@
         <v>16.0</v>
       </c>
       <c r="D270" s="12" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E270" s="14" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="F270" s="12"/>
       <c r="G270" s="12"/>
@@ -37162,7 +37206,7 @@
         <v>15.0</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E271" s="14"/>
       <c r="F271" s="12"/>
@@ -37179,7 +37223,7 @@
         <v>15.0</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="E272" s="14"/>
       <c r="F272" s="12"/>
@@ -37196,7 +37240,7 @@
         <v>15.0</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E273" s="17" t="s">
         <v>680</v>
@@ -37217,7 +37261,7 @@
         <v>14.0</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="E274" s="14"/>
       <c r="F274" s="12"/>
@@ -37234,12 +37278,12 @@
         <v>12.0</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E275" s="14"/>
       <c r="F275" s="12"/>
       <c r="G275" s="11" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="276">
@@ -37253,14 +37297,14 @@
         <v>12.0</v>
       </c>
       <c r="D276" s="12" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="E276" s="14" t="s">
         <v>236</v>
       </c>
       <c r="F276" s="12"/>
       <c r="G276" s="11" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="277">
@@ -37274,14 +37318,14 @@
         <v>12.0</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E277" s="17" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F277" s="12"/>
       <c r="G277" s="11" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="278">
@@ -37295,7 +37339,7 @@
         <v>12.0</v>
       </c>
       <c r="D278" s="12" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E278" s="14" t="s">
         <v>239</v>
@@ -37304,7 +37348,7 @@
         <v>46478.0</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="279">
@@ -37418,7 +37462,7 @@
         <v>486</v>
       </c>
       <c r="E284" s="14" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="F284" s="12"/>
       <c r="G284" s="12"/>
@@ -37451,10 +37495,10 @@
         <v>22.0</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E286" s="17" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="F286" s="12"/>
       <c r="G286" s="12"/>
@@ -37504,7 +37548,7 @@
         <v>21.0</v>
       </c>
       <c r="D289" s="12" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E289" s="14" t="s">
         <v>123</v>
@@ -37523,7 +37567,7 @@
         <v>20.0</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E290" s="14"/>
       <c r="F290" s="12"/>
@@ -37540,7 +37584,7 @@
         <v>20.0</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E291" s="14" t="s">
         <v>419</v>
@@ -37629,7 +37673,7 @@
         <v>19.0</v>
       </c>
       <c r="D296" s="12" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E296" s="14"/>
       <c r="F296" s="12"/>
@@ -37646,7 +37690,7 @@
         <v>19.0</v>
       </c>
       <c r="D297" s="12" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E297" s="14"/>
       <c r="F297" s="12"/>
@@ -37663,12 +37707,12 @@
         <v>18.0</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E298" s="14"/>
       <c r="F298" s="12"/>
       <c r="G298" s="11" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="299">
@@ -37769,7 +37813,7 @@
         <v>16.0</v>
       </c>
       <c r="D304" s="12" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E304" s="14"/>
       <c r="F304" s="12"/>
@@ -37786,7 +37830,7 @@
         <v>16.0</v>
       </c>
       <c r="D305" s="12" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E305" s="14"/>
       <c r="F305" s="12"/>
@@ -37803,10 +37847,10 @@
         <v>16.0</v>
       </c>
       <c r="D306" s="12" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E306" s="14" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="F306" s="12"/>
       <c r="G306" s="12"/>
@@ -37822,10 +37866,10 @@
         <v>16.0</v>
       </c>
       <c r="D307" s="12" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E307" s="14" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="F307" s="12"/>
       <c r="G307" s="12"/>
@@ -37858,7 +37902,7 @@
         <v>15.0</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="E309" s="14" t="s">
         <v>144</v>
@@ -37877,10 +37921,10 @@
         <v>15.0</v>
       </c>
       <c r="D310" s="12" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E310" s="14" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="F310" s="12"/>
       <c r="G310" s="12"/>
@@ -37896,7 +37940,7 @@
         <v>15.0</v>
       </c>
       <c r="D311" s="12" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="E311" s="14"/>
       <c r="F311" s="12"/>
@@ -37913,7 +37957,7 @@
         <v>15.0</v>
       </c>
       <c r="D312" s="12" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E312" s="14"/>
       <c r="F312" s="12"/>
@@ -37930,7 +37974,7 @@
         <v>15.0</v>
       </c>
       <c r="D313" s="12" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E313" s="14"/>
       <c r="F313" s="12"/>
@@ -37947,14 +37991,14 @@
         <v>11.0</v>
       </c>
       <c r="D314" s="11" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="E314" s="17" t="s">
         <v>476</v>
       </c>
       <c r="F314" s="12"/>
       <c r="G314" s="11" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="315">
@@ -38006,7 +38050,7 @@
         <v>22.0</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E317" s="14"/>
       <c r="F317" s="12"/>
@@ -38061,7 +38105,7 @@
         <v>22.0</v>
       </c>
       <c r="D320" s="11" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="E320" s="17">
         <v>11503.0</v>
@@ -38070,7 +38114,7 @@
         <v>46543.0</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="321">
@@ -38110,7 +38154,7 @@
       </c>
       <c r="F322" s="12"/>
       <c r="G322" s="11" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="323">
@@ -38143,7 +38187,7 @@
         <v>11.0</v>
       </c>
       <c r="D324" s="11" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E324" s="17">
         <v>11503.0</v>
@@ -38162,7 +38206,7 @@
         <v>1.0</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>656</v>
@@ -38227,7 +38271,7 @@
         <v>46873.0</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="329">
@@ -38241,7 +38285,7 @@
         <v>7.0</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>551</v>
@@ -38261,7 +38305,7 @@
         <v>7.0</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>551</v>
@@ -38330,7 +38374,7 @@
         <v>46576.0</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="334">
@@ -38344,7 +38388,7 @@
         <v>8.0</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>551</v>
@@ -38381,7 +38425,7 @@
         <v>8.0</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>556</v>
@@ -38461,7 +38505,7 @@
         <v>8.0</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>556</v>
@@ -38481,7 +38525,7 @@
         <v>8.0</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>556</v>
@@ -38521,7 +38565,7 @@
         <v>17.0</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="E343" s="3">
         <v>11305.0</v>
@@ -38538,7 +38582,7 @@
         <v>8.0</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>16</v>
@@ -38590,7 +38634,7 @@
         <v>6.0</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E347" s="3">
         <v>11503.0</v>
@@ -38607,7 +38651,7 @@
         <v>10.0</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="E348" s="3">
         <v>11502.0</v>
@@ -38624,7 +38668,7 @@
         <v>10.0</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E349" s="3">
         <v>11502.0</v>
@@ -38641,7 +38685,7 @@
         <v>21.0</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>16</v>
@@ -38659,7 +38703,7 @@
         <v>11.0</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>476</v>
@@ -38668,7 +38712,7 @@
         <v>46442.0</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="352">
@@ -38691,7 +38735,7 @@
         <v>46337.0</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="353">
@@ -38705,7 +38749,7 @@
         <v>8.0</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>564</v>
@@ -38725,10 +38769,10 @@
         <v>6.0</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="355">
@@ -38742,7 +38786,7 @@
         <v>3.0</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>419</v>
@@ -38759,13 +38803,13 @@
         <v>4.0</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>384</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="357">
@@ -38779,11 +38823,11 @@
         <v>11.0</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E357" s="4"/>
       <c r="G357" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="358">
@@ -38797,11 +38841,11 @@
         <v>12.0</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E358" s="4"/>
       <c r="G358" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="359">
@@ -38815,7 +38859,7 @@
         <v>11.0</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="E359" s="3">
         <v>11503.0</v>
@@ -38879,7 +38923,7 @@
         <v>21.0</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="E363" s="4"/>
     </row>
@@ -38894,7 +38938,7 @@
         <v>12.0</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>568</v>
@@ -38903,7 +38947,7 @@
         <v>46395.0</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="365">
@@ -38917,7 +38961,7 @@
         <v>10.0</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E365" s="4"/>
     </row>
@@ -38932,7 +38976,7 @@
         <v>1.0</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>16</v>
@@ -38952,7 +38996,7 @@
         <v>570</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="368">
@@ -38986,7 +39030,7 @@
         <v>797</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="370">
@@ -39037,7 +39081,7 @@
         <v>890</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="F372" s="9">
         <v>46676.0</v>
@@ -39088,7 +39132,7 @@
         <v>7.0</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>419</v>
@@ -39105,7 +39149,7 @@
         <v>12.0</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E376" s="4"/>
     </row>
@@ -39180,7 +39224,7 @@
         <v>13.0</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="E381" s="4"/>
     </row>
@@ -39210,7 +39254,7 @@
         <v>13.0</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="E383" s="4"/>
     </row>
@@ -39225,7 +39269,7 @@
         <v>15.0</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E384" s="3">
         <v>11412.0</v>
@@ -39259,10 +39303,10 @@
         <v>19.0</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="387">
@@ -39276,7 +39320,7 @@
         <v>19.0</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>345</v>
@@ -39344,7 +39388,7 @@
         <v>14.0</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>583</v>
@@ -39423,7 +39467,7 @@
         <v>15.0</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="E396" s="3" t="s">
         <v>271</v>
@@ -39440,7 +39484,7 @@
         <v>4.0</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="E397" s="3" t="s">
         <v>223</v>
@@ -39457,7 +39501,7 @@
         <v>10.0</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E398" s="3" t="s">
         <v>37</v>
@@ -39580,7 +39624,7 @@
         <v>19.0</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="E405" s="3" t="s">
         <v>419</v>
@@ -39597,7 +39641,7 @@
         <v>16.0</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>595</v>
@@ -39648,7 +39692,7 @@
         <v>8.0</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>599</v>
@@ -39682,7 +39726,7 @@
         <v>17.0</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>602</v>
@@ -39716,7 +39760,7 @@
         <v>9.0</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E413" s="3">
         <v>11504.0</v>
@@ -39733,7 +39777,7 @@
         <v>2.0</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E414" s="3">
         <v>11504.0</v>
@@ -39751,7 +39795,7 @@
         <v>3.0</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>223</v>
@@ -39805,7 +39849,7 @@
         <v>19.0</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>495</v>
@@ -39845,7 +39889,7 @@
         <v>10.0</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E420" s="4"/>
     </row>
@@ -39860,7 +39904,7 @@
         <v>11.0</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="E421" s="4"/>
     </row>
@@ -39915,7 +39959,7 @@
         <v>4.0</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>16</v>
@@ -40006,7 +40050,7 @@
         <v>17.0</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>236</v>
@@ -40195,13 +40239,13 @@
         <v>19.0</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="G439" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="440">
@@ -40249,7 +40293,7 @@
         <v>2.0</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>141</v>
@@ -40495,10 +40539,10 @@
         <v>5.0</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="F455" s="9">
         <v>46515.0</v>
@@ -40655,7 +40699,7 @@
         <v>4.0</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="E463" s="3" t="s">
         <v>495</v>
@@ -40695,7 +40739,7 @@
         <v>4.0</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="E465" s="3" t="s">
         <v>495</v>
@@ -40715,7 +40759,7 @@
         <v>4.0</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="E466" s="3" t="s">
         <v>495</v>
@@ -40735,7 +40779,7 @@
         <v>4.0</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="E467" s="3" t="s">
         <v>495</v>
@@ -40815,7 +40859,7 @@
         <v>5.0</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E471" s="3" t="s">
         <v>495</v>
@@ -40835,7 +40879,7 @@
         <v>6.0</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="E472" s="3" t="s">
         <v>156</v>
@@ -40895,7 +40939,7 @@
         <v>8.0</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="E475" s="3" t="s">
         <v>656</v>
@@ -40915,7 +40959,7 @@
         <v>9.0</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="E476" s="3" t="s">
         <v>656</v>
@@ -40935,7 +40979,7 @@
         <v>11.0</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="E477" s="3" t="s">
         <v>656</v>
@@ -40958,7 +41002,7 @@
         <v>644</v>
       </c>
       <c r="E478" s="3" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="F478" s="9">
         <v>46162.0</v>
@@ -40978,7 +41022,7 @@
         <v>652</v>
       </c>
       <c r="E479" s="3" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="F479" s="9">
         <v>46144.0</v>
@@ -40998,7 +41042,7 @@
         <v>648</v>
       </c>
       <c r="E480" s="3" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="F480" s="9">
         <v>46165.0</v>
@@ -41015,10 +41059,10 @@
         <v>13.0</v>
       </c>
       <c r="D481" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E481" s="3" t="s">
         <v>1354</v>
-      </c>
-      <c r="E481" s="3" t="s">
-        <v>1352</v>
       </c>
       <c r="F481" s="9">
         <v>46165.0</v>
@@ -41055,7 +41099,7 @@
         <v>15.0</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="E483" s="3" t="s">
         <v>37</v>
@@ -41092,7 +41136,7 @@
         <v>15.0</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="E485" s="3" t="s">
         <v>156</v>
@@ -41112,7 +41156,7 @@
         <v>16.0</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="E486" s="3" t="s">
         <v>656</v>
@@ -41132,7 +41176,7 @@
         <v>17.0</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E487" s="3" t="s">
         <v>656</v>
@@ -41152,7 +41196,7 @@
         <v>17.0</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="E488" s="3" t="s">
         <v>37</v>
@@ -41261,7 +41305,7 @@
         <v>8.0</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E494" s="4"/>
       <c r="F494" s="9">
@@ -41279,7 +41323,7 @@
         <v>18.0</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="E495" s="3" t="s">
         <v>223</v>
@@ -41350,7 +41394,7 @@
         <v>10.0</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="E499" s="3" t="s">
         <v>419</v>
@@ -41390,7 +41434,7 @@
         <v>9.0</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="E501" s="3" t="s">
         <v>419</v>
@@ -41407,7 +41451,7 @@
         <v>9.0</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="E502" s="3" t="s">
         <v>419</v>
@@ -41444,7 +41488,7 @@
         <v>13.0</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="E504" s="4"/>
     </row>
@@ -41459,7 +41503,7 @@
         <v>13.0</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E505" s="4"/>
     </row>
@@ -41474,11 +41518,11 @@
         <v>12.0</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="E506" s="4"/>
       <c r="G506" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="507">
@@ -41492,7 +41536,7 @@
         <v>15.0</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="E507" s="4"/>
     </row>
@@ -41507,7 +41551,7 @@
         <v>15.0</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="E508" s="4"/>
     </row>
@@ -41522,7 +41566,7 @@
         <v>15.0</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="E509" s="4"/>
     </row>
@@ -41537,7 +41581,7 @@
         <v>15.0</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E510" s="4"/>
     </row>
@@ -41552,7 +41596,7 @@
         <v>15.0</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="E511" s="4"/>
     </row>
@@ -41567,7 +41611,7 @@
         <v>15.0</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="E512" s="4"/>
     </row>
@@ -41582,7 +41626,7 @@
         <v>15.0</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="E513" s="4"/>
     </row>
@@ -41597,7 +41641,7 @@
         <v>15.0</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="E514" s="4"/>
     </row>
@@ -41612,7 +41656,7 @@
         <v>17.0</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E515" s="3" t="s">
         <v>602</v>
@@ -41680,7 +41724,7 @@
         <v>16.0</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="E519" s="4"/>
     </row>
@@ -41695,7 +41739,7 @@
         <v>14.0</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="E520" s="4"/>
     </row>
@@ -41710,7 +41754,7 @@
         <v>14.0</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="E521" s="4"/>
     </row>
@@ -41725,7 +41769,7 @@
         <v>14.0</v>
       </c>
       <c r="D522" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="E522" s="4"/>
     </row>
@@ -41740,7 +41784,7 @@
         <v>14.0</v>
       </c>
       <c r="D523" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="E523" s="3" t="s">
         <v>551</v>
@@ -41933,7 +41977,7 @@
         <v>14.0</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="E533" s="3" t="s">
         <v>683</v>
@@ -41953,7 +41997,7 @@
         <v>16.0</v>
       </c>
       <c r="D534" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="E534" s="3" t="s">
         <v>680</v>
@@ -41973,7 +42017,7 @@
         <v>16.0</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="E535" s="3" t="s">
         <v>680</v>
@@ -41996,7 +42040,7 @@
         <v>890</v>
       </c>
       <c r="E536" s="3" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="F536" s="9">
         <v>46725.0</v>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1150">
   <si>
     <t>ID</t>
   </si>
@@ -1915,1287 +1915,1266 @@
     <t>26#30</t>
   </si>
   <si>
-    <t>CHRER-C-SS</t>
-  </si>
-  <si>
-    <t>25#33</t>
+    <t>PRRER-C-SS</t>
+  </si>
+  <si>
+    <t>26#39</t>
+  </si>
+  <si>
+    <t>PRTDL-C-SS</t>
+  </si>
+  <si>
+    <t>26#34</t>
+  </si>
+  <si>
+    <t>PRSTL-C-YK</t>
+  </si>
+  <si>
+    <t>26#8</t>
+  </si>
+  <si>
+    <t>無庫位</t>
+  </si>
+  <si>
+    <t>34B(34-36)</t>
+  </si>
+  <si>
+    <t>JUJM(退貨)</t>
+  </si>
+  <si>
+    <t>12Q</t>
+  </si>
+  <si>
+    <t>1150415K</t>
+  </si>
+  <si>
+    <t>1150413K</t>
+  </si>
+  <si>
+    <t>AD3</t>
+  </si>
+  <si>
+    <t>ADJM (豬肉)(5入)</t>
+  </si>
+  <si>
+    <t>SPT-10入</t>
+  </si>
+  <si>
+    <t>PRSRL-420-460-GO</t>
+  </si>
+  <si>
+    <t>PRRER-上林規-YK</t>
+  </si>
+  <si>
+    <t>PRRER-3cm-SS</t>
+  </si>
+  <si>
+    <t>PRRER-900-960-SS</t>
+  </si>
+  <si>
+    <t>ACRER-280-320-TY</t>
+  </si>
+  <si>
+    <t>PRRER-一開三-SS</t>
+  </si>
+  <si>
+    <t>PRRERB-GO</t>
+  </si>
+  <si>
+    <t>PRCER-GO</t>
+  </si>
+  <si>
+    <t>M89CER-橫十字切_KR</t>
+  </si>
+  <si>
+    <t>1150122S</t>
+  </si>
+  <si>
+    <t>[異常] 1p</t>
+  </si>
+  <si>
+    <t>GMB(骨）</t>
+  </si>
+  <si>
+    <t>GMB</t>
+  </si>
+  <si>
+    <t>1150210S</t>
+  </si>
+  <si>
+    <t>1150415S</t>
+  </si>
+  <si>
+    <t>JOB(26b)</t>
+  </si>
+  <si>
+    <t>ACOB-YK(8入)</t>
+  </si>
+  <si>
+    <t>1150417K</t>
+  </si>
+  <si>
+    <t>ID1776755440734</t>
+  </si>
+  <si>
+    <t>1150410K</t>
+  </si>
+  <si>
+    <t>ID1776755702626</t>
+  </si>
+  <si>
+    <t>PRCER-YK</t>
+  </si>
+  <si>
+    <t>1150409K</t>
+  </si>
+  <si>
+    <t>ID1776756005407</t>
+  </si>
+  <si>
+    <t>CHRER-280-320-SS</t>
+  </si>
+  <si>
+    <t>ID1776830939143</t>
+  </si>
+  <si>
+    <t>電商紙袋</t>
+  </si>
+  <si>
+    <t>ID1776831008384</t>
+  </si>
+  <si>
+    <t>手提袋 模型</t>
+  </si>
+  <si>
+    <t>ID1776831054260</t>
+  </si>
+  <si>
+    <t>火腿架</t>
+  </si>
+  <si>
+    <t>ID1776831067623</t>
+  </si>
+  <si>
+    <t>ID1776831077383</t>
+  </si>
+  <si>
+    <t>ID1776831088970</t>
+  </si>
+  <si>
+    <t>ID1776831133943</t>
+  </si>
+  <si>
+    <t>紙箱</t>
+  </si>
+  <si>
+    <t>ID1776917744376</t>
+  </si>
+  <si>
+    <t>ID1776917966118</t>
+  </si>
+  <si>
+    <t>M9SRL-KR</t>
+  </si>
+  <si>
+    <t>ID1776917982996</t>
+  </si>
+  <si>
+    <t>M9TDL-KR</t>
+  </si>
+  <si>
+    <t>1140702K</t>
+  </si>
+  <si>
+    <t>ID1776918100016</t>
+  </si>
+  <si>
+    <t>M89SRL-KR (牛肉)</t>
+  </si>
+  <si>
+    <t>ID1776918492764</t>
+  </si>
+  <si>
+    <t>TQ</t>
+  </si>
+  <si>
+    <t>ID1776918517934</t>
+  </si>
+  <si>
+    <t>B(30-34)</t>
+  </si>
+  <si>
+    <t>ID1776940880649</t>
+  </si>
+  <si>
+    <t>13S(零碼)(4入)(48P)</t>
+  </si>
+  <si>
+    <t>ID1776941556959</t>
+  </si>
+  <si>
+    <t>ACSRM-TY（報廢）</t>
+  </si>
+  <si>
+    <t>1131209K</t>
+  </si>
+  <si>
+    <t>[報廢]發綠 12.51K</t>
+  </si>
+  <si>
+    <t>ID1777281985428</t>
+  </si>
+  <si>
+    <t>PRSRM-SS-對切</t>
+  </si>
+  <si>
+    <t>ID1777286256898</t>
+  </si>
+  <si>
+    <t>PRRER-280-320-YK</t>
+  </si>
+  <si>
+    <t>1150513S</t>
+  </si>
+  <si>
+    <t>ID1777286953561</t>
+  </si>
+  <si>
+    <t>GF-CKM-TY (牛肉)(6入)</t>
+  </si>
+  <si>
+    <t>1150515K(26#6)</t>
+  </si>
+  <si>
+    <t>ID1777363414962</t>
+  </si>
+  <si>
+    <t>PRTDL-YK</t>
+  </si>
+  <si>
+    <t>1150427K</t>
+  </si>
+  <si>
+    <t>[異常] 轉凍</t>
+  </si>
+  <si>
+    <t>ID1777363429496</t>
+  </si>
+  <si>
+    <t>PRSRL-SS</t>
+  </si>
+  <si>
+    <t>ID1777363462065</t>
+  </si>
+  <si>
+    <t>ID1777363475957</t>
+  </si>
+  <si>
+    <t>ACOB-TY</t>
+  </si>
+  <si>
+    <t>ID1777433910575</t>
+  </si>
+  <si>
+    <t>PSRER-280-320</t>
+  </si>
+  <si>
+    <t>1140710S</t>
+  </si>
+  <si>
+    <t>ID1777434325087</t>
+  </si>
+  <si>
+    <t>1140616K</t>
+  </si>
+  <si>
+    <t>ID1777434731664</t>
+  </si>
+  <si>
+    <t>ID1777451610853</t>
+  </si>
+  <si>
+    <t>PRRERB-YK</t>
+  </si>
+  <si>
+    <t>ID1777451628937</t>
+  </si>
+  <si>
+    <t>PRSTL-YK</t>
+  </si>
+  <si>
+    <t>1150428K</t>
+  </si>
+  <si>
+    <t>ID1777515662732</t>
+  </si>
+  <si>
+    <t>35B(#35)</t>
+  </si>
+  <si>
+    <t>ID1777515763188</t>
+  </si>
+  <si>
+    <t>T(鴨里肌)(8入)</t>
+  </si>
+  <si>
+    <t>ID1777515842006</t>
+  </si>
+  <si>
+    <t>60S(5入)(60P)</t>
+  </si>
+  <si>
+    <t>ID1777518516282</t>
+  </si>
+  <si>
+    <t>M89SRL-280-320（報廢）</t>
+  </si>
+  <si>
+    <t>ID1777518552434</t>
+  </si>
+  <si>
+    <t>藥檢品</t>
+  </si>
+  <si>
+    <t>ID1777518604803</t>
+  </si>
+  <si>
+    <t>M67-CFT-ST（報廢）</t>
+  </si>
+  <si>
+    <t>ID1777518808060</t>
+  </si>
+  <si>
+    <t>M89RER-200-250-KR</t>
+  </si>
+  <si>
+    <t>ID1777519539807</t>
+  </si>
+  <si>
+    <t>PRRER-185-225-GO</t>
+  </si>
+  <si>
+    <t>1141016S</t>
+  </si>
+  <si>
+    <t>ID1777880359815</t>
+  </si>
+  <si>
+    <t>ID1777900723432</t>
+  </si>
+  <si>
+    <t>ADHS-4入</t>
+  </si>
+  <si>
+    <t>ID1777901415357</t>
+  </si>
+  <si>
+    <t>CHTDL-YK</t>
+  </si>
+  <si>
+    <t>ID1778041215011</t>
+  </si>
+  <si>
+    <t>1140425K</t>
+  </si>
+  <si>
+    <t>ID1778057927574</t>
+  </si>
+  <si>
+    <t>M67CFT-ST</t>
+  </si>
+  <si>
+    <t>24#5</t>
+  </si>
+  <si>
+    <t>ID1778057982808</t>
+  </si>
+  <si>
+    <t>M45SRL-ST</t>
+  </si>
+  <si>
+    <t>24#7</t>
+  </si>
+  <si>
+    <t>ID1778139472526</t>
+  </si>
+  <si>
+    <t>1150429K</t>
+  </si>
+  <si>
+    <t>ID1778139597971</t>
+  </si>
+  <si>
+    <t>ID1778197333009</t>
+  </si>
+  <si>
+    <t>BRD210</t>
+  </si>
+  <si>
+    <t>ID1778197382076</t>
+  </si>
+  <si>
+    <t>ID1778197425080</t>
+  </si>
+  <si>
+    <t>ID1778197500800</t>
+  </si>
+  <si>
+    <t>CE500</t>
+  </si>
+  <si>
+    <t>ID1778197520009</t>
+  </si>
+  <si>
+    <t>BE250</t>
+  </si>
+  <si>
+    <t>ID1778227773246</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY</t>
+  </si>
+  <si>
+    <t>1140528K</t>
+  </si>
+  <si>
+    <t>ID1778227799248</t>
+  </si>
+  <si>
+    <t>1140502K</t>
+  </si>
+  <si>
+    <t>ID1778229685758</t>
+  </si>
+  <si>
+    <t>ID1778229748526</t>
+  </si>
+  <si>
+    <t>ID1778229862985</t>
+  </si>
+  <si>
+    <t>CKM-KR</t>
+  </si>
+  <si>
+    <t>ID1778229913502</t>
+  </si>
+  <si>
+    <t>CKC2</t>
+  </si>
+  <si>
+    <t>ID1778229996243</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230020559</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY-對切</t>
+  </si>
+  <si>
+    <t>ID1778230078956</t>
+  </si>
+  <si>
+    <t>PRSRMB-GO-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230144397</t>
+  </si>
+  <si>
+    <t>CHSRMB-YK-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230200332</t>
+  </si>
+  <si>
+    <t>PRRER-340-380-YK</t>
+  </si>
+  <si>
+    <t>1150507S</t>
+  </si>
+  <si>
+    <t>ID1778231168084</t>
+  </si>
+  <si>
+    <t>JUP (8月-10月)</t>
+  </si>
+  <si>
+    <t>ID1778231224509</t>
+  </si>
+  <si>
+    <t>JUP (1月 3月)</t>
+  </si>
+  <si>
+    <t>ID1778231253827</t>
+  </si>
+  <si>
+    <t>JUP (2月 4月 5月)</t>
+  </si>
+  <si>
+    <t>ID1778231360305</t>
+  </si>
+  <si>
+    <t>JUP (6月 7月)</t>
+  </si>
+  <si>
+    <t>ID1778232035767</t>
+  </si>
+  <si>
+    <t>PSSTL-5cm</t>
+  </si>
+  <si>
+    <t>ID1778464113039</t>
+  </si>
+  <si>
+    <t>LR28</t>
+  </si>
+  <si>
+    <t>[NEW]</t>
+  </si>
+  <si>
+    <t>ID1778464134245</t>
+  </si>
+  <si>
+    <t>LR26</t>
+  </si>
+  <si>
+    <t>ID1778464166470</t>
+  </si>
+  <si>
+    <t>LHS</t>
+  </si>
+  <si>
+    <t>ID1778464235655</t>
+  </si>
+  <si>
+    <t>1141224K</t>
+  </si>
+  <si>
+    <t>ID1778464298059</t>
+  </si>
+  <si>
+    <t>GF-HTR-TY</t>
+  </si>
+  <si>
+    <t>1140916K</t>
+  </si>
+  <si>
+    <t>ID1778464320356</t>
+  </si>
+  <si>
+    <t>1141002K</t>
+  </si>
+  <si>
+    <t>ID1778464331761</t>
+  </si>
+  <si>
+    <t>ID1778464346113</t>
+  </si>
+  <si>
+    <t>1141119K</t>
+  </si>
+  <si>
+    <t>ID1778464356508</t>
+  </si>
+  <si>
+    <t>1141210K</t>
+  </si>
+  <si>
+    <t>ID1778541876765</t>
+  </si>
+  <si>
+    <t>木頭沾板</t>
+  </si>
+  <si>
+    <t>ID1778542317563</t>
+  </si>
+  <si>
+    <t>LR24</t>
+  </si>
+  <si>
+    <t>ID1778542503372</t>
+  </si>
+  <si>
+    <t>PRSTL-4.5CM-YK</t>
+  </si>
+  <si>
+    <t>1150429S</t>
+  </si>
+  <si>
+    <t>[移位] 下方棧板</t>
+  </si>
+  <si>
+    <t>ID1778542971412</t>
+  </si>
+  <si>
+    <t>ACTDL-TY</t>
+  </si>
+  <si>
+    <t>1140217K</t>
+  </si>
+  <si>
+    <t>ID1778554675190</t>
+  </si>
+  <si>
+    <t>ID1778556120999</t>
+  </si>
+  <si>
+    <t>M67-TDL-KR</t>
+  </si>
+  <si>
+    <t>ID1778556295035</t>
+  </si>
+  <si>
+    <t>GF-IE-MU</t>
+  </si>
+  <si>
+    <t>ID1778559275364</t>
+  </si>
+  <si>
+    <t>PRCER-十字切-GO</t>
+  </si>
+  <si>
+    <t>ID1778559302299</t>
+  </si>
+  <si>
+    <t>ID1778559458549</t>
+  </si>
+  <si>
+    <t>ID1778572817969</t>
+  </si>
+  <si>
+    <t>1150430K</t>
+  </si>
+  <si>
+    <t>ID1778630199114</t>
+  </si>
+  <si>
+    <t>M9OB</t>
+  </si>
+  <si>
+    <t>ID1778630217355</t>
+  </si>
+  <si>
+    <t>ID1778721619934</t>
+  </si>
+  <si>
+    <t>CHSRL-280-320-YK</t>
+  </si>
+  <si>
+    <t>ID1778721668935</t>
+  </si>
+  <si>
+    <t>PRSRL-280-320-GO</t>
+  </si>
+  <si>
+    <t>ID1778721745457</t>
+  </si>
+  <si>
+    <t>PRRER-對切-GO</t>
+  </si>
+  <si>
+    <t>ID1778722895097</t>
+  </si>
+  <si>
+    <t>PRRER-260-300-YK</t>
+  </si>
+  <si>
+    <t>走道</t>
+  </si>
+  <si>
+    <t>ID1778725820187</t>
+  </si>
+  <si>
+    <t>ID1778725857328</t>
+  </si>
+  <si>
+    <t>ID1778725890173</t>
+  </si>
+  <si>
+    <t>ID1778725969618</t>
+  </si>
+  <si>
+    <t>ID1778725996303</t>
+  </si>
+  <si>
+    <t>ID1778726036367</t>
+  </si>
+  <si>
+    <t>ID1778726476402</t>
+  </si>
+  <si>
+    <t>ID1778727701166</t>
+  </si>
+  <si>
+    <t>1140105K</t>
+  </si>
+  <si>
+    <t>ID1778727905088</t>
+  </si>
+  <si>
+    <t>IST-KR</t>
+  </si>
+  <si>
+    <t>ID1778728574129</t>
+  </si>
+  <si>
+    <t>ID1778728660741</t>
+  </si>
+  <si>
+    <t>PRSRMB</t>
+  </si>
+  <si>
+    <t>ID1778728710935</t>
+  </si>
+  <si>
+    <t>BH1</t>
+  </si>
+  <si>
+    <t>1150505K</t>
+  </si>
+  <si>
+    <t>ID1778728798066</t>
+  </si>
+  <si>
+    <t>TUE-KR</t>
+  </si>
+  <si>
+    <t>ID1778728923996</t>
+  </si>
+  <si>
+    <t>ACSTL-3cm</t>
+  </si>
+  <si>
+    <t>ID1778732193420</t>
+  </si>
+  <si>
+    <t>OST-KR</t>
+  </si>
+  <si>
+    <t>1140120K</t>
+  </si>
+  <si>
+    <t>ID1778732215773</t>
+  </si>
+  <si>
+    <t>TL-KR</t>
+  </si>
+  <si>
+    <t>1141212K</t>
+  </si>
+  <si>
+    <t>ID1778732228563</t>
+  </si>
+  <si>
+    <t>ID1778732244823</t>
+  </si>
+  <si>
+    <t>1150205K</t>
+  </si>
+  <si>
+    <t>ID1778742344546</t>
+  </si>
+  <si>
+    <t>PRSRL-GO</t>
+  </si>
+  <si>
+    <t>1150416K</t>
+  </si>
+  <si>
+    <t>ID1778742406824</t>
+  </si>
+  <si>
+    <t>ID1778742423267</t>
+  </si>
+  <si>
+    <t>ID1778742460343</t>
+  </si>
+  <si>
+    <t>ID1778744206884</t>
+  </si>
+  <si>
+    <t>ID1778744460598</t>
+  </si>
+  <si>
+    <t>M9SRM-KR</t>
+  </si>
+  <si>
+    <t>ID1778744798143</t>
+  </si>
+  <si>
+    <t>ID1778744923833</t>
+  </si>
+  <si>
+    <t>M45OB-MU</t>
+  </si>
+  <si>
+    <t>ID1778745054676</t>
+  </si>
+  <si>
+    <t>34B</t>
+  </si>
+  <si>
+    <t>ID1779067878945</t>
+  </si>
+  <si>
+    <t>M5TDL-ST</t>
+  </si>
+  <si>
+    <t>ID1779067919417</t>
+  </si>
+  <si>
+    <t>M45TDL-KR</t>
+  </si>
+  <si>
+    <t>ID1779067969133</t>
+  </si>
+  <si>
+    <t>BH5</t>
+  </si>
+  <si>
+    <t>ID1779088333604</t>
+  </si>
+  <si>
+    <t>ID1779088383095</t>
+  </si>
+  <si>
+    <t>ID1779094185461</t>
+  </si>
+  <si>
+    <t>ACSRM-TY</t>
+  </si>
+  <si>
+    <t>ID1779094221377</t>
+  </si>
+  <si>
+    <t>ID1779177620923</t>
+  </si>
+  <si>
+    <t>M9RER-KR(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779177653857</t>
+  </si>
+  <si>
+    <t>M89SRL-KR(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779177671526</t>
+  </si>
+  <si>
+    <t>M67SRL-KR(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779177691109</t>
+  </si>
+  <si>
+    <t>OST-KR(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779178399646</t>
+  </si>
+  <si>
+    <t>CHSRM-SS</t>
+  </si>
+  <si>
+    <t>1150512K</t>
+  </si>
+  <si>
+    <t>ID1779198270277</t>
+  </si>
+  <si>
+    <t>1131001K</t>
+  </si>
+  <si>
+    <t>ID1779243721312</t>
+  </si>
+  <si>
+    <t>JUP(4月報廢）</t>
+  </si>
+  <si>
+    <t>ID1779243743080</t>
+  </si>
+  <si>
+    <t>鴨翅(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779243761619</t>
+  </si>
+  <si>
+    <t>鴨里肌(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779243798483</t>
+  </si>
+  <si>
+    <t>油角（報廢）</t>
+  </si>
+  <si>
+    <t>ID1779255881570</t>
+  </si>
+  <si>
+    <t>斑泊EP335(寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779255983117</t>
+  </si>
+  <si>
+    <t>錨隱廚 EP350（寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779256194102</t>
+  </si>
+  <si>
+    <t>On or 響艷信義JOC（寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779258747249</t>
+  </si>
+  <si>
+    <t>Niche JOC(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779258816523</t>
+  </si>
+  <si>
+    <t>UNCLE 一店 CKC2(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779258906179</t>
+  </si>
+  <si>
+    <t>UNCLE二店 CKC2(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779258977854</t>
+  </si>
+  <si>
+    <t>UNCLE三店CKC2(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779260005194</t>
+  </si>
+  <si>
+    <t>Pasta West East 紅廚 EP350 (寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779260726909</t>
+  </si>
+  <si>
+    <t>L’atelier Robuchon JOP (寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779260787111</t>
+  </si>
+  <si>
+    <t>ADR8</t>
+  </si>
+  <si>
+    <t>ID1779260970845</t>
+  </si>
+  <si>
+    <t>布爾喬亞 JUP (寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779327905648</t>
+  </si>
+  <si>
+    <t>ADC(豬肉）</t>
+  </si>
+  <si>
+    <t>ID1779336479059</t>
+  </si>
+  <si>
+    <t>VC405</t>
+  </si>
+  <si>
+    <t>ID1779336498030</t>
+  </si>
+  <si>
+    <t>VC408</t>
+  </si>
+  <si>
+    <t>ID1779336509597</t>
+  </si>
+  <si>
+    <t>VC407</t>
+  </si>
+  <si>
+    <t>ID1779336526988</t>
+  </si>
+  <si>
+    <t>VC401</t>
+  </si>
+  <si>
+    <t>ID1779336554211</t>
+  </si>
+  <si>
+    <t>ID1779336604468</t>
+  </si>
+  <si>
+    <t>PTMA4</t>
+  </si>
+  <si>
+    <t>ID1779336670410</t>
+  </si>
+  <si>
+    <t>PTMA1</t>
+  </si>
+  <si>
+    <t>ID1779336687710</t>
+  </si>
+  <si>
+    <t>PTMA3</t>
+  </si>
+  <si>
+    <t>ID1779336717423</t>
+  </si>
+  <si>
+    <t>CZED125</t>
+  </si>
+  <si>
+    <t>ID1779336735901</t>
+  </si>
+  <si>
+    <t>CZBR125</t>
+  </si>
+  <si>
+    <t>ID1779336752106</t>
+  </si>
+  <si>
+    <t>CZBA125</t>
+  </si>
+  <si>
+    <t>ID1779336768758</t>
+  </si>
+  <si>
+    <t>CZPV125</t>
+  </si>
+  <si>
+    <t>ID1779336804283</t>
+  </si>
+  <si>
+    <t>PGS4</t>
+  </si>
+  <si>
+    <t>ID1779336826299</t>
+  </si>
+  <si>
+    <t>PGS3</t>
+  </si>
+  <si>
+    <t>ID1779336842776</t>
+  </si>
+  <si>
+    <t>PGS1</t>
+  </si>
+  <si>
+    <t>ID1779336869690</t>
+  </si>
+  <si>
+    <t>PGR30</t>
+  </si>
+  <si>
+    <t>ID1779336887245</t>
+  </si>
+  <si>
+    <t>PDE12</t>
+  </si>
+  <si>
+    <t>ID1779336906578</t>
+  </si>
+  <si>
+    <t>PGE22</t>
+  </si>
+  <si>
+    <t>ID1779336936520</t>
+  </si>
+  <si>
+    <t>PGR24</t>
+  </si>
+  <si>
+    <t>ID1779337010716</t>
+  </si>
+  <si>
+    <t>GRW1</t>
+  </si>
+  <si>
+    <t>ID1779337463665</t>
+  </si>
+  <si>
+    <t>GRW2</t>
+  </si>
+  <si>
+    <t>ID1779337587175</t>
+  </si>
+  <si>
+    <t>GRS1</t>
+  </si>
+  <si>
+    <t>ID1779343267216</t>
+  </si>
+  <si>
+    <t>GRP100</t>
+  </si>
+  <si>
+    <t>ID1779343290594</t>
+  </si>
+  <si>
+    <t>GRS2</t>
+  </si>
+  <si>
+    <t>ID1779343310568</t>
+  </si>
+  <si>
+    <t>GRS6</t>
+  </si>
+  <si>
+    <t>ID1779343331075</t>
+  </si>
+  <si>
+    <t>GRS200</t>
+  </si>
+  <si>
+    <t>ID1779343361971</t>
+  </si>
+  <si>
+    <t>GRW3</t>
+  </si>
+  <si>
+    <t>ID1779343395723</t>
+  </si>
+  <si>
+    <t>BY12S</t>
+  </si>
+  <si>
+    <t>ID1779343415214</t>
+  </si>
+  <si>
+    <t>ID1779343445375</t>
+  </si>
+  <si>
+    <t>BY13</t>
+  </si>
+  <si>
+    <t>[異常] 出清</t>
+  </si>
+  <si>
+    <t>ID1779343478640</t>
+  </si>
+  <si>
+    <t>JO48S</t>
+  </si>
+  <si>
+    <t>ID1779343499670</t>
+  </si>
+  <si>
+    <t>JOP24S</t>
+  </si>
+  <si>
+    <t>ID1779343524379</t>
+  </si>
+  <si>
+    <t>JOA</t>
+  </si>
+  <si>
+    <t>ID1779343558098</t>
+  </si>
+  <si>
+    <t>BY12</t>
+  </si>
+  <si>
+    <t>ID1779343590997</t>
+  </si>
+  <si>
+    <t>BY92S</t>
+  </si>
+  <si>
+    <t>ID1779343680610</t>
+  </si>
+  <si>
+    <t>Domain 大直 NO12S （寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779343714862</t>
+  </si>
+  <si>
+    <t>Domain 建國NO12S （寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779343771102</t>
+  </si>
+  <si>
+    <t>台北文華 NO12S （寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779343793991</t>
+  </si>
+  <si>
+    <t>頁小館 NO12S （寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779355047243</t>
+  </si>
+  <si>
+    <t>M45FKS-C-KR</t>
+  </si>
+  <si>
+    <t>ID1779355423259</t>
+  </si>
+  <si>
+    <t>M89RER-C-KR</t>
+  </si>
+  <si>
+    <t>ID1779413117582</t>
+  </si>
+  <si>
+    <t>ID1779413244655</t>
+  </si>
+  <si>
+    <t>M89OB-C-KR</t>
+  </si>
+  <si>
+    <t>ID1779413800838</t>
+  </si>
+  <si>
+    <t>ACTDL-C-TY</t>
+  </si>
+  <si>
+    <t>ID1779413903533</t>
+  </si>
+  <si>
+    <t>PRRER-C-YK</t>
+  </si>
+  <si>
+    <t>ID1779413919146</t>
+  </si>
+  <si>
+    <t>PRSRL-C-YK</t>
+  </si>
+  <si>
+    <t>ID1779414379352</t>
+  </si>
+  <si>
+    <t>PRRER-C-GO</t>
+  </si>
+  <si>
+    <t>ID1779423814186</t>
+  </si>
+  <si>
+    <t>EMSPL-SS</t>
+  </si>
+  <si>
+    <t>26#37</t>
+  </si>
+  <si>
+    <t>ID1779423889909</t>
   </si>
   <si>
     <t>PRSRM-C-SS</t>
   </si>
   <si>
-    <t>PRTDL-C-SS</t>
-  </si>
-  <si>
-    <t>26#34</t>
-  </si>
-  <si>
-    <t>PRSTL-C-YK</t>
-  </si>
-  <si>
-    <t>26#8</t>
-  </si>
-  <si>
-    <t>無庫位</t>
-  </si>
-  <si>
-    <t>34B(34-36)</t>
-  </si>
-  <si>
-    <t>JUJM(退貨)</t>
-  </si>
-  <si>
-    <t>12Q</t>
-  </si>
-  <si>
-    <t>1150415K</t>
-  </si>
-  <si>
-    <t>1150413K</t>
-  </si>
-  <si>
-    <t>AD3</t>
-  </si>
-  <si>
-    <t>ADJM (豬肉)(5入)</t>
-  </si>
-  <si>
-    <t>SPT-10入</t>
-  </si>
-  <si>
-    <t>PRSRL-420-460-GO</t>
-  </si>
-  <si>
-    <t>PRRER-上林規-YK</t>
-  </si>
-  <si>
-    <t>PRRER-3cm-SS</t>
-  </si>
-  <si>
-    <t>PRRER-900-960-SS</t>
-  </si>
-  <si>
-    <t>ACRER-280-320-TY</t>
-  </si>
-  <si>
-    <t>PRRER-一開三-SS</t>
-  </si>
-  <si>
-    <t>PRRERB-GO</t>
-  </si>
-  <si>
-    <t>PRCER-GO</t>
-  </si>
-  <si>
-    <t>M89CER-橫十字切_KR</t>
-  </si>
-  <si>
-    <t>1150122S</t>
-  </si>
-  <si>
-    <t>[異常] 1p</t>
-  </si>
-  <si>
-    <t>GMB(骨）</t>
-  </si>
-  <si>
-    <t>GMB</t>
-  </si>
-  <si>
-    <t>1150210S</t>
-  </si>
-  <si>
-    <t>1150415S</t>
-  </si>
-  <si>
-    <t>JOB(26b)</t>
-  </si>
-  <si>
-    <t>ACOB-YK(8入)</t>
-  </si>
-  <si>
-    <t>1150417K</t>
-  </si>
-  <si>
-    <t>ID1776755440734</t>
-  </si>
-  <si>
-    <t>1150410K</t>
-  </si>
-  <si>
-    <t>ID1776755702626</t>
-  </si>
-  <si>
-    <t>PRCER-YK</t>
-  </si>
-  <si>
-    <t>1150409K</t>
-  </si>
-  <si>
-    <t>ID1776756005407</t>
-  </si>
-  <si>
-    <t>CHRER-280-320-SS</t>
-  </si>
-  <si>
-    <t>ID1776830939143</t>
-  </si>
-  <si>
-    <t>電商紙袋</t>
-  </si>
-  <si>
-    <t>ID1776831008384</t>
-  </si>
-  <si>
-    <t>手提袋 模型</t>
-  </si>
-  <si>
-    <t>ID1776831054260</t>
-  </si>
-  <si>
-    <t>火腿架</t>
-  </si>
-  <si>
-    <t>ID1776831067623</t>
-  </si>
-  <si>
-    <t>ID1776831077383</t>
-  </si>
-  <si>
-    <t>ID1776831088970</t>
-  </si>
-  <si>
-    <t>ID1776831133943</t>
-  </si>
-  <si>
-    <t>紙箱</t>
-  </si>
-  <si>
-    <t>ID1776917744376</t>
-  </si>
-  <si>
-    <t>ID1776917966118</t>
-  </si>
-  <si>
-    <t>M9SRL-KR</t>
-  </si>
-  <si>
-    <t>ID1776917982996</t>
-  </si>
-  <si>
-    <t>M9TDL-KR</t>
-  </si>
-  <si>
-    <t>1140702K</t>
-  </si>
-  <si>
-    <t>ID1776918100016</t>
-  </si>
-  <si>
-    <t>M89SRL-KR (牛肉)</t>
-  </si>
-  <si>
-    <t>ID1776918492764</t>
-  </si>
-  <si>
-    <t>TQ</t>
-  </si>
-  <si>
-    <t>ID1776918517934</t>
-  </si>
-  <si>
-    <t>B(30-34)</t>
-  </si>
-  <si>
-    <t>ID1776940880649</t>
-  </si>
-  <si>
-    <t>13S(零碼)(4入)(48P)</t>
-  </si>
-  <si>
-    <t>ID1776941556959</t>
-  </si>
-  <si>
-    <t>ACSRM-TY（報廢）</t>
-  </si>
-  <si>
-    <t>1131209K</t>
-  </si>
-  <si>
-    <t>[報廢]發綠 12.51K</t>
-  </si>
-  <si>
-    <t>ID1777281985428</t>
-  </si>
-  <si>
-    <t>PRSRM-SS-對切</t>
-  </si>
-  <si>
-    <t>ID1777286256898</t>
-  </si>
-  <si>
-    <t>PRRER-280-320-YK</t>
-  </si>
-  <si>
-    <t>1150513S</t>
-  </si>
-  <si>
-    <t>ID1777286953561</t>
-  </si>
-  <si>
-    <t>GF-CKM-TY (牛肉)(6入)</t>
-  </si>
-  <si>
-    <t>1150515K(26#6)</t>
-  </si>
-  <si>
-    <t>ID1777363414962</t>
-  </si>
-  <si>
-    <t>PRTDL-YK</t>
-  </si>
-  <si>
-    <t>1150427K</t>
-  </si>
-  <si>
-    <t>[異常] 轉凍</t>
-  </si>
-  <si>
-    <t>ID1777363429496</t>
-  </si>
-  <si>
-    <t>PRSRL-SS</t>
-  </si>
-  <si>
-    <t>ID1777363462065</t>
-  </si>
-  <si>
-    <t>ID1777363475957</t>
-  </si>
-  <si>
-    <t>ACOB-TY</t>
-  </si>
-  <si>
-    <t>ID1777433910575</t>
-  </si>
-  <si>
-    <t>PSRER-280-320</t>
-  </si>
-  <si>
-    <t>1140710S</t>
-  </si>
-  <si>
-    <t>ID1777434325087</t>
-  </si>
-  <si>
-    <t>1140616K</t>
-  </si>
-  <si>
-    <t>ID1777434731664</t>
-  </si>
-  <si>
-    <t>ID1777451610853</t>
-  </si>
-  <si>
-    <t>PRRERB-YK</t>
-  </si>
-  <si>
-    <t>ID1777451628937</t>
-  </si>
-  <si>
-    <t>PRSTL-YK</t>
-  </si>
-  <si>
-    <t>1150428K</t>
-  </si>
-  <si>
-    <t>ID1777515662732</t>
-  </si>
-  <si>
-    <t>35B(#35)</t>
-  </si>
-  <si>
-    <t>ID1777515763188</t>
-  </si>
-  <si>
-    <t>T(鴨里肌)(8入)</t>
-  </si>
-  <si>
-    <t>ID1777515842006</t>
-  </si>
-  <si>
-    <t>60S(5入)(60P)</t>
-  </si>
-  <si>
-    <t>ID1777518516282</t>
-  </si>
-  <si>
-    <t>M89SRL-280-320（報廢）</t>
-  </si>
-  <si>
-    <t>ID1777518552434</t>
-  </si>
-  <si>
-    <t>藥檢品</t>
-  </si>
-  <si>
-    <t>ID1777518604803</t>
-  </si>
-  <si>
-    <t>M67-CFT-ST（報廢）</t>
-  </si>
-  <si>
-    <t>ID1777518808060</t>
-  </si>
-  <si>
-    <t>M89RER-200-250-KR</t>
-  </si>
-  <si>
-    <t>ID1777519539807</t>
-  </si>
-  <si>
-    <t>PRRER-185-225-GO</t>
-  </si>
-  <si>
-    <t>1141016S</t>
-  </si>
-  <si>
-    <t>ID1777880359815</t>
-  </si>
-  <si>
-    <t>ID1777900723432</t>
-  </si>
-  <si>
-    <t>ADHS-4入</t>
-  </si>
-  <si>
-    <t>ID1777901415357</t>
-  </si>
-  <si>
-    <t>CHTDL-YK</t>
-  </si>
-  <si>
-    <t>ID1778041215011</t>
-  </si>
-  <si>
-    <t>1140425K</t>
-  </si>
-  <si>
-    <t>ID1778057927574</t>
-  </si>
-  <si>
-    <t>M67CFT-ST</t>
-  </si>
-  <si>
-    <t>24#5</t>
-  </si>
-  <si>
-    <t>ID1778057982808</t>
-  </si>
-  <si>
-    <t>M45SRL-ST</t>
-  </si>
-  <si>
-    <t>24#7</t>
-  </si>
-  <si>
-    <t>ID1778139472526</t>
-  </si>
-  <si>
-    <t>1150429K</t>
-  </si>
-  <si>
-    <t>ID1778139597971</t>
-  </si>
-  <si>
-    <t>ID1778197333009</t>
-  </si>
-  <si>
-    <t>BRD210</t>
-  </si>
-  <si>
-    <t>ID1778197382076</t>
-  </si>
-  <si>
-    <t>ID1778197425080</t>
-  </si>
-  <si>
-    <t>ID1778197500800</t>
-  </si>
-  <si>
-    <t>CE500</t>
-  </si>
-  <si>
-    <t>ID1778197520009</t>
-  </si>
-  <si>
-    <t>BE250</t>
-  </si>
-  <si>
-    <t>ID1778227773246</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY</t>
-  </si>
-  <si>
-    <t>1140528K</t>
-  </si>
-  <si>
-    <t>ID1778227799248</t>
-  </si>
-  <si>
-    <t>1140502K</t>
-  </si>
-  <si>
-    <t>ID1778229685758</t>
-  </si>
-  <si>
-    <t>ID1778229748526</t>
-  </si>
-  <si>
-    <t>ID1778229862985</t>
-  </si>
-  <si>
-    <t>CKM-KR</t>
-  </si>
-  <si>
-    <t>ID1778229913502</t>
-  </si>
-  <si>
-    <t>CKC2</t>
-  </si>
-  <si>
-    <t>ID1778229996243</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230020559</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY-對切</t>
-  </si>
-  <si>
-    <t>ID1778230078956</t>
-  </si>
-  <si>
-    <t>PRSRMB-GO-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230144397</t>
-  </si>
-  <si>
-    <t>CHSRMB-YK-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230200332</t>
-  </si>
-  <si>
-    <t>PRRER-340-380-YK</t>
-  </si>
-  <si>
-    <t>1150507S</t>
-  </si>
-  <si>
-    <t>ID1778231168084</t>
-  </si>
-  <si>
-    <t>JUP (8月-10月)</t>
-  </si>
-  <si>
-    <t>ID1778231224509</t>
-  </si>
-  <si>
-    <t>JUP (1月 3月)</t>
-  </si>
-  <si>
-    <t>ID1778231253827</t>
-  </si>
-  <si>
-    <t>JUP (2月 4月 5月)</t>
-  </si>
-  <si>
-    <t>ID1778231360305</t>
-  </si>
-  <si>
-    <t>JUP (6月 7月)</t>
-  </si>
-  <si>
-    <t>ID1778232035767</t>
-  </si>
-  <si>
-    <t>PSSTL-5cm</t>
-  </si>
-  <si>
-    <t>ID1778464113039</t>
-  </si>
-  <si>
-    <t>LR28</t>
-  </si>
-  <si>
-    <t>[NEW]</t>
-  </si>
-  <si>
-    <t>ID1778464134245</t>
-  </si>
-  <si>
-    <t>LR26</t>
-  </si>
-  <si>
-    <t>ID1778464166470</t>
-  </si>
-  <si>
-    <t>LHS</t>
-  </si>
-  <si>
-    <t>ID1778464235655</t>
-  </si>
-  <si>
-    <t>1141224K</t>
-  </si>
-  <si>
-    <t>ID1778464298059</t>
-  </si>
-  <si>
-    <t>GF-HTR-TY</t>
-  </si>
-  <si>
-    <t>1140916K</t>
-  </si>
-  <si>
-    <t>ID1778464320356</t>
-  </si>
-  <si>
-    <t>1141002K</t>
-  </si>
-  <si>
-    <t>ID1778464331761</t>
-  </si>
-  <si>
-    <t>ID1778464346113</t>
-  </si>
-  <si>
-    <t>1141119K</t>
-  </si>
-  <si>
-    <t>ID1778464356508</t>
-  </si>
-  <si>
-    <t>1141210K</t>
-  </si>
-  <si>
-    <t>ID1778541876765</t>
-  </si>
-  <si>
-    <t>木頭沾板</t>
-  </si>
-  <si>
-    <t>ID1778542317563</t>
-  </si>
-  <si>
-    <t>LR24</t>
-  </si>
-  <si>
-    <t>ID1778542503372</t>
-  </si>
-  <si>
-    <t>PRSTL-4.5CM-YK</t>
-  </si>
-  <si>
-    <t>1150429S</t>
-  </si>
-  <si>
-    <t>[移位] 下方棧板</t>
-  </si>
-  <si>
-    <t>ID1778542971412</t>
-  </si>
-  <si>
-    <t>ACTDL-TY</t>
-  </si>
-  <si>
-    <t>1140217K</t>
-  </si>
-  <si>
-    <t>ID1778554675190</t>
-  </si>
-  <si>
-    <t>ID1778556120999</t>
-  </si>
-  <si>
-    <t>M67-TDL-KR</t>
-  </si>
-  <si>
-    <t>ID1778556295035</t>
-  </si>
-  <si>
-    <t>GF-IE-MU</t>
-  </si>
-  <si>
-    <t>ID1778559275364</t>
-  </si>
-  <si>
-    <t>PRCER-十字切-GO</t>
-  </si>
-  <si>
-    <t>ID1778559302299</t>
-  </si>
-  <si>
-    <t>ID1778559458549</t>
-  </si>
-  <si>
-    <t>ID1778572817969</t>
-  </si>
-  <si>
-    <t>1150430K</t>
-  </si>
-  <si>
-    <t>ID1778630199114</t>
-  </si>
-  <si>
-    <t>M9OB</t>
-  </si>
-  <si>
-    <t>ID1778630217355</t>
-  </si>
-  <si>
-    <t>ID1778721619934</t>
-  </si>
-  <si>
-    <t>CHSRL-280-320-YK</t>
-  </si>
-  <si>
-    <t>ID1778721668935</t>
-  </si>
-  <si>
-    <t>PRSRL-280-320-GO</t>
-  </si>
-  <si>
-    <t>ID1778721745457</t>
-  </si>
-  <si>
-    <t>PRRER-對切-GO</t>
-  </si>
-  <si>
-    <t>ID1778722895097</t>
-  </si>
-  <si>
-    <t>PRRER-260-300-YK</t>
-  </si>
-  <si>
-    <t>走道</t>
-  </si>
-  <si>
-    <t>ID1778725820187</t>
-  </si>
-  <si>
-    <t>ID1778725857328</t>
-  </si>
-  <si>
-    <t>ID1778725890173</t>
-  </si>
-  <si>
-    <t>ID1778725969618</t>
-  </si>
-  <si>
-    <t>ID1778725996303</t>
-  </si>
-  <si>
-    <t>ID1778726036367</t>
-  </si>
-  <si>
-    <t>ID1778726476402</t>
-  </si>
-  <si>
-    <t>ID1778727701166</t>
-  </si>
-  <si>
-    <t>1140105K</t>
-  </si>
-  <si>
-    <t>ID1778727905088</t>
-  </si>
-  <si>
-    <t>IST-KR</t>
-  </si>
-  <si>
-    <t>ID1778728574129</t>
-  </si>
-  <si>
-    <t>ID1778728660741</t>
-  </si>
-  <si>
-    <t>PRSRMB</t>
-  </si>
-  <si>
-    <t>ID1778728710935</t>
-  </si>
-  <si>
-    <t>BH1</t>
-  </si>
-  <si>
-    <t>1150505K</t>
-  </si>
-  <si>
-    <t>ID1778728798066</t>
-  </si>
-  <si>
-    <t>TUE-KR</t>
-  </si>
-  <si>
-    <t>ID1778728923996</t>
-  </si>
-  <si>
-    <t>ACSTL-3cm</t>
-  </si>
-  <si>
-    <t>ID1778732193420</t>
-  </si>
-  <si>
-    <t>OST-KR</t>
-  </si>
-  <si>
-    <t>1140120K</t>
-  </si>
-  <si>
-    <t>ID1778732215773</t>
-  </si>
-  <si>
-    <t>TL-KR</t>
-  </si>
-  <si>
-    <t>1141212K</t>
-  </si>
-  <si>
-    <t>ID1778732228563</t>
-  </si>
-  <si>
-    <t>ID1778732244823</t>
-  </si>
-  <si>
-    <t>1150205K</t>
-  </si>
-  <si>
-    <t>ID1778742344546</t>
-  </si>
-  <si>
-    <t>PRSRL-GO</t>
-  </si>
-  <si>
-    <t>1150416K</t>
-  </si>
-  <si>
-    <t>ID1778742406824</t>
-  </si>
-  <si>
-    <t>ID1778742423267</t>
-  </si>
-  <si>
-    <t>ID1778742460343</t>
-  </si>
-  <si>
-    <t>ID1778744206884</t>
-  </si>
-  <si>
-    <t>ID1778744460598</t>
-  </si>
-  <si>
-    <t>M9SRM-KR</t>
-  </si>
-  <si>
-    <t>ID1778744798143</t>
-  </si>
-  <si>
-    <t>ID1778744923833</t>
-  </si>
-  <si>
-    <t>M45OB-MU</t>
-  </si>
-  <si>
-    <t>ID1778745054676</t>
-  </si>
-  <si>
-    <t>34B</t>
-  </si>
-  <si>
-    <t>ID1779067878945</t>
-  </si>
-  <si>
-    <t>M5TDL-ST</t>
-  </si>
-  <si>
-    <t>ID1779067919417</t>
-  </si>
-  <si>
-    <t>M45TDL-KR</t>
-  </si>
-  <si>
-    <t>ID1779067969133</t>
-  </si>
-  <si>
-    <t>BH5</t>
-  </si>
-  <si>
-    <t>ID1779088333604</t>
-  </si>
-  <si>
-    <t>ID1779088383095</t>
-  </si>
-  <si>
-    <t>ID1779094185461</t>
-  </si>
-  <si>
-    <t>ACSRM-TY</t>
-  </si>
-  <si>
-    <t>ID1779094221377</t>
-  </si>
-  <si>
-    <t>ID1779177620923</t>
-  </si>
-  <si>
-    <t>M9RER-KR(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779177653857</t>
-  </si>
-  <si>
-    <t>M89SRL-KR(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779177671526</t>
-  </si>
-  <si>
-    <t>M67SRL-KR(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779177691109</t>
-  </si>
-  <si>
-    <t>OST-KR(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779178399646</t>
-  </si>
-  <si>
-    <t>CHSRM-SS</t>
-  </si>
-  <si>
-    <t>1150512K</t>
-  </si>
-  <si>
-    <t>ID1779198270277</t>
-  </si>
-  <si>
-    <t>1131001K</t>
-  </si>
-  <si>
-    <t>ID1779243721312</t>
-  </si>
-  <si>
-    <t>JUP(4月報廢）</t>
-  </si>
-  <si>
-    <t>ID1779243743080</t>
-  </si>
-  <si>
-    <t>鴨翅(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779243761619</t>
-  </si>
-  <si>
-    <t>鴨里肌(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779243798483</t>
-  </si>
-  <si>
-    <t>油角（報廢）</t>
-  </si>
-  <si>
-    <t>ID1779255881570</t>
-  </si>
-  <si>
-    <t>斑泊EP335(寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779255983117</t>
-  </si>
-  <si>
-    <t>錨隱廚 EP350（寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779256194102</t>
-  </si>
-  <si>
-    <t>On or 響艷信義JOC（寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779258747249</t>
-  </si>
-  <si>
-    <t>Niche JOC(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779258816523</t>
-  </si>
-  <si>
-    <t>UNCLE 一店 CKC2(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779258906179</t>
-  </si>
-  <si>
-    <t>UNCLE二店 CKC2(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779258977854</t>
-  </si>
-  <si>
-    <t>UNCLE三店CKC2(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779260005194</t>
-  </si>
-  <si>
-    <t>Pasta West East 紅廚 EP350 (寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779260726909</t>
-  </si>
-  <si>
-    <t>L’atelier Robuchon JOP (寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779260787111</t>
-  </si>
-  <si>
-    <t>ADR8</t>
-  </si>
-  <si>
-    <t>ID1779260970845</t>
-  </si>
-  <si>
-    <t>布爾喬亞 JUP (寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779327905648</t>
-  </si>
-  <si>
-    <t>ADC(豬肉）</t>
-  </si>
-  <si>
-    <t>ID1779336479059</t>
-  </si>
-  <si>
-    <t>VC405</t>
-  </si>
-  <si>
-    <t>ID1779336498030</t>
-  </si>
-  <si>
-    <t>VC408</t>
-  </si>
-  <si>
-    <t>ID1779336509597</t>
-  </si>
-  <si>
-    <t>VC407</t>
-  </si>
-  <si>
-    <t>ID1779336526988</t>
-  </si>
-  <si>
-    <t>VC401</t>
-  </si>
-  <si>
-    <t>ID1779336554211</t>
-  </si>
-  <si>
-    <t>ID1779336604468</t>
-  </si>
-  <si>
-    <t>PTMA4</t>
-  </si>
-  <si>
-    <t>ID1779336670410</t>
-  </si>
-  <si>
-    <t>PTMA1</t>
-  </si>
-  <si>
-    <t>ID1779336687710</t>
-  </si>
-  <si>
-    <t>PTMA3</t>
-  </si>
-  <si>
-    <t>ID1779336717423</t>
-  </si>
-  <si>
-    <t>CZED125</t>
-  </si>
-  <si>
-    <t>ID1779336735901</t>
-  </si>
-  <si>
-    <t>CZBR125</t>
-  </si>
-  <si>
-    <t>ID1779336752106</t>
-  </si>
-  <si>
-    <t>CZBA125</t>
-  </si>
-  <si>
-    <t>ID1779336768758</t>
-  </si>
-  <si>
-    <t>CZPV125</t>
-  </si>
-  <si>
-    <t>ID1779336804283</t>
-  </si>
-  <si>
-    <t>PGS4</t>
-  </si>
-  <si>
-    <t>ID1779336826299</t>
-  </si>
-  <si>
-    <t>PGS3</t>
-  </si>
-  <si>
-    <t>ID1779336842776</t>
-  </si>
-  <si>
-    <t>PGS1</t>
-  </si>
-  <si>
-    <t>ID1779336869690</t>
-  </si>
-  <si>
-    <t>PGR30</t>
-  </si>
-  <si>
-    <t>ID1779336887245</t>
-  </si>
-  <si>
-    <t>PDE12</t>
-  </si>
-  <si>
-    <t>ID1779336906578</t>
-  </si>
-  <si>
-    <t>PGE22</t>
-  </si>
-  <si>
-    <t>ID1779336936520</t>
-  </si>
-  <si>
-    <t>PGR24</t>
-  </si>
-  <si>
-    <t>ID1779337010716</t>
-  </si>
-  <si>
-    <t>GRW1</t>
-  </si>
-  <si>
-    <t>ID1779337463665</t>
-  </si>
-  <si>
-    <t>GRW2</t>
-  </si>
-  <si>
-    <t>ID1779337587175</t>
-  </si>
-  <si>
-    <t>GRS1</t>
-  </si>
-  <si>
-    <t>ID1779343267216</t>
-  </si>
-  <si>
-    <t>GRP100</t>
-  </si>
-  <si>
-    <t>ID1779343290594</t>
-  </si>
-  <si>
-    <t>GRS2</t>
-  </si>
-  <si>
-    <t>ID1779343310568</t>
-  </si>
-  <si>
-    <t>GRS6</t>
-  </si>
-  <si>
-    <t>ID1779343331075</t>
-  </si>
-  <si>
-    <t>GRS200</t>
-  </si>
-  <si>
-    <t>ID1779343361971</t>
-  </si>
-  <si>
-    <t>GRW3</t>
-  </si>
-  <si>
-    <t>ID1779343395723</t>
-  </si>
-  <si>
-    <t>BY12S</t>
-  </si>
-  <si>
-    <t>ID1779343415214</t>
-  </si>
-  <si>
-    <t>ID1779343445375</t>
-  </si>
-  <si>
-    <t>BY13</t>
-  </si>
-  <si>
-    <t>[異常] 出清</t>
-  </si>
-  <si>
-    <t>ID1779343478640</t>
-  </si>
-  <si>
-    <t>JO48S</t>
-  </si>
-  <si>
-    <t>ID1779343499670</t>
-  </si>
-  <si>
-    <t>JOP24S</t>
-  </si>
-  <si>
-    <t>ID1779343524379</t>
-  </si>
-  <si>
-    <t>JOA</t>
-  </si>
-  <si>
-    <t>ID1779343558098</t>
-  </si>
-  <si>
-    <t>BY12</t>
-  </si>
-  <si>
-    <t>ID1779343590997</t>
-  </si>
-  <si>
-    <t>BY92S</t>
-  </si>
-  <si>
-    <t>ID1779343680610</t>
-  </si>
-  <si>
-    <t>Domain 大直 NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779343714862</t>
-  </si>
-  <si>
-    <t>Domain 建國NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779343771102</t>
-  </si>
-  <si>
-    <t>台北文華 NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779343793991</t>
-  </si>
-  <si>
-    <t>頁小館 NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779355047243</t>
-  </si>
-  <si>
-    <t>M45FKS-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779355423259</t>
-  </si>
-  <si>
-    <t>M89RER-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779413117582</t>
-  </si>
-  <si>
-    <t>ID1779413161910</t>
-  </si>
-  <si>
-    <t>ID1779413222224</t>
-  </si>
-  <si>
-    <t>M67RER-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779413244655</t>
-  </si>
-  <si>
-    <t>M89OB-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779413357073</t>
-  </si>
-  <si>
-    <t>26#32</t>
-  </si>
-  <si>
-    <t>ID1779413776527</t>
-  </si>
-  <si>
-    <t>GF-HTR-C-TY</t>
-  </si>
-  <si>
-    <t>ID1779413800838</t>
-  </si>
-  <si>
-    <t>ACTDL-C-TY</t>
-  </si>
-  <si>
-    <t>ID1779413903533</t>
-  </si>
-  <si>
-    <t>PRRER-C-YK</t>
-  </si>
-  <si>
-    <t>ID1779413919146</t>
-  </si>
-  <si>
-    <t>PRSRL-C-YK</t>
-  </si>
-  <si>
-    <t>ID1779414379352</t>
-  </si>
-  <si>
-    <t>PRRER-C-GO</t>
-  </si>
-  <si>
-    <t>ID1779423814186</t>
-  </si>
-  <si>
-    <t>EMSPL-SS</t>
-  </si>
-  <si>
-    <t>26#37</t>
-  </si>
-  <si>
-    <t>ID1779423889909</t>
-  </si>
-  <si>
     <t>26#36</t>
   </si>
   <si>
@@ -3395,6 +3374,93 @@
   </si>
   <si>
     <t>1140514K</t>
+  </si>
+  <si>
+    <t>ID1779952236759</t>
+  </si>
+  <si>
+    <t>ACRER-200-250-TY</t>
+  </si>
+  <si>
+    <t>ID1779952271401</t>
+  </si>
+  <si>
+    <t>ID1779952289227</t>
+  </si>
+  <si>
+    <t>GMB(骨)</t>
+  </si>
+  <si>
+    <t>ID1779952979939</t>
+  </si>
+  <si>
+    <t>M45OB-切3CM</t>
+  </si>
+  <si>
+    <t>ID1779953032414</t>
+  </si>
+  <si>
+    <t>PRRER-340-380-SS</t>
+  </si>
+  <si>
+    <t>ID1779953075175</t>
+  </si>
+  <si>
+    <t>M89OSF-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953104690</t>
+  </si>
+  <si>
+    <t>M45BBLD-1.5cm-KR</t>
+  </si>
+  <si>
+    <t>ID1779953130180</t>
+  </si>
+  <si>
+    <t>PRSRL-230-270-GO</t>
+  </si>
+  <si>
+    <t>ID1779953153190</t>
+  </si>
+  <si>
+    <t>PRRER-450-490-YK</t>
+  </si>
+  <si>
+    <t>ID1779953199741</t>
+  </si>
+  <si>
+    <t>PRRER-360-400-SS</t>
+  </si>
+  <si>
+    <t>ID1779953241499</t>
+  </si>
+  <si>
+    <t>M45BBLD-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953260859</t>
+  </si>
+  <si>
+    <t>M89CER-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953383633</t>
+  </si>
+  <si>
+    <t>ID1779956331825</t>
+  </si>
+  <si>
+    <t>PRTDL-C-GO</t>
+  </si>
+  <si>
+    <t>ID1779956377322</t>
+  </si>
+  <si>
+    <t>PRSRM-C-GO</t>
+  </si>
+  <si>
+    <t>ID1779956605362</t>
   </si>
 </sst>
 </file>
@@ -3444,7 +3510,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3502,7 +3568,6 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -11329,10 +11394,10 @@
         <v>629</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G331" s="9">
-        <v>46247.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="332">
@@ -11407,7 +11472,7 @@
         <v>635</v>
       </c>
       <c r="G334" s="9">
-        <v>46194.0</v>
+        <v>46193.0</v>
       </c>
       <c r="I334" s="2" t="s">
         <v>233</v>
@@ -11415,7 +11480,7 @@
     </row>
     <row r="335">
       <c r="A335" s="1">
-        <v>1.776148732087E12</v>
+        <v>1.776148761624E12</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>535</v>
@@ -11424,16 +11489,16 @@
         <v>11</v>
       </c>
       <c r="D335" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>636</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="G335" s="9">
-        <v>46197.0</v>
+        <v>46203.0</v>
       </c>
       <c r="I335" s="2" t="s">
         <v>233</v>
@@ -11441,25 +11506,25 @@
     </row>
     <row r="336">
       <c r="A336" s="1">
-        <v>1.776148761624E12</v>
+        <v>1.776149046956E12</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D336" s="2">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G336" s="9">
-        <v>46203.0</v>
+        <v>46182.0</v>
       </c>
       <c r="I336" s="2" t="s">
         <v>233</v>
@@ -11467,51 +11532,44 @@
     </row>
     <row r="337">
       <c r="A337" s="1">
-        <v>1.776149046956E12</v>
+        <v>1.776149087494E12</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D337" s="2">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F337" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="G337" s="9">
-        <v>46182.0</v>
-      </c>
-      <c r="I337" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="F337" s="4"/>
     </row>
     <row r="338">
       <c r="A338" s="1">
-        <v>1.776149087494E12</v>
+        <v>1.776169705463E12</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D338" s="2">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>641</v>
+        <v>534</v>
       </c>
       <c r="F338" s="4"/>
+      <c r="H338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" s="1">
-        <v>1.776169705463E12</v>
+        <v>1.776301247869E12</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>112</v>
@@ -11520,17 +11578,20 @@
         <v>11</v>
       </c>
       <c r="D339" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>534</v>
+        <v>641</v>
       </c>
       <c r="F339" s="4"/>
+      <c r="G339" s="9">
+        <v>46840.0</v>
+      </c>
       <c r="H339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" s="1">
-        <v>1.776301247869E12</v>
+        <v>1.776301425645E12</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>112</v>
@@ -11539,20 +11600,21 @@
         <v>11</v>
       </c>
       <c r="D340" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="F340" s="4"/>
+      <c r="F340" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="G340" s="9">
-        <v>46840.0</v>
-      </c>
-      <c r="H340" s="2"/>
+        <v>46640.0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1">
-        <v>1.776301425645E12</v>
+        <v>1.776327582548E12</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>112</v>
@@ -11561,41 +11623,41 @@
         <v>11</v>
       </c>
       <c r="D341" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F341" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G341" s="9">
-        <v>46640.0</v>
+      <c r="F341" s="3">
+        <v>11504.0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1">
-        <v>1.776327582548E12</v>
+        <v>1.776327623153E12</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D342" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E342" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F342" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="F342" s="3">
-        <v>11504.0</v>
+      <c r="G342" s="9">
+        <v>46949.0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1">
-        <v>1.776327623153E12</v>
+        <v>1.776327677276E12</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>112</v>
@@ -11604,7 +11666,7 @@
         <v>33</v>
       </c>
       <c r="D343" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>592</v>
@@ -11618,30 +11680,28 @@
     </row>
     <row r="344">
       <c r="A344" s="1">
-        <v>1.776327677276E12</v>
+        <v>1.776328486516E12</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D344" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>592</v>
+        <v>646</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="G344" s="9">
-        <v>46949.0</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="H344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" s="1">
-        <v>1.776328486516E12</v>
+        <v>1.776328499394E12</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>112</v>
@@ -11650,7 +11710,7 @@
         <v>25</v>
       </c>
       <c r="D345" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>647</v>
@@ -11658,11 +11718,10 @@
       <c r="F345" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" s="1">
-        <v>1.776328499394E12</v>
+        <v>1.776328514002E12</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>112</v>
@@ -11671,7 +11730,7 @@
         <v>25</v>
       </c>
       <c r="D346" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>648</v>
@@ -11682,7 +11741,7 @@
     </row>
     <row r="347">
       <c r="A347" s="1">
-        <v>1.776328514002E12</v>
+        <v>1.776334155137E12</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>112</v>
@@ -11691,18 +11750,21 @@
         <v>25</v>
       </c>
       <c r="D347" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>649</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>418</v>
+        <v>241</v>
+      </c>
+      <c r="G347" s="9">
+        <v>46537.0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1">
-        <v>1.776334155137E12</v>
+        <v>1.776334203307E12</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>112</v>
@@ -11714,41 +11776,41 @@
         <v>13.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>650</v>
+        <v>546</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>241</v>
+        <v>476</v>
       </c>
       <c r="G348" s="9">
-        <v>46537.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1">
-        <v>1.776334203307E12</v>
+        <v>1.776334423117E12</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D349" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>546</v>
+        <v>650</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>476</v>
+        <v>241</v>
       </c>
       <c r="G349" s="9">
-        <v>46530.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1">
-        <v>1.776334423117E12</v>
+        <v>1.776334444257E12</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>112</v>
@@ -11763,15 +11825,15 @@
         <v>651</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G350" s="9">
-        <v>46479.0</v>
+        <v>46468.0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1">
-        <v>1.776334444257E12</v>
+        <v>1.776334474615E12</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>112</v>
@@ -11794,7 +11856,7 @@
     </row>
     <row r="352">
       <c r="A352" s="1">
-        <v>1.776334474615E12</v>
+        <v>1.776334496105E12</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>112</v>
@@ -11808,16 +11870,11 @@
       <c r="E352" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F352" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G352" s="9">
-        <v>46468.0</v>
-      </c>
+      <c r="F352" s="4"/>
     </row>
     <row r="353">
       <c r="A353" s="1">
-        <v>1.776334496105E12</v>
+        <v>1.776334545035E12</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>112</v>
@@ -11831,11 +11888,16 @@
       <c r="E353" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="F353" s="4"/>
+      <c r="F353" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G353" s="9">
+        <v>46468.0</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1">
-        <v>1.776334545035E12</v>
+        <v>1.776398955451E12</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>112</v>
@@ -11844,21 +11906,21 @@
         <v>27</v>
       </c>
       <c r="D354" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>655</v>
+        <v>569</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>238</v>
+        <v>590</v>
       </c>
       <c r="G354" s="9">
-        <v>46468.0</v>
+        <v>46768.0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1">
-        <v>1.776398955451E12</v>
+        <v>1.776398987942E12</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>112</v>
@@ -11870,18 +11932,18 @@
         <v>17.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>569</v>
+        <v>655</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>590</v>
       </c>
       <c r="G355" s="9">
-        <v>46768.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1">
-        <v>1.776398987942E12</v>
+        <v>1.776399071673E12</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>112</v>
@@ -11893,90 +11955,90 @@
         <v>17.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>590</v>
       </c>
       <c r="G356" s="9">
-        <v>46947.0</v>
+        <v>46771.0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1">
-        <v>1.776399071673E12</v>
+        <v>1.776399111607E12</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D357" s="2">
         <v>17.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>573</v>
+        <v>656</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>590</v>
+        <v>493</v>
       </c>
       <c r="G357" s="9">
-        <v>46771.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1">
-        <v>1.776399111607E12</v>
+        <v>1.776399379582E12</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D358" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>657</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>493</v>
+        <v>658</v>
       </c>
       <c r="G358" s="9">
-        <v>46794.0</v>
+        <v>46691.0</v>
+      </c>
+      <c r="H358" s="2" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1">
-        <v>1.776399379582E12</v>
+        <v>1.776400103874E12</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D359" s="2">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>659</v>
+        <v>145</v>
       </c>
       <c r="G359" s="9">
-        <v>46691.0</v>
-      </c>
-      <c r="H359" s="2" t="s">
-        <v>660</v>
+        <v>46543.0</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1">
-        <v>1.776400103874E12</v>
+        <v>1.776400120665E12</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>112</v>
@@ -11985,21 +12047,21 @@
         <v>25</v>
       </c>
       <c r="D360" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>661</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="G360" s="9">
-        <v>46543.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1">
-        <v>1.776400120665E12</v>
+        <v>1.77640716912E12</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>112</v>
@@ -12008,21 +12070,21 @@
         <v>25</v>
       </c>
       <c r="D361" s="2">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F361" s="3" t="s">
-        <v>241</v>
+        <v>554</v>
+      </c>
+      <c r="F361" s="3">
+        <v>11503.0</v>
       </c>
       <c r="G361" s="9">
-        <v>46479.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1">
-        <v>1.77640716912E12</v>
+        <v>1.776407375241E12</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>112</v>
@@ -12031,21 +12093,21 @@
         <v>25</v>
       </c>
       <c r="D362" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F362" s="3">
-        <v>11503.0</v>
+        <v>660</v>
+      </c>
+      <c r="F362" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="G362" s="9">
-        <v>46516.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1">
-        <v>1.776407375241E12</v>
+        <v>1.77640744785E12</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>112</v>
@@ -12054,7 +12116,7 @@
         <v>25</v>
       </c>
       <c r="D363" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>661</v>
@@ -12063,97 +12125,97 @@
         <v>663</v>
       </c>
       <c r="G363" s="9">
-        <v>46669.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1">
-        <v>1.77640744785E12</v>
+        <v>1.776407858481E12</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D364" s="2">
         <v>12.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F364" s="3" t="s">
         <v>664</v>
       </c>
+      <c r="F364" s="4"/>
       <c r="G364" s="9">
         <v>46523.0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1">
-        <v>1.776407858481E12</v>
+        <v>1.776436049209E12</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D365" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>665</v>
+        <v>47</v>
       </c>
       <c r="F365" s="4"/>
-      <c r="G365" s="9">
-        <v>46523.0</v>
-      </c>
     </row>
     <row r="366">
       <c r="A366" s="1">
-        <v>1.776436049209E12</v>
+        <v>1.776659068274E12</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>537</v>
+        <v>112</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D366" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F366" s="4"/>
+        <v>665</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G366" s="9">
+        <v>46793.0</v>
+      </c>
     </row>
     <row r="367">
-      <c r="A367" s="1">
-        <v>1.776659068274E12</v>
+      <c r="A367" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D367" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>666</v>
+        <v>66</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G367" s="9">
-        <v>46793.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>112</v>
@@ -12162,67 +12224,62 @@
         <v>33</v>
       </c>
       <c r="D368" s="2">
-        <v>9.0</v>
+        <v>20.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>66</v>
+        <v>670</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G368" s="9">
-        <v>46949.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D369" s="2">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="G369" s="9">
-        <v>46793.0</v>
+        <v>46639.0</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D370" s="2">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F370" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="G370" s="9">
-        <v>46639.0</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="F370" s="4"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>10</v>
@@ -12231,34 +12288,34 @@
         <v>27</v>
       </c>
       <c r="D371" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F371" s="4"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D372" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F372" s="4"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>10</v>
@@ -12270,7 +12327,7 @@
         <v>5.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F373" s="4"/>
     </row>
@@ -12282,13 +12339,13 @@
         <v>10</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D374" s="2">
         <v>5.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F374" s="4"/>
     </row>
@@ -12300,13 +12357,13 @@
         <v>10</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D375" s="2">
         <v>5.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F375" s="4"/>
     </row>
@@ -12318,33 +12375,35 @@
         <v>10</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D376" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="F376" s="4"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D377" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="F377" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="F377" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
@@ -12360,15 +12419,18 @@
         <v>2.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>584</v>
+        <v>687</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>293</v>
+        <v>346</v>
+      </c>
+      <c r="G378" s="9">
+        <v>46488.0</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>32</v>
@@ -12380,18 +12442,15 @@
         <v>2.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G379" s="9">
-        <v>46488.0</v>
+        <v>690</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>32</v>
@@ -12400,42 +12459,42 @@
         <v>25</v>
       </c>
       <c r="D380" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>691</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="G380" s="9">
+        <v>46716.0</v>
+      </c>
+      <c r="H380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="F381" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G381" s="9">
-        <v>46716.0</v>
-      </c>
-      <c r="H381" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="F381" s="3">
+        <v>11504.0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>112</v>
@@ -12444,84 +12503,87 @@
         <v>11</v>
       </c>
       <c r="D382" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F382" s="3">
         <v>11504.0</v>
       </c>
+      <c r="H382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D383" s="2">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="F383" s="3">
-        <v>11504.0</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="F383" s="4"/>
       <c r="H383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D384" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="F384" s="4"/>
-      <c r="H384" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="F384" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G384" s="9">
+        <v>46240.0</v>
+      </c>
+      <c r="H384" s="2" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D385" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>702</v>
+        <v>671</v>
       </c>
       <c r="G385" s="9">
-        <v>46240.0</v>
-      </c>
-      <c r="H385" s="2" t="s">
-        <v>703</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>112</v>
@@ -12530,67 +12592,70 @@
         <v>11</v>
       </c>
       <c r="D386" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="G386" s="9">
-        <v>46416.0</v>
+        <v>46544.0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D387" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G387" s="9">
-        <v>46544.0</v>
+        <v>46856.0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D388" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G388" s="9">
-        <v>46856.0</v>
+        <v>46794.0</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>112</v>
@@ -12602,21 +12667,18 @@
         <v>16.0</v>
       </c>
       <c r="E389" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F389" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F389" s="3" t="s">
-        <v>714</v>
-      </c>
       <c r="G389" s="9">
-        <v>46794.0</v>
-      </c>
-      <c r="H389" s="2" t="s">
-        <v>715</v>
+        <v>46785.0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>112</v>
@@ -12628,13 +12690,13 @@
         <v>16.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>717</v>
+        <v>585</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G390" s="9">
-        <v>46785.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="391">
@@ -12651,41 +12713,44 @@
         <v>16.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>585</v>
+        <v>719</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G391" s="9">
-        <v>46789.0</v>
+        <v>46839.0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D392" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="G392" s="9">
-        <v>46839.0</v>
+        <v>46312.0</v>
+      </c>
+      <c r="H392" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>112</v>
@@ -12694,24 +12759,22 @@
         <v>11</v>
       </c>
       <c r="D393" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>722</v>
+        <v>655</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G393" s="9">
-        <v>46312.0</v>
-      </c>
-      <c r="H393" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>46669.0</v>
+      </c>
+      <c r="H393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>112</v>
@@ -12720,18 +12783,17 @@
         <v>11</v>
       </c>
       <c r="D394" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>656</v>
+        <v>573</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>725</v>
+        <v>165</v>
       </c>
       <c r="G394" s="9">
-        <v>46669.0</v>
-      </c>
-      <c r="H394" s="2"/>
+        <v>46540.0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
@@ -12741,24 +12803,24 @@
         <v>112</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D395" s="2">
-        <v>22.0</v>
+        <v>7.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>573</v>
+        <v>727</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>165</v>
+        <v>713</v>
       </c>
       <c r="G395" s="9">
-        <v>46540.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>112</v>
@@ -12770,41 +12832,39 @@
         <v>7.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="G396" s="9">
-        <v>46794.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D397" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F397" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="G397" s="9">
-        <v>46792.0</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="F397" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="H397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>112</v>
@@ -12813,176 +12873,175 @@
         <v>11</v>
       </c>
       <c r="D398" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F398" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="H398" s="2"/>
+        <v>115004.0</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D399" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F399" s="3">
-        <v>115004.0</v>
+        <v>11505.0</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D400" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="F400" s="3">
-        <v>11505.0</v>
+        <v>738</v>
+      </c>
+      <c r="F400" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G400" s="9">
+        <v>46162.0</v>
+      </c>
+      <c r="H400" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I400" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D401" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="F401" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G401" s="9">
-        <v>46162.0</v>
-      </c>
-      <c r="H401" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I401" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="F401" s="4"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D402" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="F402" s="4"/>
+        <v>742</v>
+      </c>
+      <c r="F402" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G402" s="9">
+        <v>46152.0</v>
+      </c>
+      <c r="H402" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I402" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D403" s="2">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>326</v>
+        <v>663</v>
       </c>
       <c r="G403" s="9">
-        <v>46152.0</v>
-      </c>
-      <c r="H403" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I403" s="2" t="s">
-        <v>233</v>
+        <v>46596.0</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D404" s="2">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F404" s="3" t="s">
-        <v>664</v>
+        <v>747</v>
       </c>
       <c r="G404" s="9">
-        <v>46596.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D405" s="2">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>747</v>
+        <v>648</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="G405" s="9">
-        <v>46669.0</v>
+        <v>385</v>
       </c>
     </row>
     <row r="406">
@@ -12996,148 +13055,148 @@
         <v>25</v>
       </c>
       <c r="D406" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>649</v>
+        <v>750</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>385</v>
+        <v>418</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D407" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>418</v>
+        <v>95</v>
+      </c>
+      <c r="G407" s="9">
+        <v>46694.0</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D408" s="2">
-        <v>18.0</v>
+        <v>25</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>753</v>
+        <v>559</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>95</v>
+        <v>754</v>
       </c>
       <c r="G408" s="9">
-        <v>46694.0</v>
+        <v>46410.0</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
+      </c>
+      <c r="D409" s="2">
+        <v>22.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>559</v>
+        <v>756</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G409" s="9">
-        <v>46410.0</v>
+        <v>46194.0</v>
+      </c>
+      <c r="I409" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D410" s="2">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G410" s="9">
-        <v>46194.0</v>
-      </c>
-      <c r="I410" s="2" t="s">
-        <v>233</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D411" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>760</v>
+        <v>588</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G411" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D412" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F412" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="G412" s="9">
-        <v>46913.0</v>
+        <v>643</v>
+      </c>
+      <c r="F412" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="413">
@@ -13145,24 +13204,24 @@
         <v>764</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D413" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F413" s="3">
-        <v>11505.0</v>
+        <v>765</v>
+      </c>
+      <c r="F413" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>10</v>
@@ -13174,7 +13233,7 @@
         <v>2.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>766</v>
+        <v>15</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>224</v>
@@ -13194,10 +13253,10 @@
         <v>2.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="416">
@@ -13208,21 +13267,24 @@
         <v>10</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D416" s="2">
         <v>2.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="F416" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G416" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>10</v>
@@ -13231,42 +13293,42 @@
         <v>25</v>
       </c>
       <c r="D417" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F417" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="F417" s="4"/>
       <c r="G417" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D418" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="F418" s="4"/>
+        <v>773</v>
+      </c>
+      <c r="F418" s="3" t="s">
+        <v>774</v>
+      </c>
       <c r="G418" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>32</v>
@@ -13278,36 +13340,33 @@
         <v>4.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G419" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D420" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="F420" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="G420" s="9">
-        <v>46484.0</v>
+        <v>547</v>
+      </c>
+      <c r="F420" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="421">
@@ -13315,19 +13374,19 @@
         <v>778</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D421" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F421" s="3">
-        <v>11505.0</v>
+        <v>712</v>
+      </c>
+      <c r="F421" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="422">
@@ -13338,67 +13397,70 @@
         <v>32</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D422" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>713</v>
+        <v>780</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>55</v>
+        <v>604</v>
+      </c>
+      <c r="G422" s="9">
+        <v>46577.0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D423" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>604</v>
+        <v>272</v>
       </c>
       <c r="G423" s="9">
-        <v>46577.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D424" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="G424" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>112</v>
@@ -13410,18 +13472,18 @@
         <v>17.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G425" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>112</v>
@@ -13433,18 +13495,18 @@
         <v>17.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G426" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>112</v>
@@ -13456,18 +13518,18 @@
         <v>17.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G427" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>112</v>
@@ -13479,53 +13541,50 @@
         <v>17.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F428" s="3" t="s">
-        <v>595</v>
+        <v>793</v>
       </c>
       <c r="G428" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D429" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="G429" s="9">
-        <v>46523.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D430" s="2">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>224</v>
@@ -13533,19 +13592,19 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D431" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>224</v>
@@ -13553,7 +13612,7 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>32</v>
@@ -13562,10 +13621,10 @@
         <v>27</v>
       </c>
       <c r="D432" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>224</v>
@@ -13573,50 +13632,53 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D433" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>224</v>
+        <v>238</v>
+      </c>
+      <c r="G433" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F434" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G434" s="9">
-        <v>46281.0</v>
+        <v>493</v>
+      </c>
+      <c r="H434" s="2" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>32</v>
@@ -13625,21 +13687,21 @@
         <v>11</v>
       </c>
       <c r="D435" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H435" s="2" t="s">
-        <v>807</v>
+      <c r="G435" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>32</v>
@@ -13648,67 +13710,67 @@
         <v>11</v>
       </c>
       <c r="D436" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="G436" s="9">
-        <v>47146.0</v>
+      <c r="H436" s="2" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D437" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>811</v>
+        <v>752</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H437" s="2" t="s">
-        <v>807</v>
+        <v>812</v>
+      </c>
+      <c r="G437" s="9">
+        <v>46666.0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C438" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D438" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>753</v>
+        <v>814</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="G438" s="9">
-        <v>46666.0</v>
+        <v>46583.0</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>32</v>
@@ -13720,18 +13782,18 @@
         <v>8.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G439" s="9">
-        <v>46583.0</v>
+        <v>46604.0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>32</v>
@@ -13743,13 +13805,13 @@
         <v>8.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>818</v>
+        <v>110</v>
       </c>
       <c r="G440" s="9">
-        <v>46604.0</v>
+        <v>46626.0</v>
       </c>
     </row>
     <row r="441">
@@ -13766,18 +13828,18 @@
         <v>8.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>110</v>
+        <v>820</v>
       </c>
       <c r="G441" s="9">
-        <v>46626.0</v>
+        <v>46658.0</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>32</v>
@@ -13789,105 +13851,105 @@
         <v>8.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G442" s="9">
-        <v>46658.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D443" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F443" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="G443" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="F443" s="4"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D444" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="F444" s="4"/>
+        <v>826</v>
+      </c>
+      <c r="F444" s="3" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D445" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>493</v>
+        <v>829</v>
+      </c>
+      <c r="G445" s="9">
+        <v>46792.0</v>
+      </c>
+      <c r="H445" s="2" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D446" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="G446" s="9">
-        <v>46792.0</v>
-      </c>
-      <c r="H446" s="2" t="s">
-        <v>831</v>
+        <v>46304.0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>32</v>
@@ -13896,16 +13958,16 @@
         <v>11</v>
       </c>
       <c r="D447" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>833</v>
+        <v>582</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>834</v>
+        <v>51</v>
       </c>
       <c r="G447" s="9">
-        <v>46304.0</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="448">
@@ -13919,21 +13981,21 @@
         <v>11</v>
       </c>
       <c r="D448" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>582</v>
+        <v>836</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>51</v>
+        <v>359</v>
       </c>
       <c r="G448" s="9">
-        <v>46416.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>32</v>
@@ -13942,59 +14004,59 @@
         <v>11</v>
       </c>
       <c r="D449" s="2">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="G449" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>37</v>
+        <v>663</v>
       </c>
       <c r="G450" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D451" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E451" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="B451" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C451" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D451" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E451" s="2" t="s">
-        <v>841</v>
-      </c>
       <c r="F451" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G451" s="9">
         <v>46794.0</v>
@@ -14011,16 +14073,16 @@
         <v>25</v>
       </c>
       <c r="D452" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>841</v>
+        <v>544</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G452" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="453">
@@ -14031,47 +14093,47 @@
         <v>112</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D453" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>544</v>
+        <v>729</v>
       </c>
       <c r="F453" s="3" t="s">
-        <v>664</v>
+        <v>844</v>
       </c>
       <c r="G453" s="9">
-        <v>46484.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D454" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>730</v>
+        <v>846</v>
       </c>
       <c r="F454" s="3" t="s">
-        <v>845</v>
+        <v>579</v>
       </c>
       <c r="G454" s="9">
-        <v>46792.0</v>
+        <v>46676.0</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>32</v>
@@ -14083,36 +14145,36 @@
         <v>9.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="F455" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="G455" s="9">
-        <v>46676.0</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="F455" s="4"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
         <v>848</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="F456" s="4"/>
+        <v>849</v>
+      </c>
+      <c r="F456" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G456" s="9">
+        <v>46641.0</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>112</v>
@@ -14121,21 +14183,21 @@
         <v>11</v>
       </c>
       <c r="D457" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G457" s="9">
-        <v>46641.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>112</v>
@@ -14144,44 +14206,47 @@
         <v>11</v>
       </c>
       <c r="D458" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>708</v>
+        <v>663</v>
       </c>
       <c r="G458" s="9">
-        <v>46530.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D459" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>664</v>
+        <v>707</v>
       </c>
       <c r="G459" s="9">
-        <v>46949.0</v>
+        <v>46523.0</v>
+      </c>
+      <c r="H459" s="2" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>112</v>
@@ -14190,19 +14255,16 @@
         <v>25</v>
       </c>
       <c r="D460" s="2">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>856</v>
+        <v>832</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>708</v>
+        <v>579</v>
       </c>
       <c r="G460" s="9">
-        <v>46523.0</v>
-      </c>
-      <c r="H460" s="2" t="s">
-        <v>857</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="461">
@@ -14219,13 +14281,13 @@
         <v>3.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G461" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="462">
@@ -14242,7 +14304,7 @@
         <v>3.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>449</v>
@@ -14256,7 +14318,7 @@
         <v>860</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>25</v>
@@ -14265,13 +14327,13 @@
         <v>3.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>449</v>
+        <v>579</v>
       </c>
       <c r="G463" s="9">
-        <v>46752.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="464">
@@ -14288,13 +14350,13 @@
         <v>3.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G464" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="465">
@@ -14311,13 +14373,13 @@
         <v>3.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>449</v>
+        <v>45</v>
       </c>
       <c r="G465" s="9">
-        <v>46752.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="466">
@@ -14325,22 +14387,19 @@
         <v>863</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D466" s="2">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>833</v>
+        <v>578</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G466" s="9">
-        <v>46366.0</v>
+        <v>668</v>
       </c>
     </row>
     <row r="467">
@@ -14348,68 +14407,71 @@
         <v>864</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D467" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>669</v>
+        <v>865</v>
+      </c>
+      <c r="G467" s="9">
+        <v>46670.0</v>
+      </c>
+      <c r="H467" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D468" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>572</v>
+        <v>867</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>866</v>
+        <v>95</v>
       </c>
       <c r="G468" s="9">
-        <v>46670.0</v>
-      </c>
-      <c r="H468" s="2" t="s">
-        <v>52</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D469" s="2">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>868</v>
+        <v>573</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="G469" s="9">
-        <v>46725.0</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="470">
@@ -14426,18 +14488,18 @@
         <v>22.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>573</v>
+        <v>870</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="G470" s="9">
-        <v>46556.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>112</v>
@@ -14449,41 +14511,42 @@
         <v>22.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>142</v>
+        <v>873</v>
       </c>
       <c r="G471" s="9">
-        <v>46793.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D472" s="2">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>874</v>
+        <v>606</v>
       </c>
       <c r="G472" s="9">
-        <v>46670.0</v>
-      </c>
+        <v>46254.0</v>
+      </c>
+      <c r="H472" s="2"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>32</v>
@@ -14492,37 +14555,36 @@
         <v>11</v>
       </c>
       <c r="D473" s="2">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>606</v>
+        <v>405</v>
       </c>
       <c r="G473" s="9">
-        <v>46254.0</v>
-      </c>
-      <c r="H473" s="2"/>
+        <v>46669.0</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D474" s="2">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>405</v>
+        <v>880</v>
       </c>
       <c r="G474" s="9">
         <v>46669.0</v>
@@ -14530,7 +14592,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>32</v>
@@ -14542,10 +14604,10 @@
         <v>6.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="G475" s="9">
         <v>46669.0</v>
@@ -14553,7 +14615,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>32</v>
@@ -14565,10 +14627,10 @@
         <v>6.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>884</v>
+        <v>812</v>
       </c>
       <c r="G476" s="9">
         <v>46669.0</v>
@@ -14588,10 +14650,10 @@
         <v>6.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>813</v>
+        <v>886</v>
       </c>
       <c r="G477" s="9">
         <v>46669.0</v>
@@ -14599,30 +14661,30 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D478" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G478" s="9">
-        <v>46669.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>32</v>
@@ -14634,13 +14696,13 @@
         <v>18.0</v>
       </c>
       <c r="E479" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F479" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="F479" s="3" t="s">
-        <v>890</v>
-      </c>
       <c r="G479" s="9">
-        <v>46947.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="480">
@@ -14657,10 +14719,10 @@
         <v>18.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>601</v>
+        <v>66</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G480" s="9">
         <v>46949.0</v>
@@ -14680,13 +14742,10 @@
         <v>18.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>66</v>
+        <v>832</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="G481" s="9">
-        <v>46949.0</v>
+        <v>889</v>
       </c>
     </row>
     <row r="482">
@@ -14700,13 +14759,16 @@
         <v>27</v>
       </c>
       <c r="D482" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>890</v>
+        <v>43</v>
+      </c>
+      <c r="G482" s="9">
+        <v>46730.0</v>
       </c>
     </row>
     <row r="483">
@@ -14717,39 +14779,36 @@
         <v>32</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D483" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>833</v>
+        <v>895</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G483" s="9">
-        <v>46730.0</v>
+        <v>346</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C484" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D484" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E484" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B484" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C484" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D484" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E484" s="2" t="s">
-        <v>896</v>
-      </c>
       <c r="F484" s="3" t="s">
-        <v>346</v>
+        <v>118</v>
       </c>
     </row>
     <row r="485">
@@ -14760,64 +14819,67 @@
         <v>32</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D485" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>118</v>
+        <v>441</v>
+      </c>
+      <c r="G485" s="9">
+        <v>46267.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D486" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="F486" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G486" s="9">
-        <v>46267.0</v>
+        <v>900</v>
+      </c>
+      <c r="F486" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D487" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="F487" s="3">
-        <v>11505.0</v>
+        <v>902</v>
+      </c>
+      <c r="F487" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="G487" s="9">
+        <v>46250.0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>32</v>
@@ -14829,59 +14891,59 @@
         <v>8.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>761</v>
+        <v>359</v>
       </c>
       <c r="G488" s="9">
-        <v>46250.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D489" s="2">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="G489" s="9">
-        <v>46255.0</v>
+        <v>46613.0</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D490" s="2">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>907</v>
+        <v>607</v>
       </c>
       <c r="F490" s="3" t="s">
-        <v>470</v>
+        <v>608</v>
       </c>
       <c r="G490" s="9">
-        <v>46613.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="491">
@@ -14889,22 +14951,19 @@
         <v>908</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D491" s="2">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F491" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="G491" s="9">
-        <v>46669.0</v>
+        <v>547</v>
+      </c>
+      <c r="F491" s="3">
+        <v>11504.0</v>
       </c>
     </row>
     <row r="492">
@@ -14912,24 +14971,27 @@
         <v>909</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D492" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F492" s="3">
-        <v>11504.0</v>
+        <v>910</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G492" s="9">
+        <v>46691.0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>32</v>
@@ -14941,13 +15003,13 @@
         <v>7.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F493" s="3" t="s">
-        <v>449</v>
+        <v>889</v>
       </c>
       <c r="G493" s="9">
-        <v>46691.0</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="494">
@@ -14958,24 +15020,19 @@
         <v>32</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D494" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="F494" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="G494" s="9">
-        <v>46775.0</v>
-      </c>
+        <v>913</v>
+      </c>
+      <c r="F494" s="4"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>32</v>
@@ -14987,13 +15044,13 @@
         <v>11.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F495" s="4"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>32</v>
@@ -15005,13 +15062,13 @@
         <v>11.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>32</v>
@@ -15023,77 +15080,77 @@
         <v>11.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F497" s="4"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D498" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="F498" s="4"/>
+        <v>921</v>
+      </c>
+      <c r="F498" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="G498" s="9">
+        <v>46803.0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D499" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>922</v>
+        <v>875</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G499" s="9">
-        <v>46803.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D500" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="F500" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="G500" s="9">
-        <v>46222.0</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="F500" s="4"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>32</v>
@@ -15105,13 +15162,13 @@
         <v>11.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F501" s="4"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -15123,13 +15180,13 @@
         <v>11.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F502" s="4"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>32</v>
@@ -15141,31 +15198,34 @@
         <v>11.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F503" s="4"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D504" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F504" s="4"/>
+      <c r="G504" s="9">
+        <v>46564.0</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>32</v>
@@ -15177,16 +15237,16 @@
         <v>14.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F505" s="4"/>
       <c r="G505" s="9">
-        <v>46564.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>32</v>
@@ -15198,16 +15258,16 @@
         <v>14.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F506" s="4"/>
       <c r="G506" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>32</v>
@@ -15216,10 +15276,10 @@
         <v>25</v>
       </c>
       <c r="D507" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F507" s="4"/>
       <c r="G507" s="9">
@@ -15228,7 +15288,7 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>32</v>
@@ -15240,16 +15300,16 @@
         <v>15.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F508" s="4"/>
       <c r="G508" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>32</v>
@@ -15261,7 +15321,7 @@
         <v>15.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F509" s="4"/>
       <c r="G509" s="9">
@@ -15270,7 +15330,7 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>32</v>
@@ -15282,7 +15342,7 @@
         <v>15.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F510" s="4"/>
       <c r="G510" s="9">
@@ -15291,7 +15351,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>32</v>
@@ -15300,19 +15360,19 @@
         <v>25</v>
       </c>
       <c r="D511" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F511" s="4"/>
       <c r="G511" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>32</v>
@@ -15324,98 +15384,100 @@
         <v>11.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F512" s="4"/>
       <c r="G512" s="9">
-        <v>46551.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D513" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>951</v>
-      </c>
-      <c r="F513" s="4"/>
-      <c r="G513" s="9">
-        <v>46394.0</v>
+        <v>952</v>
+      </c>
+      <c r="F513" s="3" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D514" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="F514" s="3" t="s">
-        <v>418</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="F514" s="4"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D515" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="F515" s="4"/>
+        <v>956</v>
+      </c>
+      <c r="F515" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G515" s="9">
+        <v>46759.0</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D516" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>418</v>
+        <v>37</v>
       </c>
       <c r="G516" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>537</v>
@@ -15427,7 +15489,7 @@
         <v>3.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F517" s="3" t="s">
         <v>37</v>
@@ -15438,7 +15500,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>537</v>
@@ -15450,7 +15512,7 @@
         <v>3.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>37</v>
@@ -15461,7 +15523,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>537</v>
@@ -15473,7 +15535,7 @@
         <v>3.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>37</v>
@@ -15484,7 +15546,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>537</v>
@@ -15496,10 +15558,10 @@
         <v>3.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="F520" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G520" s="9">
         <v>46406.0</v>
@@ -15519,18 +15581,18 @@
         <v>3.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="F521" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G521" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>537</v>
@@ -15542,18 +15604,18 @@
         <v>3.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G522" s="9">
-        <v>46251.0</v>
+        <v>46258.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>537</v>
@@ -15565,18 +15627,18 @@
         <v>3.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G523" s="9">
-        <v>46258.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>537</v>
@@ -15585,21 +15647,21 @@
         <v>11</v>
       </c>
       <c r="D524" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G524" s="9">
-        <v>46254.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>537</v>
@@ -15611,7 +15673,7 @@
         <v>4.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>37</v>
@@ -15622,7 +15684,7 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>537</v>
@@ -15634,7 +15696,7 @@
         <v>4.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>37</v>
@@ -15645,7 +15707,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>537</v>
@@ -15657,7 +15719,7 @@
         <v>4.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>37</v>
@@ -15668,7 +15730,7 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>537</v>
@@ -15677,21 +15739,21 @@
         <v>11</v>
       </c>
       <c r="D528" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F528" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G528" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>537</v>
@@ -15703,18 +15765,18 @@
         <v>6.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F529" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G529" s="9">
-        <v>46251.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>537</v>
@@ -15726,18 +15788,18 @@
         <v>6.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F530" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G530" s="9">
-        <v>46280.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>537</v>
@@ -15749,18 +15811,18 @@
         <v>6.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G531" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>537</v>
@@ -15772,7 +15834,7 @@
         <v>6.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>37</v>
@@ -15783,7 +15845,7 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>537</v>
@@ -15795,7 +15857,7 @@
         <v>6.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F533" s="3" t="s">
         <v>37</v>
@@ -15806,7 +15868,7 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>537</v>
@@ -15818,18 +15880,18 @@
         <v>6.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F534" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G534" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>537</v>
@@ -15838,21 +15900,21 @@
         <v>11</v>
       </c>
       <c r="D535" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F535" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G535" s="9">
-        <v>46249.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>537</v>
@@ -15864,18 +15926,18 @@
         <v>7.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F536" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G536" s="9">
-        <v>46352.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>537</v>
@@ -15887,18 +15949,18 @@
         <v>7.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F537" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G537" s="9">
-        <v>46333.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>537</v>
@@ -15907,21 +15969,21 @@
         <v>11</v>
       </c>
       <c r="D538" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G538" s="9">
-        <v>46244.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>537</v>
@@ -15933,18 +15995,18 @@
         <v>8.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F539" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G539" s="9">
-        <v>46226.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>537</v>
@@ -15956,18 +16018,18 @@
         <v>8.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F540" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G540" s="9">
-        <v>46222.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>537</v>
@@ -15979,18 +16041,18 @@
         <v>8.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F541" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G541" s="9">
-        <v>46241.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>537</v>
@@ -16002,18 +16064,18 @@
         <v>8.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F542" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G542" s="9">
-        <v>46305.0</v>
+        <v>46319.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>537</v>
@@ -16022,21 +16084,21 @@
         <v>11</v>
       </c>
       <c r="D543" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G543" s="9">
-        <v>46319.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>537</v>
@@ -16048,13 +16110,13 @@
         <v>9.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="G544" s="9">
-        <v>46365.0</v>
+        <v>46321.0</v>
       </c>
     </row>
     <row r="545">
@@ -16068,21 +16130,24 @@
         <v>11</v>
       </c>
       <c r="D545" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G545" s="9">
-        <v>46321.0</v>
+        <v>46426.0</v>
+      </c>
+      <c r="H545" s="2" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>537</v>
@@ -16094,21 +16159,18 @@
         <v>10.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G546" s="9">
-        <v>46426.0</v>
-      </c>
-      <c r="H546" s="2" t="s">
-        <v>1016</v>
+        <v>46211.0</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>537</v>
@@ -16120,18 +16182,18 @@
         <v>10.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F547" s="3" t="s">
         <v>385</v>
       </c>
       <c r="G547" s="9">
-        <v>46211.0</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>537</v>
@@ -16143,18 +16205,18 @@
         <v>10.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F548" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G548" s="9">
-        <v>46204.0</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>537</v>
@@ -16163,21 +16225,21 @@
         <v>11</v>
       </c>
       <c r="D549" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="G549" s="9">
-        <v>46345.0</v>
+        <v>46392.0</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>537</v>
@@ -16186,21 +16248,21 @@
         <v>11</v>
       </c>
       <c r="D550" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>37</v>
+        <v>493</v>
       </c>
       <c r="G550" s="9">
-        <v>46392.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>537</v>
@@ -16209,21 +16271,22 @@
         <v>11</v>
       </c>
       <c r="D551" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F551" s="3" t="s">
-        <v>493</v>
-      </c>
+        <v>1027</v>
+      </c>
+      <c r="F551" s="4"/>
       <c r="G551" s="9">
-        <v>46366.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I551" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>537</v>
@@ -16235,7 +16298,7 @@
         <v>14.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F552" s="4"/>
       <c r="G552" s="9">
@@ -16247,7 +16310,7 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>537</v>
@@ -16259,19 +16322,16 @@
         <v>14.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F553" s="4"/>
       <c r="G553" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I553" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>537</v>
@@ -16283,7 +16343,7 @@
         <v>14.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F554" s="4"/>
       <c r="G554" s="9">
@@ -16292,7 +16352,7 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>537</v>
@@ -16301,19 +16361,18 @@
         <v>11</v>
       </c>
       <c r="D555" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F555" s="4"/>
-      <c r="G555" s="9">
-        <v>46220.0</v>
+        <v>1035</v>
+      </c>
+      <c r="F555" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>537</v>
@@ -16322,10 +16381,10 @@
         <v>11</v>
       </c>
       <c r="D556" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F556" s="3" t="s">
         <v>157</v>
@@ -16333,22 +16392,25 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C557" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D557" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="F557" s="3" t="s">
         <v>157</v>
+      </c>
+      <c r="G557" s="9">
+        <v>46223.0</v>
       </c>
     </row>
     <row r="558">
@@ -16362,21 +16424,21 @@
         <v>11</v>
       </c>
       <c r="D558" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="F558" s="3" t="s">
         <v>157</v>
       </c>
       <c r="G558" s="9">
-        <v>46223.0</v>
+        <v>46228.0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>535</v>
@@ -16385,21 +16447,21 @@
         <v>11</v>
       </c>
       <c r="D559" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>157</v>
+        <v>626</v>
       </c>
       <c r="G559" s="9">
-        <v>46223.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>535</v>
@@ -16408,21 +16470,21 @@
         <v>11</v>
       </c>
       <c r="D560" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>157</v>
+        <v>631</v>
       </c>
       <c r="G560" s="9">
-        <v>46223.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>535</v>
@@ -16431,21 +16493,21 @@
         <v>11</v>
       </c>
       <c r="D561" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>157</v>
+        <v>631</v>
       </c>
       <c r="G561" s="9">
-        <v>46228.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>535</v>
@@ -16454,44 +16516,47 @@
         <v>11</v>
       </c>
       <c r="D562" s="2">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>634</v>
+        <v>1048</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>1046</v>
+        <v>399</v>
       </c>
       <c r="G562" s="9">
-        <v>46187.0</v>
-      </c>
-      <c r="I562" s="2" t="s">
-        <v>233</v>
+        <v>46274.0</v>
+      </c>
+      <c r="H562" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D563" s="2">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>627</v>
+        <v>1051</v>
+      </c>
+      <c r="G563" s="9">
+        <v>46743.0</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>535</v>
@@ -16500,67 +16565,64 @@
         <v>11</v>
       </c>
       <c r="D564" s="2">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>626</v>
+        <v>1054</v>
       </c>
       <c r="G564" s="9">
-        <v>46269.0</v>
+        <v>46207.0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D565" s="2">
-        <v>10.0</v>
+        <v>22.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="G565" s="9">
-        <v>46240.0</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D566" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>631</v>
+        <v>1057</v>
       </c>
       <c r="G566" s="9">
-        <v>46242.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>535</v>
@@ -16569,81 +16631,80 @@
         <v>11</v>
       </c>
       <c r="D567" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F567" s="3"/>
-      <c r="G567" s="9"/>
-      <c r="H567" s="2" t="s">
-        <v>715</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="F567" s="4"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D568" s="2">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>1059</v>
+        <v>227</v>
       </c>
       <c r="G568" s="9">
-        <v>46743.0</v>
+        <v>46295.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D569" s="2">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>636</v>
+        <v>1063</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>1061</v>
+        <v>399</v>
       </c>
       <c r="G569" s="9">
-        <v>46207.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D570" s="2">
-        <v>22.0</v>
+        <v>6.0</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>1063</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1064</v>
+        <v>399</v>
+      </c>
+      <c r="G570" s="9">
+        <v>46769.0</v>
       </c>
     </row>
     <row r="571">
@@ -16654,24 +16715,24 @@
         <v>535</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D571" s="2">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>1064</v>
+        <v>627</v>
       </c>
       <c r="G571" s="9">
-        <v>46516.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>535</v>
@@ -16680,85 +16741,90 @@
         <v>11</v>
       </c>
       <c r="D572" s="2">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F572" s="4"/>
+        <v>1068</v>
+      </c>
+      <c r="F572" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="G572" s="9">
+        <v>46261.0</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D573" s="2">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>227</v>
+        <v>627</v>
       </c>
       <c r="G573" s="9">
-        <v>46295.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D574" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G574" s="9">
-        <v>46769.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D575" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G575" s="9">
-        <v>46769.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>535</v>
@@ -16770,18 +16836,18 @@
         <v>3.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F576" s="3" t="s">
         <v>627</v>
       </c>
       <c r="G576" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>535</v>
@@ -16793,7 +16859,7 @@
         <v>3.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="F577" s="3" t="s">
         <v>627</v>
@@ -16804,10 +16870,10 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>11</v>
@@ -16816,225 +16882,223 @@
         <v>3.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>627</v>
+        <v>399</v>
       </c>
       <c r="G578" s="9">
-        <v>46266.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D579" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1079</v>
+        <v>716</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>627</v>
+        <v>1082</v>
       </c>
       <c r="G579" s="9">
-        <v>46223.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D580" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>627</v>
+        <v>1082</v>
       </c>
       <c r="G580" s="9">
-        <v>46266.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D581" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E581" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="F581" s="3" t="s">
         <v>1082</v>
       </c>
-      <c r="B581" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C581" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D581" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E581" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F581" s="3" t="s">
-        <v>627</v>
-      </c>
       <c r="G581" s="9">
-        <v>46266.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D582" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1085</v>
+        <v>601</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>627</v>
+        <v>1082</v>
       </c>
       <c r="G582" s="9">
-        <v>46261.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D583" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1087</v>
+        <v>895</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>399</v>
+        <v>1088</v>
       </c>
       <c r="G583" s="9">
-        <v>46769.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C584" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D584" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>717</v>
+        <v>1090</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="G584" s="9">
-        <v>46814.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D585" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>1089</v>
+        <v>1094</v>
       </c>
       <c r="G585" s="9">
-        <v>46820.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D586" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>713</v>
+        <v>1096</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>1089</v>
+        <v>458</v>
       </c>
       <c r="G586" s="9">
-        <v>46820.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D587" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>601</v>
+        <v>1098</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G587" s="9">
-        <v>46998.0</v>
-      </c>
+        <v>1099</v>
+      </c>
+      <c r="G587" s="9"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>32</v>
@@ -17046,18 +17110,15 @@
         <v>2.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>896</v>
+        <v>1101</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G588" s="9">
-        <v>46484.0</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>32</v>
@@ -17069,18 +17130,15 @@
         <v>2.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1097</v>
+        <v>879</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G589" s="9">
-        <v>46432.0</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>32</v>
@@ -17092,18 +17150,15 @@
         <v>2.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1100</v>
+        <v>584</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G590" s="9">
-        <v>46877.0</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>32</v>
@@ -17115,18 +17170,15 @@
         <v>2.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G591" s="9">
-        <v>46704.0</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>32</v>
@@ -17138,12 +17190,11 @@
         <v>2.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G592" s="9"/>
+        <v>1099</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
@@ -17162,7 +17213,10 @@
         <v>1108</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>1106</v>
+        <v>593</v>
+      </c>
+      <c r="G593" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="594">
@@ -17170,130 +17224,146 @@
         <v>1109</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D594" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>880</v>
+        <v>1110</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>1106</v>
+        <v>1111</v>
+      </c>
+      <c r="G594" s="9">
+        <v>46877.0</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D595" s="2">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>584</v>
+        <v>849</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>1106</v>
+        <v>1111</v>
+      </c>
+      <c r="G595" s="9">
+        <v>46641.0</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D596" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E596" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F596" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="B596" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C596" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D596" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E596" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F596" s="3" t="s">
-        <v>1106</v>
+      <c r="G596" s="9">
+        <v>46743.0</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D597" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F597" s="3" t="s">
-        <v>1106</v>
+        <v>1116</v>
+      </c>
+      <c r="F597" s="4"/>
+      <c r="H597" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D598" s="2">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1115</v>
+        <v>752</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>593</v>
+        <v>1118</v>
       </c>
       <c r="G598" s="9">
-        <v>46766.0</v>
+        <v>46663.0</v>
+      </c>
+      <c r="H598" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D599" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1117</v>
+        <v>582</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="G599" s="9">
-        <v>46877.0</v>
+        <v>46437.0</v>
+      </c>
+      <c r="H599" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>112</v>
@@ -17305,18 +17375,18 @@
         <v>12.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>850</v>
+        <v>1122</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="G600" s="9">
-        <v>46641.0</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>112</v>
@@ -17328,18 +17398,18 @@
         <v>11.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1121</v>
+        <v>661</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="G601" s="9">
-        <v>46743.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>112</v>
@@ -17348,19 +17418,21 @@
         <v>11</v>
       </c>
       <c r="D602" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F602" s="4"/>
-      <c r="H602" s="2" t="s">
-        <v>133</v>
+        <v>1125</v>
+      </c>
+      <c r="F602" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G602" s="9">
+        <v>46530.0</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>112</v>
@@ -17369,73 +17441,293 @@
         <v>11</v>
       </c>
       <c r="D603" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>753</v>
+        <v>1127</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1125</v>
+        <v>1111</v>
       </c>
       <c r="G603" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H603" s="2" t="s">
-        <v>133</v>
+        <v>46834.0</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D604" s="2">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>582</v>
+        <v>1129</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="G604" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H604" s="2" t="s">
-        <v>133</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="19"/>
-      <c r="F605" s="4"/>
+      <c r="A605" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D605" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E605" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F605" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G605" s="9">
+        <v>46877.0</v>
+      </c>
     </row>
     <row r="606">
-      <c r="A606" s="19"/>
-      <c r="F606" s="4"/>
+      <c r="A606" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D606" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E606" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F606" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G606" s="9">
+        <v>46872.0</v>
+      </c>
     </row>
     <row r="607">
-      <c r="A607" s="19"/>
-      <c r="F607" s="4"/>
+      <c r="A607" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D607" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E607" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F607" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G607" s="9">
+        <v>46530.0</v>
+      </c>
     </row>
     <row r="608">
-      <c r="F608" s="4"/>
+      <c r="A608" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D608" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E608" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F608" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G608" s="9">
+        <v>46734.0</v>
+      </c>
     </row>
     <row r="609">
-      <c r="F609" s="4"/>
+      <c r="A609" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D609" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E609" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F609" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G609" s="9">
+        <v>46481.0</v>
+      </c>
     </row>
     <row r="610">
-      <c r="F610" s="4"/>
+      <c r="A610" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D610" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E610" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F610" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G610" s="9">
+        <v>46872.0</v>
+      </c>
     </row>
     <row r="611">
-      <c r="F611" s="4"/>
+      <c r="A611" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D611" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E611" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F611" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G611" s="9">
+        <v>46877.0</v>
+      </c>
     </row>
     <row r="612">
-      <c r="F612" s="4"/>
+      <c r="A612" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D612" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E612" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F612" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G612" s="9">
+        <v>46641.0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D613" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E613" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G613" s="9">
+        <v>46274.0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D614" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E614" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F614" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G614" s="9">
+        <v>46274.0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D615" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E615" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F615" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G615" s="9">
+        <v>46274.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="1148">
   <si>
     <t>ID</t>
   </si>
@@ -3230,12 +3230,6 @@
   </si>
   <si>
     <t>M89TDL-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779701979254</t>
-  </si>
-  <si>
-    <t>M89FM-KR-C</t>
   </si>
   <si>
     <t>ID1779702003682</t>
@@ -16842,7 +16836,7 @@
         <v>627</v>
       </c>
       <c r="G576" s="9">
-        <v>46266.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="577">
@@ -16850,7 +16844,7 @@
         <v>1077</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>11</v>
@@ -16862,10 +16856,10 @@
         <v>1078</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>627</v>
+        <v>399</v>
       </c>
       <c r="G577" s="9">
-        <v>46261.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="578">
@@ -16873,22 +16867,22 @@
         <v>1079</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D578" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E578" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F578" s="3" t="s">
         <v>1080</v>
       </c>
-      <c r="F578" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="G578" s="9">
-        <v>46769.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="579">
@@ -16905,13 +16899,13 @@
         <v>14.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>716</v>
+        <v>1082</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G579" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="580">
@@ -16928,10 +16922,10 @@
         <v>14.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1084</v>
+        <v>712</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G580" s="9">
         <v>46820.0</v>
@@ -16939,7 +16933,7 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>112</v>
@@ -16951,36 +16945,36 @@
         <v>14.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>712</v>
+        <v>601</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G581" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D582" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>601</v>
+        <v>895</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="G582" s="9">
-        <v>46998.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="583">
@@ -16997,18 +16991,18 @@
         <v>2.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>895</v>
+        <v>1088</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="G583" s="9">
-        <v>46484.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>32</v>
@@ -17020,18 +17014,18 @@
         <v>2.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G584" s="9">
-        <v>46432.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>32</v>
@@ -17043,13 +17037,13 @@
         <v>2.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>1094</v>
+        <v>458</v>
       </c>
       <c r="G585" s="9">
-        <v>46877.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="586">
@@ -17069,15 +17063,13 @@
         <v>1096</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G586" s="9">
-        <v>46704.0</v>
-      </c>
+        <v>1097</v>
+      </c>
+      <c r="G586" s="9"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>32</v>
@@ -17089,12 +17081,11 @@
         <v>2.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G587" s="9"/>
+        <v>1097</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
@@ -17110,15 +17101,15 @@
         <v>2.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1101</v>
+        <v>879</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>32</v>
@@ -17130,15 +17121,15 @@
         <v>2.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>879</v>
+        <v>584</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>32</v>
@@ -17150,15 +17141,15 @@
         <v>2.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>584</v>
+        <v>1099</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>32</v>
@@ -17170,10 +17161,10 @@
         <v>2.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="592">
@@ -17193,7 +17184,10 @@
         <v>1106</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1099</v>
+        <v>593</v>
+      </c>
+      <c r="G592" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="593">
@@ -17201,68 +17195,68 @@
         <v>1107</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D593" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>1108</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>593</v>
+        <v>1109</v>
       </c>
       <c r="G593" s="9">
-        <v>46766.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D594" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E594" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F594" s="3" t="s">
         <v>1109</v>
       </c>
-      <c r="B594" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C594" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D594" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E594" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F594" s="3" t="s">
-        <v>1111</v>
-      </c>
       <c r="G594" s="9">
-        <v>46877.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C595" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D595" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E595" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="B595" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C595" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D595" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E595" s="2" t="s">
-        <v>849</v>
-      </c>
       <c r="F595" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G595" s="9">
-        <v>46641.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="596">
@@ -17276,16 +17270,14 @@
         <v>11</v>
       </c>
       <c r="D596" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="F596" s="3" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G596" s="9">
-        <v>46743.0</v>
+      <c r="F596" s="4"/>
+      <c r="H596" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="597">
@@ -17299,12 +17291,17 @@
         <v>11</v>
       </c>
       <c r="D597" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="E597" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="F597" s="3" t="s">
         <v>1116</v>
       </c>
-      <c r="F597" s="4"/>
+      <c r="G597" s="9">
+        <v>46663.0</v>
+      </c>
       <c r="H597" s="2" t="s">
         <v>133</v>
       </c>
@@ -17314,22 +17311,22 @@
         <v>1117</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D598" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>752</v>
+        <v>582</v>
       </c>
       <c r="F598" s="3" t="s">
         <v>1118</v>
       </c>
       <c r="G598" s="9">
-        <v>46663.0</v>
+        <v>46437.0</v>
       </c>
       <c r="H598" s="2" t="s">
         <v>133</v>
@@ -17340,25 +17337,22 @@
         <v>1119</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D599" s="2">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>582</v>
+        <v>1120</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1120</v>
+        <v>1109</v>
       </c>
       <c r="G599" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H599" s="2" t="s">
-        <v>133</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="600">
@@ -17372,21 +17366,21 @@
         <v>11</v>
       </c>
       <c r="D600" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1122</v>
+        <v>661</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G600" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>112</v>
@@ -17398,10 +17392,10 @@
         <v>11.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>661</v>
+        <v>1123</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G601" s="9">
         <v>46530.0</v>
@@ -17418,16 +17412,16 @@
         <v>11</v>
       </c>
       <c r="D602" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>1125</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G602" s="9">
-        <v>46530.0</v>
+        <v>46834.0</v>
       </c>
     </row>
     <row r="603">
@@ -17438,19 +17432,19 @@
         <v>112</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D603" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>1127</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G603" s="9">
-        <v>46834.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="604">
@@ -17470,10 +17464,10 @@
         <v>1129</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G604" s="9">
-        <v>46481.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="605">
@@ -17493,10 +17487,10 @@
         <v>1131</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G605" s="9">
-        <v>46877.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="606">
@@ -17516,10 +17510,10 @@
         <v>1133</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G606" s="9">
-        <v>46872.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="607">
@@ -17539,10 +17533,10 @@
         <v>1135</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G607" s="9">
-        <v>46530.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="608">
@@ -17562,10 +17556,10 @@
         <v>1137</v>
       </c>
       <c r="F608" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G608" s="9">
-        <v>46734.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="609">
@@ -17585,10 +17579,10 @@
         <v>1139</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G609" s="9">
-        <v>46481.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="610">
@@ -17608,10 +17602,10 @@
         <v>1141</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G610" s="9">
-        <v>46872.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="611">
@@ -17622,42 +17616,42 @@
         <v>112</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D611" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1143</v>
+        <v>849</v>
       </c>
       <c r="F611" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G611" s="9">
-        <v>46877.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D612" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E612" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B612" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C612" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D612" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E612" s="2" t="s">
-        <v>849</v>
-      </c>
       <c r="F612" s="3" t="s">
-        <v>1111</v>
+        <v>399</v>
       </c>
       <c r="G612" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="613">
@@ -17694,38 +17688,15 @@
         <v>11</v>
       </c>
       <c r="D614" s="2">
-        <v>17.0</v>
+        <v>5.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1148</v>
+        <v>655</v>
       </c>
       <c r="F614" s="3" t="s">
         <v>399</v>
       </c>
       <c r="G614" s="9">
-        <v>46274.0</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="B615" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D615" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E615" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="F615" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G615" s="9">
         <v>46274.0</v>
       </c>
     </row>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2894" uniqueCount="1153">
   <si>
     <t>ID</t>
   </si>
@@ -2737,9 +2737,6 @@
     <t>ID1779088333604</t>
   </si>
   <si>
-    <t>ID1779088383095</t>
-  </si>
-  <si>
     <t>ID1779094185461</t>
   </si>
   <si>
@@ -3455,6 +3452,24 @@
   </si>
   <si>
     <t>ID1779956605362</t>
+  </si>
+  <si>
+    <t>ID1780023477991</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>ID1780023544888</t>
+  </si>
+  <si>
+    <t>BJUJM</t>
+  </si>
+  <si>
+    <t>ID1780023826368</t>
+  </si>
+  <si>
+    <t>ACCRM-SS(A5預留用)</t>
   </si>
 </sst>
 </file>
@@ -8096,9 +8111,7 @@
       </c>
       <c r="F186" s="14"/>
       <c r="G186" s="12"/>
-      <c r="H186" s="11" t="s">
-        <v>402</v>
-      </c>
+      <c r="H186" s="11"/>
     </row>
     <row r="187">
       <c r="A187" s="10" t="s">
@@ -9555,19 +9568,19 @@
     </row>
     <row r="250">
       <c r="A250" s="1">
-        <v>1.774514208088E12</v>
+        <v>1.774514361879E12</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D250" s="2">
         <v>10.0</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>430</v>
+        <v>194</v>
       </c>
       <c r="F250" s="3">
         <v>11502.0</v>
@@ -9575,7 +9588,7 @@
     </row>
     <row r="251">
       <c r="A251" s="1">
-        <v>1.774514361879E12</v>
+        <v>1.774606467853E12</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>112</v>
@@ -9584,63 +9597,66 @@
         <v>33</v>
       </c>
       <c r="D251" s="2">
-        <v>10.0</v>
+        <v>21.0</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F251" s="3">
-        <v>11502.0</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" s="1">
-        <v>1.774606467853E12</v>
+        <v>1.77485551576E12</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D252" s="2">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>16</v>
+        <v>476</v>
+      </c>
+      <c r="G252" s="9">
+        <v>46337.0</v>
       </c>
       <c r="H252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" s="1">
-        <v>1.77485551576E12</v>
+        <v>1.774927609576E12</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D253" s="2">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>476</v>
+        <v>553</v>
       </c>
       <c r="G253" s="9">
-        <v>46337.0</v>
-      </c>
-      <c r="H253" s="2"/>
+        <v>46516.0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1">
-        <v>1.774927609576E12</v>
+        <v>1.775008569613E12</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>112</v>
@@ -9649,126 +9665,126 @@
         <v>33</v>
       </c>
       <c r="D254" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="G254" s="9">
-        <v>46516.0</v>
+        <v>554</v>
+      </c>
+      <c r="F254" s="3">
+        <v>11503.0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1">
-        <v>1.775008569613E12</v>
+        <v>1.77500901595E12</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D255" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F255" s="3">
-        <v>11503.0</v>
+        <v>555</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G255" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1">
-        <v>1.77500901595E12</v>
+        <v>1.775037421583E12</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D256" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>238</v>
+        <v>557</v>
       </c>
       <c r="G256" s="9">
-        <v>46281.0</v>
-      </c>
+        <v>46395.0</v>
+      </c>
+      <c r="H256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" s="1">
-        <v>1.775037421583E12</v>
+        <v>1.775196340343E12</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D257" s="2">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>556</v>
+        <v>510</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="G257" s="9">
-        <v>46395.0</v>
-      </c>
-      <c r="H257" s="2"/>
+        <v>16</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1">
-        <v>1.775196340343E12</v>
+        <v>1.775197005297E12</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D258" s="2">
         <v>1.0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="F258" s="3"/>
     </row>
     <row r="259">
       <c r="A259" s="1">
-        <v>1.775197005297E12</v>
+        <v>1.7751984479E12</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D259" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F259" s="3"/>
+        <v>559</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="G259" s="9">
+        <v>46613.0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1">
-        <v>1.7751984479E12</v>
+        <v>1.775199766067E12</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>32</v>
@@ -9777,64 +9793,65 @@
         <v>27</v>
       </c>
       <c r="D260" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>559</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="G260" s="9">
-        <v>46613.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1">
-        <v>1.775199766067E12</v>
+        <v>1.775199906337E12</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D261" s="2">
         <v>7.0</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>559</v>
+        <v>436</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G261" s="9">
-        <v>46704.0</v>
+        <v>418</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1">
-        <v>1.775199906337E12</v>
+        <v>1.775200228657E12</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D262" s="2">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>418</v>
+        <v>561</v>
+      </c>
+      <c r="F262" s="4"/>
+      <c r="G262" s="9">
+        <v>46162.0</v>
+      </c>
+      <c r="I262" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1">
-        <v>1.775200228657E12</v>
+        <v>1.77520025764E12</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>32</v>
@@ -9843,22 +9860,20 @@
         <v>25</v>
       </c>
       <c r="D263" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="9">
-        <v>46162.0</v>
-      </c>
-      <c r="I263" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>46424.0</v>
+      </c>
+      <c r="H263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="1">
-        <v>1.77520025764E12</v>
+        <v>1.775200271299E12</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>32</v>
@@ -9867,20 +9882,20 @@
         <v>25</v>
       </c>
       <c r="D264" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F264" s="4"/>
       <c r="G264" s="9">
-        <v>46424.0</v>
+        <v>46394.0</v>
       </c>
       <c r="H264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="1">
-        <v>1.775200271299E12</v>
+        <v>1.775200768066E12</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>32</v>
@@ -9889,20 +9904,22 @@
         <v>25</v>
       </c>
       <c r="D265" s="2">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F265" s="4"/>
       <c r="G265" s="9">
-        <v>46394.0</v>
-      </c>
-      <c r="H265" s="2"/>
+        <v>46197.0</v>
+      </c>
+      <c r="I265" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1">
-        <v>1.775200768066E12</v>
+        <v>1.775200797189E12</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>32</v>
@@ -9914,19 +9931,16 @@
         <v>12.0</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F266" s="4"/>
       <c r="G266" s="9">
-        <v>46197.0</v>
-      </c>
-      <c r="I266" s="2" t="s">
-        <v>233</v>
+        <v>46350.0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1">
-        <v>1.775200797189E12</v>
+        <v>1.775200860884E12</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>32</v>
@@ -9935,19 +9949,19 @@
         <v>25</v>
       </c>
       <c r="D267" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F267" s="4"/>
       <c r="G267" s="9">
-        <v>46350.0</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1">
-        <v>1.775200860884E12</v>
+        <v>1.77520091897E12</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>32</v>
@@ -9959,80 +9973,82 @@
         <v>14.0</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F268" s="4"/>
       <c r="G268" s="9">
-        <v>46556.0</v>
+        <v>46558.0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1">
-        <v>1.77520091897E12</v>
+        <v>1.775201602334E12</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D269" s="2">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F269" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>568</v>
+      </c>
       <c r="G269" s="9">
-        <v>46558.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1">
-        <v>1.775201602334E12</v>
+        <v>1.775201836844E12</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D270" s="2">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>66</v>
+        <v>569</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="G270" s="9">
-        <v>46949.0</v>
+        <v>346</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1">
-        <v>1.775201836844E12</v>
+        <v>1.775202270977E12</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D271" s="2">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>346</v>
+        <v>571</v>
+      </c>
+      <c r="G271" s="9">
+        <v>46743.0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1">
-        <v>1.775202270977E12</v>
+        <v>1.7752022914E12</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>32</v>
@@ -10044,18 +10060,18 @@
         <v>17.0</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>571</v>
       </c>
       <c r="G272" s="9">
-        <v>46743.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1">
-        <v>1.7752022914E12</v>
+        <v>1.775202308287E12</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>32</v>
@@ -10067,41 +10083,39 @@
         <v>17.0</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>571</v>
       </c>
       <c r="G273" s="9">
-        <v>46752.0</v>
+        <v>46750.0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1">
-        <v>1.775202308287E12</v>
+        <v>1.775202579471E12</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D274" s="2">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F274" s="3" t="s">
-        <v>571</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="F274" s="4"/>
       <c r="G274" s="9">
-        <v>46750.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1">
-        <v>1.775202579471E12</v>
+        <v>1.775202607394E12</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>32</v>
@@ -10110,19 +10124,19 @@
         <v>25</v>
       </c>
       <c r="D275" s="2">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F275" s="4"/>
       <c r="G275" s="9">
-        <v>46394.0</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1">
-        <v>1.775202607394E12</v>
+        <v>1.775202638949E12</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>32</v>
@@ -10131,83 +10145,85 @@
         <v>25</v>
       </c>
       <c r="D276" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F276" s="4"/>
       <c r="G276" s="9">
-        <v>46556.0</v>
+        <v>46403.0</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1">
-        <v>1.775202638949E12</v>
+        <v>1.775202720789E12</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D277" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F277" s="4"/>
+        <v>577</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="G277" s="9">
-        <v>46403.0</v>
+        <v>46461.0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1">
-        <v>1.775202720789E12</v>
+        <v>1.775545086281E12</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D278" s="2">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>577</v>
+        <v>478</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G278" s="9">
-        <v>46461.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1">
-        <v>1.775545086281E12</v>
+        <v>1.775610301476E12</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D279" s="2">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>478</v>
+        <v>578</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>224</v>
+        <v>579</v>
+      </c>
+      <c r="G279" s="9">
+        <v>46670.0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1">
-        <v>1.775610301476E12</v>
+        <v>1.775631108337E12</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>112</v>
@@ -10216,21 +10232,18 @@
         <v>25</v>
       </c>
       <c r="D280" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="G280" s="9">
-        <v>46670.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1">
-        <v>1.775631108337E12</v>
+        <v>1.775632091399E12</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>112</v>
@@ -10239,82 +10252,85 @@
         <v>25</v>
       </c>
       <c r="D281" s="2">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>224</v>
+        <v>581</v>
+      </c>
+      <c r="G281" s="9">
+        <v>46789.0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1">
-        <v>1.775632091399E12</v>
+        <v>1.775632284234E12</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D282" s="2">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F282" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="G282" s="9">
-        <v>46789.0</v>
+        <v>47</v>
+      </c>
+      <c r="F282" s="4"/>
+      <c r="H282" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1">
-        <v>1.775632284234E12</v>
+        <v>1.775632417627E12</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D283" s="2">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F283" s="4"/>
-      <c r="H283" s="2" t="s">
-        <v>47</v>
+        <v>438</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1">
-        <v>1.775632417627E12</v>
+        <v>1.775632538368E12</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D284" s="2">
         <v>16.0</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>438</v>
+        <v>582</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>418</v>
+        <v>583</v>
+      </c>
+      <c r="G284" s="9">
+        <v>46681.0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1">
-        <v>1.775632538368E12</v>
+        <v>1.775632588361E12</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>32</v>
@@ -10326,18 +10342,18 @@
         <v>16.0</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>583</v>
+        <v>359</v>
       </c>
       <c r="G285" s="9">
-        <v>46681.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1">
-        <v>1.775632588361E12</v>
+        <v>1.775632615999E12</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>32</v>
@@ -10349,18 +10365,18 @@
         <v>16.0</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>359</v>
+        <v>586</v>
       </c>
       <c r="G286" s="9">
-        <v>46255.0</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1">
-        <v>1.775632615999E12</v>
+        <v>1.775632807505E12</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>32</v>
@@ -10369,21 +10385,21 @@
         <v>33</v>
       </c>
       <c r="D287" s="2">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G287" s="9">
-        <v>46725.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1">
-        <v>1.775632807505E12</v>
+        <v>1.775632834905E12</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>32</v>
@@ -10395,143 +10411,143 @@
         <v>8.0</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>587</v>
       </c>
       <c r="G288" s="9">
-        <v>46789.0</v>
+        <v>46757.0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1">
-        <v>1.775632834905E12</v>
+        <v>1.775695916181E12</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D289" s="2">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G289" s="9">
-        <v>46757.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1">
-        <v>1.775695916181E12</v>
+        <v>1.775734585272E12</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D290" s="2">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F290" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="G290" s="9">
-        <v>46947.0</v>
+        <v>554</v>
+      </c>
+      <c r="F290" s="3">
+        <v>11503.0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1">
-        <v>1.775734585272E12</v>
+        <v>1.775735093999E12</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D291" s="2">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="F291" s="3">
-        <v>11503.0</v>
-      </c>
+        <v>11504.0</v>
+      </c>
+      <c r="H291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" s="1">
-        <v>1.775735093999E12</v>
+        <v>1.775786151238E12</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D292" s="2">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F292" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="H292" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="G292" s="9">
+        <v>46949.0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1">
-        <v>1.775786151238E12</v>
+        <v>1.775786456959E12</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D293" s="2">
         <v>18.0</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G293" s="9">
-        <v>46949.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1">
-        <v>1.775786456959E12</v>
+        <v>1.775786585712E12</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D294" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>594</v>
+        <v>66</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>595</v>
+        <v>493</v>
       </c>
       <c r="G294" s="9">
         <v>46794.0</v>
@@ -10539,22 +10555,22 @@
     </row>
     <row r="295">
       <c r="A295" s="1">
-        <v>1.775786585712E12</v>
+        <v>1.775799916832E12</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D295" s="2">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>66</v>
+        <v>596</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>493</v>
+        <v>16</v>
       </c>
       <c r="G295" s="9">
         <v>46794.0</v>
@@ -10562,30 +10578,30 @@
     </row>
     <row r="296">
       <c r="A296" s="1">
-        <v>1.775799916832E12</v>
+        <v>1.775818206218E12</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D296" s="2">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G296" s="9">
-        <v>46794.0</v>
+        <v>46403.0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1">
-        <v>1.775818206218E12</v>
+        <v>1.775818524868E12</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>32</v>
@@ -10594,21 +10610,21 @@
         <v>11</v>
       </c>
       <c r="D297" s="2">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G297" s="9">
-        <v>46403.0</v>
+        <v>46764.0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1">
-        <v>1.775818524868E12</v>
+        <v>1.775818556986E12</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>32</v>
@@ -10620,42 +10636,42 @@
         <v>4.0</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G298" s="9">
-        <v>46764.0</v>
-      </c>
+        <v>46769.0</v>
+      </c>
+      <c r="H298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" s="1">
-        <v>1.775818556986E12</v>
+        <v>1.776059127998E12</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D299" s="2">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G299" s="9">
-        <v>46769.0</v>
-      </c>
-      <c r="H299" s="2"/>
+        <v>46758.0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1">
-        <v>1.776059127998E12</v>
+        <v>1.77605914796E12</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>112</v>
@@ -10667,41 +10683,39 @@
         <v>19.0</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>493</v>
       </c>
       <c r="G300" s="9">
-        <v>46758.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1">
-        <v>1.77605914796E12</v>
+        <v>1.776068065666E12</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D301" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>493</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="F301" s="4"/>
       <c r="G301" s="9">
-        <v>46794.0</v>
+        <v>46426.0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1">
-        <v>1.776068065666E12</v>
+        <v>1.776137953787E12</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>32</v>
@@ -10710,19 +10724,21 @@
         <v>11</v>
       </c>
       <c r="D302" s="2">
-        <v>18.0</v>
+        <v>9.0</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F302" s="4"/>
+        <v>603</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>604</v>
+      </c>
       <c r="G302" s="9">
-        <v>46426.0</v>
+        <v>46577.0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1">
-        <v>1.776137953787E12</v>
+        <v>1.776137996426E12</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>32</v>
@@ -10737,15 +10753,15 @@
         <v>603</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G303" s="9">
-        <v>46577.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1">
-        <v>1.776137996426E12</v>
+        <v>1.776138016571E12</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>32</v>
@@ -10760,7 +10776,7 @@
         <v>603</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G304" s="9">
         <v>46254.0</v>
@@ -10768,7 +10784,7 @@
     </row>
     <row r="305">
       <c r="A305" s="1">
-        <v>1.776138016571E12</v>
+        <v>1.776138041953E12</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>32</v>
@@ -10782,16 +10798,16 @@
       <c r="E305" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="F305" s="3" t="s">
-        <v>606</v>
+      <c r="F305" s="3">
+        <v>1140221.0</v>
       </c>
       <c r="G305" s="9">
-        <v>46254.0</v>
+        <v>46368.0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1">
-        <v>1.776138041953E12</v>
+        <v>1.776138069076E12</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>32</v>
@@ -10805,16 +10821,16 @@
       <c r="E306" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="F306" s="3">
-        <v>1140221.0</v>
+      <c r="F306" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="G306" s="9">
-        <v>46368.0</v>
+        <v>46285.0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1">
-        <v>1.776138069076E12</v>
+        <v>1.776138139688E12</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>32</v>
@@ -10823,131 +10839,134 @@
         <v>11</v>
       </c>
       <c r="D307" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>371</v>
+        <v>608</v>
       </c>
       <c r="G307" s="9">
-        <v>46285.0</v>
+        <v>46596.0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1">
-        <v>1.776138139688E12</v>
+        <v>1.776138981107E12</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D308" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G308" s="9">
-        <v>46596.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1">
-        <v>1.776138981107E12</v>
+        <v>1.77613942855E12</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D309" s="2">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>610</v>
+        <v>142</v>
       </c>
       <c r="G309" s="9">
-        <v>46641.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1">
-        <v>1.77613942855E12</v>
+        <v>1.776146651219E12</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D310" s="2">
         <v>2.0</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="F310" s="3" t="s">
-        <v>142</v>
+        <v>388</v>
       </c>
       <c r="G310" s="9">
-        <v>46789.0</v>
+        <v>47286.0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1">
-        <v>1.776146651219E12</v>
+        <v>1.776146781002E12</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D311" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="F311" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="G311" s="9">
-        <v>47286.0</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="F311" s="4"/>
     </row>
     <row r="312">
       <c r="A312" s="1">
-        <v>1.776146781002E12</v>
+        <v>1.776146881019E12</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D312" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="F312" s="4"/>
+        <v>613</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G312" s="9">
+        <v>46542.0</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1">
-        <v>1.776146881019E12</v>
+        <v>1.7761469355E12</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>10</v>
@@ -10959,13 +10978,13 @@
         <v>5.0</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>16</v>
+        <v>441</v>
       </c>
       <c r="G313" s="9">
-        <v>46542.0</v>
+        <v>46987.0</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>52</v>
@@ -10973,7 +10992,7 @@
     </row>
     <row r="314">
       <c r="A314" s="1">
-        <v>1.7761469355E12</v>
+        <v>1.776146969199E12</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>10</v>
@@ -10985,13 +11004,10 @@
         <v>5.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G314" s="9">
-        <v>46987.0</v>
+        <v>16</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>52</v>
@@ -10999,7 +11015,7 @@
     </row>
     <row r="315">
       <c r="A315" s="1">
-        <v>1.776146969199E12</v>
+        <v>1.776147024701E12</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>10</v>
@@ -11011,18 +11027,21 @@
         <v>5.0</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>615</v>
+        <v>18</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G315" s="9">
+        <v>47356.0</v>
+      </c>
       <c r="H315" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1">
-        <v>1.776147024701E12</v>
+        <v>1.776147054791E12</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>10</v>
@@ -11037,10 +11056,10 @@
         <v>18</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>16</v>
+        <v>441</v>
       </c>
       <c r="G316" s="9">
-        <v>47356.0</v>
+        <v>46987.0</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>52</v>
@@ -11048,7 +11067,7 @@
     </row>
     <row r="317">
       <c r="A317" s="1">
-        <v>1.776147054791E12</v>
+        <v>1.776147153167E12</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>10</v>
@@ -11057,24 +11076,18 @@
         <v>11</v>
       </c>
       <c r="D317" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>18</v>
+        <v>615</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G317" s="9">
-        <v>46987.0</v>
-      </c>
-      <c r="H317" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1">
-        <v>1.776147153167E12</v>
+        <v>1.776147237339E12</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>10</v>
@@ -11086,15 +11099,18 @@
         <v>4.0</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G318" s="9">
+        <v>46798.0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1">
-        <v>1.776147237339E12</v>
+        <v>1.776147270323E12</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>10</v>
@@ -11103,21 +11119,21 @@
         <v>11</v>
       </c>
       <c r="D319" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G319" s="9">
-        <v>46798.0</v>
+        <v>46838.0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1">
-        <v>1.776147270323E12</v>
+        <v>1.776147321508E12</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>10</v>
@@ -11126,21 +11142,21 @@
         <v>11</v>
       </c>
       <c r="D320" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G320" s="9">
-        <v>46838.0</v>
+        <v>46402.0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1">
-        <v>1.776147321508E12</v>
+        <v>1.776147583566E12</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>10</v>
@@ -11152,18 +11168,18 @@
         <v>4.0</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G321" s="9">
-        <v>46402.0</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1">
-        <v>1.776147583566E12</v>
+        <v>1.776147678627E12</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>10</v>
@@ -11175,18 +11191,18 @@
         <v>4.0</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G322" s="9">
-        <v>46204.0</v>
+        <v>46388.0</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1">
-        <v>1.776147678627E12</v>
+        <v>1.776147764862E12</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>10</v>
@@ -11198,18 +11214,18 @@
         <v>4.0</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G323" s="9">
-        <v>46388.0</v>
+        <v>46310.0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1">
-        <v>1.776147764862E12</v>
+        <v>1.776147814402E12</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>10</v>
@@ -11218,21 +11234,21 @@
         <v>11</v>
       </c>
       <c r="D324" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G324" s="9">
-        <v>46310.0</v>
+        <v>46283.0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1">
-        <v>1.776147814402E12</v>
+        <v>1.776147841228E12</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>10</v>
@@ -11244,18 +11260,18 @@
         <v>2.0</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G325" s="9">
-        <v>46283.0</v>
+        <v>46796.0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1">
-        <v>1.776147841228E12</v>
+        <v>1.776147860658E12</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>10</v>
@@ -11267,41 +11283,44 @@
         <v>2.0</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G326" s="9">
-        <v>46796.0</v>
+        <v>46802.0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1">
-        <v>1.776147860658E12</v>
+        <v>1.776148337734E12</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>10</v>
+        <v>535</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D327" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="G327" s="9">
-        <v>46802.0</v>
+        <v>46269.0</v>
+      </c>
+      <c r="I327" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1">
-        <v>1.776148337734E12</v>
+        <v>1.776148418097E12</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>535</v>
@@ -11310,24 +11329,21 @@
         <v>11</v>
       </c>
       <c r="D328" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>625</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G328" s="9">
-        <v>46269.0</v>
-      </c>
-      <c r="I328" s="2" t="s">
-        <v>233</v>
+        <v>46247.0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1">
-        <v>1.776148418097E12</v>
+        <v>1.776148449855E12</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>535</v>
@@ -11336,10 +11352,10 @@
         <v>11</v>
       </c>
       <c r="D329" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>627</v>
@@ -11350,7 +11366,7 @@
     </row>
     <row r="330">
       <c r="A330" s="1">
-        <v>1.776148449855E12</v>
+        <v>1.776148475121E12</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>535</v>
@@ -11359,21 +11375,21 @@
         <v>11</v>
       </c>
       <c r="D330" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G330" s="9">
-        <v>46247.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1">
-        <v>1.776148475121E12</v>
+        <v>1.776148592568E12</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>535</v>
@@ -11382,21 +11398,24 @@
         <v>11</v>
       </c>
       <c r="D331" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="G331" s="9">
-        <v>46269.0</v>
+        <v>46234.0</v>
+      </c>
+      <c r="I331" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1">
-        <v>1.776148592568E12</v>
+        <v>1.776148632656E12</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>535</v>
@@ -11405,16 +11424,16 @@
         <v>11</v>
       </c>
       <c r="D332" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G332" s="9">
-        <v>46234.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I332" s="2" t="s">
         <v>233</v>
@@ -11422,7 +11441,7 @@
     </row>
     <row r="333">
       <c r="A333" s="1">
-        <v>1.776148632656E12</v>
+        <v>1.776148710229E12</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>535</v>
@@ -11431,16 +11450,16 @@
         <v>11</v>
       </c>
       <c r="D333" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G333" s="9">
-        <v>46202.0</v>
+        <v>46193.0</v>
       </c>
       <c r="I333" s="2" t="s">
         <v>233</v>
@@ -11448,7 +11467,7 @@
     </row>
     <row r="334">
       <c r="A334" s="1">
-        <v>1.776148710229E12</v>
+        <v>1.776148761624E12</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>535</v>
@@ -11457,16 +11476,16 @@
         <v>11</v>
       </c>
       <c r="D334" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G334" s="9">
-        <v>46193.0</v>
+        <v>46203.0</v>
       </c>
       <c r="I334" s="2" t="s">
         <v>233</v>
@@ -11474,25 +11493,25 @@
     </row>
     <row r="335">
       <c r="A335" s="1">
-        <v>1.776148761624E12</v>
+        <v>1.776149046956E12</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D335" s="2">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G335" s="9">
-        <v>46203.0</v>
+        <v>46182.0</v>
       </c>
       <c r="I335" s="2" t="s">
         <v>233</v>
@@ -11500,51 +11519,44 @@
     </row>
     <row r="336">
       <c r="A336" s="1">
-        <v>1.776149046956E12</v>
+        <v>1.776149087494E12</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D336" s="2">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="F336" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="G336" s="9">
-        <v>46182.0</v>
-      </c>
-      <c r="I336" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="F336" s="4"/>
     </row>
     <row r="337">
       <c r="A337" s="1">
-        <v>1.776149087494E12</v>
+        <v>1.776169705463E12</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D337" s="2">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>640</v>
+        <v>534</v>
       </c>
       <c r="F337" s="4"/>
+      <c r="H337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" s="1">
-        <v>1.776169705463E12</v>
+        <v>1.776301247869E12</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>112</v>
@@ -11553,17 +11565,20 @@
         <v>11</v>
       </c>
       <c r="D338" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>534</v>
+        <v>641</v>
       </c>
       <c r="F338" s="4"/>
+      <c r="G338" s="9">
+        <v>46840.0</v>
+      </c>
       <c r="H338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" s="1">
-        <v>1.776301247869E12</v>
+        <v>1.776301425645E12</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>112</v>
@@ -11572,20 +11587,21 @@
         <v>11</v>
       </c>
       <c r="D339" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="F339" s="4"/>
+        <v>642</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="G339" s="9">
-        <v>46840.0</v>
-      </c>
-      <c r="H339" s="2"/>
+        <v>46640.0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1">
-        <v>1.776301425645E12</v>
+        <v>1.776327582548E12</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>112</v>
@@ -11594,41 +11610,41 @@
         <v>11</v>
       </c>
       <c r="D340" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F340" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G340" s="9">
-        <v>46640.0</v>
+        <v>643</v>
+      </c>
+      <c r="F340" s="3">
+        <v>11504.0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1">
-        <v>1.776327582548E12</v>
+        <v>1.776327623153E12</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D341" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F341" s="3">
-        <v>11504.0</v>
+        <v>592</v>
+      </c>
+      <c r="F341" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="G341" s="9">
+        <v>46949.0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1">
-        <v>1.776327623153E12</v>
+        <v>1.776327677276E12</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>112</v>
@@ -11637,13 +11653,13 @@
         <v>33</v>
       </c>
       <c r="D342" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>592</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G342" s="9">
         <v>46949.0</v>
@@ -11651,30 +11667,28 @@
     </row>
     <row r="343">
       <c r="A343" s="1">
-        <v>1.776327677276E12</v>
+        <v>1.776328486516E12</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D343" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>592</v>
+        <v>646</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="G343" s="9">
-        <v>46949.0</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="H343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" s="1">
-        <v>1.776328486516E12</v>
+        <v>1.776328499394E12</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>112</v>
@@ -11683,19 +11697,18 @@
         <v>25</v>
       </c>
       <c r="D344" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" s="1">
-        <v>1.776328499394E12</v>
+        <v>1.776328514002E12</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>112</v>
@@ -11704,10 +11717,10 @@
         <v>25</v>
       </c>
       <c r="D345" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>418</v>
@@ -11715,7 +11728,7 @@
     </row>
     <row r="346">
       <c r="A346" s="1">
-        <v>1.776328514002E12</v>
+        <v>1.776334155137E12</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>112</v>
@@ -11724,18 +11737,21 @@
         <v>25</v>
       </c>
       <c r="D346" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>418</v>
+        <v>241</v>
+      </c>
+      <c r="G346" s="9">
+        <v>46537.0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1">
-        <v>1.776334155137E12</v>
+        <v>1.776334203307E12</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>112</v>
@@ -11747,41 +11763,41 @@
         <v>13.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>649</v>
+        <v>546</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>241</v>
+        <v>476</v>
       </c>
       <c r="G347" s="9">
-        <v>46537.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1">
-        <v>1.776334203307E12</v>
+        <v>1.776334423117E12</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D348" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>546</v>
+        <v>650</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>476</v>
+        <v>241</v>
       </c>
       <c r="G348" s="9">
-        <v>46530.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1">
-        <v>1.776334423117E12</v>
+        <v>1.776334444257E12</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>112</v>
@@ -11793,18 +11809,18 @@
         <v>15.0</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G349" s="9">
-        <v>46479.0</v>
+        <v>46468.0</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1">
-        <v>1.776334444257E12</v>
+        <v>1.776334474615E12</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>112</v>
@@ -11816,7 +11832,7 @@
         <v>15.0</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>238</v>
@@ -11827,7 +11843,7 @@
     </row>
     <row r="351">
       <c r="A351" s="1">
-        <v>1.776334474615E12</v>
+        <v>1.776334496105E12</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>112</v>
@@ -11839,18 +11855,13 @@
         <v>15.0</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F351" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G351" s="9">
-        <v>46468.0</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="F351" s="4"/>
     </row>
     <row r="352">
       <c r="A352" s="1">
-        <v>1.776334496105E12</v>
+        <v>1.776334545035E12</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>112</v>
@@ -11862,13 +11873,18 @@
         <v>15.0</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="F352" s="4"/>
+        <v>654</v>
+      </c>
+      <c r="F352" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G352" s="9">
+        <v>46468.0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1">
-        <v>1.776334545035E12</v>
+        <v>1.776398955451E12</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>112</v>
@@ -11877,21 +11893,21 @@
         <v>27</v>
       </c>
       <c r="D353" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>654</v>
+        <v>569</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>238</v>
+        <v>590</v>
       </c>
       <c r="G353" s="9">
-        <v>46468.0</v>
+        <v>46768.0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1">
-        <v>1.776398955451E12</v>
+        <v>1.776398987942E12</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>112</v>
@@ -11903,18 +11919,18 @@
         <v>17.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>569</v>
+        <v>655</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>590</v>
       </c>
       <c r="G354" s="9">
-        <v>46768.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1">
-        <v>1.776398987942E12</v>
+        <v>1.776399071673E12</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>112</v>
@@ -11926,90 +11942,90 @@
         <v>17.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>655</v>
+        <v>573</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>590</v>
       </c>
       <c r="G355" s="9">
-        <v>46947.0</v>
+        <v>46771.0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1">
-        <v>1.776399071673E12</v>
+        <v>1.776399111607E12</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D356" s="2">
         <v>17.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>573</v>
+        <v>656</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>590</v>
+        <v>493</v>
       </c>
       <c r="G356" s="9">
-        <v>46771.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1">
-        <v>1.776399111607E12</v>
+        <v>1.776399379582E12</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D357" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>493</v>
+        <v>658</v>
       </c>
       <c r="G357" s="9">
-        <v>46794.0</v>
+        <v>46691.0</v>
+      </c>
+      <c r="H357" s="2" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1">
-        <v>1.776399379582E12</v>
+        <v>1.776400103874E12</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D358" s="2">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>658</v>
+        <v>145</v>
       </c>
       <c r="G358" s="9">
-        <v>46691.0</v>
-      </c>
-      <c r="H358" s="2" t="s">
-        <v>659</v>
+        <v>46543.0</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1">
-        <v>1.776400103874E12</v>
+        <v>1.776400120665E12</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>112</v>
@@ -12018,21 +12034,21 @@
         <v>25</v>
       </c>
       <c r="D359" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="G359" s="9">
-        <v>46543.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1">
-        <v>1.776400120665E12</v>
+        <v>1.77640716912E12</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>112</v>
@@ -12041,21 +12057,21 @@
         <v>25</v>
       </c>
       <c r="D360" s="2">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="F360" s="3" t="s">
-        <v>241</v>
+        <v>554</v>
+      </c>
+      <c r="F360" s="3">
+        <v>11503.0</v>
       </c>
       <c r="G360" s="9">
-        <v>46479.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1">
-        <v>1.77640716912E12</v>
+        <v>1.776407375241E12</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>112</v>
@@ -12064,21 +12080,21 @@
         <v>25</v>
       </c>
       <c r="D361" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F361" s="3">
-        <v>11503.0</v>
+        <v>660</v>
+      </c>
+      <c r="F361" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="G361" s="9">
-        <v>46516.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1">
-        <v>1.776407375241E12</v>
+        <v>1.77640744785E12</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>112</v>
@@ -12087,106 +12103,106 @@
         <v>25</v>
       </c>
       <c r="D362" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G362" s="9">
-        <v>46669.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1">
-        <v>1.77640744785E12</v>
+        <v>1.776407858481E12</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D363" s="2">
         <v>12.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="F363" s="3" t="s">
-        <v>663</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="F363" s="4"/>
       <c r="G363" s="9">
         <v>46523.0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1">
-        <v>1.776407858481E12</v>
+        <v>1.776436049209E12</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D364" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>664</v>
+        <v>47</v>
       </c>
       <c r="F364" s="4"/>
-      <c r="G364" s="9">
-        <v>46523.0</v>
-      </c>
     </row>
     <row r="365">
       <c r="A365" s="1">
-        <v>1.776436049209E12</v>
+        <v>1.776659068274E12</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>537</v>
+        <v>112</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D365" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F365" s="4"/>
+        <v>665</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G365" s="9">
+        <v>46793.0</v>
+      </c>
     </row>
     <row r="366">
-      <c r="A366" s="1">
-        <v>1.776659068274E12</v>
+      <c r="A366" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D366" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>665</v>
+        <v>66</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G366" s="9">
-        <v>46793.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>112</v>
@@ -12195,67 +12211,62 @@
         <v>33</v>
       </c>
       <c r="D367" s="2">
-        <v>9.0</v>
+        <v>20.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>66</v>
+        <v>670</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="G367" s="9">
-        <v>46949.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D368" s="2">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="G368" s="9">
-        <v>46793.0</v>
+        <v>46639.0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D369" s="2">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="F369" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="G369" s="9">
-        <v>46639.0</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="F369" s="4"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>10</v>
@@ -12264,34 +12275,34 @@
         <v>27</v>
       </c>
       <c r="D370" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F370" s="4"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D371" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F371" s="4"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>10</v>
@@ -12309,13 +12320,13 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D373" s="2">
         <v>5.0</v>
@@ -12327,13 +12338,13 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D374" s="2">
         <v>5.0</v>
@@ -12345,43 +12356,45 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D375" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="F375" s="4"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D376" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="F376" s="4"/>
+        <v>584</v>
+      </c>
+      <c r="F376" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>32</v>
@@ -12393,15 +12406,18 @@
         <v>2.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>584</v>
+        <v>687</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>293</v>
+        <v>346</v>
+      </c>
+      <c r="G377" s="9">
+        <v>46488.0</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>32</v>
@@ -12413,18 +12429,15 @@
         <v>2.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G378" s="9">
-        <v>46488.0</v>
+        <v>690</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>32</v>
@@ -12433,42 +12446,42 @@
         <v>25</v>
       </c>
       <c r="D379" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>690</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="G379" s="9">
+        <v>46716.0</v>
+      </c>
+      <c r="H379" s="2"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D380" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F380" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G380" s="9">
-        <v>46716.0</v>
-      </c>
-      <c r="H380" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="F380" s="3">
+        <v>11504.0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>112</v>
@@ -12477,84 +12490,87 @@
         <v>11</v>
       </c>
       <c r="D381" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F381" s="3">
         <v>11504.0</v>
       </c>
+      <c r="H381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D382" s="2">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="F382" s="3">
-        <v>11504.0</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="F382" s="4"/>
       <c r="H382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D383" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="F383" s="4"/>
-      <c r="H383" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="F383" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G383" s="9">
+        <v>46240.0</v>
+      </c>
+      <c r="H383" s="2" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D384" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>701</v>
+        <v>671</v>
       </c>
       <c r="G384" s="9">
-        <v>46240.0</v>
-      </c>
-      <c r="H384" s="2" t="s">
-        <v>702</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>112</v>
@@ -12563,67 +12579,70 @@
         <v>11</v>
       </c>
       <c r="D385" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>671</v>
+        <v>707</v>
       </c>
       <c r="G385" s="9">
-        <v>46416.0</v>
+        <v>46544.0</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C386" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D386" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="G386" s="9">
-        <v>46544.0</v>
+        <v>46856.0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D387" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="G387" s="9">
-        <v>46856.0</v>
+        <v>46794.0</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>112</v>
@@ -12635,21 +12654,18 @@
         <v>16.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>713</v>
       </c>
       <c r="G388" s="9">
-        <v>46794.0</v>
-      </c>
-      <c r="H388" s="2" t="s">
-        <v>714</v>
+        <v>46785.0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>112</v>
@@ -12661,18 +12677,18 @@
         <v>16.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>716</v>
+        <v>585</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>713</v>
       </c>
       <c r="G389" s="9">
-        <v>46785.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>112</v>
@@ -12684,41 +12700,44 @@
         <v>16.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>585</v>
+        <v>719</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>713</v>
       </c>
       <c r="G390" s="9">
-        <v>46789.0</v>
+        <v>46839.0</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D391" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="G391" s="9">
-        <v>46839.0</v>
+        <v>46312.0</v>
+      </c>
+      <c r="H391" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>112</v>
@@ -12727,24 +12746,22 @@
         <v>11</v>
       </c>
       <c r="D392" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>721</v>
+        <v>655</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G392" s="9">
-        <v>46312.0</v>
-      </c>
-      <c r="H392" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>46669.0</v>
+      </c>
+      <c r="H392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>112</v>
@@ -12753,45 +12770,44 @@
         <v>11</v>
       </c>
       <c r="D393" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>655</v>
+        <v>573</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>724</v>
+        <v>165</v>
       </c>
       <c r="G393" s="9">
-        <v>46669.0</v>
-      </c>
-      <c r="H393" s="2"/>
+        <v>46540.0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D394" s="2">
-        <v>22.0</v>
+        <v>7.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>573</v>
+        <v>727</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>165</v>
+        <v>713</v>
       </c>
       <c r="G394" s="9">
-        <v>46540.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>112</v>
@@ -12803,41 +12819,39 @@
         <v>7.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
       <c r="G395" s="9">
-        <v>46794.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D396" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="F396" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="G396" s="9">
-        <v>46792.0</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="F396" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="H396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>112</v>
@@ -12846,181 +12860,180 @@
         <v>11</v>
       </c>
       <c r="D397" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F397" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="H397" s="2"/>
+        <v>115004.0</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D398" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="F398" s="3">
-        <v>115004.0</v>
+        <v>11505.0</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D399" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F399" s="3">
-        <v>11505.0</v>
+        <v>738</v>
+      </c>
+      <c r="F399" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G399" s="9">
+        <v>46162.0</v>
+      </c>
+      <c r="H399" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I399" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D400" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F400" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G400" s="9">
-        <v>46162.0</v>
-      </c>
-      <c r="H400" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I400" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="F400" s="4"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D401" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F401" s="4"/>
+        <v>742</v>
+      </c>
+      <c r="F401" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G401" s="9">
+        <v>46152.0</v>
+      </c>
+      <c r="H401" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I401" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D402" s="2">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>326</v>
+        <v>663</v>
       </c>
       <c r="G402" s="9">
-        <v>46152.0</v>
-      </c>
-      <c r="H402" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I402" s="2" t="s">
-        <v>233</v>
+        <v>46596.0</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D403" s="2">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>663</v>
+        <v>747</v>
       </c>
       <c r="G403" s="9">
-        <v>46596.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D404" s="2">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>746</v>
+        <v>648</v>
       </c>
       <c r="F404" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="G404" s="9">
-        <v>46669.0</v>
+        <v>385</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>32</v>
@@ -13029,173 +13042,173 @@
         <v>25</v>
       </c>
       <c r="D405" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>648</v>
+        <v>750</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>385</v>
+        <v>418</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D406" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>418</v>
+        <v>95</v>
+      </c>
+      <c r="G406" s="9">
+        <v>46694.0</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D407" s="2">
-        <v>18.0</v>
+        <v>25</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>752</v>
+        <v>559</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>95</v>
+        <v>754</v>
       </c>
       <c r="G407" s="9">
-        <v>46694.0</v>
+        <v>46410.0</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
+      </c>
+      <c r="D408" s="2">
+        <v>22.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>559</v>
+        <v>756</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="G408" s="9">
-        <v>46410.0</v>
+        <v>46194.0</v>
+      </c>
+      <c r="I408" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D409" s="2">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="G409" s="9">
-        <v>46194.0</v>
-      </c>
-      <c r="I409" s="2" t="s">
-        <v>233</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D410" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>759</v>
+        <v>588</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="G410" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D411" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F411" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="G411" s="9">
-        <v>46913.0</v>
+        <v>643</v>
+      </c>
+      <c r="F411" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D412" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F412" s="3">
-        <v>11505.0</v>
+        <v>765</v>
+      </c>
+      <c r="F412" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>10</v>
@@ -13207,7 +13220,7 @@
         <v>2.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>765</v>
+        <v>15</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>224</v>
@@ -13215,7 +13228,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>10</v>
@@ -13227,35 +13240,38 @@
         <v>2.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D415" s="2">
         <v>2.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G415" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>10</v>
@@ -13264,42 +13280,42 @@
         <v>25</v>
       </c>
       <c r="D416" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F416" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="F416" s="4"/>
       <c r="G416" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D417" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F417" s="4"/>
+        <v>773</v>
+      </c>
+      <c r="F417" s="3" t="s">
+        <v>774</v>
+      </c>
       <c r="G417" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>32</v>
@@ -13314,124 +13330,124 @@
         <v>773</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G418" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D419" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F419" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="G419" s="9">
-        <v>46484.0</v>
+        <v>547</v>
+      </c>
+      <c r="F419" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D420" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F420" s="3">
-        <v>11505.0</v>
+        <v>712</v>
+      </c>
+      <c r="F420" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D421" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>712</v>
+        <v>780</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>55</v>
+        <v>604</v>
+      </c>
+      <c r="G421" s="9">
+        <v>46577.0</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>604</v>
+        <v>272</v>
       </c>
       <c r="G422" s="9">
-        <v>46577.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D423" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="G423" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>112</v>
@@ -13443,18 +13459,18 @@
         <v>17.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G424" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>112</v>
@@ -13466,18 +13482,18 @@
         <v>17.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G425" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>112</v>
@@ -13489,18 +13505,18 @@
         <v>17.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G426" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>112</v>
@@ -13512,53 +13528,50 @@
         <v>17.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>595</v>
+        <v>793</v>
       </c>
       <c r="G427" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D428" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="F428" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="G428" s="9">
-        <v>46523.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D429" s="2">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>224</v>
@@ -13566,19 +13579,19 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D430" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>224</v>
@@ -13586,7 +13599,7 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>32</v>
@@ -13595,10 +13608,10 @@
         <v>27</v>
       </c>
       <c r="D431" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>224</v>
@@ -13606,50 +13619,53 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D432" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>224</v>
+        <v>238</v>
+      </c>
+      <c r="G432" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="2">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G433" s="9">
-        <v>46281.0</v>
+        <v>493</v>
+      </c>
+      <c r="H433" s="2" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>32</v>
@@ -13658,21 +13674,21 @@
         <v>11</v>
       </c>
       <c r="D434" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H434" s="2" t="s">
-        <v>806</v>
+      <c r="G434" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>32</v>
@@ -13681,67 +13697,67 @@
         <v>11</v>
       </c>
       <c r="D435" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="G435" s="9">
-        <v>47146.0</v>
+      <c r="H435" s="2" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>810</v>
+        <v>752</v>
       </c>
       <c r="F436" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H436" s="2" t="s">
-        <v>806</v>
+        <v>812</v>
+      </c>
+      <c r="G436" s="9">
+        <v>46666.0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D437" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>752</v>
+        <v>814</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="G437" s="9">
-        <v>46666.0</v>
+        <v>46583.0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>32</v>
@@ -13756,15 +13772,15 @@
         <v>814</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G438" s="9">
-        <v>46583.0</v>
+        <v>46604.0</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>32</v>
@@ -13779,15 +13795,15 @@
         <v>814</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>817</v>
+        <v>110</v>
       </c>
       <c r="G439" s="9">
-        <v>46604.0</v>
+        <v>46626.0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>32</v>
@@ -13802,15 +13818,15 @@
         <v>814</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>110</v>
+        <v>820</v>
       </c>
       <c r="G440" s="9">
-        <v>46626.0</v>
+        <v>46658.0</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>32</v>
@@ -13825,102 +13841,102 @@
         <v>814</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G441" s="9">
-        <v>46658.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D442" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F442" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="G442" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="F442" s="4"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D443" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="F443" s="4"/>
+        <v>826</v>
+      </c>
+      <c r="F443" s="3" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D444" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>493</v>
+        <v>829</v>
+      </c>
+      <c r="G444" s="9">
+        <v>46792.0</v>
+      </c>
+      <c r="H444" s="2" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D445" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="G445" s="9">
-        <v>46792.0</v>
-      </c>
-      <c r="H445" s="2" t="s">
-        <v>830</v>
+        <v>46304.0</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>32</v>
@@ -13929,21 +13945,21 @@
         <v>11</v>
       </c>
       <c r="D446" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>832</v>
+        <v>582</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>833</v>
+        <v>51</v>
       </c>
       <c r="G446" s="9">
-        <v>46304.0</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>32</v>
@@ -13952,21 +13968,21 @@
         <v>11</v>
       </c>
       <c r="D447" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>582</v>
+        <v>836</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>51</v>
+        <v>359</v>
       </c>
       <c r="G447" s="9">
-        <v>46416.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>32</v>
@@ -13975,53 +13991,53 @@
         <v>11</v>
       </c>
       <c r="D448" s="2">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="G448" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>37</v>
+        <v>663</v>
       </c>
       <c r="G449" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D450" s="2">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>840</v>
@@ -14035,7 +14051,7 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>112</v>
@@ -14044,67 +14060,67 @@
         <v>25</v>
       </c>
       <c r="D451" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>840</v>
+        <v>544</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G451" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D452" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>544</v>
+        <v>729</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>663</v>
+        <v>844</v>
       </c>
       <c r="G452" s="9">
-        <v>46484.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D453" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>729</v>
+        <v>846</v>
       </c>
       <c r="F453" s="3" t="s">
-        <v>844</v>
+        <v>579</v>
       </c>
       <c r="G453" s="9">
-        <v>46792.0</v>
+        <v>46676.0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>32</v>
@@ -14116,36 +14132,36 @@
         <v>9.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="F454" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="G454" s="9">
-        <v>46676.0</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="F454" s="4"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F455" s="4"/>
+        <v>849</v>
+      </c>
+      <c r="F455" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G455" s="9">
+        <v>46641.0</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>112</v>
@@ -14154,21 +14170,21 @@
         <v>11</v>
       </c>
       <c r="D456" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>707</v>
       </c>
       <c r="G456" s="9">
-        <v>46641.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>112</v>
@@ -14177,44 +14193,47 @@
         <v>11</v>
       </c>
       <c r="D457" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>707</v>
+        <v>663</v>
       </c>
       <c r="G457" s="9">
-        <v>46530.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D458" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>663</v>
+        <v>707</v>
       </c>
       <c r="G458" s="9">
-        <v>46949.0</v>
+        <v>46523.0</v>
+      </c>
+      <c r="H458" s="2" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>112</v>
@@ -14223,24 +14242,21 @@
         <v>25</v>
       </c>
       <c r="D459" s="2">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>707</v>
+        <v>579</v>
       </c>
       <c r="G459" s="9">
-        <v>46523.0</v>
-      </c>
-      <c r="H459" s="2" t="s">
-        <v>856</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>112</v>
@@ -14255,15 +14271,15 @@
         <v>832</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G460" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>112</v>
@@ -14286,10 +14302,10 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>25</v>
@@ -14301,15 +14317,15 @@
         <v>832</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>449</v>
+        <v>579</v>
       </c>
       <c r="G462" s="9">
-        <v>46752.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>32</v>
@@ -14324,15 +14340,15 @@
         <v>832</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G463" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>32</v>
@@ -14347,107 +14363,107 @@
         <v>832</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>449</v>
+        <v>45</v>
       </c>
       <c r="G464" s="9">
-        <v>46752.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D465" s="2">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>832</v>
+        <v>578</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G465" s="9">
-        <v>46366.0</v>
+        <v>668</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C466" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D466" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>668</v>
+        <v>865</v>
+      </c>
+      <c r="G466" s="9">
+        <v>46670.0</v>
+      </c>
+      <c r="H466" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D467" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>572</v>
+        <v>867</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>865</v>
+        <v>95</v>
       </c>
       <c r="G467" s="9">
-        <v>46670.0</v>
-      </c>
-      <c r="H467" s="2" t="s">
-        <v>52</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D468" s="2">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="G468" s="9">
-        <v>46725.0</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>112</v>
@@ -14459,18 +14475,18 @@
         <v>22.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>573</v>
+        <v>870</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="G469" s="9">
-        <v>46556.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>112</v>
@@ -14482,41 +14498,42 @@
         <v>22.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>142</v>
+        <v>873</v>
       </c>
       <c r="G470" s="9">
-        <v>46793.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D471" s="2">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>873</v>
+        <v>606</v>
       </c>
       <c r="G471" s="9">
-        <v>46670.0</v>
-      </c>
+        <v>46254.0</v>
+      </c>
+      <c r="H471" s="2"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>32</v>
@@ -14525,37 +14542,36 @@
         <v>11</v>
       </c>
       <c r="D472" s="2">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>606</v>
+        <v>405</v>
       </c>
       <c r="G472" s="9">
-        <v>46254.0</v>
-      </c>
-      <c r="H472" s="2"/>
+        <v>46669.0</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D473" s="2">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>405</v>
+        <v>880</v>
       </c>
       <c r="G473" s="9">
         <v>46669.0</v>
@@ -14563,7 +14579,7 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>32</v>
@@ -14575,10 +14591,10 @@
         <v>6.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="G474" s="9">
         <v>46669.0</v>
@@ -14586,7 +14602,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>32</v>
@@ -14601,7 +14617,7 @@
         <v>882</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>883</v>
+        <v>812</v>
       </c>
       <c r="G475" s="9">
         <v>46669.0</v>
@@ -14609,7 +14625,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>32</v>
@@ -14624,7 +14640,7 @@
         <v>882</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>812</v>
+        <v>886</v>
       </c>
       <c r="G476" s="9">
         <v>46669.0</v>
@@ -14632,30 +14648,30 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D477" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="G477" s="9">
-        <v>46669.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>32</v>
@@ -14667,18 +14683,18 @@
         <v>18.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>888</v>
+        <v>601</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>889</v>
       </c>
       <c r="G478" s="9">
-        <v>46947.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>32</v>
@@ -14690,7 +14706,7 @@
         <v>18.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>601</v>
+        <v>66</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>889</v>
@@ -14701,7 +14717,7 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>32</v>
@@ -14713,18 +14729,15 @@
         <v>18.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>66</v>
+        <v>832</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="G480" s="9">
-        <v>46949.0</v>
-      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>32</v>
@@ -14733,124 +14746,127 @@
         <v>27</v>
       </c>
       <c r="D481" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>832</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>889</v>
+        <v>43</v>
+      </c>
+      <c r="G481" s="9">
+        <v>46730.0</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D482" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>832</v>
+        <v>895</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G482" s="9">
-        <v>46730.0</v>
+        <v>346</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D483" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>895</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>346</v>
+        <v>118</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D484" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>118</v>
+        <v>441</v>
+      </c>
+      <c r="G484" s="9">
+        <v>46267.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D485" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="F485" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G485" s="9">
-        <v>46267.0</v>
+        <v>900</v>
+      </c>
+      <c r="F485" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D486" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="F486" s="3">
-        <v>11505.0</v>
+        <v>902</v>
+      </c>
+      <c r="F486" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="G486" s="9">
+        <v>46250.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>32</v>
@@ -14862,64 +14878,64 @@
         <v>8.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F487" s="3" t="s">
-        <v>760</v>
+        <v>359</v>
       </c>
       <c r="G487" s="9">
-        <v>46250.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="G488" s="9">
-        <v>46255.0</v>
+        <v>46613.0</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C489" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D489" s="2">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>906</v>
+        <v>607</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>470</v>
+        <v>608</v>
       </c>
       <c r="G489" s="9">
-        <v>46613.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>32</v>
@@ -14928,87 +14944,80 @@
         <v>11</v>
       </c>
       <c r="D490" s="2">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>607</v>
+        <v>909</v>
       </c>
       <c r="F490" s="3" t="s">
-        <v>608</v>
+        <v>449</v>
       </c>
       <c r="G490" s="9">
-        <v>46669.0</v>
+        <v>46691.0</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D491" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F491" s="3">
-        <v>11504.0</v>
+        <v>909</v>
+      </c>
+      <c r="F491" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="G491" s="9">
+        <v>46775.0</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D492" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="F492" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G492" s="9">
-        <v>46691.0</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="F492" s="4"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D493" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="F493" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="G493" s="9">
-        <v>46775.0</v>
-      </c>
+        <v>914</v>
+      </c>
+      <c r="F493" s="4"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>32</v>
@@ -15020,13 +15029,13 @@
         <v>11.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="F494" s="4"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>32</v>
@@ -15038,95 +15047,95 @@
         <v>11.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="F495" s="4"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D496" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="F496" s="4"/>
+        <v>920</v>
+      </c>
+      <c r="F496" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="G496" s="9">
+        <v>46803.0</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D497" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="F497" s="4"/>
+        <v>875</v>
+      </c>
+      <c r="F497" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="G497" s="9">
+        <v>46222.0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D498" s="2">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="F498" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="G498" s="9">
-        <v>46803.0</v>
-      </c>
+        <v>925</v>
+      </c>
+      <c r="F498" s="4"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D499" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="F499" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="G499" s="9">
-        <v>46222.0</v>
-      </c>
+        <v>927</v>
+      </c>
+      <c r="F499" s="4"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>32</v>
@@ -15138,13 +15147,13 @@
         <v>11.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="F500" s="4"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>32</v>
@@ -15156,49 +15165,55 @@
         <v>11.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="F501" s="4"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D502" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="F502" s="4"/>
+      <c r="G502" s="9">
+        <v>46564.0</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D503" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="F503" s="4"/>
+      <c r="G503" s="9">
+        <v>46551.0</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>32</v>
@@ -15210,16 +15225,16 @@
         <v>14.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="F504" s="4"/>
       <c r="G504" s="9">
-        <v>46564.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>32</v>
@@ -15228,19 +15243,19 @@
         <v>25</v>
       </c>
       <c r="D505" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F505" s="4"/>
       <c r="G505" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>32</v>
@@ -15249,19 +15264,19 @@
         <v>25</v>
       </c>
       <c r="D506" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="F506" s="4"/>
       <c r="G506" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>32</v>
@@ -15273,16 +15288,16 @@
         <v>15.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="F507" s="4"/>
       <c r="G507" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>32</v>
@@ -15294,7 +15309,7 @@
         <v>15.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="F508" s="4"/>
       <c r="G508" s="9">
@@ -15303,7 +15318,7 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>32</v>
@@ -15312,19 +15327,19 @@
         <v>25</v>
       </c>
       <c r="D509" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="F509" s="4"/>
       <c r="G509" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>32</v>
@@ -15333,40 +15348,39 @@
         <v>25</v>
       </c>
       <c r="D510" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="F510" s="4"/>
       <c r="G510" s="9">
-        <v>46355.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D511" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="F511" s="4"/>
-      <c r="G511" s="9">
-        <v>46551.0</v>
+        <v>951</v>
+      </c>
+      <c r="F511" s="3" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>32</v>
@@ -15375,80 +15389,85 @@
         <v>25</v>
       </c>
       <c r="D512" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="F512" s="4"/>
-      <c r="G512" s="9">
-        <v>46394.0</v>
-      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D513" s="2">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="F513" s="3" t="s">
         <v>418</v>
       </c>
+      <c r="G513" s="9">
+        <v>46759.0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D514" s="2">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="F514" s="4"/>
+        <v>957</v>
+      </c>
+      <c r="F514" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G514" s="9">
+        <v>46406.0</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D515" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="F515" s="3" t="s">
-        <v>418</v>
+        <v>37</v>
       </c>
       <c r="G515" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>537</v>
@@ -15460,7 +15479,7 @@
         <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="F516" s="3" t="s">
         <v>37</v>
@@ -15471,7 +15490,7 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>537</v>
@@ -15483,7 +15502,7 @@
         <v>3.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="F517" s="3" t="s">
         <v>37</v>
@@ -15494,7 +15513,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>537</v>
@@ -15506,10 +15525,10 @@
         <v>3.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G518" s="9">
         <v>46406.0</v>
@@ -15517,7 +15536,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>537</v>
@@ -15529,18 +15548,18 @@
         <v>3.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G519" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>537</v>
@@ -15552,18 +15571,18 @@
         <v>3.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="F520" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G520" s="9">
-        <v>46406.0</v>
+        <v>46258.0</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>537</v>
@@ -15575,18 +15594,18 @@
         <v>3.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G521" s="9">
-        <v>46251.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>537</v>
@@ -15595,21 +15614,21 @@
         <v>11</v>
       </c>
       <c r="D522" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G522" s="9">
-        <v>46258.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>537</v>
@@ -15618,21 +15637,21 @@
         <v>11</v>
       </c>
       <c r="D523" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G523" s="9">
-        <v>46254.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>537</v>
@@ -15644,7 +15663,7 @@
         <v>4.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>37</v>
@@ -15655,7 +15674,7 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>537</v>
@@ -15667,7 +15686,7 @@
         <v>4.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>37</v>
@@ -15678,7 +15697,7 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>537</v>
@@ -15687,21 +15706,21 @@
         <v>11</v>
       </c>
       <c r="D526" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G526" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>537</v>
@@ -15710,21 +15729,21 @@
         <v>11</v>
       </c>
       <c r="D527" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G527" s="9">
-        <v>46387.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>537</v>
@@ -15736,18 +15755,18 @@
         <v>6.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F528" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G528" s="9">
-        <v>46251.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>537</v>
@@ -15759,18 +15778,18 @@
         <v>6.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="F529" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G529" s="9">
-        <v>46280.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>537</v>
@@ -15782,18 +15801,18 @@
         <v>6.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F530" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G530" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>537</v>
@@ -15805,7 +15824,7 @@
         <v>6.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>37</v>
@@ -15816,7 +15835,7 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>537</v>
@@ -15828,18 +15847,18 @@
         <v>6.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G532" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>537</v>
@@ -15848,21 +15867,21 @@
         <v>11</v>
       </c>
       <c r="D533" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="F533" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G533" s="9">
-        <v>46256.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>537</v>
@@ -15871,21 +15890,21 @@
         <v>11</v>
       </c>
       <c r="D534" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="F534" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G534" s="9">
-        <v>46249.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>537</v>
@@ -15897,18 +15916,18 @@
         <v>7.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="F535" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G535" s="9">
-        <v>46352.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>537</v>
@@ -15917,21 +15936,21 @@
         <v>11</v>
       </c>
       <c r="D536" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="F536" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G536" s="9">
-        <v>46333.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>537</v>
@@ -15940,21 +15959,21 @@
         <v>11</v>
       </c>
       <c r="D537" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F537" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G537" s="9">
-        <v>46244.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>537</v>
@@ -15966,18 +15985,18 @@
         <v>8.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G538" s="9">
-        <v>46226.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>537</v>
@@ -15989,18 +16008,18 @@
         <v>8.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="F539" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G539" s="9">
-        <v>46222.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>537</v>
@@ -16012,18 +16031,18 @@
         <v>8.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="F540" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G540" s="9">
-        <v>46241.0</v>
+        <v>46319.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>537</v>
@@ -16032,21 +16051,21 @@
         <v>11</v>
       </c>
       <c r="D541" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G541" s="9">
-        <v>46305.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>537</v>
@@ -16055,21 +16074,21 @@
         <v>11</v>
       </c>
       <c r="D542" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G542" s="9">
-        <v>46319.0</v>
+        <v>46321.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>537</v>
@@ -16078,21 +16097,24 @@
         <v>11</v>
       </c>
       <c r="D543" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="G543" s="9">
-        <v>46365.0</v>
+        <v>46426.0</v>
+      </c>
+      <c r="H543" s="2" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>537</v>
@@ -16101,21 +16123,21 @@
         <v>11</v>
       </c>
       <c r="D544" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G544" s="9">
-        <v>46321.0</v>
+        <v>46211.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>537</v>
@@ -16127,21 +16149,18 @@
         <v>10.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="F545" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G545" s="9">
-        <v>46426.0</v>
-      </c>
-      <c r="H545" s="2" t="s">
-        <v>1015</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>537</v>
@@ -16153,18 +16172,18 @@
         <v>10.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G546" s="9">
-        <v>46211.0</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>537</v>
@@ -16173,21 +16192,21 @@
         <v>11</v>
       </c>
       <c r="D547" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="F547" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G547" s="9">
-        <v>46204.0</v>
+        <v>46392.0</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>537</v>
@@ -16196,21 +16215,21 @@
         <v>11</v>
       </c>
       <c r="D548" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="F548" s="3" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="G548" s="9">
-        <v>46345.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>537</v>
@@ -16219,21 +16238,22 @@
         <v>11</v>
       </c>
       <c r="D549" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F549" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>1026</v>
+      </c>
+      <c r="F549" s="4"/>
       <c r="G549" s="9">
-        <v>46392.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I549" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>537</v>
@@ -16242,21 +16262,22 @@
         <v>11</v>
       </c>
       <c r="D550" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F550" s="3" t="s">
-        <v>493</v>
-      </c>
+        <v>1028</v>
+      </c>
+      <c r="F550" s="4"/>
       <c r="G550" s="9">
-        <v>46366.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I550" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>537</v>
@@ -16268,19 +16289,16 @@
         <v>14.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="F551" s="4"/>
       <c r="G551" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I551" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>537</v>
@@ -16292,19 +16310,16 @@
         <v>14.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="F552" s="4"/>
       <c r="G552" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I552" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>537</v>
@@ -16313,19 +16328,18 @@
         <v>11</v>
       </c>
       <c r="D553" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F553" s="4"/>
-      <c r="G553" s="9">
-        <v>46220.0</v>
+        <v>1034</v>
+      </c>
+      <c r="F553" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>537</v>
@@ -16334,22 +16348,21 @@
         <v>11</v>
       </c>
       <c r="D554" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F554" s="4"/>
-      <c r="G554" s="9">
-        <v>46220.0</v>
+        <v>1036</v>
+      </c>
+      <c r="F554" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>11</v>
@@ -16358,18 +16371,21 @@
         <v>1.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F555" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="G555" s="9">
+        <v>46223.0</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>11</v>
@@ -16378,15 +16394,18 @@
         <v>2.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F556" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="G556" s="9">
+        <v>46228.0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>535</v>
@@ -16395,21 +16414,21 @@
         <v>11</v>
       </c>
       <c r="D557" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>157</v>
+        <v>626</v>
       </c>
       <c r="G557" s="9">
-        <v>46223.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>535</v>
@@ -16418,21 +16437,21 @@
         <v>11</v>
       </c>
       <c r="D558" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>157</v>
+        <v>631</v>
       </c>
       <c r="G558" s="9">
-        <v>46228.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>535</v>
@@ -16441,21 +16460,21 @@
         <v>11</v>
       </c>
       <c r="D559" s="2">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="G559" s="9">
-        <v>46269.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>535</v>
@@ -16464,44 +16483,47 @@
         <v>11</v>
       </c>
       <c r="D560" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>631</v>
+        <v>399</v>
       </c>
       <c r="G560" s="9">
-        <v>46240.0</v>
+        <v>46274.0</v>
+      </c>
+      <c r="H560" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D561" s="2">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>631</v>
+        <v>1050</v>
       </c>
       <c r="G561" s="9">
-        <v>46242.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>535</v>
@@ -16510,200 +16532,197 @@
         <v>11</v>
       </c>
       <c r="D562" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>399</v>
+        <v>1053</v>
       </c>
       <c r="G562" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H562" s="2" t="s">
-        <v>714</v>
+        <v>46207.0</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D563" s="2">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G563" s="9">
-        <v>46743.0</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D564" s="2">
-        <v>15.0</v>
+        <v>22.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="G564" s="9">
-        <v>46207.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>535</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D565" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F565" s="3" t="s">
-        <v>1057</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="F565" s="4"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D566" s="2">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>1057</v>
+        <v>227</v>
       </c>
       <c r="G566" s="9">
-        <v>46516.0</v>
+        <v>46295.0</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D567" s="2">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F567" s="4"/>
+        <v>1062</v>
+      </c>
+      <c r="F567" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G567" s="9">
+        <v>46769.0</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D568" s="2">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>227</v>
+        <v>399</v>
       </c>
       <c r="G568" s="9">
-        <v>46295.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D569" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G569" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D570" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G570" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>535</v>
@@ -16715,18 +16734,18 @@
         <v>3.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="F571" s="3" t="s">
         <v>627</v>
       </c>
       <c r="G571" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>535</v>
@@ -16738,18 +16757,18 @@
         <v>3.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="F572" s="3" t="s">
         <v>627</v>
       </c>
       <c r="G572" s="9">
-        <v>46261.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>535</v>
@@ -16761,7 +16780,7 @@
         <v>3.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="F573" s="3" t="s">
         <v>627</v>
@@ -16772,7 +16791,7 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>535</v>
@@ -16784,21 +16803,21 @@
         <v>3.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="F574" s="3" t="s">
         <v>627</v>
       </c>
       <c r="G574" s="9">
-        <v>46223.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>11</v>
@@ -16807,64 +16826,64 @@
         <v>3.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>627</v>
+        <v>399</v>
       </c>
       <c r="G575" s="9">
-        <v>46266.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D576" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1076</v>
+        <v>716</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>627</v>
+        <v>1079</v>
       </c>
       <c r="G576" s="9">
-        <v>46261.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D577" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>399</v>
+        <v>1079</v>
       </c>
       <c r="G577" s="9">
-        <v>46769.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>112</v>
@@ -16876,18 +16895,18 @@
         <v>14.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G578" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>112</v>
@@ -16899,64 +16918,64 @@
         <v>14.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1082</v>
+        <v>601</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G579" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C580" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D580" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>712</v>
+        <v>895</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="G580" s="9">
-        <v>46820.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D581" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>601</v>
+        <v>1087</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="G581" s="9">
-        <v>46998.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>32</v>
@@ -16968,18 +16987,18 @@
         <v>2.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>895</v>
+        <v>1090</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="G582" s="9">
-        <v>46484.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>32</v>
@@ -16991,18 +17010,18 @@
         <v>2.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1089</v>
+        <v>458</v>
       </c>
       <c r="G583" s="9">
-        <v>46432.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>32</v>
@@ -17014,18 +17033,16 @@
         <v>2.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G584" s="9">
-        <v>46877.0</v>
-      </c>
+        <v>1096</v>
+      </c>
+      <c r="G584" s="9"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>32</v>
@@ -17037,18 +17054,15 @@
         <v>2.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G585" s="9">
-        <v>46704.0</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>32</v>
@@ -17060,16 +17074,15 @@
         <v>2.0</v>
       </c>
       <c r="E586" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F586" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="F586" s="3" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G586" s="9"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>32</v>
@@ -17081,15 +17094,15 @@
         <v>2.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1099</v>
+        <v>584</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>32</v>
@@ -17101,15 +17114,15 @@
         <v>2.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>879</v>
+        <v>1098</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>32</v>
@@ -17121,15 +17134,15 @@
         <v>2.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>584</v>
+        <v>1103</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>32</v>
@@ -17141,58 +17154,64 @@
         <v>2.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1097</v>
+        <v>593</v>
+      </c>
+      <c r="G590" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D591" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1097</v>
+        <v>1108</v>
+      </c>
+      <c r="G591" s="9">
+        <v>46877.0</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D592" s="2">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1106</v>
+        <v>849</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>593</v>
+        <v>1108</v>
       </c>
       <c r="G592" s="9">
-        <v>46766.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>112</v>
@@ -17201,21 +17220,21 @@
         <v>11</v>
       </c>
       <c r="D593" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E593" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F593" s="3" t="s">
         <v>1108</v>
       </c>
-      <c r="F593" s="3" t="s">
-        <v>1109</v>
-      </c>
       <c r="G593" s="9">
-        <v>46877.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>112</v>
@@ -17224,21 +17243,19 @@
         <v>11</v>
       </c>
       <c r="D594" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F594" s="3" t="s">
-        <v>1109</v>
-      </c>
-      <c r="G594" s="9">
-        <v>46641.0</v>
+        <v>1113</v>
+      </c>
+      <c r="F594" s="4"/>
+      <c r="H594" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>112</v>
@@ -17247,42 +17264,50 @@
         <v>11</v>
       </c>
       <c r="D595" s="2">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1112</v>
+        <v>752</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="G595" s="9">
-        <v>46743.0</v>
+        <v>46663.0</v>
+      </c>
+      <c r="H595" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D596" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F596" s="4"/>
+        <v>582</v>
+      </c>
+      <c r="F596" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G596" s="9">
+        <v>46437.0</v>
+      </c>
       <c r="H596" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>112</v>
@@ -17291,50 +17316,44 @@
         <v>11</v>
       </c>
       <c r="D597" s="2">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>752</v>
+        <v>1119</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="G597" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H597" s="2" t="s">
-        <v>133</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D598" s="2">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>582</v>
+        <v>661</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
       <c r="G598" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H598" s="2" t="s">
-        <v>133</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>112</v>
@@ -17343,21 +17362,21 @@
         <v>11</v>
       </c>
       <c r="D599" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G599" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>112</v>
@@ -17366,67 +17385,67 @@
         <v>11</v>
       </c>
       <c r="D600" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>661</v>
+        <v>1124</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G600" s="9">
-        <v>46530.0</v>
+        <v>46834.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D601" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G601" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D602" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G602" s="9">
-        <v>46834.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>112</v>
@@ -17438,18 +17457,18 @@
         <v>14.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G603" s="9">
-        <v>46481.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>112</v>
@@ -17461,18 +17480,18 @@
         <v>14.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G604" s="9">
-        <v>46877.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>112</v>
@@ -17484,18 +17503,18 @@
         <v>14.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G605" s="9">
-        <v>46872.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>112</v>
@@ -17507,18 +17526,18 @@
         <v>14.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G606" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>112</v>
@@ -17530,18 +17549,18 @@
         <v>14.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G607" s="9">
-        <v>46734.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>112</v>
@@ -17553,87 +17572,87 @@
         <v>14.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="F608" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G608" s="9">
-        <v>46481.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D609" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1139</v>
+        <v>849</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G609" s="9">
-        <v>46872.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D610" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>1109</v>
+        <v>399</v>
       </c>
       <c r="G610" s="9">
-        <v>46877.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D611" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>849</v>
+        <v>1145</v>
       </c>
       <c r="F611" s="3" t="s">
-        <v>1109</v>
+        <v>399</v>
       </c>
       <c r="G611" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>535</v>
@@ -17642,10 +17661,10 @@
         <v>11</v>
       </c>
       <c r="D612" s="2">
-        <v>17.0</v>
+        <v>5.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1144</v>
+        <v>655</v>
       </c>
       <c r="F612" s="3" t="s">
         <v>399</v>
@@ -17656,49 +17675,66 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D613" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F613" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G613" s="9">
-        <v>46274.0</v>
-      </c>
+        <v>1148</v>
+      </c>
+      <c r="F613" s="3"/>
+      <c r="G613" s="9"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D614" s="2">
-        <v>5.0</v>
+        <v>21.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>655</v>
+        <v>1150</v>
       </c>
       <c r="F614" s="3" t="s">
-        <v>399</v>
+        <v>224</v>
       </c>
       <c r="G614" s="9">
-        <v>46274.0</v>
-      </c>
+        <v>46437.0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D615" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="E615" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F615" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G615" s="9"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2894" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="1152">
   <si>
     <t>ID</t>
   </si>
@@ -2302,9 +2302,6 @@
     <t>1150429K</t>
   </si>
   <si>
-    <t>ID1778139597971</t>
-  </si>
-  <si>
     <t>ID1778197333009</t>
   </si>
   <si>
@@ -2710,12 +2707,6 @@
     <t>M45OB-MU</t>
   </si>
   <si>
-    <t>ID1778745054676</t>
-  </si>
-  <si>
-    <t>34B</t>
-  </si>
-  <si>
     <t>ID1779067878945</t>
   </si>
   <si>
@@ -3175,301 +3166,307 @@
     <t>26#36</t>
   </si>
   <si>
-    <t>ID1779435730425</t>
-  </si>
-  <si>
-    <t>ACCRM-SS （待調A5)</t>
+    <t>ID1779437559431</t>
+  </si>
+  <si>
+    <t>ID1779441353346</t>
+  </si>
+  <si>
+    <t>M67RER-280-320-KR</t>
+  </si>
+  <si>
+    <t>ID1779701743464</t>
+  </si>
+  <si>
+    <t>MP-KR</t>
+  </si>
+  <si>
+    <t>ID1779701756769</t>
+  </si>
+  <si>
+    <t>ID1779701865759</t>
+  </si>
+  <si>
+    <t>M45BSTT-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779701896780</t>
+  </si>
+  <si>
+    <t>M67FM-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779701936239</t>
+  </si>
+  <si>
+    <t>M89RER-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779701958932</t>
+  </si>
+  <si>
+    <t>M89TDL-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779702003682</t>
+  </si>
+  <si>
+    <t>M89OB-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779702021437</t>
+  </si>
+  <si>
+    <t>M89SRL-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779719332195</t>
+  </si>
+  <si>
+    <t>KR-MP</t>
+  </si>
+  <si>
+    <t>ID1779760015433</t>
+  </si>
+  <si>
+    <t>1150525K</t>
+  </si>
+  <si>
+    <t>ID1779760027714</t>
+  </si>
+  <si>
+    <t>PRSRL-YK</t>
+  </si>
+  <si>
+    <t>ID1779760044232</t>
+  </si>
+  <si>
+    <t>ID1779760055112</t>
+  </si>
+  <si>
+    <t>ID1779768396440</t>
+  </si>
+  <si>
+    <t>1140623K</t>
+  </si>
+  <si>
+    <t>ID1779768429388</t>
+  </si>
+  <si>
+    <t>M89SRM-KR</t>
+  </si>
+  <si>
+    <t>1140508K</t>
+  </si>
+  <si>
+    <t>ID1779768468384</t>
+  </si>
+  <si>
+    <t>M89OSF-KR</t>
+  </si>
+  <si>
+    <t>1150522K</t>
+  </si>
+  <si>
+    <t>ID1779768511004</t>
+  </si>
+  <si>
+    <t>A5TDL</t>
+  </si>
+  <si>
+    <t>ID1779768548653</t>
+  </si>
+  <si>
+    <t>M45BSTT-KR</t>
+  </si>
+  <si>
+    <t>1150518K</t>
+  </si>
+  <si>
+    <t>ID1779768607674</t>
+  </si>
+  <si>
+    <t>M67FM-KR</t>
+  </si>
+  <si>
+    <t>ID1779768624471</t>
+  </si>
+  <si>
+    <t>ID1779768641201</t>
+  </si>
+  <si>
+    <t>ID1779768655644</t>
+  </si>
+  <si>
+    <t>ID1779768670511</t>
+  </si>
+  <si>
+    <t>M67OB-KR</t>
+  </si>
+  <si>
+    <t>ID1779777307015</t>
+  </si>
+  <si>
+    <t>A5RER</t>
+  </si>
+  <si>
+    <t>ID1779880646013</t>
+  </si>
+  <si>
+    <t>M89BBLD-對切-KR</t>
+  </si>
+  <si>
+    <t>1150527S</t>
+  </si>
+  <si>
+    <t>ID1779880690658</t>
+  </si>
+  <si>
+    <t>ID1779880763675</t>
+  </si>
+  <si>
+    <t>EMSPL-十字切-SS</t>
+  </si>
+  <si>
+    <t>ID1779935223860</t>
+  </si>
+  <si>
+    <t>26B</t>
+  </si>
+  <si>
+    <t>ID1779935393105</t>
+  </si>
+  <si>
+    <t>1141222K</t>
+  </si>
+  <si>
+    <t>ID1779936128614</t>
+  </si>
+  <si>
+    <t>1140514K</t>
+  </si>
+  <si>
+    <t>ID1779952236759</t>
+  </si>
+  <si>
+    <t>ACRER-200-250-TY</t>
+  </si>
+  <si>
+    <t>ID1779952271401</t>
+  </si>
+  <si>
+    <t>ID1779952289227</t>
+  </si>
+  <si>
+    <t>GMB(骨)</t>
+  </si>
+  <si>
+    <t>ID1779952979939</t>
+  </si>
+  <si>
+    <t>M45OB-切3CM</t>
+  </si>
+  <si>
+    <t>ID1779953032414</t>
+  </si>
+  <si>
+    <t>PRRER-340-380-SS</t>
+  </si>
+  <si>
+    <t>ID1779953075175</t>
+  </si>
+  <si>
+    <t>M89OSF-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953104690</t>
+  </si>
+  <si>
+    <t>M45BBLD-1.5cm-KR</t>
+  </si>
+  <si>
+    <t>ID1779953130180</t>
+  </si>
+  <si>
+    <t>PRSRL-230-270-GO</t>
+  </si>
+  <si>
+    <t>ID1779953153190</t>
+  </si>
+  <si>
+    <t>PRRER-450-490-YK</t>
+  </si>
+  <si>
+    <t>ID1779953199741</t>
+  </si>
+  <si>
+    <t>PRRER-360-400-SS</t>
+  </si>
+  <si>
+    <t>ID1779953241499</t>
+  </si>
+  <si>
+    <t>M45BBLD-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953260859</t>
+  </si>
+  <si>
+    <t>M89CER-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953383633</t>
+  </si>
+  <si>
+    <t>ID1779956331825</t>
+  </si>
+  <si>
+    <t>PRTDL-C-GO</t>
+  </si>
+  <si>
+    <t>ID1779956377322</t>
+  </si>
+  <si>
+    <t>PRSRM-C-GO</t>
+  </si>
+  <si>
+    <t>ID1779956605362</t>
+  </si>
+  <si>
+    <t>ID1780023477991</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>ID1780023544888</t>
+  </si>
+  <si>
+    <t>BJUJM</t>
+  </si>
+  <si>
+    <t>ID1780023826368</t>
+  </si>
+  <si>
+    <t>ACCRM-SS(A5預留用)</t>
   </si>
   <si>
     <t>26#19</t>
   </si>
   <si>
-    <t>ID1779435802140</t>
-  </si>
-  <si>
-    <t>ID1779437559431</t>
-  </si>
-  <si>
-    <t>ID1779441353346</t>
-  </si>
-  <si>
-    <t>M67RER-280-320-KR</t>
-  </si>
-  <si>
-    <t>ID1779701743464</t>
-  </si>
-  <si>
-    <t>MP-KR</t>
-  </si>
-  <si>
-    <t>ID1779701756769</t>
-  </si>
-  <si>
-    <t>ID1779701865759</t>
-  </si>
-  <si>
-    <t>M45BSTT-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779701896780</t>
-  </si>
-  <si>
-    <t>M67FM-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779701936239</t>
-  </si>
-  <si>
-    <t>M89RER-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779701958932</t>
-  </si>
-  <si>
-    <t>M89TDL-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779702003682</t>
-  </si>
-  <si>
-    <t>M89OB-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779702021437</t>
-  </si>
-  <si>
-    <t>M89SRL-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779719332195</t>
-  </si>
-  <si>
-    <t>KR-MP</t>
-  </si>
-  <si>
-    <t>ID1779760015433</t>
-  </si>
-  <si>
-    <t>1150525K</t>
-  </si>
-  <si>
-    <t>ID1779760027714</t>
-  </si>
-  <si>
-    <t>PRSRL-YK</t>
-  </si>
-  <si>
-    <t>ID1779760044232</t>
-  </si>
-  <si>
-    <t>ID1779760055112</t>
-  </si>
-  <si>
-    <t>ID1779768396440</t>
-  </si>
-  <si>
-    <t>1140623K</t>
-  </si>
-  <si>
-    <t>ID1779768429388</t>
-  </si>
-  <si>
-    <t>M89SRM-KR</t>
-  </si>
-  <si>
-    <t>1140508K</t>
-  </si>
-  <si>
-    <t>ID1779768468384</t>
-  </si>
-  <si>
-    <t>M89OSF-KR</t>
-  </si>
-  <si>
-    <t>1150522K</t>
-  </si>
-  <si>
-    <t>ID1779768511004</t>
-  </si>
-  <si>
-    <t>A5TDL</t>
-  </si>
-  <si>
-    <t>ID1779768548653</t>
-  </si>
-  <si>
-    <t>M45BSTT-KR</t>
-  </si>
-  <si>
-    <t>1150518K</t>
-  </si>
-  <si>
-    <t>ID1779768607674</t>
-  </si>
-  <si>
-    <t>M67FM-KR</t>
-  </si>
-  <si>
-    <t>ID1779768624471</t>
-  </si>
-  <si>
-    <t>ID1779768641201</t>
-  </si>
-  <si>
-    <t>ID1779768655644</t>
-  </si>
-  <si>
-    <t>ID1779768670511</t>
-  </si>
-  <si>
-    <t>M67OB-KR</t>
-  </si>
-  <si>
-    <t>ID1779777307015</t>
-  </si>
-  <si>
-    <t>A5RER</t>
-  </si>
-  <si>
-    <t>ID1779880646013</t>
-  </si>
-  <si>
-    <t>M89BBLD-對切-KR</t>
-  </si>
-  <si>
-    <t>1150527S</t>
-  </si>
-  <si>
-    <t>ID1779880690658</t>
-  </si>
-  <si>
-    <t>ID1779880763675</t>
-  </si>
-  <si>
-    <t>EMSPL-十字切-SS</t>
-  </si>
-  <si>
-    <t>ID1779935223860</t>
-  </si>
-  <si>
-    <t>26B</t>
-  </si>
-  <si>
-    <t>ID1779935393105</t>
-  </si>
-  <si>
-    <t>1141222K</t>
-  </si>
-  <si>
-    <t>ID1779936128614</t>
-  </si>
-  <si>
-    <t>1140514K</t>
-  </si>
-  <si>
-    <t>ID1779952236759</t>
-  </si>
-  <si>
-    <t>ACRER-200-250-TY</t>
-  </si>
-  <si>
-    <t>ID1779952271401</t>
-  </si>
-  <si>
-    <t>ID1779952289227</t>
-  </si>
-  <si>
-    <t>GMB(骨)</t>
-  </si>
-  <si>
-    <t>ID1779952979939</t>
-  </si>
-  <si>
-    <t>M45OB-切3CM</t>
-  </si>
-  <si>
-    <t>ID1779953032414</t>
-  </si>
-  <si>
-    <t>PRRER-340-380-SS</t>
-  </si>
-  <si>
-    <t>ID1779953075175</t>
-  </si>
-  <si>
-    <t>M89OSF-十字切-KR</t>
-  </si>
-  <si>
-    <t>ID1779953104690</t>
-  </si>
-  <si>
-    <t>M45BBLD-1.5cm-KR</t>
-  </si>
-  <si>
-    <t>ID1779953130180</t>
-  </si>
-  <si>
-    <t>PRSRL-230-270-GO</t>
-  </si>
-  <si>
-    <t>ID1779953153190</t>
-  </si>
-  <si>
-    <t>PRRER-450-490-YK</t>
-  </si>
-  <si>
-    <t>ID1779953199741</t>
-  </si>
-  <si>
-    <t>PRRER-360-400-SS</t>
-  </si>
-  <si>
-    <t>ID1779953241499</t>
-  </si>
-  <si>
-    <t>M45BBLD-十字切-KR</t>
-  </si>
-  <si>
-    <t>ID1779953260859</t>
-  </si>
-  <si>
-    <t>M89CER-十字切-KR</t>
-  </si>
-  <si>
-    <t>ID1779953383633</t>
-  </si>
-  <si>
-    <t>ID1779956331825</t>
-  </si>
-  <si>
-    <t>PRTDL-C-GO</t>
-  </si>
-  <si>
-    <t>ID1779956377322</t>
-  </si>
-  <si>
-    <t>PRSRM-C-GO</t>
-  </si>
-  <si>
-    <t>ID1779956605362</t>
-  </si>
-  <si>
-    <t>ID1780023477991</t>
-  </si>
-  <si>
-    <t>TS</t>
-  </si>
-  <si>
-    <t>ID1780023544888</t>
-  </si>
-  <si>
-    <t>BJUJM</t>
-  </si>
-  <si>
-    <t>ID1780023826368</t>
-  </si>
-  <si>
-    <t>ACCRM-SS(A5預留用)</t>
+    <t>ID1780285597561</t>
+  </si>
+  <si>
+    <t>廢料</t>
+  </si>
+  <si>
+    <t>（報廢）</t>
+  </si>
+  <si>
+    <t>ID1780287319374</t>
+  </si>
+  <si>
+    <t>W(A5)</t>
   </si>
 </sst>
 </file>
@@ -13171,24 +13168,24 @@
         <v>763</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D411" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F411" s="3">
-        <v>11505.0</v>
+        <v>764</v>
+      </c>
+      <c r="F411" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>10</v>
@@ -13200,7 +13197,7 @@
         <v>2.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>765</v>
+        <v>15</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>224</v>
@@ -13220,10 +13217,10 @@
         <v>2.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>15</v>
+        <v>764</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="414">
@@ -13234,21 +13231,24 @@
         <v>10</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D414" s="2">
         <v>2.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G414" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>10</v>
@@ -13257,42 +13257,42 @@
         <v>25</v>
       </c>
       <c r="D415" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F415" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="F415" s="4"/>
       <c r="G415" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C416" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D416" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F416" s="4"/>
+        <v>772</v>
+      </c>
+      <c r="F416" s="3" t="s">
+        <v>773</v>
+      </c>
       <c r="G416" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>32</v>
@@ -13304,36 +13304,33 @@
         <v>4.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G417" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D418" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="F418" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="G418" s="9">
-        <v>46484.0</v>
+        <v>547</v>
+      </c>
+      <c r="F418" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="419">
@@ -13341,19 +13338,19 @@
         <v>777</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D419" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F419" s="3">
-        <v>11505.0</v>
+        <v>712</v>
+      </c>
+      <c r="F419" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="420">
@@ -13364,67 +13361,70 @@
         <v>32</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D420" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>712</v>
+        <v>779</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>55</v>
+        <v>604</v>
+      </c>
+      <c r="G420" s="9">
+        <v>46577.0</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D421" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>604</v>
+        <v>272</v>
       </c>
       <c r="G421" s="9">
-        <v>46577.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D422" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="G422" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>112</v>
@@ -13436,18 +13436,18 @@
         <v>17.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F423" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G423" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>112</v>
@@ -13459,18 +13459,18 @@
         <v>17.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G424" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>112</v>
@@ -13482,18 +13482,18 @@
         <v>17.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>595</v>
       </c>
       <c r="G425" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>112</v>
@@ -13505,53 +13505,50 @@
         <v>17.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>595</v>
+        <v>792</v>
       </c>
       <c r="G426" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D427" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="G427" s="9">
-        <v>46523.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D428" s="2">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>224</v>
@@ -13559,19 +13556,19 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D429" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>224</v>
@@ -13579,7 +13576,7 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>32</v>
@@ -13588,10 +13585,10 @@
         <v>27</v>
       </c>
       <c r="D430" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>224</v>
@@ -13599,50 +13596,53 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D431" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>224</v>
+        <v>238</v>
+      </c>
+      <c r="G431" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="2">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G432" s="9">
-        <v>46281.0</v>
+        <v>493</v>
+      </c>
+      <c r="H432" s="2" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>32</v>
@@ -13651,21 +13651,21 @@
         <v>11</v>
       </c>
       <c r="D433" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H433" s="2" t="s">
-        <v>806</v>
+      <c r="G433" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>32</v>
@@ -13674,67 +13674,67 @@
         <v>11</v>
       </c>
       <c r="D434" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="G434" s="9">
-        <v>47146.0</v>
+      <c r="H434" s="2" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>810</v>
+        <v>752</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H435" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
+      </c>
+      <c r="G435" s="9">
+        <v>46666.0</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>752</v>
+        <v>813</v>
       </c>
       <c r="F436" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="G436" s="9">
-        <v>46666.0</v>
+        <v>46583.0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>32</v>
@@ -13746,18 +13746,18 @@
         <v>8.0</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G437" s="9">
-        <v>46583.0</v>
+        <v>46604.0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>32</v>
@@ -13769,13 +13769,13 @@
         <v>8.0</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>817</v>
+        <v>110</v>
       </c>
       <c r="G438" s="9">
-        <v>46604.0</v>
+        <v>46626.0</v>
       </c>
     </row>
     <row r="439">
@@ -13792,18 +13792,18 @@
         <v>8.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>110</v>
+        <v>819</v>
       </c>
       <c r="G439" s="9">
-        <v>46626.0</v>
+        <v>46658.0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>32</v>
@@ -13815,105 +13815,105 @@
         <v>8.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="G440" s="9">
-        <v>46658.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D441" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F441" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="G441" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>823</v>
+      </c>
+      <c r="F441" s="4"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D442" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="F442" s="4"/>
+        <v>825</v>
+      </c>
+      <c r="F442" s="3" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D443" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>493</v>
+        <v>828</v>
+      </c>
+      <c r="G443" s="9">
+        <v>46792.0</v>
+      </c>
+      <c r="H443" s="2" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D444" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="G444" s="9">
-        <v>46792.0</v>
-      </c>
-      <c r="H444" s="2" t="s">
-        <v>830</v>
+        <v>46304.0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>32</v>
@@ -13922,16 +13922,16 @@
         <v>11</v>
       </c>
       <c r="D445" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>832</v>
+        <v>582</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>833</v>
+        <v>51</v>
       </c>
       <c r="G445" s="9">
-        <v>46304.0</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="446">
@@ -13945,21 +13945,21 @@
         <v>11</v>
       </c>
       <c r="D446" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>582</v>
+        <v>835</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>51</v>
+        <v>359</v>
       </c>
       <c r="G446" s="9">
-        <v>46416.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>32</v>
@@ -13968,56 +13968,56 @@
         <v>11</v>
       </c>
       <c r="D447" s="2">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="G447" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>37</v>
+        <v>663</v>
       </c>
       <c r="G448" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D449" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E449" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="B449" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C449" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D449" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E449" s="2" t="s">
-        <v>840</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>663</v>
@@ -14037,16 +14037,16 @@
         <v>25</v>
       </c>
       <c r="D450" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>840</v>
+        <v>544</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>663</v>
       </c>
       <c r="G450" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="451">
@@ -14057,47 +14057,47 @@
         <v>112</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D451" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>544</v>
+        <v>729</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>663</v>
+        <v>843</v>
       </c>
       <c r="G451" s="9">
-        <v>46484.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D452" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>729</v>
+        <v>845</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>844</v>
+        <v>579</v>
       </c>
       <c r="G452" s="9">
-        <v>46792.0</v>
+        <v>46676.0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>32</v>
@@ -14109,36 +14109,36 @@
         <v>9.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="F453" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="G453" s="9">
-        <v>46676.0</v>
-      </c>
+        <v>813</v>
+      </c>
+      <c r="F453" s="4"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
         <v>847</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F454" s="4"/>
+        <v>848</v>
+      </c>
+      <c r="F454" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="G454" s="9">
+        <v>46641.0</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>112</v>
@@ -14147,21 +14147,21 @@
         <v>11</v>
       </c>
       <c r="D455" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F455" s="3" t="s">
         <v>707</v>
       </c>
       <c r="G455" s="9">
-        <v>46641.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>112</v>
@@ -14170,44 +14170,47 @@
         <v>11</v>
       </c>
       <c r="D456" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>707</v>
+        <v>663</v>
       </c>
       <c r="G456" s="9">
-        <v>46530.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D457" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>663</v>
+        <v>707</v>
       </c>
       <c r="G457" s="9">
-        <v>46949.0</v>
+        <v>46523.0</v>
+      </c>
+      <c r="H457" s="2" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>112</v>
@@ -14216,19 +14219,16 @@
         <v>25</v>
       </c>
       <c r="D458" s="2">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>855</v>
+        <v>831</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>707</v>
+        <v>579</v>
       </c>
       <c r="G458" s="9">
-        <v>46523.0</v>
-      </c>
-      <c r="H458" s="2" t="s">
-        <v>856</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="459">
@@ -14245,13 +14245,13 @@
         <v>3.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G459" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="460">
@@ -14268,7 +14268,7 @@
         <v>3.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>449</v>
@@ -14282,7 +14282,7 @@
         <v>859</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>25</v>
@@ -14291,13 +14291,13 @@
         <v>3.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>449</v>
+        <v>579</v>
       </c>
       <c r="G461" s="9">
-        <v>46752.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="462">
@@ -14314,13 +14314,13 @@
         <v>3.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G462" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="463">
@@ -14337,13 +14337,13 @@
         <v>3.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>449</v>
+        <v>45</v>
       </c>
       <c r="G463" s="9">
-        <v>46752.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="464">
@@ -14351,22 +14351,19 @@
         <v>862</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D464" s="2">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>832</v>
+        <v>578</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G464" s="9">
-        <v>46366.0</v>
+        <v>668</v>
       </c>
     </row>
     <row r="465">
@@ -14374,68 +14371,71 @@
         <v>863</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C465" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D465" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>668</v>
+        <v>864</v>
+      </c>
+      <c r="G465" s="9">
+        <v>46670.0</v>
+      </c>
+      <c r="H465" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D466" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>572</v>
+        <v>866</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>865</v>
+        <v>95</v>
       </c>
       <c r="G466" s="9">
-        <v>46670.0</v>
-      </c>
-      <c r="H466" s="2" t="s">
-        <v>52</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D467" s="2">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>867</v>
+        <v>573</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="G467" s="9">
-        <v>46725.0</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="468">
@@ -14452,18 +14452,18 @@
         <v>22.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>573</v>
+        <v>869</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="G468" s="9">
-        <v>46556.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>112</v>
@@ -14475,41 +14475,42 @@
         <v>22.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>142</v>
+        <v>872</v>
       </c>
       <c r="G469" s="9">
-        <v>46793.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D470" s="2">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>873</v>
+        <v>606</v>
       </c>
       <c r="G470" s="9">
-        <v>46670.0</v>
-      </c>
+        <v>46254.0</v>
+      </c>
+      <c r="H470" s="2"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>32</v>
@@ -14518,37 +14519,36 @@
         <v>11</v>
       </c>
       <c r="D471" s="2">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>606</v>
+        <v>405</v>
       </c>
       <c r="G471" s="9">
-        <v>46254.0</v>
-      </c>
-      <c r="H471" s="2"/>
+        <v>46669.0</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D472" s="2">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>405</v>
+        <v>879</v>
       </c>
       <c r="G472" s="9">
         <v>46669.0</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>32</v>
@@ -14568,10 +14568,10 @@
         <v>6.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="G473" s="9">
         <v>46669.0</v>
@@ -14579,7 +14579,7 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>32</v>
@@ -14591,10 +14591,10 @@
         <v>6.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>883</v>
+        <v>811</v>
       </c>
       <c r="G474" s="9">
         <v>46669.0</v>
@@ -14614,10 +14614,10 @@
         <v>6.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>812</v>
+        <v>885</v>
       </c>
       <c r="G475" s="9">
         <v>46669.0</v>
@@ -14625,30 +14625,30 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D476" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G476" s="9">
-        <v>46669.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>32</v>
@@ -14660,13 +14660,13 @@
         <v>18.0</v>
       </c>
       <c r="E477" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F477" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="F477" s="3" t="s">
-        <v>889</v>
-      </c>
       <c r="G477" s="9">
-        <v>46947.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="478">
@@ -14683,10 +14683,10 @@
         <v>18.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>601</v>
+        <v>66</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G478" s="9">
         <v>46949.0</v>
@@ -14706,13 +14706,10 @@
         <v>18.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>66</v>
+        <v>831</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="G479" s="9">
-        <v>46949.0</v>
+        <v>888</v>
       </c>
     </row>
     <row r="480">
@@ -14726,13 +14723,16 @@
         <v>27</v>
       </c>
       <c r="D480" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>889</v>
+        <v>43</v>
+      </c>
+      <c r="G480" s="9">
+        <v>46730.0</v>
       </c>
     </row>
     <row r="481">
@@ -14743,39 +14743,36 @@
         <v>32</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D481" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>832</v>
+        <v>894</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G481" s="9">
-        <v>46730.0</v>
+        <v>346</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C482" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D482" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E482" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B482" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C482" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D482" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E482" s="2" t="s">
-        <v>895</v>
-      </c>
       <c r="F482" s="3" t="s">
-        <v>346</v>
+        <v>118</v>
       </c>
     </row>
     <row r="483">
@@ -14786,87 +14783,93 @@
         <v>32</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D483" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>118</v>
+        <v>441</v>
+      </c>
+      <c r="G483" s="9">
+        <v>46267.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D484" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>441</v>
+        <v>760</v>
       </c>
       <c r="G484" s="9">
-        <v>46267.0</v>
+        <v>46250.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D485" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="F485" s="3">
-        <v>11505.0</v>
+        <v>901</v>
+      </c>
+      <c r="F485" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G485" s="9">
+        <v>46255.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>760</v>
+        <v>470</v>
       </c>
       <c r="G486" s="9">
-        <v>46250.0</v>
+        <v>46613.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>32</v>
@@ -14875,16 +14878,16 @@
         <v>11</v>
       </c>
       <c r="D487" s="2">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>904</v>
+        <v>607</v>
       </c>
       <c r="F487" s="3" t="s">
-        <v>359</v>
+        <v>608</v>
       </c>
       <c r="G487" s="9">
-        <v>46255.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="488">
@@ -14892,22 +14895,22 @@
         <v>905</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C488" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2">
-        <v>21.0</v>
+        <v>7.0</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>906</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="G488" s="9">
-        <v>46613.0</v>
+        <v>46691.0</v>
       </c>
     </row>
     <row r="489">
@@ -14921,16 +14924,16 @@
         <v>11</v>
       </c>
       <c r="D489" s="2">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>607</v>
+        <v>906</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>608</v>
+        <v>888</v>
       </c>
       <c r="G489" s="9">
-        <v>46669.0</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="490">
@@ -14941,20 +14944,15 @@
         <v>32</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D490" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="F490" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G490" s="9">
-        <v>46691.0</v>
-      </c>
+      <c r="F490" s="4"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
@@ -14964,24 +14962,19 @@
         <v>32</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D491" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="F491" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="G491" s="9">
-        <v>46775.0</v>
-      </c>
+        <v>911</v>
+      </c>
+      <c r="F491" s="4"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>32</v>
@@ -14993,13 +14986,13 @@
         <v>11.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F492" s="4"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>32</v>
@@ -15011,95 +15004,95 @@
         <v>11.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F493" s="4"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D494" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="F494" s="4"/>
+        <v>917</v>
+      </c>
+      <c r="F494" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="G494" s="9">
+        <v>46803.0</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D495" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="F495" s="4"/>
+        <v>874</v>
+      </c>
+      <c r="F495" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="G495" s="9">
+        <v>46222.0</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D496" s="2">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="F496" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="G496" s="9">
-        <v>46803.0</v>
-      </c>
+        <v>922</v>
+      </c>
+      <c r="F496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D497" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="F497" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="G497" s="9">
-        <v>46222.0</v>
-      </c>
+        <v>924</v>
+      </c>
+      <c r="F497" s="4"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>32</v>
@@ -15111,13 +15104,13 @@
         <v>11.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F498" s="4"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>32</v>
@@ -15129,49 +15122,55 @@
         <v>11.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F499" s="4"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D500" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F500" s="4"/>
+      <c r="G500" s="9">
+        <v>46564.0</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D501" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F501" s="4"/>
+      <c r="G501" s="9">
+        <v>46551.0</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -15183,16 +15182,16 @@
         <v>14.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F502" s="4"/>
       <c r="G502" s="9">
-        <v>46564.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>32</v>
@@ -15201,19 +15200,19 @@
         <v>25</v>
       </c>
       <c r="D503" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F503" s="4"/>
       <c r="G503" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>32</v>
@@ -15222,19 +15221,19 @@
         <v>25</v>
       </c>
       <c r="D504" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F504" s="4"/>
       <c r="G504" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>32</v>
@@ -15246,16 +15245,16 @@
         <v>15.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F505" s="4"/>
       <c r="G505" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>32</v>
@@ -15267,7 +15266,7 @@
         <v>15.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F506" s="4"/>
       <c r="G506" s="9">
@@ -15276,7 +15275,7 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>32</v>
@@ -15285,19 +15284,19 @@
         <v>25</v>
       </c>
       <c r="D507" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F507" s="4"/>
       <c r="G507" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>32</v>
@@ -15306,40 +15305,39 @@
         <v>25</v>
       </c>
       <c r="D508" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F508" s="4"/>
       <c r="G508" s="9">
-        <v>46355.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D509" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="F509" s="4"/>
-      <c r="G509" s="9">
-        <v>46551.0</v>
+        <v>948</v>
+      </c>
+      <c r="F509" s="3" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>32</v>
@@ -15348,80 +15346,85 @@
         <v>25</v>
       </c>
       <c r="D510" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F510" s="4"/>
-      <c r="G510" s="9">
-        <v>46394.0</v>
-      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D511" s="2">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>418</v>
       </c>
+      <c r="G511" s="9">
+        <v>46759.0</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D512" s="2">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="F512" s="4"/>
+        <v>954</v>
+      </c>
+      <c r="F512" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G512" s="9">
+        <v>46406.0</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>32</v>
+        <v>537</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D513" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F513" s="3" t="s">
-        <v>418</v>
+        <v>37</v>
       </c>
       <c r="G513" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>537</v>
@@ -15433,7 +15436,7 @@
         <v>3.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F514" s="3" t="s">
         <v>37</v>
@@ -15444,7 +15447,7 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>537</v>
@@ -15456,7 +15459,7 @@
         <v>3.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F515" s="3" t="s">
         <v>37</v>
@@ -15467,7 +15470,7 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>537</v>
@@ -15479,10 +15482,10 @@
         <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G516" s="9">
         <v>46406.0</v>
@@ -15508,7 +15511,7 @@
         <v>37</v>
       </c>
       <c r="G517" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="518">
@@ -15525,18 +15528,18 @@
         <v>3.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G518" s="9">
-        <v>46406.0</v>
+        <v>46258.0</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>537</v>
@@ -15548,18 +15551,18 @@
         <v>3.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G519" s="9">
-        <v>46251.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>537</v>
@@ -15568,21 +15571,21 @@
         <v>11</v>
       </c>
       <c r="D520" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F520" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G520" s="9">
-        <v>46258.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>537</v>
@@ -15591,21 +15594,21 @@
         <v>11</v>
       </c>
       <c r="D521" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G521" s="9">
-        <v>46254.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>537</v>
@@ -15617,7 +15620,7 @@
         <v>4.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>37</v>
@@ -15628,7 +15631,7 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>537</v>
@@ -15640,7 +15643,7 @@
         <v>4.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>37</v>
@@ -15651,7 +15654,7 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>537</v>
@@ -15660,21 +15663,21 @@
         <v>11</v>
       </c>
       <c r="D524" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G524" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>537</v>
@@ -15683,21 +15686,21 @@
         <v>11</v>
       </c>
       <c r="D525" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G525" s="9">
-        <v>46387.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>537</v>
@@ -15709,18 +15712,18 @@
         <v>6.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G526" s="9">
-        <v>46251.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>537</v>
@@ -15732,18 +15735,18 @@
         <v>6.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G527" s="9">
-        <v>46280.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>537</v>
@@ -15755,18 +15758,18 @@
         <v>6.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F528" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G528" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>537</v>
@@ -15778,7 +15781,7 @@
         <v>6.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F529" s="3" t="s">
         <v>37</v>
@@ -15789,7 +15792,7 @@
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>537</v>
@@ -15801,18 +15804,18 @@
         <v>6.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F530" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G530" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>537</v>
@@ -15821,21 +15824,21 @@
         <v>11</v>
       </c>
       <c r="D531" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F531" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G531" s="9">
-        <v>46256.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>537</v>
@@ -15844,21 +15847,21 @@
         <v>11</v>
       </c>
       <c r="D532" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F532" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G532" s="9">
-        <v>46249.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>537</v>
@@ -15870,18 +15873,18 @@
         <v>7.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F533" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G533" s="9">
-        <v>46352.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>537</v>
@@ -15890,21 +15893,21 @@
         <v>11</v>
       </c>
       <c r="D534" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F534" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G534" s="9">
-        <v>46333.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>537</v>
@@ -15913,21 +15916,21 @@
         <v>11</v>
       </c>
       <c r="D535" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F535" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G535" s="9">
-        <v>46244.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>537</v>
@@ -15939,18 +15942,18 @@
         <v>8.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F536" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G536" s="9">
-        <v>46226.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>537</v>
@@ -15962,18 +15965,18 @@
         <v>8.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F537" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G537" s="9">
-        <v>46222.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>537</v>
@@ -15985,18 +15988,18 @@
         <v>8.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G538" s="9">
-        <v>46241.0</v>
+        <v>46319.0</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>537</v>
@@ -16005,21 +16008,21 @@
         <v>11</v>
       </c>
       <c r="D539" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G539" s="9">
-        <v>46305.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>537</v>
@@ -16028,16 +16031,16 @@
         <v>11</v>
       </c>
       <c r="D540" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G540" s="9">
-        <v>46319.0</v>
+        <v>46321.0</v>
       </c>
     </row>
     <row r="541">
@@ -16051,21 +16054,24 @@
         <v>11</v>
       </c>
       <c r="D541" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>1010</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="G541" s="9">
-        <v>46365.0</v>
+        <v>46426.0</v>
+      </c>
+      <c r="H541" s="2" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>537</v>
@@ -16074,21 +16080,21 @@
         <v>11</v>
       </c>
       <c r="D542" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G542" s="9">
-        <v>46321.0</v>
+        <v>46211.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>537</v>
@@ -16100,21 +16106,18 @@
         <v>10.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G543" s="9">
-        <v>46426.0</v>
-      </c>
-      <c r="H543" s="2" t="s">
-        <v>1014</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>537</v>
@@ -16126,18 +16129,18 @@
         <v>10.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G544" s="9">
-        <v>46211.0</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>537</v>
@@ -16146,21 +16149,21 @@
         <v>11</v>
       </c>
       <c r="D545" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F545" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G545" s="9">
-        <v>46204.0</v>
+        <v>46392.0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>537</v>
@@ -16169,21 +16172,21 @@
         <v>11</v>
       </c>
       <c r="D546" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="G546" s="9">
-        <v>46345.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>537</v>
@@ -16192,21 +16195,22 @@
         <v>11</v>
       </c>
       <c r="D547" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F547" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>1023</v>
+      </c>
+      <c r="F547" s="4"/>
       <c r="G547" s="9">
-        <v>46392.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I547" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>537</v>
@@ -16215,21 +16219,22 @@
         <v>11</v>
       </c>
       <c r="D548" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F548" s="3" t="s">
-        <v>493</v>
-      </c>
+        <v>1025</v>
+      </c>
+      <c r="F548" s="4"/>
       <c r="G548" s="9">
-        <v>46366.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I548" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>537</v>
@@ -16241,19 +16246,16 @@
         <v>14.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F549" s="4"/>
       <c r="G549" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I549" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>537</v>
@@ -16265,19 +16267,16 @@
         <v>14.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F550" s="4"/>
       <c r="G550" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I550" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>537</v>
@@ -16286,19 +16285,18 @@
         <v>11</v>
       </c>
       <c r="D551" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F551" s="4"/>
-      <c r="G551" s="9">
-        <v>46220.0</v>
+        <v>1031</v>
+      </c>
+      <c r="F551" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>537</v>
@@ -16307,22 +16305,21 @@
         <v>11</v>
       </c>
       <c r="D552" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F552" s="4"/>
-      <c r="G552" s="9">
-        <v>46220.0</v>
+        <v>1033</v>
+      </c>
+      <c r="F552" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>11</v>
@@ -16331,10 +16328,13 @@
         <v>1.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="F553" s="3" t="s">
         <v>157</v>
+      </c>
+      <c r="G553" s="9">
+        <v>46223.0</v>
       </c>
     </row>
     <row r="554">
@@ -16342,7 +16342,7 @@
         <v>1035</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>11</v>
@@ -16355,6 +16355,9 @@
       </c>
       <c r="F554" s="3" t="s">
         <v>157</v>
+      </c>
+      <c r="G554" s="9">
+        <v>46228.0</v>
       </c>
     </row>
     <row r="555">
@@ -16368,21 +16371,21 @@
         <v>11</v>
       </c>
       <c r="D555" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>157</v>
+        <v>626</v>
       </c>
       <c r="G555" s="9">
-        <v>46223.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>535</v>
@@ -16391,21 +16394,21 @@
         <v>11</v>
       </c>
       <c r="D556" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>157</v>
+        <v>631</v>
       </c>
       <c r="G556" s="9">
-        <v>46228.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>535</v>
@@ -16414,21 +16417,21 @@
         <v>11</v>
       </c>
       <c r="D557" s="2">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="G557" s="9">
-        <v>46269.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>535</v>
@@ -16437,44 +16440,47 @@
         <v>11</v>
       </c>
       <c r="D558" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>631</v>
+        <v>399</v>
       </c>
       <c r="G558" s="9">
-        <v>46240.0</v>
+        <v>46274.0</v>
+      </c>
+      <c r="H558" s="2" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D559" s="2">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>631</v>
+        <v>1047</v>
       </c>
       <c r="G559" s="9">
-        <v>46242.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>535</v>
@@ -16483,65 +16489,57 @@
         <v>11</v>
       </c>
       <c r="D560" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>399</v>
+        <v>1050</v>
       </c>
       <c r="G560" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H560" s="2" t="s">
-        <v>714</v>
+        <v>46207.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D561" s="2">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F561" s="3" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G561" s="9">
-        <v>46743.0</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="F561" s="4"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C562" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D562" s="2">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>1053</v>
+        <v>227</v>
       </c>
       <c r="G562" s="9">
-        <v>46207.0</v>
+        <v>46295.0</v>
       </c>
     </row>
     <row r="563">
@@ -16549,47 +16547,50 @@
         <v>1054</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D563" s="2">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>1055</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>1056</v>
+        <v>399</v>
+      </c>
+      <c r="G563" s="9">
+        <v>46769.0</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D564" s="2">
-        <v>22.0</v>
+        <v>6.0</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>1055</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>1056</v>
+        <v>399</v>
       </c>
       <c r="G564" s="9">
-        <v>46516.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>535</v>
@@ -16598,34 +16599,39 @@
         <v>11</v>
       </c>
       <c r="D565" s="2">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F565" s="4"/>
+        <v>1058</v>
+      </c>
+      <c r="F565" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="G565" s="9">
+        <v>46261.0</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
         <v>1059</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D566" s="2">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>1060</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>227</v>
+        <v>627</v>
       </c>
       <c r="G566" s="9">
-        <v>46295.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="567">
@@ -16633,22 +16639,22 @@
         <v>1061</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D567" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>1062</v>
       </c>
       <c r="F567" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G567" s="9">
-        <v>46769.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="568">
@@ -16656,27 +16662,27 @@
         <v>1063</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D568" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G568" s="9">
-        <v>46769.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>535</v>
@@ -16688,18 +16694,18 @@
         <v>3.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F569" s="3" t="s">
         <v>627</v>
       </c>
       <c r="G569" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>535</v>
@@ -16711,7 +16717,7 @@
         <v>3.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F570" s="3" t="s">
         <v>627</v>
@@ -16722,10 +16728,10 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C571" s="2" t="s">
         <v>11</v>
@@ -16734,82 +16740,82 @@
         <v>3.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>627</v>
+        <v>399</v>
       </c>
       <c r="G571" s="9">
-        <v>46266.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D572" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1071</v>
+        <v>716</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>627</v>
+        <v>1072</v>
       </c>
       <c r="G572" s="9">
-        <v>46223.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D573" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E573" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F573" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="B573" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="C573" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D573" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E573" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F573" s="3" t="s">
-        <v>627</v>
-      </c>
       <c r="G573" s="9">
-        <v>46266.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D574" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1075</v>
+        <v>712</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>627</v>
+        <v>1072</v>
       </c>
       <c r="G574" s="9">
-        <v>46261.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="575">
@@ -16817,68 +16823,68 @@
         <v>1076</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D575" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1077</v>
+        <v>601</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>399</v>
+        <v>1072</v>
       </c>
       <c r="G575" s="9">
-        <v>46769.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D576" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>716</v>
+        <v>894</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G576" s="9">
-        <v>46814.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C577" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D577" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E577" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F577" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="F577" s="3" t="s">
-        <v>1079</v>
-      </c>
       <c r="G577" s="9">
-        <v>46820.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="578">
@@ -16886,50 +16892,50 @@
         <v>1082</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C578" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D578" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>712</v>
+        <v>1083</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
       <c r="G578" s="9">
-        <v>46820.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D579" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>601</v>
+        <v>1086</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1079</v>
+        <v>458</v>
       </c>
       <c r="G579" s="9">
-        <v>46998.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>32</v>
@@ -16941,18 +16947,16 @@
         <v>2.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>895</v>
+        <v>1088</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1085</v>
-      </c>
-      <c r="G580" s="9">
-        <v>46484.0</v>
-      </c>
+        <v>1089</v>
+      </c>
+      <c r="G580" s="9"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>32</v>
@@ -16964,18 +16968,15 @@
         <v>2.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G581" s="9">
-        <v>46432.0</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>32</v>
@@ -16987,18 +16988,15 @@
         <v>2.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1090</v>
+        <v>878</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G582" s="9">
-        <v>46877.0</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>32</v>
@@ -17010,13 +17008,10 @@
         <v>2.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1093</v>
+        <v>584</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G583" s="9">
-        <v>46704.0</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="584">
@@ -17033,16 +17028,15 @@
         <v>2.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G584" s="9"/>
+        <v>1089</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>32</v>
@@ -17054,15 +17048,15 @@
         <v>2.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>32</v>
@@ -17074,98 +17068,108 @@
         <v>2.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>879</v>
+        <v>1098</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>1096</v>
+        <v>593</v>
+      </c>
+      <c r="G586" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C587" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D587" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E587" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B587" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C587" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D587" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E587" s="2" t="s">
-        <v>584</v>
-      </c>
       <c r="F587" s="3" t="s">
-        <v>1096</v>
+        <v>1101</v>
+      </c>
+      <c r="G587" s="9">
+        <v>46877.0</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D588" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E588" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F588" s="3" t="s">
         <v>1101</v>
       </c>
-      <c r="B588" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C588" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D588" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E588" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F588" s="3" t="s">
-        <v>1096</v>
+      <c r="G588" s="9">
+        <v>46641.0</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D589" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1096</v>
+        <v>1101</v>
+      </c>
+      <c r="G589" s="9">
+        <v>46743.0</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D590" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F590" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="G590" s="9">
-        <v>46766.0</v>
+        <v>1106</v>
+      </c>
+      <c r="F590" s="4"/>
+      <c r="H590" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>112</v>
@@ -17174,16 +17178,19 @@
         <v>11</v>
       </c>
       <c r="D591" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1107</v>
+        <v>752</v>
       </c>
       <c r="F591" s="3" t="s">
         <v>1108</v>
       </c>
       <c r="G591" s="9">
-        <v>46877.0</v>
+        <v>46663.0</v>
+      </c>
+      <c r="H591" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="592">
@@ -17191,27 +17198,30 @@
         <v>1109</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D592" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>849</v>
+        <v>582</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="G592" s="9">
-        <v>46641.0</v>
+        <v>46437.0</v>
+      </c>
+      <c r="H592" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>112</v>
@@ -17220,21 +17230,21 @@
         <v>11</v>
       </c>
       <c r="D593" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G593" s="9">
-        <v>46743.0</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>112</v>
@@ -17243,14 +17253,16 @@
         <v>11</v>
       </c>
       <c r="D594" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F594" s="4"/>
-      <c r="H594" s="2" t="s">
-        <v>133</v>
+        <v>661</v>
+      </c>
+      <c r="F594" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G594" s="9">
+        <v>46530.0</v>
       </c>
     </row>
     <row r="595">
@@ -17264,19 +17276,16 @@
         <v>11</v>
       </c>
       <c r="D595" s="2">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>752</v>
+        <v>1115</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>1115</v>
+        <v>1101</v>
       </c>
       <c r="G595" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H595" s="2" t="s">
-        <v>133</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="596">
@@ -17284,25 +17293,22 @@
         <v>1116</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D596" s="2">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>582</v>
+        <v>1117</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>1117</v>
+        <v>1101</v>
       </c>
       <c r="G596" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H596" s="2" t="s">
-        <v>133</v>
+        <v>46834.0</v>
       </c>
     </row>
     <row r="597">
@@ -17313,19 +17319,19 @@
         <v>112</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D597" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E597" s="2" t="s">
         <v>1119</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G597" s="9">
-        <v>46775.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="598">
@@ -17336,70 +17342,70 @@
         <v>112</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D598" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>661</v>
+        <v>1121</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G598" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D599" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G599" s="9">
-        <v>46530.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D600" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G600" s="9">
-        <v>46834.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>112</v>
@@ -17411,18 +17417,18 @@
         <v>14.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G601" s="9">
-        <v>46481.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>112</v>
@@ -17434,18 +17440,18 @@
         <v>14.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G602" s="9">
-        <v>46877.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>112</v>
@@ -17457,10 +17463,10 @@
         <v>14.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G603" s="9">
         <v>46872.0</v>
@@ -17468,7 +17474,7 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>112</v>
@@ -17480,36 +17486,36 @@
         <v>14.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G604" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D605" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1134</v>
+        <v>848</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G605" s="9">
-        <v>46734.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="606">
@@ -17517,22 +17523,22 @@
         <v>1135</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D606" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>1136</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>1108</v>
+        <v>399</v>
       </c>
       <c r="G606" s="9">
-        <v>46481.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="607">
@@ -17540,22 +17546,22 @@
         <v>1137</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D607" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>1138</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>1108</v>
+        <v>399</v>
       </c>
       <c r="G607" s="9">
-        <v>46872.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="608">
@@ -17563,68 +17569,64 @@
         <v>1139</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>112</v>
+        <v>535</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D608" s="2">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1140</v>
+        <v>655</v>
       </c>
       <c r="F608" s="3" t="s">
-        <v>1108</v>
+        <v>399</v>
       </c>
       <c r="G608" s="9">
-        <v>46877.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D609" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E609" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="B609" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C609" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D609" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E609" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F609" s="3" t="s">
-        <v>1108</v>
-      </c>
-      <c r="G609" s="9">
-        <v>46641.0</v>
-      </c>
+      <c r="F609" s="3"/>
+      <c r="G609" s="9"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
         <v>1142</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D610" s="2">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>1143</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>399</v>
+        <v>224</v>
       </c>
       <c r="G610" s="9">
-        <v>46274.0</v>
+        <v>46437.0</v>
       </c>
     </row>
     <row r="611">
@@ -17632,109 +17634,67 @@
         <v>1144</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D611" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>1145</v>
       </c>
       <c r="F611" s="3" t="s">
-        <v>399</v>
+        <v>1146</v>
       </c>
       <c r="G611" s="9">
-        <v>46274.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D612" s="2">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="F612" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G612" s="9">
-        <v>46274.0</v>
+        <v>1148</v>
+      </c>
+      <c r="F612" s="3"/>
+      <c r="G612" s="9"/>
+      <c r="H612" s="2" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D613" s="2">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="F613" s="3"/>
       <c r="G613" s="9"/>
-    </row>
-    <row r="614">
-      <c r="A614" s="2" t="s">
+      <c r="H613" s="2" t="s">
         <v>1149</v>
       </c>
-      <c r="B614" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D614" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E614" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="F614" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G614" s="9">
-        <v>46437.0</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B615" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D615" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="E615" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="F615" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="G615" s="9"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="1152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="1151">
   <si>
     <t>ID</t>
   </si>
@@ -1534,6 +1534,9 @@
     <t>PRTDL-GO  (牛肉)</t>
   </si>
   <si>
+    <t>1150204K</t>
+  </si>
+  <si>
     <t>ID39835414951409</t>
   </si>
   <si>
@@ -2266,186 +2269,183 @@
     <t>ADHS-4入</t>
   </si>
   <si>
-    <t>ID1777901415357</t>
+    <t>ID1778041215011</t>
+  </si>
+  <si>
+    <t>1140425K</t>
+  </si>
+  <si>
+    <t>ID1778057927574</t>
+  </si>
+  <si>
+    <t>M67CFT-ST</t>
+  </si>
+  <si>
+    <t>24#5</t>
+  </si>
+  <si>
+    <t>ID1778057982808</t>
+  </si>
+  <si>
+    <t>M45SRL-ST</t>
+  </si>
+  <si>
+    <t>24#7</t>
+  </si>
+  <si>
+    <t>ID1778139472526</t>
+  </si>
+  <si>
+    <t>1150429K</t>
+  </si>
+  <si>
+    <t>ID1778197333009</t>
+  </si>
+  <si>
+    <t>BRD210</t>
+  </si>
+  <si>
+    <t>ID1778197382076</t>
+  </si>
+  <si>
+    <t>ID1778197425080</t>
+  </si>
+  <si>
+    <t>ID1778197500800</t>
+  </si>
+  <si>
+    <t>CE500</t>
+  </si>
+  <si>
+    <t>ID1778197520009</t>
+  </si>
+  <si>
+    <t>BE250</t>
+  </si>
+  <si>
+    <t>ID1778227773246</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY</t>
+  </si>
+  <si>
+    <t>1140528K</t>
+  </si>
+  <si>
+    <t>ID1778227799248</t>
+  </si>
+  <si>
+    <t>1140502K</t>
+  </si>
+  <si>
+    <t>ID1778229685758</t>
+  </si>
+  <si>
+    <t>ID1778229748526</t>
+  </si>
+  <si>
+    <t>ID1778229862985</t>
+  </si>
+  <si>
+    <t>CKM-KR</t>
+  </si>
+  <si>
+    <t>ID1778229913502</t>
+  </si>
+  <si>
+    <t>CKC2</t>
+  </si>
+  <si>
+    <t>ID1778229996243</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230020559</t>
+  </si>
+  <si>
+    <t>ACSRMB-TY-對切</t>
+  </si>
+  <si>
+    <t>ID1778230078956</t>
+  </si>
+  <si>
+    <t>PRSRMB-GO-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230144397</t>
+  </si>
+  <si>
+    <t>CHSRMB-YK-2.5cm</t>
+  </si>
+  <si>
+    <t>ID1778230200332</t>
+  </si>
+  <si>
+    <t>PRRER-340-380-YK</t>
+  </si>
+  <si>
+    <t>1150507S</t>
+  </si>
+  <si>
+    <t>ID1778231168084</t>
+  </si>
+  <si>
+    <t>JUP (8月-10月)</t>
+  </si>
+  <si>
+    <t>ID1778231224509</t>
+  </si>
+  <si>
+    <t>JUP (1月 3月)</t>
+  </si>
+  <si>
+    <t>ID1778231253827</t>
+  </si>
+  <si>
+    <t>JUP (2月 4月 5月)</t>
+  </si>
+  <si>
+    <t>ID1778231360305</t>
+  </si>
+  <si>
+    <t>JUP (6月 7月)</t>
+  </si>
+  <si>
+    <t>ID1778232035767</t>
+  </si>
+  <si>
+    <t>PSSTL-5cm</t>
+  </si>
+  <si>
+    <t>ID1778464113039</t>
+  </si>
+  <si>
+    <t>LR28</t>
+  </si>
+  <si>
+    <t>[NEW]</t>
+  </si>
+  <si>
+    <t>ID1778464134245</t>
+  </si>
+  <si>
+    <t>LR26</t>
+  </si>
+  <si>
+    <t>ID1778464166470</t>
+  </si>
+  <si>
+    <t>LHS</t>
+  </si>
+  <si>
+    <t>ID1778464235655</t>
   </si>
   <si>
     <t>CHTDL-YK</t>
   </si>
   <si>
-    <t>ID1778041215011</t>
-  </si>
-  <si>
-    <t>1140425K</t>
-  </si>
-  <si>
-    <t>ID1778057927574</t>
-  </si>
-  <si>
-    <t>M67CFT-ST</t>
-  </si>
-  <si>
-    <t>24#5</t>
-  </si>
-  <si>
-    <t>ID1778057982808</t>
-  </si>
-  <si>
-    <t>M45SRL-ST</t>
-  </si>
-  <si>
-    <t>24#7</t>
-  </si>
-  <si>
-    <t>ID1778139472526</t>
-  </si>
-  <si>
-    <t>1150429K</t>
-  </si>
-  <si>
-    <t>ID1778197333009</t>
-  </si>
-  <si>
-    <t>BRD210</t>
-  </si>
-  <si>
-    <t>ID1778197382076</t>
-  </si>
-  <si>
-    <t>ID1778197425080</t>
-  </si>
-  <si>
-    <t>ID1778197500800</t>
-  </si>
-  <si>
-    <t>CE500</t>
-  </si>
-  <si>
-    <t>ID1778197520009</t>
-  </si>
-  <si>
-    <t>BE250</t>
-  </si>
-  <si>
-    <t>ID1778227773246</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY</t>
-  </si>
-  <si>
-    <t>1140528K</t>
-  </si>
-  <si>
-    <t>ID1778227799248</t>
-  </si>
-  <si>
-    <t>1140502K</t>
-  </si>
-  <si>
-    <t>ID1778229685758</t>
-  </si>
-  <si>
-    <t>ID1778229748526</t>
-  </si>
-  <si>
-    <t>ID1778229862985</t>
-  </si>
-  <si>
-    <t>CKM-KR</t>
-  </si>
-  <si>
-    <t>ID1778229913502</t>
-  </si>
-  <si>
-    <t>CKC2</t>
-  </si>
-  <si>
-    <t>ID1778229996243</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230020559</t>
-  </si>
-  <si>
-    <t>ACSRMB-TY-對切</t>
-  </si>
-  <si>
-    <t>ID1778230078956</t>
-  </si>
-  <si>
-    <t>PRSRMB-GO-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230144397</t>
-  </si>
-  <si>
-    <t>CHSRMB-YK-2.5cm</t>
-  </si>
-  <si>
-    <t>ID1778230200332</t>
-  </si>
-  <si>
-    <t>PRRER-340-380-YK</t>
-  </si>
-  <si>
-    <t>1150507S</t>
-  </si>
-  <si>
-    <t>ID1778231168084</t>
-  </si>
-  <si>
-    <t>JUP (8月-10月)</t>
-  </si>
-  <si>
-    <t>ID1778231224509</t>
-  </si>
-  <si>
-    <t>JUP (1月 3月)</t>
-  </si>
-  <si>
-    <t>ID1778231253827</t>
-  </si>
-  <si>
-    <t>JUP (2月 4月 5月)</t>
-  </si>
-  <si>
-    <t>ID1778231360305</t>
-  </si>
-  <si>
-    <t>JUP (6月 7月)</t>
-  </si>
-  <si>
-    <t>ID1778232035767</t>
-  </si>
-  <si>
-    <t>PSSTL-5cm</t>
-  </si>
-  <si>
-    <t>ID1778464113039</t>
-  </si>
-  <si>
-    <t>LR28</t>
-  </si>
-  <si>
-    <t>[NEW]</t>
-  </si>
-  <si>
-    <t>ID1778464134245</t>
-  </si>
-  <si>
-    <t>LR26</t>
-  </si>
-  <si>
-    <t>ID1778464166470</t>
-  </si>
-  <si>
-    <t>LHS</t>
-  </si>
-  <si>
-    <t>ID1778464235655</t>
-  </si>
-  <si>
     <t>1141224K</t>
   </si>
   <si>
@@ -2572,15 +2572,6 @@
     <t>PRRER-對切-GO</t>
   </si>
   <si>
-    <t>ID1778722895097</t>
-  </si>
-  <si>
-    <t>PRRER-260-300-YK</t>
-  </si>
-  <si>
-    <t>走道</t>
-  </si>
-  <si>
     <t>ID1778725820187</t>
   </si>
   <si>
@@ -3361,12 +3352,6 @@
     <t>GMB(骨)</t>
   </si>
   <si>
-    <t>ID1779952979939</t>
-  </si>
-  <si>
-    <t>M45OB-切3CM</t>
-  </si>
-  <si>
     <t>ID1779953032414</t>
   </si>
   <si>
@@ -3385,12 +3370,6 @@
     <t>M45BBLD-1.5cm-KR</t>
   </si>
   <si>
-    <t>ID1779953130180</t>
-  </si>
-  <si>
-    <t>PRSRL-230-270-GO</t>
-  </si>
-  <si>
     <t>ID1779953153190</t>
   </si>
   <si>
@@ -3466,7 +3445,25 @@
     <t>ID1780287319374</t>
   </si>
   <si>
-    <t>W(A5)</t>
+    <t>W</t>
+  </si>
+  <si>
+    <t>ID1780352747610</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>ID1780368496154</t>
+  </si>
+  <si>
+    <t>BJURM</t>
+  </si>
+  <si>
+    <t>ID1780368863464</t>
+  </si>
+  <si>
+    <t>PRSRM</t>
   </si>
 </sst>
 </file>
@@ -8941,13 +8938,17 @@
       <c r="E222" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="F222" s="14"/>
-      <c r="G222" s="12"/>
+      <c r="F222" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="G222" s="18">
+        <v>46949.0</v>
+      </c>
       <c r="H222" s="11"/>
     </row>
     <row r="223">
       <c r="A223" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>112</v>
@@ -8959,7 +8960,7 @@
         <v>19.0</v>
       </c>
       <c r="E223" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>224</v>
@@ -8971,7 +8972,7 @@
     </row>
     <row r="224">
       <c r="A224" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>112</v>
@@ -8983,7 +8984,7 @@
         <v>19.0</v>
       </c>
       <c r="E224" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F224" s="17" t="s">
         <v>16</v>
@@ -8995,7 +8996,7 @@
     </row>
     <row r="225">
       <c r="A225" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>112</v>
@@ -9007,7 +9008,7 @@
         <v>18.0</v>
       </c>
       <c r="E225" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F225" s="17" t="s">
         <v>272</v>
@@ -9019,7 +9020,7 @@
     </row>
     <row r="226">
       <c r="A226" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>112</v>
@@ -9031,19 +9032,19 @@
         <v>17.0</v>
       </c>
       <c r="E226" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F226" s="14"/>
       <c r="G226" s="18">
         <v>46830.0</v>
       </c>
       <c r="H226" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B227" s="11" t="s">
         <v>112</v>
@@ -9055,7 +9056,7 @@
         <v>17.0</v>
       </c>
       <c r="E227" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F227" s="17" t="s">
         <v>148</v>
@@ -9067,7 +9068,7 @@
     </row>
     <row r="228">
       <c r="A228" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>112</v>
@@ -9079,10 +9080,10 @@
         <v>15.0</v>
       </c>
       <c r="E228" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F228" s="17" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G228" s="18">
         <v>46417.0</v>
@@ -9091,7 +9092,7 @@
     </row>
     <row r="229">
       <c r="A229" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B229" s="11" t="s">
         <v>32</v>
@@ -9113,7 +9114,7 @@
     </row>
     <row r="230">
       <c r="A230" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>32</v>
@@ -9135,7 +9136,7 @@
     </row>
     <row r="231">
       <c r="A231" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B231" s="11" t="s">
         <v>32</v>
@@ -9147,7 +9148,7 @@
         <v>13.0</v>
       </c>
       <c r="E231" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F231" s="14"/>
       <c r="G231" s="18">
@@ -9157,7 +9158,7 @@
     </row>
     <row r="232">
       <c r="A232" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>32</v>
@@ -9169,7 +9170,7 @@
         <v>20.0</v>
       </c>
       <c r="E232" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F232" s="14"/>
       <c r="G232" s="12"/>
@@ -9179,7 +9180,7 @@
     </row>
     <row r="233">
       <c r="A233" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B233" s="11" t="s">
         <v>32</v>
@@ -9191,7 +9192,7 @@
         <v>20.0</v>
       </c>
       <c r="E233" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F233" s="17"/>
       <c r="G233" s="12"/>
@@ -9201,7 +9202,7 @@
     </row>
     <row r="234">
       <c r="A234" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B234" s="11" t="s">
         <v>32</v>
@@ -9223,7 +9224,7 @@
     </row>
     <row r="235">
       <c r="A235" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B235" s="11" t="s">
         <v>32</v>
@@ -9245,7 +9246,7 @@
     </row>
     <row r="236">
       <c r="A236" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>32</v>
@@ -9257,7 +9258,7 @@
         <v>2.0</v>
       </c>
       <c r="E236" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F236" s="17" t="s">
         <v>224</v>
@@ -9267,7 +9268,7 @@
     </row>
     <row r="237">
       <c r="A237" s="10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>112</v>
@@ -9279,7 +9280,7 @@
         <v>11.0</v>
       </c>
       <c r="E237" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F237" s="17">
         <v>11503.0</v>
@@ -9292,7 +9293,7 @@
         <v>1.77436324269E12</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>11</v>
@@ -9301,7 +9302,7 @@
         <v>1.0</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>157</v>
@@ -9318,7 +9319,7 @@
         <v>1.774363425608E12</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>11</v>
@@ -9327,11 +9328,11 @@
         <v>1.0</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F239" s="4"/>
       <c r="H239" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="240">
@@ -9339,7 +9340,7 @@
         <v>1.774363487217E12</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>11</v>
@@ -9348,11 +9349,11 @@
         <v>2.0</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F240" s="4"/>
       <c r="H240" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="241">
@@ -9369,10 +9370,10 @@
         <v>15.0</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G241" s="9">
         <v>46873.0</v>
@@ -9393,10 +9394,10 @@
         <v>12.0</v>
       </c>
       <c r="E242" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F242" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="G242" s="9">
         <v>46805.0</v>
@@ -9416,10 +9417,10 @@
         <v>11.0</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G243" s="9">
         <v>46424.0</v>
@@ -9439,10 +9440,10 @@
         <v>13.0</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G244" s="9">
         <v>46432.0</v>
@@ -9463,10 +9464,10 @@
         <v>13.0</v>
       </c>
       <c r="E245" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F245" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>545</v>
       </c>
       <c r="G245" s="9">
         <v>46530.0</v>
@@ -9487,7 +9488,7 @@
         <v>2.0</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F246" s="3">
         <v>11503.0</v>
@@ -9530,7 +9531,7 @@
         <v>5.0</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>16</v>
@@ -9554,7 +9555,7 @@
         <v>4.0</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>224</v>
@@ -9597,7 +9598,7 @@
         <v>21.0</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>16</v>
@@ -9612,13 +9613,13 @@
         <v>112</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D252" s="2">
         <v>15.0</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>476</v>
@@ -9642,10 +9643,10 @@
         <v>8.0</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G253" s="9">
         <v>46516.0</v>
@@ -9665,7 +9666,7 @@
         <v>12.0</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F254" s="3">
         <v>11503.0</v>
@@ -9679,13 +9680,13 @@
         <v>112</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D255" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>238</v>
@@ -9708,10 +9709,10 @@
         <v>12.0</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G256" s="9">
         <v>46395.0</v>
@@ -9732,7 +9733,7 @@
         <v>1.0</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>16</v>
@@ -9752,7 +9753,7 @@
         <v>1.0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F258" s="3"/>
     </row>
@@ -9770,10 +9771,10 @@
         <v>3.0</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G259" s="9">
         <v>46613.0</v>
@@ -9793,7 +9794,7 @@
         <v>7.0</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>82</v>
@@ -9836,7 +9837,7 @@
         <v>12.0</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F262" s="4"/>
       <c r="G262" s="9">
@@ -9860,7 +9861,7 @@
         <v>14.0</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="9">
@@ -9882,7 +9883,7 @@
         <v>13.0</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F264" s="4"/>
       <c r="G264" s="9">
@@ -9904,7 +9905,7 @@
         <v>12.0</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F265" s="4"/>
       <c r="G265" s="9">
@@ -9928,7 +9929,7 @@
         <v>12.0</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F266" s="4"/>
       <c r="G266" s="9">
@@ -9949,7 +9950,7 @@
         <v>14.0</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F267" s="4"/>
       <c r="G267" s="9">
@@ -9970,7 +9971,7 @@
         <v>14.0</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F268" s="4"/>
       <c r="G268" s="9">
@@ -9994,7 +9995,7 @@
         <v>66</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G269" s="9">
         <v>46949.0</v>
@@ -10014,7 +10015,7 @@
         <v>4.0</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>346</v>
@@ -10034,10 +10035,10 @@
         <v>17.0</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G271" s="9">
         <v>46743.0</v>
@@ -10057,10 +10058,10 @@
         <v>17.0</v>
       </c>
       <c r="E272" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F272" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="F272" s="3" t="s">
-        <v>571</v>
       </c>
       <c r="G272" s="9">
         <v>46752.0</v>
@@ -10080,10 +10081,10 @@
         <v>17.0</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G273" s="9">
         <v>46750.0</v>
@@ -10103,7 +10104,7 @@
         <v>16.0</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F274" s="4"/>
       <c r="G274" s="9">
@@ -10124,7 +10125,7 @@
         <v>13.0</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F275" s="4"/>
       <c r="G275" s="9">
@@ -10145,7 +10146,7 @@
         <v>16.0</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F276" s="4"/>
       <c r="G276" s="9">
@@ -10166,7 +10167,7 @@
         <v>15.0</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>272</v>
@@ -10209,10 +10210,10 @@
         <v>19.0</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G279" s="9">
         <v>46670.0</v>
@@ -10232,7 +10233,7 @@
         <v>3.0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>224</v>
@@ -10252,10 +10253,10 @@
         <v>20.0</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G281" s="9">
         <v>46789.0</v>
@@ -10316,10 +10317,10 @@
         <v>16.0</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G284" s="9">
         <v>46681.0</v>
@@ -10339,7 +10340,7 @@
         <v>16.0</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>359</v>
@@ -10362,10 +10363,10 @@
         <v>16.0</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G286" s="9">
         <v>46725.0</v>
@@ -10385,10 +10386,10 @@
         <v>8.0</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G287" s="9">
         <v>46789.0</v>
@@ -10408,10 +10409,10 @@
         <v>8.0</v>
       </c>
       <c r="E288" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F288" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="F288" s="3" t="s">
-        <v>587</v>
       </c>
       <c r="G288" s="9">
         <v>46757.0</v>
@@ -10431,10 +10432,10 @@
         <v>17.0</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G289" s="9">
         <v>46947.0</v>
@@ -10454,7 +10455,7 @@
         <v>9.0</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F290" s="3">
         <v>11503.0</v>
@@ -10474,7 +10475,7 @@
         <v>2.0</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F291" s="3">
         <v>11504.0</v>
@@ -10495,10 +10496,10 @@
         <v>18.0</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G292" s="9">
         <v>46949.0</v>
@@ -10518,10 +10519,10 @@
         <v>18.0</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G293" s="9">
         <v>46794.0</v>
@@ -10564,7 +10565,7 @@
         <v>21.0</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>16</v>
@@ -10587,7 +10588,7 @@
         <v>16.0</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>16</v>
@@ -10610,7 +10611,7 @@
         <v>4.0</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>16</v>
@@ -10633,7 +10634,7 @@
         <v>4.0</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>16</v>
@@ -10657,7 +10658,7 @@
         <v>19.0</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>493</v>
@@ -10680,7 +10681,7 @@
         <v>19.0</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>493</v>
@@ -10703,7 +10704,7 @@
         <v>18.0</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F301" s="4"/>
       <c r="G301" s="9">
@@ -10724,10 +10725,10 @@
         <v>9.0</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G302" s="9">
         <v>46577.0</v>
@@ -10747,10 +10748,10 @@
         <v>9.0</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G303" s="9">
         <v>46254.0</v>
@@ -10770,10 +10771,10 @@
         <v>9.0</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G304" s="9">
         <v>46254.0</v>
@@ -10793,7 +10794,7 @@
         <v>9.0</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F305" s="3">
         <v>1140221.0</v>
@@ -10816,7 +10817,7 @@
         <v>9.0</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>371</v>
@@ -10839,10 +10840,10 @@
         <v>12.0</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G307" s="9">
         <v>46596.0</v>
@@ -10862,10 +10863,10 @@
         <v>20.0</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G308" s="9">
         <v>46641.0</v>
@@ -10885,7 +10886,7 @@
         <v>2.0</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>142</v>
@@ -10908,7 +10909,7 @@
         <v>2.0</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>388</v>
@@ -10931,7 +10932,7 @@
         <v>3.0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F311" s="4"/>
     </row>
@@ -10949,7 +10950,7 @@
         <v>5.0</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>16</v>
@@ -10975,7 +10976,7 @@
         <v>5.0</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>441</v>
@@ -11001,7 +11002,7 @@
         <v>5.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>16</v>
@@ -11076,7 +11077,7 @@
         <v>4.0</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>16</v>
@@ -11096,7 +11097,7 @@
         <v>4.0</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>16</v>
@@ -11119,7 +11120,7 @@
         <v>5.0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>16</v>
@@ -11142,7 +11143,7 @@
         <v>4.0</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>24</v>
@@ -11165,7 +11166,7 @@
         <v>4.0</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>24</v>
@@ -11188,7 +11189,7 @@
         <v>4.0</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>24</v>
@@ -11211,7 +11212,7 @@
         <v>4.0</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>24</v>
@@ -11234,7 +11235,7 @@
         <v>2.0</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>16</v>
@@ -11257,7 +11258,7 @@
         <v>2.0</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>16</v>
@@ -11280,7 +11281,7 @@
         <v>2.0</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>16</v>
@@ -11294,7 +11295,7 @@
         <v>1.776148337734E12</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>11</v>
@@ -11303,10 +11304,10 @@
         <v>8.0</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G327" s="9">
         <v>46269.0</v>
@@ -11320,7 +11321,7 @@
         <v>1.776148418097E12</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>11</v>
@@ -11329,10 +11330,10 @@
         <v>6.0</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G328" s="9">
         <v>46247.0</v>
@@ -11343,7 +11344,7 @@
         <v>1.776148449855E12</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>11</v>
@@ -11352,10 +11353,10 @@
         <v>7.0</v>
       </c>
       <c r="E329" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F329" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="F329" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="G329" s="9">
         <v>46247.0</v>
@@ -11366,7 +11367,7 @@
         <v>1.776148475121E12</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>11</v>
@@ -11375,10 +11376,10 @@
         <v>8.0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G330" s="9">
         <v>46269.0</v>
@@ -11389,7 +11390,7 @@
         <v>1.776148592568E12</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>11</v>
@@ -11398,10 +11399,10 @@
         <v>12.0</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G331" s="9">
         <v>46234.0</v>
@@ -11415,7 +11416,7 @@
         <v>1.776148632656E12</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>11</v>
@@ -11424,10 +11425,10 @@
         <v>14.0</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G332" s="9">
         <v>46202.0</v>
@@ -11441,7 +11442,7 @@
         <v>1.776148710229E12</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>11</v>
@@ -11450,10 +11451,10 @@
         <v>13.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G333" s="9">
         <v>46193.0</v>
@@ -11467,7 +11468,7 @@
         <v>1.776148761624E12</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>11</v>
@@ -11476,10 +11477,10 @@
         <v>14.0</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G334" s="9">
         <v>46203.0</v>
@@ -11493,7 +11494,7 @@
         <v>1.776149046956E12</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>25</v>
@@ -11502,10 +11503,10 @@
         <v>4.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G335" s="9">
         <v>46182.0</v>
@@ -11519,7 +11520,7 @@
         <v>1.776149087494E12</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>11</v>
@@ -11528,7 +11529,7 @@
         <v>18.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F336" s="4"/>
     </row>
@@ -11546,7 +11547,7 @@
         <v>1.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F337" s="4"/>
       <c r="H337" s="2"/>
@@ -11565,7 +11566,7 @@
         <v>5.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F338" s="4"/>
       <c r="G338" s="9">
@@ -11587,7 +11588,7 @@
         <v>18.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>224</v>
@@ -11610,7 +11611,7 @@
         <v>3.0</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F340" s="3">
         <v>11504.0</v>
@@ -11630,10 +11631,10 @@
         <v>4.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G341" s="9">
         <v>46949.0</v>
@@ -11653,10 +11654,10 @@
         <v>5.0</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G342" s="9">
         <v>46949.0</v>
@@ -11676,7 +11677,7 @@
         <v>9.0</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>418</v>
@@ -11697,7 +11698,7 @@
         <v>10.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>418</v>
@@ -11717,7 +11718,7 @@
         <v>9.0</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>418</v>
@@ -11737,7 +11738,7 @@
         <v>13.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>241</v>
@@ -11760,7 +11761,7 @@
         <v>13.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>476</v>
@@ -11777,13 +11778,13 @@
         <v>112</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D348" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>241</v>
@@ -11803,10 +11804,10 @@
         <v>27</v>
       </c>
       <c r="D349" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>238</v>
@@ -11823,13 +11824,13 @@
         <v>112</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D350" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>238</v>
@@ -11846,13 +11847,13 @@
         <v>112</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D351" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F351" s="4"/>
     </row>
@@ -11864,13 +11865,13 @@
         <v>112</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D352" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>238</v>
@@ -11893,10 +11894,10 @@
         <v>17.0</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G353" s="9">
         <v>46768.0</v>
@@ -11916,10 +11917,10 @@
         <v>17.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G354" s="9">
         <v>46947.0</v>
@@ -11939,10 +11940,10 @@
         <v>17.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G355" s="9">
         <v>46771.0</v>
@@ -11962,7 +11963,7 @@
         <v>17.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>493</v>
@@ -11985,16 +11986,16 @@
         <v>20.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G357" s="9">
         <v>46691.0</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="358">
@@ -12011,7 +12012,7 @@
         <v>11.0</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F358" s="3" t="s">
         <v>145</v>
@@ -12034,7 +12035,7 @@
         <v>12.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>241</v>
@@ -12057,7 +12058,7 @@
         <v>7.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F360" s="3">
         <v>11503.0</v>
@@ -12080,10 +12081,10 @@
         <v>11.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G361" s="9">
         <v>46669.0</v>
@@ -12103,10 +12104,10 @@
         <v>12.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G362" s="9">
         <v>46523.0</v>
@@ -12126,7 +12127,7 @@
         <v>12.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F363" s="4"/>
       <c r="G363" s="9">
@@ -12138,7 +12139,7 @@
         <v>1.776436049209E12</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
@@ -12165,10 +12166,10 @@
         <v>1.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G365" s="9">
         <v>46793.0</v>
@@ -12176,7 +12177,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>112</v>
@@ -12191,7 +12192,7 @@
         <v>66</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G366" s="9">
         <v>46949.0</v>
@@ -12199,7 +12200,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>112</v>
@@ -12211,10 +12212,10 @@
         <v>20.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G367" s="9">
         <v>46793.0</v>
@@ -12222,7 +12223,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>112</v>
@@ -12234,10 +12235,10 @@
         <v>16.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G368" s="9">
         <v>46639.0</v>
@@ -12245,7 +12246,7 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>10</v>
@@ -12257,13 +12258,13 @@
         <v>3.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F369" s="4"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>10</v>
@@ -12275,13 +12276,13 @@
         <v>4.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F370" s="4"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>10</v>
@@ -12293,13 +12294,13 @@
         <v>5.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F371" s="4"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>10</v>
@@ -12311,13 +12312,13 @@
         <v>5.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F372" s="4"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>10</v>
@@ -12329,13 +12330,13 @@
         <v>5.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F373" s="4"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>10</v>
@@ -12347,13 +12348,13 @@
         <v>5.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F374" s="4"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>10</v>
@@ -12365,13 +12366,13 @@
         <v>1.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F375" s="4"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>32</v>
@@ -12383,7 +12384,7 @@
         <v>2.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>293</v>
@@ -12391,7 +12392,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>32</v>
@@ -12403,7 +12404,7 @@
         <v>2.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>346</v>
@@ -12414,7 +12415,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>32</v>
@@ -12426,15 +12427,15 @@
         <v>2.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>32</v>
@@ -12446,7 +12447,7 @@
         <v>4.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>293</v>
@@ -12458,7 +12459,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>112</v>
@@ -12470,7 +12471,7 @@
         <v>10.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F380" s="3">
         <v>11504.0</v>
@@ -12478,7 +12479,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>112</v>
@@ -12490,7 +12491,7 @@
         <v>8.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F381" s="3">
         <v>11504.0</v>
@@ -12499,7 +12500,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>32</v>
@@ -12511,14 +12512,14 @@
         <v>3.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F382" s="4"/>
       <c r="H382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>32</v>
@@ -12530,21 +12531,21 @@
         <v>11.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G383" s="9">
         <v>46240.0</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>112</v>
@@ -12556,10 +12557,10 @@
         <v>13.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G384" s="9">
         <v>46416.0</v>
@@ -12567,7 +12568,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>112</v>
@@ -12579,10 +12580,10 @@
         <v>16.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G385" s="9">
         <v>46544.0</v>
@@ -12590,7 +12591,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>32</v>
@@ -12602,10 +12603,10 @@
         <v>11.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G386" s="9">
         <v>46856.0</v>
@@ -12613,7 +12614,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>112</v>
@@ -12625,21 +12626,21 @@
         <v>16.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G387" s="9">
         <v>46794.0</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>112</v>
@@ -12651,10 +12652,10 @@
         <v>16.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G388" s="9">
         <v>46785.0</v>
@@ -12662,7 +12663,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>112</v>
@@ -12674,10 +12675,10 @@
         <v>16.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G389" s="9">
         <v>46789.0</v>
@@ -12685,7 +12686,7 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>112</v>
@@ -12697,10 +12698,10 @@
         <v>16.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G390" s="9">
         <v>46839.0</v>
@@ -12708,7 +12709,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>112</v>
@@ -12720,10 +12721,10 @@
         <v>11.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G391" s="9">
         <v>46312.0</v>
@@ -12734,7 +12735,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>112</v>
@@ -12746,10 +12747,10 @@
         <v>17.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G392" s="9">
         <v>46669.0</v>
@@ -12758,7 +12759,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>112</v>
@@ -12770,7 +12771,7 @@
         <v>22.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>165</v>
@@ -12781,7 +12782,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>112</v>
@@ -12793,10 +12794,10 @@
         <v>7.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G394" s="9">
         <v>46794.0</v>
@@ -12804,7 +12805,7 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>112</v>
@@ -12816,10 +12817,10 @@
         <v>7.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G395" s="9">
         <v>46792.0</v>
@@ -12827,7 +12828,7 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>112</v>
@@ -12839,7 +12840,7 @@
         <v>6.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F396" s="3">
         <v>11504.0</v>
@@ -12848,7 +12849,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>112</v>
@@ -12860,7 +12861,7 @@
         <v>9.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F397" s="3">
         <v>115004.0</v>
@@ -12868,7 +12869,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>32</v>
@@ -12880,7 +12881,7 @@
         <v>3.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F398" s="3">
         <v>11505.0</v>
@@ -12888,7 +12889,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>32</v>
@@ -12900,7 +12901,7 @@
         <v>11.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>227</v>
@@ -12917,7 +12918,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>32</v>
@@ -12929,13 +12930,13 @@
         <v>22.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F400" s="4"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>32</v>
@@ -12947,7 +12948,7 @@
         <v>11.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>326</v>
@@ -12964,7 +12965,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>112</v>
@@ -12976,10 +12977,10 @@
         <v>20.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G402" s="9">
         <v>46596.0</v>
@@ -12987,22 +12988,22 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D403" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G403" s="9">
         <v>46669.0</v>
@@ -13010,7 +13011,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>32</v>
@@ -13022,7 +13023,7 @@
         <v>9.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>385</v>
@@ -13030,7 +13031,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>32</v>
@@ -13042,7 +13043,7 @@
         <v>10.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>418</v>
@@ -13050,122 +13051,119 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D406" s="2">
-        <v>18.0</v>
+        <v>25</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>752</v>
+        <v>560</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>95</v>
+        <v>753</v>
       </c>
       <c r="G406" s="9">
-        <v>46694.0</v>
+        <v>46410.0</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
+      </c>
+      <c r="D407" s="2">
+        <v>22.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>559</v>
+        <v>755</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G407" s="9">
-        <v>46410.0</v>
+        <v>46194.0</v>
+      </c>
+      <c r="I407" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D408" s="2">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="G408" s="9">
-        <v>46194.0</v>
-      </c>
-      <c r="I408" s="2" t="s">
-        <v>233</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D409" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>759</v>
+        <v>589</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G409" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D410" s="2">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>588</v>
+        <v>763</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="G410" s="9">
-        <v>46913.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>10</v>
@@ -13177,7 +13175,7 @@
         <v>2.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>224</v>
@@ -13197,10 +13195,10 @@
         <v>2.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>15</v>
+        <v>763</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="413">
@@ -13211,21 +13209,24 @@
         <v>10</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D413" s="2">
         <v>2.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G413" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>10</v>
@@ -13234,42 +13235,42 @@
         <v>25</v>
       </c>
       <c r="D414" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F414" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F414" s="4"/>
       <c r="G414" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C415" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D415" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F415" s="4"/>
+        <v>771</v>
+      </c>
+      <c r="F415" s="3" t="s">
+        <v>772</v>
+      </c>
       <c r="G415" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>32</v>
@@ -13281,36 +13282,33 @@
         <v>4.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F416" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G416" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D417" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="F417" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="G417" s="9">
-        <v>46484.0</v>
+        <v>548</v>
+      </c>
+      <c r="F417" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="418">
@@ -13318,19 +13316,19 @@
         <v>776</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D418" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F418" s="3">
-        <v>11505.0</v>
+        <v>713</v>
+      </c>
+      <c r="F418" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="419">
@@ -13341,67 +13339,70 @@
         <v>32</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D419" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>712</v>
+        <v>778</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>55</v>
+        <v>605</v>
+      </c>
+      <c r="G419" s="9">
+        <v>46577.0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D420" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>604</v>
+        <v>272</v>
       </c>
       <c r="G420" s="9">
-        <v>46577.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D421" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>272</v>
+        <v>596</v>
       </c>
       <c r="G421" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>112</v>
@@ -13413,18 +13414,18 @@
         <v>17.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G422" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>112</v>
@@ -13436,18 +13437,18 @@
         <v>17.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G423" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>112</v>
@@ -13459,18 +13460,18 @@
         <v>17.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G424" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>112</v>
@@ -13482,53 +13483,50 @@
         <v>17.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>595</v>
+        <v>791</v>
       </c>
       <c r="G425" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D426" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="G426" s="9">
-        <v>46523.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D427" s="2">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>224</v>
@@ -13536,19 +13534,19 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D428" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>224</v>
@@ -13556,7 +13554,7 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>32</v>
@@ -13565,10 +13563,10 @@
         <v>27</v>
       </c>
       <c r="D429" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>224</v>
@@ -13576,50 +13574,53 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D430" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>224</v>
+        <v>238</v>
+      </c>
+      <c r="G430" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C431" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="2">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G431" s="9">
-        <v>46281.0</v>
+        <v>493</v>
+      </c>
+      <c r="H431" s="2" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>32</v>
@@ -13628,21 +13629,21 @@
         <v>11</v>
       </c>
       <c r="D432" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H432" s="2" t="s">
-        <v>805</v>
+      <c r="G432" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>32</v>
@@ -13651,67 +13652,67 @@
         <v>11</v>
       </c>
       <c r="D433" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="G433" s="9">
-        <v>47146.0</v>
+      <c r="H433" s="2" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F434" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H434" s="2" t="s">
-        <v>805</v>
+        <v>811</v>
+      </c>
+      <c r="G434" s="9">
+        <v>46666.0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>752</v>
+        <v>813</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="G435" s="9">
-        <v>46666.0</v>
+        <v>46583.0</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>32</v>
@@ -13726,15 +13727,15 @@
         <v>813</v>
       </c>
       <c r="F436" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="G436" s="9">
-        <v>46583.0</v>
+        <v>46604.0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>32</v>
@@ -13749,15 +13750,15 @@
         <v>813</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>816</v>
+        <v>110</v>
       </c>
       <c r="G437" s="9">
-        <v>46604.0</v>
+        <v>46626.0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>32</v>
@@ -13772,15 +13773,15 @@
         <v>813</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>110</v>
+        <v>819</v>
       </c>
       <c r="G438" s="9">
-        <v>46626.0</v>
+        <v>46658.0</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>32</v>
@@ -13795,102 +13796,102 @@
         <v>813</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G439" s="9">
-        <v>46658.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D440" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="F440" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="G440" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>823</v>
+      </c>
+      <c r="F440" s="4"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D441" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F441" s="4"/>
+        <v>825</v>
+      </c>
+      <c r="F441" s="3" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D442" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>493</v>
+        <v>828</v>
+      </c>
+      <c r="G442" s="9">
+        <v>46792.0</v>
+      </c>
+      <c r="H442" s="2" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D443" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="G443" s="9">
-        <v>46792.0</v>
-      </c>
-      <c r="H443" s="2" t="s">
-        <v>829</v>
+        <v>46304.0</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>32</v>
@@ -13899,21 +13900,21 @@
         <v>11</v>
       </c>
       <c r="D444" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>831</v>
+        <v>583</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>832</v>
+        <v>51</v>
       </c>
       <c r="G444" s="9">
-        <v>46304.0</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>32</v>
@@ -13922,21 +13923,21 @@
         <v>11</v>
       </c>
       <c r="D445" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>582</v>
+        <v>835</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>51</v>
+        <v>359</v>
       </c>
       <c r="G445" s="9">
-        <v>46416.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>32</v>
@@ -13945,59 +13946,59 @@
         <v>11</v>
       </c>
       <c r="D446" s="2">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="G446" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D447" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>37</v>
+        <v>664</v>
       </c>
       <c r="G447" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D448" s="2">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G448" s="9">
         <v>46794.0</v>
@@ -14005,7 +14006,7 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>112</v>
@@ -14014,67 +14015,67 @@
         <v>25</v>
       </c>
       <c r="D449" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>839</v>
+        <v>545</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G449" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D450" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>544</v>
+        <v>730</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>663</v>
+        <v>843</v>
       </c>
       <c r="G450" s="9">
-        <v>46484.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D451" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>729</v>
+        <v>845</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>843</v>
+        <v>580</v>
       </c>
       <c r="G451" s="9">
-        <v>46792.0</v>
+        <v>46676.0</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>32</v>
@@ -14086,36 +14087,36 @@
         <v>9.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="F452" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="G452" s="9">
-        <v>46676.0</v>
-      </c>
+        <v>813</v>
+      </c>
+      <c r="F452" s="4"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="F453" s="4"/>
+        <v>848</v>
+      </c>
+      <c r="F453" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G453" s="9">
+        <v>46641.0</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>112</v>
@@ -14124,21 +14125,21 @@
         <v>11</v>
       </c>
       <c r="D454" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F454" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G454" s="9">
-        <v>46641.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>112</v>
@@ -14147,44 +14148,44 @@
         <v>11</v>
       </c>
       <c r="D455" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F455" s="3" t="s">
-        <v>707</v>
+        <v>664</v>
       </c>
       <c r="G455" s="9">
-        <v>46530.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D456" s="2">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>663</v>
+        <v>580</v>
       </c>
       <c r="G456" s="9">
-        <v>46949.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>112</v>
@@ -14193,24 +14194,21 @@
         <v>25</v>
       </c>
       <c r="D457" s="2">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>707</v>
+        <v>449</v>
       </c>
       <c r="G457" s="9">
-        <v>46523.0</v>
-      </c>
-      <c r="H457" s="2" t="s">
-        <v>855</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>112</v>
@@ -14225,18 +14223,18 @@
         <v>831</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>579</v>
+        <v>449</v>
       </c>
       <c r="G458" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>25</v>
@@ -14248,18 +14246,18 @@
         <v>831</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>449</v>
+        <v>580</v>
       </c>
       <c r="G459" s="9">
-        <v>46752.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>25</v>
@@ -14279,7 +14277,7 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>32</v>
@@ -14294,38 +14292,35 @@
         <v>831</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>579</v>
+        <v>45</v>
       </c>
       <c r="G461" s="9">
-        <v>46670.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D462" s="2">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>831</v>
+        <v>579</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G462" s="9">
-        <v>46752.0</v>
+        <v>669</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>32</v>
@@ -14337,13 +14332,16 @@
         <v>3.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>831</v>
+        <v>573</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>45</v>
+        <v>861</v>
       </c>
       <c r="G463" s="9">
-        <v>46366.0</v>
+        <v>46670.0</v>
+      </c>
+      <c r="H463" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="464">
@@ -14351,45 +14349,45 @@
         <v>862</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D464" s="2">
-        <v>19.0</v>
+        <v>7.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>578</v>
+        <v>863</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>668</v>
+        <v>95</v>
+      </c>
+      <c r="G464" s="9">
+        <v>46725.0</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D465" s="2">
-        <v>3.0</v>
+        <v>22.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>864</v>
+        <v>317</v>
       </c>
       <c r="G465" s="9">
-        <v>46670.0</v>
-      </c>
-      <c r="H465" s="2" t="s">
-        <v>52</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="466">
@@ -14397,22 +14395,22 @@
         <v>865</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D466" s="2">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>866</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="G466" s="9">
-        <v>46725.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="467">
@@ -14429,103 +14427,103 @@
         <v>22.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>573</v>
+        <v>868</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>317</v>
+        <v>869</v>
       </c>
       <c r="G467" s="9">
-        <v>46556.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C468" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D468" s="2">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>142</v>
+        <v>607</v>
       </c>
       <c r="G468" s="9">
-        <v>46793.0</v>
-      </c>
+        <v>46254.0</v>
+      </c>
+      <c r="H468" s="2"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C469" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D469" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>872</v>
+        <v>405</v>
       </c>
       <c r="G469" s="9">
-        <v>46670.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D470" s="2">
-        <v>17.0</v>
+        <v>6.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>606</v>
+        <v>876</v>
       </c>
       <c r="G470" s="9">
-        <v>46254.0</v>
-      </c>
-      <c r="H470" s="2"/>
+        <v>46669.0</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D471" s="2">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>405</v>
+        <v>879</v>
       </c>
       <c r="G471" s="9">
         <v>46669.0</v>
@@ -14533,7 +14531,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>32</v>
@@ -14548,7 +14546,7 @@
         <v>878</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>879</v>
+        <v>811</v>
       </c>
       <c r="G472" s="9">
         <v>46669.0</v>
@@ -14556,7 +14554,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>32</v>
@@ -14568,7 +14566,7 @@
         <v>6.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>882</v>
@@ -14585,47 +14583,47 @@
         <v>32</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D474" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>811</v>
+        <v>885</v>
       </c>
       <c r="G474" s="9">
-        <v>46669.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D475" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>881</v>
+        <v>602</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>885</v>
       </c>
       <c r="G475" s="9">
-        <v>46669.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>32</v>
@@ -14637,18 +14635,18 @@
         <v>18.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>887</v>
+        <v>66</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="G476" s="9">
-        <v>46947.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>32</v>
@@ -14660,18 +14658,15 @@
         <v>18.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>601</v>
+        <v>831</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="G477" s="9">
-        <v>46949.0</v>
+        <v>885</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>32</v>
@@ -14680,36 +14675,36 @@
         <v>27</v>
       </c>
       <c r="D478" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>66</v>
+        <v>831</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>888</v>
+        <v>43</v>
       </c>
       <c r="G478" s="9">
-        <v>46949.0</v>
+        <v>46730.0</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C479" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D479" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E479" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B479" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C479" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D479" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E479" s="2" t="s">
-        <v>831</v>
-      </c>
       <c r="F479" s="3" t="s">
-        <v>888</v>
+        <v>346</v>
       </c>
     </row>
     <row r="480">
@@ -14723,16 +14718,13 @@
         <v>27</v>
       </c>
       <c r="D480" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>831</v>
+        <v>891</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G480" s="9">
-        <v>46730.0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="481">
@@ -14743,16 +14735,19 @@
         <v>32</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D481" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>894</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>346</v>
+        <v>441</v>
+      </c>
+      <c r="G481" s="9">
+        <v>46267.0</v>
       </c>
     </row>
     <row r="482">
@@ -14763,67 +14758,70 @@
         <v>32</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D482" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>118</v>
+        <v>759</v>
+      </c>
+      <c r="G482" s="9">
+        <v>46250.0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D483" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>441</v>
+        <v>359</v>
       </c>
       <c r="G483" s="9">
-        <v>46267.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D484" s="2">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>760</v>
+        <v>470</v>
       </c>
       <c r="G484" s="9">
-        <v>46250.0</v>
+        <v>46613.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>32</v>
@@ -14832,16 +14830,16 @@
         <v>11</v>
       </c>
       <c r="D485" s="2">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>901</v>
+        <v>608</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>359</v>
+        <v>609</v>
       </c>
       <c r="G485" s="9">
-        <v>46255.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="486">
@@ -14849,22 +14847,22 @@
         <v>902</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C486" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2">
-        <v>21.0</v>
+        <v>7.0</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>903</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="G486" s="9">
-        <v>46613.0</v>
+        <v>46691.0</v>
       </c>
     </row>
     <row r="487">
@@ -14878,16 +14876,16 @@
         <v>11</v>
       </c>
       <c r="D487" s="2">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>607</v>
+        <v>903</v>
       </c>
       <c r="F487" s="3" t="s">
-        <v>608</v>
+        <v>885</v>
       </c>
       <c r="G487" s="9">
-        <v>46669.0</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="488">
@@ -14898,20 +14896,15 @@
         <v>32</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D488" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>906</v>
       </c>
-      <c r="F488" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G488" s="9">
-        <v>46691.0</v>
-      </c>
+      <c r="F488" s="4"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
@@ -14921,24 +14914,19 @@
         <v>32</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D489" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="F489" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="G489" s="9">
-        <v>46775.0</v>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="F489" s="4"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>32</v>
@@ -14950,13 +14938,13 @@
         <v>11.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F490" s="4"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>32</v>
@@ -14968,95 +14956,95 @@
         <v>11.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F491" s="4"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D492" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="F492" s="4"/>
+        <v>914</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="G492" s="9">
+        <v>46803.0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D493" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="F493" s="4"/>
+        <v>871</v>
+      </c>
+      <c r="F493" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="G493" s="9">
+        <v>46222.0</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D494" s="2">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="F494" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="G494" s="9">
-        <v>46803.0</v>
-      </c>
+        <v>919</v>
+      </c>
+      <c r="F494" s="4"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D495" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="F495" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="G495" s="9">
-        <v>46222.0</v>
-      </c>
+        <v>921</v>
+      </c>
+      <c r="F495" s="4"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>32</v>
@@ -15068,13 +15056,13 @@
         <v>11.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>32</v>
@@ -15086,49 +15074,55 @@
         <v>11.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F497" s="4"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D498" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F498" s="4"/>
+      <c r="G498" s="9">
+        <v>46564.0</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D499" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F499" s="4"/>
+      <c r="G499" s="9">
+        <v>46551.0</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>32</v>
@@ -15140,16 +15134,16 @@
         <v>14.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F500" s="4"/>
       <c r="G500" s="9">
-        <v>46564.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>32</v>
@@ -15158,19 +15152,19 @@
         <v>25</v>
       </c>
       <c r="D501" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F501" s="4"/>
       <c r="G501" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -15179,19 +15173,19 @@
         <v>25</v>
       </c>
       <c r="D502" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F502" s="4"/>
       <c r="G502" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>32</v>
@@ -15203,16 +15197,16 @@
         <v>15.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F503" s="4"/>
       <c r="G503" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>32</v>
@@ -15224,7 +15218,7 @@
         <v>15.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F504" s="4"/>
       <c r="G504" s="9">
@@ -15233,7 +15227,7 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>32</v>
@@ -15242,19 +15236,19 @@
         <v>25</v>
       </c>
       <c r="D505" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F505" s="4"/>
       <c r="G505" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>32</v>
@@ -15263,40 +15257,39 @@
         <v>25</v>
       </c>
       <c r="D506" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F506" s="4"/>
       <c r="G506" s="9">
-        <v>46355.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D507" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="F507" s="4"/>
-      <c r="G507" s="9">
-        <v>46551.0</v>
+        <v>945</v>
+      </c>
+      <c r="F507" s="3" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>32</v>
@@ -15305,83 +15298,88 @@
         <v>25</v>
       </c>
       <c r="D508" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F508" s="4"/>
-      <c r="G508" s="9">
-        <v>46394.0</v>
-      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D509" s="2">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>418</v>
       </c>
+      <c r="G509" s="9">
+        <v>46759.0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>32</v>
+        <v>538</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D510" s="2">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="F510" s="4"/>
+        <v>951</v>
+      </c>
+      <c r="F510" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G510" s="9">
+        <v>46406.0</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>32</v>
+        <v>538</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D511" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F511" s="3" t="s">
-        <v>418</v>
+        <v>37</v>
       </c>
       <c r="G511" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>11</v>
@@ -15390,7 +15388,7 @@
         <v>3.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F512" s="3" t="s">
         <v>37</v>
@@ -15401,10 +15399,10 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>11</v>
@@ -15413,7 +15411,7 @@
         <v>3.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F513" s="3" t="s">
         <v>37</v>
@@ -15424,10 +15422,10 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>11</v>
@@ -15436,10 +15434,10 @@
         <v>3.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G514" s="9">
         <v>46406.0</v>
@@ -15450,7 +15448,7 @@
         <v>959</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>11</v>
@@ -15465,7 +15463,7 @@
         <v>37</v>
       </c>
       <c r="G515" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="516">
@@ -15473,7 +15471,7 @@
         <v>961</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>11</v>
@@ -15482,21 +15480,21 @@
         <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G516" s="9">
-        <v>46406.0</v>
+        <v>46258.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>11</v>
@@ -15505,67 +15503,67 @@
         <v>3.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F517" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G517" s="9">
-        <v>46251.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D518" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G518" s="9">
-        <v>46258.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D519" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G519" s="9">
-        <v>46254.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>11</v>
@@ -15574,7 +15572,7 @@
         <v>4.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F520" s="3" t="s">
         <v>37</v>
@@ -15585,10 +15583,10 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>11</v>
@@ -15597,7 +15595,7 @@
         <v>4.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>37</v>
@@ -15608,56 +15606,56 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D522" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G522" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D523" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G523" s="9">
-        <v>46387.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>11</v>
@@ -15666,21 +15664,21 @@
         <v>6.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G524" s="9">
-        <v>46251.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>11</v>
@@ -15689,21 +15687,21 @@
         <v>6.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G525" s="9">
-        <v>46280.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>11</v>
@@ -15712,21 +15710,21 @@
         <v>6.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G526" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>11</v>
@@ -15735,7 +15733,7 @@
         <v>6.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>37</v>
@@ -15746,10 +15744,10 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>11</v>
@@ -15758,67 +15756,67 @@
         <v>6.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F528" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G528" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D529" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G529" s="9">
-        <v>46256.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D530" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G530" s="9">
-        <v>46249.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>11</v>
@@ -15827,67 +15825,67 @@
         <v>7.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G531" s="9">
-        <v>46352.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D532" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G532" s="9">
-        <v>46333.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D533" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F533" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G533" s="9">
-        <v>46244.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>11</v>
@@ -15896,21 +15894,21 @@
         <v>8.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F534" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G534" s="9">
-        <v>46226.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>11</v>
@@ -15919,21 +15917,21 @@
         <v>8.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F535" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G535" s="9">
-        <v>46222.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>11</v>
@@ -15942,59 +15940,59 @@
         <v>8.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F536" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G536" s="9">
-        <v>46241.0</v>
+        <v>46319.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D537" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G537" s="9">
-        <v>46305.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C538" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D538" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E538" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="B538" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C538" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D538" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="E538" s="2" t="s">
-        <v>1005</v>
-      </c>
       <c r="F538" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G538" s="9">
-        <v>46319.0</v>
+        <v>46321.0</v>
       </c>
     </row>
     <row r="539">
@@ -16002,53 +16000,56 @@
         <v>1006</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D539" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="G539" s="9">
-        <v>46365.0</v>
+        <v>46426.0</v>
+      </c>
+      <c r="H539" s="2" t="s">
+        <v>1008</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D540" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G540" s="9">
-        <v>46321.0</v>
+        <v>46211.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>11</v>
@@ -16057,24 +16058,21 @@
         <v>10.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G541" s="9">
-        <v>46426.0</v>
-      </c>
-      <c r="H541" s="2" t="s">
-        <v>1011</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>11</v>
@@ -16083,113 +16081,115 @@
         <v>10.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G542" s="9">
-        <v>46211.0</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D543" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G543" s="9">
-        <v>46204.0</v>
+        <v>46392.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D544" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="G544" s="9">
-        <v>46345.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D545" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F545" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>1020</v>
+      </c>
+      <c r="F545" s="4"/>
       <c r="G545" s="9">
-        <v>46392.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I545" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D546" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F546" s="3" t="s">
-        <v>493</v>
-      </c>
+        <v>1022</v>
+      </c>
+      <c r="F546" s="4"/>
       <c r="G546" s="9">
-        <v>46366.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I546" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>11</v>
@@ -16198,22 +16198,19 @@
         <v>14.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F547" s="4"/>
       <c r="G547" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I547" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>11</v>
@@ -16222,64 +16219,59 @@
         <v>14.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F548" s="4"/>
       <c r="G548" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I548" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D549" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F549" s="4"/>
-      <c r="G549" s="9">
-        <v>46220.0</v>
+        <v>1028</v>
+      </c>
+      <c r="F549" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D550" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F550" s="4"/>
-      <c r="G550" s="9">
-        <v>46220.0</v>
+        <v>1030</v>
+      </c>
+      <c r="F550" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>11</v>
@@ -16288,10 +16280,13 @@
         <v>1.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="F551" s="3" t="s">
         <v>157</v>
+      </c>
+      <c r="G551" s="9">
+        <v>46223.0</v>
       </c>
     </row>
     <row r="552">
@@ -16299,7 +16294,7 @@
         <v>1032</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>11</v>
@@ -16312,6 +16307,9 @@
       </c>
       <c r="F552" s="3" t="s">
         <v>157</v>
+      </c>
+      <c r="G552" s="9">
+        <v>46228.0</v>
       </c>
     </row>
     <row r="553">
@@ -16319,186 +16317,181 @@
         <v>1034</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D553" s="2">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>157</v>
+        <v>627</v>
       </c>
       <c r="G553" s="9">
-        <v>46223.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D554" s="2">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>157</v>
+        <v>632</v>
       </c>
       <c r="G554" s="9">
-        <v>46228.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D555" s="2">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="G555" s="9">
-        <v>46269.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C556" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D556" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>631</v>
+        <v>399</v>
       </c>
       <c r="G556" s="9">
-        <v>46240.0</v>
+        <v>46274.0</v>
+      </c>
+      <c r="H556" s="2" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D557" s="2">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>631</v>
+        <v>1044</v>
       </c>
       <c r="G557" s="9">
-        <v>46242.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C558" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D558" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>399</v>
+        <v>1047</v>
       </c>
       <c r="G558" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H558" s="2" t="s">
-        <v>714</v>
+        <v>46207.0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D559" s="2">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F559" s="3" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G559" s="9">
-        <v>46743.0</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="F559" s="4"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D560" s="2">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>1050</v>
+        <v>227</v>
       </c>
       <c r="G560" s="9">
-        <v>46207.0</v>
+        <v>46295.0</v>
       </c>
     </row>
     <row r="561">
@@ -16506,40 +16499,45 @@
         <v>1051</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D561" s="2">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F561" s="4"/>
+        <v>1052</v>
+      </c>
+      <c r="F561" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G561" s="9">
+        <v>46769.0</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D562" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E562" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="B562" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C562" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D562" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E562" s="2" t="s">
-        <v>1053</v>
-      </c>
       <c r="F562" s="3" t="s">
-        <v>227</v>
+        <v>399</v>
       </c>
       <c r="G562" s="9">
-        <v>46295.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="563">
@@ -16547,22 +16545,22 @@
         <v>1054</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>32</v>
+        <v>536</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D563" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>1055</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>399</v>
+        <v>628</v>
       </c>
       <c r="G563" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="564">
@@ -16570,30 +16568,30 @@
         <v>1056</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>32</v>
+        <v>536</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D564" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>399</v>
+        <v>628</v>
       </c>
       <c r="G564" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>11</v>
@@ -16602,21 +16600,21 @@
         <v>3.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G565" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C566" s="2" t="s">
         <v>11</v>
@@ -16625,21 +16623,21 @@
         <v>3.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G566" s="9">
-        <v>46261.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>11</v>
@@ -16648,10 +16646,10 @@
         <v>3.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F567" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G567" s="9">
         <v>46266.0</v>
@@ -16659,10 +16657,10 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>11</v>
@@ -16671,21 +16669,21 @@
         <v>3.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G568" s="9">
-        <v>46223.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>535</v>
+        <v>32</v>
       </c>
       <c r="C569" s="2" t="s">
         <v>11</v>
@@ -16694,64 +16692,64 @@
         <v>3.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>627</v>
+        <v>399</v>
       </c>
       <c r="G569" s="9">
-        <v>46266.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D570" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1068</v>
+        <v>717</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>627</v>
+        <v>1069</v>
       </c>
       <c r="G570" s="9">
-        <v>46261.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D571" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E571" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F571" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="B571" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C571" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D571" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E571" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F571" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="G571" s="9">
-        <v>46769.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>112</v>
@@ -16763,13 +16761,13 @@
         <v>14.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="G572" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="573">
@@ -16786,36 +16784,36 @@
         <v>14.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1074</v>
+        <v>602</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="G573" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D574" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>712</v>
+        <v>891</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="G574" s="9">
-        <v>46820.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="575">
@@ -16823,27 +16821,27 @@
         <v>1076</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D575" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>601</v>
+        <v>1077</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="G575" s="9">
-        <v>46998.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>32</v>
@@ -16855,18 +16853,18 @@
         <v>2.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>894</v>
+        <v>1080</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="G576" s="9">
-        <v>46484.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>32</v>
@@ -16878,18 +16876,18 @@
         <v>2.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>1081</v>
+        <v>458</v>
       </c>
       <c r="G577" s="9">
-        <v>46432.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>32</v>
@@ -16901,18 +16899,16 @@
         <v>2.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G578" s="9">
-        <v>46877.0</v>
-      </c>
+        <v>1086</v>
+      </c>
+      <c r="G578" s="9"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>32</v>
@@ -16924,18 +16920,15 @@
         <v>2.0</v>
       </c>
       <c r="E579" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F579" s="3" t="s">
         <v>1086</v>
-      </c>
-      <c r="F579" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G579" s="9">
-        <v>46704.0</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>32</v>
@@ -16947,12 +16940,11 @@
         <v>2.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1088</v>
+        <v>875</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G580" s="9"/>
+        <v>1086</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
@@ -16968,15 +16960,15 @@
         <v>2.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1091</v>
+        <v>585</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>32</v>
@@ -16988,15 +16980,15 @@
         <v>2.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>878</v>
+        <v>1088</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>32</v>
@@ -17008,10 +17000,10 @@
         <v>2.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>584</v>
+        <v>1093</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="584">
@@ -17028,58 +17020,64 @@
         <v>2.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1089</v>
+        <v>594</v>
+      </c>
+      <c r="G584" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D585" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>1089</v>
+        <v>1098</v>
+      </c>
+      <c r="G585" s="9">
+        <v>46877.0</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D586" s="2">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E586" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F586" s="3" t="s">
         <v>1098</v>
       </c>
-      <c r="F586" s="3" t="s">
-        <v>593</v>
-      </c>
       <c r="G586" s="9">
-        <v>46766.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>112</v>
@@ -17088,16 +17086,16 @@
         <v>11</v>
       </c>
       <c r="D587" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G587" s="9">
-        <v>46877.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="588">
@@ -17111,21 +17109,19 @@
         <v>11</v>
       </c>
       <c r="D588" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="F588" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G588" s="9">
-        <v>46641.0</v>
+        <v>1103</v>
+      </c>
+      <c r="F588" s="4"/>
+      <c r="H588" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>112</v>
@@ -17134,42 +17130,50 @@
         <v>11</v>
       </c>
       <c r="D589" s="2">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1104</v>
+        <v>810</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="G589" s="9">
-        <v>46743.0</v>
+        <v>46663.0</v>
+      </c>
+      <c r="H589" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D590" s="2">
-        <v>15.0</v>
+        <v>19.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F590" s="4"/>
+        <v>583</v>
+      </c>
+      <c r="F590" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G590" s="9">
+        <v>46437.0</v>
+      </c>
       <c r="H590" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>112</v>
@@ -17178,45 +17182,39 @@
         <v>11</v>
       </c>
       <c r="D591" s="2">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>752</v>
+        <v>1109</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="G591" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H591" s="2" t="s">
-        <v>133</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D592" s="2">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>582</v>
+        <v>662</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="G592" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H592" s="2" t="s">
-        <v>133</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="593">
@@ -17230,16 +17228,16 @@
         <v>11</v>
       </c>
       <c r="D593" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>1112</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G593" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="594">
@@ -17250,70 +17248,70 @@
         <v>112</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D594" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>661</v>
+        <v>1114</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G594" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D595" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G595" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D596" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G596" s="9">
-        <v>46834.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>112</v>
@@ -17325,18 +17323,18 @@
         <v>14.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G597" s="9">
-        <v>46481.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>112</v>
@@ -17348,18 +17346,18 @@
         <v>14.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G598" s="9">
-        <v>46877.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>112</v>
@@ -17371,10 +17369,10 @@
         <v>14.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G599" s="9">
         <v>46872.0</v>
@@ -17382,7 +17380,7 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>112</v>
@@ -17394,36 +17392,36 @@
         <v>14.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G600" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D601" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1127</v>
+        <v>848</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G601" s="9">
-        <v>46734.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="602">
@@ -17431,22 +17429,22 @@
         <v>1128</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D602" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>1129</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1101</v>
+        <v>399</v>
       </c>
       <c r="G602" s="9">
-        <v>46481.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="603">
@@ -17454,22 +17452,22 @@
         <v>1130</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D603" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>1131</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1101</v>
+        <v>399</v>
       </c>
       <c r="G603" s="9">
-        <v>46872.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="604">
@@ -17477,68 +17475,64 @@
         <v>1132</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D604" s="2">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1133</v>
+        <v>656</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1101</v>
+        <v>399</v>
       </c>
       <c r="G604" s="9">
-        <v>46877.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D605" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E605" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="B605" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C605" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D605" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E605" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="F605" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G605" s="9">
-        <v>46641.0</v>
-      </c>
+      <c r="F605" s="3"/>
+      <c r="G605" s="9"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
         <v>1135</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D606" s="2">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>1136</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>399</v>
+        <v>224</v>
       </c>
       <c r="G606" s="9">
-        <v>46274.0</v>
+        <v>46437.0</v>
       </c>
     </row>
     <row r="607">
@@ -17546,154 +17540,132 @@
         <v>1137</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D607" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>1138</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>399</v>
+        <v>1139</v>
       </c>
       <c r="G607" s="9">
-        <v>46274.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>535</v>
+        <v>112</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D608" s="2">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="F608" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G608" s="9">
-        <v>46274.0</v>
+        <v>1141</v>
+      </c>
+      <c r="F608" s="3"/>
+      <c r="G608" s="9"/>
+      <c r="H608" s="2" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D609" s="2">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="F609" s="3"/>
       <c r="G609" s="9"/>
+      <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D610" s="2">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G610" s="9">
-        <v>46437.0</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="G610" s="9"/>
+      <c r="H610" s="2"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D611" s="2">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="F611" s="3" t="s">
-        <v>1146</v>
+        <v>16</v>
       </c>
       <c r="G611" s="9">
-        <v>46516.0</v>
-      </c>
+        <v>46403.0</v>
+      </c>
+      <c r="H611" s="2"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D612" s="2">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="F612" s="3"/>
       <c r="G612" s="9"/>
       <c r="H612" s="2" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B613" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C613" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D613" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E613" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F613" s="3"/>
-      <c r="G613" s="9"/>
-      <c r="H613" s="2" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
     </row>
   </sheetData>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1155">
   <si>
     <t>ID</t>
   </si>
@@ -3205,12 +3205,6 @@
     <t>M89OB-KR-C</t>
   </si>
   <si>
-    <t>ID1779702021437</t>
-  </si>
-  <si>
-    <t>M89SRL-KR-C</t>
-  </si>
-  <si>
     <t>ID1779719332195</t>
   </si>
   <si>
@@ -3464,6 +3458,24 @@
   </si>
   <si>
     <t>PRSRM</t>
+  </si>
+  <si>
+    <t>ID1780373196844</t>
+  </si>
+  <si>
+    <t>ID1780373223783</t>
+  </si>
+  <si>
+    <t>26#7</t>
+  </si>
+  <si>
+    <t>ID1780373362857</t>
+  </si>
+  <si>
+    <t>NO12S-頁小館_寄庫</t>
+  </si>
+  <si>
+    <t>ID1780373402392</t>
   </si>
 </sst>
 </file>
@@ -9299,7 +9311,7 @@
         <v>11</v>
       </c>
       <c r="D238" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>537</v>
@@ -11301,7 +11313,7 @@
         <v>11</v>
       </c>
       <c r="D327" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>626</v>
@@ -11327,7 +11339,7 @@
         <v>11</v>
       </c>
       <c r="D328" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>626</v>
@@ -11350,7 +11362,7 @@
         <v>11</v>
       </c>
       <c r="D329" s="2">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>629</v>
@@ -11373,7 +11385,7 @@
         <v>11</v>
       </c>
       <c r="D330" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>630</v>
@@ -16277,7 +16289,7 @@
         <v>11</v>
       </c>
       <c r="D551" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>1028</v>
@@ -16323,7 +16335,7 @@
         <v>11</v>
       </c>
       <c r="D553" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>1035</v>
@@ -16346,7 +16358,7 @@
         <v>11</v>
       </c>
       <c r="D554" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>1037</v>
@@ -16403,9 +16415,7 @@
       <c r="G556" s="9">
         <v>46274.0</v>
       </c>
-      <c r="H556" s="2" t="s">
-        <v>715</v>
-      </c>
+      <c r="H556" s="2"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
@@ -16660,7 +16670,7 @@
         <v>1064</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>11</v>
@@ -16672,10 +16682,10 @@
         <v>1065</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>628</v>
+        <v>399</v>
       </c>
       <c r="G568" s="9">
-        <v>46261.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="569">
@@ -16683,22 +16693,22 @@
         <v>1066</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D569" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E569" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F569" s="3" t="s">
         <v>1067</v>
       </c>
-      <c r="F569" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="G569" s="9">
-        <v>46769.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="570">
@@ -16715,13 +16725,13 @@
         <v>14.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>717</v>
+        <v>1069</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G570" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="571">
@@ -16738,10 +16748,10 @@
         <v>14.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1071</v>
+        <v>713</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G571" s="9">
         <v>46820.0</v>
@@ -16749,7 +16759,7 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>112</v>
@@ -16761,36 +16771,36 @@
         <v>14.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>713</v>
+        <v>602</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G572" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D573" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>602</v>
+        <v>891</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G573" s="9">
-        <v>46998.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="574">
@@ -16807,18 +16817,18 @@
         <v>2.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>891</v>
+        <v>1075</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G574" s="9">
-        <v>46484.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>32</v>
@@ -16830,18 +16840,18 @@
         <v>2.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G575" s="9">
-        <v>46432.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>32</v>
@@ -16853,13 +16863,13 @@
         <v>2.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1081</v>
+        <v>458</v>
       </c>
       <c r="G576" s="9">
-        <v>46877.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="577">
@@ -16879,15 +16889,13 @@
         <v>1083</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G577" s="9">
-        <v>46704.0</v>
-      </c>
+        <v>1084</v>
+      </c>
+      <c r="G577" s="9"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>32</v>
@@ -16899,12 +16907,11 @@
         <v>2.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G578" s="9"/>
+        <v>1084</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
@@ -16920,15 +16927,15 @@
         <v>2.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1088</v>
+        <v>875</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>32</v>
@@ -16940,15 +16947,15 @@
         <v>2.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>875</v>
+        <v>585</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>32</v>
@@ -16960,15 +16967,15 @@
         <v>2.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>585</v>
+        <v>1086</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>32</v>
@@ -16980,10 +16987,10 @@
         <v>2.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="583">
@@ -17003,7 +17010,10 @@
         <v>1093</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1086</v>
+        <v>594</v>
+      </c>
+      <c r="G583" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="584">
@@ -17011,68 +17021,68 @@
         <v>1094</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D584" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>1095</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>594</v>
+        <v>1096</v>
       </c>
       <c r="G584" s="9">
-        <v>46766.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D585" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E585" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F585" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="B585" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C585" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D585" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E585" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F585" s="3" t="s">
-        <v>1098</v>
-      </c>
       <c r="G585" s="9">
-        <v>46877.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D586" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E586" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="B586" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C586" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D586" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E586" s="2" t="s">
-        <v>848</v>
-      </c>
       <c r="F586" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G586" s="9">
-        <v>46641.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="587">
@@ -17086,16 +17096,14 @@
         <v>11</v>
       </c>
       <c r="D587" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>1101</v>
       </c>
-      <c r="F587" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G587" s="9">
-        <v>46743.0</v>
+      <c r="F587" s="4"/>
+      <c r="H587" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="588">
@@ -17109,12 +17117,17 @@
         <v>11</v>
       </c>
       <c r="D588" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="E588" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="F588" s="3" t="s">
         <v>1103</v>
       </c>
-      <c r="F588" s="4"/>
+      <c r="G588" s="9">
+        <v>46663.0</v>
+      </c>
       <c r="H588" s="2" t="s">
         <v>133</v>
       </c>
@@ -17124,22 +17137,22 @@
         <v>1104</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D589" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>810</v>
+        <v>583</v>
       </c>
       <c r="F589" s="3" t="s">
         <v>1105</v>
       </c>
       <c r="G589" s="9">
-        <v>46663.0</v>
+        <v>46437.0</v>
       </c>
       <c r="H589" s="2" t="s">
         <v>133</v>
@@ -17150,25 +17163,22 @@
         <v>1106</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D590" s="2">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>583</v>
+        <v>1107</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="G590" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H590" s="2" t="s">
-        <v>133</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="591">
@@ -17182,21 +17192,21 @@
         <v>11</v>
       </c>
       <c r="D591" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1109</v>
+        <v>662</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G591" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>112</v>
@@ -17208,10 +17218,10 @@
         <v>11.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>662</v>
+        <v>1110</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G592" s="9">
         <v>46530.0</v>
@@ -17225,19 +17235,19 @@
         <v>112</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D593" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>1112</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G593" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="594">
@@ -17257,10 +17267,10 @@
         <v>1114</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G594" s="9">
-        <v>46481.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="595">
@@ -17280,10 +17290,10 @@
         <v>1116</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G595" s="9">
-        <v>46877.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="596">
@@ -17303,10 +17313,10 @@
         <v>1118</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G596" s="9">
-        <v>46872.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="597">
@@ -17326,10 +17336,10 @@
         <v>1120</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G597" s="9">
-        <v>46734.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="598">
@@ -17349,10 +17359,10 @@
         <v>1122</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G598" s="9">
-        <v>46481.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="599">
@@ -17372,10 +17382,10 @@
         <v>1124</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G599" s="9">
-        <v>46872.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="600">
@@ -17386,42 +17396,42 @@
         <v>112</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D600" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1126</v>
+        <v>848</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G600" s="9">
-        <v>46877.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C601" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D601" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E601" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="B601" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C601" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D601" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E601" s="2" t="s">
-        <v>848</v>
-      </c>
       <c r="F601" s="3" t="s">
-        <v>1098</v>
+        <v>399</v>
       </c>
       <c r="G601" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="602">
@@ -17458,10 +17468,10 @@
         <v>11</v>
       </c>
       <c r="D603" s="2">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1131</v>
+        <v>656</v>
       </c>
       <c r="F603" s="3" t="s">
         <v>399</v>
@@ -17472,45 +17482,45 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C604" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D604" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E604" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="B604" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C604" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D604" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E604" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F604" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G604" s="9">
-        <v>46274.0</v>
-      </c>
+      <c r="F604" s="3"/>
+      <c r="G604" s="9"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
         <v>1133</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D605" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="F605" s="3"/>
-      <c r="G605" s="9"/>
+      <c r="F605" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G605" s="9">
+        <v>46437.0</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
@@ -17523,21 +17533,21 @@
         <v>27</v>
       </c>
       <c r="D606" s="2">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>1136</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>224</v>
+        <v>1137</v>
       </c>
       <c r="G606" s="9">
-        <v>46437.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>112</v>
@@ -17546,57 +17556,56 @@
         <v>27</v>
       </c>
       <c r="D607" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F607" s="3" t="s">
         <v>1139</v>
       </c>
-      <c r="G607" s="9">
-        <v>46516.0</v>
+      <c r="F607" s="3"/>
+      <c r="G607" s="9"/>
+      <c r="H607" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D608" s="2">
-        <v>22.0</v>
+        <v>6.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F608" s="3"/>
       <c r="G608" s="9"/>
-      <c r="H608" s="2" t="s">
-        <v>1142</v>
-      </c>
+      <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
         <v>1143</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D609" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E609" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="F609" s="3"/>
+      <c r="F609" s="3" t="s">
+        <v>418</v>
+      </c>
       <c r="G609" s="9"/>
       <c r="H609" s="2"/>
     </row>
@@ -17605,21 +17614,23 @@
         <v>1145</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D610" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>1146</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G610" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="G610" s="9">
+        <v>46403.0</v>
+      </c>
       <c r="H610" s="2"/>
     </row>
     <row r="611">
@@ -17633,40 +17644,108 @@
         <v>11</v>
       </c>
       <c r="D611" s="2">
-        <v>4.0</v>
+        <v>21.0</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>1148</v>
       </c>
-      <c r="F611" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G611" s="9">
-        <v>46403.0</v>
-      </c>
-      <c r="H611" s="2"/>
+      <c r="F611" s="3"/>
+      <c r="G611" s="9"/>
+      <c r="H611" s="2" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
         <v>1149</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D612" s="2">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="E612" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F612" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="G612" s="9">
+        <v>46269.0</v>
+      </c>
+      <c r="H612" s="2"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="F612" s="3"/>
-      <c r="G612" s="9"/>
-      <c r="H612" s="2" t="s">
-        <v>1142</v>
-      </c>
+      <c r="B613" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D613" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E613" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G613" s="9">
+        <v>46290.0</v>
+      </c>
+      <c r="H613" s="2"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D614" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E614" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F614" s="3"/>
+      <c r="G614" s="9"/>
+      <c r="H614" s="2"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D615" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E615" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F615" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G615" s="9">
+        <v>46290.0</v>
+      </c>
+      <c r="H615" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2903" uniqueCount="1160">
   <si>
     <t>ID</t>
   </si>
@@ -3476,6 +3476,21 @@
   </si>
   <si>
     <t>ID1780373402392</t>
+  </si>
+  <si>
+    <t>ID1780447702749</t>
+  </si>
+  <si>
+    <t>GF-CKM-TY</t>
+  </si>
+  <si>
+    <t>1150601K</t>
+  </si>
+  <si>
+    <t>ID1780447833399</t>
+  </si>
+  <si>
+    <t>1150602K</t>
   </si>
 </sst>
 </file>
@@ -17747,6 +17762,54 @@
       </c>
       <c r="H615" s="2"/>
     </row>
+    <row r="616">
+      <c r="A616" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D616" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E616" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F616" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G616" s="9">
+        <v>46883.0</v>
+      </c>
+      <c r="H616" s="2"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D617" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E617" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F617" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G617" s="9">
+        <v>46883.0</v>
+      </c>
+      <c r="H617" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2903" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="1178">
   <si>
     <t>ID</t>
   </si>
@@ -1768,312 +1768,312 @@
     <t>1150112K</t>
   </si>
   <si>
+    <t>M89RER-KR</t>
+  </si>
+  <si>
+    <t>1150223K</t>
+  </si>
+  <si>
+    <t>1150331K</t>
+  </si>
+  <si>
+    <t>PRRER-YK</t>
+  </si>
+  <si>
+    <t>PRSRM-GO</t>
+  </si>
+  <si>
+    <t>1150408K</t>
+  </si>
+  <si>
+    <t>60S(5入)(60P)(煙燻鴨胸）</t>
+  </si>
+  <si>
+    <t>PRRER-GO-K</t>
+  </si>
+  <si>
+    <t>1150414K</t>
+  </si>
+  <si>
+    <t>PRCER-GO-十字切</t>
+  </si>
+  <si>
+    <t>1150409S</t>
+  </si>
+  <si>
+    <t>JOLT</t>
+  </si>
+  <si>
+    <t>BLR20-HF</t>
+  </si>
+  <si>
+    <t>BLR24-HF</t>
+  </si>
+  <si>
+    <t>BLR22-HF (7入)</t>
+  </si>
+  <si>
+    <t>PRSRMB-GO</t>
+  </si>
+  <si>
+    <t>PRTDL-GO</t>
+  </si>
+  <si>
+    <t>QC12</t>
+  </si>
+  <si>
+    <t>HTR-KR</t>
+  </si>
+  <si>
+    <t>1140903K</t>
+  </si>
+  <si>
+    <t>1131104K</t>
+  </si>
+  <si>
+    <t>1131031K</t>
+  </si>
+  <si>
+    <t>GF-TUE-TY</t>
+  </si>
+  <si>
+    <t>1140922K</t>
+  </si>
+  <si>
+    <t>CHSRL-YK</t>
+  </si>
+  <si>
+    <t>1141031K</t>
+  </si>
+  <si>
+    <t>SANS500</t>
+  </si>
+  <si>
+    <t>木盒子</t>
+  </si>
+  <si>
+    <t>IAWV100</t>
+  </si>
+  <si>
+    <t>CF6S90</t>
+  </si>
+  <si>
+    <t>IA5A90</t>
+  </si>
+  <si>
+    <t>JLPQO35</t>
+  </si>
+  <si>
+    <t>IAWO251</t>
+  </si>
+  <si>
+    <t>JLOG37</t>
+  </si>
+  <si>
+    <t>JLCP34</t>
+  </si>
+  <si>
+    <t>JLWGO34</t>
+  </si>
+  <si>
+    <t>JLPQG35</t>
+  </si>
+  <si>
+    <t>JLWGON</t>
+  </si>
+  <si>
+    <t>JLWBO</t>
+  </si>
+  <si>
+    <t>JLPQO</t>
+  </si>
+  <si>
+    <t>ACRER-C-TY</t>
+  </si>
+  <si>
+    <t>26#6</t>
+  </si>
+  <si>
+    <t>26#5</t>
+  </si>
+  <si>
+    <t>ACSRL-C-TY</t>
+  </si>
+  <si>
+    <t>ACRPC-C-TY</t>
+  </si>
+  <si>
+    <t>CHTDL-C-YK</t>
+  </si>
+  <si>
+    <t>26#13</t>
+  </si>
+  <si>
+    <t>CHSRM-C-SS</t>
+  </si>
+  <si>
+    <t>26#30</t>
+  </si>
+  <si>
+    <t>PRRER-C-SS</t>
+  </si>
+  <si>
+    <t>26#39</t>
+  </si>
+  <si>
+    <t>PRTDL-C-SS</t>
+  </si>
+  <si>
+    <t>26#34</t>
+  </si>
+  <si>
+    <t>PRSTL-C-YK</t>
+  </si>
+  <si>
+    <t>26#8</t>
+  </si>
+  <si>
+    <t>無庫位</t>
+  </si>
+  <si>
+    <t>34B(34-36)</t>
+  </si>
+  <si>
+    <t>JUJM(退貨)</t>
+  </si>
+  <si>
+    <t>12Q</t>
+  </si>
+  <si>
+    <t>1150415K</t>
+  </si>
+  <si>
+    <t>1150413K</t>
+  </si>
+  <si>
+    <t>AD3</t>
+  </si>
+  <si>
+    <t>ADJM (豬肉)(5入)</t>
+  </si>
+  <si>
+    <t>SPT-10入</t>
+  </si>
+  <si>
+    <t>PRSRL-420-460-GO</t>
+  </si>
+  <si>
+    <t>PRRER-上林規-YK</t>
+  </si>
+  <si>
+    <t>PRRER-3cm-SS</t>
+  </si>
+  <si>
+    <t>PRRER-900-960-SS</t>
+  </si>
+  <si>
+    <t>ACRER-280-320-TY</t>
+  </si>
+  <si>
+    <t>PRRER-一開三-SS</t>
+  </si>
+  <si>
+    <t>PRRERB-GO</t>
+  </si>
+  <si>
+    <t>PRCER-GO</t>
+  </si>
+  <si>
+    <t>M89CER-橫十字切_KR</t>
+  </si>
+  <si>
+    <t>1150122S</t>
+  </si>
+  <si>
+    <t>[異常] 1p</t>
+  </si>
+  <si>
+    <t>GMB(骨）</t>
+  </si>
+  <si>
+    <t>GMB</t>
+  </si>
+  <si>
+    <t>1150210S</t>
+  </si>
+  <si>
+    <t>1150415S</t>
+  </si>
+  <si>
+    <t>JOB(26b)</t>
+  </si>
+  <si>
+    <t>ACOB-YK(8入)</t>
+  </si>
+  <si>
+    <t>1150417K</t>
+  </si>
+  <si>
+    <t>ID1776755440734</t>
+  </si>
+  <si>
+    <t>1150410K</t>
+  </si>
+  <si>
+    <t>ID1776755702626</t>
+  </si>
+  <si>
+    <t>PRCER-YK</t>
+  </si>
+  <si>
+    <t>1150409K</t>
+  </si>
+  <si>
+    <t>ID1776756005407</t>
+  </si>
+  <si>
+    <t>CHRER-280-320-SS</t>
+  </si>
+  <si>
+    <t>ID1776830939143</t>
+  </si>
+  <si>
+    <t>電商紙袋</t>
+  </si>
+  <si>
+    <t>ID1776831008384</t>
+  </si>
+  <si>
+    <t>手提袋 模型</t>
+  </si>
+  <si>
+    <t>ID1776831054260</t>
+  </si>
+  <si>
+    <t>火腿架</t>
+  </si>
+  <si>
+    <t>ID1776831067623</t>
+  </si>
+  <si>
+    <t>ID1776831077383</t>
+  </si>
+  <si>
+    <t>ID1776831088970</t>
+  </si>
+  <si>
+    <t>ID1776831133943</t>
+  </si>
+  <si>
+    <t>紙箱</t>
+  </si>
+  <si>
+    <t>ID1776917744376</t>
+  </si>
+  <si>
     <t>M67TDL-KR</t>
   </si>
   <si>
-    <t>M89RER-KR</t>
-  </si>
-  <si>
-    <t>1150223K</t>
-  </si>
-  <si>
-    <t>1150331K</t>
-  </si>
-  <si>
-    <t>PRRER-YK</t>
-  </si>
-  <si>
-    <t>PRSRM-GO</t>
-  </si>
-  <si>
-    <t>1150408K</t>
-  </si>
-  <si>
-    <t>60S(5入)(60P)(煙燻鴨胸）</t>
-  </si>
-  <si>
-    <t>PRRER-GO-K</t>
-  </si>
-  <si>
-    <t>1150414K</t>
-  </si>
-  <si>
-    <t>PRCER-GO-十字切</t>
-  </si>
-  <si>
-    <t>1150409S</t>
-  </si>
-  <si>
-    <t>JOLT</t>
-  </si>
-  <si>
-    <t>BLR20-HF</t>
-  </si>
-  <si>
-    <t>BLR24-HF</t>
-  </si>
-  <si>
-    <t>BLR22-HF (7入)</t>
-  </si>
-  <si>
-    <t>PRSRMB-GO</t>
-  </si>
-  <si>
-    <t>PRTDL-GO</t>
-  </si>
-  <si>
-    <t>QC12</t>
-  </si>
-  <si>
-    <t>HTR-KR</t>
-  </si>
-  <si>
-    <t>1140903K</t>
-  </si>
-  <si>
-    <t>1131104K</t>
-  </si>
-  <si>
-    <t>1131031K</t>
-  </si>
-  <si>
-    <t>GF-TUE-TY</t>
-  </si>
-  <si>
-    <t>1140922K</t>
-  </si>
-  <si>
-    <t>CHSRL-YK</t>
-  </si>
-  <si>
-    <t>1141031K</t>
-  </si>
-  <si>
-    <t>SANS500</t>
-  </si>
-  <si>
-    <t>木盒子</t>
-  </si>
-  <si>
-    <t>IAWV100</t>
-  </si>
-  <si>
-    <t>CF6S90</t>
-  </si>
-  <si>
-    <t>IA5A90</t>
-  </si>
-  <si>
-    <t>JLPQO35</t>
-  </si>
-  <si>
-    <t>IAWO251</t>
-  </si>
-  <si>
-    <t>JLOG37</t>
-  </si>
-  <si>
-    <t>JLCP34</t>
-  </si>
-  <si>
-    <t>JLWGO34</t>
-  </si>
-  <si>
-    <t>JLPQG35</t>
-  </si>
-  <si>
-    <t>JLWGON</t>
-  </si>
-  <si>
-    <t>JLWBO</t>
-  </si>
-  <si>
-    <t>JLPQO</t>
-  </si>
-  <si>
-    <t>ACRER-C-TY</t>
-  </si>
-  <si>
-    <t>26#6</t>
-  </si>
-  <si>
-    <t>26#5</t>
-  </si>
-  <si>
-    <t>ACSRL-C-TY</t>
-  </si>
-  <si>
-    <t>ACRPC-C-TY</t>
-  </si>
-  <si>
-    <t>CHTDL-C-YK</t>
-  </si>
-  <si>
-    <t>26#13</t>
-  </si>
-  <si>
-    <t>CHSRM-C-SS</t>
-  </si>
-  <si>
-    <t>26#30</t>
-  </si>
-  <si>
-    <t>PRRER-C-SS</t>
-  </si>
-  <si>
-    <t>26#39</t>
-  </si>
-  <si>
-    <t>PRTDL-C-SS</t>
-  </si>
-  <si>
-    <t>26#34</t>
-  </si>
-  <si>
-    <t>PRSTL-C-YK</t>
-  </si>
-  <si>
-    <t>26#8</t>
-  </si>
-  <si>
-    <t>無庫位</t>
-  </si>
-  <si>
-    <t>34B(34-36)</t>
-  </si>
-  <si>
-    <t>JUJM(退貨)</t>
-  </si>
-  <si>
-    <t>12Q</t>
-  </si>
-  <si>
-    <t>1150415K</t>
-  </si>
-  <si>
-    <t>1150413K</t>
-  </si>
-  <si>
-    <t>AD3</t>
-  </si>
-  <si>
-    <t>ADJM (豬肉)(5入)</t>
-  </si>
-  <si>
-    <t>SPT-10入</t>
-  </si>
-  <si>
-    <t>PRSRL-420-460-GO</t>
-  </si>
-  <si>
-    <t>PRRER-上林規-YK</t>
-  </si>
-  <si>
-    <t>PRRER-3cm-SS</t>
-  </si>
-  <si>
-    <t>PRRER-900-960-SS</t>
-  </si>
-  <si>
-    <t>ACRER-280-320-TY</t>
-  </si>
-  <si>
-    <t>PRRER-一開三-SS</t>
-  </si>
-  <si>
-    <t>PRRERB-GO</t>
-  </si>
-  <si>
-    <t>PRCER-GO</t>
-  </si>
-  <si>
-    <t>M89CER-橫十字切_KR</t>
-  </si>
-  <si>
-    <t>1150122S</t>
-  </si>
-  <si>
-    <t>[異常] 1p</t>
-  </si>
-  <si>
-    <t>GMB(骨）</t>
-  </si>
-  <si>
-    <t>GMB</t>
-  </si>
-  <si>
-    <t>1150210S</t>
-  </si>
-  <si>
-    <t>1150415S</t>
-  </si>
-  <si>
-    <t>JOB(26b)</t>
-  </si>
-  <si>
-    <t>ACOB-YK(8入)</t>
-  </si>
-  <si>
-    <t>1150417K</t>
-  </si>
-  <si>
-    <t>ID1776755440734</t>
-  </si>
-  <si>
-    <t>1150410K</t>
-  </si>
-  <si>
-    <t>ID1776755702626</t>
-  </si>
-  <si>
-    <t>PRCER-YK</t>
-  </si>
-  <si>
-    <t>1150409K</t>
-  </si>
-  <si>
-    <t>ID1776756005407</t>
-  </si>
-  <si>
-    <t>CHRER-280-320-SS</t>
-  </si>
-  <si>
-    <t>ID1776830939143</t>
-  </si>
-  <si>
-    <t>電商紙袋</t>
-  </si>
-  <si>
-    <t>ID1776831008384</t>
-  </si>
-  <si>
-    <t>手提袋 模型</t>
-  </si>
-  <si>
-    <t>ID1776831054260</t>
-  </si>
-  <si>
-    <t>火腿架</t>
-  </si>
-  <si>
-    <t>ID1776831067623</t>
-  </si>
-  <si>
-    <t>ID1776831077383</t>
-  </si>
-  <si>
-    <t>ID1776831088970</t>
-  </si>
-  <si>
-    <t>ID1776831133943</t>
-  </si>
-  <si>
-    <t>紙箱</t>
-  </si>
-  <si>
-    <t>ID1776917744376</t>
-  </si>
-  <si>
     <t>ID1776917966118</t>
   </si>
   <si>
@@ -3491,6 +3491,60 @@
   </si>
   <si>
     <t>1150602K</t>
+  </si>
+  <si>
+    <t>ID1780472277576</t>
+  </si>
+  <si>
+    <t>L14 (C規）預定</t>
+  </si>
+  <si>
+    <t>ID1780472318713</t>
+  </si>
+  <si>
+    <t>34B (預定)</t>
+  </si>
+  <si>
+    <t>ID1780472410260</t>
+  </si>
+  <si>
+    <t>37TQ(預定)</t>
+  </si>
+  <si>
+    <t>ID1780472441121</t>
+  </si>
+  <si>
+    <t>36-38B(預定)</t>
+  </si>
+  <si>
+    <t>ID1780472484781</t>
+  </si>
+  <si>
+    <t>10Q(預定)</t>
+  </si>
+  <si>
+    <t>ID1780473214746</t>
+  </si>
+  <si>
+    <t>M9TDL-KR(預定）</t>
+  </si>
+  <si>
+    <t>1140627K</t>
+  </si>
+  <si>
+    <t>ID1780473327368</t>
+  </si>
+  <si>
+    <t>1141027K</t>
+  </si>
+  <si>
+    <t>ID1780473345775</t>
+  </si>
+  <si>
+    <t>ID1780473683215</t>
+  </si>
+  <si>
+    <t>TS（預定）</t>
   </si>
 </sst>
 </file>
@@ -10355,7 +10409,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1">
-        <v>1.775632588361E12</v>
+        <v>1.775632615999E12</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>32</v>
@@ -10370,15 +10424,15 @@
         <v>585</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>359</v>
+        <v>586</v>
       </c>
       <c r="G285" s="9">
-        <v>46255.0</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1">
-        <v>1.775632615999E12</v>
+        <v>1.775632807505E12</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>32</v>
@@ -10387,21 +10441,21 @@
         <v>33</v>
       </c>
       <c r="D286" s="2">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>587</v>
       </c>
       <c r="G286" s="9">
-        <v>46725.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1">
-        <v>1.775632807505E12</v>
+        <v>1.775632834905E12</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>32</v>
@@ -10413,143 +10467,143 @@
         <v>8.0</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G287" s="9">
-        <v>46789.0</v>
+        <v>46757.0</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1">
-        <v>1.775632834905E12</v>
+        <v>1.775695916181E12</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D288" s="2">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>589</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G288" s="9">
-        <v>46757.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1">
-        <v>1.775695916181E12</v>
+        <v>1.775734585272E12</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D289" s="2">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="F289" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="G289" s="9">
-        <v>46947.0</v>
+        <v>555</v>
+      </c>
+      <c r="F289" s="3">
+        <v>11503.0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1">
-        <v>1.775734585272E12</v>
+        <v>1.775735093999E12</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D290" s="2">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>555</v>
+        <v>591</v>
       </c>
       <c r="F290" s="3">
-        <v>11503.0</v>
-      </c>
+        <v>11504.0</v>
+      </c>
+      <c r="H290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" s="1">
-        <v>1.775735093999E12</v>
+        <v>1.775786151238E12</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D291" s="2">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="F291" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="H291" s="2"/>
+      <c r="F291" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="G291" s="9">
+        <v>46949.0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1">
-        <v>1.775786151238E12</v>
+        <v>1.775786456959E12</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D292" s="2">
         <v>18.0</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G292" s="9">
-        <v>46949.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1">
-        <v>1.775786456959E12</v>
+        <v>1.775786585712E12</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D293" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>595</v>
+        <v>66</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>596</v>
+        <v>493</v>
       </c>
       <c r="G293" s="9">
         <v>46794.0</v>
@@ -10557,22 +10611,22 @@
     </row>
     <row r="294">
       <c r="A294" s="1">
-        <v>1.775786585712E12</v>
+        <v>1.775799916832E12</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D294" s="2">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>66</v>
+        <v>596</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>493</v>
+        <v>16</v>
       </c>
       <c r="G294" s="9">
         <v>46794.0</v>
@@ -10580,16 +10634,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1">
-        <v>1.775799916832E12</v>
+        <v>1.775818206218E12</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D295" s="2">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>597</v>
@@ -10598,12 +10652,12 @@
         <v>16</v>
       </c>
       <c r="G295" s="9">
-        <v>46794.0</v>
+        <v>46403.0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1">
-        <v>1.775818206218E12</v>
+        <v>1.775818524868E12</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>32</v>
@@ -10612,7 +10666,7 @@
         <v>11</v>
       </c>
       <c r="D296" s="2">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>598</v>
@@ -10621,12 +10675,12 @@
         <v>16</v>
       </c>
       <c r="G296" s="9">
-        <v>46403.0</v>
+        <v>46764.0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1">
-        <v>1.775818524868E12</v>
+        <v>1.775818556986E12</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>32</v>
@@ -10644,36 +10698,36 @@
         <v>16</v>
       </c>
       <c r="G297" s="9">
-        <v>46764.0</v>
-      </c>
+        <v>46769.0</v>
+      </c>
+      <c r="H297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" s="1">
-        <v>1.775818556986E12</v>
+        <v>1.776059127998E12</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D298" s="2">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>600</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G298" s="9">
-        <v>46769.0</v>
-      </c>
-      <c r="H298" s="2"/>
+        <v>46758.0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1">
-        <v>1.776059127998E12</v>
+        <v>1.77605914796E12</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>112</v>
@@ -10691,35 +10745,33 @@
         <v>493</v>
       </c>
       <c r="G299" s="9">
-        <v>46758.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1">
-        <v>1.77605914796E12</v>
+        <v>1.776068065666E12</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D300" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="F300" s="3" t="s">
-        <v>493</v>
-      </c>
+      <c r="F300" s="4"/>
       <c r="G300" s="9">
-        <v>46794.0</v>
+        <v>46426.0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1">
-        <v>1.776068065666E12</v>
+        <v>1.776137953787E12</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>32</v>
@@ -10728,19 +10780,21 @@
         <v>11</v>
       </c>
       <c r="D301" s="2">
-        <v>18.0</v>
+        <v>9.0</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="F301" s="4"/>
+      <c r="F301" s="3" t="s">
+        <v>604</v>
+      </c>
       <c r="G301" s="9">
-        <v>46426.0</v>
+        <v>46577.0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1">
-        <v>1.776137953787E12</v>
+        <v>1.776137996426E12</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>32</v>
@@ -10752,18 +10806,18 @@
         <v>9.0</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>605</v>
       </c>
       <c r="G302" s="9">
-        <v>46577.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1">
-        <v>1.776137996426E12</v>
+        <v>1.776138016571E12</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>32</v>
@@ -10775,7 +10829,7 @@
         <v>9.0</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>606</v>
@@ -10786,7 +10840,7 @@
     </row>
     <row r="304">
       <c r="A304" s="1">
-        <v>1.776138016571E12</v>
+        <v>1.776138041953E12</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>32</v>
@@ -10798,18 +10852,18 @@
         <v>9.0</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F304" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
+      </c>
+      <c r="F304" s="3">
+        <v>1140221.0</v>
       </c>
       <c r="G304" s="9">
-        <v>46254.0</v>
+        <v>46368.0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1">
-        <v>1.776138041953E12</v>
+        <v>1.776138069076E12</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>32</v>
@@ -10821,18 +10875,18 @@
         <v>9.0</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F305" s="3">
-        <v>1140221.0</v>
+        <v>603</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="G305" s="9">
-        <v>46368.0</v>
+        <v>46285.0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1">
-        <v>1.776138069076E12</v>
+        <v>1.776138139688E12</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>32</v>
@@ -10841,131 +10895,134 @@
         <v>11</v>
       </c>
       <c r="D306" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>371</v>
+        <v>608</v>
       </c>
       <c r="G306" s="9">
-        <v>46285.0</v>
+        <v>46596.0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1">
-        <v>1.776138139688E12</v>
+        <v>1.776138981107E12</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D307" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G307" s="9">
-        <v>46596.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1">
-        <v>1.776138981107E12</v>
+        <v>1.77613942855E12</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D308" s="2">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>611</v>
+        <v>142</v>
       </c>
       <c r="G308" s="9">
-        <v>46641.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1">
-        <v>1.77613942855E12</v>
+        <v>1.776146651219E12</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D309" s="2">
         <v>2.0</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>142</v>
+        <v>388</v>
       </c>
       <c r="G309" s="9">
-        <v>46789.0</v>
+        <v>47286.0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1">
-        <v>1.776146651219E12</v>
+        <v>1.776146781002E12</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D310" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="F310" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="G310" s="9">
-        <v>47286.0</v>
-      </c>
+      <c r="F310" s="4"/>
     </row>
     <row r="311">
       <c r="A311" s="1">
-        <v>1.776146781002E12</v>
+        <v>1.776146881019E12</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D311" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="F311" s="4"/>
+      <c r="F311" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G311" s="9">
+        <v>46542.0</v>
+      </c>
+      <c r="H311" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1">
-        <v>1.776146881019E12</v>
+        <v>1.7761469355E12</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>10</v>
@@ -10980,10 +11037,10 @@
         <v>614</v>
       </c>
       <c r="F312" s="3" t="s">
-        <v>16</v>
+        <v>441</v>
       </c>
       <c r="G312" s="9">
-        <v>46542.0</v>
+        <v>46987.0</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>52</v>
@@ -10991,7 +11048,7 @@
     </row>
     <row r="313">
       <c r="A313" s="1">
-        <v>1.7761469355E12</v>
+        <v>1.776146969199E12</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>10</v>
@@ -11006,10 +11063,7 @@
         <v>615</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G313" s="9">
-        <v>46987.0</v>
+        <v>16</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>52</v>
@@ -11017,7 +11071,7 @@
     </row>
     <row r="314">
       <c r="A314" s="1">
-        <v>1.776146969199E12</v>
+        <v>1.776147024701E12</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>10</v>
@@ -11029,18 +11083,21 @@
         <v>5.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>616</v>
+        <v>18</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G314" s="9">
+        <v>47356.0</v>
+      </c>
       <c r="H314" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1">
-        <v>1.776147024701E12</v>
+        <v>1.776147054791E12</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>10</v>
@@ -11055,10 +11112,10 @@
         <v>18</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>16</v>
+        <v>441</v>
       </c>
       <c r="G315" s="9">
-        <v>47356.0</v>
+        <v>46987.0</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>52</v>
@@ -11066,7 +11123,7 @@
     </row>
     <row r="316">
       <c r="A316" s="1">
-        <v>1.776147054791E12</v>
+        <v>1.776147153167E12</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>10</v>
@@ -11075,24 +11132,18 @@
         <v>11</v>
       </c>
       <c r="D316" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>18</v>
+        <v>615</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="G316" s="9">
-        <v>46987.0</v>
-      </c>
-      <c r="H316" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1">
-        <v>1.776147153167E12</v>
+        <v>1.776147237339E12</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>10</v>
@@ -11109,10 +11160,13 @@
       <c r="F317" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G317" s="9">
+        <v>46798.0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1">
-        <v>1.776147237339E12</v>
+        <v>1.776147270323E12</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>10</v>
@@ -11121,7 +11175,7 @@
         <v>11</v>
       </c>
       <c r="D318" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>617</v>
@@ -11130,12 +11184,12 @@
         <v>16</v>
       </c>
       <c r="G318" s="9">
-        <v>46798.0</v>
+        <v>46838.0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1">
-        <v>1.776147270323E12</v>
+        <v>1.776147321508E12</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>10</v>
@@ -11144,21 +11198,21 @@
         <v>11</v>
       </c>
       <c r="D319" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>618</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G319" s="9">
-        <v>46838.0</v>
+        <v>46402.0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1">
-        <v>1.776147321508E12</v>
+        <v>1.776147583566E12</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>10</v>
@@ -11176,12 +11230,12 @@
         <v>24</v>
       </c>
       <c r="G320" s="9">
-        <v>46402.0</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1">
-        <v>1.776147583566E12</v>
+        <v>1.776147678627E12</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>10</v>
@@ -11199,12 +11253,12 @@
         <v>24</v>
       </c>
       <c r="G321" s="9">
-        <v>46204.0</v>
+        <v>46388.0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1">
-        <v>1.776147678627E12</v>
+        <v>1.776147764862E12</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>10</v>
@@ -11222,12 +11276,12 @@
         <v>24</v>
       </c>
       <c r="G322" s="9">
-        <v>46388.0</v>
+        <v>46310.0</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1">
-        <v>1.776147764862E12</v>
+        <v>1.776147814402E12</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>10</v>
@@ -11236,21 +11290,21 @@
         <v>11</v>
       </c>
       <c r="D323" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>622</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G323" s="9">
-        <v>46310.0</v>
+        <v>46283.0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1">
-        <v>1.776147814402E12</v>
+        <v>1.776147841228E12</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>10</v>
@@ -11268,12 +11322,12 @@
         <v>16</v>
       </c>
       <c r="G324" s="9">
-        <v>46283.0</v>
+        <v>46796.0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1">
-        <v>1.776147841228E12</v>
+        <v>1.776147860658E12</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>10</v>
@@ -11291,35 +11345,38 @@
         <v>16</v>
       </c>
       <c r="G325" s="9">
-        <v>46796.0</v>
+        <v>46802.0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1">
-        <v>1.776147860658E12</v>
+        <v>1.776148337734E12</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>10</v>
+        <v>536</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D326" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>625</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>16</v>
+        <v>626</v>
       </c>
       <c r="G326" s="9">
-        <v>46802.0</v>
+        <v>46269.0</v>
+      </c>
+      <c r="I326" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1">
-        <v>1.776148337734E12</v>
+        <v>1.776148418097E12</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>536</v>
@@ -11328,24 +11385,21 @@
         <v>11</v>
       </c>
       <c r="D327" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>627</v>
       </c>
       <c r="G327" s="9">
-        <v>46269.0</v>
-      </c>
-      <c r="I327" s="2" t="s">
-        <v>233</v>
+        <v>46247.0</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1">
-        <v>1.776148418097E12</v>
+        <v>1.776148449855E12</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>536</v>
@@ -11357,10 +11411,10 @@
         <v>4.0</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G328" s="9">
         <v>46247.0</v>
@@ -11368,7 +11422,7 @@
     </row>
     <row r="329">
       <c r="A329" s="1">
-        <v>1.776148449855E12</v>
+        <v>1.776148475121E12</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>536</v>
@@ -11377,21 +11431,21 @@
         <v>11</v>
       </c>
       <c r="D329" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>629</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G329" s="9">
-        <v>46247.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1">
-        <v>1.776148475121E12</v>
+        <v>1.776148592568E12</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>536</v>
@@ -11400,21 +11454,24 @@
         <v>11</v>
       </c>
       <c r="D330" s="2">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>630</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="G330" s="9">
-        <v>46269.0</v>
+        <v>46234.0</v>
+      </c>
+      <c r="I330" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1">
-        <v>1.776148592568E12</v>
+        <v>1.776148632656E12</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>536</v>
@@ -11423,16 +11480,16 @@
         <v>11</v>
       </c>
       <c r="D331" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G331" s="9">
-        <v>46234.0</v>
+        <v>46202.0</v>
       </c>
       <c r="I331" s="2" t="s">
         <v>233</v>
@@ -11440,7 +11497,7 @@
     </row>
     <row r="332">
       <c r="A332" s="1">
-        <v>1.776148632656E12</v>
+        <v>1.776148710229E12</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>536</v>
@@ -11449,16 +11506,16 @@
         <v>11</v>
       </c>
       <c r="D332" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G332" s="9">
-        <v>46202.0</v>
+        <v>46193.0</v>
       </c>
       <c r="I332" s="2" t="s">
         <v>233</v>
@@ -11466,7 +11523,7 @@
     </row>
     <row r="333">
       <c r="A333" s="1">
-        <v>1.776148710229E12</v>
+        <v>1.776148761624E12</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>536</v>
@@ -11475,16 +11532,16 @@
         <v>11</v>
       </c>
       <c r="D333" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G333" s="9">
-        <v>46193.0</v>
+        <v>46203.0</v>
       </c>
       <c r="I333" s="2" t="s">
         <v>233</v>
@@ -11492,25 +11549,25 @@
     </row>
     <row r="334">
       <c r="A334" s="1">
-        <v>1.776148761624E12</v>
+        <v>1.776149046956E12</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>536</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D334" s="2">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G334" s="9">
-        <v>46203.0</v>
+        <v>46182.0</v>
       </c>
       <c r="I334" s="2" t="s">
         <v>233</v>
@@ -11518,51 +11575,44 @@
     </row>
     <row r="335">
       <c r="A335" s="1">
-        <v>1.776149046956E12</v>
+        <v>1.776149087494E12</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>536</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D335" s="2">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F335" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="G335" s="9">
-        <v>46182.0</v>
-      </c>
-      <c r="I335" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="F335" s="4"/>
     </row>
     <row r="336">
       <c r="A336" s="1">
-        <v>1.776149087494E12</v>
+        <v>1.776169705463E12</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>536</v>
+        <v>112</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D336" s="2">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>641</v>
+        <v>535</v>
       </c>
       <c r="F336" s="4"/>
+      <c r="H336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" s="1">
-        <v>1.776169705463E12</v>
+        <v>1.776301247869E12</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>112</v>
@@ -11571,17 +11621,20 @@
         <v>11</v>
       </c>
       <c r="D337" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>535</v>
+        <v>641</v>
       </c>
       <c r="F337" s="4"/>
+      <c r="G337" s="9">
+        <v>46840.0</v>
+      </c>
       <c r="H337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" s="1">
-        <v>1.776301247869E12</v>
+        <v>1.776301425645E12</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>112</v>
@@ -11590,20 +11643,21 @@
         <v>11</v>
       </c>
       <c r="D338" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="F338" s="4"/>
+      <c r="F338" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="G338" s="9">
-        <v>46840.0</v>
-      </c>
-      <c r="H338" s="2"/>
+        <v>46640.0</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1">
-        <v>1.776301425645E12</v>
+        <v>1.776327582548E12</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>112</v>
@@ -11612,41 +11666,41 @@
         <v>11</v>
       </c>
       <c r="D339" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F339" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G339" s="9">
-        <v>46640.0</v>
+      <c r="F339" s="3">
+        <v>11504.0</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1">
-        <v>1.776327582548E12</v>
+        <v>1.776327623153E12</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D340" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E340" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F340" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="F340" s="3">
-        <v>11504.0</v>
+      <c r="G340" s="9">
+        <v>46949.0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1">
-        <v>1.776327623153E12</v>
+        <v>1.776327677276E12</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>112</v>
@@ -11655,10 +11709,10 @@
         <v>33</v>
       </c>
       <c r="D341" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>645</v>
@@ -11669,30 +11723,28 @@
     </row>
     <row r="342">
       <c r="A342" s="1">
-        <v>1.776327677276E12</v>
+        <v>1.776328486516E12</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D342" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>593</v>
+        <v>646</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="G342" s="9">
-        <v>46949.0</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="H342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" s="1">
-        <v>1.776328486516E12</v>
+        <v>1.776328499394E12</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>112</v>
@@ -11701,7 +11753,7 @@
         <v>25</v>
       </c>
       <c r="D343" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>647</v>
@@ -11709,11 +11761,10 @@
       <c r="F343" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" s="1">
-        <v>1.776328499394E12</v>
+        <v>1.776328514002E12</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>112</v>
@@ -11722,7 +11773,7 @@
         <v>25</v>
       </c>
       <c r="D344" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>648</v>
@@ -11733,7 +11784,7 @@
     </row>
     <row r="345">
       <c r="A345" s="1">
-        <v>1.776328514002E12</v>
+        <v>1.776334155137E12</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>112</v>
@@ -11742,18 +11793,21 @@
         <v>25</v>
       </c>
       <c r="D345" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>649</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>418</v>
+        <v>241</v>
+      </c>
+      <c r="G345" s="9">
+        <v>46537.0</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1">
-        <v>1.776334155137E12</v>
+        <v>1.776334203307E12</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>112</v>
@@ -11765,18 +11819,18 @@
         <v>13.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>650</v>
+        <v>547</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>241</v>
+        <v>476</v>
       </c>
       <c r="G346" s="9">
-        <v>46537.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1">
-        <v>1.776334203307E12</v>
+        <v>1.776334423117E12</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>112</v>
@@ -11785,27 +11839,27 @@
         <v>25</v>
       </c>
       <c r="D347" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>547</v>
+        <v>650</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>476</v>
+        <v>241</v>
       </c>
       <c r="G347" s="9">
-        <v>46530.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1">
-        <v>1.776334423117E12</v>
+        <v>1.776334444257E12</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D348" s="2">
         <v>16.0</v>
@@ -11814,21 +11868,21 @@
         <v>651</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G348" s="9">
-        <v>46479.0</v>
+        <v>46468.0</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1">
-        <v>1.776334444257E12</v>
+        <v>1.776334474615E12</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D349" s="2">
         <v>16.0</v>
@@ -11845,7 +11899,7 @@
     </row>
     <row r="350">
       <c r="A350" s="1">
-        <v>1.776334474615E12</v>
+        <v>1.776334496105E12</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>112</v>
@@ -11859,16 +11913,11 @@
       <c r="E350" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F350" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G350" s="9">
-        <v>46468.0</v>
-      </c>
+      <c r="F350" s="4"/>
     </row>
     <row r="351">
       <c r="A351" s="1">
-        <v>1.776334496105E12</v>
+        <v>1.776334545035E12</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>112</v>
@@ -11882,34 +11931,39 @@
       <c r="E351" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="F351" s="4"/>
+      <c r="F351" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G351" s="9">
+        <v>46468.0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1">
-        <v>1.776334545035E12</v>
+        <v>1.776398955451E12</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D352" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>655</v>
+        <v>570</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>238</v>
+        <v>590</v>
       </c>
       <c r="G352" s="9">
-        <v>46468.0</v>
+        <v>46768.0</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1">
-        <v>1.776398955451E12</v>
+        <v>1.776398987942E12</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>112</v>
@@ -11921,18 +11975,18 @@
         <v>17.0</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>570</v>
+        <v>655</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G353" s="9">
-        <v>46768.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1">
-        <v>1.776398987942E12</v>
+        <v>1.776399071673E12</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>112</v>
@@ -11944,90 +11998,90 @@
         <v>17.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>656</v>
+        <v>574</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G354" s="9">
-        <v>46947.0</v>
+        <v>46771.0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1">
-        <v>1.776399071673E12</v>
+        <v>1.776399111607E12</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D355" s="2">
         <v>17.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>574</v>
+        <v>656</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>591</v>
+        <v>493</v>
       </c>
       <c r="G355" s="9">
-        <v>46771.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1">
-        <v>1.776399111607E12</v>
+        <v>1.776399379582E12</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D356" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>657</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>493</v>
+        <v>658</v>
       </c>
       <c r="G356" s="9">
-        <v>46794.0</v>
+        <v>46691.0</v>
+      </c>
+      <c r="H356" s="2" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1">
-        <v>1.776399379582E12</v>
+        <v>1.776400103874E12</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D357" s="2">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>659</v>
+        <v>145</v>
       </c>
       <c r="G357" s="9">
-        <v>46691.0</v>
-      </c>
-      <c r="H357" s="2" t="s">
-        <v>660</v>
+        <v>46543.0</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1">
-        <v>1.776400103874E12</v>
+        <v>1.776400120665E12</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>112</v>
@@ -12036,21 +12090,21 @@
         <v>25</v>
       </c>
       <c r="D358" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>661</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="G358" s="9">
-        <v>46543.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1">
-        <v>1.776400120665E12</v>
+        <v>1.77640716912E12</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>112</v>
@@ -12059,21 +12113,21 @@
         <v>25</v>
       </c>
       <c r="D359" s="2">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F359" s="3" t="s">
-        <v>241</v>
+        <v>555</v>
+      </c>
+      <c r="F359" s="3">
+        <v>11503.0</v>
       </c>
       <c r="G359" s="9">
-        <v>46479.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1">
-        <v>1.77640716912E12</v>
+        <v>1.776407375241E12</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>112</v>
@@ -12082,21 +12136,21 @@
         <v>25</v>
       </c>
       <c r="D360" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F360" s="3">
-        <v>11503.0</v>
+        <v>660</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="G360" s="9">
-        <v>46516.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1">
-        <v>1.776407375241E12</v>
+        <v>1.77640744785E12</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>112</v>
@@ -12105,7 +12159,7 @@
         <v>25</v>
       </c>
       <c r="D361" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>661</v>
@@ -12114,97 +12168,97 @@
         <v>663</v>
       </c>
       <c r="G361" s="9">
-        <v>46669.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1">
-        <v>1.77640744785E12</v>
+        <v>1.776407858481E12</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D362" s="2">
         <v>12.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F362" s="3" t="s">
         <v>664</v>
       </c>
+      <c r="F362" s="4"/>
       <c r="G362" s="9">
         <v>46523.0</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1">
-        <v>1.776407858481E12</v>
+        <v>1.776436049209E12</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>32</v>
+        <v>538</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D363" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>665</v>
+        <v>47</v>
       </c>
       <c r="F363" s="4"/>
-      <c r="G363" s="9">
-        <v>46523.0</v>
-      </c>
     </row>
     <row r="364">
       <c r="A364" s="1">
-        <v>1.776436049209E12</v>
+        <v>1.776659068274E12</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>538</v>
+        <v>112</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D364" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F364" s="4"/>
+        <v>665</v>
+      </c>
+      <c r="F364" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G364" s="9">
+        <v>46793.0</v>
+      </c>
     </row>
     <row r="365">
-      <c r="A365" s="1">
-        <v>1.776659068274E12</v>
+      <c r="A365" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D365" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>666</v>
+        <v>66</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G365" s="9">
-        <v>46793.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>112</v>
@@ -12213,67 +12267,62 @@
         <v>33</v>
       </c>
       <c r="D366" s="2">
-        <v>9.0</v>
+        <v>20.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>66</v>
+        <v>670</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G366" s="9">
-        <v>46949.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D367" s="2">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="G367" s="9">
-        <v>46793.0</v>
+        <v>46639.0</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D368" s="2">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F368" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="G368" s="9">
-        <v>46639.0</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="F368" s="4"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>10</v>
@@ -12282,34 +12331,34 @@
         <v>27</v>
       </c>
       <c r="D369" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F369" s="4"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D370" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F370" s="4"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>10</v>
@@ -12321,7 +12370,7 @@
         <v>5.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F371" s="4"/>
     </row>
@@ -12333,13 +12382,13 @@
         <v>10</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D372" s="2">
         <v>5.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F372" s="4"/>
     </row>
@@ -12351,13 +12400,13 @@
         <v>10</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D373" s="2">
         <v>5.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F373" s="4"/>
     </row>
@@ -12369,37 +12418,39 @@
         <v>10</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D374" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="F374" s="4"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D375" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="F375" s="4"/>
+        <v>686</v>
+      </c>
+      <c r="F375" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>32</v>
@@ -12411,15 +12462,18 @@
         <v>2.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>585</v>
+        <v>688</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>293</v>
+        <v>346</v>
+      </c>
+      <c r="G376" s="9">
+        <v>46488.0</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>32</v>
@@ -12431,18 +12485,15 @@
         <v>2.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G377" s="9">
-        <v>46488.0</v>
+        <v>691</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>32</v>
@@ -12451,42 +12502,42 @@
         <v>25</v>
       </c>
       <c r="D378" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>691</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="G378" s="9">
+        <v>46716.0</v>
+      </c>
+      <c r="H378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D379" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="F379" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G379" s="9">
-        <v>46716.0</v>
-      </c>
-      <c r="H379" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="F379" s="3">
+        <v>11504.0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>112</v>
@@ -12495,84 +12546,87 @@
         <v>11</v>
       </c>
       <c r="D380" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F380" s="3">
         <v>11504.0</v>
       </c>
+      <c r="H380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C381" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D381" s="2">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="F381" s="3">
-        <v>11504.0</v>
-      </c>
+        <v>699</v>
+      </c>
+      <c r="F381" s="4"/>
       <c r="H381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D382" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="F382" s="4"/>
-      <c r="H382" s="2"/>
+        <v>701</v>
+      </c>
+      <c r="F382" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="G382" s="9">
+        <v>46240.0</v>
+      </c>
+      <c r="H382" s="2" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D383" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>702</v>
+        <v>671</v>
       </c>
       <c r="G383" s="9">
-        <v>46240.0</v>
-      </c>
-      <c r="H383" s="2" t="s">
-        <v>703</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>112</v>
@@ -12581,67 +12635,70 @@
         <v>11</v>
       </c>
       <c r="D384" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="G384" s="9">
-        <v>46416.0</v>
+        <v>46544.0</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C385" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D385" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="G385" s="9">
-        <v>46544.0</v>
+        <v>46856.0</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D386" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="G386" s="9">
-        <v>46856.0</v>
+        <v>46794.0</v>
+      </c>
+      <c r="H386" s="2" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>112</v>
@@ -12653,21 +12710,18 @@
         <v>16.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>714</v>
       </c>
       <c r="G387" s="9">
-        <v>46794.0</v>
-      </c>
-      <c r="H387" s="2" t="s">
-        <v>715</v>
+        <v>46785.0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>112</v>
@@ -12679,18 +12733,18 @@
         <v>16.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>717</v>
+        <v>585</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>714</v>
       </c>
       <c r="G388" s="9">
-        <v>46785.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>112</v>
@@ -12702,41 +12756,44 @@
         <v>16.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>586</v>
+        <v>720</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>714</v>
       </c>
       <c r="G389" s="9">
-        <v>46789.0</v>
+        <v>46839.0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D390" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="G390" s="9">
-        <v>46839.0</v>
+        <v>46312.0</v>
+      </c>
+      <c r="H390" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>112</v>
@@ -12745,24 +12802,22 @@
         <v>11</v>
       </c>
       <c r="D391" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>722</v>
+        <v>655</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G391" s="9">
-        <v>46312.0</v>
-      </c>
-      <c r="H391" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>46669.0</v>
+      </c>
+      <c r="H391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>112</v>
@@ -12771,45 +12826,44 @@
         <v>11</v>
       </c>
       <c r="D392" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>656</v>
+        <v>574</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>725</v>
+        <v>165</v>
       </c>
       <c r="G392" s="9">
-        <v>46669.0</v>
-      </c>
-      <c r="H392" s="2"/>
+        <v>46540.0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D393" s="2">
-        <v>22.0</v>
+        <v>7.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>574</v>
+        <v>728</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>165</v>
+        <v>714</v>
       </c>
       <c r="G393" s="9">
-        <v>46540.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>112</v>
@@ -12821,41 +12875,39 @@
         <v>7.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="G394" s="9">
-        <v>46794.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D395" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F395" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="G395" s="9">
-        <v>46792.0</v>
-      </c>
+        <v>733</v>
+      </c>
+      <c r="F395" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="H395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>112</v>
@@ -12864,181 +12916,180 @@
         <v>11</v>
       </c>
       <c r="D396" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="F396" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="H396" s="2"/>
+        <v>115004.0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D397" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="F397" s="3">
-        <v>115004.0</v>
+        <v>11505.0</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D398" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="F398" s="3">
-        <v>11505.0</v>
+        <v>739</v>
+      </c>
+      <c r="F398" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G398" s="9">
+        <v>46162.0</v>
+      </c>
+      <c r="H398" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I398" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D399" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="F399" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G399" s="9">
-        <v>46162.0</v>
-      </c>
-      <c r="H399" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I399" s="2" t="s">
-        <v>233</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="F399" s="4"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D400" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="F400" s="4"/>
+        <v>743</v>
+      </c>
+      <c r="F400" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G400" s="9">
+        <v>46152.0</v>
+      </c>
+      <c r="H400" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I400" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D401" s="2">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>326</v>
+        <v>663</v>
       </c>
       <c r="G401" s="9">
-        <v>46152.0</v>
-      </c>
-      <c r="H401" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I401" s="2" t="s">
-        <v>233</v>
+        <v>46596.0</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D402" s="2">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>664</v>
+        <v>748</v>
       </c>
       <c r="G402" s="9">
-        <v>46596.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D403" s="2">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>747</v>
+        <v>648</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="G403" s="9">
-        <v>46669.0</v>
+        <v>385</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>32</v>
@@ -13047,18 +13098,18 @@
         <v>25</v>
       </c>
       <c r="D404" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>649</v>
+        <v>751</v>
       </c>
       <c r="F404" s="3" t="s">
-        <v>385</v>
+        <v>418</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>32</v>
@@ -13066,111 +13117,111 @@
       <c r="C405" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D405" s="2">
-        <v>10.0</v>
-      </c>
       <c r="E405" s="2" t="s">
-        <v>751</v>
+        <v>560</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>418</v>
+        <v>753</v>
+      </c>
+      <c r="G405" s="9">
+        <v>46410.0</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
+      </c>
+      <c r="D406" s="2">
+        <v>22.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>560</v>
+        <v>755</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="G406" s="9">
-        <v>46410.0</v>
+        <v>46194.0</v>
+      </c>
+      <c r="I406" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D407" s="2">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="G407" s="9">
-        <v>46194.0</v>
-      </c>
-      <c r="I407" s="2" t="s">
-        <v>233</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D408" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>758</v>
+        <v>588</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G408" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D409" s="2">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>589</v>
+        <v>763</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="G409" s="9">
-        <v>46913.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>10</v>
@@ -13182,7 +13233,7 @@
         <v>2.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>763</v>
+        <v>15</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>224</v>
@@ -13190,7 +13241,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>10</v>
@@ -13202,35 +13253,38 @@
         <v>2.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>15</v>
+        <v>763</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D412" s="2">
         <v>2.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>16</v>
+        <v>37</v>
+      </c>
+      <c r="G412" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>10</v>
@@ -13239,42 +13293,42 @@
         <v>25</v>
       </c>
       <c r="D413" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="F413" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F413" s="4"/>
       <c r="G413" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C414" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D414" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F414" s="4"/>
+        <v>771</v>
+      </c>
+      <c r="F414" s="3" t="s">
+        <v>772</v>
+      </c>
       <c r="G414" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>32</v>
@@ -13289,124 +13343,124 @@
         <v>771</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G415" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D416" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F416" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="G416" s="9">
-        <v>46484.0</v>
+        <v>548</v>
+      </c>
+      <c r="F416" s="3">
+        <v>11505.0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D417" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F417" s="3">
-        <v>11505.0</v>
+        <v>713</v>
+      </c>
+      <c r="F417" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D418" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>713</v>
+        <v>778</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>55</v>
+        <v>604</v>
+      </c>
+      <c r="G418" s="9">
+        <v>46577.0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D419" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>605</v>
+        <v>272</v>
       </c>
       <c r="G419" s="9">
-        <v>46577.0</v>
+        <v>46361.0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D420" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>272</v>
+        <v>595</v>
       </c>
       <c r="G420" s="9">
-        <v>46361.0</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>112</v>
@@ -13418,18 +13472,18 @@
         <v>17.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G421" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>112</v>
@@ -13441,18 +13495,18 @@
         <v>17.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G422" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>112</v>
@@ -13464,18 +13518,18 @@
         <v>17.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G423" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>112</v>
@@ -13487,53 +13541,50 @@
         <v>17.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>596</v>
+        <v>791</v>
       </c>
       <c r="G424" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D425" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="G425" s="9">
-        <v>46523.0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D426" s="2">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>224</v>
@@ -13541,19 +13592,19 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D427" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>224</v>
@@ -13561,7 +13612,7 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>32</v>
@@ -13570,10 +13621,10 @@
         <v>27</v>
       </c>
       <c r="D428" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>224</v>
@@ -13581,50 +13632,53 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D429" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>224</v>
+        <v>238</v>
+      </c>
+      <c r="G429" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="2">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G430" s="9">
-        <v>46281.0</v>
+        <v>493</v>
+      </c>
+      <c r="H430" s="2" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>32</v>
@@ -13633,21 +13687,21 @@
         <v>11</v>
       </c>
       <c r="D431" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H431" s="2" t="s">
-        <v>804</v>
+      <c r="G431" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>32</v>
@@ -13656,67 +13710,67 @@
         <v>11</v>
       </c>
       <c r="D432" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="G432" s="9">
-        <v>47146.0</v>
+      <c r="H432" s="2" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="H433" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
+      </c>
+      <c r="G433" s="9">
+        <v>46666.0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C434" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="F434" s="3" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="G434" s="9">
-        <v>46666.0</v>
+        <v>46583.0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>32</v>
@@ -13731,15 +13785,15 @@
         <v>813</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="G435" s="9">
-        <v>46583.0</v>
+        <v>46604.0</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>32</v>
@@ -13754,15 +13808,15 @@
         <v>813</v>
       </c>
       <c r="F436" s="3" t="s">
-        <v>816</v>
+        <v>110</v>
       </c>
       <c r="G436" s="9">
-        <v>46604.0</v>
+        <v>46626.0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>32</v>
@@ -13777,15 +13831,15 @@
         <v>813</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>110</v>
+        <v>819</v>
       </c>
       <c r="G437" s="9">
-        <v>46626.0</v>
+        <v>46658.0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>32</v>
@@ -13800,102 +13854,102 @@
         <v>813</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="G438" s="9">
-        <v>46658.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D439" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="F439" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="G439" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>823</v>
+      </c>
+      <c r="F439" s="4"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D440" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F440" s="4"/>
+        <v>825</v>
+      </c>
+      <c r="F440" s="3" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D441" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>493</v>
+        <v>828</v>
+      </c>
+      <c r="G441" s="9">
+        <v>46792.0</v>
+      </c>
+      <c r="H441" s="2" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D442" s="2">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="G442" s="9">
-        <v>46792.0</v>
-      </c>
-      <c r="H442" s="2" t="s">
-        <v>829</v>
+        <v>46304.0</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>32</v>
@@ -13904,21 +13958,21 @@
         <v>11</v>
       </c>
       <c r="D443" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>831</v>
+        <v>583</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>832</v>
+        <v>51</v>
       </c>
       <c r="G443" s="9">
-        <v>46304.0</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>32</v>
@@ -13927,21 +13981,21 @@
         <v>11</v>
       </c>
       <c r="D444" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>583</v>
+        <v>835</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>51</v>
+        <v>359</v>
       </c>
       <c r="G444" s="9">
-        <v>46416.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>32</v>
@@ -13950,59 +14004,59 @@
         <v>11</v>
       </c>
       <c r="D445" s="2">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>359</v>
+        <v>37</v>
       </c>
       <c r="G445" s="9">
-        <v>46255.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D446" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>37</v>
+        <v>663</v>
       </c>
       <c r="G446" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D447" s="2">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>839</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G447" s="9">
         <v>46794.0</v>
@@ -14010,7 +14064,7 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>112</v>
@@ -14019,67 +14073,67 @@
         <v>25</v>
       </c>
       <c r="D448" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>839</v>
+        <v>545</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G448" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D449" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>545</v>
+        <v>730</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>664</v>
+        <v>843</v>
       </c>
       <c r="G449" s="9">
-        <v>46484.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D450" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>730</v>
+        <v>845</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>843</v>
+        <v>580</v>
       </c>
       <c r="G450" s="9">
-        <v>46792.0</v>
+        <v>46676.0</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>32</v>
@@ -14091,36 +14145,36 @@
         <v>9.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="F451" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="G451" s="9">
-        <v>46676.0</v>
-      </c>
+        <v>813</v>
+      </c>
+      <c r="F451" s="4"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="F452" s="4"/>
+        <v>848</v>
+      </c>
+      <c r="F452" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="G452" s="9">
+        <v>46641.0</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>112</v>
@@ -14129,21 +14183,21 @@
         <v>11</v>
       </c>
       <c r="D453" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>708</v>
       </c>
       <c r="G453" s="9">
-        <v>46641.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>112</v>
@@ -14152,44 +14206,44 @@
         <v>11</v>
       </c>
       <c r="D454" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F454" s="3" t="s">
-        <v>708</v>
+        <v>663</v>
       </c>
       <c r="G454" s="9">
-        <v>46530.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D455" s="2">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
       <c r="F455" s="3" t="s">
-        <v>664</v>
+        <v>580</v>
       </c>
       <c r="G455" s="9">
-        <v>46949.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>112</v>
@@ -14204,15 +14258,15 @@
         <v>831</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>580</v>
+        <v>449</v>
       </c>
       <c r="G456" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>112</v>
@@ -14235,10 +14289,10 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>25</v>
@@ -14250,15 +14304,15 @@
         <v>831</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>449</v>
+        <v>580</v>
       </c>
       <c r="G458" s="9">
-        <v>46752.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>32</v>
@@ -14273,15 +14327,15 @@
         <v>831</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>580</v>
+        <v>449</v>
       </c>
       <c r="G459" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>32</v>
@@ -14296,107 +14350,107 @@
         <v>831</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>449</v>
+        <v>45</v>
       </c>
       <c r="G460" s="9">
-        <v>46752.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D461" s="2">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>831</v>
+        <v>579</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G461" s="9">
-        <v>46366.0</v>
+        <v>668</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D462" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>669</v>
+        <v>861</v>
+      </c>
+      <c r="G462" s="9">
+        <v>46670.0</v>
+      </c>
+      <c r="H462" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D463" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>573</v>
+        <v>863</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>861</v>
+        <v>95</v>
       </c>
       <c r="G463" s="9">
-        <v>46670.0</v>
-      </c>
-      <c r="H463" s="2" t="s">
-        <v>52</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D464" s="2">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>863</v>
+        <v>574</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>95</v>
+        <v>317</v>
       </c>
       <c r="G464" s="9">
-        <v>46725.0</v>
+        <v>46556.0</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>112</v>
@@ -14408,18 +14462,18 @@
         <v>22.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>574</v>
+        <v>866</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="G465" s="9">
-        <v>46556.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>112</v>
@@ -14431,41 +14485,42 @@
         <v>22.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>142</v>
+        <v>869</v>
       </c>
       <c r="G466" s="9">
-        <v>46793.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C467" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D467" s="2">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>869</v>
+        <v>606</v>
       </c>
       <c r="G467" s="9">
-        <v>46670.0</v>
-      </c>
+        <v>46254.0</v>
+      </c>
+      <c r="H467" s="2"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>32</v>
@@ -14474,37 +14529,36 @@
         <v>11</v>
       </c>
       <c r="D468" s="2">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>607</v>
+        <v>405</v>
       </c>
       <c r="G468" s="9">
-        <v>46254.0</v>
-      </c>
-      <c r="H468" s="2"/>
+        <v>46669.0</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D469" s="2">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>405</v>
+        <v>876</v>
       </c>
       <c r="G469" s="9">
         <v>46669.0</v>
@@ -14512,7 +14566,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>32</v>
@@ -14524,10 +14578,10 @@
         <v>6.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G470" s="9">
         <v>46669.0</v>
@@ -14535,7 +14589,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>32</v>
@@ -14550,7 +14604,7 @@
         <v>878</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>879</v>
+        <v>811</v>
       </c>
       <c r="G471" s="9">
         <v>46669.0</v>
@@ -14558,7 +14612,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>32</v>
@@ -14573,7 +14627,7 @@
         <v>878</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>811</v>
+        <v>882</v>
       </c>
       <c r="G472" s="9">
         <v>46669.0</v>
@@ -14581,30 +14635,30 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D473" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G473" s="9">
-        <v>46669.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>32</v>
@@ -14616,18 +14670,18 @@
         <v>18.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>884</v>
+        <v>601</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>885</v>
       </c>
       <c r="G474" s="9">
-        <v>46947.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>32</v>
@@ -14639,7 +14693,7 @@
         <v>18.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>602</v>
+        <v>66</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>885</v>
@@ -14650,7 +14704,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>32</v>
@@ -14662,18 +14716,15 @@
         <v>18.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>66</v>
+        <v>831</v>
       </c>
       <c r="F476" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="G476" s="9">
-        <v>46949.0</v>
-      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>32</v>
@@ -14682,104 +14733,107 @@
         <v>27</v>
       </c>
       <c r="D477" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>831</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>885</v>
+        <v>43</v>
+      </c>
+      <c r="G477" s="9">
+        <v>46730.0</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D478" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>831</v>
+        <v>891</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G478" s="9">
-        <v>46730.0</v>
+        <v>346</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D479" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>891</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>346</v>
+        <v>118</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D480" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>118</v>
+        <v>441</v>
+      </c>
+      <c r="G480" s="9">
+        <v>46267.0</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D481" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>441</v>
+        <v>759</v>
       </c>
       <c r="G481" s="9">
-        <v>46267.0</v>
+        <v>46250.0</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>32</v>
@@ -14791,64 +14845,64 @@
         <v>8.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>759</v>
+        <v>359</v>
       </c>
       <c r="G482" s="9">
-        <v>46250.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C483" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D483" s="2">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="G483" s="9">
-        <v>46255.0</v>
+        <v>46613.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D484" s="2">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>900</v>
+        <v>607</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>470</v>
+        <v>608</v>
       </c>
       <c r="G484" s="9">
-        <v>46613.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>32</v>
@@ -14857,21 +14911,21 @@
         <v>11</v>
       </c>
       <c r="D485" s="2">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>608</v>
+        <v>903</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>609</v>
+        <v>449</v>
       </c>
       <c r="G485" s="9">
-        <v>46669.0</v>
+        <v>46691.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>32</v>
@@ -14886,38 +14940,33 @@
         <v>903</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>449</v>
+        <v>885</v>
       </c>
       <c r="G486" s="9">
-        <v>46691.0</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D487" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="F487" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="G487" s="9">
-        <v>46775.0</v>
-      </c>
+        <v>906</v>
+      </c>
+      <c r="F487" s="4"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>32</v>
@@ -14929,13 +14978,13 @@
         <v>11.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F488" s="4"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>32</v>
@@ -14947,13 +14996,13 @@
         <v>11.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="F489" s="4"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>32</v>
@@ -14965,77 +15014,77 @@
         <v>11.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="F490" s="4"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D491" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="F491" s="4"/>
+        <v>914</v>
+      </c>
+      <c r="F491" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="G491" s="9">
+        <v>46803.0</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C492" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D492" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>914</v>
+        <v>871</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G492" s="9">
-        <v>46803.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D493" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="F493" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="G493" s="9">
-        <v>46222.0</v>
-      </c>
+        <v>919</v>
+      </c>
+      <c r="F493" s="4"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>32</v>
@@ -15047,13 +15096,13 @@
         <v>11.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F494" s="4"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>32</v>
@@ -15065,13 +15114,13 @@
         <v>11.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F495" s="4"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>32</v>
@@ -15083,31 +15132,34 @@
         <v>11.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="F496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D497" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="F497" s="4"/>
+      <c r="G497" s="9">
+        <v>46564.0</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>32</v>
@@ -15119,16 +15171,16 @@
         <v>14.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="F498" s="4"/>
       <c r="G498" s="9">
-        <v>46564.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>32</v>
@@ -15140,16 +15192,16 @@
         <v>14.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="F499" s="4"/>
       <c r="G499" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>32</v>
@@ -15158,10 +15210,10 @@
         <v>25</v>
       </c>
       <c r="D500" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F500" s="4"/>
       <c r="G500" s="9">
@@ -15170,7 +15222,7 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>32</v>
@@ -15182,16 +15234,16 @@
         <v>15.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="F501" s="4"/>
       <c r="G501" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -15203,7 +15255,7 @@
         <v>15.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="F502" s="4"/>
       <c r="G502" s="9">
@@ -15212,7 +15264,7 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>32</v>
@@ -15224,7 +15276,7 @@
         <v>15.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="F503" s="4"/>
       <c r="G503" s="9">
@@ -15233,7 +15285,7 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>32</v>
@@ -15242,19 +15294,19 @@
         <v>25</v>
       </c>
       <c r="D504" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="F504" s="4"/>
       <c r="G504" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>32</v>
@@ -15266,98 +15318,100 @@
         <v>11.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="F505" s="4"/>
       <c r="G505" s="9">
-        <v>46551.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D506" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="F506" s="4"/>
-      <c r="G506" s="9">
-        <v>46394.0</v>
+        <v>945</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D507" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>945</v>
-      </c>
-      <c r="F507" s="3" t="s">
-        <v>418</v>
-      </c>
+        <v>947</v>
+      </c>
+      <c r="F507" s="4"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D508" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="F508" s="4"/>
+        <v>949</v>
+      </c>
+      <c r="F508" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G508" s="9">
+        <v>46759.0</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>32</v>
+        <v>538</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D509" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F509" s="3" t="s">
-        <v>418</v>
+        <v>37</v>
       </c>
       <c r="G509" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>538</v>
@@ -15369,7 +15423,7 @@
         <v>3.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="F510" s="3" t="s">
         <v>37</v>
@@ -15380,7 +15434,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>538</v>
@@ -15392,7 +15446,7 @@
         <v>3.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>37</v>
@@ -15403,7 +15457,7 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>538</v>
@@ -15415,7 +15469,7 @@
         <v>3.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F512" s="3" t="s">
         <v>37</v>
@@ -15426,7 +15480,7 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>538</v>
@@ -15438,10 +15492,10 @@
         <v>3.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F513" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G513" s="9">
         <v>46406.0</v>
@@ -15449,7 +15503,7 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>538</v>
@@ -15461,18 +15515,18 @@
         <v>3.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>385</v>
+        <v>37</v>
       </c>
       <c r="G514" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>538</v>
@@ -15484,18 +15538,18 @@
         <v>3.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="F515" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G515" s="9">
-        <v>46251.0</v>
+        <v>46258.0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>538</v>
@@ -15507,18 +15561,18 @@
         <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="F516" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G516" s="9">
-        <v>46258.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>538</v>
@@ -15527,21 +15581,21 @@
         <v>11</v>
       </c>
       <c r="D517" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="F517" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G517" s="9">
-        <v>46254.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>538</v>
@@ -15553,7 +15607,7 @@
         <v>4.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>37</v>
@@ -15564,7 +15618,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>538</v>
@@ -15576,7 +15630,7 @@
         <v>4.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>37</v>
@@ -15587,7 +15641,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>538</v>
@@ -15599,7 +15653,7 @@
         <v>4.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F520" s="3" t="s">
         <v>37</v>
@@ -15610,7 +15664,7 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>538</v>
@@ -15619,21 +15673,21 @@
         <v>11</v>
       </c>
       <c r="D521" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G521" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>538</v>
@@ -15645,18 +15699,18 @@
         <v>6.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G522" s="9">
-        <v>46251.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>538</v>
@@ -15668,18 +15722,18 @@
         <v>6.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G523" s="9">
-        <v>46280.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>538</v>
@@ -15691,18 +15745,18 @@
         <v>6.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G524" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>538</v>
@@ -15714,7 +15768,7 @@
         <v>6.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>37</v>
@@ -15725,7 +15779,7 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>538</v>
@@ -15737,7 +15791,7 @@
         <v>6.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>37</v>
@@ -15748,7 +15802,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>538</v>
@@ -15760,18 +15814,18 @@
         <v>6.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G527" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>538</v>
@@ -15780,21 +15834,21 @@
         <v>11</v>
       </c>
       <c r="D528" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F528" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G528" s="9">
-        <v>46249.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>538</v>
@@ -15806,18 +15860,18 @@
         <v>7.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F529" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G529" s="9">
-        <v>46352.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>538</v>
@@ -15829,18 +15883,18 @@
         <v>7.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F530" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G530" s="9">
-        <v>46333.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>538</v>
@@ -15849,21 +15903,21 @@
         <v>11</v>
       </c>
       <c r="D531" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G531" s="9">
-        <v>46244.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>538</v>
@@ -15875,18 +15929,18 @@
         <v>8.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G532" s="9">
-        <v>46226.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>538</v>
@@ -15898,18 +15952,18 @@
         <v>8.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="F533" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G533" s="9">
-        <v>46222.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>538</v>
@@ -15921,18 +15975,18 @@
         <v>8.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="F534" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G534" s="9">
-        <v>46241.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>538</v>
@@ -15944,18 +15998,18 @@
         <v>8.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="F535" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G535" s="9">
-        <v>46305.0</v>
+        <v>46319.0</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>538</v>
@@ -15964,21 +16018,21 @@
         <v>11</v>
       </c>
       <c r="D536" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F536" s="3" t="s">
-        <v>16</v>
+        <v>493</v>
       </c>
       <c r="G536" s="9">
-        <v>46319.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>538</v>
@@ -15993,15 +16047,15 @@
         <v>1004</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>493</v>
+        <v>37</v>
       </c>
       <c r="G537" s="9">
-        <v>46365.0</v>
+        <v>46321.0</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>538</v>
@@ -16010,21 +16064,24 @@
         <v>11</v>
       </c>
       <c r="D538" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G538" s="9">
-        <v>46321.0</v>
+        <v>46426.0</v>
+      </c>
+      <c r="H538" s="2" t="s">
+        <v>1008</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>538</v>
@@ -16036,21 +16093,18 @@
         <v>10.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>37</v>
+        <v>385</v>
       </c>
       <c r="G539" s="9">
-        <v>46426.0</v>
-      </c>
-      <c r="H539" s="2" t="s">
-        <v>1008</v>
+        <v>46211.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>538</v>
@@ -16062,18 +16116,18 @@
         <v>10.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="F540" s="3" t="s">
         <v>385</v>
       </c>
       <c r="G540" s="9">
-        <v>46211.0</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>538</v>
@@ -16085,18 +16139,18 @@
         <v>10.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G541" s="9">
-        <v>46204.0</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>538</v>
@@ -16105,21 +16159,21 @@
         <v>11</v>
       </c>
       <c r="D542" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>388</v>
+        <v>37</v>
       </c>
       <c r="G542" s="9">
-        <v>46345.0</v>
+        <v>46392.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>538</v>
@@ -16128,21 +16182,21 @@
         <v>11</v>
       </c>
       <c r="D543" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>37</v>
+        <v>493</v>
       </c>
       <c r="G543" s="9">
-        <v>46392.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>538</v>
@@ -16151,21 +16205,22 @@
         <v>11</v>
       </c>
       <c r="D544" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F544" s="3" t="s">
-        <v>493</v>
-      </c>
+        <v>1020</v>
+      </c>
+      <c r="F544" s="4"/>
       <c r="G544" s="9">
-        <v>46366.0</v>
+        <v>46178.0</v>
+      </c>
+      <c r="I544" s="2" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>538</v>
@@ -16177,7 +16232,7 @@
         <v>14.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F545" s="4"/>
       <c r="G545" s="9">
@@ -16189,7 +16244,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>538</v>
@@ -16201,19 +16256,16 @@
         <v>14.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="F546" s="4"/>
       <c r="G546" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I546" s="2" t="s">
-        <v>233</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>538</v>
@@ -16225,7 +16277,7 @@
         <v>14.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F547" s="4"/>
       <c r="G547" s="9">
@@ -16234,7 +16286,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>538</v>
@@ -16243,19 +16295,18 @@
         <v>11</v>
       </c>
       <c r="D548" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F548" s="4"/>
-      <c r="G548" s="9">
-        <v>46220.0</v>
+        <v>1028</v>
+      </c>
+      <c r="F548" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>538</v>
@@ -16264,10 +16315,10 @@
         <v>11</v>
       </c>
       <c r="D549" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="F549" s="3" t="s">
         <v>157</v>
@@ -16275,10 +16326,10 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>11</v>
@@ -16287,15 +16338,18 @@
         <v>2.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="F550" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="G550" s="9">
+        <v>46223.0</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>536</v>
@@ -16307,18 +16361,18 @@
         <v>2.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="F551" s="3" t="s">
         <v>157</v>
       </c>
       <c r="G551" s="9">
-        <v>46223.0</v>
+        <v>46228.0</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>536</v>
@@ -16327,21 +16381,21 @@
         <v>11</v>
       </c>
       <c r="D552" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>157</v>
+        <v>626</v>
       </c>
       <c r="G552" s="9">
-        <v>46228.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>536</v>
@@ -16350,21 +16404,21 @@
         <v>11</v>
       </c>
       <c r="D553" s="2">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="G553" s="9">
-        <v>46269.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>536</v>
@@ -16373,21 +16427,21 @@
         <v>11</v>
       </c>
       <c r="D554" s="2">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G554" s="9">
-        <v>46240.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>536</v>
@@ -16396,68 +16450,68 @@
         <v>11</v>
       </c>
       <c r="D555" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>632</v>
+        <v>399</v>
       </c>
       <c r="G555" s="9">
-        <v>46242.0</v>
-      </c>
+        <v>46274.0</v>
+      </c>
+      <c r="H555" s="2"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>536</v>
+        <v>112</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D556" s="2">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>399</v>
+        <v>1044</v>
       </c>
       <c r="G556" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H556" s="2"/>
+        <v>46743.0</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D557" s="2">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="G557" s="9">
-        <v>46743.0</v>
+        <v>46207.0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>536</v>
@@ -16466,62 +16520,62 @@
         <v>11</v>
       </c>
       <c r="D558" s="2">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F558" s="3" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G558" s="9">
-        <v>46207.0</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="F558" s="4"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>536</v>
+        <v>112</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D559" s="2">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="F559" s="4"/>
+        <v>1050</v>
+      </c>
+      <c r="F559" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G559" s="9">
+        <v>46295.0</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D560" s="2">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>227</v>
+        <v>399</v>
       </c>
       <c r="G560" s="9">
-        <v>46295.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>32</v>
@@ -16530,7 +16584,7 @@
         <v>33</v>
       </c>
       <c r="D561" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>1052</v>
@@ -16544,30 +16598,30 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>32</v>
+        <v>536</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D562" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>399</v>
+        <v>627</v>
       </c>
       <c r="G562" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>536</v>
@@ -16579,10 +16633,10 @@
         <v>3.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G563" s="9">
         <v>46261.0</v>
@@ -16590,7 +16644,7 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>536</v>
@@ -16602,18 +16656,18 @@
         <v>3.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G564" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>536</v>
@@ -16625,18 +16679,18 @@
         <v>3.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G565" s="9">
-        <v>46266.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>536</v>
@@ -16648,21 +16702,21 @@
         <v>3.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G566" s="9">
-        <v>46223.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>11</v>
@@ -16671,41 +16725,41 @@
         <v>3.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F567" s="3" t="s">
-        <v>628</v>
+        <v>399</v>
       </c>
       <c r="G567" s="9">
-        <v>46266.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D568" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1065</v>
+        <v>717</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>399</v>
+        <v>1067</v>
       </c>
       <c r="G568" s="9">
-        <v>46769.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>112</v>
@@ -16717,18 +16771,18 @@
         <v>14.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>717</v>
+        <v>1069</v>
       </c>
       <c r="F569" s="3" t="s">
         <v>1067</v>
       </c>
       <c r="G569" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>112</v>
@@ -16740,7 +16794,7 @@
         <v>14.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1069</v>
+        <v>713</v>
       </c>
       <c r="F570" s="3" t="s">
         <v>1067</v>
@@ -16751,7 +16805,7 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>112</v>
@@ -16763,41 +16817,41 @@
         <v>14.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>713</v>
+        <v>601</v>
       </c>
       <c r="F571" s="3" t="s">
         <v>1067</v>
       </c>
       <c r="G571" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C572" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D572" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>602</v>
+        <v>891</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="G572" s="9">
-        <v>46998.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>32</v>
@@ -16809,18 +16863,18 @@
         <v>2.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>891</v>
+        <v>1075</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="G573" s="9">
-        <v>46484.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>32</v>
@@ -16832,18 +16886,18 @@
         <v>2.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="G574" s="9">
-        <v>46432.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>32</v>
@@ -16855,18 +16909,18 @@
         <v>2.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>1079</v>
+        <v>458</v>
       </c>
       <c r="G575" s="9">
-        <v>46877.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>32</v>
@@ -16878,18 +16932,16 @@
         <v>2.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G576" s="9">
-        <v>46704.0</v>
-      </c>
+        <v>1084</v>
+      </c>
+      <c r="G576" s="9"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>32</v>
@@ -16901,16 +16953,15 @@
         <v>2.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="F577" s="3" t="s">
         <v>1084</v>
       </c>
-      <c r="G577" s="9"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>32</v>
@@ -16922,7 +16973,7 @@
         <v>2.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1086</v>
+        <v>875</v>
       </c>
       <c r="F578" s="3" t="s">
         <v>1084</v>
@@ -16930,7 +16981,7 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>32</v>
@@ -16942,7 +16993,7 @@
         <v>2.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>875</v>
+        <v>686</v>
       </c>
       <c r="F579" s="3" t="s">
         <v>1084</v>
@@ -16950,7 +17001,7 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>32</v>
@@ -16962,7 +17013,7 @@
         <v>2.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>585</v>
+        <v>1086</v>
       </c>
       <c r="F580" s="3" t="s">
         <v>1084</v>
@@ -16970,7 +17021,7 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>32</v>
@@ -16982,7 +17033,7 @@
         <v>2.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="F581" s="3" t="s">
         <v>1084</v>
@@ -16990,7 +17041,7 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>32</v>
@@ -17002,38 +17053,41 @@
         <v>2.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1084</v>
+        <v>593</v>
+      </c>
+      <c r="G582" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D583" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>594</v>
+        <v>1096</v>
       </c>
       <c r="G583" s="9">
-        <v>46766.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>112</v>
@@ -17042,21 +17096,21 @@
         <v>11</v>
       </c>
       <c r="D584" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1095</v>
+        <v>848</v>
       </c>
       <c r="F584" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G584" s="9">
-        <v>46877.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>112</v>
@@ -17065,21 +17119,21 @@
         <v>11</v>
       </c>
       <c r="D585" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>848</v>
+        <v>1099</v>
       </c>
       <c r="F585" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G585" s="9">
-        <v>46641.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>112</v>
@@ -17088,21 +17142,19 @@
         <v>11</v>
       </c>
       <c r="D586" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F586" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G586" s="9">
-        <v>46743.0</v>
+        <v>1101</v>
+      </c>
+      <c r="F586" s="4"/>
+      <c r="H586" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>112</v>
@@ -17111,37 +17163,42 @@
         <v>11</v>
       </c>
       <c r="D587" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F587" s="4"/>
+        <v>810</v>
+      </c>
+      <c r="F587" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G587" s="9">
+        <v>46663.0</v>
+      </c>
       <c r="H587" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D588" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>810</v>
+        <v>583</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="G588" s="9">
-        <v>46663.0</v>
+        <v>46437.0</v>
       </c>
       <c r="H588" s="2" t="s">
         <v>133</v>
@@ -17149,33 +17206,30 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D589" s="2">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>583</v>
+        <v>1107</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="G589" s="9">
-        <v>46437.0</v>
-      </c>
-      <c r="H589" s="2" t="s">
-        <v>133</v>
+        <v>46775.0</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>112</v>
@@ -17184,21 +17238,21 @@
         <v>11</v>
       </c>
       <c r="D590" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1107</v>
+        <v>661</v>
       </c>
       <c r="F590" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G590" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>112</v>
@@ -17210,7 +17264,7 @@
         <v>11.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>662</v>
+        <v>1110</v>
       </c>
       <c r="F591" s="3" t="s">
         <v>1096</v>
@@ -17221,30 +17275,30 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D592" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="F592" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G592" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>112</v>
@@ -17256,18 +17310,18 @@
         <v>14.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F593" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G593" s="9">
-        <v>46481.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>112</v>
@@ -17279,18 +17333,18 @@
         <v>14.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F594" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G594" s="9">
-        <v>46877.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>112</v>
@@ -17302,18 +17356,18 @@
         <v>14.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="F595" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G595" s="9">
-        <v>46872.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>112</v>
@@ -17325,18 +17379,18 @@
         <v>14.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="F596" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G596" s="9">
-        <v>46734.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>112</v>
@@ -17348,18 +17402,18 @@
         <v>14.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F597" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G597" s="9">
-        <v>46481.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>112</v>
@@ -17371,64 +17425,64 @@
         <v>14.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F598" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G598" s="9">
-        <v>46872.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D599" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1124</v>
+        <v>848</v>
       </c>
       <c r="F599" s="3" t="s">
         <v>1096</v>
       </c>
       <c r="G599" s="9">
-        <v>46877.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D600" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>848</v>
+        <v>1127</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1096</v>
+        <v>399</v>
       </c>
       <c r="G600" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>536</v>
@@ -17440,7 +17494,7 @@
         <v>17.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="F601" s="3" t="s">
         <v>399</v>
@@ -17451,7 +17505,7 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>536</v>
@@ -17460,10 +17514,10 @@
         <v>11</v>
       </c>
       <c r="D602" s="2">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1129</v>
+        <v>655</v>
       </c>
       <c r="F602" s="3" t="s">
         <v>399</v>
@@ -17474,49 +17528,49 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D603" s="2">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F603" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G603" s="9">
-        <v>46274.0</v>
-      </c>
+        <v>1132</v>
+      </c>
+      <c r="F603" s="3"/>
+      <c r="G603" s="9"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D604" s="2">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F604" s="3"/>
-      <c r="G604" s="9"/>
+        <v>1134</v>
+      </c>
+      <c r="F604" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G604" s="9">
+        <v>46437.0</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>112</v>
@@ -17525,21 +17579,21 @@
         <v>27</v>
       </c>
       <c r="D605" s="2">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>224</v>
+        <v>1137</v>
       </c>
       <c r="G605" s="9">
-        <v>46437.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>112</v>
@@ -17548,85 +17602,86 @@
         <v>27</v>
       </c>
       <c r="D606" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F606" s="3" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G606" s="9">
-        <v>46516.0</v>
+        <v>1139</v>
+      </c>
+      <c r="F606" s="3"/>
+      <c r="G606" s="9"/>
+      <c r="H606" s="2" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D607" s="2">
-        <v>22.0</v>
+        <v>6.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="F607" s="3"/>
       <c r="G607" s="9"/>
-      <c r="H607" s="2" t="s">
-        <v>1140</v>
-      </c>
+      <c r="H607" s="2"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D608" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F608" s="3"/>
+        <v>1144</v>
+      </c>
+      <c r="F608" s="3" t="s">
+        <v>418</v>
+      </c>
       <c r="G608" s="9"/>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D609" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G609" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="G609" s="9">
+        <v>46403.0</v>
+      </c>
       <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>112</v>
@@ -17635,44 +17690,44 @@
         <v>11</v>
       </c>
       <c r="D610" s="2">
-        <v>4.0</v>
+        <v>21.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F610" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G610" s="9">
-        <v>46403.0</v>
-      </c>
-      <c r="H610" s="2"/>
+        <v>1148</v>
+      </c>
+      <c r="F610" s="3"/>
+      <c r="G610" s="9"/>
+      <c r="H610" s="2" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>112</v>
+        <v>536</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D611" s="2">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F611" s="3"/>
-      <c r="G611" s="9"/>
-      <c r="H611" s="2" t="s">
-        <v>1140</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="F611" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="G611" s="9">
+        <v>46269.0</v>
+      </c>
+      <c r="H611" s="2"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>536</v>
@@ -17684,19 +17739,19 @@
         <v>8.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>626</v>
+        <v>1035</v>
       </c>
       <c r="F612" s="3" t="s">
-        <v>627</v>
+        <v>1151</v>
       </c>
       <c r="G612" s="9">
-        <v>46269.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H612" s="2"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>536</v>
@@ -17708,19 +17763,15 @@
         <v>8.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F613" s="3" t="s">
-        <v>1151</v>
-      </c>
-      <c r="G613" s="9">
-        <v>46290.0</v>
-      </c>
+        <v>1153</v>
+      </c>
+      <c r="F613" s="3"/>
+      <c r="G613" s="9"/>
       <c r="H613" s="2"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>536</v>
@@ -17732,39 +17783,43 @@
         <v>8.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F614" s="3"/>
-      <c r="G614" s="9"/>
+        <v>629</v>
+      </c>
+      <c r="F614" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G614" s="9">
+        <v>46290.0</v>
+      </c>
       <c r="H614" s="2"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>536</v>
+        <v>32</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D615" s="2">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>630</v>
+        <v>1156</v>
       </c>
       <c r="F615" s="3" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="G615" s="9">
-        <v>46290.0</v>
+        <v>46883.0</v>
       </c>
       <c r="H615" s="2"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>32</v>
@@ -17779,7 +17834,7 @@
         <v>1156</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="G616" s="9">
         <v>46883.0</v>
@@ -17788,27 +17843,201 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="C617" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D617" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E617" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F617" s="3">
+        <v>11503.0</v>
+      </c>
+      <c r="G617" s="9"/>
+      <c r="H617" s="2"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D618" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E618" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F618" s="3">
+        <v>11505.0</v>
+      </c>
+      <c r="G618" s="9"/>
+      <c r="H618" s="2"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D619" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E619" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F619" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G619" s="9"/>
+      <c r="H619" s="2"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D620" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E620" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F620" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G620" s="9"/>
+      <c r="H620" s="2"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D621" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E621" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F621" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G621" s="9"/>
+      <c r="H621" s="2"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D622" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E622" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F622" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G622" s="9"/>
+      <c r="H622" s="2"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D623" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E623" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F623" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G623" s="9"/>
+      <c r="H623" s="2"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D624" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E624" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F624" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="G624" s="9"/>
+      <c r="H624" s="2"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C625" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D617" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="E617" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F617" s="3" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G617" s="9">
-        <v>46883.0</v>
-      </c>
-      <c r="H617" s="2"/>
+      <c r="D625" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E625" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F625" s="3">
+        <v>11505.0</v>
+      </c>
+      <c r="G625" s="9"/>
+      <c r="H625" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2950" uniqueCount="1183">
   <si>
     <t>ID</t>
   </si>
@@ -3545,6 +3545,21 @@
   </si>
   <si>
     <t>TS（預定）</t>
+  </si>
+  <si>
+    <t>ID1780490983707</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>待查核</t>
+  </si>
+  <si>
+    <t>ID1780492852348</t>
   </si>
 </sst>
 </file>
@@ -18039,6 +18054,56 @@
       <c r="G625" s="9"/>
       <c r="H625" s="2"/>
     </row>
+    <row r="626">
+      <c r="A626" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D626" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E626" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F626" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G626" s="9">
+        <v>46177.0</v>
+      </c>
+      <c r="H626" s="2" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D627" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E627" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="F627" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G627" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H627" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="1186">
   <si>
     <t>ID</t>
   </si>
@@ -3505,21 +3505,18 @@
     <t>ID1780472410260</t>
   </si>
   <si>
-    <t>37TQ(預定)</t>
+    <t>37TQ</t>
   </si>
   <si>
     <t>ID1780472441121</t>
   </si>
   <si>
-    <t>36-38B(預定)</t>
+    <t>36-38B</t>
   </si>
   <si>
     <t>ID1780472484781</t>
   </si>
   <si>
-    <t>10Q(預定)</t>
-  </si>
-  <si>
     <t>ID1780473214746</t>
   </si>
   <si>
@@ -3544,15 +3541,6 @@
     <t>TS（預定）</t>
   </si>
   <si>
-    <t>ID1780490983707</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>待查核</t>
-  </si>
-  <si>
     <t>ID1780492852348</t>
   </si>
   <si>
@@ -3572,6 +3560,15 @@
   </si>
   <si>
     <t>#35</t>
+  </si>
+  <si>
+    <t>ID1780546652417</t>
+  </si>
+  <si>
+    <t>ID1780546669489</t>
+  </si>
+  <si>
+    <t>ID1780546690451</t>
   </si>
 </sst>
 </file>
@@ -17955,7 +17952,7 @@
         <v>3.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1168</v>
+        <v>547</v>
       </c>
       <c r="F620" s="3">
         <v>11504.0</v>
@@ -17965,7 +17962,7 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>32</v>
@@ -17977,17 +17974,17 @@
         <v>2.0</v>
       </c>
       <c r="E621" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F621" s="3" t="s">
         <v>1170</v>
-      </c>
-      <c r="F621" s="3" t="s">
-        <v>1171</v>
       </c>
       <c r="G621" s="9"/>
       <c r="H621" s="2"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>111</v>
@@ -18002,14 +17999,14 @@
         <v>608</v>
       </c>
       <c r="F622" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G622" s="9"/>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>111</v>
@@ -18031,7 +18028,7 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>32</v>
@@ -18043,7 +18040,7 @@
         <v>4.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="F624" s="3">
         <v>11505.0</v>
@@ -18053,7 +18050,7 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>111</v>
@@ -18062,39 +18059,37 @@
         <v>11</v>
       </c>
       <c r="D625" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>1178</v>
+        <v>547</v>
       </c>
       <c r="F625" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G625" s="9">
-        <v>46177.0</v>
-      </c>
-      <c r="H625" s="2" t="s">
-        <v>1179</v>
-      </c>
+      <c r="G625" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H625" s="2"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D626" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F626" s="3" t="s">
-        <v>38</v>
+        <v>1178</v>
+      </c>
+      <c r="F626" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G626" s="2" t="s">
         <v>38</v>
@@ -18103,7 +18098,7 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>32</v>
@@ -18115,7 +18110,7 @@
         <v>17.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F627" s="3">
         <v>11506.0</v>
@@ -18127,19 +18122,19 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D628" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F628" s="3">
         <v>11506.0</v>
@@ -18151,27 +18146,75 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D629" s="2">
         <v>1.0</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F629" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G629" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="F629" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G629" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H629" s="2"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D630" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E630" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F630" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G630" s="9">
+        <v>47531.0</v>
+      </c>
+      <c r="H630" s="2"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D631" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E631" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F631" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G631" s="9">
+        <v>47531.0</v>
+      </c>
+      <c r="H631" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="1193">
   <si>
     <t>ID</t>
   </si>
@@ -3569,6 +3569,27 @@
   </si>
   <si>
     <t>ID1780546690451</t>
+  </si>
+  <si>
+    <t>ID1780577694690</t>
+  </si>
+  <si>
+    <t>SS26#42</t>
+  </si>
+  <si>
+    <t>ID1780577914932</t>
+  </si>
+  <si>
+    <t>26#42</t>
+  </si>
+  <si>
+    <t>ID1780577956618</t>
+  </si>
+  <si>
+    <t>ID1780577996991</t>
+  </si>
+  <si>
+    <t>ID1780578034415</t>
   </si>
 </sst>
 </file>
@@ -18216,6 +18237,126 @@
       </c>
       <c r="H631" s="2"/>
     </row>
+    <row r="632">
+      <c r="A632" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D632" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E632" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="F632" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G632" s="9">
+        <v>46217.0</v>
+      </c>
+      <c r="H632" s="2"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D633" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E633" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F633" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G633" s="9">
+        <v>46223.0</v>
+      </c>
+      <c r="H633" s="2"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D634" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G634" s="9">
+        <v>46221.0</v>
+      </c>
+      <c r="H634" s="2"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D635" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E635" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G635" s="9">
+        <v>46214.0</v>
+      </c>
+      <c r="H635" s="2"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D636" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E636" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G636" s="9">
+        <v>46214.0</v>
+      </c>
+      <c r="H636" s="2"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="1176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="1175">
   <si>
     <t>ID</t>
   </si>
@@ -829,6 +829,9 @@
     <t>UNCLE 一店 JUP(寄庫)</t>
   </si>
   <si>
+    <t>同品在庫: 極冷庫-右2F-15</t>
+  </si>
+  <si>
     <t>ID39835414951198</t>
   </si>
   <si>
@@ -970,7 +973,7 @@
     <t>1130729K</t>
   </si>
   <si>
-    <t>(走道)</t>
+    <t>(報廢)</t>
   </si>
   <si>
     <t>ID39835414951232</t>
@@ -985,9 +988,6 @@
     <t>24#4</t>
   </si>
   <si>
-    <t>即期品-5月</t>
-  </si>
-  <si>
     <t>ID39835414951235</t>
   </si>
   <si>
@@ -1030,9 +1030,6 @@
     <t>24#8</t>
   </si>
   <si>
-    <t>異常</t>
-  </si>
-  <si>
     <t>ID39835414951250</t>
   </si>
   <si>
@@ -1645,6 +1642,9 @@
     <t>SS26#24</t>
   </si>
   <si>
+    <t>同品在庫: 極冷庫-左4F-8</t>
+  </si>
+  <si>
     <t>L17</t>
   </si>
   <si>
@@ -1897,6 +1897,9 @@
     <t>無庫位</t>
   </si>
   <si>
+    <t>需補貨</t>
+  </si>
+  <si>
     <t>34B(34-36)</t>
   </si>
   <si>
@@ -3013,18 +3016,6 @@
     <t>BY92S</t>
   </si>
   <si>
-    <t>ID1779343680610</t>
-  </si>
-  <si>
-    <t>Domain 大直 NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779343714862</t>
-  </si>
-  <si>
-    <t>Domain 建國NO12S （寄庫）</t>
-  </si>
-  <si>
     <t>ID1779343771102</t>
   </si>
   <si>
@@ -3539,6 +3530,12 @@
   </si>
   <si>
     <t>ID1780622891013</t>
+  </si>
+  <si>
+    <t>ID1780708907917</t>
+  </si>
+  <si>
+    <t>離線回傳測試</t>
   </si>
 </sst>
 </file>
@@ -6360,9 +6357,7 @@
         <v>264</v>
       </c>
       <c r="F110" s="14"/>
-      <c r="G110" s="19">
-        <v>46162.0</v>
-      </c>
+      <c r="G110" s="19"/>
       <c r="H110" s="11"/>
       <c r="I110" s="2" t="s">
         <v>229</v>
@@ -6434,11 +6429,13 @@
       <c r="G113" s="19">
         <v>46261.0</v>
       </c>
-      <c r="H113" s="12"/>
+      <c r="H113" s="11" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>32</v>
@@ -6450,7 +6447,7 @@
         <v>15.0</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F114" s="14"/>
       <c r="G114" s="19">
@@ -6460,7 +6457,7 @@
     </row>
     <row r="115">
       <c r="A115" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>32</v>
@@ -6472,7 +6469,7 @@
         <v>15.0</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F115" s="14"/>
       <c r="G115" s="19">
@@ -6485,7 +6482,7 @@
     </row>
     <row r="116">
       <c r="A116" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>32</v>
@@ -6497,7 +6494,7 @@
         <v>15.0</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="19">
@@ -6507,7 +6504,7 @@
     </row>
     <row r="117">
       <c r="A117" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B117" s="11" t="s">
         <v>32</v>
@@ -6519,7 +6516,7 @@
         <v>14.0</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F117" s="14"/>
       <c r="G117" s="19">
@@ -6529,7 +6526,7 @@
     </row>
     <row r="118">
       <c r="A118" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>32</v>
@@ -6541,7 +6538,7 @@
         <v>13.0</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F118" s="14"/>
       <c r="G118" s="19">
@@ -6551,7 +6548,7 @@
     </row>
     <row r="119">
       <c r="A119" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>32</v>
@@ -6563,7 +6560,7 @@
         <v>13.0</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F119" s="14"/>
       <c r="G119" s="19">
@@ -6573,7 +6570,7 @@
     </row>
     <row r="120">
       <c r="A120" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>32</v>
@@ -6585,7 +6582,7 @@
         <v>13.0</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F120" s="14"/>
       <c r="G120" s="19">
@@ -6595,7 +6592,7 @@
     </row>
     <row r="121">
       <c r="A121" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>32</v>
@@ -6607,7 +6604,7 @@
         <v>12.0</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F121" s="14"/>
       <c r="G121" s="19">
@@ -6617,7 +6614,7 @@
     </row>
     <row r="122">
       <c r="A122" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>32</v>
@@ -6629,21 +6626,21 @@
         <v>9.0</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G122" s="19">
         <v>46716.0</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>32</v>
@@ -6655,21 +6652,21 @@
         <v>9.0</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F123" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G123" s="19">
         <v>46716.0</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>32</v>
@@ -6681,10 +6678,10 @@
         <v>4.0</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F124" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G124" s="19">
         <v>46716.0</v>
@@ -6693,7 +6690,7 @@
     </row>
     <row r="125">
       <c r="A125" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>32</v>
@@ -6705,21 +6702,21 @@
         <v>9.0</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F125" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G125" s="19">
         <v>46716.0</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>32</v>
@@ -6731,21 +6728,21 @@
         <v>9.0</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G126" s="19">
         <v>46716.0</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>32</v>
@@ -6757,21 +6754,21 @@
         <v>9.0</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G127" s="19">
         <v>46716.0</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>32</v>
@@ -6786,14 +6783,14 @@
         <v>98</v>
       </c>
       <c r="F128" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G128" s="19"/>
       <c r="H128" s="11"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>32</v>
@@ -6805,10 +6802,10 @@
         <v>8.0</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F129" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G129" s="19">
         <v>46703.0</v>
@@ -6817,7 +6814,7 @@
     </row>
     <row r="130">
       <c r="A130" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>32</v>
@@ -6832,7 +6829,7 @@
         <v>96</v>
       </c>
       <c r="F130" s="17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G130" s="19">
         <v>46703.0</v>
@@ -6841,7 +6838,7 @@
     </row>
     <row r="131">
       <c r="A131" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>32</v>
@@ -6853,10 +6850,10 @@
         <v>8.0</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F131" s="17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G131" s="19">
         <v>46703.0</v>
@@ -6865,7 +6862,7 @@
     </row>
     <row r="132">
       <c r="A132" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B132" s="11" t="s">
         <v>32</v>
@@ -6877,10 +6874,10 @@
         <v>7.0</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G132" s="19">
         <v>46577.0</v>
@@ -6889,7 +6886,7 @@
     </row>
     <row r="133">
       <c r="A133" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>32</v>
@@ -6901,10 +6898,10 @@
         <v>7.0</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F133" s="17" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G133" s="19">
         <v>46612.0</v>
@@ -6913,7 +6910,7 @@
     </row>
     <row r="134">
       <c r="A134" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>32</v>
@@ -6925,10 +6922,10 @@
         <v>7.0</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F134" s="17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G134" s="19">
         <v>46634.0</v>
@@ -6937,7 +6934,7 @@
     </row>
     <row r="135">
       <c r="A135" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>32</v>
@@ -6949,16 +6946,16 @@
         <v>11.0</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G135" s="19">
         <v>46157.0</v>
       </c>
       <c r="H135" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>229</v>
@@ -6966,7 +6963,7 @@
     </row>
     <row r="136">
       <c r="A136" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>32</v>
@@ -6981,7 +6978,7 @@
         <v>96</v>
       </c>
       <c r="F136" s="17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G136" s="19">
         <v>46187.0</v>
@@ -6993,7 +6990,7 @@
     </row>
     <row r="137">
       <c r="A137" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>32</v>
@@ -7008,13 +7005,13 @@
         <v>104</v>
       </c>
       <c r="F137" s="17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G137" s="19">
         <v>46152.0</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I137" s="2" t="s">
         <v>229</v>
@@ -7130,17 +7127,15 @@
         <v>22.0</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F142" s="17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G142" s="19">
         <v>46187.0</v>
       </c>
-      <c r="H142" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H142" s="11"/>
       <c r="I142" s="2" t="s">
         <v>229</v>
       </c>
@@ -7159,7 +7154,7 @@
         <v>11.0</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F143" s="17" t="s">
         <v>338</v>
@@ -7168,7 +7163,7 @@
         <v>46148.0</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>229</v>
@@ -7176,7 +7171,7 @@
     </row>
     <row r="144">
       <c r="A144" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>32</v>
@@ -7188,10 +7183,10 @@
         <v>2.0</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F144" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G144" s="19">
         <v>46284.0</v>
@@ -7200,7 +7195,7 @@
     </row>
     <row r="145">
       <c r="A145" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>32</v>
@@ -7212,10 +7207,10 @@
         <v>4.0</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F145" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G145" s="19">
         <v>46488.0</v>
@@ -7224,7 +7219,7 @@
     </row>
     <row r="146">
       <c r="A146" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>32</v>
@@ -7236,16 +7231,16 @@
         <v>11.0</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F146" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G146" s="19">
         <v>46148.0</v>
       </c>
       <c r="H146" s="11" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>229</v>
@@ -7253,7 +7248,7 @@
     </row>
     <row r="147">
       <c r="A147" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>32</v>
@@ -7265,19 +7260,19 @@
         <v>1.0</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F147" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G147" s="12"/>
       <c r="H147" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>32</v>
@@ -7289,7 +7284,7 @@
         <v>1.0</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F148" s="17" t="s">
         <v>24</v>
@@ -7301,7 +7296,7 @@
     </row>
     <row r="149">
       <c r="A149" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>32</v>
@@ -7313,17 +7308,17 @@
         <v>1.0</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F149" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G149" s="12"/>
       <c r="H149" s="12"/>
     </row>
     <row r="150">
       <c r="A150" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>32</v>
@@ -7338,7 +7333,7 @@
         <v>116</v>
       </c>
       <c r="F150" s="17" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G150" s="19">
         <v>46334.0</v>
@@ -7347,7 +7342,7 @@
     </row>
     <row r="151">
       <c r="A151" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>32</v>
@@ -7362,7 +7357,7 @@
         <v>121</v>
       </c>
       <c r="F151" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G151" s="19">
         <v>46255.0</v>
@@ -7371,7 +7366,7 @@
     </row>
     <row r="152">
       <c r="A152" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>32</v>
@@ -7383,10 +7378,10 @@
         <v>1.0</v>
       </c>
       <c r="E152" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F152" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G152" s="19">
         <v>46255.0</v>
@@ -7395,7 +7390,7 @@
     </row>
     <row r="153">
       <c r="A153" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>32</v>
@@ -7407,10 +7402,10 @@
         <v>1.0</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F153" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G153" s="19">
         <v>46255.0</v>
@@ -7419,7 +7414,7 @@
     </row>
     <row r="154">
       <c r="A154" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>32</v>
@@ -7431,19 +7426,19 @@
         <v>21.0</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F154" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G154" s="12"/>
       <c r="H154" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>32</v>
@@ -7455,10 +7450,10 @@
         <v>21.0</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F155" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G155" s="12"/>
       <c r="H155" s="11" t="s">
@@ -7467,7 +7462,7 @@
     </row>
     <row r="156">
       <c r="A156" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>32</v>
@@ -7479,10 +7474,10 @@
         <v>21.0</v>
       </c>
       <c r="E156" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="F156" s="14" t="s">
         <v>367</v>
-      </c>
-      <c r="F156" s="14" t="s">
-        <v>368</v>
       </c>
       <c r="G156" s="12"/>
       <c r="H156" s="11" t="s">
@@ -7491,7 +7486,7 @@
     </row>
     <row r="157">
       <c r="A157" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>32</v>
@@ -7503,7 +7498,7 @@
         <v>20.0</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F157" s="17" t="s">
         <v>16</v>
@@ -7515,7 +7510,7 @@
     </row>
     <row r="158">
       <c r="A158" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>32</v>
@@ -7527,7 +7522,7 @@
         <v>19.0</v>
       </c>
       <c r="E158" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F158" s="17" t="s">
         <v>269</v>
@@ -7539,7 +7534,7 @@
     </row>
     <row r="159">
       <c r="A159" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>32</v>
@@ -7551,7 +7546,7 @@
         <v>19.0</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F159" s="17" t="s">
         <v>16</v>
@@ -7563,7 +7558,7 @@
     </row>
     <row r="160">
       <c r="A160" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>32</v>
@@ -7575,7 +7570,7 @@
         <v>17.0</v>
       </c>
       <c r="E160" s="11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F160" s="17" t="s">
         <v>16</v>
@@ -7587,7 +7582,7 @@
     </row>
     <row r="161">
       <c r="A161" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>32</v>
@@ -7599,10 +7594,10 @@
         <v>15.0</v>
       </c>
       <c r="E161" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="F161" s="17" t="s">
         <v>378</v>
-      </c>
-      <c r="F161" s="17" t="s">
-        <v>379</v>
       </c>
       <c r="G161" s="19">
         <v>46215.0</v>
@@ -7611,7 +7606,7 @@
     </row>
     <row r="162">
       <c r="A162" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>32</v>
@@ -7623,10 +7618,10 @@
         <v>15.0</v>
       </c>
       <c r="E162" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="F162" s="17" t="s">
         <v>381</v>
-      </c>
-      <c r="F162" s="17" t="s">
-        <v>382</v>
       </c>
       <c r="G162" s="19">
         <v>46626.0</v>
@@ -7635,7 +7630,7 @@
     </row>
     <row r="163">
       <c r="A163" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>32</v>
@@ -7647,7 +7642,7 @@
         <v>14.0</v>
       </c>
       <c r="E163" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F163" s="17" t="s">
         <v>16</v>
@@ -7659,7 +7654,7 @@
     </row>
     <row r="164">
       <c r="A164" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>32</v>
@@ -7683,7 +7678,7 @@
     </row>
     <row r="165">
       <c r="A165" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B165" s="11" t="s">
         <v>32</v>
@@ -7695,7 +7690,7 @@
         <v>14.0</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F165" s="17" t="s">
         <v>16</v>
@@ -7707,7 +7702,7 @@
     </row>
     <row r="166">
       <c r="A166" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>32</v>
@@ -7719,7 +7714,7 @@
         <v>13.0</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F166" s="17" t="s">
         <v>269</v>
@@ -7731,7 +7726,7 @@
     </row>
     <row r="167">
       <c r="A167" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>32</v>
@@ -7743,7 +7738,7 @@
         <v>12.0</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F167" s="17" t="s">
         <v>16</v>
@@ -7755,7 +7750,7 @@
     </row>
     <row r="168">
       <c r="A168" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>32</v>
@@ -7767,10 +7762,10 @@
         <v>11.0</v>
       </c>
       <c r="E168" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="F168" s="17" t="s">
         <v>392</v>
-      </c>
-      <c r="F168" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="G168" s="19">
         <v>46883.0</v>
@@ -7779,7 +7774,7 @@
     </row>
     <row r="169">
       <c r="A169" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>32</v>
@@ -7803,7 +7798,7 @@
     </row>
     <row r="170">
       <c r="A170" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>32</v>
@@ -7825,7 +7820,7 @@
     </row>
     <row r="171">
       <c r="A171" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>111</v>
@@ -7837,10 +7832,10 @@
         <v>11.0</v>
       </c>
       <c r="E171" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="F171" s="17" t="s">
         <v>397</v>
-      </c>
-      <c r="F171" s="17" t="s">
-        <v>398</v>
       </c>
       <c r="G171" s="19">
         <v>46304.0</v>
@@ -7849,7 +7844,7 @@
     </row>
     <row r="172">
       <c r="A172" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>32</v>
@@ -7861,7 +7856,7 @@
         <v>9.0</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F172" s="17" t="s">
         <v>224</v>
@@ -7873,7 +7868,7 @@
     </row>
     <row r="173">
       <c r="A173" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>32</v>
@@ -7885,10 +7880,10 @@
         <v>9.0</v>
       </c>
       <c r="E173" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="F173" s="17" t="s">
         <v>402</v>
-      </c>
-      <c r="F173" s="17" t="s">
-        <v>403</v>
       </c>
       <c r="G173" s="19">
         <v>46555.0</v>
@@ -7897,7 +7892,7 @@
     </row>
     <row r="174">
       <c r="A174" s="10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>32</v>
@@ -7909,17 +7904,17 @@
         <v>8.0</v>
       </c>
       <c r="E174" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F174" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G174" s="12"/>
       <c r="H174" s="12"/>
     </row>
     <row r="175">
       <c r="A175" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>32</v>
@@ -7931,17 +7926,17 @@
         <v>7.0</v>
       </c>
       <c r="E175" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F175" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G175" s="12"/>
       <c r="H175" s="12"/>
     </row>
     <row r="176">
       <c r="A176" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>32</v>
@@ -7953,7 +7948,7 @@
         <v>7.0</v>
       </c>
       <c r="E176" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F176" s="17" t="s">
         <v>156</v>
@@ -7965,7 +7960,7 @@
     </row>
     <row r="177">
       <c r="A177" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>32</v>
@@ -7977,10 +7972,10 @@
         <v>6.0</v>
       </c>
       <c r="E177" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F177" s="17" t="s">
         <v>411</v>
-      </c>
-      <c r="F177" s="17" t="s">
-        <v>412</v>
       </c>
       <c r="G177" s="19">
         <v>46731.0</v>
@@ -7989,7 +7984,7 @@
     </row>
     <row r="178">
       <c r="A178" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>32</v>
@@ -8001,7 +7996,7 @@
         <v>6.0</v>
       </c>
       <c r="E178" s="11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F178" s="17">
         <v>11504.0</v>
@@ -8011,7 +8006,7 @@
     </row>
     <row r="179">
       <c r="A179" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>32</v>
@@ -8023,7 +8018,7 @@
         <v>6.0</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F179" s="17" t="s">
         <v>37</v>
@@ -8032,12 +8027,12 @@
         <v>46641.0</v>
       </c>
       <c r="H179" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>32</v>
@@ -8049,10 +8044,10 @@
         <v>5.0</v>
       </c>
       <c r="E180" s="11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F180" s="17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G180" s="19">
         <v>46711.0</v>
@@ -8061,7 +8056,7 @@
     </row>
     <row r="181">
       <c r="A181" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B181" s="11" t="s">
         <v>32</v>
@@ -8085,7 +8080,7 @@
     </row>
     <row r="182">
       <c r="A182" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>32</v>
@@ -8097,7 +8092,7 @@
         <v>3.0</v>
       </c>
       <c r="E182" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F182" s="14"/>
       <c r="G182" s="12"/>
@@ -8105,7 +8100,7 @@
     </row>
     <row r="183">
       <c r="A183" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>32</v>
@@ -8117,7 +8112,7 @@
         <v>3.0</v>
       </c>
       <c r="E183" s="11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F183" s="14"/>
       <c r="G183" s="12"/>
@@ -8125,7 +8120,7 @@
     </row>
     <row r="184">
       <c r="A184" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>32</v>
@@ -8137,7 +8132,7 @@
         <v>2.0</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="12"/>
@@ -8145,7 +8140,7 @@
     </row>
     <row r="185">
       <c r="A185" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>32</v>
@@ -8157,7 +8152,7 @@
         <v>1.0</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F185" s="14"/>
       <c r="G185" s="12"/>
@@ -8165,7 +8160,7 @@
     </row>
     <row r="186">
       <c r="A186" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>32</v>
@@ -8177,17 +8172,17 @@
         <v>3.0</v>
       </c>
       <c r="E186" s="11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F186" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G186" s="12"/>
       <c r="H186" s="12"/>
     </row>
     <row r="187">
       <c r="A187" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B187" s="11" t="s">
         <v>32</v>
@@ -8199,17 +8194,17 @@
         <v>3.0</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F187" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G187" s="12"/>
       <c r="H187" s="12"/>
     </row>
     <row r="188">
       <c r="A188" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>111</v>
@@ -8221,10 +8216,10 @@
         <v>21.0</v>
       </c>
       <c r="E188" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="F188" s="17" t="s">
         <v>434</v>
-      </c>
-      <c r="F188" s="17" t="s">
-        <v>435</v>
       </c>
       <c r="G188" s="19">
         <v>46267.0</v>
@@ -8233,7 +8228,7 @@
     </row>
     <row r="189">
       <c r="A189" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>32</v>
@@ -8245,7 +8240,7 @@
         <v>10.0</v>
       </c>
       <c r="E189" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F189" s="17" t="s">
         <v>16</v>
@@ -8255,7 +8250,7 @@
     </row>
     <row r="190">
       <c r="A190" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>32</v>
@@ -8267,7 +8262,7 @@
         <v>13.0</v>
       </c>
       <c r="E190" s="11" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F190" s="17" t="s">
         <v>16</v>
@@ -8277,7 +8272,7 @@
     </row>
     <row r="191">
       <c r="A191" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B191" s="11" t="s">
         <v>111</v>
@@ -8289,10 +8284,10 @@
         <v>22.0</v>
       </c>
       <c r="E191" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="F191" s="17" t="s">
         <v>440</v>
-      </c>
-      <c r="F191" s="17" t="s">
-        <v>441</v>
       </c>
       <c r="G191" s="12"/>
       <c r="H191" s="11" t="s">
@@ -8301,7 +8296,7 @@
     </row>
     <row r="192">
       <c r="A192" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B192" s="11" t="s">
         <v>111</v>
@@ -8316,7 +8311,7 @@
         <v>158</v>
       </c>
       <c r="F192" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G192" s="19">
         <v>46347.0</v>
@@ -8327,7 +8322,7 @@
     </row>
     <row r="193">
       <c r="A193" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>111</v>
@@ -8351,7 +8346,7 @@
     </row>
     <row r="194">
       <c r="A194" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>111</v>
@@ -8363,7 +8358,7 @@
         <v>22.0</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F194" s="14"/>
       <c r="G194" s="12"/>
@@ -8373,7 +8368,7 @@
     </row>
     <row r="195">
       <c r="A195" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B195" s="11" t="s">
         <v>111</v>
@@ -8385,10 +8380,10 @@
         <v>22.0</v>
       </c>
       <c r="E195" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="F195" s="17" t="s">
         <v>448</v>
-      </c>
-      <c r="F195" s="17" t="s">
-        <v>449</v>
       </c>
       <c r="G195" s="12"/>
       <c r="H195" s="11" t="s">
@@ -8397,7 +8392,7 @@
     </row>
     <row r="196">
       <c r="A196" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>111</v>
@@ -8412,7 +8407,7 @@
         <v>93</v>
       </c>
       <c r="F196" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G196" s="19">
         <v>46767.0</v>
@@ -8421,7 +8416,7 @@
     </row>
     <row r="197">
       <c r="A197" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>111</v>
@@ -8433,10 +8428,10 @@
         <v>21.0</v>
       </c>
       <c r="E197" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F197" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G197" s="19">
         <v>46767.0</v>
@@ -8445,7 +8440,7 @@
     </row>
     <row r="198">
       <c r="A198" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>111</v>
@@ -8460,7 +8455,7 @@
         <v>219</v>
       </c>
       <c r="F198" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G198" s="19">
         <v>46736.0</v>
@@ -8469,7 +8464,7 @@
     </row>
     <row r="199">
       <c r="A199" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B199" s="11" t="s">
         <v>111</v>
@@ -8481,10 +8476,10 @@
         <v>21.0</v>
       </c>
       <c r="E199" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="F199" s="17" t="s">
         <v>455</v>
-      </c>
-      <c r="F199" s="17" t="s">
-        <v>456</v>
       </c>
       <c r="G199" s="19">
         <v>46774.0</v>
@@ -8493,7 +8488,7 @@
     </row>
     <row r="200">
       <c r="A200" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>111</v>
@@ -8508,7 +8503,7 @@
         <v>101</v>
       </c>
       <c r="F200" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G200" s="19">
         <v>46670.0</v>
@@ -8517,7 +8512,7 @@
     </row>
     <row r="201">
       <c r="A201" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>111</v>
@@ -8532,7 +8527,7 @@
         <v>158</v>
       </c>
       <c r="F201" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G201" s="19">
         <v>46752.0</v>
@@ -8541,7 +8536,7 @@
     </row>
     <row r="202">
       <c r="A202" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>111</v>
@@ -8556,14 +8551,14 @@
         <v>101</v>
       </c>
       <c r="F202" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G202" s="12"/>
       <c r="H202" s="12"/>
     </row>
     <row r="203">
       <c r="A203" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B203" s="11" t="s">
         <v>32</v>
@@ -8575,7 +8570,7 @@
         <v>11.0</v>
       </c>
       <c r="E203" s="11" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F203" s="17" t="s">
         <v>232</v>
@@ -8584,7 +8579,7 @@
         <v>46162.0</v>
       </c>
       <c r="H203" s="11" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I203" s="2" t="s">
         <v>229</v>
@@ -8592,7 +8587,7 @@
     </row>
     <row r="204">
       <c r="A204" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>111</v>
@@ -8604,10 +8599,10 @@
         <v>15.0</v>
       </c>
       <c r="E204" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="F204" s="17" t="s">
         <v>466</v>
-      </c>
-      <c r="F204" s="17" t="s">
-        <v>467</v>
       </c>
       <c r="G204" s="19">
         <v>46481.0</v>
@@ -8616,7 +8611,7 @@
     </row>
     <row r="205">
       <c r="A205" s="10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>111</v>
@@ -8628,7 +8623,7 @@
         <v>4.0</v>
       </c>
       <c r="E205" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F205" s="17" t="s">
         <v>224</v>
@@ -8638,7 +8633,7 @@
     </row>
     <row r="206">
       <c r="A206" s="10" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>111</v>
@@ -8650,7 +8645,7 @@
         <v>3.0</v>
       </c>
       <c r="E206" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F206" s="17" t="s">
         <v>224</v>
@@ -8660,7 +8655,7 @@
     </row>
     <row r="207">
       <c r="A207" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>111</v>
@@ -8672,7 +8667,7 @@
         <v>3.0</v>
       </c>
       <c r="E207" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F207" s="17" t="s">
         <v>224</v>
@@ -8682,7 +8677,7 @@
     </row>
     <row r="208">
       <c r="A208" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>111</v>
@@ -8694,7 +8689,7 @@
         <v>3.0</v>
       </c>
       <c r="E208" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F208" s="17" t="s">
         <v>224</v>
@@ -8704,7 +8699,7 @@
     </row>
     <row r="209">
       <c r="A209" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>111</v>
@@ -8716,10 +8711,10 @@
         <v>2.0</v>
       </c>
       <c r="E209" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="F209" s="17" t="s">
         <v>475</v>
-      </c>
-      <c r="F209" s="17" t="s">
-        <v>476</v>
       </c>
       <c r="G209" s="19">
         <v>46618.0</v>
@@ -8728,7 +8723,7 @@
     </row>
     <row r="210">
       <c r="A210" s="10" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>32</v>
@@ -8740,7 +8735,7 @@
         <v>1.0</v>
       </c>
       <c r="E210" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F210" s="14"/>
       <c r="G210" s="12"/>
@@ -8748,7 +8743,7 @@
     </row>
     <row r="211">
       <c r="A211" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>111</v>
@@ -8760,10 +8755,10 @@
         <v>22.0</v>
       </c>
       <c r="E211" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="F211" s="17" t="s">
         <v>480</v>
-      </c>
-      <c r="F211" s="17" t="s">
-        <v>481</v>
       </c>
       <c r="G211" s="19">
         <v>46516.0</v>
@@ -8772,7 +8767,7 @@
     </row>
     <row r="212">
       <c r="A212" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>111</v>
@@ -8784,10 +8779,10 @@
         <v>21.0</v>
       </c>
       <c r="E212" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="F212" s="17" t="s">
         <v>483</v>
-      </c>
-      <c r="F212" s="17" t="s">
-        <v>484</v>
       </c>
       <c r="G212" s="19">
         <v>46759.0</v>
@@ -8796,7 +8791,7 @@
     </row>
     <row r="213">
       <c r="A213" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B213" s="11" t="s">
         <v>111</v>
@@ -8808,7 +8803,7 @@
         <v>20.0</v>
       </c>
       <c r="E213" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F213" s="17" t="s">
         <v>141</v>
@@ -8820,7 +8815,7 @@
     </row>
     <row r="214">
       <c r="A214" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>111</v>
@@ -8832,7 +8827,7 @@
         <v>20.0</v>
       </c>
       <c r="E214" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F214" s="17" t="s">
         <v>224</v>
@@ -8844,7 +8839,7 @@
     </row>
     <row r="215">
       <c r="A215" s="10" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>111</v>
@@ -8856,7 +8851,7 @@
         <v>20.0</v>
       </c>
       <c r="E215" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F215" s="17" t="s">
         <v>232</v>
@@ -8868,7 +8863,7 @@
     </row>
     <row r="216">
       <c r="A216" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>111</v>
@@ -8880,10 +8875,10 @@
         <v>20.0</v>
       </c>
       <c r="E216" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="F216" s="17" t="s">
         <v>492</v>
-      </c>
-      <c r="F216" s="17" t="s">
-        <v>493</v>
       </c>
       <c r="G216" s="19">
         <v>46544.0</v>
@@ -8892,7 +8887,7 @@
     </row>
     <row r="217">
       <c r="A217" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B217" s="11" t="s">
         <v>111</v>
@@ -8904,10 +8899,10 @@
         <v>19.0</v>
       </c>
       <c r="E217" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F217" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G217" s="19">
         <v>46394.0</v>
@@ -8916,7 +8911,7 @@
     </row>
     <row r="218">
       <c r="A218" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>111</v>
@@ -8928,10 +8923,10 @@
         <v>21.0</v>
       </c>
       <c r="E218" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="F218" s="17" t="s">
         <v>497</v>
-      </c>
-      <c r="F218" s="17" t="s">
-        <v>498</v>
       </c>
       <c r="G218" s="19">
         <v>46949.0</v>
@@ -8940,7 +8935,7 @@
     </row>
     <row r="219">
       <c r="A219" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>111</v>
@@ -8952,7 +8947,7 @@
         <v>19.0</v>
       </c>
       <c r="E219" s="11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F219" s="17" t="s">
         <v>224</v>
@@ -8964,7 +8959,7 @@
     </row>
     <row r="220">
       <c r="A220" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>111</v>
@@ -8976,7 +8971,7 @@
         <v>19.0</v>
       </c>
       <c r="E220" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F220" s="17" t="s">
         <v>16</v>
@@ -8988,7 +8983,7 @@
     </row>
     <row r="221">
       <c r="A221" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>111</v>
@@ -9000,7 +8995,7 @@
         <v>18.0</v>
       </c>
       <c r="E221" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F221" s="17" t="s">
         <v>269</v>
@@ -9012,7 +9007,7 @@
     </row>
     <row r="222">
       <c r="A222" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>111</v>
@@ -9024,7 +9019,7 @@
         <v>17.0</v>
       </c>
       <c r="E222" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F222" s="14"/>
       <c r="G222" s="19">
@@ -9034,7 +9029,7 @@
     </row>
     <row r="223">
       <c r="A223" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>111</v>
@@ -9046,7 +9041,7 @@
         <v>17.0</v>
       </c>
       <c r="E223" s="11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>147</v>
@@ -9058,7 +9053,7 @@
     </row>
     <row r="224">
       <c r="A224" s="10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>111</v>
@@ -9070,10 +9065,10 @@
         <v>15.0</v>
       </c>
       <c r="E224" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="F224" s="17" t="s">
         <v>510</v>
-      </c>
-      <c r="F224" s="17" t="s">
-        <v>511</v>
       </c>
       <c r="G224" s="19">
         <v>46417.0</v>
@@ -9082,7 +9077,7 @@
     </row>
     <row r="225">
       <c r="A225" s="10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>32</v>
@@ -9104,7 +9099,7 @@
     </row>
     <row r="226">
       <c r="A226" s="10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>32</v>
@@ -9126,7 +9121,7 @@
     </row>
     <row r="227">
       <c r="A227" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B227" s="11" t="s">
         <v>32</v>
@@ -9138,7 +9133,7 @@
         <v>13.0</v>
       </c>
       <c r="E227" s="11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F227" s="14"/>
       <c r="G227" s="19">
@@ -9148,7 +9143,7 @@
     </row>
     <row r="228">
       <c r="A228" s="10" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>32</v>
@@ -9160,7 +9155,7 @@
         <v>20.0</v>
       </c>
       <c r="E228" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F228" s="14"/>
       <c r="G228" s="12"/>
@@ -9170,7 +9165,7 @@
     </row>
     <row r="229">
       <c r="A229" s="10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B229" s="11" t="s">
         <v>32</v>
@@ -9182,7 +9177,7 @@
         <v>20.0</v>
       </c>
       <c r="E229" s="11" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F229" s="17"/>
       <c r="G229" s="12"/>
@@ -9192,7 +9187,7 @@
     </row>
     <row r="230">
       <c r="A230" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>32</v>
@@ -9214,7 +9209,7 @@
     </row>
     <row r="231">
       <c r="A231" s="10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B231" s="11" t="s">
         <v>32</v>
@@ -9226,7 +9221,7 @@
         <v>18.0</v>
       </c>
       <c r="E231" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F231" s="17" t="s">
         <v>16</v>
@@ -9236,7 +9231,7 @@
     </row>
     <row r="232">
       <c r="A232" s="10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>32</v>
@@ -9248,7 +9243,7 @@
         <v>2.0</v>
       </c>
       <c r="E232" s="11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F232" s="17" t="s">
         <v>224</v>
@@ -9258,7 +9253,7 @@
     </row>
     <row r="233">
       <c r="A233" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B233" s="11" t="s">
         <v>111</v>
@@ -9270,7 +9265,7 @@
         <v>11.0</v>
       </c>
       <c r="E233" s="11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F233" s="17">
         <v>11503.0</v>
@@ -9283,7 +9278,7 @@
         <v>1.77436324269E12</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>11</v>
@@ -9292,7 +9287,7 @@
         <v>2.0</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>156</v>
@@ -9309,7 +9304,7 @@
         <v>1.774363425608E12</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>11</v>
@@ -9318,11 +9313,11 @@
         <v>1.0</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F235" s="4"/>
       <c r="H235" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236">
@@ -9330,7 +9325,7 @@
         <v>1.774363487217E12</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>11</v>
@@ -9339,11 +9334,11 @@
         <v>2.0</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F236" s="4"/>
       <c r="H236" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="237">
@@ -9360,10 +9355,10 @@
         <v>15.0</v>
       </c>
       <c r="E237" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F237" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>532</v>
       </c>
       <c r="G237" s="9">
         <v>46873.0</v>
@@ -9384,10 +9379,10 @@
         <v>12.0</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G238" s="9">
         <v>46805.0</v>
@@ -9407,10 +9402,10 @@
         <v>11.0</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G239" s="9">
         <v>46424.0</v>
@@ -9430,10 +9425,10 @@
         <v>13.0</v>
       </c>
       <c r="E240" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F240" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="G240" s="9">
         <v>46530.0</v>
@@ -9454,7 +9449,7 @@
         <v>2.0</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F241" s="3">
         <v>11503.0</v>
@@ -9462,6 +9457,7 @@
       <c r="G241" s="9">
         <v>46826.0</v>
       </c>
+      <c r="H241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" s="1">
@@ -9497,7 +9493,7 @@
         <v>5.0</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>16</v>
@@ -9521,7 +9517,7 @@
         <v>4.0</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>224</v>
@@ -9564,7 +9560,7 @@
         <v>21.0</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>16</v>
@@ -9585,10 +9581,10 @@
         <v>15.0</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G247" s="9">
         <v>46337.0</v>
@@ -9609,13 +9605,16 @@
         <v>8.0</v>
       </c>
       <c r="E248" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F248" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="G248" s="9">
         <v>46516.0</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="249">
@@ -9699,7 +9698,7 @@
         <v>1.0</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>16</v>
@@ -9783,10 +9782,10 @@
         <v>7.0</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="257">
@@ -9806,9 +9805,7 @@
         <v>551</v>
       </c>
       <c r="F257" s="4"/>
-      <c r="G257" s="9">
-        <v>46162.0</v>
-      </c>
+      <c r="G257" s="9"/>
       <c r="I257" s="2" t="s">
         <v>229</v>
       </c>
@@ -9984,7 +9981,7 @@
         <v>559</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G265" s="9">
         <v>46488.0</v>
@@ -10159,7 +10156,7 @@
         <v>4.0</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>224</v>
@@ -10202,7 +10199,7 @@
         <v>3.0</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>224</v>
@@ -10266,10 +10263,10 @@
         <v>16.0</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="279">
@@ -10491,7 +10488,7 @@
         <v>65</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G288" s="9">
         <v>46794.0</v>
@@ -10607,7 +10604,7 @@
         <v>589</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G293" s="9">
         <v>46758.0</v>
@@ -10630,7 +10627,7 @@
         <v>590</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G294" s="9">
         <v>46794.0</v>
@@ -10720,7 +10717,7 @@
         <v>592</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G298" s="9">
         <v>46285.0</v>
@@ -10812,7 +10809,7 @@
         <v>598</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G302" s="9">
         <v>47286.0</v>
@@ -10879,7 +10876,7 @@
         <v>601</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G305" s="9">
         <v>46987.0</v>
@@ -10954,7 +10951,7 @@
         <v>18</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G308" s="9">
         <v>46987.0</v>
@@ -11074,6 +11071,9 @@
       <c r="G313" s="9">
         <v>46204.0</v>
       </c>
+      <c r="I313" s="2" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1">
@@ -11195,7 +11195,7 @@
         <v>1.776148337734E12</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>11</v>
@@ -11221,7 +11221,7 @@
         <v>1.776148418097E12</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>11</v>
@@ -11244,7 +11244,7 @@
         <v>1.776148449855E12</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>11</v>
@@ -11267,7 +11267,7 @@
         <v>1.776148475121E12</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>11</v>
@@ -11290,7 +11290,7 @@
         <v>1.776148592568E12</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>11</v>
@@ -11316,7 +11316,7 @@
         <v>1.776148632656E12</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>11</v>
@@ -11342,7 +11342,7 @@
         <v>1.776148710229E12</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>11</v>
@@ -11368,7 +11368,7 @@
         <v>1.776148761624E12</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>11</v>
@@ -11394,7 +11394,7 @@
         <v>1.776149046956E12</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
@@ -11420,7 +11420,7 @@
         <v>1.776149087494E12</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>11</v>
@@ -11447,10 +11447,12 @@
         <v>1.0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F329" s="4"/>
-      <c r="H329" s="2"/>
+      <c r="H329" s="2" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1">
@@ -11466,7 +11468,7 @@
         <v>5.0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F330" s="4"/>
       <c r="G330" s="9">
@@ -11488,7 +11490,7 @@
         <v>18.0</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>224</v>
@@ -11511,7 +11513,7 @@
         <v>3.0</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F332" s="3">
         <v>11504.0</v>
@@ -11534,7 +11536,7 @@
         <v>581</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G333" s="9">
         <v>46949.0</v>
@@ -11557,7 +11559,7 @@
         <v>581</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G334" s="9">
         <v>46949.0</v>
@@ -11577,10 +11579,10 @@
         <v>9.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H335" s="2"/>
     </row>
@@ -11598,10 +11600,10 @@
         <v>10.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="337">
@@ -11618,10 +11620,10 @@
         <v>9.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="338">
@@ -11638,7 +11640,7 @@
         <v>13.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>238</v>
@@ -11661,10 +11663,10 @@
         <v>13.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G339" s="9">
         <v>46530.0</v>
@@ -11684,7 +11686,7 @@
         <v>16.0</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>238</v>
@@ -11707,7 +11709,7 @@
         <v>16.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>235</v>
@@ -11730,7 +11732,7 @@
         <v>16.0</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>235</v>
@@ -11753,7 +11755,7 @@
         <v>16.0</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F343" s="4"/>
     </row>
@@ -11771,7 +11773,7 @@
         <v>16.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>235</v>
@@ -11817,7 +11819,7 @@
         <v>17.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>579</v>
@@ -11863,10 +11865,10 @@
         <v>17.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G348" s="9">
         <v>46794.0</v>
@@ -11886,16 +11888,16 @@
         <v>20.0</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G349" s="9">
         <v>46691.0</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="350">
@@ -11912,7 +11914,7 @@
         <v>11.0</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>144</v>
@@ -11935,7 +11937,7 @@
         <v>12.0</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>238</v>
@@ -11981,10 +11983,10 @@
         <v>11.0</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G353" s="9">
         <v>46669.0</v>
@@ -12004,10 +12006,10 @@
         <v>12.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G354" s="9">
         <v>46523.0</v>
@@ -12027,7 +12029,7 @@
         <v>12.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F355" s="4"/>
       <c r="G355" s="9">
@@ -12039,7 +12041,7 @@
         <v>1.776436049209E12</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
@@ -12066,10 +12068,10 @@
         <v>1.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G357" s="9">
         <v>46793.0</v>
@@ -12077,7 +12079,7 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>111</v>
@@ -12092,7 +12094,7 @@
         <v>65</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G358" s="9">
         <v>46949.0</v>
@@ -12100,7 +12102,7 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>111</v>
@@ -12112,10 +12114,10 @@
         <v>20.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G359" s="9">
         <v>46793.0</v>
@@ -12123,7 +12125,7 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>111</v>
@@ -12135,10 +12137,10 @@
         <v>16.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G360" s="9">
         <v>46639.0</v>
@@ -12146,7 +12148,7 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>10</v>
@@ -12158,13 +12160,13 @@
         <v>3.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F361" s="4"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>10</v>
@@ -12176,13 +12178,13 @@
         <v>4.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F362" s="4"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>10</v>
@@ -12194,13 +12196,13 @@
         <v>5.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F363" s="4"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>10</v>
@@ -12212,13 +12214,13 @@
         <v>5.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F364" s="4"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>10</v>
@@ -12230,13 +12232,13 @@
         <v>5.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F365" s="4"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>10</v>
@@ -12248,13 +12250,13 @@
         <v>5.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F366" s="4"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>10</v>
@@ -12266,13 +12268,13 @@
         <v>1.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F367" s="4"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>32</v>
@@ -12284,15 +12286,15 @@
         <v>2.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>32</v>
@@ -12304,10 +12306,10 @@
         <v>2.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G369" s="9">
         <v>46488.0</v>
@@ -12315,7 +12317,7 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>32</v>
@@ -12327,15 +12329,15 @@
         <v>2.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F370" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>32</v>
@@ -12347,10 +12349,10 @@
         <v>4.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G371" s="9">
         <v>46716.0</v>
@@ -12359,7 +12361,7 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>111</v>
@@ -12371,7 +12373,7 @@
         <v>10.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F372" s="3">
         <v>11504.0</v>
@@ -12382,7 +12384,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>111</v>
@@ -12394,7 +12396,7 @@
         <v>8.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F373" s="3">
         <v>11504.0</v>
@@ -12403,7 +12405,7 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>32</v>
@@ -12415,14 +12417,14 @@
         <v>3.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F374" s="4"/>
       <c r="H374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>32</v>
@@ -12434,21 +12436,21 @@
         <v>11.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G375" s="9">
         <v>46240.0</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>111</v>
@@ -12460,10 +12462,10 @@
         <v>13.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G376" s="9">
         <v>46416.0</v>
@@ -12471,7 +12473,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>111</v>
@@ -12483,10 +12485,10 @@
         <v>16.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G377" s="9">
         <v>46544.0</v>
@@ -12494,7 +12496,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>111</v>
@@ -12506,21 +12508,21 @@
         <v>16.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G378" s="9">
         <v>46794.0</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>111</v>
@@ -12532,10 +12534,10 @@
         <v>16.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G379" s="9">
         <v>46785.0</v>
@@ -12543,7 +12545,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>111</v>
@@ -12558,7 +12560,7 @@
         <v>574</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G380" s="9">
         <v>46789.0</v>
@@ -12566,7 +12568,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>111</v>
@@ -12578,10 +12580,10 @@
         <v>16.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G381" s="9">
         <v>46839.0</v>
@@ -12589,7 +12591,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>111</v>
@@ -12601,10 +12603,10 @@
         <v>11.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G382" s="9">
         <v>46312.0</v>
@@ -12615,7 +12617,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>111</v>
@@ -12627,10 +12629,10 @@
         <v>17.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G383" s="9">
         <v>46669.0</v>
@@ -12639,7 +12641,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>111</v>
@@ -12651,10 +12653,10 @@
         <v>7.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G384" s="9">
         <v>46794.0</v>
@@ -12662,7 +12664,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>111</v>
@@ -12674,10 +12676,10 @@
         <v>7.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G385" s="9">
         <v>46792.0</v>
@@ -12685,7 +12687,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>111</v>
@@ -12697,7 +12699,7 @@
         <v>6.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F386" s="3">
         <v>11504.0</v>
@@ -12706,7 +12708,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>111</v>
@@ -12718,7 +12720,7 @@
         <v>9.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F387" s="3">
         <v>115004.0</v>
@@ -12729,7 +12731,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>32</v>
@@ -12741,7 +12743,7 @@
         <v>3.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F388" s="3">
         <v>11505.0</v>
@@ -12749,7 +12751,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>32</v>
@@ -12761,7 +12763,7 @@
         <v>11.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>232</v>
@@ -12770,7 +12772,7 @@
         <v>46162.0</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I389" s="2" t="s">
         <v>229</v>
@@ -12778,7 +12780,7 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>32</v>
@@ -12790,13 +12792,13 @@
         <v>22.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F390" s="4"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>32</v>
@@ -12808,16 +12810,16 @@
         <v>11.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G391" s="9">
         <v>46152.0</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I391" s="2" t="s">
         <v>229</v>
@@ -12825,7 +12827,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>111</v>
@@ -12837,10 +12839,10 @@
         <v>20.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G392" s="9">
         <v>46596.0</v>
@@ -12848,7 +12850,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>111</v>
@@ -12860,10 +12862,10 @@
         <v>16.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G393" s="9">
         <v>46669.0</v>
@@ -12871,7 +12873,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>32</v>
@@ -12883,15 +12885,15 @@
         <v>9.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>32</v>
@@ -12903,15 +12905,15 @@
         <v>10.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>32</v>
@@ -12923,7 +12925,7 @@
         <v>549</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G396" s="9">
         <v>46410.0</v>
@@ -12931,7 +12933,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>32</v>
@@ -12943,10 +12945,10 @@
         <v>22.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G397" s="9">
         <v>46194.0</v>
@@ -12957,7 +12959,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>32</v>
@@ -12969,10 +12971,10 @@
         <v>5.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G398" s="9">
         <v>46257.0</v>
@@ -12980,7 +12982,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>111</v>
@@ -12995,7 +12997,7 @@
         <v>577</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G399" s="9">
         <v>46913.0</v>
@@ -13003,7 +13005,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>10</v>
@@ -13015,7 +13017,7 @@
         <v>2.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>224</v>
@@ -13023,7 +13025,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>10</v>
@@ -13043,7 +13045,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>10</v>
@@ -13055,7 +13057,7 @@
         <v>2.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>16</v>
@@ -13063,7 +13065,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>10</v>
@@ -13075,7 +13077,7 @@
         <v>2.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>37</v>
@@ -13086,7 +13088,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>10</v>
@@ -13098,7 +13100,7 @@
         <v>3.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F404" s="4"/>
       <c r="G404" s="9">
@@ -13107,7 +13109,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>32</v>
@@ -13119,10 +13121,10 @@
         <v>4.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F405" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G405" s="9">
         <v>46507.0</v>
@@ -13130,7 +13132,7 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>32</v>
@@ -13142,10 +13144,10 @@
         <v>4.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G406" s="9">
         <v>46484.0</v>
@@ -13153,7 +13155,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>111</v>
@@ -13165,7 +13167,7 @@
         <v>6.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F407" s="3">
         <v>11505.0</v>
@@ -13173,7 +13175,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>32</v>
@@ -13185,7 +13187,7 @@
         <v>5.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>56</v>
@@ -13193,7 +13195,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>111</v>
@@ -13205,7 +13207,7 @@
         <v>1.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F409" s="3" t="s">
         <v>269</v>
@@ -13216,7 +13218,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>111</v>
@@ -13228,7 +13230,7 @@
         <v>17.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>584</v>
@@ -13239,7 +13241,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>111</v>
@@ -13251,7 +13253,7 @@
         <v>17.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>584</v>
@@ -13262,7 +13264,7 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>111</v>
@@ -13274,7 +13276,7 @@
         <v>17.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>584</v>
@@ -13285,7 +13287,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>111</v>
@@ -13297,7 +13299,7 @@
         <v>17.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>584</v>
@@ -13308,7 +13310,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>111</v>
@@ -13320,10 +13322,10 @@
         <v>17.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G414" s="9">
         <v>46523.0</v>
@@ -13331,7 +13333,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>111</v>
@@ -13343,7 +13345,7 @@
         <v>22.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>224</v>
@@ -13351,7 +13353,7 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>111</v>
@@ -13363,7 +13365,7 @@
         <v>12.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F416" s="3" t="s">
         <v>224</v>
@@ -13371,7 +13373,7 @@
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>32</v>
@@ -13383,7 +13385,7 @@
         <v>19.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>224</v>
@@ -13391,7 +13393,7 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>32</v>
@@ -13403,7 +13405,7 @@
         <v>6.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>224</v>
@@ -13411,7 +13413,7 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>111</v>
@@ -13423,7 +13425,7 @@
         <v>14.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>235</v>
@@ -13434,7 +13436,7 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>32</v>
@@ -13446,18 +13448,18 @@
         <v>10.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>32</v>
@@ -13469,10 +13471,10 @@
         <v>18.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G421" s="9">
         <v>47146.0</v>
@@ -13480,7 +13482,7 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>32</v>
@@ -13492,18 +13494,18 @@
         <v>10.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>111</v>
@@ -13515,10 +13517,10 @@
         <v>18.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G423" s="9">
         <v>46666.0</v>
@@ -13526,7 +13528,7 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>32</v>
@@ -13538,10 +13540,10 @@
         <v>8.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G424" s="9">
         <v>46604.0</v>
@@ -13549,7 +13551,7 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>32</v>
@@ -13561,7 +13563,7 @@
         <v>8.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>109</v>
@@ -13572,7 +13574,7 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>32</v>
@@ -13584,10 +13586,10 @@
         <v>8.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G426" s="9">
         <v>46658.0</v>
@@ -13595,7 +13597,7 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>32</v>
@@ -13607,10 +13609,10 @@
         <v>8.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G427" s="9">
         <v>46669.0</v>
@@ -13618,7 +13620,7 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>10</v>
@@ -13630,13 +13632,13 @@
         <v>4.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F428" s="4"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>32</v>
@@ -13648,15 +13650,15 @@
         <v>11.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>111</v>
@@ -13668,21 +13670,21 @@
         <v>17.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="G430" s="9">
         <v>46792.0</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>32</v>
@@ -13694,10 +13696,10 @@
         <v>8.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G431" s="9">
         <v>46304.0</v>
@@ -13705,7 +13707,7 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>32</v>
@@ -13728,7 +13730,7 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>32</v>
@@ -13740,10 +13742,10 @@
         <v>20.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G433" s="9">
         <v>46255.0</v>
@@ -13751,7 +13753,7 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>32</v>
@@ -13763,7 +13765,7 @@
         <v>12.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>37</v>
@@ -13774,7 +13776,7 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>111</v>
@@ -13786,10 +13788,10 @@
         <v>20.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G435" s="9">
         <v>46794.0</v>
@@ -13797,7 +13799,7 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>111</v>
@@ -13809,10 +13811,10 @@
         <v>18.0</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F436" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G436" s="9">
         <v>46794.0</v>
@@ -13820,7 +13822,7 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>111</v>
@@ -13832,10 +13834,10 @@
         <v>13.0</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G437" s="9">
         <v>46484.0</v>
@@ -13843,7 +13845,7 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>111</v>
@@ -13855,10 +13857,10 @@
         <v>20.0</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="G438" s="9">
         <v>46792.0</v>
@@ -13866,7 +13868,7 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>32</v>
@@ -13878,7 +13880,7 @@
         <v>9.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>569</v>
@@ -13889,7 +13891,7 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>32</v>
@@ -13901,13 +13903,13 @@
         <v>9.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F440" s="4"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>111</v>
@@ -13919,10 +13921,10 @@
         <v>12.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G441" s="9">
         <v>46641.0</v>
@@ -13930,7 +13932,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>111</v>
@@ -13942,10 +13944,10 @@
         <v>11.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G442" s="9">
         <v>46530.0</v>
@@ -13953,7 +13955,7 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>111</v>
@@ -13965,10 +13967,10 @@
         <v>13.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G443" s="9">
         <v>46949.0</v>
@@ -13976,7 +13978,7 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>111</v>
@@ -13988,7 +13990,7 @@
         <v>3.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>569</v>
@@ -13999,7 +14001,7 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>111</v>
@@ -14011,10 +14013,10 @@
         <v>3.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G445" s="9">
         <v>46752.0</v>
@@ -14022,7 +14024,7 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>111</v>
@@ -14034,10 +14036,10 @@
         <v>3.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G446" s="9">
         <v>46752.0</v>
@@ -14045,7 +14047,7 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>32</v>
@@ -14057,7 +14059,7 @@
         <v>3.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>569</v>
@@ -14068,7 +14070,7 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>32</v>
@@ -14080,10 +14082,10 @@
         <v>3.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G448" s="9">
         <v>46752.0</v>
@@ -14091,7 +14093,7 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>32</v>
@@ -14103,7 +14105,7 @@
         <v>3.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>46</v>
@@ -14114,7 +14116,7 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>111</v>
@@ -14129,12 +14131,12 @@
         <v>568</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>32</v>
@@ -14149,7 +14151,7 @@
         <v>562</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G451" s="9">
         <v>46670.0</v>
@@ -14160,7 +14162,7 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>32</v>
@@ -14172,7 +14174,7 @@
         <v>7.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>94</v>
@@ -14183,7 +14185,7 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>111</v>
@@ -14198,7 +14200,7 @@
         <v>563</v>
       </c>
       <c r="F453" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G453" s="9">
         <v>46556.0</v>
@@ -14206,7 +14208,7 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>111</v>
@@ -14218,7 +14220,7 @@
         <v>22.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F454" s="3" t="s">
         <v>141</v>
@@ -14229,7 +14231,7 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>111</v>
@@ -14241,10 +14243,10 @@
         <v>22.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F455" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G455" s="9">
         <v>46670.0</v>
@@ -14252,7 +14254,7 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>32</v>
@@ -14264,10 +14266,10 @@
         <v>17.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G456" s="9">
         <v>46254.0</v>
@@ -14276,7 +14278,7 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>32</v>
@@ -14288,10 +14290,10 @@
         <v>11.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G457" s="9">
         <v>46669.0</v>
@@ -14299,7 +14301,7 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>32</v>
@@ -14311,10 +14313,10 @@
         <v>6.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G458" s="9">
         <v>46669.0</v>
@@ -14322,7 +14324,7 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>32</v>
@@ -14334,10 +14336,10 @@
         <v>6.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G459" s="9">
         <v>46669.0</v>
@@ -14345,7 +14347,7 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>32</v>
@@ -14357,10 +14359,10 @@
         <v>6.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G460" s="9">
         <v>46669.0</v>
@@ -14368,7 +14370,7 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>32</v>
@@ -14380,10 +14382,10 @@
         <v>6.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G461" s="9">
         <v>46669.0</v>
@@ -14391,7 +14393,7 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>32</v>
@@ -14403,10 +14405,10 @@
         <v>18.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G462" s="9">
         <v>46947.0</v>
@@ -14414,7 +14416,7 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>32</v>
@@ -14429,7 +14431,7 @@
         <v>590</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G463" s="9">
         <v>46949.0</v>
@@ -14437,7 +14439,7 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>32</v>
@@ -14452,7 +14454,7 @@
         <v>65</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G464" s="9">
         <v>46949.0</v>
@@ -14460,7 +14462,7 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>32</v>
@@ -14472,15 +14474,15 @@
         <v>18.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>32</v>
@@ -14492,7 +14494,7 @@
         <v>3.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F466" s="3" t="s">
         <v>44</v>
@@ -14503,7 +14505,7 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>32</v>
@@ -14515,15 +14517,15 @@
         <v>4.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>32</v>
@@ -14535,7 +14537,7 @@
         <v>1.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>117</v>
@@ -14543,7 +14545,7 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>32</v>
@@ -14555,10 +14557,10 @@
         <v>2.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G469" s="9">
         <v>46267.0</v>
@@ -14566,7 +14568,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>32</v>
@@ -14578,10 +14580,10 @@
         <v>8.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G470" s="9">
         <v>46250.0</v>
@@ -14589,7 +14591,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>32</v>
@@ -14601,10 +14603,10 @@
         <v>8.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G471" s="9">
         <v>46255.0</v>
@@ -14612,7 +14614,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>111</v>
@@ -14624,10 +14626,10 @@
         <v>20.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G472" s="9">
         <v>46613.0</v>
@@ -14635,7 +14637,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>32</v>
@@ -14658,7 +14660,7 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>32</v>
@@ -14670,10 +14672,10 @@
         <v>7.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G474" s="9">
         <v>46691.0</v>
@@ -14681,7 +14683,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>32</v>
@@ -14693,10 +14695,10 @@
         <v>7.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G475" s="9">
         <v>46775.0</v>
@@ -14704,7 +14706,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>32</v>
@@ -14716,13 +14718,13 @@
         <v>11.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F476" s="4"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>32</v>
@@ -14734,13 +14736,13 @@
         <v>11.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F477" s="4"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>32</v>
@@ -14752,13 +14754,13 @@
         <v>11.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F478" s="4"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>32</v>
@@ -14770,13 +14772,13 @@
         <v>11.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F479" s="4"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>111</v>
@@ -14788,10 +14790,10 @@
         <v>21.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="G480" s="9">
         <v>46803.0</v>
@@ -14799,7 +14801,7 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>32</v>
@@ -14811,10 +14813,10 @@
         <v>22.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="G481" s="9">
         <v>46222.0</v>
@@ -14822,7 +14824,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>32</v>
@@ -14834,13 +14836,13 @@
         <v>11.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F482" s="4"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>32</v>
@@ -14852,13 +14854,13 @@
         <v>11.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F483" s="4"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>32</v>
@@ -14870,13 +14872,13 @@
         <v>11.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F484" s="4"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>32</v>
@@ -14888,13 +14890,13 @@
         <v>11.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F485" s="4"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>32</v>
@@ -14906,7 +14908,7 @@
         <v>14.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F486" s="4"/>
       <c r="G486" s="9">
@@ -14915,7 +14917,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>32</v>
@@ -14927,7 +14929,7 @@
         <v>14.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F487" s="4"/>
       <c r="G487" s="9">
@@ -14936,7 +14938,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>32</v>
@@ -14948,7 +14950,7 @@
         <v>14.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F488" s="4"/>
       <c r="G488" s="9">
@@ -14957,7 +14959,7 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>32</v>
@@ -14969,7 +14971,7 @@
         <v>15.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F489" s="4"/>
       <c r="G489" s="9">
@@ -14978,7 +14980,7 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>32</v>
@@ -14990,7 +14992,7 @@
         <v>15.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F490" s="4"/>
       <c r="G490" s="9">
@@ -14999,7 +15001,7 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>32</v>
@@ -15011,7 +15013,7 @@
         <v>15.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F491" s="4"/>
       <c r="G491" s="9">
@@ -15020,7 +15022,7 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>32</v>
@@ -15032,7 +15034,7 @@
         <v>15.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F492" s="4"/>
       <c r="G492" s="9">
@@ -15041,7 +15043,7 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>32</v>
@@ -15053,7 +15055,7 @@
         <v>11.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F493" s="4"/>
       <c r="G493" s="9">
@@ -15062,7 +15064,7 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>32</v>
@@ -15074,7 +15076,7 @@
         <v>11.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F494" s="4"/>
       <c r="G494" s="9">
@@ -15083,7 +15085,7 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>111</v>
@@ -15095,15 +15097,15 @@
         <v>8.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>32</v>
@@ -15115,13 +15117,13 @@
         <v>12.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>32</v>
@@ -15133,10 +15135,10 @@
         <v>15.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G497" s="9">
         <v>46759.0</v>
@@ -15144,10 +15146,10 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>11</v>
@@ -15156,7 +15158,7 @@
         <v>3.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F498" s="3" t="s">
         <v>37</v>
@@ -15167,10 +15169,10 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>11</v>
@@ -15179,7 +15181,7 @@
         <v>3.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>37</v>
@@ -15190,10 +15192,10 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>11</v>
@@ -15202,7 +15204,7 @@
         <v>3.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>37</v>
@@ -15213,10 +15215,10 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>11</v>
@@ -15225,7 +15227,7 @@
         <v>3.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>37</v>
@@ -15236,10 +15238,10 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>11</v>
@@ -15248,10 +15250,10 @@
         <v>3.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G502" s="9">
         <v>46406.0</v>
@@ -15259,10 +15261,10 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>11</v>
@@ -15271,7 +15273,7 @@
         <v>3.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>37</v>
@@ -15282,10 +15284,10 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>11</v>
@@ -15294,7 +15296,7 @@
         <v>3.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F504" s="3" t="s">
         <v>37</v>
@@ -15305,10 +15307,10 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>11</v>
@@ -15317,7 +15319,7 @@
         <v>3.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F505" s="3" t="s">
         <v>37</v>
@@ -15328,10 +15330,10 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>11</v>
@@ -15340,7 +15342,7 @@
         <v>4.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>37</v>
@@ -15351,10 +15353,10 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>11</v>
@@ -15363,7 +15365,7 @@
         <v>4.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>37</v>
@@ -15374,10 +15376,10 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>11</v>
@@ -15386,7 +15388,7 @@
         <v>4.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F508" s="3" t="s">
         <v>37</v>
@@ -15397,10 +15399,10 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>11</v>
@@ -15409,7 +15411,7 @@
         <v>4.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>37</v>
@@ -15420,10 +15422,10 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>11</v>
@@ -15432,7 +15434,7 @@
         <v>6.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F510" s="3" t="s">
         <v>37</v>
@@ -15443,10 +15445,10 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>11</v>
@@ -15455,7 +15457,7 @@
         <v>6.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>37</v>
@@ -15466,10 +15468,10 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>11</v>
@@ -15478,7 +15480,7 @@
         <v>6.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F512" s="3" t="s">
         <v>37</v>
@@ -15489,10 +15491,10 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>11</v>
@@ -15501,7 +15503,7 @@
         <v>6.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F513" s="3" t="s">
         <v>37</v>
@@ -15512,10 +15514,10 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>11</v>
@@ -15524,7 +15526,7 @@
         <v>6.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F514" s="3" t="s">
         <v>37</v>
@@ -15535,10 +15537,10 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>11</v>
@@ -15547,7 +15549,7 @@
         <v>6.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F515" s="3" t="s">
         <v>37</v>
@@ -15558,10 +15560,10 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>11</v>
@@ -15570,7 +15572,7 @@
         <v>6.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F516" s="3" t="s">
         <v>37</v>
@@ -15581,10 +15583,10 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>11</v>
@@ -15593,7 +15595,7 @@
         <v>7.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F517" s="3" t="s">
         <v>16</v>
@@ -15604,10 +15606,10 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>11</v>
@@ -15616,7 +15618,7 @@
         <v>7.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>16</v>
@@ -15627,10 +15629,10 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>11</v>
@@ -15639,7 +15641,7 @@
         <v>7.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>16</v>
@@ -15650,10 +15652,10 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>11</v>
@@ -15662,7 +15664,7 @@
         <v>8.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F520" s="3" t="s">
         <v>16</v>
@@ -15673,10 +15675,10 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>11</v>
@@ -15685,7 +15687,7 @@
         <v>8.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>16</v>
@@ -15696,10 +15698,10 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>11</v>
@@ -15708,7 +15710,7 @@
         <v>8.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>16</v>
@@ -15719,10 +15721,10 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>11</v>
@@ -15731,7 +15733,7 @@
         <v>8.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>16</v>
@@ -15742,10 +15744,10 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>11</v>
@@ -15754,7 +15756,7 @@
         <v>8.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>16</v>
@@ -15765,10 +15767,10 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>11</v>
@@ -15777,10 +15779,10 @@
         <v>9.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F525" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G525" s="9">
         <v>46365.0</v>
@@ -15788,10 +15790,10 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>11</v>
@@ -15800,7 +15802,7 @@
         <v>9.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>37</v>
@@ -15811,10 +15813,10 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>11</v>
@@ -15823,7 +15825,7 @@
         <v>10.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>37</v>
@@ -15832,15 +15834,15 @@
         <v>46426.0</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>11</v>
@@ -15849,10 +15851,10 @@
         <v>10.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F528" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G528" s="9">
         <v>46211.0</v>
@@ -15860,10 +15862,10 @@
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>11</v>
@@ -15872,21 +15874,24 @@
         <v>10.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G529" s="9">
         <v>46204.0</v>
       </c>
+      <c r="I529" s="2" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>11</v>
@@ -15895,10 +15900,10 @@
         <v>10.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G530" s="9">
         <v>46345.0</v>
@@ -15906,10 +15911,10 @@
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>11</v>
@@ -15918,7 +15923,7 @@
         <v>11.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>37</v>
@@ -15929,10 +15934,10 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>11</v>
@@ -15941,10 +15946,10 @@
         <v>13.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F532" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G532" s="9">
         <v>46366.0</v>
@@ -15952,10 +15957,10 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>11</v>
@@ -15964,22 +15969,19 @@
         <v>14.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F533" s="4"/>
       <c r="G533" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I533" s="2" t="s">
-        <v>229</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>11</v>
@@ -15988,76 +15990,74 @@
         <v>14.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F534" s="4"/>
       <c r="G534" s="9">
-        <v>46178.0</v>
-      </c>
-      <c r="I534" s="2" t="s">
-        <v>229</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D535" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F535" s="4"/>
-      <c r="G535" s="9">
-        <v>46220.0</v>
+        <v>1006</v>
+      </c>
+      <c r="F535" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D536" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F536" s="4"/>
-      <c r="G536" s="9">
-        <v>46220.0</v>
+        <v>1008</v>
+      </c>
+      <c r="F536" s="3" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D537" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="F537" s="3" t="s">
         <v>156</v>
+      </c>
+      <c r="G537" s="9">
+        <v>46223.0</v>
       </c>
     </row>
     <row r="538">
@@ -16065,7 +16065,7 @@
         <v>1010</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>11</v>
@@ -16078,6 +16078,9 @@
       </c>
       <c r="F538" s="3" t="s">
         <v>156</v>
+      </c>
+      <c r="G538" s="9">
+        <v>46228.0</v>
       </c>
     </row>
     <row r="539">
@@ -16085,184 +16088,182 @@
         <v>1012</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D539" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>156</v>
+        <v>613</v>
       </c>
       <c r="G539" s="9">
-        <v>46223.0</v>
+        <v>46269.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D540" s="2">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>156</v>
+        <v>618</v>
       </c>
       <c r="G540" s="9">
-        <v>46228.0</v>
+        <v>46240.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D541" s="2">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="G541" s="9">
-        <v>46269.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D542" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>618</v>
+        <v>1020</v>
       </c>
       <c r="G542" s="9">
-        <v>46240.0</v>
-      </c>
+        <v>46274.0</v>
+      </c>
+      <c r="H542" s="2"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D543" s="2">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>618</v>
+        <v>1023</v>
       </c>
       <c r="G543" s="9">
-        <v>46242.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D544" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="G544" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H544" s="2"/>
+        <v>46207.0</v>
+      </c>
+      <c r="I544" s="2" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>111</v>
+        <v>525</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D545" s="2">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F545" s="3" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G545" s="9">
-        <v>46743.0</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="F545" s="4"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D546" s="2">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>1029</v>
+        <v>232</v>
       </c>
       <c r="G546" s="9">
-        <v>46207.0</v>
+        <v>46295.0</v>
       </c>
     </row>
     <row r="547">
@@ -16270,40 +16271,45 @@
         <v>1030</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>526</v>
+        <v>32</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D547" s="2">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="F547" s="4"/>
+        <v>1031</v>
+      </c>
+      <c r="F547" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G547" s="9">
+        <v>46769.0</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C548" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D548" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E548" s="2" t="s">
         <v>1031</v>
       </c>
-      <c r="B548" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C548" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D548" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E548" s="2" t="s">
-        <v>1032</v>
-      </c>
       <c r="F548" s="3" t="s">
-        <v>232</v>
+        <v>1020</v>
       </c>
       <c r="G548" s="9">
-        <v>46295.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="549">
@@ -16311,22 +16317,22 @@
         <v>1033</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>32</v>
+        <v>525</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D549" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E549" s="2" t="s">
         <v>1034</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>1023</v>
+        <v>614</v>
       </c>
       <c r="G549" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="550">
@@ -16334,30 +16340,30 @@
         <v>1035</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>32</v>
+        <v>525</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D550" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>1023</v>
+        <v>614</v>
       </c>
       <c r="G550" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>11</v>
@@ -16366,21 +16372,21 @@
         <v>3.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F551" s="3" t="s">
         <v>614</v>
       </c>
       <c r="G551" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>11</v>
@@ -16389,21 +16395,21 @@
         <v>3.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F552" s="3" t="s">
         <v>614</v>
       </c>
       <c r="G552" s="9">
-        <v>46261.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>11</v>
@@ -16412,7 +16418,7 @@
         <v>3.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F553" s="3" t="s">
         <v>614</v>
@@ -16423,10 +16429,10 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>526</v>
+        <v>32</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>11</v>
@@ -16435,64 +16441,64 @@
         <v>3.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>614</v>
+        <v>1020</v>
       </c>
       <c r="G554" s="9">
-        <v>46223.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D555" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1045</v>
+        <v>702</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>614</v>
+        <v>1046</v>
       </c>
       <c r="G555" s="9">
-        <v>46266.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D556" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E556" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F556" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="B556" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C556" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D556" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E556" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F556" s="3" t="s">
-        <v>1023</v>
-      </c>
       <c r="G556" s="9">
-        <v>46769.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>111</v>
@@ -16504,13 +16510,13 @@
         <v>14.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="G557" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="558">
@@ -16527,36 +16533,36 @@
         <v>14.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1051</v>
+        <v>590</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="G558" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D559" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>697</v>
+        <v>873</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="G559" s="9">
-        <v>46820.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="560">
@@ -16564,27 +16570,27 @@
         <v>1053</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D560" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>590</v>
+        <v>1054</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="G560" s="9">
-        <v>46998.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>32</v>
@@ -16596,18 +16602,18 @@
         <v>2.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>872</v>
+        <v>1057</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="G561" s="9">
-        <v>46484.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>32</v>
@@ -16619,18 +16625,18 @@
         <v>2.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>1058</v>
+        <v>448</v>
       </c>
       <c r="G562" s="9">
-        <v>46432.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>32</v>
@@ -16642,18 +16648,16 @@
         <v>2.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G563" s="9">
-        <v>46877.0</v>
-      </c>
+        <v>1063</v>
+      </c>
+      <c r="G563" s="9"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>32</v>
@@ -16665,18 +16669,15 @@
         <v>2.0</v>
       </c>
       <c r="E564" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F564" s="3" t="s">
         <v>1063</v>
-      </c>
-      <c r="F564" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G564" s="9">
-        <v>46704.0</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>32</v>
@@ -16688,12 +16689,11 @@
         <v>2.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1065</v>
+        <v>857</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>1066</v>
-      </c>
-      <c r="G565" s="9"/>
+        <v>1063</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
@@ -16709,15 +16709,15 @@
         <v>2.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1068</v>
+        <v>674</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>32</v>
@@ -16729,15 +16729,15 @@
         <v>2.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>856</v>
+        <v>1065</v>
       </c>
       <c r="F567" s="3" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>32</v>
@@ -16749,10 +16749,10 @@
         <v>2.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>673</v>
+        <v>1070</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="569">
@@ -16769,58 +16769,67 @@
         <v>2.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>1066</v>
+        <v>582</v>
+      </c>
+      <c r="G569" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D570" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1066</v>
+        <v>1075</v>
+      </c>
+      <c r="G570" s="9">
+        <v>46877.0</v>
+      </c>
+      <c r="H570" s="2" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D571" s="2">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E571" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="F571" s="3" t="s">
         <v>1075</v>
       </c>
-      <c r="F571" s="3" t="s">
-        <v>582</v>
-      </c>
       <c r="G571" s="9">
-        <v>46766.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>111</v>
@@ -16829,16 +16838,16 @@
         <v>11</v>
       </c>
       <c r="D572" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G572" s="9">
-        <v>46877.0</v>
+        <v>46743.0</v>
       </c>
       <c r="H572" s="2" t="s">
         <v>186</v>
@@ -16855,21 +16864,17 @@
         <v>11</v>
       </c>
       <c r="D573" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="F573" s="3" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G573" s="9">
-        <v>46641.0</v>
-      </c>
+        <v>1080</v>
+      </c>
+      <c r="F573" s="4"/>
+      <c r="H573" s="2"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>111</v>
@@ -16878,24 +16883,24 @@
         <v>11</v>
       </c>
       <c r="D574" s="2">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1081</v>
+        <v>792</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="G574" s="9">
-        <v>46743.0</v>
+        <v>46663.0</v>
       </c>
       <c r="H574" s="2" t="s">
-        <v>186</v>
+        <v>132</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>111</v>
@@ -16904,17 +16909,21 @@
         <v>11</v>
       </c>
       <c r="D575" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F575" s="4"/>
-      <c r="H575" s="2"/>
+        <v>1084</v>
+      </c>
+      <c r="F575" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G575" s="9">
+        <v>46775.0</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>111</v>
@@ -16923,19 +16932,16 @@
         <v>11</v>
       </c>
       <c r="D576" s="2">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>791</v>
+        <v>649</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="G576" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H576" s="2" t="s">
-        <v>132</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="577">
@@ -16949,16 +16955,16 @@
         <v>11</v>
       </c>
       <c r="D577" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>1087</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G577" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="578">
@@ -16969,47 +16975,47 @@
         <v>111</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D578" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>648</v>
+        <v>1089</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G578" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D579" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G579" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>111</v>
@@ -17021,18 +17027,18 @@
         <v>14.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G580" s="9">
-        <v>46481.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>111</v>
@@ -17044,18 +17050,18 @@
         <v>14.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G581" s="9">
-        <v>46877.0</v>
+        <v>46734.0</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>111</v>
@@ -17067,18 +17073,18 @@
         <v>14.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G582" s="9">
-        <v>46872.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>111</v>
@@ -17090,18 +17096,18 @@
         <v>14.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G583" s="9">
-        <v>46734.0</v>
+        <v>46872.0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>111</v>
@@ -17113,36 +17119,36 @@
         <v>14.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G584" s="9">
-        <v>46481.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D585" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1102</v>
+        <v>829</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G585" s="9">
-        <v>46872.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="586">
@@ -17150,22 +17156,22 @@
         <v>1103</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>111</v>
+        <v>525</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D586" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E586" s="2" t="s">
         <v>1104</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>1078</v>
+        <v>1020</v>
       </c>
       <c r="G586" s="9">
-        <v>46877.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="587">
@@ -17173,42 +17179,42 @@
         <v>1105</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>111</v>
+        <v>525</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D587" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>828</v>
+        <v>1106</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1078</v>
+        <v>1020</v>
       </c>
       <c r="G587" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D588" s="2">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1107</v>
+        <v>643</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="G588" s="9">
         <v>46274.0</v>
@@ -17219,69 +17225,69 @@
         <v>1108</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>526</v>
+        <v>32</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D589" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="E589" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="F589" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G589" s="9">
-        <v>46274.0</v>
-      </c>
+      <c r="F589" s="3"/>
+      <c r="G589" s="9"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
         <v>1110</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D590" s="2">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>642</v>
+        <v>1111</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1023</v>
+        <v>224</v>
       </c>
       <c r="G590" s="9">
-        <v>46274.0</v>
+        <v>46437.0</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D591" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F591" s="3"/>
-      <c r="G591" s="9"/>
+        <v>1113</v>
+      </c>
+      <c r="F591" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G591" s="9">
+        <v>46516.0</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>111</v>
@@ -17290,126 +17296,128 @@
         <v>27</v>
       </c>
       <c r="D592" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F592" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G592" s="9">
-        <v>46437.0</v>
+        <v>1116</v>
+      </c>
+      <c r="F592" s="3"/>
+      <c r="G592" s="9"/>
+      <c r="H592" s="2" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D593" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F593" s="3" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G593" s="9">
-        <v>46516.0</v>
-      </c>
+        <v>1119</v>
+      </c>
+      <c r="F593" s="3"/>
+      <c r="G593" s="9"/>
+      <c r="H593" s="2"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D594" s="2">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F594" s="3"/>
+        <v>1121</v>
+      </c>
+      <c r="F594" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="G594" s="9"/>
-      <c r="H594" s="2" t="s">
-        <v>1120</v>
-      </c>
+      <c r="H594" s="2"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D595" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F595" s="3"/>
-      <c r="G595" s="9"/>
+        <v>1123</v>
+      </c>
+      <c r="F595" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G595" s="9">
+        <v>46403.0</v>
+      </c>
       <c r="H595" s="2"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D596" s="2">
-        <v>3.0</v>
+        <v>21.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1124</v>
+        <v>578</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G596" s="9"/>
+        <v>1125</v>
+      </c>
+      <c r="G596" s="9">
+        <v>46337.0</v>
+      </c>
       <c r="H596" s="2"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>111</v>
+        <v>525</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D597" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1126</v>
+        <v>612</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>16</v>
+        <v>613</v>
       </c>
       <c r="G597" s="9">
-        <v>46403.0</v>
+        <v>46269.0</v>
       </c>
       <c r="H597" s="2"/>
     </row>
@@ -17418,22 +17426,22 @@
         <v>1127</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>111</v>
+        <v>525</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D598" s="2">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>578</v>
+        <v>1013</v>
       </c>
       <c r="F598" s="3" t="s">
         <v>1128</v>
       </c>
       <c r="G598" s="9">
-        <v>46337.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H598" s="2"/>
     </row>
@@ -17442,7 +17450,7 @@
         <v>1129</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>11</v>
@@ -17451,22 +17459,18 @@
         <v>8.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="F599" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="G599" s="9">
-        <v>46269.0</v>
-      </c>
+        <v>1130</v>
+      </c>
+      <c r="F599" s="3"/>
+      <c r="G599" s="9"/>
       <c r="H599" s="2"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>11</v>
@@ -17475,10 +17479,10 @@
         <v>8.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1016</v>
+        <v>616</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="G600" s="9">
         <v>46290.0</v>
@@ -17490,67 +17494,69 @@
         <v>1132</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>526</v>
+        <v>32</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D601" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E601" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="F601" s="3"/>
-      <c r="G601" s="9"/>
+      <c r="F601" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G601" s="9">
+        <v>46883.0</v>
+      </c>
       <c r="H601" s="2"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>526</v>
+        <v>32</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D602" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>616</v>
+        <v>1133</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1131</v>
+        <v>392</v>
       </c>
       <c r="G602" s="9">
-        <v>46290.0</v>
+        <v>46883.0</v>
       </c>
       <c r="H602" s="2"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D603" s="2">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F603" s="3" t="s">
         <v>1137</v>
       </c>
-      <c r="G603" s="9">
-        <v>46883.0</v>
-      </c>
+      <c r="F603" s="3">
+        <v>11505.0</v>
+      </c>
+      <c r="G603" s="9"/>
       <c r="H603" s="2"/>
     </row>
     <row r="604">
@@ -17558,50 +17564,48 @@
         <v>1138</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D604" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F604" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G604" s="9">
-        <v>46883.0</v>
-      </c>
+        <v>1139</v>
+      </c>
+      <c r="F604" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G604" s="9"/>
       <c r="H604" s="2"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D605" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F605" s="3">
-        <v>11505.0</v>
+        <v>11504.0</v>
       </c>
       <c r="G605" s="9"/>
       <c r="H605" s="2"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>111</v>
@@ -17610,10 +17614,10 @@
         <v>27</v>
       </c>
       <c r="D606" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1142</v>
+        <v>536</v>
       </c>
       <c r="F606" s="3">
         <v>11504.0</v>
@@ -17626,26 +17630,26 @@
         <v>1143</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D607" s="2">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="F607" s="3">
-        <v>11504.0</v>
+      <c r="F607" s="3" t="s">
+        <v>1145</v>
       </c>
       <c r="G607" s="9"/>
       <c r="H607" s="2"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>111</v>
@@ -17654,35 +17658,35 @@
         <v>27</v>
       </c>
       <c r="D608" s="2">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F608" s="3">
-        <v>11504.0</v>
+        <v>596</v>
+      </c>
+      <c r="F608" s="3" t="s">
+        <v>1147</v>
       </c>
       <c r="G608" s="9"/>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D609" s="2">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1147</v>
+        <v>596</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1148</v>
+        <v>597</v>
       </c>
       <c r="G609" s="9"/>
       <c r="H609" s="2"/>
@@ -17695,40 +17699,44 @@
         <v>111</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D610" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>596</v>
+        <v>536</v>
       </c>
       <c r="F610" s="3" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G610" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="G610" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="H610" s="2"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D611" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E611" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B611" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C611" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D611" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E611" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="F611" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="G611" s="9"/>
+      <c r="F611" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G611" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="H611" s="2"/>
     </row>
     <row r="612">
@@ -17736,19 +17744,19 @@
         <v>1152</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D612" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F612" s="3" t="s">
-        <v>38</v>
+        <v>1153</v>
+      </c>
+      <c r="F612" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G612" s="2" t="s">
         <v>38</v>
@@ -17757,19 +17765,19 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D613" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F613" s="3">
         <v>11506.0</v>
@@ -17781,25 +17789,25 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D614" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F614" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G614" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="F614" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G614" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H614" s="2"/>
     </row>
@@ -17808,28 +17816,28 @@
         <v>1157</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D615" s="2">
         <v>1.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F615" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G615" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="F615" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G615" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H615" s="2"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>10</v>
@@ -17838,7 +17846,7 @@
         <v>25</v>
       </c>
       <c r="D616" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E616" s="2" t="s">
         <v>20</v>
@@ -17853,25 +17861,25 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D617" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E617" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F617" s="3" t="s">
         <v>1160</v>
       </c>
-      <c r="B617" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C617" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D617" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E617" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F617" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G617" s="9">
-        <v>47531.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H617" s="2"/>
     </row>
@@ -17880,31 +17888,31 @@
         <v>1161</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>10</v>
+        <v>525</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D618" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>20</v>
+        <v>621</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>37</v>
+        <v>1162</v>
       </c>
       <c r="G618" s="9">
-        <v>47531.0</v>
+        <v>46223.0</v>
       </c>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>11</v>
@@ -17913,13 +17921,13 @@
         <v>10.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>623</v>
+        <v>1025</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G619" s="9">
-        <v>46217.0</v>
+        <v>46221.0</v>
       </c>
       <c r="H619" s="2"/>
     </row>
@@ -17928,7 +17936,7 @@
         <v>1164</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>11</v>
@@ -17937,67 +17945,59 @@
         <v>10.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="G620" s="9">
-        <v>46223.0</v>
+        <v>46214.0</v>
       </c>
       <c r="H620" s="2"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="C621" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D621" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F621" s="3" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G621" s="9">
-        <v>46221.0</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="F621" s="3"/>
+      <c r="G621" s="9"/>
       <c r="H621" s="2"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="C622" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D622" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F622" s="3" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G622" s="9">
-        <v>46214.0</v>
-      </c>
+        <v>1141</v>
+      </c>
+      <c r="F622" s="3"/>
+      <c r="G622" s="9"/>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>111</v>
@@ -18006,18 +18006,22 @@
         <v>11</v>
       </c>
       <c r="D623" s="2">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="F623" s="3"/>
-      <c r="G623" s="9"/>
+        <v>882</v>
+      </c>
+      <c r="F623" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G623" s="9">
+        <v>46636.0</v>
+      </c>
       <c r="H623" s="2"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>111</v>
@@ -18026,61 +18030,63 @@
         <v>11</v>
       </c>
       <c r="D624" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F624" s="3"/>
-      <c r="G624" s="9"/>
+        <v>560</v>
+      </c>
+      <c r="F624" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="G624" s="9">
+        <v>46814.0</v>
+      </c>
       <c r="H624" s="2"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D625" s="2">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="F625" s="3" t="s">
-        <v>141</v>
+        <v>1109</v>
+      </c>
+      <c r="F625" s="3">
+        <v>11505.0</v>
       </c>
       <c r="G625" s="9">
-        <v>46636.0</v>
+        <v>46814.0</v>
       </c>
       <c r="H625" s="2"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D626" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E626" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B626" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C626" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D626" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E626" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="F626" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="G626" s="9">
-        <v>46814.0</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="G626" s="9"/>
       <c r="H626" s="2"/>
     </row>
     <row r="627">
@@ -18091,20 +18097,18 @@
         <v>111</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D627" s="2">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F627" s="3">
-        <v>11505.0</v>
-      </c>
-      <c r="G627" s="9">
-        <v>46814.0</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="F627" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G627" s="9"/>
       <c r="H627" s="2"/>
     </row>
     <row r="628">
@@ -18115,41 +18119,21 @@
         <v>111</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D628" s="2">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
       <c r="E628" s="2" t="s">
         <v>1174</v>
       </c>
       <c r="F628" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="G628" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="G628" s="9">
+        <v>46179.0</v>
+      </c>
       <c r="H628" s="2"/>
-    </row>
-    <row r="629">
-      <c r="A629" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B629" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C629" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D629" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E629" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="F629" s="3" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G629" s="9"/>
-      <c r="H629" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="1175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="1172">
   <si>
     <t>ID</t>
   </si>
@@ -1498,6 +1498,9 @@
     <t>JOLT (豬肉)</t>
   </si>
   <si>
+    <t>同品在庫: 極冷庫-左1F-19</t>
+  </si>
+  <si>
     <t>ID39835414951408</t>
   </si>
   <si>
@@ -1897,9 +1900,6 @@
     <t>無庫位</t>
   </si>
   <si>
-    <t>需補貨</t>
-  </si>
-  <si>
     <t>34B(34-36)</t>
   </si>
   <si>
@@ -3460,9 +3460,6 @@
     <t>ID1780473345775</t>
   </si>
   <si>
-    <t>ID1780492852348</t>
-  </si>
-  <si>
     <t>ID1780534348697</t>
   </si>
   <si>
@@ -3530,12 +3527,6 @@
   </si>
   <si>
     <t>ID1780622891013</t>
-  </si>
-  <si>
-    <t>ID1780708907917</t>
-  </si>
-  <si>
-    <t>離線回傳測試</t>
   </si>
 </sst>
 </file>
@@ -8907,11 +8898,13 @@
       <c r="G217" s="19">
         <v>46394.0</v>
       </c>
-      <c r="H217" s="12"/>
+      <c r="H217" s="11" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>111</v>
@@ -8923,10 +8916,10 @@
         <v>21.0</v>
       </c>
       <c r="E218" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F218" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G218" s="19">
         <v>46949.0</v>
@@ -8935,7 +8928,7 @@
     </row>
     <row r="219">
       <c r="A219" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>111</v>
@@ -8947,7 +8940,7 @@
         <v>19.0</v>
       </c>
       <c r="E219" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F219" s="17" t="s">
         <v>224</v>
@@ -8959,7 +8952,7 @@
     </row>
     <row r="220">
       <c r="A220" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>111</v>
@@ -8971,7 +8964,7 @@
         <v>19.0</v>
       </c>
       <c r="E220" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F220" s="17" t="s">
         <v>16</v>
@@ -8983,7 +8976,7 @@
     </row>
     <row r="221">
       <c r="A221" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>111</v>
@@ -8995,7 +8988,7 @@
         <v>18.0</v>
       </c>
       <c r="E221" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F221" s="17" t="s">
         <v>269</v>
@@ -9007,7 +9000,7 @@
     </row>
     <row r="222">
       <c r="A222" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>111</v>
@@ -9019,7 +9012,7 @@
         <v>17.0</v>
       </c>
       <c r="E222" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F222" s="14"/>
       <c r="G222" s="19">
@@ -9029,7 +9022,7 @@
     </row>
     <row r="223">
       <c r="A223" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>111</v>
@@ -9041,7 +9034,7 @@
         <v>17.0</v>
       </c>
       <c r="E223" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>147</v>
@@ -9053,7 +9046,7 @@
     </row>
     <row r="224">
       <c r="A224" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>111</v>
@@ -9065,10 +9058,10 @@
         <v>15.0</v>
       </c>
       <c r="E224" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F224" s="17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G224" s="19">
         <v>46417.0</v>
@@ -9077,7 +9070,7 @@
     </row>
     <row r="225">
       <c r="A225" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>32</v>
@@ -9099,7 +9092,7 @@
     </row>
     <row r="226">
       <c r="A226" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>32</v>
@@ -9121,7 +9114,7 @@
     </row>
     <row r="227">
       <c r="A227" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B227" s="11" t="s">
         <v>32</v>
@@ -9133,7 +9126,7 @@
         <v>13.0</v>
       </c>
       <c r="E227" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F227" s="14"/>
       <c r="G227" s="19">
@@ -9143,7 +9136,7 @@
     </row>
     <row r="228">
       <c r="A228" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>32</v>
@@ -9155,7 +9148,7 @@
         <v>20.0</v>
       </c>
       <c r="E228" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F228" s="14"/>
       <c r="G228" s="12"/>
@@ -9165,7 +9158,7 @@
     </row>
     <row r="229">
       <c r="A229" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B229" s="11" t="s">
         <v>32</v>
@@ -9177,7 +9170,7 @@
         <v>20.0</v>
       </c>
       <c r="E229" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F229" s="17"/>
       <c r="G229" s="12"/>
@@ -9187,7 +9180,7 @@
     </row>
     <row r="230">
       <c r="A230" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>32</v>
@@ -9209,7 +9202,7 @@
     </row>
     <row r="231">
       <c r="A231" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B231" s="11" t="s">
         <v>32</v>
@@ -9231,7 +9224,7 @@
     </row>
     <row r="232">
       <c r="A232" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>32</v>
@@ -9243,7 +9236,7 @@
         <v>2.0</v>
       </c>
       <c r="E232" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F232" s="17" t="s">
         <v>224</v>
@@ -9253,7 +9246,7 @@
     </row>
     <row r="233">
       <c r="A233" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B233" s="11" t="s">
         <v>111</v>
@@ -9265,7 +9258,7 @@
         <v>11.0</v>
       </c>
       <c r="E233" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F233" s="17">
         <v>11503.0</v>
@@ -9278,7 +9271,7 @@
         <v>1.77436324269E12</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>11</v>
@@ -9287,7 +9280,7 @@
         <v>2.0</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>156</v>
@@ -9304,7 +9297,7 @@
         <v>1.774363425608E12</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>11</v>
@@ -9313,11 +9306,11 @@
         <v>1.0</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F235" s="4"/>
       <c r="H235" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="236">
@@ -9325,7 +9318,7 @@
         <v>1.774363487217E12</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>11</v>
@@ -9334,11 +9327,11 @@
         <v>2.0</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F236" s="4"/>
       <c r="H236" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="237">
@@ -9355,10 +9348,10 @@
         <v>15.0</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G237" s="9">
         <v>46873.0</v>
@@ -9379,10 +9372,10 @@
         <v>12.0</v>
       </c>
       <c r="E238" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F238" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="G238" s="9">
         <v>46805.0</v>
@@ -9402,10 +9395,10 @@
         <v>11.0</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G239" s="9">
         <v>46424.0</v>
@@ -9425,10 +9418,10 @@
         <v>13.0</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G240" s="9">
         <v>46530.0</v>
@@ -9449,7 +9442,7 @@
         <v>2.0</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F241" s="3">
         <v>11503.0</v>
@@ -9493,7 +9486,7 @@
         <v>5.0</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>16</v>
@@ -9517,7 +9510,7 @@
         <v>4.0</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>224</v>
@@ -9560,7 +9553,7 @@
         <v>21.0</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>16</v>
@@ -9581,7 +9574,7 @@
         <v>15.0</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>466</v>
@@ -9605,16 +9598,16 @@
         <v>8.0</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G248" s="9">
         <v>46516.0</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="249">
@@ -9631,7 +9624,7 @@
         <v>12.0</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F249" s="3">
         <v>11503.0</v>
@@ -9651,7 +9644,7 @@
         <v>16.0</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>235</v>
@@ -9674,10 +9667,10 @@
         <v>12.0</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G251" s="9">
         <v>46395.0</v>
@@ -9698,7 +9691,7 @@
         <v>1.0</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>16</v>
@@ -9718,7 +9711,7 @@
         <v>1.0</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F253" s="3"/>
     </row>
@@ -9736,10 +9729,10 @@
         <v>3.0</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G254" s="9">
         <v>46613.0</v>
@@ -9759,7 +9752,7 @@
         <v>7.0</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>81</v>
@@ -9802,7 +9795,7 @@
         <v>12.0</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F257" s="4"/>
       <c r="G257" s="9"/>
@@ -9824,7 +9817,7 @@
         <v>14.0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F258" s="4"/>
       <c r="G258" s="9">
@@ -9846,7 +9839,7 @@
         <v>13.0</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F259" s="4"/>
       <c r="G259" s="9">
@@ -9868,7 +9861,7 @@
         <v>12.0</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F260" s="4"/>
       <c r="G260" s="9">
@@ -9892,7 +9885,7 @@
         <v>12.0</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F261" s="4"/>
       <c r="G261" s="9">
@@ -9913,7 +9906,7 @@
         <v>14.0</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F262" s="4"/>
       <c r="G262" s="9">
@@ -9934,7 +9927,7 @@
         <v>14.0</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="9">
@@ -9958,7 +9951,7 @@
         <v>65</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G264" s="9">
         <v>46949.0</v>
@@ -9978,7 +9971,7 @@
         <v>4.0</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>342</v>
@@ -10001,10 +9994,10 @@
         <v>17.0</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G266" s="9">
         <v>46743.0</v>
@@ -10024,10 +10017,10 @@
         <v>17.0</v>
       </c>
       <c r="E267" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F267" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="G267" s="9">
         <v>46752.0</v>
@@ -10047,10 +10040,10 @@
         <v>17.0</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G268" s="9">
         <v>46750.0</v>
@@ -10070,7 +10063,7 @@
         <v>16.0</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F269" s="4"/>
       <c r="G269" s="9">
@@ -10091,7 +10084,7 @@
         <v>13.0</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F270" s="4"/>
       <c r="G270" s="9">
@@ -10112,7 +10105,7 @@
         <v>16.0</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F271" s="4"/>
       <c r="G271" s="9">
@@ -10133,7 +10126,7 @@
         <v>15.0</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>269</v>
@@ -10176,10 +10169,10 @@
         <v>19.0</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G274" s="9">
         <v>46670.0</v>
@@ -10199,7 +10192,7 @@
         <v>3.0</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>224</v>
@@ -10219,10 +10212,10 @@
         <v>20.0</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G276" s="9">
         <v>46789.0</v>
@@ -10283,10 +10276,10 @@
         <v>16.0</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G279" s="9">
         <v>46681.0</v>
@@ -10306,10 +10299,10 @@
         <v>16.0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G280" s="9">
         <v>46725.0</v>
@@ -10329,10 +10322,10 @@
         <v>8.0</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G281" s="9">
         <v>46789.0</v>
@@ -10352,10 +10345,10 @@
         <v>8.0</v>
       </c>
       <c r="E282" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F282" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="F282" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="G282" s="9">
         <v>46757.0</v>
@@ -10375,10 +10368,10 @@
         <v>17.0</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G283" s="9">
         <v>46947.0</v>
@@ -10398,7 +10391,7 @@
         <v>9.0</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F284" s="3">
         <v>11503.0</v>
@@ -10418,7 +10411,7 @@
         <v>2.0</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F285" s="3">
         <v>11504.0</v>
@@ -10439,10 +10432,10 @@
         <v>18.0</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G286" s="9">
         <v>46949.0</v>
@@ -10462,10 +10455,10 @@
         <v>18.0</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G287" s="9">
         <v>46794.0</v>
@@ -10508,7 +10501,7 @@
         <v>21.0</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>16</v>
@@ -10531,7 +10524,7 @@
         <v>16.0</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>16</v>
@@ -10554,7 +10547,7 @@
         <v>4.0</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>16</v>
@@ -10577,7 +10570,7 @@
         <v>4.0</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>16</v>
@@ -10601,7 +10594,7 @@
         <v>19.0</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>483</v>
@@ -10624,7 +10617,7 @@
         <v>19.0</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>483</v>
@@ -10647,7 +10640,7 @@
         <v>18.0</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F295" s="4"/>
       <c r="G295" s="9">
@@ -10668,10 +10661,10 @@
         <v>9.0</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G296" s="9">
         <v>46577.0</v>
@@ -10691,7 +10684,7 @@
         <v>9.0</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F297" s="3">
         <v>1140221.0</v>
@@ -10714,7 +10707,7 @@
         <v>9.0</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>367</v>
@@ -10737,10 +10730,10 @@
         <v>12.0</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G299" s="9">
         <v>46596.0</v>
@@ -10760,10 +10753,10 @@
         <v>20.0</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G300" s="9">
         <v>46641.0</v>
@@ -10783,7 +10776,7 @@
         <v>2.0</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>141</v>
@@ -10806,7 +10799,7 @@
         <v>2.0</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>381</v>
@@ -10829,7 +10822,7 @@
         <v>3.0</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F303" s="4"/>
     </row>
@@ -10847,7 +10840,7 @@
         <v>5.0</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>16</v>
@@ -10873,7 +10866,7 @@
         <v>5.0</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>434</v>
@@ -10899,7 +10892,7 @@
         <v>5.0</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>16</v>
@@ -10974,7 +10967,7 @@
         <v>4.0</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>16</v>
@@ -10994,7 +10987,7 @@
         <v>4.0</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>16</v>
@@ -11017,7 +11010,7 @@
         <v>5.0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>16</v>
@@ -11040,7 +11033,7 @@
         <v>4.0</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>24</v>
@@ -11063,7 +11056,7 @@
         <v>4.0</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>24</v>
@@ -11089,7 +11082,7 @@
         <v>4.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>24</v>
@@ -11112,7 +11105,7 @@
         <v>4.0</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>24</v>
@@ -11135,7 +11128,7 @@
         <v>2.0</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>16</v>
@@ -11158,7 +11151,7 @@
         <v>2.0</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>16</v>
@@ -11181,7 +11174,7 @@
         <v>2.0</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F318" s="3" t="s">
         <v>16</v>
@@ -11195,7 +11188,7 @@
         <v>1.776148337734E12</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>11</v>
@@ -11204,10 +11197,10 @@
         <v>6.0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G319" s="9">
         <v>46269.0</v>
@@ -11221,7 +11214,7 @@
         <v>1.776148418097E12</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>11</v>
@@ -11230,10 +11223,10 @@
         <v>4.0</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G320" s="9">
         <v>46247.0</v>
@@ -11244,7 +11237,7 @@
         <v>1.776148449855E12</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>11</v>
@@ -11253,10 +11246,10 @@
         <v>4.0</v>
       </c>
       <c r="E321" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F321" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="F321" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="G321" s="9">
         <v>46247.0</v>
@@ -11267,7 +11260,7 @@
         <v>1.776148475121E12</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>11</v>
@@ -11276,10 +11269,10 @@
         <v>6.0</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G322" s="9">
         <v>46269.0</v>
@@ -11290,7 +11283,7 @@
         <v>1.776148592568E12</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>11</v>
@@ -11299,10 +11292,10 @@
         <v>12.0</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G323" s="9">
         <v>46234.0</v>
@@ -11316,7 +11309,7 @@
         <v>1.776148632656E12</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>11</v>
@@ -11325,10 +11318,10 @@
         <v>14.0</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G324" s="9">
         <v>46202.0</v>
@@ -11342,7 +11335,7 @@
         <v>1.776148710229E12</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>11</v>
@@ -11351,10 +11344,10 @@
         <v>13.0</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F325" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G325" s="9">
         <v>46193.0</v>
@@ -11368,7 +11361,7 @@
         <v>1.776148761624E12</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>11</v>
@@ -11377,10 +11370,10 @@
         <v>14.0</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G326" s="9">
         <v>46203.0</v>
@@ -11394,7 +11387,7 @@
         <v>1.776149046956E12</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>25</v>
@@ -11403,10 +11396,10 @@
         <v>4.0</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G327" s="9">
         <v>46182.0</v>
@@ -11420,7 +11413,7 @@
         <v>1.776149087494E12</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>11</v>
@@ -11429,7 +11422,7 @@
         <v>18.0</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F328" s="4"/>
     </row>
@@ -11447,12 +11440,10 @@
         <v>1.0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F329" s="4"/>
-      <c r="H329" s="2" t="s">
-        <v>628</v>
-      </c>
+      <c r="H329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" s="1">
@@ -11533,7 +11524,7 @@
         <v>4.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>632</v>
@@ -11556,7 +11547,7 @@
         <v>5.0</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>633</v>
@@ -11663,7 +11654,7 @@
         <v>13.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>466</v>
@@ -11796,10 +11787,10 @@
         <v>17.0</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G345" s="9">
         <v>46768.0</v>
@@ -11822,7 +11813,7 @@
         <v>643</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G346" s="9">
         <v>46947.0</v>
@@ -11842,10 +11833,10 @@
         <v>17.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G347" s="9">
         <v>46771.0</v>
@@ -11960,7 +11951,7 @@
         <v>7.0</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F352" s="3">
         <v>11503.0</v>
@@ -12041,7 +12032,7 @@
         <v>1.776436049209E12</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>25</v>
@@ -12557,7 +12548,7 @@
         <v>16.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F380" s="3" t="s">
         <v>699</v>
@@ -12922,7 +12913,7 @@
         <v>25</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>737</v>
@@ -12994,7 +12985,7 @@
         <v>7.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>745</v>
@@ -13167,11 +13158,12 @@
         <v>6.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F407" s="3">
         <v>11505.0</v>
       </c>
+      <c r="H407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
@@ -13233,7 +13225,7 @@
         <v>764</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G410" s="9">
         <v>46408.0</v>
@@ -13256,7 +13248,7 @@
         <v>766</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G411" s="9">
         <v>46473.0</v>
@@ -13279,7 +13271,7 @@
         <v>768</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G412" s="9">
         <v>46758.0</v>
@@ -13302,7 +13294,7 @@
         <v>770</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G413" s="9">
         <v>46431.0</v>
@@ -13719,7 +13711,7 @@
         <v>19.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>52</v>
@@ -13883,7 +13875,7 @@
         <v>826</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G439" s="9">
         <v>46676.0</v>
@@ -13993,7 +13985,7 @@
         <v>811</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G444" s="9">
         <v>46670.0</v>
@@ -14062,7 +14054,7 @@
         <v>811</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G447" s="9">
         <v>46670.0</v>
@@ -14128,7 +14120,7 @@
         <v>19.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>656</v>
@@ -14148,7 +14140,7 @@
         <v>3.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>842</v>
@@ -14197,7 +14189,7 @@
         <v>22.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>315</v>
@@ -14428,7 +14420,7 @@
         <v>18.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>867</v>
@@ -14649,10 +14641,10 @@
         <v>13.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G473" s="9">
         <v>46669.0</v>
@@ -15149,7 +15141,7 @@
         <v>932</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>11</v>
@@ -15172,7 +15164,7 @@
         <v>934</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>11</v>
@@ -15195,7 +15187,7 @@
         <v>936</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>11</v>
@@ -15218,7 +15210,7 @@
         <v>938</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>11</v>
@@ -15241,7 +15233,7 @@
         <v>940</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>11</v>
@@ -15264,7 +15256,7 @@
         <v>941</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>11</v>
@@ -15287,7 +15279,7 @@
         <v>943</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>11</v>
@@ -15310,7 +15302,7 @@
         <v>945</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>11</v>
@@ -15333,7 +15325,7 @@
         <v>947</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>11</v>
@@ -15356,7 +15348,7 @@
         <v>949</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>11</v>
@@ -15379,7 +15371,7 @@
         <v>951</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>11</v>
@@ -15402,7 +15394,7 @@
         <v>953</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>11</v>
@@ -15425,7 +15417,7 @@
         <v>955</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>11</v>
@@ -15448,7 +15440,7 @@
         <v>957</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>11</v>
@@ -15471,7 +15463,7 @@
         <v>959</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>11</v>
@@ -15494,7 +15486,7 @@
         <v>961</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>11</v>
@@ -15517,7 +15509,7 @@
         <v>963</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>11</v>
@@ -15540,7 +15532,7 @@
         <v>965</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>11</v>
@@ -15563,7 +15555,7 @@
         <v>967</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>11</v>
@@ -15586,7 +15578,7 @@
         <v>969</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>11</v>
@@ -15609,7 +15601,7 @@
         <v>971</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>11</v>
@@ -15632,7 +15624,7 @@
         <v>973</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>11</v>
@@ -15655,7 +15647,7 @@
         <v>975</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>11</v>
@@ -15678,7 +15670,7 @@
         <v>977</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>11</v>
@@ -15701,7 +15693,7 @@
         <v>979</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>11</v>
@@ -15724,7 +15716,7 @@
         <v>981</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>11</v>
@@ -15747,7 +15739,7 @@
         <v>983</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>11</v>
@@ -15770,7 +15762,7 @@
         <v>985</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>11</v>
@@ -15793,7 +15785,7 @@
         <v>987</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>11</v>
@@ -15816,7 +15808,7 @@
         <v>988</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>11</v>
@@ -15842,7 +15834,7 @@
         <v>991</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>11</v>
@@ -15865,7 +15857,7 @@
         <v>993</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>11</v>
@@ -15891,7 +15883,7 @@
         <v>995</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>11</v>
@@ -15914,7 +15906,7 @@
         <v>997</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>11</v>
@@ -15937,7 +15929,7 @@
         <v>999</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>11</v>
@@ -15960,7 +15952,7 @@
         <v>1001</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>11</v>
@@ -15981,7 +15973,7 @@
         <v>1003</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>11</v>
@@ -16002,7 +15994,7 @@
         <v>1005</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>11</v>
@@ -16022,7 +16014,7 @@
         <v>1007</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>11</v>
@@ -16042,7 +16034,7 @@
         <v>1009</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>11</v>
@@ -16065,7 +16057,7 @@
         <v>1010</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>11</v>
@@ -16088,7 +16080,7 @@
         <v>1012</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>11</v>
@@ -16100,7 +16092,7 @@
         <v>1013</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G539" s="9">
         <v>46269.0</v>
@@ -16111,7 +16103,7 @@
         <v>1014</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>11</v>
@@ -16123,7 +16115,7 @@
         <v>1015</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G540" s="9">
         <v>46240.0</v>
@@ -16134,7 +16126,7 @@
         <v>1016</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>11</v>
@@ -16146,7 +16138,7 @@
         <v>1017</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G541" s="9">
         <v>46242.0</v>
@@ -16157,7 +16149,7 @@
         <v>1018</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>11</v>
@@ -16204,7 +16196,7 @@
         <v>1024</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>11</v>
@@ -16230,7 +16222,7 @@
         <v>1027</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>11</v>
@@ -16239,7 +16231,7 @@
         <v>21.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F545" s="4"/>
     </row>
@@ -16317,7 +16309,7 @@
         <v>1033</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>11</v>
@@ -16329,7 +16321,7 @@
         <v>1034</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G549" s="9">
         <v>46261.0</v>
@@ -16340,7 +16332,7 @@
         <v>1035</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>11</v>
@@ -16352,7 +16344,7 @@
         <v>1036</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G550" s="9">
         <v>46261.0</v>
@@ -16363,7 +16355,7 @@
         <v>1037</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>11</v>
@@ -16375,7 +16367,7 @@
         <v>1038</v>
       </c>
       <c r="F551" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G551" s="9">
         <v>46266.0</v>
@@ -16386,7 +16378,7 @@
         <v>1039</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>11</v>
@@ -16398,7 +16390,7 @@
         <v>1040</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G552" s="9">
         <v>46223.0</v>
@@ -16409,7 +16401,7 @@
         <v>1041</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>11</v>
@@ -16421,7 +16413,7 @@
         <v>1042</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G553" s="9">
         <v>46266.0</v>
@@ -16533,7 +16525,7 @@
         <v>14.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F558" s="3" t="s">
         <v>1046</v>
@@ -16772,7 +16764,7 @@
         <v>1072</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G569" s="9">
         <v>46766.0</v>
@@ -17156,7 +17148,7 @@
         <v>1103</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>11</v>
@@ -17179,7 +17171,7 @@
         <v>1105</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>11</v>
@@ -17202,7 +17194,7 @@
         <v>1107</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C588" s="2" t="s">
         <v>11</v>
@@ -17387,7 +17379,7 @@
         <v>21.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F596" s="3" t="s">
         <v>1125</v>
@@ -17402,7 +17394,7 @@
         <v>1126</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C597" s="2" t="s">
         <v>11</v>
@@ -17411,10 +17403,10 @@
         <v>8.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G597" s="9">
         <v>46269.0</v>
@@ -17426,7 +17418,7 @@
         <v>1127</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>11</v>
@@ -17450,7 +17442,7 @@
         <v>1129</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C599" s="2" t="s">
         <v>11</v>
@@ -17470,7 +17462,7 @@
         <v>1131</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>11</v>
@@ -17479,7 +17471,7 @@
         <v>8.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>1128</v>
@@ -17617,7 +17609,7 @@
         <v>3.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F606" s="3">
         <v>11504.0</v>
@@ -17661,7 +17653,7 @@
         <v>18.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F608" s="3" t="s">
         <v>1147</v>
@@ -17683,10 +17675,10 @@
         <v>18.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G609" s="9"/>
       <c r="H609" s="2"/>
@@ -17696,19 +17688,19 @@
         <v>1149</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D610" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F610" s="3" t="s">
-        <v>38</v>
+        <v>1150</v>
+      </c>
+      <c r="F610" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G610" s="2" t="s">
         <v>38</v>
@@ -17717,7 +17709,7 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>32</v>
@@ -17729,7 +17721,7 @@
         <v>17.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F611" s="3">
         <v>11506.0</v>
@@ -17741,19 +17733,19 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D612" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F612" s="3">
         <v>11506.0</v>
@@ -17765,25 +17757,25 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D613" s="2">
         <v>1.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="F613" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G613" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G613" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H613" s="2"/>
     </row>
@@ -17795,7 +17787,7 @@
         <v>10</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D614" s="2">
         <v>1.0</v>
@@ -17819,10 +17811,10 @@
         <v>10</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D615" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E615" s="2" t="s">
         <v>20</v>
@@ -17840,31 +17832,31 @@
         <v>1158</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>10</v>
+        <v>526</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D616" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>20</v>
+        <v>624</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>37</v>
+        <v>1159</v>
       </c>
       <c r="G616" s="9">
-        <v>47531.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H616" s="2"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C617" s="2" t="s">
         <v>11</v>
@@ -17873,22 +17865,22 @@
         <v>10.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G617" s="9">
-        <v>46217.0</v>
+        <v>46223.0</v>
       </c>
       <c r="H617" s="2"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>11</v>
@@ -17897,13 +17889,13 @@
         <v>10.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>621</v>
+        <v>1025</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G618" s="9">
-        <v>46223.0</v>
+        <v>46221.0</v>
       </c>
       <c r="H618" s="2"/>
     </row>
@@ -17912,7 +17904,7 @@
         <v>1163</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C619" s="2" t="s">
         <v>11</v>
@@ -17921,13 +17913,13 @@
         <v>10.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1025</v>
+        <v>620</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G619" s="9">
-        <v>46221.0</v>
+        <v>46214.0</v>
       </c>
       <c r="H619" s="2"/>
     </row>
@@ -17936,23 +17928,19 @@
         <v>1164</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>525</v>
+        <v>111</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D620" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F620" s="3" t="s">
-        <v>1162</v>
-      </c>
-      <c r="G620" s="9">
-        <v>46214.0</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="F620" s="3"/>
+      <c r="G620" s="9"/>
       <c r="H620" s="2"/>
     </row>
     <row r="621">
@@ -17966,10 +17954,10 @@
         <v>11</v>
       </c>
       <c r="D621" s="2">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>631</v>
+        <v>1141</v>
       </c>
       <c r="F621" s="3"/>
       <c r="G621" s="9"/>
@@ -17986,13 +17974,17 @@
         <v>11</v>
       </c>
       <c r="D622" s="2">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F622" s="3"/>
-      <c r="G622" s="9"/>
+        <v>882</v>
+      </c>
+      <c r="F622" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G622" s="9">
+        <v>46636.0</v>
+      </c>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
@@ -18006,16 +17998,16 @@
         <v>11</v>
       </c>
       <c r="D623" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>882</v>
+        <v>561</v>
       </c>
       <c r="F623" s="3" t="s">
-        <v>141</v>
+        <v>897</v>
       </c>
       <c r="G623" s="9">
-        <v>46636.0</v>
+        <v>46814.0</v>
       </c>
       <c r="H623" s="2"/>
     </row>
@@ -18027,16 +18019,16 @@
         <v>111</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D624" s="2">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F624" s="3" t="s">
-        <v>897</v>
+        <v>1109</v>
+      </c>
+      <c r="F624" s="3">
+        <v>11505.0</v>
       </c>
       <c r="G624" s="9">
         <v>46814.0</v>
@@ -18051,25 +18043,23 @@
         <v>111</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D625" s="2">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F625" s="3">
-        <v>11505.0</v>
-      </c>
-      <c r="G625" s="9">
-        <v>46814.0</v>
-      </c>
+        <v>1170</v>
+      </c>
+      <c r="F625" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="G625" s="9"/>
       <c r="H625" s="2"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>111</v>
@@ -18081,59 +18071,13 @@
         <v>15.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1171</v>
+        <v>678</v>
       </c>
       <c r="F626" s="3" t="s">
-        <v>483</v>
+        <v>1145</v>
       </c>
       <c r="G626" s="9"/>
       <c r="H626" s="2"/>
-    </row>
-    <row r="627">
-      <c r="A627" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B627" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C627" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D627" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E627" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F627" s="3" t="s">
-        <v>1145</v>
-      </c>
-      <c r="G627" s="9"/>
-      <c r="H627" s="2"/>
-    </row>
-    <row r="628">
-      <c r="A628" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B628" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D628" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E628" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="F628" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G628" s="9">
-        <v>46179.0</v>
-      </c>
-      <c r="H628" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="1178">
   <si>
     <t>ID</t>
   </si>
@@ -3545,12 +3545,6 @@
   </si>
   <si>
     <t>JOC2</t>
-  </si>
-  <si>
-    <t>ID1780751519662</t>
-  </si>
-  <si>
-    <t>同步測試</t>
   </si>
 </sst>
 </file>
@@ -18136,30 +18130,6 @@
       </c>
       <c r="H627" s="2"/>
     </row>
-    <row r="628">
-      <c r="A628" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B628" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D628" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E628" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F628" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G628" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H628" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1178">
   <si>
     <t>ID</t>
   </si>
@@ -17123,6 +17123,9 @@
       <c r="G583" s="9">
         <v>46872.0</v>
       </c>
+      <c r="H583" s="2" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="1174">
   <si>
     <t>ID</t>
   </si>
@@ -1504,9 +1504,6 @@
     <t>JOLT (豬肉)</t>
   </si>
   <si>
-    <t>同品在庫: 極冷庫-左1F-19</t>
-  </si>
-  <si>
     <t>ID39835414951408</t>
   </si>
   <si>
@@ -1540,9 +1537,6 @@
     <t>28B(28-30) (鴨胸)</t>
   </si>
   <si>
-    <t>補貨: 無庫存</t>
-  </si>
-  <si>
     <t>ID39835414951417</t>
   </si>
   <si>
@@ -2704,804 +2698,789 @@
     <t>OST-KR(報廢）</t>
   </si>
   <si>
-    <t>ID1779178399646</t>
-  </si>
-  <si>
-    <t>CHSRM-SS</t>
+    <t>ID1779198270277</t>
+  </si>
+  <si>
+    <t>1131001K</t>
+  </si>
+  <si>
+    <t>ID1779243721312</t>
+  </si>
+  <si>
+    <t>JUP(4月報廢）</t>
+  </si>
+  <si>
+    <t>ID1779243743080</t>
+  </si>
+  <si>
+    <t>鴨翅(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779243761619</t>
+  </si>
+  <si>
+    <t>鴨里肌(報廢）</t>
+  </si>
+  <si>
+    <t>ID1779243798483</t>
+  </si>
+  <si>
+    <t>油角（報廢）</t>
+  </si>
+  <si>
+    <t>ID1779255881570</t>
+  </si>
+  <si>
+    <t>斑泊EP335(寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779255983117</t>
+  </si>
+  <si>
+    <t>錨隱廚 EP350（寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779256194102</t>
+  </si>
+  <si>
+    <t>On or 響艷信義JOC（寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779258747249</t>
+  </si>
+  <si>
+    <t>Niche JOC(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779258816523</t>
+  </si>
+  <si>
+    <t>UNCLE 一店 CKC2(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779258906179</t>
+  </si>
+  <si>
+    <t>UNCLE二店 CKC2(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779258977854</t>
+  </si>
+  <si>
+    <t>UNCLE三店CKC2(寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779260005194</t>
+  </si>
+  <si>
+    <t>Pasta West East 紅廚 EP350 (寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779260726909</t>
+  </si>
+  <si>
+    <t>L’atelier Robuchon JOP (寄庫)</t>
+  </si>
+  <si>
+    <t>ID1779260787111</t>
+  </si>
+  <si>
+    <t>ADR8</t>
+  </si>
+  <si>
+    <t>ID1779260970845</t>
+  </si>
+  <si>
+    <t>布爾喬亞 JUP (寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779327905648</t>
+  </si>
+  <si>
+    <t>ADC(豬肉）</t>
+  </si>
+  <si>
+    <t>ID1779336479059</t>
+  </si>
+  <si>
+    <t>VC405</t>
+  </si>
+  <si>
+    <t>ID1779336498030</t>
+  </si>
+  <si>
+    <t>VC408</t>
+  </si>
+  <si>
+    <t>ID1779336509597</t>
+  </si>
+  <si>
+    <t>VC407</t>
+  </si>
+  <si>
+    <t>ID1779336526988</t>
+  </si>
+  <si>
+    <t>VC401</t>
+  </si>
+  <si>
+    <t>ID1779336554211</t>
+  </si>
+  <si>
+    <t>ID1779336604468</t>
+  </si>
+  <si>
+    <t>PTMA4</t>
+  </si>
+  <si>
+    <t>ID1779336670410</t>
+  </si>
+  <si>
+    <t>PTMA1</t>
+  </si>
+  <si>
+    <t>ID1779336687710</t>
+  </si>
+  <si>
+    <t>PTMA3</t>
+  </si>
+  <si>
+    <t>ID1779336717423</t>
+  </si>
+  <si>
+    <t>CZED125</t>
+  </si>
+  <si>
+    <t>ID1779336735901</t>
+  </si>
+  <si>
+    <t>CZBR125</t>
+  </si>
+  <si>
+    <t>ID1779336752106</t>
+  </si>
+  <si>
+    <t>CZBA125</t>
+  </si>
+  <si>
+    <t>ID1779336768758</t>
+  </si>
+  <si>
+    <t>CZPV125</t>
+  </si>
+  <si>
+    <t>ID1779336804283</t>
+  </si>
+  <si>
+    <t>PGS4</t>
+  </si>
+  <si>
+    <t>ID1779336826299</t>
+  </si>
+  <si>
+    <t>PGS3</t>
+  </si>
+  <si>
+    <t>ID1779336842776</t>
+  </si>
+  <si>
+    <t>PGS1</t>
+  </si>
+  <si>
+    <t>ID1779336869690</t>
+  </si>
+  <si>
+    <t>PGR30</t>
+  </si>
+  <si>
+    <t>ID1779336887245</t>
+  </si>
+  <si>
+    <t>PDE12</t>
+  </si>
+  <si>
+    <t>ID1779336906578</t>
+  </si>
+  <si>
+    <t>PGE22</t>
+  </si>
+  <si>
+    <t>ID1779336936520</t>
+  </si>
+  <si>
+    <t>PGR24</t>
+  </si>
+  <si>
+    <t>ID1779337010716</t>
+  </si>
+  <si>
+    <t>GRW1</t>
+  </si>
+  <si>
+    <t>ID1779337463665</t>
+  </si>
+  <si>
+    <t>GRW2</t>
+  </si>
+  <si>
+    <t>ID1779337587175</t>
+  </si>
+  <si>
+    <t>GRS1</t>
+  </si>
+  <si>
+    <t>ID1779343267216</t>
+  </si>
+  <si>
+    <t>GRP100</t>
+  </si>
+  <si>
+    <t>ID1779343290594</t>
+  </si>
+  <si>
+    <t>GRS2</t>
+  </si>
+  <si>
+    <t>ID1779343310568</t>
+  </si>
+  <si>
+    <t>GRS6</t>
+  </si>
+  <si>
+    <t>ID1779343331075</t>
+  </si>
+  <si>
+    <t>GRS200</t>
+  </si>
+  <si>
+    <t>ID1779343361971</t>
+  </si>
+  <si>
+    <t>GRW3</t>
+  </si>
+  <si>
+    <t>ID1779343395723</t>
+  </si>
+  <si>
+    <t>BY12S</t>
+  </si>
+  <si>
+    <t>ID1779343415214</t>
+  </si>
+  <si>
+    <t>ID1779343445375</t>
+  </si>
+  <si>
+    <t>BY13</t>
+  </si>
+  <si>
+    <t>[異常] 出清</t>
+  </si>
+  <si>
+    <t>ID1779343478640</t>
+  </si>
+  <si>
+    <t>JO48S</t>
+  </si>
+  <si>
+    <t>ID1779343499670</t>
+  </si>
+  <si>
+    <t>JOP24S</t>
+  </si>
+  <si>
+    <t>ID1779343524379</t>
+  </si>
+  <si>
+    <t>JOA</t>
+  </si>
+  <si>
+    <t>ID1779343558098</t>
+  </si>
+  <si>
+    <t>BY12</t>
+  </si>
+  <si>
+    <t>ID1779343590997</t>
+  </si>
+  <si>
+    <t>BY92S</t>
+  </si>
+  <si>
+    <t>ID1779343771102</t>
+  </si>
+  <si>
+    <t>台北文華 NO12S （寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779343793991</t>
+  </si>
+  <si>
+    <t>頁小館 NO12S （寄庫）</t>
+  </si>
+  <si>
+    <t>ID1779355047243</t>
+  </si>
+  <si>
+    <t>M45FKS-C-KR</t>
+  </si>
+  <si>
+    <t>ID1779355423259</t>
+  </si>
+  <si>
+    <t>M89RER-C-KR</t>
+  </si>
+  <si>
+    <t>ID1779413117582</t>
+  </si>
+  <si>
+    <t>ID1779413244655</t>
+  </si>
+  <si>
+    <t>M89OB-C-KR</t>
+  </si>
+  <si>
+    <t>ID1779413919146</t>
+  </si>
+  <si>
+    <t>PRSRL-C-YK</t>
+  </si>
+  <si>
+    <t>ID1779414379352</t>
+  </si>
+  <si>
+    <t>PRRER-C-GO</t>
+  </si>
+  <si>
+    <t>26#4</t>
+  </si>
+  <si>
+    <t>ID1779423814186</t>
+  </si>
+  <si>
+    <t>EMSPL-SS</t>
+  </si>
+  <si>
+    <t>26#37</t>
+  </si>
+  <si>
+    <t>ID1779423889909</t>
+  </si>
+  <si>
+    <t>PRSRM-C-SS</t>
+  </si>
+  <si>
+    <t>26#36</t>
+  </si>
+  <si>
+    <t>ID1779437559431</t>
+  </si>
+  <si>
+    <t>ID1779441353346</t>
+  </si>
+  <si>
+    <t>M67RER-280-320-KR</t>
+  </si>
+  <si>
+    <t>ID1779701743464</t>
+  </si>
+  <si>
+    <t>MP-KR</t>
+  </si>
+  <si>
+    <t>ID1779701756769</t>
+  </si>
+  <si>
+    <t>ID1779701865759</t>
+  </si>
+  <si>
+    <t>M45BSTT-KR-C</t>
+  </si>
+  <si>
+    <t>26#5</t>
+  </si>
+  <si>
+    <t>ID1779701936239</t>
+  </si>
+  <si>
+    <t>M89RER-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779701958932</t>
+  </si>
+  <si>
+    <t>M89TDL-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779702003682</t>
+  </si>
+  <si>
+    <t>M89OB-KR-C</t>
+  </si>
+  <si>
+    <t>ID1779719332195</t>
+  </si>
+  <si>
+    <t>KR-MP</t>
+  </si>
+  <si>
+    <t>ID1779760015433</t>
+  </si>
+  <si>
+    <t>1150525K</t>
+  </si>
+  <si>
+    <t>ID1779760027714</t>
+  </si>
+  <si>
+    <t>PRSRL-YK</t>
+  </si>
+  <si>
+    <t>ID1779760044232</t>
+  </si>
+  <si>
+    <t>ID1779760055112</t>
+  </si>
+  <si>
+    <t>ID1779768396440</t>
+  </si>
+  <si>
+    <t>1140623K</t>
+  </si>
+  <si>
+    <t>ID1779768429388</t>
+  </si>
+  <si>
+    <t>M89SRM-KR</t>
+  </si>
+  <si>
+    <t>1140508K</t>
+  </si>
+  <si>
+    <t>ID1779768468384</t>
+  </si>
+  <si>
+    <t>M89OSF-KR</t>
+  </si>
+  <si>
+    <t>1150522K</t>
+  </si>
+  <si>
+    <t>ID1779768511004</t>
+  </si>
+  <si>
+    <t>A5TDL</t>
+  </si>
+  <si>
+    <t>ID1779768548653</t>
+  </si>
+  <si>
+    <t>M45BSTT-KR</t>
+  </si>
+  <si>
+    <t>1150518K</t>
+  </si>
+  <si>
+    <t>ID1779768607674</t>
+  </si>
+  <si>
+    <t>M67FM-KR</t>
+  </si>
+  <si>
+    <t>ID1779768624471</t>
+  </si>
+  <si>
+    <t>ID1779768641201</t>
+  </si>
+  <si>
+    <t>ID1779768655644</t>
+  </si>
+  <si>
+    <t>ID1779768670511</t>
+  </si>
+  <si>
+    <t>M67OB-KR</t>
+  </si>
+  <si>
+    <t>ID1779777307015</t>
+  </si>
+  <si>
+    <t>A5RER</t>
+  </si>
+  <si>
+    <t>ID1779880690658</t>
+  </si>
+  <si>
+    <t>1150527S</t>
+  </si>
+  <si>
+    <t>ID1779880763675</t>
+  </si>
+  <si>
+    <t>EMSPL-十字切-SS</t>
+  </si>
+  <si>
+    <t>ID1779935223860</t>
+  </si>
+  <si>
+    <t>26B</t>
+  </si>
+  <si>
+    <t>ID1779935393105</t>
+  </si>
+  <si>
+    <t>1141222K</t>
+  </si>
+  <si>
+    <t>ID1779952236759</t>
+  </si>
+  <si>
+    <t>ACRER-200-250-TY</t>
+  </si>
+  <si>
+    <t>ID1779952271401</t>
+  </si>
+  <si>
+    <t>ID1779952289227</t>
+  </si>
+  <si>
+    <t>GMB(骨)</t>
+  </si>
+  <si>
+    <t>ID1779953032414</t>
+  </si>
+  <si>
+    <t>PRRER-340-380-SS</t>
+  </si>
+  <si>
+    <t>ID1779953075175</t>
+  </si>
+  <si>
+    <t>M89OSF-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953153190</t>
+  </si>
+  <si>
+    <t>PRRER-450-490-YK</t>
+  </si>
+  <si>
+    <t>ID1779953199741</t>
+  </si>
+  <si>
+    <t>PRRER-360-400-SS</t>
+  </si>
+  <si>
+    <t>ID1779953260859</t>
+  </si>
+  <si>
+    <t>M89CER-十字切-KR</t>
+  </si>
+  <si>
+    <t>ID1779953383633</t>
+  </si>
+  <si>
+    <t>ID1779956331825</t>
+  </si>
+  <si>
+    <t>PRTDL-C-GO</t>
+  </si>
+  <si>
+    <t>ID1779956377322</t>
+  </si>
+  <si>
+    <t>PRSRM-C-GO</t>
+  </si>
+  <si>
+    <t>ID1780023544888</t>
+  </si>
+  <si>
+    <t>BJUJM</t>
+  </si>
+  <si>
+    <t>ID1780023826368</t>
+  </si>
+  <si>
+    <t>ACCRM-SS(A5預留用)</t>
+  </si>
+  <si>
+    <t>26#19</t>
+  </si>
+  <si>
+    <t>ID1780285597561</t>
+  </si>
+  <si>
+    <t>廢料</t>
+  </si>
+  <si>
+    <t>（報廢）</t>
+  </si>
+  <si>
+    <t>ID1780287319374</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>ID1780352747610</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <t>ID1780368496154</t>
+  </si>
+  <si>
+    <t>BJURM</t>
+  </si>
+  <si>
+    <t>ID1780368863464</t>
+  </si>
+  <si>
+    <t>1140303K</t>
+  </si>
+  <si>
+    <t>ID1780373196844</t>
+  </si>
+  <si>
+    <t>ID1780373223783</t>
+  </si>
+  <si>
+    <t>ACTDL-C-TY</t>
+  </si>
+  <si>
+    <t>26#7</t>
+  </si>
+  <si>
+    <t>ID1780373362857</t>
+  </si>
+  <si>
+    <t>NO12S-頁小館_寄庫</t>
+  </si>
+  <si>
+    <t>ID1780373402392</t>
+  </si>
+  <si>
+    <t>ACRPC-C-TY</t>
+  </si>
+  <si>
+    <t>ID1780447702749</t>
+  </si>
+  <si>
+    <t>GF-CKM-TY</t>
+  </si>
+  <si>
+    <t>1150601K</t>
+  </si>
+  <si>
+    <t>ID1780447833399</t>
+  </si>
+  <si>
+    <t>ID1780472318713</t>
+  </si>
+  <si>
+    <t>34B</t>
+  </si>
+  <si>
+    <t>ID1780472410260</t>
+  </si>
+  <si>
+    <t>37TQ</t>
+  </si>
+  <si>
+    <t>ID1780472441121</t>
+  </si>
+  <si>
+    <t>36-38B</t>
+  </si>
+  <si>
+    <t>ID1780472484781</t>
+  </si>
+  <si>
+    <t>ID1780473214746</t>
+  </si>
+  <si>
+    <t>M9TDL-KR(預定）</t>
+  </si>
+  <si>
+    <t>1140627K</t>
+  </si>
+  <si>
+    <t>ID1780473327368</t>
+  </si>
+  <si>
+    <t>1141027K</t>
+  </si>
+  <si>
+    <t>ID1780473345775</t>
+  </si>
+  <si>
+    <t>ID1780534348697</t>
+  </si>
+  <si>
+    <t>12S</t>
+  </si>
+  <si>
+    <t>ID1780534369366</t>
+  </si>
+  <si>
+    <t>60S</t>
+  </si>
+  <si>
+    <t>ID1780534471460</t>
+  </si>
+  <si>
+    <t>#35</t>
+  </si>
+  <si>
+    <t>ID1780546652417</t>
+  </si>
+  <si>
+    <t>ID1780546669489</t>
+  </si>
+  <si>
+    <t>ID1780546690451</t>
+  </si>
+  <si>
+    <t>ID1780577694690</t>
+  </si>
+  <si>
+    <t>SS26#42</t>
+  </si>
+  <si>
+    <t>ID1780577914932</t>
+  </si>
+  <si>
+    <t>26#42</t>
+  </si>
+  <si>
+    <t>ID1780577956618</t>
+  </si>
+  <si>
+    <t>ID1780578034415</t>
+  </si>
+  <si>
+    <t>ID1780621800914</t>
+  </si>
+  <si>
+    <t>ID1780622105167</t>
+  </si>
+  <si>
+    <t>ID1780622353914</t>
+  </si>
+  <si>
+    <t>ID1780622609170</t>
   </si>
   <si>
     <t>1150512K</t>
   </si>
   <si>
-    <t>ID1779198270277</t>
-  </si>
-  <si>
-    <t>1131001K</t>
-  </si>
-  <si>
-    <t>ID1779243721312</t>
-  </si>
-  <si>
-    <t>JUP(4月報廢）</t>
-  </si>
-  <si>
-    <t>ID1779243743080</t>
-  </si>
-  <si>
-    <t>鴨翅(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779243761619</t>
-  </si>
-  <si>
-    <t>鴨里肌(報廢）</t>
-  </si>
-  <si>
-    <t>ID1779243798483</t>
-  </si>
-  <si>
-    <t>油角（報廢）</t>
-  </si>
-  <si>
-    <t>ID1779255881570</t>
-  </si>
-  <si>
-    <t>斑泊EP335(寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779255983117</t>
-  </si>
-  <si>
-    <t>錨隱廚 EP350（寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779256194102</t>
-  </si>
-  <si>
-    <t>On or 響艷信義JOC（寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779258747249</t>
-  </si>
-  <si>
-    <t>Niche JOC(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779258816523</t>
-  </si>
-  <si>
-    <t>UNCLE 一店 CKC2(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779258906179</t>
-  </si>
-  <si>
-    <t>UNCLE二店 CKC2(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779258977854</t>
-  </si>
-  <si>
-    <t>UNCLE三店CKC2(寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779260005194</t>
-  </si>
-  <si>
-    <t>Pasta West East 紅廚 EP350 (寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779260726909</t>
-  </si>
-  <si>
-    <t>L’atelier Robuchon JOP (寄庫)</t>
-  </si>
-  <si>
-    <t>ID1779260787111</t>
-  </si>
-  <si>
-    <t>ADR8</t>
-  </si>
-  <si>
-    <t>ID1779260970845</t>
-  </si>
-  <si>
-    <t>布爾喬亞 JUP (寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779327905648</t>
-  </si>
-  <si>
-    <t>ADC(豬肉）</t>
-  </si>
-  <si>
-    <t>ID1779336479059</t>
-  </si>
-  <si>
-    <t>VC405</t>
-  </si>
-  <si>
-    <t>ID1779336498030</t>
-  </si>
-  <si>
-    <t>VC408</t>
-  </si>
-  <si>
-    <t>ID1779336509597</t>
-  </si>
-  <si>
-    <t>VC407</t>
-  </si>
-  <si>
-    <t>ID1779336526988</t>
-  </si>
-  <si>
-    <t>VC401</t>
-  </si>
-  <si>
-    <t>ID1779336554211</t>
-  </si>
-  <si>
-    <t>ID1779336604468</t>
-  </si>
-  <si>
-    <t>PTMA4</t>
-  </si>
-  <si>
-    <t>ID1779336670410</t>
-  </si>
-  <si>
-    <t>PTMA1</t>
-  </si>
-  <si>
-    <t>ID1779336687710</t>
-  </si>
-  <si>
-    <t>PTMA3</t>
-  </si>
-  <si>
-    <t>ID1779336717423</t>
-  </si>
-  <si>
-    <t>CZED125</t>
-  </si>
-  <si>
-    <t>ID1779336735901</t>
-  </si>
-  <si>
-    <t>CZBR125</t>
-  </si>
-  <si>
-    <t>ID1779336752106</t>
-  </si>
-  <si>
-    <t>CZBA125</t>
-  </si>
-  <si>
-    <t>ID1779336768758</t>
-  </si>
-  <si>
-    <t>CZPV125</t>
-  </si>
-  <si>
-    <t>ID1779336804283</t>
-  </si>
-  <si>
-    <t>PGS4</t>
-  </si>
-  <si>
-    <t>ID1779336826299</t>
-  </si>
-  <si>
-    <t>PGS3</t>
-  </si>
-  <si>
-    <t>ID1779336842776</t>
-  </si>
-  <si>
-    <t>PGS1</t>
-  </si>
-  <si>
-    <t>ID1779336869690</t>
-  </si>
-  <si>
-    <t>PGR30</t>
-  </si>
-  <si>
-    <t>ID1779336887245</t>
-  </si>
-  <si>
-    <t>PDE12</t>
-  </si>
-  <si>
-    <t>ID1779336906578</t>
-  </si>
-  <si>
-    <t>PGE22</t>
-  </si>
-  <si>
-    <t>ID1779336936520</t>
-  </si>
-  <si>
-    <t>PGR24</t>
-  </si>
-  <si>
-    <t>ID1779337010716</t>
-  </si>
-  <si>
-    <t>GRW1</t>
-  </si>
-  <si>
-    <t>ID1779337463665</t>
-  </si>
-  <si>
-    <t>GRW2</t>
-  </si>
-  <si>
-    <t>ID1779337587175</t>
-  </si>
-  <si>
-    <t>GRS1</t>
-  </si>
-  <si>
-    <t>ID1779343267216</t>
-  </si>
-  <si>
-    <t>GRP100</t>
-  </si>
-  <si>
-    <t>ID1779343290594</t>
-  </si>
-  <si>
-    <t>GRS2</t>
-  </si>
-  <si>
-    <t>ID1779343310568</t>
-  </si>
-  <si>
-    <t>GRS6</t>
-  </si>
-  <si>
-    <t>ID1779343331075</t>
-  </si>
-  <si>
-    <t>GRS200</t>
-  </si>
-  <si>
-    <t>ID1779343361971</t>
-  </si>
-  <si>
-    <t>GRW3</t>
-  </si>
-  <si>
-    <t>ID1779343395723</t>
-  </si>
-  <si>
-    <t>BY12S</t>
-  </si>
-  <si>
-    <t>ID1779343415214</t>
-  </si>
-  <si>
-    <t>ID1779343445375</t>
-  </si>
-  <si>
-    <t>BY13</t>
-  </si>
-  <si>
-    <t>[異常] 出清</t>
-  </si>
-  <si>
-    <t>ID1779343478640</t>
-  </si>
-  <si>
-    <t>JO48S</t>
-  </si>
-  <si>
-    <t>ID1779343499670</t>
-  </si>
-  <si>
-    <t>JOP24S</t>
-  </si>
-  <si>
-    <t>ID1779343524379</t>
-  </si>
-  <si>
-    <t>JOA</t>
-  </si>
-  <si>
-    <t>ID1779343558098</t>
-  </si>
-  <si>
-    <t>BY12</t>
-  </si>
-  <si>
-    <t>ID1779343590997</t>
-  </si>
-  <si>
-    <t>BY92S</t>
-  </si>
-  <si>
-    <t>ID1779343771102</t>
-  </si>
-  <si>
-    <t>台北文華 NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779343793991</t>
-  </si>
-  <si>
-    <t>頁小館 NO12S （寄庫）</t>
-  </si>
-  <si>
-    <t>ID1779355047243</t>
-  </si>
-  <si>
-    <t>M45FKS-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779355423259</t>
-  </si>
-  <si>
-    <t>M89RER-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779413117582</t>
-  </si>
-  <si>
-    <t>ID1779413244655</t>
-  </si>
-  <si>
-    <t>M89OB-C-KR</t>
-  </si>
-  <si>
-    <t>ID1779413919146</t>
-  </si>
-  <si>
-    <t>PRSRL-C-YK</t>
-  </si>
-  <si>
-    <t>ID1779414379352</t>
-  </si>
-  <si>
-    <t>PRRER-C-GO</t>
-  </si>
-  <si>
-    <t>26#4</t>
-  </si>
-  <si>
-    <t>ID1779423814186</t>
-  </si>
-  <si>
-    <t>EMSPL-SS</t>
-  </si>
-  <si>
-    <t>26#37</t>
-  </si>
-  <si>
-    <t>ID1779423889909</t>
-  </si>
-  <si>
-    <t>PRSRM-C-SS</t>
-  </si>
-  <si>
-    <t>26#36</t>
-  </si>
-  <si>
-    <t>ID1779437559431</t>
-  </si>
-  <si>
-    <t>ID1779441353346</t>
-  </si>
-  <si>
-    <t>M67RER-280-320-KR</t>
-  </si>
-  <si>
-    <t>ID1779701743464</t>
-  </si>
-  <si>
-    <t>MP-KR</t>
-  </si>
-  <si>
-    <t>ID1779701756769</t>
-  </si>
-  <si>
-    <t>ID1779701865759</t>
-  </si>
-  <si>
-    <t>M45BSTT-KR-C</t>
-  </si>
-  <si>
-    <t>26#5</t>
-  </si>
-  <si>
-    <t>ID1779701936239</t>
-  </si>
-  <si>
-    <t>M89RER-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779701958932</t>
-  </si>
-  <si>
-    <t>M89TDL-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779702003682</t>
-  </si>
-  <si>
-    <t>M89OB-KR-C</t>
-  </si>
-  <si>
-    <t>ID1779719332195</t>
-  </si>
-  <si>
-    <t>KR-MP</t>
-  </si>
-  <si>
-    <t>ID1779760015433</t>
-  </si>
-  <si>
-    <t>1150525K</t>
-  </si>
-  <si>
-    <t>ID1779760027714</t>
-  </si>
-  <si>
-    <t>PRSRL-YK</t>
-  </si>
-  <si>
-    <t>ID1779760044232</t>
-  </si>
-  <si>
-    <t>ID1779760055112</t>
-  </si>
-  <si>
-    <t>ID1779768396440</t>
-  </si>
-  <si>
-    <t>1140623K</t>
-  </si>
-  <si>
-    <t>ID1779768429388</t>
-  </si>
-  <si>
-    <t>M89SRM-KR</t>
-  </si>
-  <si>
-    <t>1140508K</t>
-  </si>
-  <si>
-    <t>ID1779768468384</t>
-  </si>
-  <si>
-    <t>M89OSF-KR</t>
-  </si>
-  <si>
-    <t>1150522K</t>
-  </si>
-  <si>
-    <t>ID1779768511004</t>
-  </si>
-  <si>
-    <t>A5TDL</t>
-  </si>
-  <si>
-    <t>ID1779768548653</t>
-  </si>
-  <si>
-    <t>M45BSTT-KR</t>
-  </si>
-  <si>
-    <t>1150518K</t>
-  </si>
-  <si>
-    <t>ID1779768607674</t>
-  </si>
-  <si>
-    <t>M67FM-KR</t>
-  </si>
-  <si>
-    <t>ID1779768624471</t>
-  </si>
-  <si>
-    <t>ID1779768641201</t>
-  </si>
-  <si>
-    <t>ID1779768655644</t>
-  </si>
-  <si>
-    <t>ID1779768670511</t>
-  </si>
-  <si>
-    <t>M67OB-KR</t>
-  </si>
-  <si>
-    <t>ID1779777307015</t>
-  </si>
-  <si>
-    <t>A5RER</t>
-  </si>
-  <si>
-    <t>ID1779880646013</t>
-  </si>
-  <si>
-    <t>M89BBLD-對切-KR</t>
-  </si>
-  <si>
-    <t>1150527S</t>
-  </si>
-  <si>
-    <t>ID1779880690658</t>
-  </si>
-  <si>
-    <t>ID1779880763675</t>
-  </si>
-  <si>
-    <t>EMSPL-十字切-SS</t>
-  </si>
-  <si>
-    <t>ID1779935223860</t>
-  </si>
-  <si>
-    <t>26B</t>
-  </si>
-  <si>
-    <t>ID1779935393105</t>
-  </si>
-  <si>
-    <t>1141222K</t>
-  </si>
-  <si>
-    <t>ID1779952236759</t>
-  </si>
-  <si>
-    <t>ACRER-200-250-TY</t>
-  </si>
-  <si>
-    <t>ID1779952271401</t>
-  </si>
-  <si>
-    <t>ID1779952289227</t>
-  </si>
-  <si>
-    <t>GMB(骨)</t>
-  </si>
-  <si>
-    <t>ID1779953032414</t>
-  </si>
-  <si>
-    <t>PRRER-340-380-SS</t>
-  </si>
-  <si>
-    <t>ID1779953075175</t>
-  </si>
-  <si>
-    <t>M89OSF-十字切-KR</t>
-  </si>
-  <si>
-    <t>ID1779953153190</t>
-  </si>
-  <si>
-    <t>PRRER-450-490-YK</t>
-  </si>
-  <si>
-    <t>ID1779953199741</t>
-  </si>
-  <si>
-    <t>PRRER-360-400-SS</t>
-  </si>
-  <si>
-    <t>ID1779953260859</t>
-  </si>
-  <si>
-    <t>M89CER-十字切-KR</t>
-  </si>
-  <si>
-    <t>ID1779953383633</t>
-  </si>
-  <si>
-    <t>ID1779956331825</t>
-  </si>
-  <si>
-    <t>PRTDL-C-GO</t>
-  </si>
-  <si>
-    <t>ID1779956377322</t>
-  </si>
-  <si>
-    <t>PRSRM-C-GO</t>
-  </si>
-  <si>
-    <t>ID1780023477991</t>
+    <t>ID1780622739687</t>
   </si>
   <si>
     <t>TS</t>
   </si>
   <si>
-    <t>ID1780023544888</t>
-  </si>
-  <si>
-    <t>BJUJM</t>
-  </si>
-  <si>
-    <t>ID1780023826368</t>
-  </si>
-  <si>
-    <t>ACCRM-SS(A5預留用)</t>
-  </si>
-  <si>
-    <t>26#19</t>
-  </si>
-  <si>
-    <t>ID1780285597561</t>
-  </si>
-  <si>
-    <t>廢料</t>
-  </si>
-  <si>
-    <t>（報廢）</t>
-  </si>
-  <si>
-    <t>ID1780287319374</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>ID1780352747610</t>
-  </si>
-  <si>
-    <t>ADC</t>
-  </si>
-  <si>
-    <t>ID1780368496154</t>
-  </si>
-  <si>
-    <t>BJURM</t>
-  </si>
-  <si>
-    <t>ID1780368863464</t>
-  </si>
-  <si>
-    <t>1140303K</t>
-  </si>
-  <si>
-    <t>ID1780373196844</t>
-  </si>
-  <si>
-    <t>ID1780373223783</t>
-  </si>
-  <si>
-    <t>ACTDL-C-TY</t>
-  </si>
-  <si>
-    <t>26#7</t>
-  </si>
-  <si>
-    <t>ID1780373362857</t>
-  </si>
-  <si>
-    <t>NO12S-頁小館_寄庫</t>
-  </si>
-  <si>
-    <t>ID1780373402392</t>
-  </si>
-  <si>
-    <t>ACRPC-C-TY</t>
-  </si>
-  <si>
-    <t>ID1780447702749</t>
-  </si>
-  <si>
-    <t>GF-CKM-TY</t>
-  </si>
-  <si>
-    <t>1150601K</t>
-  </si>
-  <si>
-    <t>ID1780447833399</t>
-  </si>
-  <si>
-    <t>ID1780472318713</t>
-  </si>
-  <si>
-    <t>34B</t>
-  </si>
-  <si>
-    <t>ID1780472410260</t>
-  </si>
-  <si>
-    <t>37TQ</t>
-  </si>
-  <si>
-    <t>ID1780472441121</t>
-  </si>
-  <si>
-    <t>36-38B</t>
-  </si>
-  <si>
-    <t>ID1780472484781</t>
-  </si>
-  <si>
-    <t>ID1780473214746</t>
-  </si>
-  <si>
-    <t>M9TDL-KR(預定）</t>
-  </si>
-  <si>
-    <t>1140627K</t>
-  </si>
-  <si>
-    <t>ID1780473327368</t>
-  </si>
-  <si>
-    <t>1141027K</t>
-  </si>
-  <si>
-    <t>ID1780473345775</t>
-  </si>
-  <si>
-    <t>ID1780534348697</t>
-  </si>
-  <si>
-    <t>12S</t>
-  </si>
-  <si>
-    <t>ID1780534369366</t>
-  </si>
-  <si>
-    <t>60S</t>
-  </si>
-  <si>
-    <t>ID1780534471460</t>
-  </si>
-  <si>
-    <t>#35</t>
-  </si>
-  <si>
-    <t>ID1780546652417</t>
-  </si>
-  <si>
-    <t>ID1780546669489</t>
-  </si>
-  <si>
-    <t>ID1780546690451</t>
-  </si>
-  <si>
-    <t>ID1780577694690</t>
-  </si>
-  <si>
-    <t>SS26#42</t>
-  </si>
-  <si>
-    <t>ID1780577914932</t>
-  </si>
-  <si>
-    <t>26#42</t>
-  </si>
-  <si>
-    <t>ID1780577956618</t>
-  </si>
-  <si>
-    <t>ID1780578034415</t>
-  </si>
-  <si>
-    <t>ID1780621800914</t>
-  </si>
-  <si>
-    <t>ID1780622105167</t>
-  </si>
-  <si>
-    <t>ID1780622353914</t>
-  </si>
-  <si>
-    <t>ID1780622609170</t>
-  </si>
-  <si>
-    <t>ID1780622739687</t>
-  </si>
-  <si>
     <t>ID1780622862949</t>
   </si>
   <si>
@@ -3517,16 +3496,13 @@
     <t>JOC2</t>
   </si>
   <si>
-    <t>ID1780922779832</t>
+    <t>ID1780922795158</t>
   </si>
   <si>
     <t>CKM-KR</t>
   </si>
   <si>
     <t>1150520K</t>
-  </si>
-  <si>
-    <t>ID1780922795158</t>
   </si>
   <si>
     <t>ID1780922844412</t>
@@ -8933,13 +8909,11 @@
       <c r="G217" s="19">
         <v>46394.0</v>
       </c>
-      <c r="H217" s="11" t="s">
-        <v>497</v>
-      </c>
+      <c r="H217" s="11"/>
     </row>
     <row r="218">
       <c r="A218" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>112</v>
@@ -8951,10 +8925,10 @@
         <v>21.0</v>
       </c>
       <c r="E218" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="F218" s="17" t="s">
         <v>499</v>
-      </c>
-      <c r="F218" s="17" t="s">
-        <v>500</v>
       </c>
       <c r="G218" s="19">
         <v>46949.0</v>
@@ -8963,7 +8937,7 @@
     </row>
     <row r="219">
       <c r="A219" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>112</v>
@@ -8975,7 +8949,7 @@
         <v>19.0</v>
       </c>
       <c r="E219" s="11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F219" s="17" t="s">
         <v>225</v>
@@ -8987,7 +8961,7 @@
     </row>
     <row r="220">
       <c r="A220" s="10" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>112</v>
@@ -8999,7 +8973,7 @@
         <v>19.0</v>
       </c>
       <c r="E220" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F220" s="17" t="s">
         <v>17</v>
@@ -9011,7 +8985,7 @@
     </row>
     <row r="221">
       <c r="A221" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>112</v>
@@ -9023,7 +8997,7 @@
         <v>18.0</v>
       </c>
       <c r="E221" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F221" s="17" t="s">
         <v>270</v>
@@ -9035,7 +9009,7 @@
     </row>
     <row r="222">
       <c r="A222" s="10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>112</v>
@@ -9047,19 +9021,17 @@
         <v>17.0</v>
       </c>
       <c r="E222" s="11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F222" s="14"/>
       <c r="G222" s="19">
         <v>46830.0</v>
       </c>
-      <c r="H222" s="11" t="s">
-        <v>509</v>
-      </c>
+      <c r="H222" s="11"/>
     </row>
     <row r="223">
       <c r="A223" s="10" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>112</v>
@@ -9071,7 +9043,7 @@
         <v>17.0</v>
       </c>
       <c r="E223" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>148</v>
@@ -9083,7 +9055,7 @@
     </row>
     <row r="224">
       <c r="A224" s="10" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>112</v>
@@ -9095,10 +9067,10 @@
         <v>15.0</v>
       </c>
       <c r="E224" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F224" s="17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G224" s="19">
         <v>46417.0</v>
@@ -9107,7 +9079,7 @@
     </row>
     <row r="225">
       <c r="A225" s="10" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>33</v>
@@ -9129,7 +9101,7 @@
     </row>
     <row r="226">
       <c r="A226" s="10" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>33</v>
@@ -9151,7 +9123,7 @@
     </row>
     <row r="227">
       <c r="A227" s="10" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B227" s="11" t="s">
         <v>33</v>
@@ -9163,7 +9135,7 @@
         <v>13.0</v>
       </c>
       <c r="E227" s="11" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F227" s="14"/>
       <c r="G227" s="19">
@@ -9173,7 +9145,7 @@
     </row>
     <row r="228">
       <c r="A228" s="10" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>33</v>
@@ -9185,7 +9157,7 @@
         <v>20.0</v>
       </c>
       <c r="E228" s="11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F228" s="14"/>
       <c r="G228" s="12"/>
@@ -9195,7 +9167,7 @@
     </row>
     <row r="229">
       <c r="A229" s="10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B229" s="11" t="s">
         <v>33</v>
@@ -9207,7 +9179,7 @@
         <v>20.0</v>
       </c>
       <c r="E229" s="11" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F229" s="17"/>
       <c r="G229" s="12"/>
@@ -9217,7 +9189,7 @@
     </row>
     <row r="230">
       <c r="A230" s="10" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>33</v>
@@ -9239,7 +9211,7 @@
     </row>
     <row r="231">
       <c r="A231" s="10" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B231" s="11" t="s">
         <v>33</v>
@@ -9261,7 +9233,7 @@
     </row>
     <row r="232">
       <c r="A232" s="10" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>33</v>
@@ -9273,7 +9245,7 @@
         <v>2.0</v>
       </c>
       <c r="E232" s="11" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F232" s="17" t="s">
         <v>225</v>
@@ -9283,7 +9255,7 @@
     </row>
     <row r="233">
       <c r="A233" s="10" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B233" s="11" t="s">
         <v>112</v>
@@ -9295,7 +9267,7 @@
         <v>11.0</v>
       </c>
       <c r="E233" s="11" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F233" s="17">
         <v>11503.0</v>
@@ -9308,7 +9280,7 @@
         <v>1.77436324269E12</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>12</v>
@@ -9317,7 +9289,7 @@
         <v>2.0</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>157</v>
@@ -9334,7 +9306,7 @@
         <v>1.774363425608E12</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>12</v>
@@ -9343,11 +9315,11 @@
         <v>1.0</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F235" s="4"/>
       <c r="H235" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="236">
@@ -9355,7 +9327,7 @@
         <v>1.774363487217E12</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>12</v>
@@ -9364,11 +9336,11 @@
         <v>2.0</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F236" s="4"/>
       <c r="H236" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="237">
@@ -9385,10 +9357,10 @@
         <v>15.0</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G237" s="9">
         <v>46873.0</v>
@@ -9409,10 +9381,10 @@
         <v>12.0</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G238" s="9">
         <v>46805.0</v>
@@ -9432,10 +9404,10 @@
         <v>11.0</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G239" s="9">
         <v>46424.0</v>
@@ -9455,10 +9427,10 @@
         <v>13.0</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G240" s="9">
         <v>46530.0</v>
@@ -9479,7 +9451,7 @@
         <v>2.0</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F241" s="3">
         <v>11503.0</v>
@@ -9514,7 +9486,7 @@
         <v>1.774488862747E12</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>12</v>
@@ -9523,7 +9495,7 @@
         <v>5.0</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>17</v>
@@ -9547,7 +9519,7 @@
         <v>4.0</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>225</v>
@@ -9590,7 +9562,7 @@
         <v>21.0</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>17</v>
@@ -9611,7 +9583,7 @@
         <v>15.0</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>468</v>
@@ -9635,16 +9607,16 @@
         <v>8.0</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G248" s="9">
         <v>46516.0</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="249">
@@ -9661,7 +9633,7 @@
         <v>12.0</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F249" s="3">
         <v>11503.0</v>
@@ -9681,7 +9653,7 @@
         <v>16.0</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>236</v>
@@ -9704,10 +9676,10 @@
         <v>12.0</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G251" s="9">
         <v>46395.0</v>
@@ -9728,7 +9700,7 @@
         <v>1.0</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>17</v>
@@ -9748,7 +9720,7 @@
         <v>1.0</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F253" s="3"/>
     </row>
@@ -9766,10 +9738,10 @@
         <v>3.0</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G254" s="9">
         <v>46613.0</v>
@@ -9789,7 +9761,7 @@
         <v>7.0</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>82</v>
@@ -9832,7 +9804,7 @@
         <v>12.0</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F257" s="4"/>
       <c r="G257" s="9"/>
@@ -9854,7 +9826,7 @@
         <v>14.0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F258" s="4"/>
       <c r="G258" s="9">
@@ -9876,7 +9848,7 @@
         <v>13.0</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F259" s="4"/>
       <c r="G259" s="9">
@@ -9898,7 +9870,7 @@
         <v>12.0</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F260" s="4"/>
       <c r="G260" s="9">
@@ -9922,7 +9894,7 @@
         <v>12.0</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F261" s="4"/>
       <c r="G261" s="9">
@@ -9943,7 +9915,7 @@
         <v>14.0</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F262" s="4"/>
       <c r="G262" s="9">
@@ -9964,7 +9936,7 @@
         <v>14.0</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="9">
@@ -9988,7 +9960,7 @@
         <v>66</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G264" s="9">
         <v>46949.0</v>
@@ -10008,7 +9980,7 @@
         <v>4.0</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>344</v>
@@ -10031,10 +10003,10 @@
         <v>17.0</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G266" s="9">
         <v>46743.0</v>
@@ -10054,10 +10026,10 @@
         <v>17.0</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G267" s="9">
         <v>46752.0</v>
@@ -10077,10 +10049,10 @@
         <v>17.0</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G268" s="9">
         <v>46750.0</v>
@@ -10100,7 +10072,7 @@
         <v>16.0</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F269" s="4"/>
       <c r="G269" s="9">
@@ -10121,7 +10093,7 @@
         <v>13.0</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F270" s="4"/>
       <c r="G270" s="9">
@@ -10142,7 +10114,7 @@
         <v>16.0</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F271" s="4"/>
       <c r="G271" s="9">
@@ -10163,7 +10135,7 @@
         <v>15.0</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>270</v>
@@ -10206,10 +10178,10 @@
         <v>19.0</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G274" s="9">
         <v>46670.0</v>
@@ -10229,7 +10201,7 @@
         <v>3.0</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>225</v>
@@ -10249,10 +10221,10 @@
         <v>20.0</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G276" s="9">
         <v>46789.0</v>
@@ -10313,10 +10285,10 @@
         <v>16.0</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G279" s="9">
         <v>46681.0</v>
@@ -10336,10 +10308,10 @@
         <v>16.0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G280" s="9">
         <v>46725.0</v>
@@ -10359,10 +10331,10 @@
         <v>8.0</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G281" s="9">
         <v>46789.0</v>
@@ -10382,10 +10354,10 @@
         <v>8.0</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G282" s="9">
         <v>46757.0</v>
@@ -10405,10 +10377,10 @@
         <v>17.0</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G283" s="9">
         <v>46947.0</v>
@@ -10428,7 +10400,7 @@
         <v>9.0</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F284" s="3">
         <v>11503.0</v>
@@ -10448,7 +10420,7 @@
         <v>2.0</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F285" s="3">
         <v>11504.0</v>
@@ -10469,10 +10441,10 @@
         <v>18.0</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G286" s="9">
         <v>46949.0</v>
@@ -10492,10 +10464,10 @@
         <v>18.0</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G287" s="9">
         <v>46794.0</v>
@@ -10538,7 +10510,7 @@
         <v>21.0</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>17</v>
@@ -10561,7 +10533,7 @@
         <v>16.0</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>17</v>
@@ -10584,7 +10556,7 @@
         <v>4.0</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>17</v>
@@ -10607,7 +10579,7 @@
         <v>4.0</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>17</v>
@@ -10631,7 +10603,7 @@
         <v>19.0</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>485</v>
@@ -10654,7 +10626,7 @@
         <v>19.0</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>485</v>
@@ -10677,7 +10649,7 @@
         <v>18.0</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F295" s="4"/>
       <c r="G295" s="9">
@@ -10698,10 +10670,10 @@
         <v>9.0</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G296" s="9">
         <v>46577.0</v>
@@ -10721,7 +10693,7 @@
         <v>9.0</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>369</v>
@@ -10744,10 +10716,10 @@
         <v>12.0</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G298" s="9">
         <v>46596.0</v>
@@ -10767,10 +10739,10 @@
         <v>20.0</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G299" s="9">
         <v>46641.0</v>
@@ -10790,7 +10762,7 @@
         <v>2.0</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>142</v>
@@ -10813,7 +10785,7 @@
         <v>2.0</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>383</v>
@@ -10836,7 +10808,7 @@
         <v>3.0</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F302" s="4"/>
     </row>
@@ -10854,7 +10826,7 @@
         <v>5.0</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>17</v>
@@ -10880,7 +10852,7 @@
         <v>5.0</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>436</v>
@@ -10906,7 +10878,7 @@
         <v>5.0</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>17</v>
@@ -10981,7 +10953,7 @@
         <v>4.0</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>17</v>
@@ -11001,7 +10973,7 @@
         <v>4.0</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>17</v>
@@ -11024,7 +10996,7 @@
         <v>5.0</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>17</v>
@@ -11047,7 +11019,7 @@
         <v>4.0</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>25</v>
@@ -11070,7 +11042,7 @@
         <v>4.0</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>25</v>
@@ -11096,7 +11068,7 @@
         <v>4.0</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>25</v>
@@ -11119,7 +11091,7 @@
         <v>4.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>25</v>
@@ -11142,7 +11114,7 @@
         <v>2.0</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>17</v>
@@ -11165,7 +11137,7 @@
         <v>2.0</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F316" s="3" t="s">
         <v>17</v>
@@ -11188,7 +11160,7 @@
         <v>2.0</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F317" s="3" t="s">
         <v>17</v>
@@ -11202,7 +11174,7 @@
         <v>1.776148337734E12</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>12</v>
@@ -11211,10 +11183,10 @@
         <v>6.0</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G318" s="9">
         <v>46269.0</v>
@@ -11228,7 +11200,7 @@
         <v>1.776148592568E12</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>12</v>
@@ -11237,10 +11209,10 @@
         <v>12.0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G319" s="9">
         <v>46234.0</v>
@@ -11254,7 +11226,7 @@
         <v>1.776148632656E12</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>12</v>
@@ -11263,10 +11235,10 @@
         <v>14.0</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G320" s="9">
         <v>46202.0</v>
@@ -11280,7 +11252,7 @@
         <v>1.776148710229E12</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>12</v>
@@ -11289,10 +11261,10 @@
         <v>13.0</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F321" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G321" s="9">
         <v>46193.0</v>
@@ -11306,7 +11278,7 @@
         <v>1.776148761624E12</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>12</v>
@@ -11315,10 +11287,10 @@
         <v>14.0</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G322" s="9">
         <v>46203.0</v>
@@ -11332,7 +11304,7 @@
         <v>1.776149046956E12</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>26</v>
@@ -11341,10 +11313,10 @@
         <v>4.0</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G323" s="9">
         <v>46182.0</v>
@@ -11358,7 +11330,7 @@
         <v>1.776149087494E12</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>12</v>
@@ -11367,7 +11339,7 @@
         <v>18.0</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F324" s="4"/>
     </row>
@@ -11385,7 +11357,7 @@
         <v>1.0</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F325" s="4"/>
       <c r="H325" s="2"/>
@@ -11404,7 +11376,7 @@
         <v>5.0</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F326" s="4"/>
       <c r="G326" s="9">
@@ -11426,7 +11398,7 @@
         <v>18.0</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>225</v>
@@ -11449,7 +11421,7 @@
         <v>3.0</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F328" s="3">
         <v>11504.0</v>
@@ -11469,10 +11441,10 @@
         <v>4.0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G329" s="9">
         <v>46949.0</v>
@@ -11492,10 +11464,10 @@
         <v>5.0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G330" s="9">
         <v>46949.0</v>
@@ -11515,7 +11487,7 @@
         <v>9.0</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>413</v>
@@ -11536,7 +11508,7 @@
         <v>10.0</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>413</v>
@@ -11556,7 +11528,7 @@
         <v>9.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>413</v>
@@ -11576,7 +11548,7 @@
         <v>13.0</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>239</v>
@@ -11599,7 +11571,7 @@
         <v>13.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>468</v>
@@ -11622,7 +11594,7 @@
         <v>16.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>239</v>
@@ -11645,7 +11617,7 @@
         <v>16.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>236</v>
@@ -11668,7 +11640,7 @@
         <v>16.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>236</v>
@@ -11691,7 +11663,7 @@
         <v>16.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F339" s="4"/>
     </row>
@@ -11709,7 +11681,7 @@
         <v>16.0</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>236</v>
@@ -11732,10 +11704,10 @@
         <v>17.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G341" s="9">
         <v>46768.0</v>
@@ -11755,10 +11727,10 @@
         <v>17.0</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G342" s="9">
         <v>46947.0</v>
@@ -11778,10 +11750,10 @@
         <v>17.0</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G343" s="9">
         <v>46771.0</v>
@@ -11801,7 +11773,7 @@
         <v>17.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>485</v>
@@ -11824,16 +11796,16 @@
         <v>20.0</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G345" s="9">
         <v>46691.0</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="346">
@@ -11850,7 +11822,7 @@
         <v>11.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>145</v>
@@ -11873,7 +11845,7 @@
         <v>12.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>239</v>
@@ -11896,7 +11868,7 @@
         <v>7.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F348" s="3">
         <v>11503.0</v>
@@ -11919,10 +11891,10 @@
         <v>11.0</v>
       </c>
       <c r="E349" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F349" s="3" t="s">
         <v>649</v>
-      </c>
-      <c r="F349" s="3" t="s">
-        <v>651</v>
       </c>
       <c r="G349" s="9">
         <v>46669.0</v>
@@ -11942,10 +11914,10 @@
         <v>12.0</v>
       </c>
       <c r="E350" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F350" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="F350" s="3" t="s">
-        <v>652</v>
       </c>
       <c r="G350" s="9">
         <v>46523.0</v>
@@ -11965,7 +11937,7 @@
         <v>12.0</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F351" s="4"/>
       <c r="G351" s="9">
@@ -11977,7 +11949,7 @@
         <v>1.776436049209E12</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>26</v>
@@ -12004,10 +11976,10 @@
         <v>1.0</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G353" s="9">
         <v>46793.0</v>
@@ -12015,7 +11987,7 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>112</v>
@@ -12030,7 +12002,7 @@
         <v>66</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G354" s="9">
         <v>46949.0</v>
@@ -12038,7 +12010,7 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>112</v>
@@ -12050,10 +12022,10 @@
         <v>20.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G355" s="9">
         <v>46793.0</v>
@@ -12061,7 +12033,7 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>112</v>
@@ -12073,10 +12045,10 @@
         <v>16.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G356" s="9">
         <v>46639.0</v>
@@ -12084,7 +12056,7 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>11</v>
@@ -12096,13 +12068,13 @@
         <v>3.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F357" s="4"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>11</v>
@@ -12114,13 +12086,13 @@
         <v>4.0</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F358" s="4"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>11</v>
@@ -12132,13 +12104,13 @@
         <v>5.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F359" s="4"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>11</v>
@@ -12150,13 +12122,13 @@
         <v>5.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F360" s="4"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>11</v>
@@ -12168,13 +12140,13 @@
         <v>5.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F361" s="4"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>11</v>
@@ -12186,13 +12158,13 @@
         <v>5.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F362" s="4"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>11</v>
@@ -12204,13 +12176,13 @@
         <v>1.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F363" s="4"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>33</v>
@@ -12222,7 +12194,7 @@
         <v>2.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>292</v>
@@ -12230,7 +12202,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>33</v>
@@ -12242,7 +12214,7 @@
         <v>2.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>344</v>
@@ -12253,7 +12225,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>33</v>
@@ -12265,15 +12237,15 @@
         <v>2.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>33</v>
@@ -12285,7 +12257,7 @@
         <v>4.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>292</v>
@@ -12297,7 +12269,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>112</v>
@@ -12309,7 +12281,7 @@
         <v>10.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F368" s="3">
         <v>11504.0</v>
@@ -12320,7 +12292,7 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>112</v>
@@ -12332,7 +12304,7 @@
         <v>8.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F369" s="3">
         <v>11504.0</v>
@@ -12341,7 +12313,7 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>33</v>
@@ -12353,14 +12325,14 @@
         <v>3.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F370" s="4"/>
       <c r="H370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>33</v>
@@ -12372,21 +12344,21 @@
         <v>11.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G371" s="9">
         <v>46240.0</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>112</v>
@@ -12398,10 +12370,10 @@
         <v>13.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G372" s="9">
         <v>46416.0</v>
@@ -12409,7 +12381,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>112</v>
@@ -12421,10 +12393,10 @@
         <v>16.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G373" s="9">
         <v>46544.0</v>
@@ -12432,7 +12404,7 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>112</v>
@@ -12444,21 +12416,21 @@
         <v>16.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G374" s="9">
         <v>46794.0</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>112</v>
@@ -12470,10 +12442,10 @@
         <v>16.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G375" s="9">
         <v>46785.0</v>
@@ -12481,7 +12453,7 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>112</v>
@@ -12493,10 +12465,10 @@
         <v>16.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G376" s="9">
         <v>46789.0</v>
@@ -12504,7 +12476,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>112</v>
@@ -12516,10 +12488,10 @@
         <v>16.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G377" s="9">
         <v>46839.0</v>
@@ -12527,7 +12499,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>112</v>
@@ -12539,10 +12511,10 @@
         <v>11.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G378" s="9">
         <v>46312.0</v>
@@ -12553,7 +12525,7 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>112</v>
@@ -12565,10 +12537,10 @@
         <v>17.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G379" s="9">
         <v>46669.0</v>
@@ -12577,7 +12549,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>112</v>
@@ -12589,10 +12561,10 @@
         <v>7.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G380" s="9">
         <v>46794.0</v>
@@ -12600,7 +12572,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>112</v>
@@ -12612,10 +12584,10 @@
         <v>7.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="G381" s="9">
         <v>46792.0</v>
@@ -12623,7 +12595,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>112</v>
@@ -12635,7 +12607,7 @@
         <v>6.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F382" s="3">
         <v>11504.0</v>
@@ -12644,7 +12616,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>112</v>
@@ -12656,7 +12628,7 @@
         <v>9.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F383" s="3">
         <v>115004.0</v>
@@ -12667,7 +12639,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>33</v>
@@ -12679,7 +12651,7 @@
         <v>3.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F384" s="3">
         <v>11505.0</v>
@@ -12687,7 +12659,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>33</v>
@@ -12699,7 +12671,7 @@
         <v>11.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>233</v>
@@ -12716,7 +12688,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>33</v>
@@ -12728,13 +12700,13 @@
         <v>22.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F386" s="4"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>33</v>
@@ -12746,7 +12718,7 @@
         <v>11.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>325</v>
@@ -12763,7 +12735,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>112</v>
@@ -12775,10 +12747,10 @@
         <v>20.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G388" s="9">
         <v>46596.0</v>
@@ -12786,7 +12758,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>112</v>
@@ -12798,10 +12770,10 @@
         <v>16.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G389" s="9">
         <v>46669.0</v>
@@ -12809,7 +12781,7 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>33</v>
@@ -12821,7 +12793,7 @@
         <v>9.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>404</v>
@@ -12829,7 +12801,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>33</v>
@@ -12841,7 +12813,7 @@
         <v>10.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>413</v>
@@ -12849,7 +12821,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>33</v>
@@ -12858,10 +12830,10 @@
         <v>26</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G392" s="9">
         <v>46410.0</v>
@@ -12869,7 +12841,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>33</v>
@@ -12881,10 +12853,10 @@
         <v>22.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G393" s="9">
         <v>46194.0</v>
@@ -12895,7 +12867,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>33</v>
@@ -12907,10 +12879,10 @@
         <v>5.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G394" s="9">
         <v>46257.0</v>
@@ -12918,7 +12890,7 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>112</v>
@@ -12930,10 +12902,10 @@
         <v>7.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G395" s="9">
         <v>46913.0</v>
@@ -12941,7 +12913,7 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>11</v>
@@ -12953,7 +12925,7 @@
         <v>2.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>225</v>
@@ -12961,7 +12933,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>11</v>
@@ -12981,7 +12953,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>11</v>
@@ -12993,7 +12965,7 @@
         <v>2.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>17</v>
@@ -13001,7 +12973,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>11</v>
@@ -13013,7 +12985,7 @@
         <v>2.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>38</v>
@@ -13024,7 +12996,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>11</v>
@@ -13036,7 +13008,7 @@
         <v>3.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F400" s="4"/>
       <c r="G400" s="9">
@@ -13045,7 +13017,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>33</v>
@@ -13057,10 +13029,10 @@
         <v>4.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G401" s="9">
         <v>46507.0</v>
@@ -13068,7 +13040,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>33</v>
@@ -13080,10 +13052,10 @@
         <v>4.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G402" s="9">
         <v>46484.0</v>
@@ -13091,7 +13063,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>112</v>
@@ -13103,7 +13075,7 @@
         <v>6.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F403" s="3">
         <v>11505.0</v>
@@ -13112,7 +13084,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>33</v>
@@ -13124,7 +13096,7 @@
         <v>5.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>57</v>
@@ -13132,7 +13104,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>112</v>
@@ -13144,7 +13116,7 @@
         <v>1.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>270</v>
@@ -13154,12 +13126,12 @@
       </c>
       <c r="H405" s="2"/>
       <c r="J405" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>112</v>
@@ -13171,10 +13143,10 @@
         <v>17.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G406" s="9">
         <v>46408.0</v>
@@ -13182,7 +13154,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>112</v>
@@ -13194,10 +13166,10 @@
         <v>17.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G407" s="9">
         <v>46473.0</v>
@@ -13205,7 +13177,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>112</v>
@@ -13217,10 +13189,10 @@
         <v>17.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G408" s="9">
         <v>46758.0</v>
@@ -13228,7 +13200,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>112</v>
@@ -13240,10 +13212,10 @@
         <v>17.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G409" s="9">
         <v>46431.0</v>
@@ -13251,7 +13223,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>112</v>
@@ -13263,10 +13235,10 @@
         <v>17.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G410" s="9">
         <v>46523.0</v>
@@ -13274,7 +13246,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>112</v>
@@ -13286,7 +13258,7 @@
         <v>22.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>225</v>
@@ -13294,7 +13266,7 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>112</v>
@@ -13306,7 +13278,7 @@
         <v>12.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>225</v>
@@ -13314,7 +13286,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>33</v>
@@ -13326,7 +13298,7 @@
         <v>19.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="F413" s="3" t="s">
         <v>225</v>
@@ -13334,7 +13306,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>33</v>
@@ -13346,7 +13318,7 @@
         <v>6.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>225</v>
@@ -13354,7 +13326,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>112</v>
@@ -13366,7 +13338,7 @@
         <v>14.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>236</v>
@@ -13377,7 +13349,7 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>33</v>
@@ -13389,18 +13361,18 @@
         <v>10.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="F416" s="3" t="s">
         <v>485</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>33</v>
@@ -13412,7 +13384,7 @@
         <v>18.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>485</v>
@@ -13423,7 +13395,7 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>33</v>
@@ -13435,18 +13407,18 @@
         <v>10.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>485</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>112</v>
@@ -13458,10 +13430,10 @@
         <v>18.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G419" s="9">
         <v>46666.0</v>
@@ -13469,7 +13441,7 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>33</v>
@@ -13481,10 +13453,10 @@
         <v>8.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G420" s="9">
         <v>46604.0</v>
@@ -13492,7 +13464,7 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>33</v>
@@ -13504,7 +13476,7 @@
         <v>8.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F421" s="3" t="s">
         <v>110</v>
@@ -13515,7 +13487,7 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>33</v>
@@ -13527,10 +13499,10 @@
         <v>8.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G422" s="9">
         <v>46658.0</v>
@@ -13538,7 +13510,7 @@
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>33</v>
@@ -13550,10 +13522,10 @@
         <v>8.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G423" s="9">
         <v>46669.0</v>
@@ -13561,7 +13533,7 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>11</v>
@@ -13573,13 +13545,13 @@
         <v>4.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F424" s="4"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>33</v>
@@ -13591,7 +13563,7 @@
         <v>11.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>485</v>
@@ -13599,7 +13571,7 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>112</v>
@@ -13611,21 +13583,21 @@
         <v>17.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="G426" s="9">
         <v>46792.0</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>33</v>
@@ -13637,10 +13609,10 @@
         <v>8.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="G427" s="9">
         <v>46304.0</v>
@@ -13648,7 +13620,7 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>33</v>
@@ -13660,7 +13632,7 @@
         <v>19.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>53</v>
@@ -13671,7 +13643,7 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>33</v>
@@ -13683,7 +13655,7 @@
         <v>20.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>357</v>
@@ -13694,7 +13666,7 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>33</v>
@@ -13706,7 +13678,7 @@
         <v>12.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>38</v>
@@ -13717,7 +13689,7 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>112</v>
@@ -13729,10 +13701,10 @@
         <v>20.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G431" s="9">
         <v>46794.0</v>
@@ -13740,7 +13712,7 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>112</v>
@@ -13752,10 +13724,10 @@
         <v>18.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G432" s="9">
         <v>46794.0</v>
@@ -13763,7 +13735,7 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>112</v>
@@ -13775,10 +13747,10 @@
         <v>13.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G433" s="9">
         <v>46484.0</v>
@@ -13786,7 +13758,7 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>112</v>
@@ -13798,10 +13770,10 @@
         <v>20.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F434" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G434" s="9">
         <v>46792.0</v>
@@ -13809,7 +13781,7 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>33</v>
@@ -13821,10 +13793,10 @@
         <v>9.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G435" s="9">
         <v>46676.0</v>
@@ -13832,7 +13804,7 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>33</v>
@@ -13844,13 +13816,13 @@
         <v>9.0</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F436" s="4"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>112</v>
@@ -13862,10 +13834,10 @@
         <v>12.0</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G437" s="9">
         <v>46641.0</v>
@@ -13873,7 +13845,7 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>112</v>
@@ -13885,10 +13857,10 @@
         <v>11.0</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G438" s="9">
         <v>46530.0</v>
@@ -13896,7 +13868,7 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>112</v>
@@ -13908,10 +13880,10 @@
         <v>13.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G439" s="9">
         <v>46949.0</v>
@@ -13919,7 +13891,7 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>112</v>
@@ -13931,10 +13903,10 @@
         <v>3.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G440" s="9">
         <v>46670.0</v>
@@ -13942,7 +13914,7 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>112</v>
@@ -13954,7 +13926,7 @@
         <v>3.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>444</v>
@@ -13965,7 +13937,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>112</v>
@@ -13977,7 +13949,7 @@
         <v>3.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F442" s="3" t="s">
         <v>444</v>
@@ -13988,7 +13960,7 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>33</v>
@@ -14000,10 +13972,10 @@
         <v>3.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G443" s="9">
         <v>46670.0</v>
@@ -14011,7 +13983,7 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>33</v>
@@ -14023,7 +13995,7 @@
         <v>3.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>444</v>
@@ -14034,7 +14006,7 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>33</v>
@@ -14046,7 +14018,7 @@
         <v>3.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F445" s="3" t="s">
         <v>47</v>
@@ -14057,7 +14029,7 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>112</v>
@@ -14069,15 +14041,15 @@
         <v>19.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>33</v>
@@ -14089,10 +14061,10 @@
         <v>3.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G447" s="9">
         <v>46670.0</v>
@@ -14103,7 +14075,7 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>33</v>
@@ -14115,7 +14087,7 @@
         <v>7.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>95</v>
@@ -14126,7 +14098,7 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>112</v>
@@ -14138,7 +14110,7 @@
         <v>22.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>316</v>
@@ -14149,7 +14121,7 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>112</v>
@@ -14161,7 +14133,7 @@
         <v>22.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>142</v>
@@ -14172,7 +14144,7 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>112</v>
@@ -14184,10 +14156,10 @@
         <v>22.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G451" s="9">
         <v>46670.0</v>
@@ -14195,7 +14167,7 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>33</v>
@@ -14207,10 +14179,10 @@
         <v>17.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G452" s="9">
         <v>46254.0</v>
@@ -14219,7 +14191,7 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>33</v>
@@ -14231,7 +14203,7 @@
         <v>11.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>399</v>
@@ -14242,7 +14214,7 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>33</v>
@@ -14254,10 +14226,10 @@
         <v>6.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="F454" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G454" s="9">
         <v>46669.0</v>
@@ -14265,7 +14237,7 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>33</v>
@@ -14277,10 +14249,10 @@
         <v>6.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F455" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G455" s="9">
         <v>46669.0</v>
@@ -14288,7 +14260,7 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>33</v>
@@ -14300,10 +14272,10 @@
         <v>6.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G456" s="9">
         <v>46669.0</v>
@@ -14311,7 +14283,7 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>33</v>
@@ -14323,10 +14295,10 @@
         <v>6.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G457" s="9">
         <v>46669.0</v>
@@ -14334,7 +14306,7 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>33</v>
@@ -14346,10 +14318,10 @@
         <v>18.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G458" s="9">
         <v>46947.0</v>
@@ -14357,7 +14329,7 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>33</v>
@@ -14369,10 +14341,10 @@
         <v>18.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G459" s="9">
         <v>46949.0</v>
@@ -14380,7 +14352,7 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>33</v>
@@ -14395,7 +14367,7 @@
         <v>66</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G460" s="9">
         <v>46949.0</v>
@@ -14403,7 +14375,7 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>33</v>
@@ -14415,15 +14387,15 @@
         <v>18.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>33</v>
@@ -14435,7 +14407,7 @@
         <v>3.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>45</v>
@@ -14446,7 +14418,7 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>33</v>
@@ -14458,7 +14430,7 @@
         <v>4.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>344</v>
@@ -14466,7 +14438,7 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>33</v>
@@ -14478,7 +14450,7 @@
         <v>1.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F464" s="3" t="s">
         <v>118</v>
@@ -14486,7 +14458,7 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>33</v>
@@ -14498,7 +14470,7 @@
         <v>2.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F465" s="3" t="s">
         <v>436</v>
@@ -14509,7 +14481,7 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>33</v>
@@ -14521,10 +14493,10 @@
         <v>8.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G466" s="9">
         <v>46250.0</v>
@@ -14532,7 +14504,7 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>33</v>
@@ -14544,7 +14516,7 @@
         <v>8.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>357</v>
@@ -14555,7 +14527,7 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>112</v>
@@ -14567,7 +14539,7 @@
         <v>20.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>462</v>
@@ -14578,7 +14550,7 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>33</v>
@@ -14590,10 +14562,10 @@
         <v>13.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G469" s="9">
         <v>46669.0</v>
@@ -14601,7 +14573,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>33</v>
@@ -14613,7 +14585,7 @@
         <v>7.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>444</v>
@@ -14624,7 +14596,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>33</v>
@@ -14636,10 +14608,10 @@
         <v>7.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G471" s="9">
         <v>46775.0</v>
@@ -14647,7 +14619,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>33</v>
@@ -14659,13 +14631,13 @@
         <v>11.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F472" s="4"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>33</v>
@@ -14677,13 +14649,13 @@
         <v>11.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F473" s="4"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>33</v>
@@ -14695,13 +14667,13 @@
         <v>11.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F474" s="4"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>33</v>
@@ -14713,59 +14685,54 @@
         <v>11.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F475" s="4"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D476" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>898</v>
+        <v>852</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G476" s="9">
-        <v>46803.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D477" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="F477" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="G477" s="9">
-        <v>46222.0</v>
-      </c>
+        <v>898</v>
+      </c>
+      <c r="F477" s="4"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>33</v>
@@ -14777,13 +14744,13 @@
         <v>11.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="F478" s="4"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>33</v>
@@ -14795,13 +14762,13 @@
         <v>11.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="F479" s="4"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>33</v>
@@ -14813,31 +14780,34 @@
         <v>11.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="F480" s="4"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D481" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F481" s="4"/>
+      <c r="G481" s="9">
+        <v>46564.0</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>33</v>
@@ -14849,16 +14819,16 @@
         <v>14.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="F482" s="4"/>
       <c r="G482" s="9">
-        <v>46564.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>33</v>
@@ -14870,16 +14840,16 @@
         <v>14.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="F483" s="4"/>
       <c r="G483" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>33</v>
@@ -14888,10 +14858,10 @@
         <v>26</v>
       </c>
       <c r="D484" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F484" s="4"/>
       <c r="G484" s="9">
@@ -14900,7 +14870,7 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>33</v>
@@ -14912,16 +14882,16 @@
         <v>15.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="F485" s="4"/>
       <c r="G485" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>33</v>
@@ -14933,7 +14903,7 @@
         <v>15.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="F486" s="4"/>
       <c r="G486" s="9">
@@ -14942,7 +14912,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>33</v>
@@ -14954,7 +14924,7 @@
         <v>15.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="F487" s="4"/>
       <c r="G487" s="9">
@@ -14963,7 +14933,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>33</v>
@@ -14972,19 +14942,19 @@
         <v>26</v>
       </c>
       <c r="D488" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="F488" s="4"/>
       <c r="G488" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>33</v>
@@ -14996,101 +14966,103 @@
         <v>11.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="F489" s="4"/>
       <c r="G489" s="9">
-        <v>46551.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D490" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="F490" s="4"/>
-      <c r="G490" s="9">
-        <v>46394.0</v>
+        <v>924</v>
+      </c>
+      <c r="F490" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C491" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D491" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="F491" s="3" t="s">
-        <v>413</v>
-      </c>
+        <v>926</v>
+      </c>
+      <c r="F491" s="4"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D492" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="F492" s="4"/>
+        <v>928</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G492" s="9">
+        <v>46759.0</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>33</v>
+        <v>529</v>
       </c>
       <c r="C493" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D493" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F493" s="3" t="s">
-        <v>413</v>
+        <v>38</v>
       </c>
       <c r="G493" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>12</v>
@@ -15099,7 +15071,7 @@
         <v>3.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>38</v>
@@ -15110,10 +15082,10 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C495" s="2" t="s">
         <v>12</v>
@@ -15122,7 +15094,7 @@
         <v>3.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>38</v>
@@ -15133,10 +15105,10 @@
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C496" s="2" t="s">
         <v>12</v>
@@ -15145,7 +15117,7 @@
         <v>3.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>38</v>
@@ -15156,10 +15128,10 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>12</v>
@@ -15168,10 +15140,10 @@
         <v>3.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>38</v>
+        <v>404</v>
       </c>
       <c r="G497" s="9">
         <v>46406.0</v>
@@ -15179,10 +15151,10 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>12</v>
@@ -15194,18 +15166,18 @@
         <v>939</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>404</v>
+        <v>38</v>
       </c>
       <c r="G498" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C499" s="2" t="s">
         <v>12</v>
@@ -15214,21 +15186,21 @@
         <v>3.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G499" s="9">
-        <v>46251.0</v>
+        <v>46258.0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>12</v>
@@ -15237,44 +15209,44 @@
         <v>3.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G500" s="9">
-        <v>46258.0</v>
+        <v>46254.0</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D501" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G501" s="9">
-        <v>46254.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>12</v>
@@ -15283,7 +15255,7 @@
         <v>4.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>38</v>
@@ -15294,10 +15266,10 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>12</v>
@@ -15306,7 +15278,7 @@
         <v>4.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>38</v>
@@ -15317,10 +15289,10 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>12</v>
@@ -15329,7 +15301,7 @@
         <v>4.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="F504" s="3" t="s">
         <v>38</v>
@@ -15340,33 +15312,33 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D505" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="F505" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G505" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>12</v>
@@ -15375,21 +15347,21 @@
         <v>6.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G506" s="9">
-        <v>46251.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>12</v>
@@ -15398,21 +15370,21 @@
         <v>6.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G507" s="9">
-        <v>46280.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>12</v>
@@ -15421,21 +15393,21 @@
         <v>6.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="F508" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G508" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>12</v>
@@ -15444,7 +15416,7 @@
         <v>6.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>38</v>
@@ -15455,10 +15427,10 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>12</v>
@@ -15467,7 +15439,7 @@
         <v>6.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="F510" s="3" t="s">
         <v>38</v>
@@ -15478,10 +15450,10 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>12</v>
@@ -15490,44 +15462,44 @@
         <v>6.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G511" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D512" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="F512" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G512" s="9">
-        <v>46249.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>12</v>
@@ -15536,21 +15508,21 @@
         <v>7.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F513" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G513" s="9">
-        <v>46352.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C514" s="2" t="s">
         <v>12</v>
@@ -15559,44 +15531,44 @@
         <v>7.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="F514" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G514" s="9">
-        <v>46333.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D515" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="F515" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G515" s="9">
-        <v>46244.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C516" s="2" t="s">
         <v>12</v>
@@ -15605,21 +15577,21 @@
         <v>8.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="F516" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G516" s="9">
-        <v>46226.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C517" s="2" t="s">
         <v>12</v>
@@ -15628,21 +15600,21 @@
         <v>8.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="F517" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G517" s="9">
-        <v>46222.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C518" s="2" t="s">
         <v>12</v>
@@ -15651,21 +15623,21 @@
         <v>8.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G518" s="9">
-        <v>46241.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>12</v>
@@ -15674,44 +15646,44 @@
         <v>8.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G519" s="9">
-        <v>46305.0</v>
+        <v>46319.0</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D520" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="F520" s="3" t="s">
-        <v>17</v>
+        <v>485</v>
       </c>
       <c r="G520" s="9">
-        <v>46319.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>12</v>
@@ -15720,44 +15692,47 @@
         <v>9.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="F521" s="3" t="s">
-        <v>485</v>
+        <v>38</v>
       </c>
       <c r="G521" s="9">
-        <v>46365.0</v>
+        <v>46321.0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D522" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G522" s="9">
-        <v>46321.0</v>
+        <v>46426.0</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>12</v>
@@ -15766,24 +15741,21 @@
         <v>10.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>38</v>
+        <v>404</v>
       </c>
       <c r="G523" s="9">
-        <v>46426.0</v>
-      </c>
-      <c r="H523" s="2" t="s">
-        <v>992</v>
+        <v>46211.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>12</v>
@@ -15792,21 +15764,24 @@
         <v>10.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>404</v>
       </c>
       <c r="G524" s="9">
-        <v>46211.0</v>
+        <v>46204.0</v>
+      </c>
+      <c r="I524" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>12</v>
@@ -15815,93 +15790,88 @@
         <v>10.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="F525" s="3" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="G525" s="9">
-        <v>46204.0</v>
-      </c>
-      <c r="I525" s="2" t="s">
-        <v>230</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C526" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D526" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="F526" s="3" t="s">
-        <v>383</v>
+        <v>38</v>
       </c>
       <c r="G526" s="9">
-        <v>46345.0</v>
+        <v>46392.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D527" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="F527" s="3" t="s">
-        <v>38</v>
+        <v>485</v>
       </c>
       <c r="G527" s="9">
-        <v>46392.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D528" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F528" s="3" t="s">
-        <v>485</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="F528" s="4"/>
       <c r="G528" s="9">
-        <v>46366.0</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>12</v>
@@ -15910,7 +15880,7 @@
         <v>14.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="F529" s="4"/>
       <c r="G529" s="9">
@@ -15919,40 +15889,39 @@
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C530" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D530" s="2">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F530" s="4"/>
-      <c r="G530" s="9">
-        <v>46220.0</v>
+        <v>1003</v>
+      </c>
+      <c r="F530" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C531" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D531" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>157</v>
@@ -15960,10 +15929,10 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>12</v>
@@ -15972,18 +15941,21 @@
         <v>2.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="G532" s="9">
+        <v>46223.0</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C533" s="2" t="s">
         <v>12</v>
@@ -15998,172 +15970,172 @@
         <v>157</v>
       </c>
       <c r="G533" s="9">
-        <v>46223.0</v>
+        <v>46228.0</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D534" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="F534" s="3" t="s">
-        <v>157</v>
+        <v>618</v>
       </c>
       <c r="G534" s="9">
-        <v>46228.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D535" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="F535" s="3" t="s">
-        <v>620</v>
+        <v>1013</v>
       </c>
       <c r="G535" s="9">
-        <v>46242.0</v>
-      </c>
+        <v>46274.0</v>
+      </c>
+      <c r="H535" s="2"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C536" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D536" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E536" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F536" s="3" t="s">
         <v>1016</v>
       </c>
-      <c r="B536" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C536" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D536" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="E536" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F536" s="3" t="s">
-        <v>1018</v>
-      </c>
       <c r="G536" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H536" s="2"/>
+        <v>46743.0</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C537" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D537" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E537" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F537" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="B537" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C537" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D537" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E537" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F537" s="3" t="s">
-        <v>1021</v>
-      </c>
       <c r="G537" s="9">
-        <v>46743.0</v>
+        <v>46207.0</v>
+      </c>
+      <c r="I537" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D538" s="2">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F538" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G538" s="9">
-        <v>46207.0</v>
-      </c>
-      <c r="I538" s="2" t="s">
-        <v>230</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="F538" s="4"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D539" s="2">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F539" s="4"/>
+        <v>1022</v>
+      </c>
+      <c r="F539" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G539" s="9">
+        <v>46295.0</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D540" s="2">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>233</v>
+        <v>1013</v>
       </c>
       <c r="G540" s="9">
-        <v>46295.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>33</v>
@@ -16172,13 +16144,13 @@
         <v>34</v>
       </c>
       <c r="D541" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G541" s="9">
         <v>46769.0</v>
@@ -16186,33 +16158,33 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>33</v>
+        <v>527</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D542" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="G542" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>12</v>
@@ -16221,21 +16193,21 @@
         <v>3.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G543" s="9">
-        <v>46261.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>12</v>
@@ -16244,21 +16216,21 @@
         <v>3.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G544" s="9">
-        <v>46266.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C545" s="2" t="s">
         <v>12</v>
@@ -16267,21 +16239,21 @@
         <v>3.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="F545" s="3" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G545" s="9">
-        <v>46223.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>529</v>
+        <v>33</v>
       </c>
       <c r="C546" s="2" t="s">
         <v>12</v>
@@ -16290,41 +16262,41 @@
         <v>3.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>1033</v>
+        <v>1013</v>
       </c>
       <c r="G546" s="9">
-        <v>46266.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D547" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1041</v>
+        <v>701</v>
       </c>
       <c r="F547" s="3" t="s">
-        <v>1018</v>
+        <v>1038</v>
       </c>
       <c r="G547" s="9">
-        <v>46769.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>112</v>
@@ -16336,18 +16308,18 @@
         <v>14.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>703</v>
+        <v>1040</v>
       </c>
       <c r="F548" s="3" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="G548" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>112</v>
@@ -16359,10 +16331,10 @@
         <v>14.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1045</v>
+        <v>697</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="G549" s="9">
         <v>46820.0</v>
@@ -16370,7 +16342,7 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>112</v>
@@ -16382,41 +16354,41 @@
         <v>14.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>699</v>
+        <v>593</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="G550" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D551" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>595</v>
+        <v>873</v>
       </c>
       <c r="F551" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G551" s="9">
-        <v>46998.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>33</v>
@@ -16428,18 +16400,18 @@
         <v>2.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>875</v>
+        <v>1046</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G552" s="9">
-        <v>46484.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>33</v>
@@ -16451,18 +16423,18 @@
         <v>2.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G553" s="9">
-        <v>46432.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>33</v>
@@ -16474,18 +16446,18 @@
         <v>2.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>1055</v>
+        <v>450</v>
       </c>
       <c r="G554" s="9">
-        <v>46877.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>33</v>
@@ -16497,18 +16469,16 @@
         <v>2.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="G555" s="9">
-        <v>46704.0</v>
-      </c>
+        <v>1055</v>
+      </c>
+      <c r="G555" s="9"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>33</v>
@@ -16520,16 +16490,15 @@
         <v>2.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G556" s="9"/>
+        <v>1055</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>33</v>
@@ -16541,15 +16510,15 @@
         <v>2.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1062</v>
+        <v>857</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>33</v>
@@ -16561,15 +16530,15 @@
         <v>2.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>859</v>
+        <v>673</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>33</v>
@@ -16581,15 +16550,15 @@
         <v>2.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>675</v>
+        <v>1057</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>33</v>
@@ -16604,12 +16573,12 @@
         <v>1062</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>33</v>
@@ -16621,38 +16590,41 @@
         <v>2.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>1060</v>
+        <v>585</v>
+      </c>
+      <c r="G561" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D562" s="2">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1069</v>
+        <v>829</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>587</v>
+        <v>1066</v>
       </c>
       <c r="G562" s="9">
-        <v>46766.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>112</v>
@@ -16661,22 +16633,22 @@
         <v>12</v>
       </c>
       <c r="D563" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G563" s="9">
-        <v>46877.0</v>
+        <v>46743.0</v>
       </c>
       <c r="H563" s="2"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>112</v>
@@ -16685,21 +16657,17 @@
         <v>12</v>
       </c>
       <c r="D564" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="F564" s="3" t="s">
-        <v>1072</v>
-      </c>
-      <c r="G564" s="9">
-        <v>46641.0</v>
-      </c>
+        <v>1070</v>
+      </c>
+      <c r="F564" s="4"/>
+      <c r="H564" s="2"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>112</v>
@@ -16708,24 +16676,24 @@
         <v>12</v>
       </c>
       <c r="D565" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1075</v>
+        <v>697</v>
       </c>
       <c r="F565" s="3" t="s">
         <v>1072</v>
       </c>
       <c r="G565" s="9">
-        <v>46743.0</v>
+        <v>46663.0</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>112</v>
@@ -16734,17 +16702,21 @@
         <v>12</v>
       </c>
       <c r="D566" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F566" s="4"/>
-      <c r="H566" s="2"/>
+        <v>1074</v>
+      </c>
+      <c r="F566" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G566" s="9">
+        <v>46775.0</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>112</v>
@@ -16753,24 +16725,21 @@
         <v>12</v>
       </c>
       <c r="D567" s="2">
-        <v>18.0</v>
+        <v>11.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>794</v>
+        <v>648</v>
       </c>
       <c r="F567" s="3" t="s">
-        <v>1079</v>
+        <v>1066</v>
       </c>
       <c r="G567" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H567" s="2" t="s">
-        <v>133</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>112</v>
@@ -16779,67 +16748,67 @@
         <v>12</v>
       </c>
       <c r="D568" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G568" s="9">
-        <v>46775.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D569" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>650</v>
+        <v>1079</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G569" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D570" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G570" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>112</v>
@@ -16851,18 +16820,21 @@
         <v>14.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G571" s="9">
-        <v>46481.0</v>
+        <v>46734.0</v>
+      </c>
+      <c r="H571" s="2" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>112</v>
@@ -16874,18 +16846,18 @@
         <v>14.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G572" s="9">
-        <v>46877.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>112</v>
@@ -16897,316 +16869,316 @@
         <v>14.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G573" s="9">
-        <v>46734.0</v>
-      </c>
-      <c r="H573" s="2" t="s">
-        <v>329</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D574" s="2">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1092</v>
+        <v>829</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G574" s="9">
-        <v>46481.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D575" s="2">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>1072</v>
+        <v>1013</v>
       </c>
       <c r="G575" s="9">
-        <v>46877.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D576" s="2">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>831</v>
+        <v>1092</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1072</v>
+        <v>1013</v>
       </c>
       <c r="G576" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D577" s="2">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>1018</v>
+        <v>225</v>
       </c>
       <c r="G577" s="9">
-        <v>46274.0</v>
+        <v>46437.0</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D578" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>1018</v>
+        <v>1097</v>
       </c>
       <c r="G578" s="9">
-        <v>46274.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D579" s="2">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="F579" s="3"/>
       <c r="G579" s="9"/>
+      <c r="H579" s="2" t="s">
+        <v>1100</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D580" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E580" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="B580" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C580" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D580" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E580" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F580" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="G580" s="9">
-        <v>46437.0</v>
-      </c>
+      <c r="F580" s="3"/>
+      <c r="G580" s="9"/>
+      <c r="H580" s="2"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D581" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E581" s="2" t="s">
         <v>1104</v>
       </c>
-      <c r="B581" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C581" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D581" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="E581" s="2" t="s">
-        <v>1105</v>
-      </c>
       <c r="F581" s="3" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G581" s="9">
-        <v>46516.0</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="G581" s="9"/>
+      <c r="H581" s="2"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D582" s="2">
-        <v>22.0</v>
+        <v>4.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F582" s="3"/>
-      <c r="G582" s="9"/>
-      <c r="H582" s="2" t="s">
-        <v>1109</v>
-      </c>
+        <v>1106</v>
+      </c>
+      <c r="F582" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G582" s="9">
+        <v>46403.0</v>
+      </c>
+      <c r="H582" s="2"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D583" s="2">
-        <v>6.0</v>
+        <v>21.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F583" s="3"/>
-      <c r="G583" s="9"/>
+        <v>581</v>
+      </c>
+      <c r="F583" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G583" s="9">
+        <v>46337.0</v>
+      </c>
       <c r="H583" s="2"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>33</v>
+        <v>527</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D584" s="2">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1113</v>
+        <v>615</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="G584" s="9"/>
+        <v>616</v>
+      </c>
+      <c r="G584" s="9">
+        <v>46269.0</v>
+      </c>
       <c r="H584" s="2"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D585" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>17</v>
+        <v>1112</v>
       </c>
       <c r="G585" s="9">
-        <v>46403.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H585" s="2"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="C586" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D586" s="2">
-        <v>21.0</v>
+        <v>8.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F586" s="3" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G586" s="9">
-        <v>46337.0</v>
-      </c>
+        <v>1114</v>
+      </c>
+      <c r="F586" s="3"/>
+      <c r="G586" s="9"/>
       <c r="H586" s="2"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C587" s="2" t="s">
         <v>12</v>
@@ -17215,179 +17187,177 @@
         <v>8.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>617</v>
+        <v>1116</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>618</v>
+        <v>1112</v>
       </c>
       <c r="G587" s="9">
-        <v>46269.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H587" s="2"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D588" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E588" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F588" s="3" t="s">
         <v>1119</v>
       </c>
-      <c r="B588" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C588" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D588" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="E588" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="F588" s="3" t="s">
-        <v>1121</v>
-      </c>
       <c r="G588" s="9">
-        <v>46290.0</v>
+        <v>46883.0</v>
       </c>
       <c r="H588" s="2"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>529</v>
+        <v>33</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D589" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F589" s="3"/>
-      <c r="G589" s="9"/>
+        <v>1118</v>
+      </c>
+      <c r="F589" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="G589" s="9">
+        <v>46883.0</v>
+      </c>
       <c r="H589" s="2"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D590" s="2">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F590" s="3" t="s">
-        <v>1121</v>
-      </c>
-      <c r="G590" s="9">
-        <v>46290.0</v>
-      </c>
+        <v>1122</v>
+      </c>
+      <c r="F590" s="3">
+        <v>11505.0</v>
+      </c>
+      <c r="G590" s="9"/>
       <c r="H590" s="2"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D591" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F591" s="3" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G591" s="9">
-        <v>46883.0</v>
-      </c>
+        <v>1124</v>
+      </c>
+      <c r="F591" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G591" s="9"/>
       <c r="H591" s="2"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D592" s="2">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F592" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="G592" s="9">
-        <v>46883.0</v>
-      </c>
+        <v>1126</v>
+      </c>
+      <c r="F592" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G592" s="9"/>
       <c r="H592" s="2"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D593" s="2">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1131</v>
+        <v>538</v>
       </c>
       <c r="F593" s="3">
-        <v>11505.0</v>
+        <v>11504.0</v>
       </c>
       <c r="G593" s="9"/>
       <c r="H593" s="2"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D594" s="2">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F594" s="3">
-        <v>11504.0</v>
+        <v>1129</v>
+      </c>
+      <c r="F594" s="3" t="s">
+        <v>1130</v>
       </c>
       <c r="G594" s="9"/>
       <c r="H594" s="2"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>112</v>
@@ -17396,20 +17366,20 @@
         <v>28</v>
       </c>
       <c r="D595" s="2">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F595" s="3">
-        <v>11504.0</v>
+        <v>599</v>
+      </c>
+      <c r="F595" s="3" t="s">
+        <v>1132</v>
       </c>
       <c r="G595" s="9"/>
       <c r="H595" s="2"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>112</v>
@@ -17418,20 +17388,20 @@
         <v>28</v>
       </c>
       <c r="D596" s="2">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F596" s="3">
-        <v>11504.0</v>
+        <v>599</v>
+      </c>
+      <c r="F596" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="G596" s="9"/>
       <c r="H596" s="2"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>33</v>
@@ -17440,211 +17410,217 @@
         <v>26</v>
       </c>
       <c r="D597" s="2">
-        <v>2.0</v>
+        <v>17.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F597" s="3" t="s">
-        <v>1139</v>
-      </c>
-      <c r="G597" s="9"/>
+        <v>1135</v>
+      </c>
+      <c r="F597" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G597" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="H597" s="2"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D598" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F598" s="3" t="s">
-        <v>1141</v>
-      </c>
-      <c r="G598" s="9"/>
+        <v>1137</v>
+      </c>
+      <c r="F598" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G598" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="H598" s="2"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D599" s="2">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F599" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="G599" s="9"/>
+        <v>1139</v>
+      </c>
+      <c r="F599" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G599" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="H599" s="2"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D600" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F600" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G600" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F600" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G600" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H600" s="2"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D601" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F601" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G601" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F601" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G601" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H601" s="2"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D602" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F602" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G602" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F602" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G602" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H602" s="2"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>11</v>
+        <v>527</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D603" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>21</v>
+        <v>623</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>38</v>
+        <v>1144</v>
       </c>
       <c r="G603" s="9">
-        <v>47531.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H603" s="2"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>11</v>
+        <v>527</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D604" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>21</v>
+        <v>621</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>38</v>
+        <v>1146</v>
       </c>
       <c r="G604" s="9">
-        <v>47531.0</v>
+        <v>46223.0</v>
       </c>
       <c r="H604" s="2"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>11</v>
+        <v>527</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D605" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>21</v>
+        <v>1018</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>38</v>
+        <v>1146</v>
       </c>
       <c r="G605" s="9">
-        <v>47531.0</v>
+        <v>46221.0</v>
       </c>
       <c r="H605" s="2"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C606" s="2" t="s">
         <v>12</v>
@@ -17653,91 +17629,83 @@
         <v>10.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="G606" s="9">
-        <v>46217.0</v>
+        <v>46214.0</v>
       </c>
       <c r="H606" s="2"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D607" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F607" s="3" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G607" s="9">
-        <v>46223.0</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="F607" s="3"/>
+      <c r="G607" s="9"/>
       <c r="H607" s="2"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D608" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F608" s="3" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G608" s="9">
-        <v>46221.0</v>
-      </c>
+        <v>1126</v>
+      </c>
+      <c r="F608" s="3"/>
+      <c r="G608" s="9"/>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>529</v>
+        <v>112</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D609" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>621</v>
+        <v>882</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1155</v>
+        <v>142</v>
       </c>
       <c r="G609" s="9">
-        <v>46214.0</v>
+        <v>46636.0</v>
       </c>
       <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>112</v>
@@ -17746,148 +17714,152 @@
         <v>12</v>
       </c>
       <c r="D610" s="2">
-        <v>4.0</v>
+        <v>21.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="F610" s="3"/>
-      <c r="G610" s="9"/>
+        <v>563</v>
+      </c>
+      <c r="F610" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G610" s="9">
+        <v>46814.0</v>
+      </c>
       <c r="H610" s="2"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D611" s="2">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F611" s="3"/>
-      <c r="G611" s="9"/>
+        <v>1155</v>
+      </c>
+      <c r="F611" s="3">
+        <v>11505.0</v>
+      </c>
+      <c r="G611" s="9">
+        <v>46814.0</v>
+      </c>
       <c r="H611" s="2"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D612" s="2">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>884</v>
+        <v>1157</v>
       </c>
       <c r="F612" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G612" s="9">
-        <v>46636.0</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="G612" s="9"/>
       <c r="H612" s="2"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D613" s="2">
-        <v>21.0</v>
+        <v>15.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>565</v>
+        <v>677</v>
       </c>
       <c r="F613" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="G613" s="9">
-        <v>46814.0</v>
-      </c>
+        <v>1130</v>
+      </c>
+      <c r="G613" s="9"/>
       <c r="H613" s="2"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D614" s="2">
         <v>5.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F614" s="3">
-        <v>11505.0</v>
+        <v>1160</v>
+      </c>
+      <c r="F614" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G614" s="9">
-        <v>46814.0</v>
+        <v>46436.0</v>
       </c>
       <c r="H614" s="2"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D615" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E615" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F615" s="3" t="s">
         <v>1163</v>
       </c>
-      <c r="B615" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D615" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E615" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F615" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="G615" s="9"/>
+      <c r="G615" s="9">
+        <v>46871.0</v>
+      </c>
       <c r="H615" s="2"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D616" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E616" s="2" t="s">
         <v>1165</v>
       </c>
-      <c r="B616" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C616" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D616" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E616" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F616" s="3" t="s">
-        <v>1139</v>
-      </c>
+      <c r="F616" s="3"/>
       <c r="G616" s="9"/>
       <c r="H616" s="2"/>
     </row>
@@ -17899,19 +17871,19 @@
         <v>112</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D617" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E617" s="2" t="s">
         <v>1167</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>17</v>
+        <v>413</v>
       </c>
       <c r="G617" s="9">
-        <v>46436.0</v>
+        <v>46767.0</v>
       </c>
       <c r="H617" s="2"/>
     </row>
@@ -17920,47 +17892,43 @@
         <v>1168</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>33</v>
+        <v>527</v>
       </c>
       <c r="C618" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D618" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E618" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="F618" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="F618" s="3" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G618" s="9">
-        <v>46871.0</v>
-      </c>
+      <c r="G618" s="9"/>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D619" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E619" s="2" t="s">
         <v>1171</v>
       </c>
-      <c r="B619" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C619" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D619" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="E619" s="2" t="s">
-        <v>1169</v>
-      </c>
       <c r="F619" s="3" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G619" s="9">
-        <v>46871.0</v>
-      </c>
+        <v>1028</v>
+      </c>
+      <c r="G619" s="9"/>
       <c r="H619" s="2"/>
     </row>
     <row r="620">
@@ -17968,110 +17936,22 @@
         <v>1172</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="C620" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D620" s="2">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="E620" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="F620" s="3"/>
+      <c r="F620" s="3" t="s">
+        <v>616</v>
+      </c>
       <c r="G620" s="9"/>
       <c r="H620" s="2"/>
-    </row>
-    <row r="621">
-      <c r="A621" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B621" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C621" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D621" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="E621" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="F621" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="G621" s="9">
-        <v>46767.0</v>
-      </c>
-      <c r="H621" s="2"/>
-    </row>
-    <row r="622">
-      <c r="A622" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B622" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C622" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D622" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E622" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="F622" s="3" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G622" s="9"/>
-      <c r="H622" s="2"/>
-    </row>
-    <row r="623">
-      <c r="A623" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D623" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E623" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F623" s="3" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G623" s="9"/>
-      <c r="H623" s="2"/>
-    </row>
-    <row r="624">
-      <c r="A624" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B624" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D624" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E624" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F624" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="G624" s="9"/>
-      <c r="H624" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="1194">
   <si>
     <t>ID</t>
   </si>
@@ -3340,12 +3340,6 @@
     <t>60S</t>
   </si>
   <si>
-    <t>ID1780534471460</t>
-  </si>
-  <si>
-    <t>#35</t>
-  </si>
-  <si>
     <t>ID1780546652417</t>
   </si>
   <si>
@@ -3578,6 +3572,27 @@
   </si>
   <si>
     <t>ID1781060467529</t>
+  </si>
+  <si>
+    <t>ID1781138810658</t>
+  </si>
+  <si>
+    <t>#21</t>
+  </si>
+  <si>
+    <t>ID1781138851460</t>
+  </si>
+  <si>
+    <t>ID1781138942905</t>
+  </si>
+  <si>
+    <t>13S</t>
+  </si>
+  <si>
+    <t>ID1781138976518</t>
+  </si>
+  <si>
+    <t>ID1781138989872</t>
   </si>
 </sst>
 </file>
@@ -16849,7 +16864,7 @@
         <v>1093</v>
       </c>
       <c r="F569" s="3">
-        <v>11505.0</v>
+        <v>11506.0</v>
       </c>
       <c r="G569" s="9"/>
       <c r="H569" s="2"/>
@@ -17039,34 +17054,34 @@
         <v>1109</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D578" s="2">
         <v>1.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F578" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G578" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F578" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G578" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H578" s="2"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D579" s="2">
         <v>1.0</v>
@@ -17084,16 +17099,16 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D580" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E580" s="2" t="s">
         <v>21</v>
@@ -17108,25 +17123,25 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D581" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E581" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F581" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="B581" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C581" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D581" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E581" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F581" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="G581" s="9">
-        <v>47531.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H581" s="2"/>
     </row>
@@ -17144,19 +17159,19 @@
         <v>10.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>614</v>
+        <v>1115</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G582" s="9">
-        <v>46217.0</v>
+        <v>46223.0</v>
       </c>
       <c r="H582" s="2"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>521</v>
@@ -17168,13 +17183,13 @@
         <v>10.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G583" s="9">
-        <v>46223.0</v>
+        <v>46221.0</v>
       </c>
       <c r="H583" s="2"/>
     </row>
@@ -17192,43 +17207,39 @@
         <v>10.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1120</v>
+        <v>612</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G584" s="9">
-        <v>46221.0</v>
+        <v>46214.0</v>
       </c>
       <c r="H584" s="2"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>521</v>
+        <v>112</v>
       </c>
       <c r="C585" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D585" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="F585" s="3" t="s">
-        <v>1118</v>
-      </c>
-      <c r="G585" s="9">
-        <v>46214.0</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="F585" s="3"/>
+      <c r="G585" s="9"/>
       <c r="H585" s="2"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>112</v>
@@ -17237,10 +17248,10 @@
         <v>12</v>
       </c>
       <c r="D586" s="2">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>619</v>
+        <v>1097</v>
       </c>
       <c r="F586" s="3"/>
       <c r="G586" s="9"/>
@@ -17248,7 +17259,7 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>112</v>
@@ -17257,36 +17268,40 @@
         <v>12</v>
       </c>
       <c r="D587" s="2">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F587" s="3"/>
-      <c r="G587" s="9"/>
+        <v>872</v>
+      </c>
+      <c r="F587" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G587" s="9">
+        <v>46636.0</v>
+      </c>
       <c r="H587" s="2"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D588" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="E588" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F588" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="B588" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C588" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D588" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E588" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="F588" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="G588" s="9">
-        <v>46636.0</v>
+        <v>46814.0</v>
       </c>
       <c r="H588" s="2"/>
     </row>
@@ -17298,16 +17313,16 @@
         <v>112</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D589" s="2">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F589" s="3" t="s">
         <v>1126</v>
+      </c>
+      <c r="F589" s="3">
+        <v>11505.0</v>
       </c>
       <c r="G589" s="9">
         <v>46814.0</v>
@@ -17322,20 +17337,18 @@
         <v>112</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D590" s="2">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="F590" s="3">
-        <v>11505.0</v>
-      </c>
-      <c r="G590" s="9">
-        <v>46814.0</v>
-      </c>
+      <c r="F590" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="G590" s="9"/>
       <c r="H590" s="2"/>
     </row>
     <row r="591">
@@ -17352,34 +17365,36 @@
         <v>15.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1130</v>
+        <v>667</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>480</v>
+        <v>1101</v>
       </c>
       <c r="G591" s="9"/>
       <c r="H591" s="2"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D592" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E592" s="2" t="s">
         <v>1131</v>
       </c>
-      <c r="B592" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C592" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D592" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E592" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F592" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G592" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="G592" s="9">
+        <v>46436.0</v>
+      </c>
       <c r="H592" s="2"/>
     </row>
     <row r="593">
@@ -17387,50 +17402,46 @@
         <v>1132</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C593" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D593" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>1133</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>17</v>
+        <v>1134</v>
       </c>
       <c r="G593" s="9">
-        <v>46436.0</v>
-      </c>
-      <c r="H593" s="2"/>
+        <v>46871.0</v>
+      </c>
+      <c r="H593" s="2" t="s">
+        <v>1135</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C594" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D594" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F594" s="3" t="s">
-        <v>1136</v>
-      </c>
-      <c r="G594" s="9">
-        <v>46871.0</v>
-      </c>
-      <c r="H594" s="2" t="s">
         <v>1137</v>
       </c>
+      <c r="F594" s="3"/>
+      <c r="G594" s="9"/>
+      <c r="H594" s="2"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
@@ -17440,16 +17451,20 @@
         <v>112</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D595" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E595" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="F595" s="3"/>
-      <c r="G595" s="9"/>
+      <c r="F595" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G595" s="9">
+        <v>46767.0</v>
+      </c>
       <c r="H595" s="2"/>
     </row>
     <row r="596">
@@ -17457,22 +17472,22 @@
         <v>1140</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>112</v>
+        <v>521</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D596" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>1141</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>411</v>
+        <v>1001</v>
       </c>
       <c r="G596" s="9">
-        <v>46767.0</v>
+        <v>46261.0</v>
       </c>
       <c r="H596" s="2"/>
     </row>
@@ -17487,41 +17502,37 @@
         <v>12</v>
       </c>
       <c r="D597" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1143</v>
+        <v>786</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1001</v>
+        <v>609</v>
       </c>
       <c r="G597" s="9">
-        <v>46261.0</v>
+        <v>46205.0</v>
       </c>
       <c r="H597" s="2"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D598" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E598" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B598" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="C598" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D598" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E598" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="F598" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="G598" s="9">
-        <v>46205.0</v>
-      </c>
+      <c r="F598" s="3"/>
+      <c r="G598" s="9"/>
       <c r="H598" s="2"/>
     </row>
     <row r="599">
@@ -17535,7 +17546,7 @@
         <v>34</v>
       </c>
       <c r="D599" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E599" s="2" t="s">
         <v>1146</v>
@@ -17555,10 +17566,10 @@
         <v>34</v>
       </c>
       <c r="D600" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1148</v>
+        <v>656</v>
       </c>
       <c r="F600" s="3"/>
       <c r="G600" s="9"/>
@@ -17566,22 +17577,26 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>11</v>
+        <v>523</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D601" s="2">
         <v>4.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="F601" s="3"/>
-      <c r="G601" s="9"/>
+        <v>1149</v>
+      </c>
+      <c r="F601" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G601" s="9">
+        <v>46387.0</v>
+      </c>
       <c r="H601" s="2"/>
     </row>
     <row r="602">
@@ -17595,7 +17610,7 @@
         <v>12</v>
       </c>
       <c r="D602" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>1151</v>
@@ -17691,22 +17706,22 @@
         <v>12</v>
       </c>
       <c r="D606" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1159</v>
+        <v>839</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>38</v>
+        <v>986</v>
       </c>
       <c r="G606" s="9">
-        <v>46387.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H606" s="2"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>523</v>
@@ -17718,7 +17733,7 @@
         <v>12.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>839</v>
+        <v>1137</v>
       </c>
       <c r="F607" s="3" t="s">
         <v>986</v>
@@ -17730,7 +17745,7 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>523</v>
@@ -17739,22 +17754,22 @@
         <v>12</v>
       </c>
       <c r="D608" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1139</v>
+        <v>948</v>
       </c>
       <c r="F608" s="3" t="s">
-        <v>986</v>
+        <v>480</v>
       </c>
       <c r="G608" s="9">
-        <v>46217.0</v>
+        <v>46308.0</v>
       </c>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>523</v>
@@ -17766,19 +17781,19 @@
         <v>10.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>948</v>
+        <v>923</v>
       </c>
       <c r="F609" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G609" s="9">
-        <v>46308.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>523</v>
@@ -17790,13 +17805,13 @@
         <v>10.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>923</v>
+        <v>1163</v>
       </c>
       <c r="F610" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G610" s="9">
-        <v>46521.0</v>
+        <v>46525.0</v>
       </c>
       <c r="H610" s="2"/>
     </row>
@@ -17814,19 +17829,19 @@
         <v>10.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1165</v>
+        <v>921</v>
       </c>
       <c r="F611" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G611" s="9">
-        <v>46525.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H611" s="2"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>523</v>
@@ -17838,7 +17853,7 @@
         <v>10.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="F612" s="3" t="s">
         <v>480</v>
@@ -17850,7 +17865,7 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>523</v>
@@ -17862,19 +17877,19 @@
         <v>10.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="F613" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G613" s="9">
-        <v>46521.0</v>
+        <v>46527.0</v>
       </c>
       <c r="H613" s="2"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>523</v>
@@ -17886,13 +17901,13 @@
         <v>10.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>919</v>
+        <v>1168</v>
       </c>
       <c r="F614" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G614" s="9">
-        <v>46527.0</v>
+        <v>46356.0</v>
       </c>
       <c r="H614" s="2"/>
     </row>
@@ -17916,7 +17931,7 @@
         <v>480</v>
       </c>
       <c r="G615" s="9">
-        <v>46356.0</v>
+        <v>46366.0</v>
       </c>
       <c r="H615" s="2"/>
     </row>
@@ -17940,7 +17955,7 @@
         <v>480</v>
       </c>
       <c r="G616" s="9">
-        <v>46366.0</v>
+        <v>46336.0</v>
       </c>
       <c r="H616" s="2"/>
     </row>
@@ -17955,22 +17970,22 @@
         <v>12</v>
       </c>
       <c r="D617" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>1174</v>
+        <v>942</v>
       </c>
       <c r="F617" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G617" s="9">
-        <v>46336.0</v>
+        <v>46310.0</v>
       </c>
       <c r="H617" s="2"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>523</v>
@@ -17982,19 +17997,19 @@
         <v>11.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="F618" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G618" s="9">
-        <v>46310.0</v>
+        <v>46354.0</v>
       </c>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>523</v>
@@ -18006,13 +18021,13 @@
         <v>11.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>928</v>
+        <v>1176</v>
       </c>
       <c r="F619" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G619" s="9">
-        <v>46354.0</v>
+        <v>46360.0</v>
       </c>
       <c r="H619" s="2"/>
     </row>
@@ -18030,19 +18045,19 @@
         <v>11.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1178</v>
+        <v>944</v>
       </c>
       <c r="F620" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G620" s="9">
-        <v>46360.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H620" s="2"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>523</v>
@@ -18054,19 +18069,19 @@
         <v>11.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="F621" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G621" s="9">
-        <v>46333.0</v>
+        <v>46346.0</v>
       </c>
       <c r="H621" s="2"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>523</v>
@@ -18078,19 +18093,19 @@
         <v>11.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F622" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G622" s="9">
-        <v>46346.0</v>
+        <v>46342.0</v>
       </c>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>523</v>
@@ -18102,13 +18117,13 @@
         <v>11.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>938</v>
+        <v>1181</v>
       </c>
       <c r="F623" s="3" t="s">
         <v>480</v>
       </c>
       <c r="G623" s="9">
-        <v>46342.0</v>
+        <v>46343.0</v>
       </c>
       <c r="H623" s="2"/>
     </row>
@@ -18117,28 +18132,28 @@
         <v>1182</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D624" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1183</v>
+        <v>632</v>
       </c>
       <c r="F624" s="3" t="s">
-        <v>480</v>
+        <v>992</v>
       </c>
       <c r="G624" s="9">
-        <v>46343.0</v>
+        <v>46228.0</v>
       </c>
       <c r="H624" s="2"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>521</v>
@@ -18147,22 +18162,22 @@
         <v>12</v>
       </c>
       <c r="D625" s="2">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>632</v>
+        <v>559</v>
       </c>
       <c r="F625" s="3" t="s">
-        <v>992</v>
+        <v>1083</v>
       </c>
       <c r="G625" s="9">
-        <v>46228.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H625" s="2"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>521</v>
@@ -18174,7 +18189,7 @@
         <v>7.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>559</v>
+        <v>802</v>
       </c>
       <c r="F626" s="3" t="s">
         <v>1083</v>
@@ -18186,7 +18201,7 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>521</v>
@@ -18198,7 +18213,7 @@
         <v>7.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>802</v>
+        <v>564</v>
       </c>
       <c r="F627" s="3" t="s">
         <v>1083</v>
@@ -18210,7 +18225,7 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>521</v>
@@ -18219,22 +18234,20 @@
         <v>12</v>
       </c>
       <c r="D628" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>564</v>
+        <v>870</v>
       </c>
       <c r="F628" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G628" s="9">
-        <v>46290.0</v>
-      </c>
+        <v>1001</v>
+      </c>
+      <c r="G628" s="9"/>
       <c r="H628" s="2"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>521</v>
@@ -18243,16 +18256,104 @@
         <v>12</v>
       </c>
       <c r="D629" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="F629" s="3" t="s">
-        <v>1001</v>
+        <v>1188</v>
+      </c>
+      <c r="F629" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G629" s="9"/>
       <c r="H629" s="2"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D630" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E630" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F630" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G630" s="9"/>
+      <c r="H630" s="2"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D631" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E631" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F631" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G631" s="9"/>
+      <c r="H631" s="2"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D632" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E632" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F632" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G632" s="9"/>
+      <c r="H632" s="2"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D633" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E633" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F633" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G633" s="9"/>
+      <c r="H633" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="1203">
   <si>
     <t>ID</t>
   </si>
@@ -448,7 +448,7 @@
     <t>ID3983541495190</t>
   </si>
   <si>
-    <t>ACRER-TY-280-320  (牛肉)(切)</t>
+    <t>ACRER-280-320-TY  (牛肉)(切)</t>
   </si>
   <si>
     <t>1150310S</t>
@@ -1744,7 +1744,7 @@
     <t>1150414K</t>
   </si>
   <si>
-    <t>PRCER-GO-十字切</t>
+    <t>PRCER-十字切-GO</t>
   </si>
   <si>
     <t>1150409S</t>
@@ -1849,10 +1849,7 @@
     <t>26#34</t>
   </si>
   <si>
-    <t>無庫位</t>
-  </si>
-  <si>
-    <t>34B(34-36)</t>
+    <t>34B (34-36)</t>
   </si>
   <si>
     <t>JUJM(退貨)</t>
@@ -2011,7 +2008,7 @@
     <t>ID1776918100016</t>
   </si>
   <si>
-    <t>M89SRL-KR (牛肉)</t>
+    <t>M89SRL-KR</t>
   </si>
   <si>
     <t>ID1776918492764</t>
@@ -2047,7 +2044,7 @@
     <t>ID1777281985428</t>
   </si>
   <si>
-    <t>PRSRM-SS-對切</t>
+    <t>PRSRM-對切-SS</t>
   </si>
   <si>
     <t>ID1777286256898</t>
@@ -2263,25 +2260,25 @@
     <t>ID1778229996243</t>
   </si>
   <si>
-    <t>ACSRMB-TY-2.5cm</t>
+    <t>ACSRMB-2.5cm-TY</t>
   </si>
   <si>
     <t>ID1778230020559</t>
   </si>
   <si>
-    <t>ACSRMB-TY-對切</t>
+    <t>ACSRMB-對切-TY</t>
   </si>
   <si>
     <t>ID1778230078956</t>
   </si>
   <si>
-    <t>PRSRMB-GO-2.5cm</t>
+    <t>PRSRMB-2.5cm-GO</t>
   </si>
   <si>
     <t>ID1778230144397</t>
   </si>
   <si>
-    <t>CHSRMB-YK-2.5cm</t>
+    <t>CHSRMB-2.5cm-YK</t>
   </si>
   <si>
     <t>ID1778230200332</t>
@@ -2419,9 +2416,6 @@
     <t>ID1778559275364</t>
   </si>
   <si>
-    <t>PRCER-十字切-GO</t>
-  </si>
-  <si>
     <t>ID1778559302299</t>
   </si>
   <si>
@@ -2665,12 +2659,6 @@
     <t>油角（報廢）</t>
   </si>
   <si>
-    <t>ID1779255881570</t>
-  </si>
-  <si>
-    <t>斑泊EP335(寄庫）</t>
-  </si>
-  <si>
     <t>ID1779255983117</t>
   </si>
   <si>
@@ -3266,9 +3254,6 @@
   </si>
   <si>
     <t>ID1780473214746</t>
-  </si>
-  <si>
-    <t>M9TDL-KR(預定）</t>
   </si>
   <si>
     <t>1140627K</t>
@@ -11182,25 +11167,26 @@
     </row>
     <row r="313">
       <c r="A313" s="1">
-        <v>1.776149087494E12</v>
+        <v>1.776169705463E12</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D313" s="2">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>612</v>
+        <v>518</v>
       </c>
       <c r="F313" s="4"/>
+      <c r="H313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" s="1">
-        <v>1.776169705463E12</v>
+        <v>1.776301247869E12</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>112</v>
@@ -11209,17 +11195,20 @@
         <v>12</v>
       </c>
       <c r="D314" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>518</v>
+        <v>612</v>
       </c>
       <c r="F314" s="4"/>
+      <c r="G314" s="9">
+        <v>46840.0</v>
+      </c>
       <c r="H314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" s="1">
-        <v>1.776301247869E12</v>
+        <v>1.776301425645E12</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>112</v>
@@ -11228,20 +11217,21 @@
         <v>12</v>
       </c>
       <c r="D315" s="2">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="F315" s="4"/>
+      <c r="F315" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="G315" s="9">
-        <v>46840.0</v>
-      </c>
-      <c r="H315" s="2"/>
+        <v>46640.0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1">
-        <v>1.776301425645E12</v>
+        <v>1.776327582548E12</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>112</v>
@@ -11250,41 +11240,41 @@
         <v>12</v>
       </c>
       <c r="D316" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="F316" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G316" s="9">
-        <v>46640.0</v>
+      <c r="F316" s="3">
+        <v>11504.0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1">
-        <v>1.776327582548E12</v>
+        <v>1.776327623153E12</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D317" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E317" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F317" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="F317" s="3">
-        <v>11504.0</v>
+      <c r="G317" s="9">
+        <v>46949.0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1">
-        <v>1.776327623153E12</v>
+        <v>1.776327677276E12</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>112</v>
@@ -11293,7 +11283,7 @@
         <v>34</v>
       </c>
       <c r="D318" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>575</v>
@@ -11307,30 +11297,28 @@
     </row>
     <row r="319">
       <c r="A319" s="1">
-        <v>1.776327677276E12</v>
+        <v>1.776328486516E12</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D319" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>575</v>
+        <v>617</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="G319" s="9">
-        <v>46949.0</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="H319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" s="1">
-        <v>1.776328486516E12</v>
+        <v>1.776328499394E12</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>112</v>
@@ -11339,7 +11327,7 @@
         <v>26</v>
       </c>
       <c r="D320" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>618</v>
@@ -11347,11 +11335,10 @@
       <c r="F320" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" s="1">
-        <v>1.776328499394E12</v>
+        <v>1.776328514002E12</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>112</v>
@@ -11360,7 +11347,7 @@
         <v>26</v>
       </c>
       <c r="D321" s="2">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>619</v>
@@ -11371,7 +11358,7 @@
     </row>
     <row r="322">
       <c r="A322" s="1">
-        <v>1.776328514002E12</v>
+        <v>1.776334155137E12</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>112</v>
@@ -11380,18 +11367,21 @@
         <v>26</v>
       </c>
       <c r="D322" s="2">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>620</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>409</v>
+        <v>231</v>
+      </c>
+      <c r="G322" s="9">
+        <v>46537.0</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1">
-        <v>1.776334155137E12</v>
+        <v>1.776334203307E12</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>112</v>
@@ -11403,18 +11393,18 @@
         <v>13.0</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>621</v>
+        <v>528</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>231</v>
+        <v>464</v>
       </c>
       <c r="G323" s="9">
-        <v>46537.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1">
-        <v>1.776334203307E12</v>
+        <v>1.776334423117E12</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>112</v>
@@ -11423,27 +11413,27 @@
         <v>26</v>
       </c>
       <c r="D324" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>528</v>
+        <v>621</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>464</v>
+        <v>231</v>
       </c>
       <c r="G324" s="9">
-        <v>46530.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1">
-        <v>1.776334423117E12</v>
+        <v>1.776334444257E12</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D325" s="2">
         <v>16.0</v>
@@ -11452,21 +11442,21 @@
         <v>622</v>
       </c>
       <c r="F325" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G325" s="9">
-        <v>46479.0</v>
+        <v>46468.0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1">
-        <v>1.776334444257E12</v>
+        <v>1.776334474615E12</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D326" s="2">
         <v>16.0</v>
@@ -11483,7 +11473,7 @@
     </row>
     <row r="327">
       <c r="A327" s="1">
-        <v>1.776334474615E12</v>
+        <v>1.776334496105E12</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>112</v>
@@ -11497,16 +11487,11 @@
       <c r="E327" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="F327" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G327" s="9">
-        <v>46468.0</v>
-      </c>
+      <c r="F327" s="4"/>
     </row>
     <row r="328">
       <c r="A328" s="1">
-        <v>1.776334496105E12</v>
+        <v>1.776334545035E12</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>112</v>
@@ -11520,34 +11505,39 @@
       <c r="E328" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="F328" s="4"/>
+      <c r="F328" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G328" s="9">
+        <v>46468.0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1">
-        <v>1.776334545035E12</v>
+        <v>1.776398987942E12</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D329" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>626</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>234</v>
+        <v>573</v>
       </c>
       <c r="G329" s="9">
-        <v>46468.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1">
-        <v>1.776398987942E12</v>
+        <v>1.776399071673E12</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>112</v>
@@ -11565,18 +11555,18 @@
         <v>573</v>
       </c>
       <c r="G330" s="9">
-        <v>46947.0</v>
+        <v>46771.0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1">
-        <v>1.776399071673E12</v>
+        <v>1.776399111607E12</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D331" s="2">
         <v>17.0</v>
@@ -11585,64 +11575,64 @@
         <v>628</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>573</v>
+        <v>478</v>
       </c>
       <c r="G331" s="9">
-        <v>46771.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1">
-        <v>1.776399111607E12</v>
+        <v>1.776399379582E12</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D332" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>629</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>478</v>
+        <v>630</v>
       </c>
       <c r="G332" s="9">
-        <v>46794.0</v>
+        <v>46691.0</v>
+      </c>
+      <c r="H332" s="2" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1">
-        <v>1.776399379582E12</v>
+        <v>1.776400103874E12</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D333" s="2">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>631</v>
+        <v>143</v>
       </c>
       <c r="G333" s="9">
-        <v>46691.0</v>
-      </c>
-      <c r="H333" s="2" t="s">
-        <v>632</v>
+        <v>46543.0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1">
-        <v>1.776400103874E12</v>
+        <v>1.776400120665E12</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>112</v>
@@ -11651,21 +11641,21 @@
         <v>26</v>
       </c>
       <c r="D334" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>633</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>143</v>
+        <v>231</v>
       </c>
       <c r="G334" s="9">
-        <v>46543.0</v>
+        <v>46479.0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1">
-        <v>1.776400120665E12</v>
+        <v>1.77640716912E12</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>112</v>
@@ -11674,21 +11664,21 @@
         <v>26</v>
       </c>
       <c r="D335" s="2">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="F335" s="3" t="s">
-        <v>231</v>
+        <v>540</v>
+      </c>
+      <c r="F335" s="3">
+        <v>11503.0</v>
       </c>
       <c r="G335" s="9">
-        <v>46479.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1">
-        <v>1.77640716912E12</v>
+        <v>1.776407375241E12</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>112</v>
@@ -11697,21 +11687,21 @@
         <v>26</v>
       </c>
       <c r="D336" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F336" s="3">
-        <v>11503.0</v>
+        <v>632</v>
+      </c>
+      <c r="F336" s="3" t="s">
+        <v>634</v>
       </c>
       <c r="G336" s="9">
-        <v>46516.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1">
-        <v>1.776407375241E12</v>
+        <v>1.77640744785E12</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>112</v>
@@ -11720,7 +11710,7 @@
         <v>26</v>
       </c>
       <c r="D337" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>633</v>
@@ -11729,97 +11719,97 @@
         <v>635</v>
       </c>
       <c r="G337" s="9">
-        <v>46669.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1">
-        <v>1.77640744785E12</v>
+        <v>1.776407858481E12</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D338" s="2">
         <v>12.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="F338" s="3" t="s">
         <v>636</v>
       </c>
+      <c r="F338" s="4"/>
       <c r="G338" s="9">
         <v>46523.0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1">
-        <v>1.776407858481E12</v>
+        <v>1.776436049209E12</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>33</v>
+        <v>521</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D339" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>637</v>
+        <v>49</v>
       </c>
       <c r="F339" s="4"/>
-      <c r="G339" s="9">
-        <v>46523.0</v>
-      </c>
     </row>
     <row r="340">
       <c r="A340" s="1">
-        <v>1.776436049209E12</v>
+        <v>1.776659068274E12</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>521</v>
+        <v>112</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D340" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F340" s="4"/>
+        <v>637</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="G340" s="9">
+        <v>46793.0</v>
+      </c>
     </row>
     <row r="341">
-      <c r="A341" s="1">
-        <v>1.776659068274E12</v>
+      <c r="A341" s="2" t="s">
+        <v>639</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D341" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>638</v>
+        <v>66</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G341" s="9">
-        <v>46793.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>112</v>
@@ -11828,67 +11818,62 @@
         <v>34</v>
       </c>
       <c r="D342" s="2">
-        <v>9.0</v>
+        <v>20.0</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>66</v>
+        <v>642</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G342" s="9">
-        <v>46949.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D343" s="2">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="G343" s="9">
-        <v>46793.0</v>
+        <v>46639.0</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D344" s="2">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F344" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="G344" s="9">
-        <v>46639.0</v>
-      </c>
+        <v>647</v>
+      </c>
+      <c r="F344" s="4"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>11</v>
@@ -11897,34 +11882,34 @@
         <v>28</v>
       </c>
       <c r="D345" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F345" s="4"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D346" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F346" s="4"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>11</v>
@@ -11936,7 +11921,7 @@
         <v>5.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F347" s="4"/>
     </row>
@@ -11948,13 +11933,13 @@
         <v>11</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D348" s="2">
         <v>5.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F348" s="4"/>
     </row>
@@ -11966,13 +11951,13 @@
         <v>11</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D349" s="2">
         <v>5.0</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F349" s="4"/>
     </row>
@@ -11984,37 +11969,39 @@
         <v>11</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D350" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F350" s="4"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D351" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F351" s="4"/>
+        <v>658</v>
+      </c>
+      <c r="F351" s="3" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>33</v>
@@ -12026,15 +12013,18 @@
         <v>2.0</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>285</v>
+        <v>338</v>
+      </c>
+      <c r="G352" s="9">
+        <v>46488.0</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>33</v>
@@ -12046,18 +12036,15 @@
         <v>2.0</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G353" s="9">
-        <v>46488.0</v>
+        <v>663</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>33</v>
@@ -12066,42 +12053,45 @@
         <v>26</v>
       </c>
       <c r="D354" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>664</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="G354" s="9">
+        <v>46716.0</v>
+      </c>
+      <c r="H354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D355" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F355" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G355" s="9">
-        <v>46716.0</v>
-      </c>
-      <c r="H355" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="F355" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="H355" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>112</v>
@@ -12110,87 +12100,87 @@
         <v>12</v>
       </c>
       <c r="D356" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F356" s="3">
         <v>11504.0</v>
       </c>
-      <c r="H356" s="2" t="s">
-        <v>386</v>
-      </c>
+      <c r="H356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D357" s="2">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F357" s="3">
-        <v>11504.0</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="F357" s="4"/>
       <c r="H357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D358" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F358" s="4"/>
-      <c r="H358" s="2"/>
+        <v>673</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="G358" s="9">
+        <v>46240.0</v>
+      </c>
+      <c r="H358" s="2" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D359" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>675</v>
+        <v>643</v>
       </c>
       <c r="G359" s="9">
-        <v>46240.0</v>
-      </c>
-      <c r="H359" s="2" t="s">
-        <v>676</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>112</v>
@@ -12199,44 +12189,45 @@
         <v>12</v>
       </c>
       <c r="D360" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>644</v>
+        <v>680</v>
       </c>
       <c r="G360" s="9">
-        <v>46416.0</v>
+        <v>46544.0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D361" s="2">
         <v>16.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="G361" s="9">
-        <v>46544.0</v>
-      </c>
+        <v>46794.0</v>
+      </c>
+      <c r="H361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>112</v>
@@ -12248,19 +12239,18 @@
         <v>16.0</v>
       </c>
       <c r="E362" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F362" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="F362" s="3" t="s">
-        <v>684</v>
-      </c>
       <c r="G362" s="9">
-        <v>46794.0</v>
-      </c>
-      <c r="H362" s="2"/>
+        <v>46785.0</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>112</v>
@@ -12272,13 +12262,13 @@
         <v>16.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>686</v>
+        <v>568</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G363" s="9">
-        <v>46785.0</v>
+        <v>46789.0</v>
       </c>
     </row>
     <row r="364">
@@ -12295,41 +12285,44 @@
         <v>16.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>568</v>
+        <v>688</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G364" s="9">
-        <v>46789.0</v>
+        <v>46839.0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D365" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G365" s="9">
-        <v>46839.0</v>
+        <v>46312.0</v>
+      </c>
+      <c r="H365" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>112</v>
@@ -12338,48 +12331,45 @@
         <v>12</v>
       </c>
       <c r="D366" s="2">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>691</v>
+        <v>626</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G366" s="9">
-        <v>46312.0</v>
-      </c>
-      <c r="H366" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>46669.0</v>
+      </c>
+      <c r="H366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D367" s="2">
-        <v>17.0</v>
+        <v>7.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>627</v>
+        <v>695</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="G367" s="9">
-        <v>46669.0</v>
-      </c>
-      <c r="H367" s="2"/>
+        <v>46794.0</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>112</v>
@@ -12391,41 +12381,39 @@
         <v>7.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>684</v>
+        <v>698</v>
       </c>
       <c r="G368" s="9">
-        <v>46794.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D369" s="2">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="F369" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="G369" s="9">
-        <v>46792.0</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="F369" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="H369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>112</v>
@@ -12434,179 +12422,178 @@
         <v>12</v>
       </c>
       <c r="D370" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F370" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="H370" s="2"/>
+        <v>115004.0</v>
+      </c>
+      <c r="H370" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D371" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F371" s="3">
-        <v>115004.0</v>
-      </c>
-      <c r="H371" s="2" t="s">
-        <v>181</v>
+        <v>11505.0</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D372" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="F372" s="3">
-        <v>11505.0</v>
+        <v>706</v>
+      </c>
+      <c r="F372" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G372" s="9">
+        <v>46162.0</v>
+      </c>
+      <c r="H372" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I372" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D373" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F373" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G373" s="9">
-        <v>46162.0</v>
-      </c>
-      <c r="H373" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I373" s="2" t="s">
-        <v>223</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="F373" s="4"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D374" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="F374" s="4"/>
+        <v>710</v>
+      </c>
+      <c r="F374" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G374" s="9">
+        <v>46152.0</v>
+      </c>
+      <c r="H374" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I374" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D375" s="2">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>319</v>
+        <v>635</v>
       </c>
       <c r="G375" s="9">
-        <v>46152.0</v>
-      </c>
-      <c r="H375" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I375" s="2" t="s">
-        <v>223</v>
+        <v>46596.0</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D376" s="2">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>636</v>
+        <v>715</v>
       </c>
       <c r="G376" s="9">
-        <v>46596.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C377" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D377" s="2">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>715</v>
+        <v>619</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="G377" s="9">
-        <v>46669.0</v>
+        <v>399</v>
       </c>
     </row>
     <row r="378">
@@ -12620,18 +12607,18 @@
         <v>26</v>
       </c>
       <c r="D378" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>620</v>
+        <v>718</v>
       </c>
       <c r="F378" s="3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>33</v>
@@ -12639,114 +12626,114 @@
       <c r="C379" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D379" s="2">
-        <v>10.0</v>
-      </c>
       <c r="E379" s="2" t="s">
-        <v>719</v>
+        <v>545</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>409</v>
+        <v>720</v>
+      </c>
+      <c r="G379" s="9">
+        <v>46410.0</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D380" s="2">
+        <v>22.0</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>545</v>
+        <v>722</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G380" s="9">
-        <v>46410.0</v>
+        <v>46194.0</v>
+      </c>
+      <c r="H380" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="I380" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D381" s="2">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="G381" s="9">
-        <v>46194.0</v>
-      </c>
-      <c r="H381" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="I381" s="2" t="s">
-        <v>223</v>
+        <v>46257.0</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D382" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>727</v>
+        <v>571</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G382" s="9">
-        <v>46257.0</v>
+        <v>46913.0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D383" s="2">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>571</v>
+        <v>731</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="G383" s="9">
-        <v>46913.0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>11</v>
@@ -12758,7 +12745,7 @@
         <v>2.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>732</v>
+        <v>16</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>218</v>
@@ -12778,10 +12765,10 @@
         <v>2.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>16</v>
+        <v>731</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>218</v>
+        <v>17</v>
       </c>
     </row>
     <row r="386">
@@ -12792,21 +12779,24 @@
         <v>11</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D386" s="2">
         <v>2.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="G386" s="9">
+        <v>46843.0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>11</v>
@@ -12815,42 +12805,42 @@
         <v>26</v>
       </c>
       <c r="D387" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F387" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="F387" s="4"/>
       <c r="G387" s="9">
-        <v>46843.0</v>
+        <v>46642.0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D388" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F388" s="4"/>
+        <v>739</v>
+      </c>
+      <c r="F388" s="3" t="s">
+        <v>740</v>
+      </c>
       <c r="G388" s="9">
-        <v>46642.0</v>
+        <v>46507.0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>33</v>
@@ -12862,109 +12852,109 @@
         <v>4.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G389" s="9">
-        <v>46507.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D390" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F390" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="G390" s="9">
-        <v>46484.0</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="F390" s="3">
+        <v>11505.0</v>
+      </c>
+      <c r="H390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
         <v>744</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D391" s="2">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F391" s="3">
-        <v>11505.0</v>
-      </c>
-      <c r="H391" s="2"/>
+        <v>682</v>
+      </c>
+      <c r="F391" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
         <v>745</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D392" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>683</v>
+        <v>746</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>57</v>
+        <v>263</v>
+      </c>
+      <c r="G392" s="9">
+        <v>46361.0</v>
+      </c>
+      <c r="H392" s="2"/>
+      <c r="J392" s="2" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D393" s="2">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>263</v>
+        <v>578</v>
       </c>
       <c r="G393" s="9">
-        <v>46361.0</v>
-      </c>
-      <c r="H393" s="2"/>
-      <c r="J393" s="2" t="s">
-        <v>748</v>
+        <v>46408.0</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>112</v>
@@ -12976,18 +12966,18 @@
         <v>17.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>578</v>
       </c>
       <c r="G394" s="9">
-        <v>46408.0</v>
+        <v>46473.0</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>112</v>
@@ -12999,18 +12989,18 @@
         <v>17.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>578</v>
       </c>
       <c r="G395" s="9">
-        <v>46473.0</v>
+        <v>46758.0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>112</v>
@@ -13022,18 +13012,18 @@
         <v>17.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>578</v>
       </c>
       <c r="G396" s="9">
-        <v>46758.0</v>
+        <v>46431.0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>112</v>
@@ -13042,56 +13032,53 @@
         <v>26</v>
       </c>
       <c r="D397" s="2">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>578</v>
+        <v>758</v>
       </c>
       <c r="G397" s="9">
-        <v>46431.0</v>
+        <v>46523.0</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D398" s="2">
-        <v>14.0</v>
+        <v>22.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="G398" s="9">
-        <v>46523.0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D399" s="2">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>218</v>
@@ -13099,19 +13086,19 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D400" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>218</v>
@@ -13119,7 +13106,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>33</v>
@@ -13128,10 +13115,10 @@
         <v>28</v>
       </c>
       <c r="D401" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>218</v>
@@ -13139,50 +13126,53 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D402" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>218</v>
+        <v>234</v>
+      </c>
+      <c r="G402" s="9">
+        <v>46281.0</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C403" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D403" s="2">
-        <v>14.0</v>
+        <v>10.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G403" s="9">
-        <v>46281.0</v>
+        <v>478</v>
+      </c>
+      <c r="H403" s="2" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>33</v>
@@ -13191,21 +13181,21 @@
         <v>12</v>
       </c>
       <c r="D404" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="H404" s="2" t="s">
-        <v>772</v>
+      <c r="G404" s="9">
+        <v>47146.0</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>33</v>
@@ -13214,67 +13204,67 @@
         <v>12</v>
       </c>
       <c r="D405" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="G405" s="9">
-        <v>47146.0</v>
+      <c r="H405" s="2" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D406" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F406" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="H406" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
+      </c>
+      <c r="G406" s="9">
+        <v>46666.0</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C407" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D407" s="2">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G407" s="9">
-        <v>46666.0</v>
+        <v>46604.0</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>33</v>
@@ -13286,13 +13276,13 @@
         <v>8.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>782</v>
+        <v>110</v>
       </c>
       <c r="G408" s="9">
-        <v>46604.0</v>
+        <v>46626.0</v>
       </c>
     </row>
     <row r="409">
@@ -13309,18 +13299,18 @@
         <v>8.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>110</v>
+        <v>784</v>
       </c>
       <c r="G409" s="9">
-        <v>46626.0</v>
+        <v>46658.0</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>33</v>
@@ -13332,59 +13322,56 @@
         <v>8.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G410" s="9">
-        <v>46658.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D411" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F411" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="G411" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>788</v>
+      </c>
+      <c r="F411" s="4"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D412" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F412" s="4"/>
+        <v>790</v>
+      </c>
+      <c r="F412" s="3" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>33</v>
@@ -13393,18 +13380,21 @@
         <v>12</v>
       </c>
       <c r="D413" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>478</v>
+        <v>793</v>
+      </c>
+      <c r="G413" s="9">
+        <v>46304.0</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>33</v>
@@ -13413,16 +13403,16 @@
         <v>12</v>
       </c>
       <c r="D414" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>793</v>
+        <v>566</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>794</v>
+        <v>53</v>
       </c>
       <c r="G414" s="9">
-        <v>46304.0</v>
+        <v>46416.0</v>
       </c>
     </row>
     <row r="415">
@@ -13436,21 +13426,21 @@
         <v>12</v>
       </c>
       <c r="D415" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>566</v>
+        <v>796</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>53</v>
+        <v>797</v>
       </c>
       <c r="G415" s="9">
-        <v>46416.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>33</v>
@@ -13459,39 +13449,39 @@
         <v>12</v>
       </c>
       <c r="D416" s="2">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F416" s="3" t="s">
-        <v>798</v>
+        <v>38</v>
       </c>
       <c r="G416" s="9">
-        <v>46877.0</v>
+        <v>46737.0</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D417" s="2">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>800</v>
+        <v>577</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>38</v>
+        <v>635</v>
       </c>
       <c r="G417" s="9">
-        <v>46737.0</v>
+        <v>46794.0</v>
       </c>
     </row>
     <row r="418">
@@ -13502,16 +13492,16 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D418" s="2">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>802</v>
+        <v>577</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G418" s="9">
         <v>46794.0</v>
@@ -13519,7 +13509,7 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>112</v>
@@ -13528,16 +13518,16 @@
         <v>26</v>
       </c>
       <c r="D419" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G419" s="9">
-        <v>46794.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="420">
@@ -13548,19 +13538,19 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D420" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E420" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F420" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="F420" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="G420" s="9">
-        <v>46484.0</v>
+        <v>46792.0</v>
       </c>
     </row>
     <row r="421">
@@ -13568,22 +13558,22 @@
         <v>806</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D421" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>698</v>
+        <v>807</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>807</v>
+        <v>563</v>
       </c>
       <c r="G421" s="9">
-        <v>46792.0</v>
+        <v>46676.0</v>
       </c>
     </row>
     <row r="422">
@@ -13600,32 +13590,32 @@
         <v>9.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="F422" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="G422" s="9">
-        <v>46676.0</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="F422" s="4"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D423" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E423" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B423" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D423" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="E423" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F423" s="4"/>
+      <c r="F423" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="G423" s="9">
+        <v>46641.0</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
@@ -13638,16 +13628,16 @@
         <v>12</v>
       </c>
       <c r="D424" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>812</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G424" s="9">
-        <v>46641.0</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="425">
@@ -13661,16 +13651,16 @@
         <v>12</v>
       </c>
       <c r="D425" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>814</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>681</v>
+        <v>635</v>
       </c>
       <c r="G425" s="9">
-        <v>46530.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="426">
@@ -13681,24 +13671,24 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D426" s="2">
-        <v>13.0</v>
+        <v>3.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>816</v>
+        <v>792</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>636</v>
+        <v>563</v>
       </c>
       <c r="G426" s="9">
-        <v>46949.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>112</v>
@@ -13710,18 +13700,18 @@
         <v>3.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F427" s="3" t="s">
-        <v>563</v>
+        <v>440</v>
       </c>
       <c r="G427" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>112</v>
@@ -13733,7 +13723,7 @@
         <v>3.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>440</v>
@@ -13744,10 +13734,10 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>26</v>
@@ -13756,18 +13746,18 @@
         <v>3.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>440</v>
+        <v>563</v>
       </c>
       <c r="G429" s="9">
-        <v>46752.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>33</v>
@@ -13779,18 +13769,18 @@
         <v>3.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>563</v>
+        <v>440</v>
       </c>
       <c r="G430" s="9">
-        <v>46670.0</v>
+        <v>46752.0</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>33</v>
@@ -13802,56 +13792,59 @@
         <v>3.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F431" s="3" t="s">
-        <v>440</v>
+        <v>47</v>
       </c>
       <c r="G431" s="9">
-        <v>46752.0</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D432" s="2">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>793</v>
+        <v>562</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G432" s="9">
-        <v>46366.0</v>
+        <v>640</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C433" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D433" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>641</v>
+        <v>823</v>
+      </c>
+      <c r="G433" s="9">
+        <v>46670.0</v>
+      </c>
+      <c r="H433" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="434">
@@ -13862,22 +13855,19 @@
         <v>33</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D434" s="2">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>557</v>
+        <v>825</v>
       </c>
       <c r="F434" s="3" t="s">
-        <v>825</v>
+        <v>95</v>
       </c>
       <c r="G434" s="9">
-        <v>46670.0</v>
-      </c>
-      <c r="H434" s="2" t="s">
-        <v>54</v>
+        <v>46725.0</v>
       </c>
     </row>
     <row r="435">
@@ -13885,22 +13875,22 @@
         <v>826</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D435" s="2">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>827</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="G435" s="9">
-        <v>46725.0</v>
+        <v>46793.0</v>
       </c>
     </row>
     <row r="436">
@@ -13920,38 +13910,39 @@
         <v>829</v>
       </c>
       <c r="F436" s="3" t="s">
-        <v>140</v>
+        <v>830</v>
       </c>
       <c r="G436" s="9">
-        <v>46793.0</v>
+        <v>46670.0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C437" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D437" s="2">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F437" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="G437" s="9">
-        <v>46670.0</v>
-      </c>
+        <v>46254.0</v>
+      </c>
+      <c r="H437" s="2"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>33</v>
@@ -13960,18 +13951,17 @@
         <v>12</v>
       </c>
       <c r="D438" s="2">
-        <v>17.0</v>
+        <v>11.0</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F438" s="3" t="s">
-        <v>835</v>
+        <v>394</v>
       </c>
       <c r="G438" s="9">
-        <v>46254.0</v>
-      </c>
-      <c r="H438" s="2"/>
+        <v>46669.0</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
@@ -13981,16 +13971,16 @@
         <v>33</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D439" s="2">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>837</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>394</v>
+        <v>838</v>
       </c>
       <c r="G439" s="9">
         <v>46669.0</v>
@@ -13998,7 +13988,7 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>33</v>
@@ -14010,10 +14000,10 @@
         <v>6.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G440" s="9">
         <v>46669.0</v>
@@ -14021,7 +14011,7 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>33</v>
@@ -14033,10 +14023,10 @@
         <v>6.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>843</v>
+        <v>778</v>
       </c>
       <c r="G441" s="9">
         <v>46669.0</v>
@@ -14044,7 +14034,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>33</v>
@@ -14056,10 +14046,10 @@
         <v>6.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>779</v>
+        <v>844</v>
       </c>
       <c r="G442" s="9">
         <v>46669.0</v>
@@ -14073,24 +14063,24 @@
         <v>33</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D443" s="2">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="G443" s="9">
-        <v>46669.0</v>
+        <v>46947.0</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>33</v>
@@ -14102,18 +14092,18 @@
         <v>18.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>848</v>
+        <v>584</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G444" s="9">
-        <v>46947.0</v>
+        <v>46949.0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>33</v>
@@ -14125,10 +14115,10 @@
         <v>18.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>584</v>
+        <v>66</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G445" s="9">
         <v>46949.0</v>
@@ -14136,7 +14126,7 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>33</v>
@@ -14148,18 +14138,15 @@
         <v>18.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>66</v>
+        <v>792</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="G446" s="9">
-        <v>46949.0</v>
+        <v>847</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>33</v>
@@ -14168,36 +14155,36 @@
         <v>28</v>
       </c>
       <c r="D447" s="2">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>849</v>
+        <v>45</v>
+      </c>
+      <c r="G447" s="9">
+        <v>46730.0</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D448" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E448" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="B448" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C448" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D448" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E448" s="2" t="s">
-        <v>793</v>
-      </c>
       <c r="F448" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G448" s="9">
-        <v>46730.0</v>
+        <v>338</v>
       </c>
     </row>
     <row r="449">
@@ -14208,36 +14195,39 @@
         <v>33</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D449" s="2">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>338</v>
+        <v>118</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D450" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E450" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="B450" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C450" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D450" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E450" s="2" t="s">
-        <v>855</v>
-      </c>
       <c r="F450" s="3" t="s">
-        <v>118</v>
+        <v>432</v>
+      </c>
+      <c r="G450" s="9">
+        <v>46267.0</v>
       </c>
     </row>
     <row r="451">
@@ -14248,19 +14238,19 @@
         <v>33</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D451" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>858</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>432</v>
+        <v>351</v>
       </c>
       <c r="G451" s="9">
-        <v>46267.0</v>
+        <v>46255.0</v>
       </c>
     </row>
     <row r="452">
@@ -14268,22 +14258,22 @@
         <v>859</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D452" s="2">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>860</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="G452" s="9">
-        <v>46255.0</v>
+        <v>46613.0</v>
       </c>
     </row>
     <row r="453">
@@ -14291,46 +14281,47 @@
         <v>861</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D453" s="2">
-        <v>20.0</v>
+        <v>13.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>862</v>
+        <v>588</v>
       </c>
       <c r="F453" s="3" t="s">
-        <v>458</v>
+        <v>589</v>
       </c>
       <c r="G453" s="9">
-        <v>46613.0</v>
+        <v>46669.0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C454" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D454" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E454" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="B454" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C454" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D454" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E454" s="2" t="s">
-        <v>588</v>
-      </c>
       <c r="F454" s="3" t="s">
-        <v>589</v>
+        <v>847</v>
       </c>
       <c r="G454" s="9">
-        <v>46669.0</v>
-      </c>
+        <v>46775.0</v>
+      </c>
+      <c r="H454" s="2"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
@@ -14340,21 +14331,15 @@
         <v>33</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D455" s="2">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="F455" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="G455" s="9">
-        <v>46775.0</v>
-      </c>
-      <c r="H455" s="2"/>
+      <c r="F455" s="4"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
@@ -14418,15 +14403,20 @@
         <v>33</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D459" s="2">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
       <c r="E459" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="F459" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="F459" s="4"/>
+      <c r="G459" s="9">
+        <v>46222.0</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
@@ -14436,20 +14426,15 @@
         <v>33</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D460" s="2">
-        <v>22.0</v>
+        <v>11.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="F460" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="G460" s="9">
-        <v>46222.0</v>
-      </c>
+      <c r="F460" s="4"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
@@ -14513,15 +14498,18 @@
         <v>33</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D464" s="2">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>883</v>
       </c>
       <c r="F464" s="4"/>
+      <c r="G464" s="9">
+        <v>46551.0</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
@@ -14541,7 +14529,7 @@
       </c>
       <c r="F465" s="4"/>
       <c r="G465" s="9">
-        <v>46564.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="466">
@@ -14555,14 +14543,14 @@
         <v>26</v>
       </c>
       <c r="D466" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>887</v>
       </c>
       <c r="F466" s="4"/>
       <c r="G466" s="9">
-        <v>46551.0</v>
+        <v>46436.0</v>
       </c>
     </row>
     <row r="467">
@@ -14576,14 +14564,14 @@
         <v>26</v>
       </c>
       <c r="D467" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>889</v>
       </c>
       <c r="F467" s="4"/>
       <c r="G467" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="468">
@@ -14604,7 +14592,7 @@
       </c>
       <c r="F468" s="4"/>
       <c r="G468" s="9">
-        <v>46436.0</v>
+        <v>46355.0</v>
       </c>
     </row>
     <row r="469">
@@ -14639,14 +14627,14 @@
         <v>26</v>
       </c>
       <c r="D470" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>895</v>
       </c>
       <c r="F470" s="4"/>
       <c r="G470" s="9">
-        <v>46355.0</v>
+        <v>46551.0</v>
       </c>
     </row>
     <row r="471">
@@ -14660,14 +14648,14 @@
         <v>26</v>
       </c>
       <c r="D471" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>897</v>
       </c>
       <c r="F471" s="4"/>
       <c r="G471" s="9">
-        <v>46355.0</v>
+        <v>46394.0</v>
       </c>
     </row>
     <row r="472">
@@ -14675,20 +14663,19 @@
         <v>898</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D472" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F472" s="4"/>
-      <c r="G472" s="9">
-        <v>46551.0</v>
+      <c r="F472" s="3" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="473">
@@ -14702,34 +14689,34 @@
         <v>26</v>
       </c>
       <c r="D473" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>901</v>
       </c>
       <c r="F473" s="4"/>
-      <c r="G473" s="9">
-        <v>46394.0</v>
-      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
         <v>902</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D474" s="2">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>903</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>409</v>
+      </c>
+      <c r="G474" s="9">
+        <v>46759.0</v>
       </c>
     </row>
     <row r="475">
@@ -14737,40 +14724,45 @@
         <v>904</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>33</v>
+        <v>521</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D475" s="2">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="F475" s="4"/>
+      <c r="F475" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G475" s="9">
+        <v>46406.0</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
         <v>906</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>33</v>
+        <v>521</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D476" s="2">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>907</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>409</v>
+        <v>38</v>
       </c>
       <c r="G476" s="9">
-        <v>46759.0</v>
+        <v>46406.0</v>
       </c>
     </row>
     <row r="477">
@@ -14833,10 +14825,10 @@
         <v>3.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>38</v>
+        <v>399</v>
       </c>
       <c r="G479" s="9">
         <v>46406.0</v>
@@ -14844,7 +14836,7 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>521</v>
@@ -14856,18 +14848,18 @@
         <v>3.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G480" s="9">
-        <v>46406.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>521</v>
@@ -14876,16 +14868,16 @@
         <v>12</v>
       </c>
       <c r="D481" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>399</v>
+        <v>38</v>
       </c>
       <c r="G481" s="9">
-        <v>46406.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="482">
@@ -14899,7 +14891,7 @@
         <v>12</v>
       </c>
       <c r="D482" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>918</v>
@@ -14908,7 +14900,7 @@
         <v>38</v>
       </c>
       <c r="G482" s="9">
-        <v>46251.0</v>
+        <v>46387.0</v>
       </c>
     </row>
     <row r="483">
@@ -14968,7 +14960,7 @@
         <v>12</v>
       </c>
       <c r="D485" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>924</v>
@@ -14977,7 +14969,7 @@
         <v>38</v>
       </c>
       <c r="G485" s="9">
-        <v>46387.0</v>
+        <v>46251.0</v>
       </c>
     </row>
     <row r="486">
@@ -14991,7 +14983,7 @@
         <v>12</v>
       </c>
       <c r="D486" s="2">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>926</v>
@@ -15000,7 +14992,7 @@
         <v>38</v>
       </c>
       <c r="G486" s="9">
-        <v>46387.0</v>
+        <v>46280.0</v>
       </c>
     </row>
     <row r="487">
@@ -15023,7 +15015,7 @@
         <v>38</v>
       </c>
       <c r="G487" s="9">
-        <v>46251.0</v>
+        <v>46234.0</v>
       </c>
     </row>
     <row r="488">
@@ -15046,7 +15038,7 @@
         <v>38</v>
       </c>
       <c r="G488" s="9">
-        <v>46280.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="489">
@@ -15069,7 +15061,7 @@
         <v>38</v>
       </c>
       <c r="G489" s="9">
-        <v>46234.0</v>
+        <v>46256.0</v>
       </c>
     </row>
     <row r="490">
@@ -15092,7 +15084,7 @@
         <v>38</v>
       </c>
       <c r="G490" s="9">
-        <v>46256.0</v>
+        <v>46249.0</v>
       </c>
     </row>
     <row r="491">
@@ -15106,16 +15098,16 @@
         <v>12</v>
       </c>
       <c r="D491" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>936</v>
       </c>
       <c r="F491" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G491" s="9">
-        <v>46256.0</v>
+        <v>46352.0</v>
       </c>
     </row>
     <row r="492">
@@ -15129,16 +15121,16 @@
         <v>12</v>
       </c>
       <c r="D492" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>938</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G492" s="9">
-        <v>46249.0</v>
+        <v>46333.0</v>
       </c>
     </row>
     <row r="493">
@@ -15161,7 +15153,7 @@
         <v>17</v>
       </c>
       <c r="G493" s="9">
-        <v>46352.0</v>
+        <v>46244.0</v>
       </c>
     </row>
     <row r="494">
@@ -15175,7 +15167,7 @@
         <v>12</v>
       </c>
       <c r="D494" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>942</v>
@@ -15184,7 +15176,7 @@
         <v>17</v>
       </c>
       <c r="G494" s="9">
-        <v>46333.0</v>
+        <v>46226.0</v>
       </c>
     </row>
     <row r="495">
@@ -15198,7 +15190,7 @@
         <v>12</v>
       </c>
       <c r="D495" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>944</v>
@@ -15207,7 +15199,7 @@
         <v>17</v>
       </c>
       <c r="G495" s="9">
-        <v>46244.0</v>
+        <v>46222.0</v>
       </c>
     </row>
     <row r="496">
@@ -15230,7 +15222,7 @@
         <v>17</v>
       </c>
       <c r="G496" s="9">
-        <v>46226.0</v>
+        <v>46241.0</v>
       </c>
     </row>
     <row r="497">
@@ -15253,7 +15245,7 @@
         <v>17</v>
       </c>
       <c r="G497" s="9">
-        <v>46222.0</v>
+        <v>46305.0</v>
       </c>
     </row>
     <row r="498">
@@ -15267,16 +15259,16 @@
         <v>12</v>
       </c>
       <c r="D498" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>950</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>17</v>
+        <v>478</v>
       </c>
       <c r="G498" s="9">
-        <v>46241.0</v>
+        <v>46365.0</v>
       </c>
     </row>
     <row r="499">
@@ -15290,17 +15282,18 @@
         <v>12</v>
       </c>
       <c r="D499" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>952</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="G499" s="9">
-        <v>46305.0</v>
-      </c>
+        <v>46392.0</v>
+      </c>
+      <c r="H499" s="2"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
@@ -15313,21 +15306,24 @@
         <v>12</v>
       </c>
       <c r="D500" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>954</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>478</v>
+        <v>399</v>
       </c>
       <c r="G500" s="9">
-        <v>46365.0</v>
+        <v>46211.0</v>
+      </c>
+      <c r="H500" s="2" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>521</v>
@@ -15339,19 +15335,24 @@
         <v>12.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F501" s="3" t="s">
-        <v>38</v>
+        <v>399</v>
       </c>
       <c r="G501" s="9">
-        <v>46392.0</v>
-      </c>
-      <c r="H501" s="2"/>
+        <v>46204.0</v>
+      </c>
+      <c r="H501" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="I501" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>521</v>
@@ -15363,16 +15364,13 @@
         <v>12.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="G502" s="9">
-        <v>46211.0</v>
-      </c>
-      <c r="H502" s="2" t="s">
-        <v>959</v>
+        <v>46345.0</v>
       </c>
     </row>
     <row r="503">
@@ -15386,22 +15384,16 @@
         <v>12</v>
       </c>
       <c r="D503" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>961</v>
       </c>
       <c r="F503" s="3" t="s">
-        <v>399</v>
+        <v>478</v>
       </c>
       <c r="G503" s="9">
-        <v>46204.0</v>
-      </c>
-      <c r="H503" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="I503" s="2" t="s">
-        <v>223</v>
+        <v>46366.0</v>
       </c>
     </row>
     <row r="504">
@@ -15415,16 +15407,14 @@
         <v>12</v>
       </c>
       <c r="D504" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="F504" s="3" t="s">
-        <v>377</v>
-      </c>
+      <c r="F504" s="4"/>
       <c r="G504" s="9">
-        <v>46345.0</v>
+        <v>46220.0</v>
       </c>
     </row>
     <row r="505">
@@ -15432,22 +15422,22 @@
         <v>964</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D505" s="2">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>965</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>478</v>
+        <v>406</v>
       </c>
       <c r="G505" s="9">
-        <v>46366.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="506">
@@ -15455,20 +15445,22 @@
         <v>966</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D506" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="F506" s="4"/>
+      <c r="F506" s="3" t="s">
+        <v>406</v>
+      </c>
       <c r="G506" s="9">
-        <v>46220.0</v>
+        <v>46228.0</v>
       </c>
     </row>
     <row r="507">
@@ -15482,16 +15474,16 @@
         <v>12</v>
       </c>
       <c r="D507" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>969</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>406</v>
+        <v>607</v>
       </c>
       <c r="G507" s="9">
-        <v>46223.0</v>
+        <v>46242.0</v>
       </c>
     </row>
     <row r="508">
@@ -15505,44 +15497,45 @@
         <v>12</v>
       </c>
       <c r="D508" s="2">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>971</v>
       </c>
       <c r="F508" s="3" t="s">
-        <v>406</v>
+        <v>972</v>
       </c>
       <c r="G508" s="9">
-        <v>46228.0</v>
-      </c>
+        <v>46274.0</v>
+      </c>
+      <c r="H508" s="2"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D509" s="2">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F509" s="3" t="s">
-        <v>607</v>
+        <v>975</v>
       </c>
       <c r="G509" s="9">
-        <v>46242.0</v>
+        <v>46743.0</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>519</v>
@@ -15551,133 +15544,132 @@
         <v>12</v>
       </c>
       <c r="D510" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="F510" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="G510" s="9">
-        <v>46274.0</v>
-      </c>
-      <c r="H510" s="2"/>
+        <v>46215.0</v>
+      </c>
+      <c r="H510" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="I510" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D511" s="2">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="F511" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="G511" s="9">
-        <v>46743.0</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="F511" s="4"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
         <v>980</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D512" s="2">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>981</v>
       </c>
       <c r="F512" s="3" t="s">
-        <v>982</v>
+        <v>226</v>
       </c>
       <c r="G512" s="9">
-        <v>46215.0</v>
-      </c>
-      <c r="H512" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="I512" s="2" t="s">
-        <v>223</v>
+        <v>46295.0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C513" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D513" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E513" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="B513" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C513" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D513" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E513" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F513" s="4"/>
+      <c r="F513" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="G513" s="9">
+        <v>46769.0</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
         <v>984</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D514" s="2">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>226</v>
+        <v>972</v>
       </c>
       <c r="G514" s="9">
-        <v>46295.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D515" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E515" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="B515" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C515" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D515" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E515" s="2" t="s">
+      <c r="F515" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="F515" s="3" t="s">
-        <v>976</v>
-      </c>
       <c r="G515" s="9">
-        <v>46769.0</v>
+        <v>46261.0</v>
       </c>
     </row>
     <row r="516">
@@ -15685,27 +15677,27 @@
         <v>988</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>33</v>
+        <v>519</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D516" s="2">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="F516" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="F516" s="3" t="s">
-        <v>976</v>
-      </c>
       <c r="G516" s="9">
-        <v>46769.0</v>
+        <v>46266.0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>519</v>
@@ -15717,13 +15709,13 @@
         <v>3.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F517" s="3" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G517" s="9">
-        <v>46261.0</v>
+        <v>46223.0</v>
       </c>
     </row>
     <row r="518">
@@ -15743,7 +15735,7 @@
         <v>993</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G518" s="9">
         <v>46266.0</v>
@@ -15754,7 +15746,7 @@
         <v>994</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>519</v>
+        <v>33</v>
       </c>
       <c r="C519" s="2" t="s">
         <v>12</v>
@@ -15766,10 +15758,10 @@
         <v>995</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>991</v>
+        <v>972</v>
       </c>
       <c r="G519" s="9">
-        <v>46223.0</v>
+        <v>46769.0</v>
       </c>
     </row>
     <row r="520">
@@ -15777,22 +15769,22 @@
         <v>996</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D520" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E520" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F520" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="F520" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="G520" s="9">
-        <v>46266.0</v>
+        <v>46814.0</v>
       </c>
     </row>
     <row r="521">
@@ -15800,22 +15792,22 @@
         <v>998</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D521" s="2">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>999</v>
       </c>
       <c r="F521" s="3" t="s">
-        <v>976</v>
+        <v>997</v>
       </c>
       <c r="G521" s="9">
-        <v>46769.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="522">
@@ -15832,18 +15824,18 @@
         <v>14.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G522" s="9">
-        <v>46814.0</v>
+        <v>46820.0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>112</v>
@@ -15855,64 +15847,64 @@
         <v>14.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1003</v>
+        <v>584</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G523" s="9">
-        <v>46820.0</v>
+        <v>46998.0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C524" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D524" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>683</v>
+        <v>853</v>
       </c>
       <c r="F524" s="3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="G524" s="9">
-        <v>46820.0</v>
+        <v>46484.0</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C525" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D525" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>584</v>
+        <v>1005</v>
       </c>
       <c r="F525" s="3" t="s">
-        <v>1001</v>
+        <v>1006</v>
       </c>
       <c r="G525" s="9">
-        <v>46998.0</v>
+        <v>46432.0</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>33</v>
@@ -15924,18 +15916,18 @@
         <v>2.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>855</v>
+        <v>1008</v>
       </c>
       <c r="F526" s="3" t="s">
-        <v>1007</v>
+        <v>797</v>
       </c>
       <c r="G526" s="9">
-        <v>46484.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>33</v>
@@ -15947,13 +15939,13 @@
         <v>2.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F527" s="3" t="s">
-        <v>1010</v>
+        <v>446</v>
       </c>
       <c r="G527" s="9">
-        <v>46432.0</v>
+        <v>46704.0</v>
       </c>
     </row>
     <row r="528">
@@ -15973,15 +15965,13 @@
         <v>1012</v>
       </c>
       <c r="F528" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="G528" s="9">
-        <v>46877.0</v>
-      </c>
+        <v>1013</v>
+      </c>
+      <c r="G528" s="9"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>33</v>
@@ -15993,18 +15983,15 @@
         <v>2.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="G529" s="9">
-        <v>46704.0</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>33</v>
@@ -16016,16 +16003,15 @@
         <v>2.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1016</v>
+        <v>837</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G530" s="9"/>
+        <v>1013</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>33</v>
@@ -16037,15 +16023,15 @@
         <v>2.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1019</v>
+        <v>658</v>
       </c>
       <c r="F531" s="3" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>33</v>
@@ -16057,15 +16043,15 @@
         <v>2.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>839</v>
+        <v>1019</v>
       </c>
       <c r="F532" s="3" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>33</v>
@@ -16077,10 +16063,13 @@
         <v>2.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>659</v>
+        <v>1021</v>
       </c>
       <c r="F533" s="3" t="s">
-        <v>1017</v>
+        <v>576</v>
+      </c>
+      <c r="G533" s="9">
+        <v>46766.0</v>
       </c>
     </row>
     <row r="534">
@@ -16088,19 +16077,22 @@
         <v>1022</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D534" s="2">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="E534" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="F534" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="F534" s="3" t="s">
-        <v>1017</v>
+      <c r="G534" s="9">
+        <v>46641.0</v>
       </c>
     </row>
     <row r="535">
@@ -16108,50 +16100,47 @@
         <v>1024</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D535" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="E535" s="2" t="s">
         <v>1025</v>
       </c>
       <c r="F535" s="3" t="s">
-        <v>576</v>
+        <v>1026</v>
       </c>
       <c r="G535" s="9">
-        <v>46766.0</v>
-      </c>
+        <v>46743.0</v>
+      </c>
+      <c r="H535" s="2"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D536" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F536" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G536" s="9">
-        <v>46641.0</v>
-      </c>
+        <v>1028</v>
+      </c>
+      <c r="F536" s="4"/>
+      <c r="H536" s="2"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>112</v>
@@ -16160,18 +16149,20 @@
         <v>12</v>
       </c>
       <c r="D537" s="2">
-        <v>11.0</v>
+        <v>21.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1029</v>
+        <v>682</v>
       </c>
       <c r="F537" s="3" t="s">
         <v>1030</v>
       </c>
       <c r="G537" s="9">
-        <v>46743.0</v>
-      </c>
-      <c r="H537" s="2"/>
+        <v>46663.0</v>
+      </c>
+      <c r="H537" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
@@ -16184,61 +16175,62 @@
         <v>12</v>
       </c>
       <c r="D538" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F538" s="4"/>
-      <c r="H538" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="F538" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G538" s="9">
+        <v>46530.0</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C539" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D539" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E539" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="B539" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C539" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D539" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E539" s="2" t="s">
-        <v>683</v>
-      </c>
       <c r="F539" s="3" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="G539" s="9">
-        <v>46663.0</v>
-      </c>
-      <c r="H539" s="2" t="s">
-        <v>133</v>
+        <v>46530.0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C540" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D540" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E540" s="2" t="s">
         <v>1035</v>
       </c>
-      <c r="B540" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C540" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D540" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E540" s="2" t="s">
-        <v>634</v>
-      </c>
       <c r="F540" s="3" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G540" s="9">
-        <v>46530.0</v>
+        <v>46481.0</v>
       </c>
     </row>
     <row r="541">
@@ -16249,19 +16241,19 @@
         <v>112</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D541" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>1037</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G541" s="9">
-        <v>46530.0</v>
+        <v>46877.0</v>
       </c>
     </row>
     <row r="542">
@@ -16275,13 +16267,13 @@
         <v>26</v>
       </c>
       <c r="D542" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>1039</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G542" s="9">
         <v>46481.0</v>
@@ -16304,7 +16296,7 @@
         <v>1041</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G543" s="9">
         <v>46877.0</v>
@@ -16318,65 +16310,65 @@
         <v>112</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D544" s="2">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1043</v>
+        <v>810</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G544" s="9">
-        <v>46481.0</v>
+        <v>46641.0</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C545" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D545" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E545" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="B545" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C545" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D545" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E545" s="2" t="s">
-        <v>1045</v>
-      </c>
       <c r="F545" s="3" t="s">
-        <v>1027</v>
+        <v>972</v>
       </c>
       <c r="G545" s="9">
-        <v>46877.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C546" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D546" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="B546" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C546" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D546" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E546" s="2" t="s">
-        <v>812</v>
-      </c>
       <c r="F546" s="3" t="s">
-        <v>1027</v>
+        <v>972</v>
       </c>
       <c r="G546" s="9">
-        <v>46641.0</v>
+        <v>46274.0</v>
       </c>
     </row>
     <row r="547">
@@ -16384,91 +16376,87 @@
         <v>1047</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D547" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>1048</v>
       </c>
       <c r="F547" s="3" t="s">
-        <v>976</v>
+        <v>1049</v>
       </c>
       <c r="G547" s="9">
-        <v>46274.0</v>
+        <v>46516.0</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D548" s="2">
-        <v>17.0</v>
+        <v>22.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F548" s="3" t="s">
-        <v>976</v>
-      </c>
-      <c r="G548" s="9">
-        <v>46274.0</v>
+        <v>1051</v>
+      </c>
+      <c r="F548" s="3"/>
+      <c r="G548" s="9"/>
+      <c r="H548" s="2" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D549" s="2">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F549" s="3" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G549" s="9">
-        <v>46516.0</v>
-      </c>
+        <v>1054</v>
+      </c>
+      <c r="F549" s="3"/>
+      <c r="G549" s="9"/>
+      <c r="H549" s="2"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D550" s="2">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F550" s="3"/>
+        <v>1056</v>
+      </c>
+      <c r="F550" s="3" t="s">
+        <v>409</v>
+      </c>
       <c r="G550" s="9"/>
-      <c r="H550" s="2" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H550" s="2"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
@@ -16478,16 +16466,20 @@
         <v>112</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D551" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="F551" s="3"/>
-      <c r="G551" s="9"/>
+      <c r="F551" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G551" s="9">
+        <v>46403.0</v>
+      </c>
       <c r="H551" s="2"/>
     </row>
     <row r="552">
@@ -16495,21 +16487,23 @@
         <v>1059</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D552" s="2">
-        <v>3.0</v>
+        <v>21.0</v>
       </c>
       <c r="E552" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F552" s="3" t="s">
         <v>1060</v>
       </c>
-      <c r="F552" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G552" s="9"/>
+      <c r="G552" s="9">
+        <v>46337.0</v>
+      </c>
       <c r="H552" s="2"/>
     </row>
     <row r="553">
@@ -16517,46 +16511,46 @@
         <v>1061</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D553" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1062</v>
+        <v>604</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>17</v>
+        <v>605</v>
       </c>
       <c r="G553" s="9">
-        <v>46403.0</v>
+        <v>46269.0</v>
       </c>
       <c r="H553" s="2"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D554" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E554" s="2" t="s">
         <v>1063</v>
-      </c>
-      <c r="B554" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C554" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D554" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E554" s="2" t="s">
-        <v>572</v>
       </c>
       <c r="F554" s="3" t="s">
         <v>1064</v>
       </c>
       <c r="G554" s="9">
-        <v>46337.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H554" s="2"/>
     </row>
@@ -16574,19 +16568,15 @@
         <v>8.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F555" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="G555" s="9">
-        <v>46269.0</v>
-      </c>
+        <v>1066</v>
+      </c>
+      <c r="F555" s="3"/>
+      <c r="G555" s="9"/>
       <c r="H555" s="2"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>519</v>
@@ -16598,10 +16588,10 @@
         <v>8.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="G556" s="9">
         <v>46290.0</v>
@@ -16613,42 +16603,46 @@
         <v>1069</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>519</v>
+        <v>33</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D557" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="F557" s="3"/>
-      <c r="G557" s="9"/>
+      <c r="F557" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G557" s="9">
+        <v>46883.0</v>
+      </c>
       <c r="H557" s="2"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>519</v>
+        <v>33</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D558" s="2">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>1068</v>
+        <v>389</v>
       </c>
       <c r="G558" s="9">
-        <v>46290.0</v>
+        <v>46883.0</v>
       </c>
       <c r="H558" s="2"/>
     </row>
@@ -16657,47 +16651,43 @@
         <v>1073</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D559" s="2">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="F559" s="3" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G559" s="9">
-        <v>46883.0</v>
-      </c>
+      <c r="F559" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G559" s="9"/>
       <c r="H559" s="2"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C560" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D560" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E560" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="B560" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C560" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D560" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E560" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F560" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="G560" s="9">
-        <v>46883.0</v>
-      </c>
+      <c r="F560" s="3">
+        <v>11504.0</v>
+      </c>
+      <c r="G560" s="9"/>
       <c r="H560" s="2"/>
     </row>
     <row r="561">
@@ -16708,16 +16698,16 @@
         <v>112</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D561" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>1078</v>
       </c>
       <c r="F561" s="3">
-        <v>11506.0</v>
+        <v>11504.0</v>
       </c>
       <c r="G561" s="9"/>
       <c r="H561" s="2"/>
@@ -16733,10 +16723,10 @@
         <v>28</v>
       </c>
       <c r="D562" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1080</v>
+        <v>530</v>
       </c>
       <c r="F562" s="3">
         <v>11504.0</v>
@@ -16746,29 +16736,29 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C563" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D563" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E563" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="F563" s="3" t="s">
         <v>1081</v>
-      </c>
-      <c r="B563" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C563" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D563" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="E563" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F563" s="3">
-        <v>11504.0</v>
       </c>
       <c r="G563" s="9"/>
       <c r="H563" s="2"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>112</v>
@@ -16777,15 +16767,15 @@
         <v>28</v>
       </c>
       <c r="D564" s="2">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F564" s="3">
-        <v>11504.0</v>
-      </c>
-      <c r="G564" s="9"/>
+        <v>1083</v>
+      </c>
+      <c r="F564" s="3"/>
+      <c r="G564" s="9">
+        <v>46820.0</v>
+      </c>
       <c r="H564" s="2"/>
     </row>
     <row r="565">
@@ -16793,13 +16783,13 @@
         <v>1084</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D565" s="2">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>1085</v>
@@ -16807,7 +16797,9 @@
       <c r="F565" s="3" t="s">
         <v>1086</v>
       </c>
-      <c r="G565" s="9"/>
+      <c r="G565" s="9">
+        <v>46641.0</v>
+      </c>
       <c r="H565" s="2"/>
     </row>
     <row r="566">
@@ -16815,20 +16807,22 @@
         <v>1087</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D566" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="F566" s="3"/>
-      <c r="G566" s="9">
-        <v>46820.0</v>
+      <c r="F566" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G566" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H566" s="2"/>
     </row>
@@ -16837,76 +16831,76 @@
         <v>1089</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D567" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="F567" s="3" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G567" s="9">
-        <v>46641.0</v>
+      <c r="F567" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G567" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H567" s="2"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C568" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D568" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F568" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G568" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F568" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G568" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H568" s="2"/>
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D569" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="F569" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G569" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F569" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G569" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H569" s="2"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>11</v>
@@ -16915,7 +16909,7 @@
         <v>26</v>
       </c>
       <c r="D570" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>21</v>
@@ -16930,49 +16924,49 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>11</v>
+        <v>519</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D571" s="2">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>21</v>
+        <v>610</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>38</v>
+        <v>1095</v>
       </c>
       <c r="G571" s="9">
-        <v>47531.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H571" s="2"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C572" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D572" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E572" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F572" s="3" t="s">
         <v>1098</v>
       </c>
-      <c r="B572" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C572" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D572" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E572" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F572" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="G572" s="9">
-        <v>47531.0</v>
+        <v>46223.0</v>
       </c>
       <c r="H572" s="2"/>
     </row>
@@ -16990,13 +16984,13 @@
         <v>10.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>610</v>
+        <v>1100</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G573" s="9">
-        <v>46217.0</v>
+        <v>46221.0</v>
       </c>
       <c r="H573" s="2"/>
     </row>
@@ -17014,67 +17008,63 @@
         <v>10.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1102</v>
+        <v>608</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="G574" s="9">
-        <v>46223.0</v>
+        <v>46214.0</v>
       </c>
       <c r="H574" s="2"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D575" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F575" s="3" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G575" s="9">
-        <v>46221.0</v>
-      </c>
+        <v>1078</v>
+      </c>
+      <c r="F575" s="3"/>
+      <c r="G575" s="9"/>
       <c r="H575" s="2"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D576" s="2">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>608</v>
+        <v>860</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1103</v>
+        <v>140</v>
       </c>
       <c r="G576" s="9">
-        <v>46214.0</v>
+        <v>46636.0</v>
       </c>
       <c r="H576" s="2"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>112</v>
@@ -17083,130 +17073,136 @@
         <v>12</v>
       </c>
       <c r="D577" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F577" s="3"/>
-      <c r="G577" s="9"/>
+        <v>555</v>
+      </c>
+      <c r="F577" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G577" s="9">
+        <v>46814.0</v>
+      </c>
       <c r="H577" s="2"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D578" s="2">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="F578" s="3" t="s">
-        <v>140</v>
+        <v>1107</v>
+      </c>
+      <c r="F578" s="3">
+        <v>11505.0</v>
       </c>
       <c r="G578" s="9">
-        <v>46636.0</v>
+        <v>46814.0</v>
       </c>
       <c r="H578" s="2"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D579" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E579" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B579" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C579" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D579" s="2">
-        <v>21.0</v>
-      </c>
-      <c r="E579" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="F579" s="3" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G579" s="9">
-        <v>46814.0</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="G579" s="9"/>
       <c r="H579" s="2"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D580" s="2">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F580" s="3">
-        <v>11505.0</v>
-      </c>
-      <c r="G580" s="9">
-        <v>46814.0</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="F580" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G580" s="9"/>
       <c r="H580" s="2"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D581" s="2">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="G581" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="G581" s="9">
+        <v>46436.0</v>
+      </c>
       <c r="H581" s="2"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C582" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D582" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E582" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F582" s="3" t="s">
         <v>1115</v>
       </c>
-      <c r="B582" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C582" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D582" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E582" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F582" s="3" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G582" s="9"/>
-      <c r="H582" s="2"/>
+      <c r="G582" s="9">
+        <v>46871.0</v>
+      </c>
+      <c r="H582" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
@@ -17219,17 +17215,13 @@
         <v>12</v>
       </c>
       <c r="D583" s="2">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="F583" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G583" s="9">
-        <v>46436.0</v>
-      </c>
+      <c r="F583" s="3"/>
+      <c r="G583" s="9"/>
       <c r="H583" s="2"/>
     </row>
     <row r="584">
@@ -17237,122 +17229,116 @@
         <v>1118</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D584" s="2">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>1119</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1120</v>
+        <v>409</v>
       </c>
       <c r="G584" s="9">
-        <v>46871.0</v>
-      </c>
-      <c r="H584" s="2" t="s">
-        <v>202</v>
-      </c>
+        <v>46767.0</v>
+      </c>
+      <c r="H584" s="2"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D585" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E585" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B585" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C585" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D585" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E585" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F585" s="3"/>
-      <c r="G585" s="9"/>
+      <c r="F585" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="G585" s="9">
+        <v>46261.0</v>
+      </c>
       <c r="H585" s="2"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D586" s="2">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1124</v>
+        <v>780</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>409</v>
+        <v>605</v>
       </c>
       <c r="G586" s="9">
-        <v>46767.0</v>
+        <v>46205.0</v>
       </c>
       <c r="H586" s="2"/>
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>519</v>
+        <v>11</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D587" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="F587" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="G587" s="9">
-        <v>46261.0</v>
-      </c>
+        <v>1124</v>
+      </c>
+      <c r="F587" s="3"/>
+      <c r="G587" s="9"/>
       <c r="H587" s="2"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>519</v>
+        <v>11</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D588" s="2">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F588" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="G588" s="9">
-        <v>46205.0</v>
-      </c>
+        <v>1126</v>
+      </c>
+      <c r="F588" s="3"/>
+      <c r="G588" s="9"/>
       <c r="H588" s="2"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>11</v>
@@ -17361,10 +17347,10 @@
         <v>34</v>
       </c>
       <c r="D589" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1129</v>
+        <v>651</v>
       </c>
       <c r="F589" s="3"/>
       <c r="G589" s="9"/>
@@ -17372,47 +17358,55 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>11</v>
+        <v>521</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D590" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F590" s="3"/>
-      <c r="G590" s="9"/>
+        <v>1129</v>
+      </c>
+      <c r="F590" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G590" s="9">
+        <v>46387.0</v>
+      </c>
       <c r="H590" s="2"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>11</v>
+        <v>521</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D591" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F591" s="3"/>
-      <c r="G591" s="9"/>
+        <v>1131</v>
+      </c>
+      <c r="F591" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G591" s="9">
+        <v>46387.0</v>
+      </c>
       <c r="H591" s="2"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>521</v>
@@ -17421,10 +17415,10 @@
         <v>12</v>
       </c>
       <c r="D592" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F592" s="3" t="s">
         <v>38</v>
@@ -17436,7 +17430,7 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>521</v>
@@ -17448,7 +17442,7 @@
         <v>5.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F593" s="3" t="s">
         <v>38</v>
@@ -17460,7 +17454,7 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>521</v>
@@ -17472,7 +17466,7 @@
         <v>5.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="F594" s="3" t="s">
         <v>38</v>
@@ -17484,7 +17478,7 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>521</v>
@@ -17493,22 +17487,22 @@
         <v>12</v>
       </c>
       <c r="D595" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1140</v>
+        <v>829</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>38</v>
+        <v>972</v>
       </c>
       <c r="G595" s="9">
-        <v>46387.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H595" s="2"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>521</v>
@@ -17517,22 +17511,22 @@
         <v>12</v>
       </c>
       <c r="D596" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1142</v>
+        <v>1117</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>38</v>
+        <v>972</v>
       </c>
       <c r="G596" s="9">
-        <v>46387.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H596" s="2"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>521</v>
@@ -17541,22 +17535,22 @@
         <v>12</v>
       </c>
       <c r="D597" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>831</v>
+        <v>934</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>976</v>
+        <v>478</v>
       </c>
       <c r="G597" s="9">
-        <v>46217.0</v>
+        <v>46308.0</v>
       </c>
       <c r="H597" s="2"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>521</v>
@@ -17565,22 +17559,22 @@
         <v>12</v>
       </c>
       <c r="D598" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1122</v>
+        <v>909</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>976</v>
+        <v>478</v>
       </c>
       <c r="G598" s="9">
-        <v>46217.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H598" s="2"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>521</v>
@@ -17592,19 +17586,19 @@
         <v>10.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>938</v>
+        <v>1143</v>
       </c>
       <c r="F599" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G599" s="9">
-        <v>46308.0</v>
+        <v>46525.0</v>
       </c>
       <c r="H599" s="2"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>521</v>
@@ -17616,7 +17610,7 @@
         <v>10.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>478</v>
@@ -17628,7 +17622,7 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>521</v>
@@ -17640,19 +17634,19 @@
         <v>10.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1148</v>
+        <v>911</v>
       </c>
       <c r="F601" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G601" s="9">
-        <v>46525.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H601" s="2"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>521</v>
@@ -17664,19 +17658,19 @@
         <v>10.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="F602" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G602" s="9">
-        <v>46521.0</v>
+        <v>46527.0</v>
       </c>
       <c r="H602" s="2"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>521</v>
@@ -17688,19 +17682,19 @@
         <v>10.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>915</v>
+        <v>1148</v>
       </c>
       <c r="F603" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G603" s="9">
-        <v>46521.0</v>
+        <v>46356.0</v>
       </c>
       <c r="H603" s="2"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>521</v>
@@ -17712,19 +17706,19 @@
         <v>10.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>909</v>
+        <v>1150</v>
       </c>
       <c r="F604" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G604" s="9">
-        <v>46527.0</v>
+        <v>46366.0</v>
       </c>
       <c r="H604" s="2"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>521</v>
@@ -17736,19 +17730,19 @@
         <v>10.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F605" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G605" s="9">
-        <v>46356.0</v>
+        <v>46336.0</v>
       </c>
       <c r="H605" s="2"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>521</v>
@@ -17757,22 +17751,22 @@
         <v>12</v>
       </c>
       <c r="D606" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1155</v>
+        <v>928</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G606" s="9">
-        <v>46366.0</v>
+        <v>46310.0</v>
       </c>
       <c r="H606" s="2"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>521</v>
@@ -17781,22 +17775,22 @@
         <v>12</v>
       </c>
       <c r="D607" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1157</v>
+        <v>914</v>
       </c>
       <c r="F607" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G607" s="9">
-        <v>46336.0</v>
+        <v>46354.0</v>
       </c>
       <c r="H607" s="2"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>521</v>
@@ -17808,19 +17802,19 @@
         <v>11.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>932</v>
+        <v>1156</v>
       </c>
       <c r="F608" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G608" s="9">
-        <v>46310.0</v>
+        <v>46360.0</v>
       </c>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>521</v>
@@ -17832,19 +17826,19 @@
         <v>11.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="F609" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G609" s="9">
-        <v>46354.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>521</v>
@@ -17856,19 +17850,19 @@
         <v>11.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1161</v>
+        <v>926</v>
       </c>
       <c r="F610" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G610" s="9">
-        <v>46360.0</v>
+        <v>46346.0</v>
       </c>
       <c r="H610" s="2"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>521</v>
@@ -17880,19 +17874,19 @@
         <v>11.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="F611" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G611" s="9">
-        <v>46333.0</v>
+        <v>46342.0</v>
       </c>
       <c r="H611" s="2"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>521</v>
@@ -17904,67 +17898,67 @@
         <v>11.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>930</v>
+        <v>1161</v>
       </c>
       <c r="F612" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G612" s="9">
-        <v>46346.0</v>
+        <v>46343.0</v>
       </c>
       <c r="H612" s="2"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D613" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>928</v>
+        <v>627</v>
       </c>
       <c r="F613" s="3" t="s">
-        <v>478</v>
+        <v>978</v>
       </c>
       <c r="G613" s="9">
-        <v>46342.0</v>
+        <v>46228.0</v>
       </c>
       <c r="H613" s="2"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D614" s="2">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1166</v>
+        <v>557</v>
       </c>
       <c r="F614" s="3" t="s">
-        <v>478</v>
+        <v>1064</v>
       </c>
       <c r="G614" s="9">
-        <v>46343.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H614" s="2"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>519</v>
@@ -17973,22 +17967,22 @@
         <v>12</v>
       </c>
       <c r="D615" s="2">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>628</v>
+        <v>792</v>
       </c>
       <c r="F615" s="3" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="G615" s="9">
-        <v>46228.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H615" s="2"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>519</v>
@@ -18000,10 +17994,10 @@
         <v>7.0</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="G616" s="9">
         <v>46290.0</v>
@@ -18012,7 +18006,7 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>519</v>
@@ -18021,22 +18015,20 @@
         <v>12</v>
       </c>
       <c r="D617" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>793</v>
+        <v>858</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G617" s="9">
-        <v>46290.0</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="G617" s="9"/>
       <c r="H617" s="2"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>519</v>
@@ -18045,22 +18037,20 @@
         <v>12</v>
       </c>
       <c r="D618" s="2">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F618" s="3" t="s">
-        <v>1068</v>
-      </c>
-      <c r="G618" s="9">
-        <v>46290.0</v>
-      </c>
+        <v>1168</v>
+      </c>
+      <c r="F618" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G618" s="9"/>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>519</v>
@@ -18069,32 +18059,32 @@
         <v>12</v>
       </c>
       <c r="D619" s="2">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="F619" s="3" t="s">
-        <v>991</v>
+        <v>1028</v>
+      </c>
+      <c r="F619" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G619" s="9"/>
       <c r="H619" s="2"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>519</v>
+        <v>33</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D620" s="2">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F620" s="3">
         <v>11506.0</v>
@@ -18104,19 +18094,19 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>519</v>
+        <v>33</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D621" s="2">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1032</v>
+        <v>1088</v>
       </c>
       <c r="F621" s="3">
         <v>11506.0</v>
@@ -18126,19 +18116,19 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D622" s="2">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1176</v>
+        <v>1090</v>
       </c>
       <c r="F622" s="3">
         <v>11506.0</v>
@@ -18148,46 +18138,50 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>33</v>
+        <v>519</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D623" s="2">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F623" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G623" s="9"/>
+        <v>1175</v>
+      </c>
+      <c r="F623" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G623" s="9">
+        <v>46793.0</v>
+      </c>
       <c r="H623" s="2"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C624" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D624" s="2">
-        <v>4.0</v>
+        <v>21.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="F624" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G624" s="9"/>
+        <v>1178</v>
+      </c>
+      <c r="F624" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G624" s="9">
+        <v>46437.0</v>
+      </c>
       <c r="H624" s="2"/>
     </row>
     <row r="625">
@@ -18195,146 +18189,146 @@
         <v>1179</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D625" s="2">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="E625" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="F625" s="3" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G625" s="9">
-        <v>46793.0</v>
-      </c>
-      <c r="H625" s="2"/>
+      <c r="F625" s="3"/>
+      <c r="G625" s="9"/>
+      <c r="H625" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D626" s="2">
         <v>21.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F626" s="3" t="s">
-        <v>218</v>
+        <v>1026</v>
       </c>
       <c r="G626" s="9">
-        <v>46437.0</v>
+        <v>46750.0</v>
       </c>
       <c r="H626" s="2"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D627" s="2">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F627" s="3"/>
-      <c r="G627" s="9"/>
-      <c r="H627" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="F627" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G627" s="9">
+        <v>46641.0</v>
+      </c>
+      <c r="H627" s="2"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D628" s="2">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="F628" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G628" s="9">
-        <v>46750.0</v>
+        <v>46736.0</v>
       </c>
       <c r="H628" s="2"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D629" s="2">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>812</v>
+        <v>1187</v>
       </c>
       <c r="F629" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G629" s="9">
-        <v>46641.0</v>
+        <v>46716.0</v>
       </c>
       <c r="H629" s="2"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D630" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E630" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="B630" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C630" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D630" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="E630" s="2" t="s">
-        <v>1190</v>
-      </c>
       <c r="F630" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G630" s="9">
-        <v>46736.0</v>
+        <v>46488.0</v>
       </c>
       <c r="H630" s="2"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>112</v>
@@ -18346,19 +18340,19 @@
         <v>13.0</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G631" s="9">
-        <v>46716.0</v>
+        <v>46872.0</v>
       </c>
       <c r="H631" s="2"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>112</v>
@@ -18370,19 +18364,19 @@
         <v>13.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F632" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G632" s="9">
-        <v>46488.0</v>
+        <v>46872.0</v>
       </c>
       <c r="H632" s="2"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>112</v>
@@ -18394,19 +18388,19 @@
         <v>13.0</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F633" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G633" s="9">
-        <v>46872.0</v>
+        <v>46488.0</v>
       </c>
       <c r="H633" s="2"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>112</v>
@@ -18418,19 +18412,19 @@
         <v>13.0</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="F634" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G634" s="9">
-        <v>46872.0</v>
+        <v>46768.0</v>
       </c>
       <c r="H634" s="2"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>112</v>
@@ -18442,91 +18436,91 @@
         <v>13.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1200</v>
+        <v>812</v>
       </c>
       <c r="F635" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G635" s="9">
-        <v>46488.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H635" s="2"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D636" s="2">
         <v>13.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F636" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G636" s="9">
-        <v>46768.0</v>
+        <v>47036.0</v>
       </c>
       <c r="H636" s="2"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D637" s="2">
         <v>13.0</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>814</v>
+        <v>1199</v>
       </c>
       <c r="F637" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G637" s="9">
-        <v>46530.0</v>
+        <v>46752.0</v>
       </c>
       <c r="H637" s="2"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D638" s="2">
         <v>13.0</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="F638" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G638" s="9">
-        <v>47036.0</v>
+        <v>46736.0</v>
       </c>
       <c r="H638" s="2"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>112</v>
@@ -18535,66 +18529,18 @@
         <v>26</v>
       </c>
       <c r="D639" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1204</v>
+        <v>1035</v>
       </c>
       <c r="F639" s="3" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G639" s="9">
-        <v>46752.0</v>
+        <v>46540.0</v>
       </c>
       <c r="H639" s="2"/>
-    </row>
-    <row r="640">
-      <c r="A640" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B640" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C640" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D640" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E640" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F640" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G640" s="9">
-        <v>46736.0</v>
-      </c>
-      <c r="H640" s="2"/>
-    </row>
-    <row r="641">
-      <c r="A641" s="2" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B641" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C641" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D641" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="E641" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F641" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G641" s="9">
-        <v>46540.0</v>
-      </c>
-      <c r="H641" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1206">
   <si>
     <t>ID</t>
   </si>
@@ -3620,6 +3620,15 @@
   </si>
   <si>
     <t>ID1781232348136</t>
+  </si>
+  <si>
+    <t>ID1781485466888</t>
+  </si>
+  <si>
+    <t>ID1781486548434</t>
+  </si>
+  <si>
+    <t>#35(預定)</t>
   </si>
 </sst>
 </file>
@@ -13238,6 +13247,9 @@
       <c r="G406" s="9">
         <v>46666.0</v>
       </c>
+      <c r="H406" s="2" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
@@ -18382,7 +18394,7 @@
         <v>112</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D633" s="2">
         <v>13.0</v>
@@ -18406,7 +18418,7 @@
         <v>112</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D634" s="2">
         <v>13.0</v>
@@ -18541,6 +18553,52 @@
         <v>46540.0</v>
       </c>
       <c r="H639" s="2"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C640" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D640" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E640" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G640" s="9">
+        <v>46544.0</v>
+      </c>
+      <c r="H640" s="2"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D641" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E641" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F641" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G641" s="9"/>
+      <c r="H641" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3043" uniqueCount="1205">
   <si>
     <t>ID</t>
   </si>
@@ -181,6 +181,9 @@
     <t>ID3983541495116</t>
   </si>
   <si>
+    <t>極冷庫-左</t>
+  </si>
+  <si>
     <t>A5CER-GB  (牛肉)(日)</t>
   </si>
   <si>
@@ -349,9 +352,6 @@
     <t>ID3983541495151</t>
   </si>
   <si>
-    <t>極冷庫-左</t>
-  </si>
-  <si>
     <t>1150206K</t>
   </si>
   <si>
@@ -1606,9 +1606,6 @@
     <t>10Q</t>
   </si>
   <si>
-    <t>庫存: 極冷庫-左4F-6, 極冷庫-左3F-3</t>
-  </si>
-  <si>
     <t>極冷庫-left</t>
   </si>
   <si>
@@ -3250,9 +3247,6 @@
     <t>36-38B</t>
   </si>
   <si>
-    <t>ID1780472484781</t>
-  </si>
-  <si>
     <t>ID1780473214746</t>
   </si>
   <si>
@@ -3629,6 +3623,9 @@
   </si>
   <si>
     <t>#35(預定)</t>
+  </si>
+  <si>
+    <t>ID1781515900527</t>
   </si>
 </sst>
 </file>
@@ -4370,19 +4367,19 @@
         <v>55</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="18">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" s="19">
         <v>46730.0</v>
@@ -4391,7 +4388,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>33</v>
@@ -4403,10 +4400,10 @@
         <v>17.0</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" s="19">
         <v>46729.0</v>
@@ -4415,7 +4412,7 @@
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>33</v>
@@ -4427,10 +4424,10 @@
         <v>17.0</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" s="19">
         <v>46729.0</v>
@@ -4439,7 +4436,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>33</v>
@@ -4451,17 +4448,17 @@
         <v>15.0</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>33</v>
@@ -4473,10 +4470,10 @@
         <v>14.0</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="19">
         <v>46949.0</v>
@@ -4485,7 +4482,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>33</v>
@@ -4497,10 +4494,10 @@
         <v>13.0</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="19">
         <v>46949.0</v>
@@ -4509,7 +4506,7 @@
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>33</v>
@@ -4521,7 +4518,7 @@
         <v>12.0</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F25" s="14"/>
       <c r="G25" s="19">
@@ -4531,7 +4528,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>33</v>
@@ -4543,7 +4540,7 @@
         <v>11.0</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>17</v>
@@ -4555,7 +4552,7 @@
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>33</v>
@@ -4567,17 +4564,17 @@
         <v>10.0</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>33</v>
@@ -4589,17 +4586,17 @@
         <v>9.0</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G28" s="12"/>
       <c r="H28" s="12"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>33</v>
@@ -4611,17 +4608,17 @@
         <v>9.0</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>33</v>
@@ -4633,17 +4630,17 @@
         <v>8.0</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>33</v>
@@ -4655,10 +4652,10 @@
         <v>7.0</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" s="19">
         <v>46704.0</v>
@@ -4669,7 +4666,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>33</v>
@@ -4681,10 +4678,10 @@
         <v>7.0</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G32" s="19">
         <v>46704.0</v>
@@ -4693,7 +4690,7 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>33</v>
@@ -4705,10 +4702,10 @@
         <v>7.0</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G33" s="19">
         <v>46704.0</v>
@@ -4717,7 +4714,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>33</v>
@@ -4729,10 +4726,10 @@
         <v>7.0</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G34" s="19">
         <v>46704.0</v>
@@ -4741,7 +4738,7 @@
     </row>
     <row r="35">
       <c r="A35" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>33</v>
@@ -4753,10 +4750,10 @@
         <v>7.0</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" s="19">
         <v>46704.0</v>
@@ -4765,7 +4762,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>33</v>
@@ -4777,10 +4774,10 @@
         <v>7.0</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G36" s="19">
         <v>46704.0</v>
@@ -4789,7 +4786,7 @@
     </row>
     <row r="37">
       <c r="A37" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>33</v>
@@ -4801,10 +4798,10 @@
         <v>7.0</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G37" s="19">
         <v>46723.0</v>
@@ -4813,7 +4810,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>33</v>
@@ -4825,10 +4822,10 @@
         <v>7.0</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G38" s="19">
         <v>46723.0</v>
@@ -4837,7 +4834,7 @@
     </row>
     <row r="39">
       <c r="A39" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>33</v>
@@ -4849,10 +4846,10 @@
         <v>8.0</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G39" s="19">
         <v>46711.0</v>
@@ -4861,7 +4858,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>33</v>
@@ -4873,10 +4870,10 @@
         <v>4.0</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G40" s="19">
         <v>46691.0</v>
@@ -4885,7 +4882,7 @@
     </row>
     <row r="41">
       <c r="A41" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>33</v>
@@ -4897,10 +4894,10 @@
         <v>22.0</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G41" s="19">
         <v>46224.0</v>
@@ -4909,7 +4906,7 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>33</v>
@@ -4921,10 +4918,10 @@
         <v>3.0</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G42" s="19">
         <v>46304.0</v>
@@ -4933,7 +4930,7 @@
     </row>
     <row r="43">
       <c r="A43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>33</v>
@@ -4945,10 +4942,10 @@
         <v>3.0</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G43" s="19">
         <v>46634.0</v>
@@ -4957,10 +4954,10 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>26</v>
@@ -4969,7 +4966,7 @@
         <v>19.0</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>113</v>
@@ -5039,7 +5036,7 @@
         <v>1.0</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F47" s="14"/>
       <c r="G47" s="12"/>
@@ -5059,7 +5056,7 @@
         <v>1.0</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="12"/>
@@ -5145,7 +5142,7 @@
         <v>1.0</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>118</v>
@@ -5206,7 +5203,7 @@
         <v>134</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>28</v>
@@ -5232,7 +5229,7 @@
         <v>138</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>26</v>
@@ -5256,7 +5253,7 @@
         <v>141</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>26</v>
@@ -5280,7 +5277,7 @@
         <v>144</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>28</v>
@@ -5304,7 +5301,7 @@
         <v>147</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>28</v>
@@ -5328,7 +5325,7 @@
         <v>150</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>28</v>
@@ -5350,7 +5347,7 @@
         <v>153</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>28</v>
@@ -5374,7 +5371,7 @@
         <v>156</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>28</v>
@@ -5398,7 +5395,7 @@
         <v>158</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>28</v>
@@ -5418,7 +5415,7 @@
         <v>160</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>12</v>
@@ -5442,7 +5439,7 @@
         <v>163</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>12</v>
@@ -5462,7 +5459,7 @@
         <v>165</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>12</v>
@@ -5482,7 +5479,7 @@
         <v>167</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>12</v>
@@ -5506,7 +5503,7 @@
         <v>169</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>12</v>
@@ -5530,7 +5527,7 @@
         <v>172</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>12</v>
@@ -5550,7 +5547,7 @@
         <v>174</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>12</v>
@@ -5574,7 +5571,7 @@
         <v>177</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>12</v>
@@ -5594,7 +5591,7 @@
         <v>179</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>12</v>
@@ -5616,7 +5613,7 @@
         <v>182</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C73" s="12" t="s">
         <v>12</v>
@@ -5636,7 +5633,7 @@
         <v>184</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C74" s="12" t="s">
         <v>12</v>
@@ -5656,7 +5653,7 @@
         <v>186</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>12</v>
@@ -5676,7 +5673,7 @@
         <v>188</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>12</v>
@@ -5698,7 +5695,7 @@
         <v>190</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>12</v>
@@ -5718,7 +5715,7 @@
         <v>192</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>12</v>
@@ -5740,7 +5737,7 @@
         <v>194</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>12</v>
@@ -5762,7 +5759,7 @@
         <v>196</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>12</v>
@@ -5782,7 +5779,7 @@
         <v>198</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>12</v>
@@ -5802,7 +5799,7 @@
         <v>200</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>12</v>
@@ -5824,7 +5821,7 @@
         <v>203</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>34</v>
@@ -5846,7 +5843,7 @@
         <v>205</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C84" s="12" t="s">
         <v>34</v>
@@ -5866,7 +5863,7 @@
         <v>207</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>34</v>
@@ -5888,7 +5885,7 @@
         <v>209</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C86" s="12" t="s">
         <v>34</v>
@@ -5930,7 +5927,7 @@
         <v>212</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>28</v>
@@ -5954,7 +5951,7 @@
         <v>215</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>34</v>
@@ -5976,7 +5973,7 @@
         <v>216</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>34</v>
@@ -6029,7 +6026,7 @@
         <v>224</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>12</v>
@@ -6053,7 +6050,7 @@
         <v>227</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>12</v>
@@ -6077,7 +6074,7 @@
         <v>229</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>26</v>
@@ -6101,7 +6098,7 @@
         <v>232</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>26</v>
@@ -6125,7 +6122,7 @@
         <v>235</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>26</v>
@@ -6180,7 +6177,7 @@
         <v>21.0</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F98" s="14"/>
       <c r="G98" s="12"/>
@@ -6224,7 +6221,7 @@
         <v>21.0</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F100" s="14"/>
       <c r="G100" s="12"/>
@@ -6303,7 +6300,7 @@
         <v>249</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>26</v>
@@ -6327,7 +6324,7 @@
         <v>252</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>26</v>
@@ -6808,7 +6805,7 @@
         <v>8.0</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F125" s="17" t="s">
         <v>298</v>
@@ -6854,7 +6851,7 @@
         <v>8.0</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F127" s="17" t="s">
         <v>302</v>
@@ -7003,7 +7000,7 @@
         <v>22.0</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>316</v>
@@ -7032,7 +7029,7 @@
         <v>11.0</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>319</v>
@@ -7126,7 +7123,7 @@
         <v>330</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>26</v>
@@ -7135,7 +7132,7 @@
         <v>21.0</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F138" s="17" t="s">
         <v>331</v>
@@ -7379,7 +7376,7 @@
         <v>350</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>12</v>
@@ -7846,7 +7843,7 @@
         <v>11.0</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F167" s="17" t="s">
         <v>263</v>
@@ -7859,7 +7856,7 @@
         <v>392</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>12</v>
@@ -8243,7 +8240,7 @@
         <v>430</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C185" s="11" t="s">
         <v>26</v>
@@ -8311,7 +8308,7 @@
         <v>436</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C188" s="11" t="s">
         <v>26</v>
@@ -8335,7 +8332,7 @@
         <v>439</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C189" s="11" t="s">
         <v>26</v>
@@ -8361,7 +8358,7 @@
         <v>441</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C190" s="11" t="s">
         <v>26</v>
@@ -8385,7 +8382,7 @@
         <v>442</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C191" s="12" t="s">
         <v>26</v>
@@ -8407,7 +8404,7 @@
         <v>444</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>26</v>
@@ -8431,7 +8428,7 @@
         <v>447</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C193" s="11" t="s">
         <v>26</v>
@@ -8440,7 +8437,7 @@
         <v>21.0</v>
       </c>
       <c r="E193" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F193" s="17" t="s">
         <v>448</v>
@@ -8455,7 +8452,7 @@
         <v>449</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C194" s="11" t="s">
         <v>26</v>
@@ -8479,7 +8476,7 @@
         <v>450</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C195" s="11" t="s">
         <v>26</v>
@@ -8503,7 +8500,7 @@
         <v>453</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C196" s="11" t="s">
         <v>26</v>
@@ -8512,7 +8509,7 @@
         <v>19.0</v>
       </c>
       <c r="E196" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F196" s="17" t="s">
         <v>454</v>
@@ -8529,7 +8526,7 @@
         <v>456</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>26</v>
@@ -8553,7 +8550,7 @@
         <v>457</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C198" s="11" t="s">
         <v>26</v>
@@ -8562,7 +8559,7 @@
         <v>19.0</v>
       </c>
       <c r="E198" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F198" s="17" t="s">
         <v>458</v>
@@ -8604,7 +8601,7 @@
         <v>462</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C200" s="11" t="s">
         <v>26</v>
@@ -8628,7 +8625,7 @@
         <v>465</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C201" s="12" t="s">
         <v>26</v>
@@ -8650,7 +8647,7 @@
         <v>467</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C202" s="11" t="s">
         <v>26</v>
@@ -8672,7 +8669,7 @@
         <v>469</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C203" s="11" t="s">
         <v>26</v>
@@ -8694,7 +8691,7 @@
         <v>470</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C204" s="12" t="s">
         <v>26</v>
@@ -8736,7 +8733,7 @@
         <v>473</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C206" s="11" t="s">
         <v>12</v>
@@ -8760,7 +8757,7 @@
         <v>476</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C207" s="11" t="s">
         <v>12</v>
@@ -8786,7 +8783,7 @@
         <v>479</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C208" s="11" t="s">
         <v>12</v>
@@ -8810,7 +8807,7 @@
         <v>481</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C209" s="11" t="s">
         <v>12</v>
@@ -8834,7 +8831,7 @@
         <v>483</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C210" s="11" t="s">
         <v>12</v>
@@ -8858,7 +8855,7 @@
         <v>486</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C211" s="11" t="s">
         <v>12</v>
@@ -8882,7 +8879,7 @@
         <v>488</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C212" s="11" t="s">
         <v>12</v>
@@ -8906,7 +8903,7 @@
         <v>491</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C213" s="11" t="s">
         <v>12</v>
@@ -8932,7 +8929,7 @@
         <v>494</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>12</v>
@@ -8956,7 +8953,7 @@
         <v>496</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C215" s="11" t="s">
         <v>12</v>
@@ -8980,7 +8977,7 @@
         <v>498</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>12</v>
@@ -9002,7 +8999,7 @@
         <v>500</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C217" s="11" t="s">
         <v>12</v>
@@ -9026,7 +9023,7 @@
         <v>502</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>12</v>
@@ -9226,7 +9223,7 @@
         <v>517</v>
       </c>
       <c r="B227" s="11" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C227" s="11" t="s">
         <v>34</v>
@@ -9316,7 +9313,7 @@
         <v>1.774477758555E12</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>12</v>
@@ -9340,7 +9337,7 @@
         <v>1.774478387384E12</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>26</v>
@@ -9363,7 +9360,7 @@
         <v>1.774478428996E12</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>26</v>
@@ -9386,7 +9383,7 @@
         <v>1.774482109714E12</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>26</v>
@@ -9410,7 +9407,7 @@
         <v>1.774487055644E12</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>12</v>
@@ -9422,14 +9419,12 @@
         <v>530</v>
       </c>
       <c r="F235" s="3">
-        <v>11503.0</v>
+        <v>11504.0</v>
       </c>
       <c r="G235" s="9">
         <v>46826.0</v>
       </c>
-      <c r="H235" s="2" t="s">
-        <v>531</v>
-      </c>
+      <c r="H235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" s="1">
@@ -9456,7 +9451,7 @@
         <v>1.774488862747E12</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>12</v>
@@ -9465,7 +9460,7 @@
         <v>5.0</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>17</v>
@@ -9480,7 +9475,7 @@
         <v>1.774497620145E12</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>12</v>
@@ -9489,7 +9484,7 @@
         <v>4.0</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>218</v>
@@ -9503,7 +9498,7 @@
         <v>1.774514361879E12</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>34</v>
@@ -9523,7 +9518,7 @@
         <v>1.774606467853E12</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>34</v>
@@ -9532,7 +9527,7 @@
         <v>21.0</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>17</v>
@@ -9544,7 +9539,7 @@
         <v>1.77485551576E12</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>26</v>
@@ -9553,7 +9548,7 @@
         <v>15.0</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>464</v>
@@ -9568,7 +9563,7 @@
         <v>1.774927609576E12</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>34</v>
@@ -9577,16 +9572,16 @@
         <v>8.0</v>
       </c>
       <c r="E242" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F242" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="G242" s="9">
         <v>46516.0</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="243">
@@ -9594,7 +9589,7 @@
         <v>1.775008569613E12</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>34</v>
@@ -9603,7 +9598,7 @@
         <v>12.0</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F243" s="3">
         <v>11503.0</v>
@@ -9614,7 +9609,7 @@
         <v>1.77500901595E12</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>26</v>
@@ -9623,7 +9618,7 @@
         <v>16.0</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>234</v>
@@ -9637,7 +9632,7 @@
         <v>1.775037421583E12</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>12</v>
@@ -9646,10 +9641,10 @@
         <v>12.0</v>
       </c>
       <c r="E245" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F245" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="G245" s="9">
         <v>46395.0</v>
@@ -9690,7 +9685,7 @@
         <v>1.0</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F247" s="3"/>
     </row>
@@ -9708,10 +9703,10 @@
         <v>3.0</v>
       </c>
       <c r="E248" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F248" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="G248" s="9">
         <v>46613.0</v>
@@ -9731,10 +9726,10 @@
         <v>7.0</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G249" s="9">
         <v>46704.0</v>
@@ -9774,7 +9769,7 @@
         <v>12.0</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F251" s="4"/>
       <c r="G251" s="9"/>
@@ -9796,7 +9791,7 @@
         <v>14.0</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F252" s="4"/>
       <c r="G252" s="9">
@@ -9818,7 +9813,7 @@
         <v>13.0</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F253" s="4"/>
       <c r="G253" s="9">
@@ -9840,7 +9835,7 @@
         <v>12.0</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F254" s="4"/>
       <c r="G254" s="9">
@@ -9864,7 +9859,7 @@
         <v>12.0</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F255" s="4"/>
       <c r="G255" s="9">
@@ -9885,7 +9880,7 @@
         <v>14.0</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F256" s="4"/>
       <c r="G256" s="9">
@@ -9906,7 +9901,7 @@
         <v>14.0</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F257" s="4"/>
       <c r="G257" s="9">
@@ -9927,10 +9922,10 @@
         <v>19.0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G258" s="9">
         <v>46949.0</v>
@@ -9950,10 +9945,10 @@
         <v>17.0</v>
       </c>
       <c r="E259" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F259" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="G259" s="9">
         <v>46743.0</v>
@@ -9973,10 +9968,10 @@
         <v>17.0</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G260" s="9">
         <v>46752.0</v>
@@ -9996,7 +9991,7 @@
         <v>16.0</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F261" s="4"/>
       <c r="G261" s="9">
@@ -10017,7 +10012,7 @@
         <v>13.0</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F262" s="4"/>
       <c r="G262" s="9">
@@ -10038,7 +10033,7 @@
         <v>16.0</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F263" s="4"/>
       <c r="G263" s="9">
@@ -10059,7 +10054,7 @@
         <v>15.0</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>263</v>
@@ -10073,7 +10068,7 @@
         <v>1.775545086281E12</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>28</v>
@@ -10093,7 +10088,7 @@
         <v>1.775610301476E12</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>26</v>
@@ -10102,10 +10097,10 @@
         <v>19.0</v>
       </c>
       <c r="E266" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F266" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>563</v>
       </c>
       <c r="G266" s="9">
         <v>46670.0</v>
@@ -10116,7 +10111,7 @@
         <v>1.775631108337E12</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>26</v>
@@ -10125,7 +10120,7 @@
         <v>3.0</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>218</v>
@@ -10136,7 +10131,7 @@
         <v>1.775632091399E12</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>26</v>
@@ -10145,10 +10140,10 @@
         <v>20.0</v>
       </c>
       <c r="E268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F268" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="G268" s="9">
         <v>46789.0</v>
@@ -10209,10 +10204,10 @@
         <v>16.0</v>
       </c>
       <c r="E271" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F271" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="G271" s="9">
         <v>46681.0</v>
@@ -10232,10 +10227,10 @@
         <v>16.0</v>
       </c>
       <c r="E272" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F272" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="F272" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="G272" s="9">
         <v>46725.0</v>
@@ -10255,10 +10250,10 @@
         <v>8.0</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G273" s="9">
         <v>46789.0</v>
@@ -10278,10 +10273,10 @@
         <v>8.0</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G274" s="9">
         <v>46757.0</v>
@@ -10292,7 +10287,7 @@
         <v>1.775695916181E12</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>28</v>
@@ -10301,10 +10296,10 @@
         <v>17.0</v>
       </c>
       <c r="E275" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F275" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>573</v>
       </c>
       <c r="G275" s="9">
         <v>46947.0</v>
@@ -10315,7 +10310,7 @@
         <v>1.775734585272E12</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>12</v>
@@ -10324,7 +10319,7 @@
         <v>9.0</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F276" s="3">
         <v>11503.0</v>
@@ -10344,7 +10339,7 @@
         <v>2.0</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F277" s="3">
         <v>11504.0</v>
@@ -10356,7 +10351,7 @@
         <v>1.775786151238E12</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>34</v>
@@ -10365,10 +10360,10 @@
         <v>18.0</v>
       </c>
       <c r="E278" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F278" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="F278" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="G278" s="9">
         <v>46949.0</v>
@@ -10379,7 +10374,7 @@
         <v>1.775786456959E12</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>26</v>
@@ -10388,10 +10383,10 @@
         <v>18.0</v>
       </c>
       <c r="E279" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F279" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>578</v>
       </c>
       <c r="G279" s="9">
         <v>46794.0</v>
@@ -10402,7 +10397,7 @@
         <v>1.775786585712E12</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>34</v>
@@ -10411,7 +10406,7 @@
         <v>19.0</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>478</v>
@@ -10434,7 +10429,7 @@
         <v>21.0</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>17</v>
@@ -10457,7 +10452,7 @@
         <v>16.0</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>17</v>
@@ -10480,7 +10475,7 @@
         <v>4.0</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>17</v>
@@ -10503,7 +10498,7 @@
         <v>4.0</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>17</v>
@@ -10518,7 +10513,7 @@
         <v>1.776059127998E12</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>34</v>
@@ -10527,7 +10522,7 @@
         <v>19.0</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>478</v>
@@ -10541,7 +10536,7 @@
         <v>1.77605914796E12</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>34</v>
@@ -10550,7 +10545,7 @@
         <v>19.0</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>478</v>
@@ -10573,7 +10568,7 @@
         <v>18.0</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F287" s="4"/>
       <c r="G287" s="9">
@@ -10594,10 +10589,10 @@
         <v>9.0</v>
       </c>
       <c r="E288" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F288" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="F288" s="3" t="s">
-        <v>587</v>
       </c>
       <c r="G288" s="9">
         <v>46577.0</v>
@@ -10617,7 +10612,7 @@
         <v>9.0</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>363</v>
@@ -10640,10 +10635,10 @@
         <v>12.0</v>
       </c>
       <c r="E290" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F290" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="F290" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="G290" s="9">
         <v>46596.0</v>
@@ -10654,7 +10649,7 @@
         <v>1.77613942855E12</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>26</v>
@@ -10663,7 +10658,7 @@
         <v>2.0</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>140</v>
@@ -10686,7 +10681,7 @@
         <v>2.0</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>377</v>
@@ -10709,7 +10704,7 @@
         <v>3.0</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F293" s="4"/>
     </row>
@@ -10727,7 +10722,7 @@
         <v>5.0</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>17</v>
@@ -10753,7 +10748,7 @@
         <v>5.0</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>432</v>
@@ -10779,7 +10774,7 @@
         <v>5.0</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>17</v>
@@ -10854,7 +10849,7 @@
         <v>4.0</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>17</v>
@@ -10874,7 +10869,7 @@
         <v>4.0</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>17</v>
@@ -10897,7 +10892,7 @@
         <v>5.0</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>17</v>
@@ -10920,7 +10915,7 @@
         <v>4.0</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>25</v>
@@ -10943,7 +10938,7 @@
         <v>4.0</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>25</v>
@@ -10969,7 +10964,7 @@
         <v>4.0</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>25</v>
@@ -10992,7 +10987,7 @@
         <v>4.0</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>25</v>
@@ -11015,7 +11010,7 @@
         <v>2.0</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>17</v>
@@ -11038,7 +11033,7 @@
         <v>2.0</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>17</v>
@@ -11061,7 +11056,7 @@
         <v>2.0</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>17</v>
@@ -11084,10 +11079,10 @@
         <v>6.0</v>
       </c>
       <c r="E309" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F309" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="F309" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="G309" s="9">
         <v>46269.0</v>
@@ -11110,10 +11105,10 @@
         <v>12.0</v>
       </c>
       <c r="E310" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="F310" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="F310" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="G310" s="9">
         <v>46234.0</v>
@@ -11136,10 +11131,10 @@
         <v>14.0</v>
       </c>
       <c r="E311" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F311" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="F311" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="G311" s="9">
         <v>46202.0</v>
@@ -11162,10 +11157,10 @@
         <v>14.0</v>
       </c>
       <c r="E312" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F312" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="F312" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="G312" s="9">
         <v>46203.0</v>
@@ -11179,7 +11174,7 @@
         <v>1.776169705463E12</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>12</v>
@@ -11198,7 +11193,7 @@
         <v>1.776301247869E12</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>12</v>
@@ -11207,7 +11202,7 @@
         <v>5.0</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F314" s="4"/>
       <c r="G314" s="9">
@@ -11220,7 +11215,7 @@
         <v>1.776301425645E12</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>12</v>
@@ -11229,7 +11224,7 @@
         <v>18.0</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>218</v>
@@ -11243,7 +11238,7 @@
         <v>1.776327582548E12</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>12</v>
@@ -11252,7 +11247,7 @@
         <v>3.0</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F316" s="3">
         <v>11504.0</v>
@@ -11263,7 +11258,7 @@
         <v>1.776327623153E12</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>34</v>
@@ -11272,10 +11267,10 @@
         <v>4.0</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G317" s="9">
         <v>46949.0</v>
@@ -11286,7 +11281,7 @@
         <v>1.776327677276E12</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>34</v>
@@ -11295,10 +11290,10 @@
         <v>5.0</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G318" s="9">
         <v>46949.0</v>
@@ -11309,7 +11304,7 @@
         <v>1.776328486516E12</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>26</v>
@@ -11318,7 +11313,7 @@
         <v>9.0</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>409</v>
@@ -11330,7 +11325,7 @@
         <v>1.776328499394E12</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>26</v>
@@ -11339,7 +11334,7 @@
         <v>10.0</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>409</v>
@@ -11350,7 +11345,7 @@
         <v>1.776328514002E12</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>26</v>
@@ -11359,7 +11354,7 @@
         <v>9.0</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>409</v>
@@ -11370,7 +11365,7 @@
         <v>1.776334155137E12</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>26</v>
@@ -11379,7 +11374,7 @@
         <v>13.0</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>231</v>
@@ -11393,7 +11388,7 @@
         <v>1.776334203307E12</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>26</v>
@@ -11416,7 +11411,7 @@
         <v>1.776334423117E12</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>26</v>
@@ -11425,7 +11420,7 @@
         <v>16.0</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>231</v>
@@ -11439,7 +11434,7 @@
         <v>1.776334444257E12</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>28</v>
@@ -11448,7 +11443,7 @@
         <v>16.0</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>234</v>
@@ -11462,7 +11457,7 @@
         <v>1.776334474615E12</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>26</v>
@@ -11471,7 +11466,7 @@
         <v>16.0</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>234</v>
@@ -11485,7 +11480,7 @@
         <v>1.776334496105E12</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>26</v>
@@ -11494,7 +11489,7 @@
         <v>16.0</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F327" s="4"/>
     </row>
@@ -11503,7 +11498,7 @@
         <v>1.776334545035E12</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>26</v>
@@ -11512,7 +11507,7 @@
         <v>16.0</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>234</v>
@@ -11526,7 +11521,7 @@
         <v>1.776398987942E12</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>28</v>
@@ -11535,10 +11530,10 @@
         <v>17.0</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G329" s="9">
         <v>46947.0</v>
@@ -11549,7 +11544,7 @@
         <v>1.776399071673E12</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>28</v>
@@ -11558,10 +11553,10 @@
         <v>17.0</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G330" s="9">
         <v>46771.0</v>
@@ -11572,7 +11567,7 @@
         <v>1.776399111607E12</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>34</v>
@@ -11581,7 +11576,7 @@
         <v>17.0</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>478</v>
@@ -11595,7 +11590,7 @@
         <v>1.776399379582E12</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>12</v>
@@ -11604,16 +11599,16 @@
         <v>20.0</v>
       </c>
       <c r="E332" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F332" s="3" t="s">
         <v>629</v>
-      </c>
-      <c r="F332" s="3" t="s">
-        <v>630</v>
       </c>
       <c r="G332" s="9">
         <v>46691.0</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="333">
@@ -11621,7 +11616,7 @@
         <v>1.776400103874E12</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>26</v>
@@ -11630,7 +11625,7 @@
         <v>11.0</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>143</v>
@@ -11644,7 +11639,7 @@
         <v>1.776400120665E12</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>26</v>
@@ -11653,7 +11648,7 @@
         <v>12.0</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>231</v>
@@ -11667,7 +11662,7 @@
         <v>1.77640716912E12</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>26</v>
@@ -11676,7 +11671,7 @@
         <v>7.0</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F335" s="3">
         <v>11503.0</v>
@@ -11690,7 +11685,7 @@
         <v>1.776407375241E12</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>26</v>
@@ -11699,10 +11694,10 @@
         <v>11.0</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G336" s="9">
         <v>46669.0</v>
@@ -11713,7 +11708,7 @@
         <v>1.77640744785E12</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>26</v>
@@ -11722,10 +11717,10 @@
         <v>12.0</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G337" s="9">
         <v>46523.0</v>
@@ -11745,7 +11740,7 @@
         <v>12.0</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F338" s="4"/>
       <c r="G338" s="9">
@@ -11775,7 +11770,7 @@
         <v>1.776659068274E12</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>26</v>
@@ -11784,10 +11779,10 @@
         <v>1.0</v>
       </c>
       <c r="E340" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="F340" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="F340" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="G340" s="9">
         <v>46793.0</v>
@@ -11795,10 +11790,10 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>34</v>
@@ -11807,10 +11802,10 @@
         <v>9.0</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G341" s="9">
         <v>46949.0</v>
@@ -11818,10 +11813,10 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>34</v>
@@ -11830,10 +11825,10 @@
         <v>20.0</v>
       </c>
       <c r="E342" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F342" s="3" t="s">
         <v>642</v>
-      </c>
-      <c r="F342" s="3" t="s">
-        <v>643</v>
       </c>
       <c r="G342" s="9">
         <v>46793.0</v>
@@ -11841,10 +11836,10 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>12</v>
@@ -11853,10 +11848,10 @@
         <v>16.0</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G343" s="9">
         <v>46639.0</v>
@@ -11864,7 +11859,7 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>11</v>
@@ -11876,13 +11871,13 @@
         <v>3.0</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F344" s="4"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>11</v>
@@ -11894,13 +11889,13 @@
         <v>4.0</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F345" s="4"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>11</v>
@@ -11912,13 +11907,13 @@
         <v>5.0</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F346" s="4"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>11</v>
@@ -11930,13 +11925,13 @@
         <v>5.0</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F347" s="4"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>11</v>
@@ -11948,13 +11943,13 @@
         <v>5.0</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F348" s="4"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>11</v>
@@ -11966,13 +11961,13 @@
         <v>5.0</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F349" s="4"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>11</v>
@@ -11984,13 +11979,13 @@
         <v>1.0</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F350" s="4"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>33</v>
@@ -12002,7 +11997,7 @@
         <v>2.0</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>285</v>
@@ -12010,7 +12005,7 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>33</v>
@@ -12022,7 +12017,7 @@
         <v>2.0</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>338</v>
@@ -12033,7 +12028,7 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>33</v>
@@ -12045,15 +12040,15 @@
         <v>2.0</v>
       </c>
       <c r="E353" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F353" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="F353" s="3" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>33</v>
@@ -12065,7 +12060,7 @@
         <v>4.0</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>285</v>
@@ -12077,10 +12072,10 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>12</v>
@@ -12089,7 +12084,7 @@
         <v>10.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F355" s="3">
         <v>11504.0</v>
@@ -12100,10 +12095,10 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>12</v>
@@ -12112,7 +12107,7 @@
         <v>8.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F356" s="3">
         <v>11504.0</v>
@@ -12121,7 +12116,7 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>33</v>
@@ -12133,14 +12128,14 @@
         <v>3.0</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F357" s="4"/>
       <c r="H357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>33</v>
@@ -12152,24 +12147,24 @@
         <v>11.0</v>
       </c>
       <c r="E358" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="F358" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="F358" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="G358" s="9">
         <v>46240.0</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>12</v>
@@ -12178,10 +12173,10 @@
         <v>13.0</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G359" s="9">
         <v>46416.0</v>
@@ -12189,10 +12184,10 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>12</v>
@@ -12201,10 +12196,10 @@
         <v>16.0</v>
       </c>
       <c r="E360" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F360" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="F360" s="3" t="s">
-        <v>680</v>
       </c>
       <c r="G360" s="9">
         <v>46544.0</v>
@@ -12212,10 +12207,10 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>28</v>
@@ -12224,10 +12219,10 @@
         <v>16.0</v>
       </c>
       <c r="E361" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F361" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="F361" s="3" t="s">
-        <v>683</v>
       </c>
       <c r="G361" s="9">
         <v>46794.0</v>
@@ -12236,10 +12231,10 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>28</v>
@@ -12248,10 +12243,10 @@
         <v>16.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G362" s="9">
         <v>46785.0</v>
@@ -12259,10 +12254,10 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>28</v>
@@ -12271,10 +12266,10 @@
         <v>16.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G363" s="9">
         <v>46789.0</v>
@@ -12282,10 +12277,10 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>28</v>
@@ -12294,10 +12289,10 @@
         <v>16.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G364" s="9">
         <v>46839.0</v>
@@ -12305,10 +12300,10 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>12</v>
@@ -12317,10 +12312,10 @@
         <v>11.0</v>
       </c>
       <c r="E365" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="F365" s="3" t="s">
         <v>690</v>
-      </c>
-      <c r="F365" s="3" t="s">
-        <v>691</v>
       </c>
       <c r="G365" s="9">
         <v>46312.0</v>
@@ -12331,10 +12326,10 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>12</v>
@@ -12343,10 +12338,10 @@
         <v>17.0</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G366" s="9">
         <v>46669.0</v>
@@ -12355,10 +12350,10 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>28</v>
@@ -12367,10 +12362,10 @@
         <v>7.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G367" s="9">
         <v>46794.0</v>
@@ -12378,10 +12373,10 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>28</v>
@@ -12390,10 +12385,10 @@
         <v>7.0</v>
       </c>
       <c r="E368" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="F368" s="3" t="s">
         <v>697</v>
-      </c>
-      <c r="F368" s="3" t="s">
-        <v>698</v>
       </c>
       <c r="G368" s="9">
         <v>46792.0</v>
@@ -12401,10 +12396,10 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>12</v>
@@ -12413,7 +12408,7 @@
         <v>6.0</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F369" s="3">
         <v>11504.0</v>
@@ -12422,10 +12417,10 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>12</v>
@@ -12434,7 +12429,7 @@
         <v>9.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F370" s="3">
         <v>115004.0</v>
@@ -12445,7 +12440,7 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>33</v>
@@ -12457,7 +12452,7 @@
         <v>3.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F371" s="3">
         <v>11505.0</v>
@@ -12465,7 +12460,7 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>33</v>
@@ -12477,7 +12472,7 @@
         <v>11.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>226</v>
@@ -12494,7 +12489,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>33</v>
@@ -12506,13 +12501,13 @@
         <v>22.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F373" s="4"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>33</v>
@@ -12524,7 +12519,7 @@
         <v>11.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>319</v>
@@ -12541,10 +12536,10 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>12</v>
@@ -12553,10 +12548,10 @@
         <v>20.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G375" s="9">
         <v>46596.0</v>
@@ -12564,10 +12559,10 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>26</v>
@@ -12576,10 +12571,10 @@
         <v>16.0</v>
       </c>
       <c r="E376" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F376" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="F376" s="3" t="s">
-        <v>715</v>
       </c>
       <c r="G376" s="9">
         <v>46669.0</v>
@@ -12587,7 +12582,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>33</v>
@@ -12599,7 +12594,7 @@
         <v>9.0</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>399</v>
@@ -12607,7 +12602,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>33</v>
@@ -12619,7 +12614,7 @@
         <v>10.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>409</v>
@@ -12627,7 +12622,7 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>33</v>
@@ -12636,10 +12631,10 @@
         <v>26</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G379" s="9">
         <v>46410.0</v>
@@ -12647,7 +12642,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>33</v>
@@ -12659,16 +12654,16 @@
         <v>22.0</v>
       </c>
       <c r="E380" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F380" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="F380" s="3" t="s">
-        <v>723</v>
       </c>
       <c r="G380" s="9">
         <v>46194.0</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I380" s="2" t="s">
         <v>223</v>
@@ -12676,7 +12671,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>33</v>
@@ -12688,10 +12683,10 @@
         <v>5.0</v>
       </c>
       <c r="E381" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="F381" s="3" t="s">
         <v>726</v>
-      </c>
-      <c r="F381" s="3" t="s">
-        <v>727</v>
       </c>
       <c r="G381" s="9">
         <v>46257.0</v>
@@ -12699,10 +12694,10 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C382" s="2" t="s">
         <v>34</v>
@@ -12711,10 +12706,10 @@
         <v>7.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G382" s="9">
         <v>46913.0</v>
@@ -12722,7 +12717,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>11</v>
@@ -12734,7 +12729,7 @@
         <v>2.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>218</v>
@@ -12742,7 +12737,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>11</v>
@@ -12762,7 +12757,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>11</v>
@@ -12774,7 +12769,7 @@
         <v>2.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>17</v>
@@ -12782,7 +12777,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>11</v>
@@ -12794,7 +12789,7 @@
         <v>2.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>38</v>
@@ -12805,7 +12800,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>11</v>
@@ -12817,7 +12812,7 @@
         <v>3.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F387" s="4"/>
       <c r="G387" s="9">
@@ -12826,7 +12821,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>33</v>
@@ -12838,10 +12833,10 @@
         <v>4.0</v>
       </c>
       <c r="E388" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="F388" s="3" t="s">
         <v>739</v>
-      </c>
-      <c r="F388" s="3" t="s">
-        <v>740</v>
       </c>
       <c r="G388" s="9">
         <v>46507.0</v>
@@ -12849,7 +12844,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>33</v>
@@ -12861,10 +12856,10 @@
         <v>4.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F389" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G389" s="9">
         <v>46484.0</v>
@@ -12872,10 +12867,10 @@
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>34</v>
@@ -12893,7 +12888,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>33</v>
@@ -12905,18 +12900,18 @@
         <v>5.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>12</v>
@@ -12925,7 +12920,7 @@
         <v>1.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>263</v>
@@ -12935,15 +12930,15 @@
       </c>
       <c r="H392" s="2"/>
       <c r="J392" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>26</v>
@@ -12952,10 +12947,10 @@
         <v>17.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G393" s="9">
         <v>46408.0</v>
@@ -12963,10 +12958,10 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>26</v>
@@ -12975,10 +12970,10 @@
         <v>17.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F394" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G394" s="9">
         <v>46473.0</v>
@@ -12986,10 +12981,10 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>26</v>
@@ -12998,10 +12993,10 @@
         <v>17.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G395" s="9">
         <v>46758.0</v>
@@ -13009,10 +13004,10 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>26</v>
@@ -13021,10 +13016,10 @@
         <v>17.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G396" s="9">
         <v>46431.0</v>
@@ -13032,10 +13027,10 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>26</v>
@@ -13044,10 +13039,10 @@
         <v>14.0</v>
       </c>
       <c r="E397" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="F397" s="3" t="s">
         <v>757</v>
-      </c>
-      <c r="F397" s="3" t="s">
-        <v>758</v>
       </c>
       <c r="G397" s="9">
         <v>46523.0</v>
@@ -13055,10 +13050,10 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>34</v>
@@ -13067,7 +13062,7 @@
         <v>22.0</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>218</v>
@@ -13075,10 +13070,10 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>28</v>
@@ -13087,7 +13082,7 @@
         <v>12.0</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>218</v>
@@ -13095,7 +13090,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>33</v>
@@ -13107,7 +13102,7 @@
         <v>19.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>218</v>
@@ -13115,7 +13110,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>33</v>
@@ -13127,7 +13122,7 @@
         <v>6.0</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>218</v>
@@ -13135,10 +13130,10 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C402" s="2" t="s">
         <v>12</v>
@@ -13147,7 +13142,7 @@
         <v>14.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>234</v>
@@ -13158,7 +13153,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>33</v>
@@ -13170,18 +13165,18 @@
         <v>10.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>478</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>33</v>
@@ -13193,7 +13188,7 @@
         <v>18.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>478</v>
@@ -13204,7 +13199,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>33</v>
@@ -13216,21 +13211,21 @@
         <v>10.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>478</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C406" s="2" t="s">
         <v>12</v>
@@ -13239,10 +13234,10 @@
         <v>18.0</v>
       </c>
       <c r="E406" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="F406" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="F406" s="3" t="s">
-        <v>778</v>
       </c>
       <c r="G406" s="9">
         <v>46666.0</v>
@@ -13253,7 +13248,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>33</v>
@@ -13265,10 +13260,10 @@
         <v>8.0</v>
       </c>
       <c r="E407" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="F407" s="3" t="s">
         <v>780</v>
-      </c>
-      <c r="F407" s="3" t="s">
-        <v>781</v>
       </c>
       <c r="G407" s="9">
         <v>46604.0</v>
@@ -13276,7 +13271,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>33</v>
@@ -13288,10 +13283,10 @@
         <v>8.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G408" s="9">
         <v>46626.0</v>
@@ -13299,7 +13294,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>33</v>
@@ -13311,10 +13306,10 @@
         <v>8.0</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G409" s="9">
         <v>46658.0</v>
@@ -13322,7 +13317,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>33</v>
@@ -13334,10 +13329,10 @@
         <v>8.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G410" s="9">
         <v>46669.0</v>
@@ -13345,7 +13340,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>11</v>
@@ -13357,13 +13352,13 @@
         <v>4.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F411" s="4"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>33</v>
@@ -13375,7 +13370,7 @@
         <v>11.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>478</v>
@@ -13383,7 +13378,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>33</v>
@@ -13395,10 +13390,10 @@
         <v>8.0</v>
       </c>
       <c r="E413" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F413" s="3" t="s">
         <v>792</v>
-      </c>
-      <c r="F413" s="3" t="s">
-        <v>793</v>
       </c>
       <c r="G413" s="9">
         <v>46304.0</v>
@@ -13406,7 +13401,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>33</v>
@@ -13418,7 +13413,7 @@
         <v>19.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>53</v>
@@ -13429,7 +13424,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>33</v>
@@ -13441,10 +13436,10 @@
         <v>20.0</v>
       </c>
       <c r="E415" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="F415" s="3" t="s">
         <v>796</v>
-      </c>
-      <c r="F415" s="3" t="s">
-        <v>797</v>
       </c>
       <c r="G415" s="9">
         <v>46877.0</v>
@@ -13452,7 +13447,7 @@
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>33</v>
@@ -13464,7 +13459,7 @@
         <v>12.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F416" s="3" t="s">
         <v>38</v>
@@ -13475,10 +13470,10 @@
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C417" s="2" t="s">
         <v>12</v>
@@ -13487,10 +13482,10 @@
         <v>20.0</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G417" s="9">
         <v>46794.0</v>
@@ -13498,10 +13493,10 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C418" s="2" t="s">
         <v>26</v>
@@ -13510,10 +13505,10 @@
         <v>18.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G418" s="9">
         <v>46794.0</v>
@@ -13521,10 +13516,10 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>26</v>
@@ -13533,10 +13528,10 @@
         <v>13.0</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G419" s="9">
         <v>46484.0</v>
@@ -13544,10 +13539,10 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C420" s="2" t="s">
         <v>28</v>
@@ -13556,10 +13551,10 @@
         <v>20.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G420" s="9">
         <v>46792.0</v>
@@ -13567,7 +13562,7 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>33</v>
@@ -13579,10 +13574,10 @@
         <v>9.0</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G421" s="9">
         <v>46676.0</v>
@@ -13590,7 +13585,7 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>33</v>
@@ -13602,16 +13597,16 @@
         <v>9.0</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F422" s="4"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>12</v>
@@ -13620,10 +13615,10 @@
         <v>12.0</v>
       </c>
       <c r="E423" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F423" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G423" s="9">
         <v>46641.0</v>
@@ -13631,10 +13626,10 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C424" s="2" t="s">
         <v>12</v>
@@ -13643,10 +13638,10 @@
         <v>11.0</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G424" s="9">
         <v>46530.0</v>
@@ -13654,10 +13649,10 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>12</v>
@@ -13666,10 +13661,10 @@
         <v>13.0</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G425" s="9">
         <v>46949.0</v>
@@ -13677,10 +13672,10 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C426" s="2" t="s">
         <v>26</v>
@@ -13689,10 +13684,10 @@
         <v>3.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G426" s="9">
         <v>46670.0</v>
@@ -13700,10 +13695,10 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>26</v>
@@ -13712,7 +13707,7 @@
         <v>3.0</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>440</v>
@@ -13723,10 +13718,10 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>26</v>
@@ -13735,7 +13730,7 @@
         <v>3.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>440</v>
@@ -13746,7 +13741,7 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>33</v>
@@ -13758,10 +13753,10 @@
         <v>3.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G429" s="9">
         <v>46670.0</v>
@@ -13769,7 +13764,7 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>33</v>
@@ -13781,7 +13776,7 @@
         <v>3.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>440</v>
@@ -13792,7 +13787,7 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>33</v>
@@ -13804,7 +13799,7 @@
         <v>3.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>47</v>
@@ -13815,10 +13810,10 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C432" s="2" t="s">
         <v>26</v>
@@ -13827,15 +13822,15 @@
         <v>19.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>33</v>
@@ -13847,10 +13842,10 @@
         <v>3.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G433" s="9">
         <v>46670.0</v>
@@ -13861,7 +13856,7 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>33</v>
@@ -13873,10 +13868,10 @@
         <v>7.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F434" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G434" s="9">
         <v>46725.0</v>
@@ -13884,10 +13879,10 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C435" s="2" t="s">
         <v>12</v>
@@ -13896,7 +13891,7 @@
         <v>22.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>140</v>
@@ -13907,10 +13902,10 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>12</v>
@@ -13919,10 +13914,10 @@
         <v>22.0</v>
       </c>
       <c r="E436" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="F436" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="F436" s="3" t="s">
-        <v>830</v>
       </c>
       <c r="G436" s="9">
         <v>46670.0</v>
@@ -13930,7 +13925,7 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>33</v>
@@ -13942,10 +13937,10 @@
         <v>17.0</v>
       </c>
       <c r="E437" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F437" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="F437" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="G437" s="9">
         <v>46254.0</v>
@@ -13954,7 +13949,7 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>33</v>
@@ -13966,7 +13961,7 @@
         <v>11.0</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F438" s="3" t="s">
         <v>394</v>
@@ -13977,7 +13972,7 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>33</v>
@@ -13989,10 +13984,10 @@
         <v>6.0</v>
       </c>
       <c r="E439" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F439" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="F439" s="3" t="s">
-        <v>838</v>
       </c>
       <c r="G439" s="9">
         <v>46669.0</v>
@@ -14000,7 +13995,7 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>33</v>
@@ -14012,10 +14007,10 @@
         <v>6.0</v>
       </c>
       <c r="E440" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F440" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="F440" s="3" t="s">
-        <v>841</v>
       </c>
       <c r="G440" s="9">
         <v>46669.0</v>
@@ -14023,7 +14018,7 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>33</v>
@@ -14035,10 +14030,10 @@
         <v>6.0</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G441" s="9">
         <v>46669.0</v>
@@ -14046,7 +14041,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>33</v>
@@ -14058,10 +14053,10 @@
         <v>6.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G442" s="9">
         <v>46669.0</v>
@@ -14069,7 +14064,7 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>33</v>
@@ -14081,10 +14076,10 @@
         <v>18.0</v>
       </c>
       <c r="E443" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="F443" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="F443" s="3" t="s">
-        <v>847</v>
       </c>
       <c r="G443" s="9">
         <v>46947.0</v>
@@ -14092,7 +14087,7 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>33</v>
@@ -14104,10 +14099,10 @@
         <v>18.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G444" s="9">
         <v>46949.0</v>
@@ -14115,7 +14110,7 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>33</v>
@@ -14127,10 +14122,10 @@
         <v>18.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G445" s="9">
         <v>46949.0</v>
@@ -14138,7 +14133,7 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>33</v>
@@ -14150,15 +14145,15 @@
         <v>18.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>33</v>
@@ -14170,7 +14165,7 @@
         <v>3.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>45</v>
@@ -14181,7 +14176,7 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>33</v>
@@ -14193,7 +14188,7 @@
         <v>4.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>338</v>
@@ -14201,7 +14196,7 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>33</v>
@@ -14213,7 +14208,7 @@
         <v>1.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>118</v>
@@ -14221,7 +14216,7 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>33</v>
@@ -14233,7 +14228,7 @@
         <v>2.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>432</v>
@@ -14244,7 +14239,7 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>33</v>
@@ -14256,7 +14251,7 @@
         <v>8.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>351</v>
@@ -14267,10 +14262,10 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>12</v>
@@ -14279,7 +14274,7 @@
         <v>20.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>458</v>
@@ -14290,7 +14285,7 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>33</v>
@@ -14302,10 +14297,10 @@
         <v>13.0</v>
       </c>
       <c r="E453" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F453" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="F453" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="G453" s="9">
         <v>46669.0</v>
@@ -14313,7 +14308,7 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>33</v>
@@ -14325,10 +14320,10 @@
         <v>7.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F454" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G454" s="9">
         <v>46775.0</v>
@@ -14337,7 +14332,7 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>33</v>
@@ -14349,13 +14344,13 @@
         <v>11.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F455" s="4"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>33</v>
@@ -14367,13 +14362,13 @@
         <v>11.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F456" s="4"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>33</v>
@@ -14385,13 +14380,13 @@
         <v>11.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F457" s="4"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>33</v>
@@ -14403,13 +14398,13 @@
         <v>11.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F458" s="4"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>33</v>
@@ -14421,10 +14416,10 @@
         <v>22.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G459" s="9">
         <v>46222.0</v>
@@ -14432,7 +14427,7 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>33</v>
@@ -14444,13 +14439,13 @@
         <v>11.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F460" s="4"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>33</v>
@@ -14462,13 +14457,13 @@
         <v>11.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F461" s="4"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>33</v>
@@ -14480,13 +14475,13 @@
         <v>11.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F462" s="4"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>33</v>
@@ -14498,13 +14493,13 @@
         <v>11.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F463" s="4"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>33</v>
@@ -14516,7 +14511,7 @@
         <v>14.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F464" s="4"/>
       <c r="G464" s="9">
@@ -14525,7 +14520,7 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>33</v>
@@ -14537,7 +14532,7 @@
         <v>14.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F465" s="4"/>
       <c r="G465" s="9">
@@ -14546,7 +14541,7 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>33</v>
@@ -14558,7 +14553,7 @@
         <v>15.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F466" s="4"/>
       <c r="G466" s="9">
@@ -14567,7 +14562,7 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>33</v>
@@ -14579,7 +14574,7 @@
         <v>15.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F467" s="4"/>
       <c r="G467" s="9">
@@ -14588,7 +14583,7 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>33</v>
@@ -14600,7 +14595,7 @@
         <v>15.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F468" s="4"/>
       <c r="G468" s="9">
@@ -14609,7 +14604,7 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>33</v>
@@ -14621,7 +14616,7 @@
         <v>15.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F469" s="4"/>
       <c r="G469" s="9">
@@ -14630,7 +14625,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>33</v>
@@ -14642,7 +14637,7 @@
         <v>11.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F470" s="4"/>
       <c r="G470" s="9">
@@ -14651,7 +14646,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>33</v>
@@ -14663,7 +14658,7 @@
         <v>11.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F471" s="4"/>
       <c r="G471" s="9">
@@ -14672,10 +14667,10 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C472" s="2" t="s">
         <v>26</v>
@@ -14684,7 +14679,7 @@
         <v>8.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F472" s="3" t="s">
         <v>409</v>
@@ -14692,7 +14687,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>33</v>
@@ -14704,13 +14699,13 @@
         <v>12.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F473" s="4"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>33</v>
@@ -14722,7 +14717,7 @@
         <v>15.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>409</v>
@@ -14733,7 +14728,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>521</v>
@@ -14745,7 +14740,7 @@
         <v>3.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>38</v>
@@ -14756,7 +14751,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>521</v>
@@ -14768,7 +14763,7 @@
         <v>3.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F476" s="3" t="s">
         <v>38</v>
@@ -14779,7 +14774,7 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>521</v>
@@ -14791,7 +14786,7 @@
         <v>3.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>38</v>
@@ -14802,7 +14797,7 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>521</v>
@@ -14814,7 +14809,7 @@
         <v>3.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>38</v>
@@ -14825,7 +14820,7 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>521</v>
@@ -14837,7 +14832,7 @@
         <v>3.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>399</v>
@@ -14848,7 +14843,7 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>521</v>
@@ -14860,7 +14855,7 @@
         <v>3.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>38</v>
@@ -14871,7 +14866,7 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>521</v>
@@ -14883,7 +14878,7 @@
         <v>4.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F481" s="3" t="s">
         <v>38</v>
@@ -14894,7 +14889,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>521</v>
@@ -14906,7 +14901,7 @@
         <v>4.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F482" s="3" t="s">
         <v>38</v>
@@ -14917,7 +14912,7 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>521</v>
@@ -14929,7 +14924,7 @@
         <v>4.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F483" s="3" t="s">
         <v>38</v>
@@ -14940,7 +14935,7 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>521</v>
@@ -14952,7 +14947,7 @@
         <v>4.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F484" s="3" t="s">
         <v>38</v>
@@ -14963,7 +14958,7 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>521</v>
@@ -14975,7 +14970,7 @@
         <v>6.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F485" s="3" t="s">
         <v>38</v>
@@ -14986,7 +14981,7 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>521</v>
@@ -14998,7 +14993,7 @@
         <v>6.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F486" s="3" t="s">
         <v>38</v>
@@ -15009,7 +15004,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>521</v>
@@ -15021,7 +15016,7 @@
         <v>6.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F487" s="3" t="s">
         <v>38</v>
@@ -15032,7 +15027,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>521</v>
@@ -15044,7 +15039,7 @@
         <v>6.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F488" s="3" t="s">
         <v>38</v>
@@ -15055,7 +15050,7 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>521</v>
@@ -15067,7 +15062,7 @@
         <v>6.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F489" s="3" t="s">
         <v>38</v>
@@ -15078,7 +15073,7 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>521</v>
@@ -15090,7 +15085,7 @@
         <v>6.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F490" s="3" t="s">
         <v>38</v>
@@ -15101,7 +15096,7 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>521</v>
@@ -15113,7 +15108,7 @@
         <v>7.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F491" s="3" t="s">
         <v>17</v>
@@ -15124,7 +15119,7 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>521</v>
@@ -15136,7 +15131,7 @@
         <v>7.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F492" s="3" t="s">
         <v>17</v>
@@ -15147,7 +15142,7 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>521</v>
@@ -15159,7 +15154,7 @@
         <v>7.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F493" s="3" t="s">
         <v>17</v>
@@ -15170,7 +15165,7 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>521</v>
@@ -15182,7 +15177,7 @@
         <v>8.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>17</v>
@@ -15193,7 +15188,7 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>521</v>
@@ -15205,7 +15200,7 @@
         <v>8.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>17</v>
@@ -15216,7 +15211,7 @@
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>521</v>
@@ -15228,7 +15223,7 @@
         <v>8.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>17</v>
@@ -15239,7 +15234,7 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>521</v>
@@ -15251,7 +15246,7 @@
         <v>8.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F497" s="3" t="s">
         <v>17</v>
@@ -15262,7 +15257,7 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>521</v>
@@ -15274,7 +15269,7 @@
         <v>9.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F498" s="3" t="s">
         <v>478</v>
@@ -15285,7 +15280,7 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>521</v>
@@ -15297,7 +15292,7 @@
         <v>12.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>38</v>
@@ -15309,7 +15304,7 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>521</v>
@@ -15321,7 +15316,7 @@
         <v>12.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>399</v>
@@ -15330,12 +15325,12 @@
         <v>46211.0</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>521</v>
@@ -15347,7 +15342,7 @@
         <v>12.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>399</v>
@@ -15356,7 +15351,7 @@
         <v>46204.0</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="I501" s="2" t="s">
         <v>223</v>
@@ -15364,7 +15359,7 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>521</v>
@@ -15376,7 +15371,7 @@
         <v>12.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>377</v>
@@ -15387,7 +15382,7 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>521</v>
@@ -15399,7 +15394,7 @@
         <v>13.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>478</v>
@@ -15410,7 +15405,7 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>521</v>
@@ -15422,7 +15417,7 @@
         <v>14.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F504" s="4"/>
       <c r="G504" s="9">
@@ -15431,7 +15426,7 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>519</v>
@@ -15443,7 +15438,7 @@
         <v>2.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F505" s="3" t="s">
         <v>406</v>
@@ -15454,7 +15449,7 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>519</v>
@@ -15466,7 +15461,7 @@
         <v>2.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>406</v>
@@ -15477,7 +15472,7 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>519</v>
@@ -15489,10 +15484,10 @@
         <v>11.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G507" s="9">
         <v>46242.0</v>
@@ -15500,7 +15495,7 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>519</v>
@@ -15512,10 +15507,10 @@
         <v>16.0</v>
       </c>
       <c r="E508" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F508" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="F508" s="3" t="s">
-        <v>972</v>
       </c>
       <c r="G508" s="9">
         <v>46274.0</v>
@@ -15524,10 +15519,10 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>26</v>
@@ -15536,10 +15531,10 @@
         <v>1.0</v>
       </c>
       <c r="E509" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="F509" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="F509" s="3" t="s">
-        <v>975</v>
       </c>
       <c r="G509" s="9">
         <v>46743.0</v>
@@ -15547,7 +15542,7 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>519</v>
@@ -15559,16 +15554,16 @@
         <v>15.0</v>
       </c>
       <c r="E510" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="F510" s="3" t="s">
         <v>977</v>
-      </c>
-      <c r="F510" s="3" t="s">
-        <v>978</v>
       </c>
       <c r="G510" s="9">
         <v>46215.0</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="I510" s="2" t="s">
         <v>223</v>
@@ -15576,7 +15571,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>519</v>
@@ -15588,16 +15583,16 @@
         <v>21.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F511" s="4"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C512" s="2" t="s">
         <v>12</v>
@@ -15606,7 +15601,7 @@
         <v>20.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F512" s="3" t="s">
         <v>226</v>
@@ -15617,7 +15612,7 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>33</v>
@@ -15629,10 +15624,10 @@
         <v>5.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F513" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G513" s="9">
         <v>46769.0</v>
@@ -15640,7 +15635,7 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>33</v>
@@ -15652,10 +15647,10 @@
         <v>6.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G514" s="9">
         <v>46769.0</v>
@@ -15663,7 +15658,7 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>519</v>
@@ -15675,10 +15670,10 @@
         <v>3.0</v>
       </c>
       <c r="E515" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="F515" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="F515" s="3" t="s">
-        <v>987</v>
       </c>
       <c r="G515" s="9">
         <v>46261.0</v>
@@ -15686,7 +15681,7 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>519</v>
@@ -15698,10 +15693,10 @@
         <v>3.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G516" s="9">
         <v>46266.0</v>
@@ -15709,7 +15704,7 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>519</v>
@@ -15721,10 +15716,10 @@
         <v>3.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F517" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G517" s="9">
         <v>46223.0</v>
@@ -15732,7 +15727,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>519</v>
@@ -15744,10 +15739,10 @@
         <v>3.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G518" s="9">
         <v>46266.0</v>
@@ -15755,7 +15750,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>33</v>
@@ -15767,10 +15762,10 @@
         <v>3.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G519" s="9">
         <v>46769.0</v>
@@ -15778,10 +15773,10 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C520" s="2" t="s">
         <v>28</v>
@@ -15790,10 +15785,10 @@
         <v>14.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F520" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G520" s="9">
         <v>46814.0</v>
@@ -15801,10 +15796,10 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C521" s="2" t="s">
         <v>28</v>
@@ -15813,10 +15808,10 @@
         <v>14.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F521" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G521" s="9">
         <v>46820.0</v>
@@ -15824,10 +15819,10 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C522" s="2" t="s">
         <v>28</v>
@@ -15836,10 +15831,10 @@
         <v>14.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G522" s="9">
         <v>46820.0</v>
@@ -15847,10 +15842,10 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C523" s="2" t="s">
         <v>28</v>
@@ -15859,10 +15854,10 @@
         <v>14.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G523" s="9">
         <v>46998.0</v>
@@ -15870,7 +15865,7 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>33</v>
@@ -15882,10 +15877,10 @@
         <v>2.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F524" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G524" s="9">
         <v>46484.0</v>
@@ -15893,7 +15888,7 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>33</v>
@@ -15905,10 +15900,10 @@
         <v>2.0</v>
       </c>
       <c r="E525" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F525" s="3" t="s">
         <v>1005</v>
-      </c>
-      <c r="F525" s="3" t="s">
-        <v>1006</v>
       </c>
       <c r="G525" s="9">
         <v>46432.0</v>
@@ -15916,7 +15911,7 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>33</v>
@@ -15928,10 +15923,10 @@
         <v>2.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F526" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G526" s="9">
         <v>46877.0</v>
@@ -15939,7 +15934,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>33</v>
@@ -15951,7 +15946,7 @@
         <v>2.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>446</v>
@@ -15962,7 +15957,7 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>33</v>
@@ -15974,16 +15969,16 @@
         <v>2.0</v>
       </c>
       <c r="E528" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F528" s="3" t="s">
         <v>1012</v>
-      </c>
-      <c r="F528" s="3" t="s">
-        <v>1013</v>
       </c>
       <c r="G528" s="9"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>33</v>
@@ -15995,15 +15990,15 @@
         <v>2.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>33</v>
@@ -16015,15 +16010,15 @@
         <v>2.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>33</v>
@@ -16035,15 +16030,15 @@
         <v>2.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F531" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>33</v>
@@ -16055,15 +16050,15 @@
         <v>2.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F532" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>33</v>
@@ -16075,10 +16070,10 @@
         <v>2.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F533" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G533" s="9">
         <v>46766.0</v>
@@ -16086,10 +16081,10 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C534" s="2" t="s">
         <v>26</v>
@@ -16098,10 +16093,10 @@
         <v>14.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F534" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G534" s="9">
         <v>46641.0</v>
@@ -16109,10 +16104,10 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C535" s="2" t="s">
         <v>12</v>
@@ -16121,10 +16116,10 @@
         <v>11.0</v>
       </c>
       <c r="E535" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F535" s="3" t="s">
         <v>1025</v>
-      </c>
-      <c r="F535" s="3" t="s">
-        <v>1026</v>
       </c>
       <c r="G535" s="9">
         <v>46743.0</v>
@@ -16133,10 +16128,10 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C536" s="2" t="s">
         <v>12</v>
@@ -16145,17 +16140,17 @@
         <v>15.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F536" s="4"/>
       <c r="H536" s="2"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>12</v>
@@ -16164,10 +16159,10 @@
         <v>21.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="G537" s="9">
         <v>46663.0</v>
@@ -16178,10 +16173,10 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C538" s="2" t="s">
         <v>12</v>
@@ -16190,10 +16185,10 @@
         <v>11.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F538" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G538" s="9">
         <v>46530.0</v>
@@ -16201,10 +16196,10 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C539" s="2" t="s">
         <v>12</v>
@@ -16213,10 +16208,10 @@
         <v>11.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G539" s="9">
         <v>46530.0</v>
@@ -16224,10 +16219,10 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C540" s="2" t="s">
         <v>26</v>
@@ -16236,10 +16231,10 @@
         <v>14.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G540" s="9">
         <v>46481.0</v>
@@ -16247,10 +16242,10 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>28</v>
@@ -16259,10 +16254,10 @@
         <v>13.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G541" s="9">
         <v>46877.0</v>
@@ -16270,10 +16265,10 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C542" s="2" t="s">
         <v>26</v>
@@ -16282,10 +16277,10 @@
         <v>13.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G542" s="9">
         <v>46481.0</v>
@@ -16293,10 +16288,10 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C543" s="2" t="s">
         <v>28</v>
@@ -16305,10 +16300,10 @@
         <v>13.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G543" s="9">
         <v>46877.0</v>
@@ -16316,10 +16311,10 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C544" s="2" t="s">
         <v>12</v>
@@ -16328,10 +16323,10 @@
         <v>12.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G544" s="9">
         <v>46641.0</v>
@@ -16339,7 +16334,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>519</v>
@@ -16351,10 +16346,10 @@
         <v>17.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F545" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G545" s="9">
         <v>46274.0</v>
@@ -16362,7 +16357,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>519</v>
@@ -16374,10 +16369,10 @@
         <v>17.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G546" s="9">
         <v>46274.0</v>
@@ -16385,10 +16380,10 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>28</v>
@@ -16397,10 +16392,10 @@
         <v>19.0</v>
       </c>
       <c r="E547" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F547" s="3" t="s">
         <v>1048</v>
-      </c>
-      <c r="F547" s="3" t="s">
-        <v>1049</v>
       </c>
       <c r="G547" s="9">
         <v>46516.0</v>
@@ -16408,10 +16403,10 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>28</v>
@@ -16420,20 +16415,20 @@
         <v>22.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F548" s="3"/>
       <c r="G548" s="9"/>
       <c r="H548" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>26</v>
@@ -16442,7 +16437,7 @@
         <v>6.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F549" s="3"/>
       <c r="G549" s="9"/>
@@ -16450,7 +16445,7 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>33</v>
@@ -16462,7 +16457,7 @@
         <v>3.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F550" s="3" t="s">
         <v>409</v>
@@ -16472,10 +16467,10 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>12</v>
@@ -16484,7 +16479,7 @@
         <v>4.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F551" s="3" t="s">
         <v>17</v>
@@ -16496,10 +16491,10 @@
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>12</v>
@@ -16508,10 +16503,10 @@
         <v>21.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G552" s="9">
         <v>46337.0</v>
@@ -16520,7 +16515,7 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>519</v>
@@ -16532,10 +16527,10 @@
         <v>8.0</v>
       </c>
       <c r="E553" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F553" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="F553" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="G553" s="9">
         <v>46269.0</v>
@@ -16544,7 +16539,7 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>519</v>
@@ -16556,10 +16551,10 @@
         <v>8.0</v>
       </c>
       <c r="E554" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F554" s="3" t="s">
         <v>1063</v>
-      </c>
-      <c r="F554" s="3" t="s">
-        <v>1064</v>
       </c>
       <c r="G554" s="9">
         <v>46290.0</v>
@@ -16568,7 +16563,7 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>519</v>
@@ -16580,7 +16575,7 @@
         <v>8.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F555" s="3"/>
       <c r="G555" s="9"/>
@@ -16588,7 +16583,7 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>519</v>
@@ -16600,10 +16595,10 @@
         <v>8.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G556" s="9">
         <v>46290.0</v>
@@ -16612,7 +16607,7 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>33</v>
@@ -16624,10 +16619,10 @@
         <v>12.0</v>
       </c>
       <c r="E557" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F557" s="3" t="s">
         <v>1070</v>
-      </c>
-      <c r="F557" s="3" t="s">
-        <v>1071</v>
       </c>
       <c r="G557" s="9">
         <v>46883.0</v>
@@ -16636,7 +16631,7 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>33</v>
@@ -16648,7 +16643,7 @@
         <v>12.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F558" s="3" t="s">
         <v>389</v>
@@ -16660,10 +16655,10 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>26</v>
@@ -16672,7 +16667,7 @@
         <v>5.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F559" s="3">
         <v>11506.0</v>
@@ -16682,10 +16677,10 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C560" s="2" t="s">
         <v>28</v>
@@ -16694,7 +16689,7 @@
         <v>10.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F560" s="3">
         <v>11504.0</v>
@@ -16704,10 +16699,10 @@
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C561" s="2" t="s">
         <v>28</v>
@@ -16716,7 +16711,7 @@
         <v>9.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F561" s="3">
         <v>11504.0</v>
@@ -16726,22 +16721,22 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D562" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E562" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F562" s="3" t="s">
         <v>1079</v>
-      </c>
-      <c r="B562" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C562" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D562" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E562" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F562" s="3">
-        <v>11504.0</v>
       </c>
       <c r="G562" s="9"/>
       <c r="H562" s="2"/>
@@ -16751,21 +16746,21 @@
         <v>1080</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D563" s="2">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F563" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="G563" s="9"/>
+      <c r="F563" s="3"/>
+      <c r="G563" s="9">
+        <v>46820.0</v>
+      </c>
       <c r="H563" s="2"/>
     </row>
     <row r="564">
@@ -16773,7 +16768,7 @@
         <v>1082</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>28</v>
@@ -16784,33 +16779,35 @@
       <c r="E564" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="F564" s="3"/>
+      <c r="F564" s="3" t="s">
+        <v>1084</v>
+      </c>
       <c r="G564" s="9">
-        <v>46820.0</v>
+        <v>46641.0</v>
       </c>
       <c r="H564" s="2"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D565" s="2">
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F565" s="3" t="s">
         <v>1086</v>
       </c>
-      <c r="G565" s="9">
-        <v>46641.0</v>
+      <c r="F565" s="3">
+        <v>11506.0</v>
+      </c>
+      <c r="G565" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="H565" s="2"/>
     </row>
@@ -16843,34 +16840,34 @@
         <v>1089</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C567" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D567" s="2">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F567" s="3">
-        <v>11506.0</v>
-      </c>
-      <c r="G567" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="F567" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G567" s="9">
+        <v>47531.0</v>
       </c>
       <c r="H567" s="2"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D568" s="2">
         <v>1.0</v>
@@ -16888,16 +16885,16 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D569" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E569" s="2" t="s">
         <v>21</v>
@@ -16912,25 +16909,25 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D570" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E570" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="F570" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="B570" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C570" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D570" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E570" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F570" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="G570" s="9">
-        <v>47531.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H570" s="2"/>
     </row>
@@ -16948,19 +16945,19 @@
         <v>10.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>610</v>
+        <v>1095</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G571" s="9">
-        <v>46217.0</v>
+        <v>46223.0</v>
       </c>
       <c r="H571" s="2"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>519</v>
@@ -16972,13 +16969,13 @@
         <v>10.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G572" s="9">
-        <v>46223.0</v>
+        <v>46221.0</v>
       </c>
       <c r="H572" s="2"/>
     </row>
@@ -16996,81 +16993,81 @@
         <v>10.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1100</v>
+        <v>607</v>
       </c>
       <c r="F573" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G573" s="9">
-        <v>46221.0</v>
+        <v>46214.0</v>
       </c>
       <c r="H573" s="2"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>519</v>
+        <v>56</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D574" s="2">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F574" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G574" s="9">
-        <v>46214.0</v>
-      </c>
+        <v>1077</v>
+      </c>
+      <c r="F574" s="3"/>
+      <c r="G574" s="9"/>
       <c r="H574" s="2"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D575" s="2">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F575" s="3"/>
-      <c r="G575" s="9"/>
+        <v>859</v>
+      </c>
+      <c r="F575" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G575" s="9">
+        <v>46636.0</v>
+      </c>
       <c r="H575" s="2"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D576" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="E576" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F576" s="3" t="s">
         <v>1103</v>
       </c>
-      <c r="B576" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C576" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D576" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E576" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="F576" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="G576" s="9">
-        <v>46636.0</v>
+        <v>46814.0</v>
       </c>
       <c r="H576" s="2"/>
     </row>
@@ -17079,19 +17076,19 @@
         <v>1104</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D577" s="2">
-        <v>21.0</v>
+        <v>5.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F577" s="3" t="s">
         <v>1105</v>
+      </c>
+      <c r="F577" s="3">
+        <v>11505.0</v>
       </c>
       <c r="G577" s="9">
         <v>46814.0</v>
@@ -17103,23 +17100,21 @@
         <v>1106</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D578" s="2">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="E578" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="F578" s="3">
-        <v>11505.0</v>
-      </c>
-      <c r="G578" s="9">
-        <v>46814.0</v>
-      </c>
+      <c r="F578" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G578" s="9"/>
       <c r="H578" s="2"/>
     </row>
     <row r="579">
@@ -17127,7 +17122,7 @@
         <v>1108</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C579" s="2" t="s">
         <v>28</v>
@@ -17136,34 +17131,36 @@
         <v>15.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1109</v>
+        <v>661</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>478</v>
+        <v>1079</v>
       </c>
       <c r="G579" s="9"/>
       <c r="H579" s="2"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D580" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E580" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B580" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C580" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D580" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E580" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="F580" s="3" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G580" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="G580" s="9">
+        <v>46436.0</v>
+      </c>
       <c r="H580" s="2"/>
     </row>
     <row r="581">
@@ -17171,69 +17168,69 @@
         <v>1111</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="C581" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D581" s="2">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>1112</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>17</v>
+        <v>1113</v>
       </c>
       <c r="G581" s="9">
-        <v>46436.0</v>
-      </c>
-      <c r="H581" s="2"/>
+        <v>46871.0</v>
+      </c>
+      <c r="H581" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C582" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D582" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F582" s="3" t="s">
         <v>1115</v>
       </c>
-      <c r="G582" s="9">
-        <v>46871.0</v>
-      </c>
-      <c r="H582" s="2" t="s">
-        <v>202</v>
-      </c>
+      <c r="F582" s="3"/>
+      <c r="G582" s="9"/>
+      <c r="H582" s="2"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
         <v>1116</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D583" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="F583" s="3"/>
-      <c r="G583" s="9"/>
+      <c r="F583" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="G583" s="9">
+        <v>46767.0</v>
+      </c>
       <c r="H583" s="2"/>
     </row>
     <row r="584">
@@ -17241,22 +17238,22 @@
         <v>1118</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>112</v>
+        <v>519</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D584" s="2">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>1119</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>409</v>
+        <v>986</v>
       </c>
       <c r="G584" s="9">
-        <v>46767.0</v>
+        <v>46261.0</v>
       </c>
       <c r="H584" s="2"/>
     </row>
@@ -17271,41 +17268,37 @@
         <v>12</v>
       </c>
       <c r="D585" s="2">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1121</v>
+        <v>779</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>987</v>
+        <v>604</v>
       </c>
       <c r="G585" s="9">
-        <v>46261.0</v>
+        <v>46205.0</v>
       </c>
       <c r="H585" s="2"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D586" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E586" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="B586" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C586" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D586" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E586" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="F586" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="G586" s="9">
-        <v>46205.0</v>
-      </c>
+      <c r="F586" s="3"/>
+      <c r="G586" s="9"/>
       <c r="H586" s="2"/>
     </row>
     <row r="587">
@@ -17319,7 +17312,7 @@
         <v>34</v>
       </c>
       <c r="D587" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>1124</v>
@@ -17339,10 +17332,10 @@
         <v>34</v>
       </c>
       <c r="D588" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1126</v>
+        <v>650</v>
       </c>
       <c r="F588" s="3"/>
       <c r="G588" s="9"/>
@@ -17350,22 +17343,26 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>11</v>
+        <v>521</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D589" s="2">
         <v>4.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F589" s="3"/>
-      <c r="G589" s="9"/>
+        <v>1127</v>
+      </c>
+      <c r="F589" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G589" s="9">
+        <v>46387.0</v>
+      </c>
       <c r="H589" s="2"/>
     </row>
     <row r="590">
@@ -17379,7 +17376,7 @@
         <v>12</v>
       </c>
       <c r="D590" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>1129</v>
@@ -17475,22 +17472,22 @@
         <v>12</v>
       </c>
       <c r="D594" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1137</v>
+        <v>828</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>38</v>
+        <v>971</v>
       </c>
       <c r="G594" s="9">
-        <v>46387.0</v>
+        <v>46217.0</v>
       </c>
       <c r="H594" s="2"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>521</v>
@@ -17502,10 +17499,10 @@
         <v>12.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>829</v>
+        <v>1115</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G595" s="9">
         <v>46217.0</v>
@@ -17514,7 +17511,7 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>521</v>
@@ -17523,22 +17520,22 @@
         <v>12</v>
       </c>
       <c r="D596" s="2">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1117</v>
+        <v>933</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>972</v>
+        <v>478</v>
       </c>
       <c r="G596" s="9">
-        <v>46217.0</v>
+        <v>46308.0</v>
       </c>
       <c r="H596" s="2"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>521</v>
@@ -17550,19 +17547,19 @@
         <v>10.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>934</v>
+        <v>908</v>
       </c>
       <c r="F597" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G597" s="9">
-        <v>46308.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H597" s="2"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>521</v>
@@ -17574,13 +17571,13 @@
         <v>10.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>909</v>
+        <v>1141</v>
       </c>
       <c r="F598" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G598" s="9">
-        <v>46521.0</v>
+        <v>46525.0</v>
       </c>
       <c r="H598" s="2"/>
     </row>
@@ -17598,19 +17595,19 @@
         <v>10.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1143</v>
+        <v>906</v>
       </c>
       <c r="F599" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G599" s="9">
-        <v>46525.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H599" s="2"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>521</v>
@@ -17622,7 +17619,7 @@
         <v>10.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>478</v>
@@ -17634,7 +17631,7 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>521</v>
@@ -17646,19 +17643,19 @@
         <v>10.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="F601" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G601" s="9">
-        <v>46521.0</v>
+        <v>46527.0</v>
       </c>
       <c r="H601" s="2"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>521</v>
@@ -17670,13 +17667,13 @@
         <v>10.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>905</v>
+        <v>1146</v>
       </c>
       <c r="F602" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G602" s="9">
-        <v>46527.0</v>
+        <v>46356.0</v>
       </c>
       <c r="H602" s="2"/>
     </row>
@@ -17700,7 +17697,7 @@
         <v>478</v>
       </c>
       <c r="G603" s="9">
-        <v>46356.0</v>
+        <v>46366.0</v>
       </c>
       <c r="H603" s="2"/>
     </row>
@@ -17724,7 +17721,7 @@
         <v>478</v>
       </c>
       <c r="G604" s="9">
-        <v>46366.0</v>
+        <v>46336.0</v>
       </c>
       <c r="H604" s="2"/>
     </row>
@@ -17739,22 +17736,22 @@
         <v>12</v>
       </c>
       <c r="D605" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1152</v>
+        <v>927</v>
       </c>
       <c r="F605" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G605" s="9">
-        <v>46336.0</v>
+        <v>46310.0</v>
       </c>
       <c r="H605" s="2"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>521</v>
@@ -17766,19 +17763,19 @@
         <v>11.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>928</v>
+        <v>913</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G606" s="9">
-        <v>46310.0</v>
+        <v>46354.0</v>
       </c>
       <c r="H606" s="2"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>521</v>
@@ -17790,13 +17787,13 @@
         <v>11.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>914</v>
+        <v>1154</v>
       </c>
       <c r="F607" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G607" s="9">
-        <v>46354.0</v>
+        <v>46360.0</v>
       </c>
       <c r="H607" s="2"/>
     </row>
@@ -17814,19 +17811,19 @@
         <v>11.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1156</v>
+        <v>929</v>
       </c>
       <c r="F608" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G608" s="9">
-        <v>46360.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>521</v>
@@ -17838,19 +17835,19 @@
         <v>11.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="F609" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G609" s="9">
-        <v>46333.0</v>
+        <v>46346.0</v>
       </c>
       <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>521</v>
@@ -17862,19 +17859,19 @@
         <v>11.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="F610" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G610" s="9">
-        <v>46346.0</v>
+        <v>46342.0</v>
       </c>
       <c r="H610" s="2"/>
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>521</v>
@@ -17886,13 +17883,13 @@
         <v>11.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>924</v>
+        <v>1159</v>
       </c>
       <c r="F611" s="3" t="s">
         <v>478</v>
       </c>
       <c r="G611" s="9">
-        <v>46342.0</v>
+        <v>46343.0</v>
       </c>
       <c r="H611" s="2"/>
     </row>
@@ -17901,28 +17898,28 @@
         <v>1160</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D612" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1161</v>
+        <v>626</v>
       </c>
       <c r="F612" s="3" t="s">
-        <v>478</v>
+        <v>977</v>
       </c>
       <c r="G612" s="9">
-        <v>46343.0</v>
+        <v>46228.0</v>
       </c>
       <c r="H612" s="2"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>519</v>
@@ -17931,22 +17928,22 @@
         <v>12</v>
       </c>
       <c r="D613" s="2">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>627</v>
+        <v>556</v>
       </c>
       <c r="F613" s="3" t="s">
-        <v>978</v>
+        <v>1063</v>
       </c>
       <c r="G613" s="9">
-        <v>46228.0</v>
+        <v>46290.0</v>
       </c>
       <c r="H613" s="2"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>519</v>
@@ -17958,10 +17955,10 @@
         <v>7.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>557</v>
+        <v>791</v>
       </c>
       <c r="F614" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G614" s="9">
         <v>46290.0</v>
@@ -17970,7 +17967,7 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>519</v>
@@ -17982,10 +17979,10 @@
         <v>7.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>792</v>
+        <v>561</v>
       </c>
       <c r="F615" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G615" s="9">
         <v>46290.0</v>
@@ -17994,7 +17991,7 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>519</v>
@@ -18003,22 +18000,20 @@
         <v>12</v>
       </c>
       <c r="D616" s="2">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>562</v>
+        <v>857</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G616" s="9">
-        <v>46290.0</v>
-      </c>
+        <v>986</v>
+      </c>
+      <c r="G616" s="9"/>
       <c r="H616" s="2"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>519</v>
@@ -18027,13 +18022,13 @@
         <v>12</v>
       </c>
       <c r="D617" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="F617" s="3" t="s">
-        <v>987</v>
+        <v>1166</v>
+      </c>
+      <c r="F617" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G617" s="9"/>
       <c r="H617" s="2"/>
@@ -18049,10 +18044,10 @@
         <v>12</v>
       </c>
       <c r="D618" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>1168</v>
+        <v>1027</v>
       </c>
       <c r="F618" s="3">
         <v>11506.0</v>
@@ -18062,19 +18057,19 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D619" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E619" s="2" t="s">
         <v>1169</v>
-      </c>
-      <c r="B619" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="C619" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D619" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E619" s="2" t="s">
-        <v>1028</v>
       <